--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -1,41 +1,506 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s00954045\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88519437-6611-432A-81C3-BF4A87873F33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="竞品对比" sheetId="1" r:id="rId1"/>
-    <sheet name="指标统计" sheetId="7" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标统计" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
-  <si>
-    <t>准确性</t>
-  </si>
-  <si>
-    <t>相关性</t>
-  </si>
-  <si>
-    <t>通顺性</t>
-  </si>
-  <si>
-    <t>其它问题</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:21
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;秒&quot;"/>
+  </numFmts>
+  <fonts count="5">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="0"/>
+  <cols>
+    <col width="55.375" customWidth="1" style="5" min="1" max="1"/>
+    <col width="56.125" customWidth="1" style="5" min="2" max="2"/>
+    <col width="9" customWidth="1" style="5" min="3" max="3"/>
+    <col width="9" customWidth="1" style="4" min="4" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13.5" customHeight="1" s="9">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>纪要</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>消耗时间</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>文本长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1" s="9">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:21
 最近呢霍伊斯根主席各位朋友，各位同事，我们所处的是一个更加变乱交织的世界。大家都关心这个世界今后向何处去。借用今年慕安会报告的主题来回答的话，那就是走向多极化。80年前联合国成立时，只有51个会员国，到今天是193个国家，共乘一艘大船。多极化的世界既是历史的必然，也正在成为现实。多极化是否会带来动荡失序，冲突对抗是否意味着大国主导弱肉强食。中国给出的答案是我们应当推动平等有序的世界多极化。这是习近平主席提出的又一个重大主张，也是我们对多极世界真诚的期许。中国必将是多极体系中的确定性因素。将坚定做变革世界中的建设性力量。在此我表达4点看法。一是应当倡导平等相待，列强争霸曾给人类带来灾难。两次世界大战殷鉴不远，殖民体系也罢，
 • 发言者 1 01:58
 中心外围体系也罢，不平等的秩序注定土崩瓦解。世界各国独立自主，风起云涌，国际关系民主法不可阻挡。坚持权利平等机会平等规则平等，应当成为建设多极世界的基本原则。正是秉+D5持这样的原则，中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。这不会导致西方的缺失，而将促进世界的正和慕安会近年来邀请更多全球南方国家出席会议，这是明智之举。每一个国家的声音都应该得到倾听。每一个国家都可以在多极格局中找到自身的位置，发挥自己的作用。二是应当尊重国际法治。中国有句古话没有规矩不成方圆，
@@ -93,9 +558,40 @@
 and IT would be very good that what you are,what you are also proposing. More talks and discussion on these issues withmaterialS here in munich. I wish you again. Good luck to you on your trip to new york and thank you for being such a goodguest here to the munich security conference.
 • 发言者 2 25:12
 Thank you for this all the best. .</t>
-  </si>
-  <si>
-    <t>• 发言者 1 01:35
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>新闻发布</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t># 发布会概况
+王毅在慕尼黑安全会议上发表讲话，围绕多极化世界、国际秩序及热点问题阐述中方立场，提出四点主张：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，多极化是历史必然并正在成为现实，中国主张推动平等有序的世界多极化，中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。王毅还就中欧关系表示，欧洲是多极世界的重要一极，中欧是伙伴而不是对手，今年是中欧建交50周年，中方愿同欧方用好这一契机，深化战略沟通和互利合作。在回答提问时，王毅就联合国与国际秩序规则、乌克兰问题、中美关系分别作出回应。
+# 核心信息
+王毅提出四点主张：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，强调联合国宪章宗旨和原则是国际关系根本遵循，国家不论大小强弱都是国际法治利益攸关方，大国要带头讲诚信讲法治，摒弃言行不一、零和博弈，遵守国际法不能搞双重标准，应支持中国实现完全统一；三是践行多边主义，表示联合国是践行多边主义、推进全球治理的核心平台，应固本强基而非拆梁毁柱，中国承担超过**20%**的联合国会费，履行`巴黎协定`，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，指出保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己，应坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化。关键数据：去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**；中国加入了几乎所有普遍性的政府间国际组织和**600多项**国际公约；联合国成立时只有**51个**会员国，今天是**193个**国家。中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接。
+# 官方表态
+关于多极化：王毅表示，多极化的世界既是历史的必然，也正在成为现实，中国给出的答案是应当推动平等有序的世界多极化，这是习近平主席提出的又一个重大主张。关于国际法治：王毅表示，联合国宪章宗旨和原则是处于国际关系的根本遵循，也是建设多极世界的重要基石，国家不论大小强弱都是国际法治的利益攸关方，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈，在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。关于多边主义：王毅表示，联合国是践行多边主义、推进全球治理的核心平台，对于这座大厦应该固本强基，而不是拆梁毁柱，中国坚持真正的多边主义，倡导共商共建共享的全球治理观。关于开放共赢：王毅表示，保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。关于中欧关系：王毅表示，中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手，今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。关于联合国与国际秩序规则：王毅表示，中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展，需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。关于乌克兰问题：王毅表示，中国同俄罗斯是两大邻国，有着漫长的边界，两国建立了结盟不对抗、不针对第三方的睦邻友好关系，进而建立了全面战略伙伴关系，中国同俄罗斯之间的交往是正常的国与国之间的交往；中国历来主张一切争端和冲突都应该通过对话寻求政治解决，乌克兰问题上同样如此，从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释，任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识，所有当事方包括利益攸关方都应该适时的参与到和谈的进程当中，欧洲更有必要为此发挥重要的作用。关于中美关系：王毅表示，中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢，中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底。
+# Q&amp;A环节
+问（发言者2）：你提到国际秩序，也提到需要尊重联合国宪章，现在有很多质疑，我们看到俄罗斯入侵乌克兰，我们看到美国总统威胁使用武力入侵格陵兰和巴拿马，以及巴勒斯坦人流离失所，你的国家也被指控违反海洋法或世界人权宣言。你现在从这里前往纽约参加安理会，你是否继续相信联合国？你是否相信联合国宪章？你是否也会为联合国改革而努力？联合国宪章在你的优先事项中排多高？ → 答（王毅）：说到秩序，这几年总有人说中国要改变秩序，中国要另起炉灶，但现在再说这种话的人可能不会太多了，因为真正要挑战秩序、在毁约退群的国家出现了；中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展。谈到规则，我们需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则，这应该是我们的最大的公约数。
+问（发言者2）：自2022年以来慕安会的一个话题就是俄罗斯入侵乌克兰，在俄罗斯入侵前几天你曾说过主权、独立和领土完整应该得到尊重和保障，乌克兰也不例外，你确认了联合国宪章。今天俄罗斯已成为中国的加油站，这意味着你对乌克兰有很大影响力。你是否看到现在有更多压力来结束这场战争，你能否减少俄罗斯向你国供应天然气的可能性或降低价格，或停止一些双用途物资，以便对俄罗斯施加更多压力来结束这场战争？ → 答（王毅）：中国同俄罗斯是两大邻国，有着漫长的边界，两国关系过去经历过一番曲折的经历，之后我们双方吸取教训，建立了结盟不对抗、不针对第三方的睦邻友好关系，进而增进了战略互信，建立了全面战略伙伴关系。中国同俄罗斯之间的交往是正常的国与国之间的交往。如果中国不从俄罗斯买油气，哪个国家能够提供如此巨量的油气来满足中国民众的需求呢？那是不可能的，也是不保险的。中国在对待地区热点问题上是有我们的立场的，我们历来主张一切争端和冲突都应该通过对话寻求政治解决，因为武力和制裁不可能真正和彻底的解决问题，乌克兰问题上同样如此。从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决。习近平主席提出的4点主张是中国立场的最权威的阐释。我们派出的特使去各国斡旋，我们同巴西等南方国家发起了和平之友。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识。所有当事方包括利益攸关方，都应该适时的参与到这个和谈的进程当中。这场战事发生在欧洲大地上，欧洲更有必要为此发挥重要的作用。
+问（发言者2）：我们时间不多了，但至少请你简要预览一下你认为我们和中国之间的关系将如何发展？ → 答（王毅）：中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，这体现了作为大国的战略定力和国际信誉。我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢。中国和美国制度确实不一样，这是我们各自人民做出的选择，如果想改造或者颠覆对方的话，那是不切实际的，正确的态度就是相互尊重。中美两个大国总不能冲突起来吧，因为那将殃及整个世界，所以还是要开展对话，加强交往，增进了解，建立信任。合作共赢，这是因为国际社会期待中美开展合作，全球性的挑战也需要中美携手来应对。中方已经准备好了，我们愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。我们当然希望美方能够相向而行，但是如果美方不愿意，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，我们必将坚定的维护中国的主权、中国的国家的尊严和我们的正当发展权利，必将坚决的回击美方的单边和霸凌的这种行径。</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>7004/3331</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" s="9">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 01:35
 好的，同学们欢迎回来。我们刚刚说了一点小小的插曲，但是没有关系，我们在接下来的时间里面呢，把时间交给咱们的电子科学与工程学院的三位老师，来给大家介绍一下我们学院的一个整体的情况。好。
 • 发言者 2 01:54
 同学们家长们上午好。首先我给大家汇报一下电子学院的学院历史情况。在电子科技大学建校之初，1956年就成立了无线电系，电真空器件系无线电零件系，1979年1992年2001年2018年，经过4次的院系调整，成立了电子科学与工程学院，科普示范性微电子学院。2023年响应国家新的号召，成立了电子科学与工程学院与基层电路学院。电子科学与与技术是电子学院的一级学科，它属于国家重点一级学科。它下面有5个二级学科方向，第1个是电磁场与微波技术，第二是电路与系统，第三是微电子学与固体电子学，第四是物理电子学。
@@ -245,9 +741,49 @@
 好，同学们后会有期了，再见。
 • 发言者 2 53:06
 好再见。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:01
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>沟通交流会</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t># 沟通背景与目的
+本次沟通为电子科学与工程学院面向考生和家长的直播介绍会，由三位老师及学生代表分别介绍学院整体情况与各研究方向，并解答夏令营相关问题。段院介绍学院历史沿革、学科布局、师生规模、科研经费与平台情况；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术和电路与系统方向；李天明教授介绍物理电子学方向；2023级博士研究生田雨桐从学生视角分享择校理由与建议。互动答疑环节，段院回复今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。
+# 信息同步
+**段院（学院整体情况）**：介绍学院历史沿革，1956年建校成立无线电系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科；本科生1545人，招生专业为工科试验班电子工程类，含电子科学技术、电磁场与无线技术；硕士博士研究生1975人；教师302人，教师总数269人，两院院士2人、领军人才19人、青年人才28人；近5年科研到账经费稳定在3~4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利授权1300余件；20个科研团队，年度经费过千万团队15个、过亿元团队1个；拥有2个国家级平台、4个国际合作平台、7个省部级科研平台，共建国际姊妹院系2个，主办高水平国际会议13场。
+**柳教授（电子信息材料与元器件方向）**：该方向以材料为基础、器件为核心、应用为目标导向，2021年中国集成电路电子产品进口额度达2.8万元（原文），为原有进口量1.7倍，属卡脖子问题之一，应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域；研究队伍含国家级人才10余人，两个团队——邓龙江院士电磁辐射控制材料与技术团队（研究人员19人，正高13、副高15，论文300余篇，课题130余项，年均到账经费3000多万元，授权发明专利100余项，国家科技进步或技术发明二等奖共3项）和张怀武教授磁电薄膜与微型器件团队（研究人员17人，正高15、副高2，课题100余项，科技进步二等奖共3项，SCI论文400余篇，年均到账经费2000余万元）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室；科研面积2万余平米，超精尖3000平，两条国家重大任务试验生产线，大型设备500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
+**张教授（电磁场与微波技术和电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，始于1956年由林卫干先生和谢楚芳先生创建，有6个团队，拥有中国高校最先进的微波暗室群体及微波毫米波太Hz仿真测试平台；研究成果包括杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵应用于中电14所某大型机载相控阵雷达，樊勇教授团队毫米波平面集成天线、太Hz雷达成像系统（0.22太Hz、0.34太Hz、0.42太Hz，分辨率小于1厘米）并于2023年成都大运会田径项目示范应用，李恩教授团队微波毫米波测量技术、生物医学电磁学及成像，延波教授团队微波毫米波太Hz芯片、三毫米导引头前端等；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，81年招收研究生，88年成立首批博士后流动站，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人，康凯教授团队毫米波CMOS芯片，连续三年获全国大学生集成电路创新创业大赛奖项。
+**李天明教授（物理电子学方向）**：该学科为物理学与电子科学技术交叉学科，典型如微波电子学、光电子学，特点为基础性与前沿性、学科边界不清晰；学校物理电子学起源于1956年建校时前苏联专家帮助下成立的电子控器件专业，1979年刘成刚院士带领下成立高能电子学研究所，2018年成立电子科学与工程学院；经过近70年发展，纵向向上游仿真设计数字模拟材料、下游系统应用发展，横向向毫米波到太赫兹频段及与医学交叉发展；拥有自主知识产权商用软件MMST和切皮克；团队共9个；每年到校科研经费接近2亿元，为学院最多；是世界上最大的真空器件研究中心；2023年成功举办行业内顶级会议；学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。
+**学生代表田雨桐（择校分享）**：2023级电子科学与技术专业博士研究生，分享选择电子学院的8个理由：城市成都（新一线城市、电子信息产业前端，英特尔华为京东方等汇聚）；电子科大为电子信息人才培育代名词；电子科学与技术学科第四轮学科评估A+全国第一；研究团队实力（所在毫米波技术与系统应用团队由樊勇老师带领，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向，团队硕博毕业生百分百就业率）；奖助体系全覆盖高额度长周期；建议先选研究团队再选导师，借助文献检索网站了解导师。
+**互动答疑**：有考生和家长询问夏令营具体时间和形式，段院回复今年计划举办夏令营活动，时间待定，感兴趣的同学可加入QQ群（群号978499108），相关信息会及时发布；直播尾声进行抽奖，口令为“一生一世，逐梦未来”，奖品为学校马克杯套装。
+# 达成共识
+各方确认的信息：段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍各研究方向，学生代表田雨桐分享择校理由与建议。
+达成的共识：**今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。**
+段院原话：
+&gt; 我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会唉到时会及时的发布。
+# 待协调事项
+事项：夏令营具体时间和形式尚未确定，需后续明确并发布。
+对接人：未明确
+负责人：段院
+预计完成时间：待定，相关信息通过QQ群（978499108）及时发布。</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>13887/2555</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="9">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:01
 然后我再说一下我们这个议程，就是我会说个几分钟，就是我们这一年的一些发展状况，就主要是一些数据，就是你比如说营业额开票额，包括年终奖的总额，我们今年也公布一下，但是个人上我们就决定就不一一的公布了，这个我们也和大家去聊，包括我也和一些朋友去参考了一些东西。然后然后我反正我总结完之后呢，我们我会给就是每一个我因为我们现在也分了短视频，商务商务没有坐在一起，商务还有我们的无论你叫文案也好拍，摄也好，拍摄都算执行吧，
 • 发言者 1 00:43
 几个部门每个部门进行一个简单的一个评价，然后评价完之后我们就从这边开始好了，艺人就每个人都会就是说两句评价，但是一般都是肯定性的，有个问题性的，我们明年再说和去年大家应该也比较熟悉，我们就你可以理解为夸两句我们发个红包。然后我们评价完之后，然后那个就个人完评价完之后，我们就是在发这个就是我评价你的时候，你也可以逼几句就说几句，也可以没有台词，这个无所谓，如果但是说实话，人家有些公司特别是机构组织架构大的数值是非常重要的一个环节。
@@ -767,9 +1303,38 @@
 nice准备321起。
 • 发言者 1 01:18:10
 好勒。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:10
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>总结复盘会</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t># 复盘目标与结果概况
+本次复盘会围绕2023年公司发展数据、年终奖发放标准、各部门与个人评价及颁奖抽奖展开。预期目标是通报全年经营状况并明确年终奖发放口径，实际结果是年终奖转账总额226,000元，人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27；最高工资含年终奖两三人拿到手20万多，平均到手1万多；2023年平均人工支出相对提高，平时工资提高约25万，年终奖比去年多1312万多；干满一年从去年四五人到今年12人；公司总量提升但成本往上跑，结余到账往下跑，还有百来万没收回来；老板每人比去年少拿约10万，承担亏100万风险。老板称成本控制非常差，是最大的癌症、根源问题，归因于老板关心关注不够、不够雷厉风行、出现问题没及时解决，成本控制问题明年开会时再说。年终奖发放标准为：入职两三个月或半年以内发红包，去年600、800，今年可能1000左右；满一年以一个月基本工资为基准，无大披露无大问题会更高；超过一年不过多考虑年限，看当年表现；干得久又非常满意的有高预算，实际拿到可能两三万，预算可给大几万但需给理由。部门评价方面，对短视频部门整体满意并认可，明年期待账号开始变现；对执行部门表示认可，今年项目没做砸过；商务部门从结果看基本达到预期，整个部门拿到的活约300万左右。颁奖共6人5项奖，最佳新人奖颁给红叶子和张扬，最佳进步奖颁给欧阳小元，最佳员工奖颁给游腾宇，特别贡献奖颁给李海腾。
+# 亮点事项
+短视频账号运营超出预期：视频号从3月1日700多粉涨到8万，小红书2000加涨到6.4万，抖音2000加涨到5.7万，B站3.1万涨到7.6万，6月20日外出拍摄视频后起色；直播在视频号4、5场，平均在线5000人加，前100人平均在线50分钟以上。促成成功的关键动作是郭东辉在6月20日前潘老师多次提醒其出去找工作、项目不想干了的情况下坚持不放弃，并破釜沉舟说服潘老师到外面去拍摄，加上forty到来后继续坚持；其所有内容决策均有数据支撑，晚上8:00~9:00抽一小时刷侃哥、巧克力、克瑞斯金等英语老师直播间，研究内容与互动。**最具复用价值的经验是：面对项目可能被放弃时，先说服自己坚持，再以数据支撑内容决策，并找到破壳的点逐个击破。** 个人评价方面，刘腾宇职业性专业性纪律性最好，年终奖在既定标准上再拉一档，可能翻倍；张文倩表现高出老板期待，宁波等难活也完成了；宋俊逸第一次安排活即效率不错，监狱、财经等项目未出问题；张扬基本达到期待，老板认为2023年干到最有价值的一件事就是把他招进来；张启表现高于预期，有主观能动性，主动联系客户打电话。
+# 不足事项
+成本控制非常差 → 根因是老板关心关注不够、不够雷厉风行、出现问题没及时解决，是最大的癌症、根源问题；若今年没有增量、成本控制又是今年状况就不开这个会。公司结余到账往下跑，还有百来万没收回来，稍微缩水；老板每人比去年少拿约10万，承担亏100万风险。郭东辉克服本不应面对的困难，公司限制其发挥，应表示歉意；6月20日前潘老师多次提醒郭东辉出去找工作，项目不想干了；账号目前没有变现，直播现在没有课程无法变现；郭东辉一人负责多个平台，精力不充沛。张文倩在法院项目上与同学沟通吃力，对方踢皮球，不知道标准怎么做。钱德峰后半年拍摄密集，两个月连轴转没有一天休息。外援成本高，公司内部可搞定的简单机位却凑不出人。后期人员加班严重，后半年基本都在加班，很少正常休息；人不够是加班最大的因素，是老板判断失误。商务给活断断续续，造成不需要招这么多人的错觉。张启项目少，老板给的支持比较少；张启自评2023年没达到自己预期，效率、时间、项目沟通和甲方做得不太好。
+# 改进计划
+成本控制问题明年开会时再说，责任人无，时间明年开会。短视频部门明年期待账号开始变现，老板会投入更大精力，责任人老板，时间明年。执行部门明年期待老板更多组织协调、减少侵占休息时间，责任人老板，时间明年。商务部门明年会给予更多支持和帮助，责任人老板，时间明年。张扬的具体问题明年再说，责任人无，时间明年。李国宇的具体问题明年再说，责任人无，时间明年。徐艺玲更高的期待明年再说，责任人无，时间明年。年终奖具体数额不公布，以发到手的为准，责任人无，时间无。</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>24562/1759</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1" s="9">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:10
 装备了。调出来的时候我们生活
 • 发言者 2 00:17
 还让你上学或者不含不含那三个月工资。再加15%的就是15个群体。但是他那个比如是不是刚才说的就是流失额流转，所以去不上退的时候，快递他原来我们交的，那他不知从后边才来的，他都交费了。交费当时是什么呢？当时是我的公司管理工作。什么时候能达到10,200人，这块不能不太清楚其他的职业吧。能推进去。都可以。就退回去吧，我再推进点推，但是他出去他是上网的。从而选择一个地方可以。我们还有10多年的这个项目。
@@ -1295,9 +1860,37 @@
 你们再那个啥了。就是我和他
 • 发言者 2 01:03:16
 关系就是啥意思？</t>
-  </si>
-  <si>
-    <t>• 发言者 1 02:06
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议围绕小区物业服务缺失、业主大会召开与业委会成立、物业费欠费及双方拟走法律程序等矛盾进行协调。业主方称已有200来户业主接龙要求召开业主大会，业委会工作组有6个群、准业主分5个群，最早业主群已建5、6年，建议尽快召开业主大会由全体业主表决；物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主代表列举11项服务缺失问题，包括入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏且上个月进贼未获数据、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重、北边围墙用烂铁皮挡着且有缺口不安全、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员从办公室近10人减至4人、维修从5人减至2人。物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。
+## 业主大会召开与业委会成立
+- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早业主群已建5、6年。业主方建议尽快召开业主大会由全体业主表决，物业方称未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
+- 业主代表列举11项服务缺失问题：入户庭院门柱灯从未开启；内部水系从未开启；售楼处门口迎宾水系从未开启；监控几乎全部损坏，上个月进贼未获数据；监控室24小时值班及一键直达服务自王艳芳上任后荒废；绿化死亡严重，物业管家称等明年发芽；北边围墙用烂铁皮挡着，有缺口不安全，物业承诺定制围挡未兑现；快递柜、直饮水机、宽带、暖气开户等民生附属问题无进展；雨水倒灌自2019年造成财产损失未解决；物业人员配备严重不足，办公室从近10人减至4人，维修从5人减至2人。
+## 物业方回应与经营困难
+- 物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题，属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>21511/1505</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1" s="9">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 02:06
 就是
 • 发言者 2 02:06
 都是一些比较基础的问题，因为我挑的这4个这个博士生，我自己代表这个多模态大模型和具身智能的这个融合这个方向。然后呢雄辉呢是这个于洋老师的博士生，他是这个强化学习做得非常厉害，然后呢薛寒博士呢是卢策武老师的博士生，然后呢他是在这个数据的这个收集以及这个柔性物体的操作方面非常的有心得，然后志龙呢也是于洋老师的博士生，他是在这个具身模型世界模型方面非常有建树，然后我非常期待志龙和这个赵昊老师能在这个世世界模型上能够有一些这个碰撞，就是其实是两个领域，因为志龙呢是从这个做强化学习那一套这个据世界模型来入手的。
@@ -1529,9 +2122,38 @@
 Exactly,然后被标准化以后，应该也对应该也没有什么大问题，最后技术上会是比较统一的，但是business上会是一个很加复杂的问题，因为他们赌的就是会脱钩会卡脖子嘛是吧？这就是另一个问题了。Ok好，我就大概简单说这么多。
 • 发言者 2 01:03:04
 好感，那感谢各位老师还有各位同学的这个精彩发言。然后看大家还有要补充的。要发言的吗？那那个没有的话，那感谢各位老师，然后那个那我们这次的那个圆桌论坛就结束了，也感谢各位听众来等一下。那各位老师我们合张影就是那个那感谢各位听众来。参加我们这个会议，相信今天这个我觉得今天整个从报告到这个圆桌论坛的质量，还是能匹配得上一个顶会的这个workshop的质量的，然后也希望大家能都值回票赞。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:10
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>工作研讨会</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t># 研讨背景与议题
+本次圆桌由主持人（多模态大模型与具身智能融合方向）主持，参与讨论的包括于洋老师的博士生雄辉（强化学习）、卢策吾老师的博士生薛寒（数据收集与柔性物体操作）、于洋老师的博士生志龙（具身模型与世界模型）以及赵浩、王岳等老师。研讨围绕具身智能的模型形态、硬件期待、世界模型定义、模仿与强化学习路线及数据scaling五个议题展开。核心痛点在于：具身智能究竟收敛为统一端到端模型还是分层形态、硬件如何支撑真机evaluation的scale up、世界模型是否需要3D inductive bias、模仿学习与强化学习如何取舍，以及真机数据与仿真数据如何配比。
+# 核心观点
+模型形态议题：主持人提出大脑大模型、小脑大模型、端到端模型等形态，并以派灵收集6000多小时数据训出端到端模型为例，询问是统一模型还是前段固定加Action refiner；王岳认为大模型直通底层会消除硬件迭代可能性，至少应分上下层，大脑不变、小脑适应肢体；发言者6认为当前大模型不是终极形态，世界模型可能更接近人脑水平，但也不是最终形态。硬件形态议题：发言者3从机械与传感器角度反问具身身体会收敛成人形还是非人形，并提到机械智能、软手抓取；薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up，现有工业机械臂并非为此设计，需要柔顺硬件结构；主持人认为具身是软硬件协同优化范式，以松龄二代和凝胶夹爪为例，认为协同进化；发言者6认为人形机器人和特种机器人将来都会存在，特斯拉花一半精力做22自由度灵巧手。世界模型议题：主持人介绍赵浩从computer vision角度评价世界模型，涉及是否需重构所有pixel和3D，并提到4D world model投稿；志龙从强化学习角度认为世界模型第一要素是可交互，回溯到Dyna Q和杨乐坤的表征与转移，当前世界模型物理规律欠缺明显；赵浩认为CV界追求重建物理世界动态，可作为RL世界模型的工具，但三维计算机视觉技术栈长，RL博士生难完全学习，并讨论inductive bias随数据规模变化；王岳以游戏跳楼例子认为世界模型可能做不到统一，policy可能是一个；发言者9提出不同物理结构可能有统一表征，讨论condition与M个模型复杂度。策略学习路线议题：主持人提出强化学习与模仿学习两大流派，派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈，语言模型有RLHF和o1思维链、MCTS；发言者10介绍公司采用模型强化加机理融合，监督学习动作空间大、数据分布不足，强化学习强依赖仿真环境、sim-to-real迁移难，需限定决策空间和任务分层；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化都不行；王岳认为pid有反馈就可作为reward，强化必然走得成；发言者11认为IL和RL没有本质冲突，只是想要一个latent状态。数据采集与scaling议题：主持人请杨立新和薛寒分享真机数据收集经验，赵浩和主持人代表仿真生成数据流派；杨立新强调视角控制和标定重要，open X等数据集相机视角不固定，且缺少物体运动信息，其团队采集刚体和关节体；薛寒all in真机采集，认为柔性体仿真需先进图形学技术如IPC、算力要求高、人才少，真机数据是更低成本方案，终极形态可能是脑机接口或可穿戴设备无感采集，互联网视频与机器人所需数据差异大；主持人提到ego4d数据清洗三个月，仿真数据加少量真机数据可显著提升成功率；赵浩认为真实还是仿真看成本，提出2025年应推广大规模利用无标注真实数据，国产仿真系统是产业问题。
+# 达成共识与解决方案
+研讨未形成正式决议，但各方在以下认知上趋于一致：**具身智能是软硬件协同优化的范式**，硬件需具备高寿命、高可靠性与柔顺结构以支撑真机evaluation的scale up；**模型形态至少应分上下层**，大脑保持稳定、小脑适应肢体与硬件变化，而非单一端到端直通底层；**世界模型与强化学习的关系上**，CV界重建物理世界动态的成果可作为RL世界模型的工具，但RL更关注可交互性与策略学习；**策略学习路线上**，复杂任务宜先模仿后强化，单独模仿或单独强化均难以覆盖，混合多种方式是目前较实际的解；**数据路线上**，真机数据与仿真数据并非相斥，仿真数据加少量真机数据可显著提升成功率，真实还是仿真应case by case看成本。
+# 未决分歧与后续探索
+未决分歧包括：具身智能最终会收敛成统一端到端模型，还是前段固定加Action refiner的分层形态；具身的身体会收敛成人形机器人还是非人形形态；世界模型是否需要3D inductive bias，还是由数据规模决定；世界模型最终是一个还是多个，policy是否可能统一；模仿学习和强化学习最终路线是单独一种还是混合；未来是否强依赖英伟达生态，还是会有国产仿真产品支持。后续探索方向包括：赵浩提出2025年应推广大规模利用无标注真实数据；薛寒提出可穿戴式设备或脑机接口作为无感采集的终极形态；主持人提出仿真数据与少量真机数据结合的训练方法；国产仿真系统作为产业问题需business by business讨论。</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>21458/2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1" s="9">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:10
 现在
 • 发言者 2 00:10
 公布法庭纪律在合议庭评判请诉讼各方参与人全体航行人员起立。你是对法庭的尊重。二诉讼各方参与人与全体旁听人服从法庭的指挥，尊重执法礼仪。遵守法庭纪律，不得实施下列一鼓掌喧哗。二吸烟禁食。三拨打或接听电话。四对庭审活动进行录音录像拍照或使用移动通信工具的传播途径活动。五其他危害。秩序的成为。三注重参与人发言或提问。应当经达成许可。是旁听人员不得进入审判活动区，不得随意站立走动，不得发言评论和记录。五在执行过程中，诉讼参与人或者旁听人员扰乱法庭秩序，情节较轻的，审判长可以口头警告制止训诫等。
@@ -2013,9 +2635,50 @@
 金融债权已得到充分保护。通过本案的审理，我们还发现本案设计的生产设备等动产抵押权与融资租赁物所有权的冲突，是司法实践中的普遍性的难题。金融风险防控还有较大的空间，其根本的原因是我们国家还未建立统一的动产登记制度，现有的动产融资租赁登记系统和动产抵押登记系统尚缺乏有效的衔接。未从根本上防范和解决此类矛盾纠纷。我们将根据最高人民法院关于加强司法建议工作的意见的规定，向有关部门提出司法建议。共同推进国家治理的现代化。
 • 发言者 3 01:48:18
 今天的庭审到此结束。阅看庭审笔录并签名。如有遗漏和差错可以申请补正。现在闭庭。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:11
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>庭审记录</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t># 庭审概况
+本案系国家开发银行（上诉人）与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司（被上诉人）金融借款合同纠纷二审，国开行不服云南省高级人民法院2018云民初88号民事判决向本院提起上诉。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。经核对，各方出庭人员身份均符合法律规定，东源煤电、东源煤业、曲靖电力三方委托共同诉讼代理人合并发表意见，各方确认已收到诉讼文书及开庭传票。庭审围绕三个争议焦点调查辩论：抵押权与融资租赁所有权冲突及善意取得、罚息复利计算及起算日期、东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案，各方均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。
+# 原告诉称与被告辩称
+国开行主张其抵押权完整无瑕疵，已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，尽到审慎义务构成善意取得；招银租赁主张国开行未在抵押时点查询融资租赁登记，不构成善意，东源煤电出资系无权处分，招银租赁2012年已取得设备所有权。
+| 方 | 诉讼请求/答辩意见 | 事实与理由 |
+| --- | --- | --- |
+| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利及违约金 | 已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，已尽审慎义务；利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源煤电东源煤业应按借款合同第24条第3项支付千分之一违约金 |
+| 被上诉人东源煤电、东源煤业、曲靖电力 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意；罚息不应作为复利计算基数；不应连带给付违约金 | 招银租赁2012年已取得设备所有权，东源煤电出资系无权处分；2018年6月13日宣布提前到期未给合理期限；复利再计算复利无合同依据；国开行未举证证明违约行为且未按合同约定先行限期纠正 |
+| 被上诉人招银租赁 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意 | 国开行应提供2015年12月操作抵押时点在人行征信中心的查询结果；东源煤电出资系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得设备所有权 |
+# 举证与法庭调查
+**一、举证与质证**
+国开行提交2018年9月对曲靖电力公司的融资租赁查询证书、证据第54页和第58页东源煤电公司曲靖电力公司对设备权属的证明材料和股东会决议、证据第108页核查表；招银租赁提交2015年12月2日邮件及东源公司融资情况统计表、回租设备清单（证据第7页）、2013年和2015年审计报告（证据第82页、第95页）。
+**二、法官询问要点**
+合议庭就中国人民银行征信中心融资租赁登记的性质及法律后果、融资租赁登记系统查询方式、案涉5套设备是否登记唯一识别码、国开行贷款前风控是否要求保留查询记录、融资租赁司法解释第9条第2款举证责任分担、不同登记机构信息冲突如何处理等问题进行询问。
+**三、双方辩论的争议焦点**
+1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已按央行规定查询融资租赁系统且无记录、设备为通用设备无唯一标识码、构成善意取得；招银租赁主张国开行未在抵押时点查询、不构成善意、东源煤电出资系无权处分、其2012年已取得设备所有权。
+2. 罚息复利计算及起算日期：国开行主张利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源方主张2018年6月13日宣布提前到期未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
+3. 东源煤电东源煤业是否应连带给付违约金：国开行主张按借款合同第24条第3项支付千分之一违约金、东源方未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约行为且未按合同约定先行限期纠正。
+# 庭审结果
+合议庭归纳三个争议焦点：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息复利计算及起算日期；三是东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案：国开行对东源煤电债权利息罚息复利共计6474.4513万元；确认招银租赁对涉案6项设备享有所有权、对应债权数额1377.4137万元，确认国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置程序，变现价款双方各得50%、实现费用双方各担50%；未实现债权按破产重整计划预留方案实现；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；各方对一审判决第2项第4项无争议按其判项内容在调解书中确认；一审诉讼费用中国开行诉请部分按一审判决执行、招银租赁诉请部分诉讼费用由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%；本协议签订后各方就本案涉及问题不再存在任何争议。各方对调解方案均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>28485/2240</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1" s="9">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:11
 我们可以开始了吗？可以了。好的，那我们开始开会。尊敬的合作局金昌柱以及公司国内的领导，那么根据我们验收工作安排，我们现在召开我们原占比二玉米面加工厂项目的中期验收会议。由于时间关系和工作安排，那个我们在昨天与那个合作局和金昌处的对接过程中，考虑到今天会议的时间的确定呢，以及这个有限的会议时间，我们提前召开了这个我们验收组以及参与单位的一个预备会，把截止目前完成的工作的情况呢，也做了一个梳理和内部通报，以期呢为这个参建单位提前争争取整改和完善的时间。
 • 发言者 1 01:08
 那么根据我们之前的计划和安排，由我来代表这个一会呢由我来代表验收组吧，截止目前工作的开展情况和存在的问题做一个简单的汇报和评述。然后呢请我们的管理组以及技术组就存在问题的逐渐整改情况做简单的做一个汇报。那么会后呢后面呢再请我们有关的领导做指示，那么会后呢继续安排我们剩下的一个点的这个现场验收工作。那么截止今天为止呢，我们以这个已经完成了卢萨卡点除弹料加工调试以外的所有唉验收工作。蒙蒙泽这个点呢已经完成了，
@@ -2155,9 +2818,93 @@
 好的好的，大家保重
 • 发言者 6 44:08
 唉行。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:02
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>项目进度会</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t># 项目概况
+本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18号19号提前介入前期摸排，20号召开首次会议，分内业检查和外业检查，按建筑工程、安装工程、机电设备专业方向开展。截止今天已完成卢萨卡点除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收工作，姆皮卡点现场验收工作尚未开展；因带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。内业方面，管理组技术组基本能够按照项目合同从开工到过程中组建项目执行团队并按流程程序开展工作，受疫情及项目特殊情况影响主要人员基本能保证在前方岗位，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求，但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。外业方面，建筑部分原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准，因资料完整整理结果没出来今天不下最后结论；安装部分以钢结构为主，所有材料从国内定制发货到现场，设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。财务验收专家对本项目财务资料进行查阅并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准；不可预见费方面，检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+# 进度追踪
+各模块进展如下：
+- **卢萨卡点验收**：已完成除弹料加工调试以外的所有验收工作。
+- **蒙泽点验收**：已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程。
+- **姆皮卡点验收**：现场验收工作尚未开展，内业资料已提前拿到卢萨卡点。
+- **内业资料**：管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，验收组查阅资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。
+- **建筑部分**：原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论。
+- **安装部分**：钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底。
+- **机电设备**：验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。
+- **财务**：财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。
+- **不可预见费**：检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+| 模块 | 进展 | 状态 |
+| --- | --- | --- |
+| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
+| 蒙泽点验收 | 已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程 | ✅已完成 |
+| 姆皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | ⛔阻塞 |
+| 内业资料 | 管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，基本评价为满足项目有关标准和规范要求；分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善 | 🔄进行中 |
+| 建筑部分 | 原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论 | 🔄进行中 |
+| 安装部分 | 钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底 | 🔄进行中 |
+| 机电设备 | 验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准 | ✅已完成 |
+| 财务 | 财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准 | ✅已完成 |
+| 不可预见费 | 检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接 | 🔄进行中 |
+# 风险预警
+整体健康度：🟡低风险。主要风险与瓶颈如下：
+- 人员履约方面，个别同志进出场时间以及护照还需施工部和管理组进一步完善，个别岗位人员因各种原因有申请更换流程，个别特种人员证件有效期可能因出国后国内延期或更新未及时到位。
+- 人员统计数量尤其是技术组对厂家服务人员可能没有计算进去，投标和合同文件对数量有要求。
+- 内业资料分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散。
+- 某厂区非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，若移交外方投入使用后再出现大面积开裂，对外影响不太好。
+- 监控管线因设备启动震动，管线接头处有脱落。
+- 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌。
+- 卢萨卡点廊墙最端头横向分布只有三个竖条，可能影响巡检和维护人员安全保障。
+- 不可预见费使用有关依据证据和数据还需进一步完善，必须做到充分无误。
+- 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方。
+- 赞比亚雨季路况不好，去姆皮卡路途遥远，交通安全风险；新冠疫情防控风险。
+| 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
+| --- | --- | --- | --- | --- |
+| 人员履约：个别同志进出场时间以及护照资料需完善，个别岗位人员有更换申请流程 | 🟡低风险 | 影响验收报告闭合条件 | 管理组、技术组 | 在形成验收报告之前完善进出场时间及护照资料，达到闭合条件 |
+| 人员统计数量尤其是技术组对厂家服务人员可能未计入 | 🟡低风险 | 投标和合同文件对数量有要求，影响履约统计 | 技术组 | 完善人员统计，将厂家服务人员等EPC项目团队人员计入 |
+| 个别特种人员证件有效期可能因出国后国内延期或更新未及时到位 | 🟡低风险 | 影响人员履约合规性 | 执行单位 | 与国内人力资源对接，确认延期或更新情况并完善 |
+| 内业资料分类整理及少量质检和管理机构验收签字规范性不足 | 🟡低风险 | 影响竣工文件组卷成册 | 执行单位、技术组 | 按项目执行有关标准和规范及国家有关规范，及时汇总卢萨卡、分类成册、按竣工文件归档要求组卷 |
+| 竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散 | 🟡低风险 | 影响资料集中归档进度 | 执行单位 | 抓紧将三个厂区资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码 |
+| 某厂区非主要通道范围内混凝土路面有少量开裂现象 | 🔴高风险 | 若移交外方投入使用后再出现大面积开裂，对外影响不太好 | 管理组、总包单位 | 共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，在末次会之前、最迟出报告之前完成整改，验收组复核形成闭环 |
+| 监控管线因设备启动震动，管线接头处有脱落 | 🟡低风险 | 影响监控有效性和安全性，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
+| 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌 | 🟡低风险 | 影响设备运行与成品保护 | 施工组 | 检查并考虑增加覆盖面积或通过技术措施解决 |
+| 卢萨卡点廊墙最端头横向分布只有三个竖条 | 🟢正常 | 可能影响巡检和维护人员安全保障 | 施工组 | 建议中间加两个竖条，从视觉上更安全，为巡检和维护人员提供安全保障 |
+| 不可预见费使用有关依据证据和数据还需进一步完善 | 🟡低风险 | 影响费用动用合规性与验收报告表述 | 验收组、施工单位 | 后续利用时间做专门对接，确保依据证据和数据充分无误 |
+| 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方 | 🟡低风险 | 影响交付前成品状态 | 管理组、总包单位 | 交给外方之前继续做好成品保护，破损地方及时修补 |
+| 赞比亚雨季路况不好，去姆皮卡路途遥远 | 🟡低风险 | 交通安全风险 | 验收组 | 注意交通安全，争取安安全全平平安安完成任务 |
+| 新冠疫情防控风险 | 🟡低风险 | 影响人员健康与验收进度 | 验收组、参建单位 | 注意新冠疫情防控 |
+# 后续计划
+下一周期核心交付物与关键时间节点如下：
+- **在末次会之前、最迟在出报告之前完成混凝土路面开裂整改**，由管理组和总包单位共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，整改完成后由验收组进行复核，在报告中形成闭环。
+- **在验收完成第一时间将三个厂区资料全部汇总于卢萨卡**，包括竣工图进行分类汇总、分类组卷及编码，由技术组按验收组专家要求及援外项目执行手册管理办法规定执行。
+- **在形成验收报告之前完善个别同志进出场时间以及护照资料**，达到闭合条件，由管理组和技术组负责。
+- **与国内人力资源对接完善个别特种人员证件有效期延期或更新问题**，由执行单位负责。
+- **全面检查监控管线接头脱落问题**，保证有效性和安全性，由施工组负责。
+- **检查卢萨卡点加工提升桶往上位置雨水倒灌问题**，考虑增加覆盖面积或通过技术措施解决。
+- **建议卢萨卡点廊墙最端头中间加两个竖条**，为巡检和维护人员提供安全保障。
+- **交给外方之前继续做好成品保护**，破损地方及时修补。
+- 会后及时安排接下来的工作情况，通过适当渠道向后方的领导汇报整个工作进展情况。
+*依赖前提：姆皮卡点现场验收工作尚未开展，需在会后安排并注意雨季路况与交通安全；不可预见费有关依据证据和数据需进一步完善，后续专门对接。*</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>11110/4902</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1" s="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:02
 各位尊敬的投资者，各位客户朋友们，大家周一早上好，欢迎来参加我们的每周一度的中金宏观策略争论，我是策略组的刘刚凯文。那我们今天呢也是带来了最近大家比较关心的一些热点内容，也是比较丰富的内容。首先呢这个关于这个大美丽法案是最近海外市场大家关注的焦点，他对美国经济对于美股市场美债有什么影响，对于美元流动性有什么冲击？那反过来呢是否会通过这个来影响港股的流动性，会影响呢外围资金流向的变化。这一点呢是我们今天给大家重点解读的一部分。
 • 发言者 1 00:38
 第2块呢大家可能也注意到了，就是那它到底有什么影响？那市场好像还反映的出奇的冷静。再加上呢这个市场也处在这个位置，也在观望接下来关税的谈判，所以在关税上我们给大家做一个更新。那除了这个以外呢，回到这个中国市场回到国内的基本面的情况，最近大家最为关心的政策上的变化呢就是所谓的反内卷。但反内卷对于不同行业的含义以及这一次呢可能的影响，我们呢请到了我们公用事业风光公用事业的首席分析师刘佳妮来跟我们谈谈对于行业层面的影响。
@@ -2351,9 +3098,38 @@
 好的，非常感谢雪晴老师给我们带来关于游戏行业的分享和更新观点，也是非常明确。接下来等待一定的催化剂，在目前的位置上呢依然是一个好的配置的时间点。而且呢有可能会迎来一定催化剂下，包括新品催化下的这个戴维斯双击。我们从策略角度呢也提示大家关注相关的板块。就像我刚才提到的一样，从这个大的方向上，我们去在合适的位置对吧？合适的这个位置上，合适的时间上去选择长期正确的板块，可能在结构性的行情下是更加符合现在策略的一个投资方向。
 • 发言者 1 01:12:37
 好，再次感谢那各位投资者如果有问题的话，可以直接联系这个传媒组和我们的雪琴老师。以上呢就是我们今天这一期宏观策略争论的所有的内容。内容还是非常丰富的，也是再次感谢各位投资者对我们持续的关注。我们下周同一时间再见，感谢大家。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:10
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>新闻发布</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t># 发布会概况
+本次中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性三大宏观热点展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就反内卷与光伏、人形机器人、游戏板块进行行业更新。会议核心信息包括：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年。整体基调为：大美丽法案对信用周期中长期有利但三季度有流动性波折，美股美债波动提供再配置机会、不悲观；关税大概率是谈判技巧、市场逐渐脱敏；港股三季度流动性边际收紧、指数在23000~24000区间震荡；反内卷政策有望夯实光伏行业底部；人形机器人三季度是二季度迷茫期到商业兑现的过渡阶段；游戏板块在消费、政策和新品周期三重利好下有望在调整后再次实现戴维斯双击。
+# 核心信息
+大美丽法案三大块：第一，解决债务上限，提高约**5万亿美元**，违约风险消除；第二，延长2017年减税，新增支出**3.4万亿**、一年**3400亿**，同时减掉其他支出**1.4万**（包括减少对新能源补贴）；第三，取消899条款，避免对海外投资者持有美债利息征税。关税收入每年**3000~4000亿**可对冲支出，赤字率基本维持**5~6%**。7~9月发债约**1万亿**带来流动性抽水，2023年三季度曾发1万亿债推高美债利率从**3.8~5%**、美元走强、美股小幅下跌**4~5%**。关税四点信息：一定会做以支撑收入、需维持**10~12%**有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到**18%**，通胀年底抬升至**3.3~3.4%**但不改变路径。光伏2025年需求**650~700GW**，电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**，产业链价格跌**70~90%**；反内卷政策级别提升：2月国常会、6月29日起人民日报发声、7月1日中财委第六次会议、7月3日工信部座谈会；多晶硅期货反弹至**40元/公斤**、硅片报价涨**10%**、电池涨**2分**。人形机器人二季度A股板块跌约**9%**、跑输机械**12个百分点**，特斯拉供应商回调**30~40%**；智元机器人收购上市、宇树科技年收入破**10亿**、两家中标中国移动**1.2亿**订单。游戏6月单月版号**158个**创2018年以来新高，1~5月游戏市场规模同比增长**17%**多、手游增长**20%**，吉比特《仗剑传说》首月流水**2亿多**、巨人网络《超自然行动组》6月流水**过亿**，当前TTM PE约**30倍**、2025年静态PE约**20倍**。
+# 官方表态
+刘刚凯文：&gt; 我们并不是完全的认同，去美元化这个观点的。现在这个预期基本成了一个非常拥挤的共识，而且主要是基于宏大趋势。把美元弱当成去美元化，把美元弱和美股弱直接划等号，是市场两个最大的误区。&gt; 大美丽法案对信用周期中长期有利，但三季度有流动性波折；美股美债波动提供再配置机会，不悲观。&gt; 关税大概率是谈判技巧，市场逐渐脱敏，但需关注8月1日谈判和8月12日中美谈判及转口限制。&gt; 港股三季度流动性边际收紧，指数在23000~24000区间震荡，建议低迷时介入、亢奋时锁定利润。刘佳妮：&gt; 反内卷政策有望夯实行业底部，硅料整合最迫切，头部一体化组件企业穿越周期能力较强。郭文秀：&gt; 三季度是二季度迷茫期到商业兑现的过渡阶段，建议关注华为云生态接入、头部企业出货量跨越500/1000台、电机硬件优化三类信号。张雪琴：&gt; 游戏板块在消费、政策和新品周期三重利好下，有望在调整后再次实现戴维斯双击。
+# Q&amp;A环节
+问：大美丽法案对美股美债和美元流动性有什么影响？ → 答：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年，信用周期框架下美国下半年环比改善，四季度美元可能小幅走强、美股可能反弹跑赢。问：关税谈判最新变化及对市场影响？ → 答：关税四点信息为一定会做以支撑收入、需维持10~12%有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到18%，通胀年底抬升至3.3~3.4%但不改变路径，需关注8月1日谈判和8月12日中美谈判及转口限制。问：反内卷对光伏行业的影响？ → 答：光伏2025年需求650~700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍，产业链价格跌70~90%；反内卷政策级别提升，硅料环节最易切入，多晶硅期货反弹至40元/公斤、硅片报价涨10%、电池涨2分，组件跟涨意愿但受136号文电价不确定性影响。问：人形机器人三季度核心趋势和投资逻辑？ → 答：二季度A股机器人板块跌约9%、跑输机械12个百分点，特斯拉供应商回调30~40%；三季度三条主线为华为云生态开放、本土企业技术闭环、特斯拉延期带来硬件替代窗口；关注物流端场景、电机和轻量化方向。问：游戏板块最近状态及投资机会？ → 答：政策端友好度空前，6月单月版号158个创2018年以来新高，1~5月游戏市场规模同比增长17%多、手游增长20%；中型厂商新品成为核心催化，当前TTM PE约30倍、2025年静态PE约20倍，新品利润有滞后性、明年兑现，有望在调整后再次实现戴维斯双击。</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>22868/2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1" s="9">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:10
 请坐。
 • 发言者 2 00:11
 那今天这节课的老师要给同学们来讲一个主题班会，它的名字叫什么呀？梦想。那我们班有没有同学有哪些梦想呢？当保安。真的可以，同学们可以积极的发言，有什么梦想呀？要当喜剧男。要当喜剧人，在每一个班说的时候，每一个班的人都会有想当太空人。那说明这个广告词真的是深入人心。想当世界冠军。想当什么世界冠军。想当主角。那个一般他有的同学他说他想当一个歌手，所以我就刚刚让他上来唱了两首。对。班有没有同学想当歌手呀？
@@ -2651,9 +3427,54 @@
 那到时候我们再回过头来看一下我们的这个我们为什么现当下我们现在自己为什么会定下这些梦想呢？那好，那等一下每个小组的同学，第1个同学的老师把每个同学的梦想收一下，那这节课就上到这里了。同学们下课。
 • 发言者 4 36:26
 你们辛苦了。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:00
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课程为以「梦想」为主题的班会课，教师先提问班会主题名称并邀请同学分享梦想，有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手，教师提到有同学想当歌手并让其上来唱了两首歌，鼓励自愿为原则在结束前再唱一首。教师随后分享自己的梦想是成为受学生喜爱、有名望的优秀人民教师，并讲述自己曾想考中国美术学院、单考通过但因离家远和没钱未去，最终去了广东技术师范大学（原民族学院，后改名广师大），自己是定向生、免学费、需回龙川县教书，当时哭了三天但后来越来越喜爱教师行业。教师播放航模少年和想成为歌手的普通人的视频，组织4个大组作为梦想观察团讨论实现梦想需要的条件，并以马云中考考两次、高考多次、现成为中国首富为例说明坚持的重要。最后教师请同学们写下自己的梦想清单并分组分享，收齐每个同学的梦想。
+# 核心知识点梳理
+**丑小鸭的梦想**：想变成白天鹅。
+**教师的梦想**：成为受学生喜爱、有名望的优秀人民教师；此前愿望清单包括考中国美术学院（单考通过，因离家远和没钱未去）、加入学生会、参加各种比赛、保持专业排名第一（专业41人）、考教师资格证。
+**定向生**：免学费，需回龙川县教书；定向不能考研，只能在职考研，且学费自交。
+**实现梦想的条件**：学生提到坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结 `学习`、`坚持`、`行动` 是梦想必不可少的三个条件，机会留给有准备的人。
+**马云案例**：中考考两次才考上高中，高考多次，现成为中国首富，说明起点高低不重要、坚持才重要；马云的新梦想是希望未来15年世界因他们而改变，享受改变他人的乐趣。
+**梦想的调整**：梦想可以一步步立高，如先考进年级前百再定前50，实现不了可以调整。
+⭐ 难点：理解定向生不能考研、只能在职考研且学费自交的限制；理解梦想可以调整、一步步立高。
+*易混点*：定向生与普通师范生的区别；梦想实现不了与放弃梦想的区别。
+# 课堂互动与答疑
+问：班会主题叫什么？→ 答：梦想。
+问：同学们有什么梦想？→ 答：有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手。
+问：老师的梦想是什么？→ 答：成为受学生喜爱、有名望的优秀人民教师。
+问：实现梦想需要具备哪些条件？→ 答：坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结学习、坚持、行动是必不可少的三个条件。
+问：如果缺少一个条件，梦想还会实现吗？→ 答：具备某一个条件梦想都有可能实现，都具备则会更快实现。
+问：马云的新梦想是什么？→ 答：希望未来15年世界因他们而改变，享受改变他人的乐趣。
+&gt; 不被嘲笑的梦想就是梦想。
+&gt; 机会都是留给有准备的人。
+&gt; 梦想还是要有的，万一实现了呢？
+&gt; 每一个梦想都是值得我们尊重的。
+# 课后任务与学习建议
+教师请同学们拿出纸写下自己的梦想清单，可列第1个、第2个、第3个，实现之后可以打勾，并思考实现梦想需要的时间和收获。写完后各小组第1个同学分享梦想，教师收齐每个同学的梦想。教师强调写梦想要实在一点、诚恳一点，梦想可以制定多个，先定小目标再定大目标，实现不了可以调整。复习重点为实现梦想的条件（学习、坚持、行动）及梦想可以一步步立高、可以调整。</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>9362/1348</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1" s="9">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:00
 【新思想引领新时代改革开放】以文化自信筑牢强国复兴精神之基建设中华民族现代文明
 • 发言者 1 00:14
 文化兴国运兴，文化强民族强。没有高度的文化自信，没有文化的繁荣兴盛，就没有中华民族伟大复兴。党的十八大以来，习近平总书记以强烈的文化自觉与历史担当，以重大理论创新指导具体实践，在“五位一体”总体布局中对文化建设作出战略部署，在全面深化改革中纵深推进文化体制改革，引领社会主义文化强国建设在正本清源、守正创新中取得历史性成就、发生历史性变革。全党全国各族人民文化自信明显增强，全社会凝聚力和向心力极大提升，汇聚起强国建设、民族复兴的磅礴精神力量。
@@ -2811,9 +3632,37 @@
 新时代新征程，上海、浙江坚定不移全面深化改革、扩大开放，在推进中国式现代化建设中走在前列。
 • 发言者 1 30:27
 今天（7月14日）的《全面深化改革中国式现代化万千气象》，让我们一起走进上海、浙江。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:03
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次内容为新闻联播式综合报道，涵盖新思想引领新时代改革开放的文化建设、赵乐际对俄罗斯正式友好访问并出席中俄议会合作委员会第九次会议、夏粮产量创历史新高、6月国家铁路货运指标增长、上半年快递业发展提速、油气管网建设提速、渝川皖等地应对降雨天气，以及国内国际联播快讯等议题。文化建设方面，报道围绕文化兴国运兴、文化强民族强展开，强调党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展，坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议；今年是中俄建交75周年，双方表示从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障，沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政，访问期间赵乐际向俄无名烈士墓敬献花圈。经济民生方面，今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加主因，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金，小麦质量为近年来最好水平；6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，化肥农药运量增幅最大，同比增长26.2%，中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%；上半年我国快递业务量超800亿件，快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件；油气管网建设提速，预计全年新增管道里程超4000公里，西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米，目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米，按照规划到2025年初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。防汛方面，7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区内涝、滑坡，消防救援人员紧急出动转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来洪峰流量45000立方米每秒量级洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群减小三峡水库入库洪峰流量。国内联播快讯方面，北京上半年计划新开工的320个市区重大项目全部实现开工，总投资超过4000亿元；燕矶长江大桥北岸主塔封顶，下一步转入主缆施工阶段，大桥连接湖北鄂州和黄冈，主跨1860米；第二十三届环青海湖国际公路自行车赛在海北州门源县收官，22支车队154名运动员决出5个奖项冠军；内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底；“中非儿童手拉手”活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。国际联播快讯方面，美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，枪击造成一名观众死亡、两名观众重伤，枪手被特勤局狙击手打死，动机有待查明；以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明谴责；以军袭击黎巴嫩多个边境村镇，黎真主党武装称打击以军集结地；叙利亚大马士革卡夫苏萨地区等遭空袭，造成1名政府军士兵死亡、3人受伤；俄称打击乌军列车点，乌称击退俄军进攻；加拿大东北部林火蔓延，拉布拉多城9600人被疏散，加拿大正在应对500多起活跃林火，其中超400起处于失控状态。
+## 新思想引领新时代改革开放：以文化自信筑牢强国复兴精神之基
+- 报道围绕文化兴国运兴、文化强民族强展开，强调没有高度文化自信就没有中华民族伟大复兴；党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。
+- 习近平总书记就弘扬和发展中华文化提出一系列重要论述，在孔子故里翻看《孔子家语通解》《论语诠解》，在岳麓书院凝望“实事求是”匾额，在三苏祠强调从中华优秀传统文化中汲取治国理政的理念和思维，在武夷山朱熹园提出以时代精神激活中华优秀传统文化的生命力。从深入实施中华文明探源工程到高标准推进国家文化公园建设，从中国共产党历史展览馆、国家版本馆等文化地标落成到《复兴文库》、“中国历代绘画大系”出版，中华优秀传统文化与革命文化、社会主义先进文化融会贯通。深化国有文艺院团改革、树立以人民为中心的创作导向，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
+## 赵乐际对俄罗斯进行正式友好访问并出席中俄议会合作委员会第九次会议
+- 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科的邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。赵乐际向普京转达了习近平主席的亲切问候和良好祝愿，指出今年是中俄建交75周年，中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献。普京请赵乐际转达对习近平主席的亲切问候，表示俄中立法机构始终保持高水平合作。与马特维延科、沃洛金分别会谈时，赵乐际表示要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持，两国立法机构要立足职能职责，用好中俄议会合作委员会、双边友好小组等机制和平台，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障。马特维延科表示发展对华关系得到俄社会的广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，指出两国立法机构要密切战略协作，服务中俄关系发展大局；交流治国理政经验，助力各自国家发展振兴；发挥立法机构职能作用，以法治方式促进务实合作；传承弘扬传统友谊，不断夯实国家关系的社会和民意基础；加强多边协作，从立法机构层面团结壮大“全球南方”力量。访问期间，赵乐际在莫斯科向俄无名烈士墓敬献了花圈。</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>7755/3290</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1" s="9">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:03
 现在来看讲义，首先呢我把我们在光学部分，因为咱们一共有三讲来学习光学，其实呢对于有些同学来说呢是新课，但还对于有些同学来说呢，今天这部分内容呢是一个复习。咱们在初中阶段的光学，不管是讲直线传播，还是光的反射，还是光的折射，实际上呢在我们物理上叫什么呢？叫几何光学。大家看这我们称之为这个也就是说这个几何光学呢应该说是人类从2000多年前就开始研究，比方像咱们今天要给大家，不管是讲新课还是复习的直线传播和反射，实际上在2000多年前的那个古希腊时期，那时候的哲学家们就已经找到这些规律了。
 • 发言者 1 01:00
 包括我们要讲的折射现象，还有咱们讲的折射规律，当然后人做的第1个工作是把折射规律变成折射定律。但是咱们初中阶段讲的还是规律，所以呢这是同学们要学的东西，今天可能会有点说老师怎么我们学的东西好几千年前就已经知道了，是这样，所以这是几何光学。然后等到同学们到了高中的时候，这部分知识以前高中也讲，但现在高中呢已经完全不讲了，他认为没有什么意义。其实也不对。我们其实照镜子呀大家戴眼镜其实还属于几何光学的范畴。
@@ -3035,9 +3884,59 @@
 后来的结果就电线就自个着了，所以呢还到处找呢，为什么自燃？实际上就是因为这个所以像咱们现在很多地方就是设计师他愿意用这种玻璃幕墙，为什么呢？因为设计师的设计费是根据你这个建筑成本来算的，你当然用玻璃幕墙比用砖头贵，然后呢咱们一般的人觉得好看就行，但是它缺点是什么呢？就有很多这种叫光污染。这种光污染有的时候就会引起很多种隐患，像很多树木什么就反而死了，而且呢你声音它都反射，所以有时候你会感觉到就在楼中间走，那噪音特别大，为什么所有的声音它发散不出，它通过这个凹面就反射回来了。
 • 发言者 1 01:43:30
 好，以及它的应用是透镜。今天咱们上到这，</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:14
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课为三讲光学中的第一讲，部分同学是新学、部分是复习，内容涵盖光的直线传播、光的反射（平面镜、凸面镜、凹面镜即球面镜）、光的折射（凸透镜、凹透镜）及透镜应用（显微镜、望远镜），初中光学统称几何光学，高中不再讲几何光学而讲干涉、衍射。光源定义为自身能够发光的物体，分自然光源（太阳、萤火虫）与人造光源（火把、蜡烛、煤油灯、电灯），光线用带箭头直线表示、是物理模型并非真实存在。光在均匀介质中沿直线传播，实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成；小孔成像一定成倒立实像、放大缩小不一定、与孔形状无关。光在真空中传播速度为3×10^8米每秒即3×10^5千米每秒，约每秒绕地球赤道7圈半，水中约为真空中的3/4、玻璃中约为2/3。光的反射定律为反射光线、入射光线和法线在同一平面内，反射光线与法线、入射光线分居法线两侧，反射角等于入射角；平面镜成正立、等大的虚像；凸面镜对光线起发散作用、成正立缩小的虚像，凹面镜对光线起会聚作用、有焦点F。
+# 核心知识点梳理
+**几何光学**：初中光学（直线传播、反射、折射）统称几何光学，2000多年前古希腊哲学家已发现相关规律；高中不再讲几何光学，转而讲干涉、衍射。
+**光源**：自身能够发光的物体。自然光源如太阳、萤火虫；人造光源从火把、蜡烛、煤油灯到电灯。
+**光线**：用带箭头的直线表示，是物理模型，并非真实存在。光源按形状可分点光源（如蜡烛）和平行光源（如太阳）。
+**光在均匀介质中沿直线传播**：可用玻璃罩加熏香或点香、激光笔照射证明；吸管弯折后激光打不到墙上同一点。实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成。
+⭐ **小孔成像**：一定成倒立实像，放大缩小不一定，与孔形状无关，如树荫下光斑。
+⭐ **日食月食**：日食为太阳、月球、地球同一直线且月球在中间，分日全食、日偏食、日环食；月食为太阳、地球、月球同一直线且地球在中间，月偏食是月球部分在1号区域、部分在2或3区域。
+**光速**：真空中 `3×10^8米每秒` 即 `3×10^5千米每秒`，约每秒绕地球赤道7圈半；空气中约 `2.99×10^8米每秒`，近似取 `3×10^8`；水中约为真空中的3/4，玻璃中约为2/3。练习中激光从地球到月球1.25秒，距离为 `3.75×10^8米`；雷电先见闪电后闻雷声因光速比声速快，15度时声速340米每秒。
+**光的反射定律**：通过硬纸壳、透明胶带、平面镜和激光笔的探究实验验证。定义入射光线AO、入射点O、反射光线OB、法线OP（垂直于镜面、是角AOB的角平分线）、入射角与反射角；法线不存在、画虚线。三句话：反射光线、入射光线和法线在同一平面内（共面）；反射光线与法线、入射光线分居法线两侧；反射角等于入射角。垂直入射时入射角和反射角均为0度，反射光线与平面镜夹角40度时入射角为50度；作图先画法线、保留作图痕迹、利用对称找点。
+**镜面反射与漫反射**：镜面反射是平行光射到光滑镜面后反射光线仍平行、只在特定方向看到反射光；漫反射是表面凹凸不平时反射光线射向各个方向、生活中大多数反射是漫反射。黑板、电影银幕、投影幕布发生漫反射，黑板反光看不清字是镜面反射；无论镜面反射还是漫反射都遵守光的反射定律。雨后夜晚迎着月光走亮处是水潭、背着月光走暗处是水潭；光路可逆。
+**平面镜成像**：实验用玻璃板代替平面镜以便移动蜡烛找像，用刻度尺比较像与物到镜面的距离，选两段完全相同蜡烛比较像与物大小；平面镜成正立、等大的虚像，不能用光屏承接，像与物连线与镜面垂直、像到镜面距离与物到镜面距离相等；玻璃板与水平面不垂直或玻璃板有厚度（两面反射成像）会导致数据不相等或看到两个像；平静水面、光滑金属表面可充当平面镜。
+**球面镜**：凸面镜对光线起发散作用、成正立缩小的虚像，用于汽车后视镜、丁字路口拐弯处；凹面镜对光线起会聚作用、有焦点F，用于手电筒、汽车前大灯、探照灯、耳鼻喉科医生头镜、西藏太阳灶；作图可用以直代曲方法。
+# 课堂互动与答疑
+问 → 答：为什么用玻璃板代替平面镜做实验？→ 因为若用镜子虽有反射，但无法移动后面的蜡烛来找像，故用玻璃板代替平面镜。
+问 → 答：实验为什么选用刻度尺？→ 为了便于比较像与物相对镜面的距离。
+问 → 答：为什么选取两段完全相同的蜡烛？→ 为了比较像与物的大小。
+问 → 答：光屏能否接收到蜡烛的烛焰的像？→ 不能，因为实际光线没有到达后面，成的是虚像。
+问 → 答：记录数据中蜡烛到玻璃板的距离与像到玻璃板的距离有几组不相等，原因可能是什么？→ 一是玻璃板与水平面不垂直，二是玻璃板有厚度、它的两个面发生反射成像。
+问 → 答：在玻璃板同一侧看到同一个蜡烛的两个像，原因是什么？→ 玻璃板有厚度，它的两个面发生反射成像的结果。
+问 → 答：为什么引进法线？→ 主要是为后面讲折射作准备，法线真实不存在，画虚线。
+&gt; 光线是真实存在的吗？我画一个写上它实际上是一个物理模型。
+&gt; 三点一线实际上原理是什么？就是这个光在均匀介质中沿直线传播。
+&gt; 光在真空中传播速度是3×10^8米每秒，基本上一秒钟绕地球赤道7圈半。
+&gt; 无论哪种反射都要遵守光的反射定律。
+&gt; 作图一定是先去做一条法线，作图痕迹要留下。
+# 课后任务与学习建议
+教师布置的课堂练习为练习第1至5题、第10和第11题、第13至24题等，要求当堂完成并讲解答案。复习重点为：光在均匀介质中沿直线传播及其实例、光的反射定律三句话、镜面反射与漫反射的区别、平面镜成像特点（正立、等大的虚像）、凸面镜与凹面镜的作用与应用。学习建议：可在家用纸杯底部用针扎小孔、蒙塑料布、点蜡烛做小孔成像实验；用硬纸壳、透明胶带、平面镜和激光笔做反射定律实验；用白纸和小镜子配合手电筒观察镜面反射与漫反射；建议购买激光笔辅助研究直线传播与反射实验。教师提醒注意保护眼睛，长时间看屏幕、判卷等最费眼睛，视力下降后矫正视力约0.7，应重视用眼健康。</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>25691/2518</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1" s="9">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:14
 电气工程基础是大家进入到专业课来的，所接触到的第1门课，也可以说是一门专业的入门课。我们这一门课程的教学目的，希望能够解决这样两个问题。第1个问题是希望大家能够掌握电力系统的4个典型的环节，包括发电输电配电用电这样4个典型环节的构成工作原理。以及与电力系统整体之间的关系，建立起电力系统的整体概念。这是第1个目标。第2个目标是希望大家能够掌握电力系统在分析设计运行管理这些方面的最基础的理论，最基本的技术以及基本的计算方法。
 • 发言者 1 01:05
 那么通过这样两个目标，等等最基本的工作。所以这一门课是我们专业的入门课，也是对大家今后工作非常重要的一门课程。这一门课的前修课程要求大家对电路理论和电机学的知识应该有一定的了解，特别是变压器和同步电机的相关知识，在我们这一门课上有比较高的要求。那么对这些方面有欠缺的同学，希望大家下去应该把相关的内容做一定的补充。我们这一门课学后还后面还有很多的后续课程，最重要的后续课程就是这样4门课。电力系统分析。
@@ -3131,9 +4030,50 @@
 比如说咱们华工变电站，面那个箱子里面装的，这也是个变电站，我们叫相似面。那么这样一个变电站它的电压等级是多少呢？10千伏变到380对吧？所以它是一个10千伏变电站。这样一个变电站。我们关山边上设了有一个变电站，它的最高电压等级是220千伏，所以我们叫做220千伏的变电站。就好像你们去参观过的是吧？在我们凤凰山变电站就在我们这边不远，凤凰山有一个变电站，你们好像也参观过，它的最高电压等级500千伏。
 • 发言者 1 43:54
 所以我们把它叫做500千伏的变电站，这是按照最高电压等级来进行分类的，这是一种方法。是按它的主要的功率，所流通的方向是从变压器的高压侧流向低压侧呢，还是从低压侧流向高压侧？那么我们把这个变压变电站，分为升压变压和降压变。变电站。如果这个辩论战的大家注意是最主要的功率，最主要的功率。那么大部分功率都是从高压侧向低压侧在传输，我们称之为降压变电站。反过来在发电厂里面，大部分功率是从发电机发出来的这个低压侧升压升到高压侧的，我们叫升压变电站。好，休息一下。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:05
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课为《电气工程基础》课程导论，该课是进入专业课接触的第一门课，也是专业入门课。教学目的有两个：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程要求对电路理论和电机学知识有一定了解，特别是变压器和同步电机相关知识要求较高，有欠缺的同学需下去补充；后续最重要的四门课程为电力系统分析、电力系统继电保护、电力系统自动化和高电压技术。第一章涉及电力系统基本概念最多、最重要，要求掌握电力系统、电力网、动力系统和变电站等基本概念，理解电力系统特点及由此引起的最基础理论，理解对电力系统提出的要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中心点接地方式特点。课程还梳理了电力发展简史、三相交流输电优势，以及电力系统形成与定义、电网分类与变电站分类。
+# 核心知识点梳理
+**一、课程定位与目标**：电气工程基础是进入专业课接触的第一门课、专业入门课。教学目的：①掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；②掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程：电路理论、电机学，特别是变压器和同步电机相关知识要求较高。后续最重要的四门课程：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
+**二、第一章重点内容**：①学习和掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站；②理解电力系统的特点及由这些特点引起的设计运行等方面最基础的理论；③理解对电力系统提出的要求，涉及运行、设计和维护各方面；④掌握电力系统的电能质量指标，包括国家标准对这些指标规定的范围；⑤了解电力系统常用的接地方式，特别是工作接地即中心点接地方式的不同特点。
+⭐**三个学习难点**：①由电力系统特点引出的最基本原理，如电能不能大量储存，决定了电力系统的有功功率和无功功率的动态平衡问题；②电力系统额定电压的规定非常繁杂，要注意把这些规定搞清楚；③各种中心点的接地方式，直接影响后面所学习的多个章节内容，学习起来也比较困难。
+**三、学习方法建议**：对基本概念注意其内涵和外延，并适当结合实际；思考方法上从电力系统的特点要求出发，注意从最基础的原理去推导，不要去记结论，因为结论性东西在使用条件变化时就会发生变化；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。
+**四、电力发展简史**：电力发展从直流开始。福泰勒使用2000米导线连接瓦斯发电机，拖动直流发电机和电动机，证明直流远距离两公里输电可行。1874年俄国工程师在彼得堡建立4.5公里直流输电线路，功率4.5千瓦。1882年法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端343伏、末端850伏，输送功率200瓦，损耗78%。1883年德普勒进行14公里输电试验，输送功率1.1千瓦，损耗55%。1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展为五线制。19世纪末法国方剑将多台直流发电机串联提高电压，将75千瓦电力送75千米。20世纪初瑞典科学家在串联直流发电机上装短路器，之后20多年建15条直流输电线路，最大为1906年投运的法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦线路，1927年改建为260公里、125千伏、19000千瓦。直流输电受制约因素多、设备复杂、运行方式复杂、造价高、可靠性差。
+交流方面：1876年俄国科学家发明单相变压器，主要用于照明；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行；威斯汀豪斯与爱迪生进行交直流电力战争，爱迪生和凯尔文主张直流，威斯汀豪斯和特斯拉主张交流；1886年威斯汀豪斯在麻省进行1000米、30千伏交流输电示范，又在意大利建成17英里高压输电线路；1886年俄国科学家发明三相交流电和三相异步电动机；法国到德国的交流输电线路被认为是第一条交流输电线路。交流输电随高电压技术和绝缘技术发展：1898年发明真实绝缘子，美国加利福尼亚输电电压提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，首次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压1150千伏线路投运后降压到500千伏运行。国内：220千伏1941年投运，330千伏1972年投运，500千伏1981年投运，2009年1000千伏交流特高压投运。直流用于联网：1954年瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆，100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。中国第一个直流输电工程连接舟山群岛与浙江定海电网；第二个是1989年葛上直流，葛洲坝电厂到上海，±500千伏；今年6月投运云广直流±800千伏特高压直流工程。
+**五、三相交流输电优势**：交流指ABC三相对称系统，优点：①易于产生旋转磁场，三相电动机容易做驱动；②瞬时功率恒定，不随时间变化；③输电线路导线量即金属消耗量最少。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流。国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小。
+**六、电力系统的形成与定义**：最早单台发电机孤立向附近负荷供电，可靠性差。后将多台发电机连接起来提高可靠性，但导线有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离不能太长。解决办法是升高电压，电压升高后电流减小，有功功率损耗和电压降落减小，输电距离变长，采用变压器升压降压。这样构成电力系统雏形，多台发电机共同向负荷供电，可装大机组，供电范围越来越大，带来经济效益。输电距离很长时，中间装设变电站用降压变压器向当地供电，并解决稳定问题。现代电力系统：发电机发出电，通过升压变压器升压，经输电线路传输到负荷中心，再降压给用电设备使用。**电力系统**定义为变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能，由发电、输电、配电、用电四个环节组成。**电力网**是变压器和输电线路构成的网络，即电力系统去掉发电机和用电设备的部分。**动力系统**是电力系统基础上加上发电厂动力部分（如火电厂锅炉、汽机、煤炭输送处理系统，水电厂水轮机、水坝、水库等）。
+**七、电网分类与变电站分类**：按规模将电网分为地方电力网、区域电力网、超高压远距离输送网络。地方电力网向固定地方供电，电压等级早期35千伏及以下，现在常为110千伏及以下，供电半径20~50公里；区域电力网电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心；超高压远距离输送网络电压等级500千伏或1000千伏，东北有330千伏，主要任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统，如特高压系统从山西晋东南到湖北荆门，跨三省，连接华北电网和华中电网。举例：武汉电网属地方电力网，主要供电电压110千伏和35千伏，少数220千伏；华中网是典型区域网；葛上直流、三峡到上海输电线路属超高压远距离输电网络。变电站分类常见三种：按电压等级分类，按最高电压等级称为多少千伏变电站，如华工变电站10千伏、关山变电站220千伏、凤凰山变电站500千伏；按主要功率流通方向分为升压变电站和降压变电站，大部分功率从高压侧向低压侧传输为降压变电站，从低压侧向高压侧为升压变电站。
+# 课堂互动与答疑
+问：我们国家为什么采用交流、为什么采用三相三线制？→ 答：交流指ABC三相对称系统，至少具有三个方面的优点：第一，易于产生旋转磁场，因此三相电动机很容易做驱动；第二，瞬时功率是恒定的，不随时间变化；第三，输电线路所采用的导线量即金属消耗量最少。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此三相三线制输电系统在交流输电领域得到广泛应用。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。
+&gt; 对基本概念，我们要注意它的内涵和外延，并且适当地结合实际。
+&gt; 对于思考的方法，我们要从电力系统的特点要求出发，注意从最基础的原理去进行推导，不要去记一些结论。
+&gt; 这些结论性的东西，往往当它的使用条件变化的时候就将发生变化。
+&gt; 关于这方面的内容，我希望大家下去做一些进一步的阅读，作为电气专业的学生，我们应该了解我们电力发展的一个基本的发展史。
+# 课后任务与学习建议
+教师推荐三本书，供大家下去阅读。教师强调第一章为重点内容，要求大家以重点内容进行掌握，并提醒学完章节后仔细体会学习方法：注意基本概念的内涵和外延并适当结合实际；从电力系统的特点要求出发，从最基础的原理去推导，不记结论；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。教师要求对电路理论和电机学知识有欠缺的同学下去把相关内容做一定的补充，特别是变压器和同步电机的相关知识。教师希望学生下去对电力发展史方面的内容做进一步的阅读，了解电力发展的基本发展史。原文未提及具体作业提交要求。</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>11163/4089</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1" s="9">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:05
 但这些东西本质上来说就是逗你玩的，对吧？就是故弄玄虚而已，所以他玩这一出的话呢，无非就是逗你玩。因为它的本质是下面那个东西。啊。而下面的东西又是通过另外一个东西观察到，但是他非不这么写，他就非要写成这种东西。这种东西其实是妨碍你理解的。但是会让你觉得magic.好朋友们大家好，欢迎来到频道，我是皮卡，那本期视频呢是一个新的系列的试水之作。新的系列的它的一个核心呢就是评论，那就是说我会带着大家去看一些网上的帖子，一些网友的关于一些数学问题的回答和尝试。
 • 发言者 1 00:48
 然后呢我会在里面给出我的评论，然后呢按照我的主观的想法去那那么接下来就带up主呢就带着大家来看一下这篇帖子，这个是发这个是提问在Stack exchange上面的，我经常提到这个网站，stack exchange.我简称为Mse mass stack exchange.这个呢是国外的一个非常有名的网站，它呢就是约等于这个知乎吧，但是我觉得跟知乎的定位是完全不一样的，因为这个网站上你只能提数学问题，而且只能提具体的数学问题。
@@ -3197,9 +4137,42 @@
 N+1分支1。那分子分母呢？分母也很简单，log1+n分支1嘛。对吧？这两个求极限太简单了。对吧？太简单了。那就是1。是不是？那就做了这个事情。但是我说实话，这个纯粹就是你先知道结果你才这么做的。当你不知道hn是一个怎样的变化率的时候，你让我猜你通过比如说计算一些数据，像高像欧拉那样，你算它个几十项，你大概知道是什么样子。如果你连猜都猜不出来的话，你你不可能去上来就蒙一个log n的。你我就说你凭什么不log log n的平方呢？
 • 发言者 1 27:17
 你凭什么不蒙个根号n呢对不对？去凑嘛。我觉得这个不自然，我觉得这个完全不自然，完全不自然。唉那么今天我们评论就讲到这里吧，这个后面还有很多方法，我们有机会再评论不过下，下次的话看反响吧，如果反响不错的话，我们出下一期我们可以再找一个帖子，再找一个话题来聊这个事。然后如果还不错的话呢，就是看看看网友的一些投稿吧。有网友去解决某些问题，他们的一些尝试思路之类的。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:05
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>知识笔记</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t># 知识主题与概述
+本笔记围绕调和级数收敛与发散这一经典问题展开，核心议题是评论 Stack Exchange（MSE）上网友对该问题的多种证明思路。UP主皮卡从高中数学讲起，先给出级数收敛与发散的简化定义：序列 `an=1/n`，前n项和 `sn`，若所有 `sn` 都小于某个固定实数 `a` 则收敛，若 `sn` 大于某个无界递增的 `bn` 则发散。随后评论了网友的分组求和证明，并补充柯西凝聚判别法，指出其证明过程与分组求和一模一样，对非负不增序列，收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1。UP主还联想到高斯求和 `1+2+…+100` 时用 `1+100`、`2+99` 等分组，每组 `101`，说明分组求和思路普遍。第二个证明用调和数 `hn` 大于 `log(n+1)` 证明发散，涉及积分估计与差分两种流派；网友取对数将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`，UP主认为这与差分方法本质相同，是故弄玄虚。第三个流派用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+# 核心概念
+**级数收敛与发散的定义**：序列 `an=1/n`，前n项和 `sn=1+1/2+…+1/n`。若所有 `sn` 都小于某个固定实数 `a`，则收敛；若 `sn` 大于某个明显递增且无界的 `bn`，则发散。
+**分组求和证明**：将 `1/2+1/3` 分为一组，`1/4` 至 `1/7` 为一组，`1/8` 至 `1/15` 为一组，每组和都大于 `1/2`，任意多组相加无上界，故发散。
+**柯西凝聚判别法**：证明过程与分组求和一模一样，对非负不增序列，其收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1，便于判断增长缓慢的序列。
+**高斯求和**：`1+2+…+100` 用 `1+100`、`2+99`、`3+98` 等分组，每组 `101`，只需数有多少个 `101`，体现分组求和思路的普遍性。
+**调和数 `hn` 与 `log(n+1)`**：第二个证明用 `hn` 大于 `log(n+1)` 证明发散，`log` 无上界故 `hn` 无上界；有积分估计流派和差分流派，积分估计用矩形面积近似 `hn` 并放缩。
+**取对数与连乘积**：网友两边取对数，利用 `e^(a+b)=e^a·e^b` 将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`。
+**Stolz 定理**：第三个流派试图证明 `hn` 与 `log n` 同增长级别，用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+# 核心结论
+核心结论：调和级数发散，网友的分组求和证明、柯西凝聚判别法、`hn&gt;log(n+1)` 证明、取对数连乘积证明以及 Stolz 定理求极限均指向这一结论。易混淆点：**分组求和与柯西凝聚判别法证明过程一模一样**；**取对数连乘积方法与差分方法本质相同**；**Stolz 定理求 `hn/log n` 极限为1是先知道结果再凑，不自然**。待澄清问题：UP主表示后面还有很多方法，有机会再评论；下次是否出下一期取决于反响。</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>7465/1391</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1" s="9">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:05
 Github不只是全球最大的同性交友平台，它其实是每个人都可以用的巨大的宝藏资源库，几乎我们想找的资源教程工具什么的，在github上都能够找到正经一点的，比如说麻省理工斯坦福等名校的公开课字节，阿里腾讯等大厂的面试题和面试经验。Google,阿里这些大公司最新的开源大模型，用AI搞副业赚钱的教程，AI学习资料等等，不正经的，比如说国内这些年缺网火爆的表情包大合集火到150岁养生指南，国内996最严重的大厂黑名单，还有不能播的。
 • 发言者 1 00:49
 那这次就让我们工作室的老李来带我们在
@@ -3245,9 +4218,60 @@
 GPT这类工具，比如我让ChatGPT帮我找github daily它会及时的分享各种最新最热门的项目。
 • 发言者 1 09:47
 好，这就是本期视频的全部内容了，上面提到的所有的开源项目，包括后面的教程，还有一些视频里面没有提到，但我们觉得很不错的项目都整理在文档里面了，需要的可以领取，这里是宣教我们下期见拜。</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:07
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>知识笔记</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t># 知识主题与概述
+本笔记围绕 GitHub 作为资源库的知识主题展开，核心议题包括 GitHub 上的实用热门项目、国内访问加速方法、页面汉化与搜索技巧，以及项目主页功能与热门项目跟踪方式。主要观点为：GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到，涵盖麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂面试题与面试经验，Google、阿里等大公司最新开源大模型，以及用 AI 搞副业赚钱的教程和 AI 学习资料等。整体逻辑框架为：先介绍正经与不正经的实用项目，再逐一解决访问、汉化、搜索等使用问题，最后说明文档整理与领取方式。
+# 核心概念
+## **GitHub 资源库定位**
+GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。正经资源包括麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂的面试题和面试经验，Google、阿里等大公司最新的开源大模型，用 AI 搞副业赚钱的教程，AI 学习资料等；不正经资源包括国内这些年全网火爆的表情包大合集、活到 150 岁养生指南、国内 996 最严重的大厂黑名单等。
+## **实用热门项目**
+- **B 班值不值得上**：评估工作性价比，输入年薪、工作地区、年假、通勤时长、学历、工作年限及领导同事是否 SB 等因素，综合给出工作性价比分数和评级。
+- **表情包博物馆**：国内过去这些年全网爆火的表情包大合集，包含甄嬛传、罗翔老师、特朗普、马保国等表情包。
+- **活到 150 岁指南**：分享经过科学研究证实的健康知识，如间歇性进食对身体有好处，会促进胆汁代谢、炎症自愈；吃天然发酵类食品可以改善肠道菌群生态等。
+- **一键做证件照**：上传一张大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
+- **丐版健身教练**：可选择自重、哑铃、弹力带、长凳等，选择要练习的肌肉群后给出用身体自重练习的参考动画。
+- **PDF 教材合集**：收集国内所有小学、初中、高中一部分大学的 PDF 教材，全部免费用。
+- **全自动视频生成项目** `Morning Printer Turbo`。
+- **声音克隆模型** `ChatTTS`：零样本语言克隆，情感控制非常到位，克隆的声音就像真人说话一样。
+- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，教程内容整理成一份 500 多页的 PDF 文档，含大量示意图。
+- **awesome AI apps**：收录大模型最新的 agent 应用，如医学影像数据分析的 agent、AI 投资的 agent、竞争对手情报分析 agent 等。
+## **GitHub 访问加速方法**
+- **Watt Toolkit 加速软件**：进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速，即可流畅上 GitHub。
+- **GitHub 镜像站**：如 `gh proxy`，浏览器点开就直接上 GitHub，默认是镜像的项目地址，搜其他项目也没问题。
+- **魔法**：个人最推荐的方法。
+## **GitHub 页面汉化**
+给浏览器装翻译插件，推荐谷歌 `Translate` 或 `沉浸式翻译`，装好后可直接把网页翻译成中文；动手能力强的还可给浏览器安装汉化插件。
+## **GitHub 搜索技巧**
+- **原生搜索**：按搜索词精准匹配，搜 `screen record` 和 `screen recording` 按星标排序结果不一样。
+- **AI 搜索**：推荐用 ChatGPT 等工具，用中文指令如“在 github 上帮我找好用的录屏软件”，能搜全热门录屏工具并总结成表格。
+## **项目主页功能与热门项目跟踪**
+- **项目主页功能**：`star` 相当于收藏和点赞，`watch` 是关注项目，`fork` 是复制项目，`about` 是项目简介，`release` 是软件安装包，`readme` 是项目说明书，`commit` 日期可理解为最近更新时间。
+- **跟踪热门项目**：点开左侧 `explore`，在 `trending` 里能看到全站当天、本周、本月最热门的项目；也可用 ChatGPT 找 `github daily`。
+# 核心结论
+GitHub 是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。国内访问 GitHub 卡顿难，可用 Watt Toolkit 加速软件、gh proxy 等镜像站或魔法解决，其中 Watt Toolkit 更流畅，镜像站速度稳定性较差，个人最推荐魔法。页面满屏英文可装谷歌 Translate 或沉浸式翻译插件汉化。原生搜索按精准匹配，搜 `screen record` 与 `screen recording` 结果不一致，推荐用 ChatGPT 等 AI 工具以中文指令搜索。项目主页的 `star`、`watch`、`fork`、`about`、`release`、`readme`、`commit` 日期等功能需了解；跟踪热门项目可看 `explore` 的 `trending`，或用 ChatGPT 找 `github daily`。所有开源项目、教程及视频未提到的项目都整理在文档里，需要的可以三连关注免费领取。</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>4014/2303</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="9">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:07
 锵锵三人行，首先得感谢马先生，马先生太好了，拉来一个他的朋友，但是这个朋友我更有兴趣跟你聊一聊，因为你是明朝那些事的作者，对，听着名字都像日本人当年明月是4个字，日本忍者，我觉得你是唉很少在电视上露面吧，
 • 发言者 2 00:27
 还经常不过就不是访谈类节目吧。
@@ -3601,9 +4625,122 @@
 非常有城府，你所以说我说这个人呢就看真的是被写坏的，就是嘉靖呢那个时候嘉因为明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的。这些人一般来说他都有某些程度的偏颇，因为如果你把它说太好，嘉靖上台先搞了个叫什么大礼仪事件，为这事死了很多人，可以说是也折腾了很多人，为什么就为给自己父亲争个名分，因为他父亲是王爷，他要把他追封为皇帝。所以说就是说历史就非常玄幻，就是我说的就是玄幻，就什么程度就是说有些事儿你看到你以为这么回事，实际上不是这么回事，对，所以
 • 发言者 1 38:31
 我就觉得看很多人专家写历史，我都觉得现在不爱聊说什么西方傲慢与偏见嘛，实际我看很多人研究历史就有傲慢与偏见，就是没有我同意你的观点就是说你没有设身处地，你老觉得你自个聪明，我判断他昏庸无能，对吧？其实这不是傲慢与偏见，我们能知道</t>
-  </si>
-  <si>
-    <t>• 发言者 1 00:05
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>采访记录</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本次对话由窦文涛主持，嘉宾为马先生与《明朝那些事》作者当年明月，从刚播完的日本电视剧《大奥》谈起，认为它是《大长今》之后最有影响的外国剧，三部剧时间跨度约相当于中国晚明到清初，另有一部在明治维新之前。对话认为日本文化核心是极端精神与忠诚文化，凡事做到尽头、发自内心，与中国讲中庸、讲融合的文化差异极大，并举例战后日本用30年成为世界第二经济强国、跳槽率最低、终身雇佣制、豆腐厂按点开工、做绳子的人几年不赚钱铺市场等。关于生死观，对话提到日本人重视死亡而非单纯藐视生命，剖腹自杀、看樱花只看落的那一天，被认为源于岛国生存条件恶劣。关于明史，当年明月表示写明朝是因为明史资料最多、自己最熟，但明清史料说法不一如罗生门，明朝本身跌宕起伏，朱元璋从乞丐到皇帝被推崇为人才，历史经验教训难以套用。对话还提到正德皇帝被写坏、豹房实为动物园、晚明江南市民生活富足、明末灾荒与瘟疫导致李自成起义和明朝灭亡，以及中国王朝约300年大限。
+# 访谈详细记录
+一、《大奥》与日本文化
+- 发言者3认为《大奥》是大长今以后可能最有影响的外国电视剧，拍得非常好。
+- 发言者3介绍该剧三部，前两部大概相当于中国晚明到清初，发言者2补充后来还有一部在明治维新之前，是一部有跨越性的历史剧。
+- 发言者2表示吸引他的是严谨的精神，看日本剧看不到群众演员笑场。
+- 发言者3称听人说这是大长今以后最重要的外国剧，第1集片头将军出场时所有人呈45度开始鞠躬，依次鞠躬，场面之华丽包括色彩，一看就不一样。
+- 发言者3介绍大奥就是普通话说的后宫，日本话的奥指很深的地方，屋子最里处叫奥，一般人不准进去。
+- 发言者2说明日本天皇一直是摆设，实际掌管权力的是幕府将军，德川家康开创德川幕府后日本所有权力掌握在一个人手上。
+- 发言者2称从实际上看幕府将军对天皇一点都不崇拜，天皇没钱办活动找将军要钱，将军不给，活动没办，后来还有为表示对幕府抗议而退位的。
+- 发言者2认为日本文化从头到尾没有变，核心是极端精神，所有事情要做到尽头。
+- 发言者3称日本是发自内心的，战后1945年以后用30年成为世界第二经济强国，是必然不是偶然，是唯一没有资源的国家。
+- 发言者2认为中国文化精神是中庸，讲究融合，是一条最适合的路；日本精神恰相反，坚持一个原则。
+- 发言者3称日本是忠诚文化的典型国度，坚韧不拔，做到极致。
+- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
+- 发言者3称日本跳槽率最低，每一次跳槽都是社会资源的浪费。
+- 发言者2称西方经济学家一直不能理解日本终身雇佣制，认为缺乏竞争会导致效率极低下，但日本终身雇佣了人家还是积极性特别高。
+- 发言者3举例去日本参观最底层工厂，豆腐规定当天做当天卖，夜里11:45所有人坐好看着表，12点整所有人站起来开始工作，四点多钟干完，然后上市，今天的豆腐今天卖。
+- 发言者2认为日本是岛国，没有资源，经常火山地震，人对世界有极强求生欲望，必须融入团体按固定规则做事才能生存。
+- 发言者3称日本投机取巧的人没有生存环境，社会文化的鄙视非常难过，所以不能生存。
+- 发言者3举例日本做绳子做到全日本第一的人，长达几年不赚钱，从批发处进货一分钱不赚送给客户，等把市场铺平后，拿单子跟两边各加2%，全国4%就是不得了的一个数。
+- 发言者2称慢慢走或者不偷奸耍滑，是一条更快到达成功的道路。
+- 发言者3称在这种文化中你愿意也做不成，你的文化不允许这种现象生存；强调忠诚最终一定要落到一个好处，所以这个民族才团结。
+- 发言者2称很不愿意做日本人，因为很多时候像盲从，而且他们有一种寻死的潜在欲望。
+二、日本生死观与忠诚
+- 发言者2称日本人看樱花不看发芽的时候，只看落那一天，由于常年以来生活在岛国上，生存条件太恶劣，对死亡不是藐视，是有点向往或者说不惧怕。
+- 发言者2称二战时日军到中国有那么多暴行，是一种藐视生命的行为。
+- 发言者3认为日本民族不是藐视生命，是重视死亡，是翻着的；剖腹自杀不是藐视生命，是重视死亡；经济危机时日本很多身家万贯的人剖腹自杀。
+- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
+- 发言者3称我们不能再用另外一个标准去评判它。
+三、明朝历史与明史研究
+- 发言者2表示写明朝是因为明史最熟，明史资料最多；历史界研究有两个难点，第一是先秦春秋，没史料，史记就那么一两篇，都是编的；第二是明清，明实录几千万字，明代史官的记录，明通鉴、明史纪事本末、明会典、纲目三编这些书堆得比山还高，但一个说法可能有7个不同，一个事件可能有7个不同说法，就好像罗生门。
+- 发言者3称明朝本身260多年的过程跌宕起伏，几次都要死没死了，土木堡之变、夺门之变各种之变特别多，皇上已经被瓦剌军抓起来了，哥几个一攒吧说那不算，又把弟弟扶起来了，完全构成一个现代版的电视剧。
+- 发言者1提到当年明月对朱元璋好像很推崇。
+- 发言者3称一个乞丐坐到最上面独此一份，刘邦好歹是个村长亭长。
+- 发言者2称推崇朱元璋因为他太不容易了，从一乞丐一直到最后推翻元朝当上了皇帝，定了多少规章制度，明朝的规章制度由他定下来，基本上没有什么太大的改动。
+- 发言者3认为人的因素最大，改变时势一定是出现一个人。
+- 发言者2称朱元璋天分相当高，举例李云龙没上过军事院校能打仗，会打仗的人打仗，不用看兵书，天赋。
+- 发言者1提到朱元璋的选择有点逼上梁山的性质，好友汤和让他去参加起义军，他在庙里犹豫，怕被杀头，后来因为信差送信被人告发，没办法只能去起义。
+- 发言者2称历史最重要的是你一定要弄明白它是发生过的，当年那是造反，于他而言是非常有风险的事儿。
+- 发言者3称历史你回过头看谁都是一个聪明人，你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
+- 发言者3称明朝有仁宣盛世，晚明时尽管史书上一再说政治如何黑暗、皇帝如何不上朝，但老百姓生活很好。
+- 发言者4提到金瓶梅写的西门庆是一个阶层。
+- 发言者2称明末那段时间很多真相是被掩盖的，市民生活特别轻松舒服，想去哪去哪，连皇册都不用了，到处走，去给人打工；当年江浙一带兴起了工商业，给人当雇工活得很滋润；三言二拍这种娱乐产品的出现说明有能够养活自己的资本；后来李自成闹起义是因为陕西那一带发生了大规模的灾荒。
+- 发言者3称从当时器皿可以看到人的生活乐趣，明末工艺变得非常精细，有点像日本的工艺，日本派了大量工匠跟中国交流。
+- 发言者2称看到的史料穿什么都有，至少江南那一带确实非常富足。
+- 发言者3称文征明、唐寅、董其昌都是那个时期的人。
+- 发言者3称一到朱搭的时候，八大山人明末了，画的都是翻白眼，前面无文化派的人画的都是小桥流水。
+- 发言者2称历史经验教训说多少次了，我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+- 发言者2称历史那个事儿发生的时候是有背景的，你不比前人聪明，甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
+- 发言者2称史书上记载下来是照片，而实际上古人的生活都是录像，你不知道为那一幕之前跟之后是什么，不知道当时为什么要做这个选择，所以千万不能套用，套用那一定要倒霉。
+- 发言者2称明代这个朝代很有趣，什么事都有，宦官专政魏忠贤、刘瑾，文官专政张居正，皇帝专政朱元璋、朱棣，谁都可能当老大，而且什么都能发生，皇帝出去了还能回来了，还能做皇帝。
+- 发言者2称晚明时期吴三桂跟满清合作要入关，陈圆圆是一个原因，还有一个原因是他认为崇祯死了，当时说法是我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝。
+- 发言者2称1644年明朝灭亡那一年，李自成军打到京城没有人抵抗，因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天看疙瘩瘟就是天花。
+- 发言者3称中国的历史王朝300年都是大限，一逼近300年的时候你自己就没就完了。
+- 发言者3称中国历史上如果严格讲跨过300年大限的只有宋朝，南北宋接上以后，退让了大半个国土，保证了它延续了319年；汉朝中间隔断14年是彻底空的；唐朝明朝清朝都没跨过这个界限。
+- 发言者2称今天数世界上公司超过276人的有几家呢，没有几家，明朝做公司多大摊子几千万人。
+四、明朝皇帝与晚明社会
+- 发言者1提到一种观点说明朝和清朝在美这方面，故宫金碧辉煌大红大紫是满族人的趣味，真正明朝不是这样。
+- 发言者3称宋明两个朝代是典型的汉人政权，汉人是文人政权，对美的判断不是表象的；满族是异族，对美的判断都是表象的；今天凡是那种非常外在美直观能看到美的都卖得非常贵，但在100年前晚清到民国初年的收藏，这种东西都不值钱，一定是素雅的。
+- 发言者2称明朝皇帝是九五至尊，但皇上说要去一趟江南，大臣说不行就不行，明武宗正德皇帝要去，不让去，全跪金水桥前面，后来气坏了到锦衣卫去打，打死了十几个，还是不让去。
+- 发言者1提到明朝有些史官就是要跟皇帝说点难听的，让你砍我的头，这样我青史留名，冒死就为了个名。
+- 发言者3称这就是文化的力量，文化的力量是一个超出我们想象的力量。
+- 发言者2称明武宗正德后来打服了一批人，非要去不去不行，到扬州说我要什么东西，政府说没有东西没有了，有也不给，皇帝不生气，说那我就回去，还让人准备酒席，然后说吃不了，你们把酒席折合成银两，我带回去。
+- 发言者3称正德皇帝是明朝整个皇帝中最特殊、最鬼怪的一个个性，过去对他的评价非常低，说他荒淫，豹房是他弄的。
+- 发言者1提到一个爱当木匠的皇帝，发言者3称那是天启，直接干活，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好，他成就感特大。
+- 发言者3称这从侧面反映了当时社会的一种时尚，当时家具在每个人心目中地位高，明式家具现在在国际上那么高的地位绝对不是偶然的。
+- 发言者2称明代皇帝本身确实也没什么事干，明神宗几十年不上朝，但他不出去。
+- 发言者2称但凡是明朝的皇帝，后人不会说前朝自己朝代的皇帝多差，正德特别差是因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以不能够把他写得太好。
+- 发言者2称正德皇帝被说特别荒淫，豹房其实就是玩的地方，里边养了豹子，有动物园，女人肯定是有的，但在后宫也是女人，不影响其他什么问题。
+- 发言者3称正德皇帝是有定论的说明朝最荒淫的皇帝，清朝最荒淫的是咸丰，咸丰还留了个种，正德不留种，没少找女人但没有生育能力。
+- 发言者3称正德皇帝对宫廷以外的女人都有兴趣，宫廷内的女人确实没兴趣，因为宫廷内的女人被训练过，禁忌太多，太保守。
+- 发言者2称据说正德去过，但没有具体的史料能够确实，史料没法记。
+- 发言者2称正德从江南回来，没有进京城，在通州先停了半天，先派人打探，这是史料记载的，先停在这儿，你们先给我把情况看清楚了，京城里有没有人想搞埋伏搞圈套，非常有城府。
+- 发言者2称明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般都有某些程度的偏颇，因为嘉靖上台先搞了个大礼仪事件，为这事死了很多人，为给自己父亲争个名分，他父亲是王爷，他要把他追封为皇帝。
+- 发言者1称很多人研究历史就有傲慢与偏见，没有设身处地，老觉得自己聪明，判断他昏庸无能。
+# 关键引语与金句
+&gt; 慢慢来才是最快的方法。
+&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+&gt; 历史最重要的是什么呢？就是你一定要弄明白它是发生过的。
+&gt; 史书上记载下来是什么。照片，我打个比方是照片照片，而我们实际上我们的生活，古人的生活都是录像。
+&gt; 你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
+&gt; 文化的力量是一个超出我们想象的力量。
+&gt; 所有人按照自己的角色去做自己的事情，最节省成本了，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
+&gt; 我是商人就做商人的事儿，我是奶妈就做奶妈的事儿，我是王后就是王后的事，我什么都可以做自己的事，就是不管别人的事。
+&gt; 中国的文化精神是什么？是中庸。
+&gt; 日本的精神就恰相反，他坚持一个原则。
+&gt; 一个乞丐对有这个历史上有这种最底层的人坐到最上面独此一份。
+&gt; 他太不容易了，我们今天说你做个什么事能做成呢？这人从一乞丐一直到最后推翻元朝当上了皇帝。
+&gt; 历史你回过头看谁都是一个聪明人，你当时都不聪明。
+&gt; 原话引语……</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>14719/5104</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1" s="9">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>• 发言者 1 00:05
 你好，我姓严，
 • 发言者 2 00:06
 是这里消化专科的医生，我想了解一下你的病情，先核实一下你的名字好吗？我叫张学恒，好，这样我就好称呼你。张先生你好，多大年龄了？48岁。那你这次来看病主要是哪里不舒服？
@@ -3923,9 +5060,44 @@
 要做胃镜的话，我想能不能给我安排在后天，因为我爱人她后天可以请假，我想有一个人陪同也比较方便一些，
 • 发言者 2 24:46
 那也行，我们后天也是做胃镜。的时间，那我们就可以先预约在后天吧，到时候你做了胃镜活检以后，正好我们张大夫查房，这样的话安排应该来说还是比较好的。那很好好的。那就这样子，我把你的情况先总结了，以后向张医生汇报，然后我们下一步再来讨论关于治疗的问题，你看你还有什么问题需要再询问我吗？其他的没什么问题了，没有什么问题了，那你就先休息好吧？好的，谢谢再见。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:05
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>就医咨询</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t># 就诊概况
+患者张学恒，48岁，成都人，在成都轻工研究所从事科研工作，本次就诊于消化专科。主诉上腹反复疼痛3个月，4年来经常发作、每年春天较多，心窝处有烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大，疼痛可忍受、白天发作、无夜间痛醒；曾出现两次黑大便，一次一年前、一次三个月前，均查大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后转黄；最近两个月吐过几次黄水样酸的东西，晚上胀想吐、吐后舒服。既往16岁得过甲肝、在三医院住院一个月、出院各项指标正常，对磺胺药过敏，无手术史。医生表示等检查资料更全面后再判断是否需要手术，能药物控制治好就不用手术；要求患者留大便做检查，胃镜预约在后天进行，并将在总结情况后向上级医生张医生汇报再讨论治疗。
+# 诊断与检查结果
+医生本次未给出明确诊断结论，表示等检查资料都更加全面以后再判断是否需要做手术，临床上有很多药物对消化系统疾病有很好的治疗效果，若能用药控制病情治好就不用做手术。关键检查方面，患者曾两次因黑大便查大便提示大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后大便转黄；最近三个月大便均为黄色、无灰色大便，小便正常。患者自述有低血压约90/60，父亲76岁也有低血压；母亲75岁诊断冠心病、吃药控制较好。本次就诊尚未做检查，医生要求留大便做检查以了解有无相关出血，并安排胃镜及活检。
+# 治疗方案与医嘱
+用药方案：患者自述最近一直吃药，先服“大叔”，刚开始一天两次、每次一颗有效，后效果越来越差、量加至每天四五次仍不好；又开过武汉药厂国产`奥美拉唑`和`阿莫西林`，还吃所里医务室配制的胃炎合剂，反复用药反复发作。治疗计划：医生要求患者留大便做检查，因曾两次黑便需了解有无相关出血；胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结情况向上级医生张医生汇报后再商量下一步处理意见，是否需要手术待检查资料更全面后判断。生活注意事项：医生指出经常熬夜对疾病有一定影响，**以后还是得注意**；**抽烟对疾病有影响，应尽量少抽或不抽**，患者已限制在10支以内并想慢慢戒；**酒对胃上的疾病影响挺大**，患者有便血情况，以后需注意；医生建议尽量少喝酒、若能戒烟对疾病有好处。
+| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
+| --- | --- | --- | --- | --- |
+| 大叔 | 最初每次一颗，后加量 | 最初一天两次，后加至每天四五次 | 口服 | 刚开始有效，后效果越来越差，加量后效果仍不好 |
+| 奥美拉唑 | 未明确 | 未明确 | 口服 | 武汉药厂国产；刚开始吃有些效果，停药后反复出现疼痛 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同开，具体剂量频次未明确 |
+| 胃炎合剂 | 未明确 | 未明确 | 口服 | 所里医务室自己配制，效果反复 |
+# 复诊与预警信号
+复诊时间：胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结患者情况后向上级医生张医生汇报，再回来与患者商量下一步处理意见。需立即就医的预警信号：原文未明确列出具体预警症状，医生要求患者留大便做检查，因曾出现两次黑便，需了解有无相关出血。</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>8519/1371</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1" s="9">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:05
 现在开始法庭纪律，在合议庭审判长宣布开庭时，请诉讼各方参与人全体旁听人员起立，一是对法庭的尊重。二，诉讼各方参与人与全体旁听人。在执行任务中依靠服从法庭的指挥，尊重司法，遵守法庭纪律，不得实施下列行为，一鼓掌、欢呼，二吸烟、进食，三拨打。接听电话，四对庭审活动进行录音录像、拍照或使用移动通信工具等传播庭审活动，五其他危害法庭安全或妨害。
 发言人 1  00:00:45
 自己的什么？诉讼参与人发言的时候，应当经法庭许可。四、旁听人员不得进入审判活动区，不得随意站立、走动，需要发言的，应当。建议在庭审过程中，诉讼参与人的诉讼人的办法和秩序，情节较轻的，审判长可以警告、训诫、责令退出法庭。看春晚，集结每一个开心观众的心。请对谁上来可以打我的敌人。
@@ -4863,9 +6035,67 @@
 现代化。今天的庭审到此结束。闭庭后，请各方当事人。越看题目。没有，你用，我才能做，可以申请。所以。
 发言人 3  01:48:32
 现在闭庭。原题及亲子代表是代表。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:25
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>庭审记录</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t># 庭审概况
+本案系国家开发银行因与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，对本案公开开庭审理，各方当事人均已到庭，法庭准备工作就绪。庭审围绕三个争议焦点展开调查辩论：一是抵押权与融资租赁所有权冲突及善意取得，二是罚息、复利计算，三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。
+# 原告诉称与被告辩称
+见下表。
+| 方 | 诉讼请求/答辩意见 | 事实与理由 |
+| --- | --- | --- |
+| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利计算及违约金请求 | 已按人民银行规定程序完成贷款抵押刑事审查、资料审查、法律审查；2018年9月查询曲靖电力公司租赁情况无融资租赁登记；2018年核查表（证据108页）显示曲靖电力公司名下仍无融资租赁登记；评估报告明确曲靖电力公司在建工程价值5.7亿、机械设备价值5.1亿；设备为通用设备无唯一标识，只能对抵押人名下信息调查；抵押设备金额、使用上均明确为曲靖电力公司；借款合同第24条第三项约定千分之一违约金，东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约 |
+| 被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司 | 主张2018年6月13日宣布贷款提前到期不符合合同约定，未给合理期限；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金，应予驳回 | 2015年12月2日邮件发送时间与2015年12月20日签订抵押合同时间吻合；统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务；借款合同第24条第二款第二项约定宣布提前到期应发通知并限期偿还，限期偿还与立即偿还概念不同；人民币利率管理规定第21条针对贷款期内不能按期支付的利息计收复利，不包括逾期罚息；东源公司以煤炭开采为主营业务，2015年下半年资金链断裂，2019年2月19日破产重整受理时负债76.2亿元，2016年去产能安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠 |
+| 被上诉人招银金融租赁有限公司 | 主张国开行未查询人行征信中心融资租赁登记，不构成善意；东源煤电出资行为系无权处分；招银租赁2012年即取得租赁设备所有权 | 2012年8月对东源煤电相关设备进行物权确权审查，要求提供六项设备买卖合同、大部分发票及到货确认单；设备交付到货即取得所有权，招银租赁同时获得租赁设备所有权；国开行2015年办理抵押登记，时间在后且未进行相应审查义务；融资租赁登记系统初始登记附件清单载明设备名称、数量、进场时间、生产厂商及存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台；设备唯一标识码非必填项，暗设五套设备当时刚交付无唯一识别码故未登记 |
+# 举证与法庭调查
+## 一、举证与质证
+### （一）国开行举证
+1. 2018年9月对曲靖电力公司租赁情况的查询证书（第五组证据第一项），用以证明已对融资租赁登记信息进行核查。招银租赁质证认为该查询证书不符合要求，根据201493号中国人民银行关于融资租赁登记系统规定，国开行在操作抵押时点未查询人行征信中心结果，无论以设备名义还是以电力公司名义查询，均未进行相应查询。
+2. 证据四冶合成58亿，含东源煤电公司、曲靖电力公司对案涉设备的权属证明，用以证明设备所有权确属曲靖电力公司。
+3. 2018年核查表（证据108页），用以证明2018年再次核查曲靖电力公司名下仍无融资租赁登记信息。
+4. 2015年12月2日邮件及统计表，东源方用以证明已告知设备融资租赁情况。国开行质证认为该邮件正文及附表均无设备存在融资租赁的文字，统计表中招银租赁一栏记载的融资额度及抵押类型为不动产抵押，看不出东源方履行过告知义务。
+### （二）东源方举证
+1. 2015年12月2日邮件及融资情况表，主张邮件发送时间与2015年12月20日签订抵押合同时间吻合，统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务。
+2. 东源公司经营困难情况说明：以煤炭开采为主营业务，2015年下半年出现资金链断裂，2019年2月19日人民法院受理破产重整时点负债高达76.2亿元，2016年响应去产能政策安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠。
+### （三）招银租赁举证
+1. 一审提交证据7页回租设备清单，载明设备名称和生产厂家，未提及设备型号。国开行质证认为即便提交该清单，开行角度亦无法对设备进行同一性测试；清单提示2012年3月1日，而抵押设备铭牌记载生产日期均在2013年以后，部分为2013年11月、2013年12月、2014年3月，看不出是同一设备。
+2. 2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4个亿且已实缴。国开行认为招银租赁有理由知道或应当知道设备出资情况。
+3. 融资租赁登记系统初始登记附件清单，含设备名称、数量、进场时间、生产厂商及存放地点，显示存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台。
+## 二、法官询问要点
+1. 合议庭询问各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果。国开行认为系行业强制性规范，目的是防范动产设备多处抵押或融资冲突；招银租赁认为系行业性质、非物权法定登记，仅强化动产权利外观、可能产生对抗效力，不影响所有权设立转移；东源方认为系行业指导性规范文件，非强制性，不当然产生物权后果。
+2. 合议庭询问央行金融租赁查询方式能否保证查询到登记结果。国开行称能使用的查询方式就是查询单位；招银租赁称可通过公司名称或设备两种方式查询，以设备查询涉及种类物区分问题。
+3. 合议庭询问设备唯一标识码是否为必填项。招银租赁称不是必填项，发电机组铭牌只有型号和参数，无发动机号类唯一标识；暗设五套设备当时刚交付、无唯一识别码，故未登记。
+4. 合议庭询问国开行内部风控是否规定必须查询、未查到是否需将未查到单据作为风控材料。国开行称办理动产抵押时需调查该系统并筛查，因无表现故未保留筛查记录，内部无此规定。
+5. 合议庭询问国开行认为未查到登记结果即可免责的逻辑。国开行称按央行规定查询融资租赁系统，抵押人为曲靖电力公司，查询后系统无记载，2018年6月截图亦无显示，至今无结果，说明行为无过失。
+6. 合议庭询问若通过其他渠道知道抵押设备存在租赁是否仍需查询。招银租赁称仍需通过央行系统查询，央行规定出台背景是实践中大量存在此类案例，只有确定标准才能衡量双方是否善意。
+7. 合议庭询问各方如何看待因不同登记机构产生登记瑕疵。国开行认为涉及人民银行融资租赁登记系统与动产抵押登记的冲突，系统信息不完整、体系相互隔离、信息不流畅，未形成相互联通，可能带来交易风险；东源方称非专业机构，提供不了相关建议；招银租赁认为规范不统一、登记机构不统一、信息不对称，建议从立法层面统一对金融主体和市场主体要求，发挥行业协会作用，从操作和技能方面推动登记平台统一化。
+## 三、双方辩论的争议焦点
+1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已尽合理审慎义务、构成善意取得；东源方主张邮件已告知且设备名称相同并用红色标注、国开行应尽注意义务；招银租赁主张2012年即取得设备所有权、国开行2015年办理抵押时未查询登记、不构成善意。
+2. 罚息、复利计算：国开行主张利息自2017年12月21日至2018年6月12日合计2179万5727.08元、罚息自2018年6月13日至2019年2月19日合计4105万零579.57元、复利自2018年3月21日至2019年2月19日合计191万8206元；东源方主张2018年6月13日宣布贷款提前到期不符合合同约定、未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
+3. 违约金连带责任：国开行主张依借款合同第24条第三项约定应支付千分之一违约金、东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约；东源方主张国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金、应予驳回。
+# 庭审结果
+本案争议焦点为三项：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息、复利计算；三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字。经本院主持调解，各方当事人自愿达成调解协议，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。调解方案主要内容：确定国开行对东源公司债权扣除破产中已清偿本金外，利息2017年12月21日至2018年6月12日合计2179万5727.08元、罚息2018年6月13日至2019年2月19日合计4105万零579.57元、复利2018年3月21日至2019年2月19日合计191万8206元，三项共计6474万4513元；确定招银租赁对涉案六项设备享有所有权、对应债权数额1377万4137万元，确定国开行对93项设备有抵押权，双方对案涉全部发电设备整体盘活处置并从变现款中实现各自债权，生效20日内由国开行向一审法院提出执行申请启动司法变现，变现价格双方各50%、实现费用双方各担50%；变现款不足清偿债务或变现后招银租赁未实现债权，在执行法院处具体本裁定后按破产重整计划中预留方案实现债权，破产管理人对招银租赁债权予以纳入预留方案，由东源煤电按此前招银租赁在东源煤电破产重组程序中有担保清偿方案予以清偿；如司法变现不能实现国开行和招银租赁权益，通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营；各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认；一审诉讼费用中对于国开行诉请部分按一审判决执行，对于招银租赁诉请部分诉讼费由二审法院按规定根据证据确定，二审诉讼费由本院依法确定。合议庭指出本案涉及生产设备的动产抵押权与融资租赁物所有权冲突是司法实践中普遍性难题，金融风险防控还有较大空间，根本原因在于国家还未建立统一的动产登记制度，现有动产融资租赁登记系统和动产抵押登记系统缺乏有效衔接，将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议，共同推进国家治理现代化。</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>30731/4434</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1" s="9">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:25
 画面是完整流程大公开。
 发言人 2  00:00:31
 各位，早上好。考生你好，欢迎参加今天的面试。今天的面试一共20分钟，回答4个问题。请合理把握好时间，逐题回答。答题时不要紧张，语言尽可能简洁明了。在你面前有一张题纸和草稿纸，请不要在题纸上做任何记录。如果你准备好了，现在就开始答题，请计时员计时。
@@ -4955,9 +6185,45 @@
 好，今天的面试到此结束，感谢你的参与。
 发言人 3  00:17:34
 谢谢各位考官，各位考官辛苦了。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:11
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>面试报告</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t># 候选人概况与面试岗位
+本次为公务员面试模拟，面试共20分钟、回答4个问题，考生确认准备好后由计时员计时，题纸和草稿纸可用但不得在题纸上做任何记录。考生依次作答四题：第一题围绕骏马、风筝、陀螺三句绳子意象谈对公务员工作的启示；第二题以市政府办公室工作人员小王身份谈如何组织本市AI相关企业调研；第三题以市级服务标兵小王身份现场模拟答复记者关于地下排水管道返堵的质疑；第四题从公共服务角度谈道路改造与雨污分流工程扰民矛盾的处理思路。四题均作答完毕，考官询问是否还有需要补充的内容，考生表示没有要补充的，面试到此结束。
+# 能力评估
+按专业/技术能力、项目经验、沟通协作三个维度评估，评级与依据见下表。
+| 评估维度 | 推荐评级 | 评估依据（具体事例） |
+| --- | --- | --- |
+| 专业/技术能力 | 良 | 第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省（吾日三省吾身）、权利与责任（权利清单、责任清单）、连轴转的动力（基层与机关加班加点、材料撰写中的责任感与成就感）；第二题提出查阅国务院、中央办公厅人工智能发展指导意见及省厅相关举措，制定包含客观与主观两方面、分市场状况、服务需求、管理措施三部分的调研方案；第四题区分主要矛盾与次要矛盾并提出防噪墙、洒水降尘等具体措施。 |
+| 项目经验 | 中 | 第二题以市政府办公室工作人员小王身份提出AI相关企业调研的组织实施思路：先补课充实AI知识储备、学习兄弟城市调研经验、摸清上级领导和中央部门指示要求；与企业对接阅读发展报告、制定调查问卷并请单位AI专家学者修改完善、以座谈会形式听取企业意见，询问人才对口引进、政策倾斜、用地审批、人才吸引机制和长效培养机制等具体服务需求。 |
+| 沟通协作 | 良 | 第三题现场模拟答复记者时先询问记者姓氏并自称片区负责人小王，说明管道为上世纪90年代社区集中整治时所修建、城区属老城区改造难度大、夏天用水高峰问题集中出现，表示已联系维修师傅正赶往现场维修，长久管道硬件问题已汇报上级部门，将通过城市综合保障工程完善硬件、改善基础设施，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题提出通过交通广播推荐出行路线、加强宣传引导市民多使用公交、以公告形式在网络上发布政府举措。 |
+| 应变与时间管理 | 中 | 面试共20分钟、回答4个问题，考生确认准备好后由计时员计时；第四题作答中收到“离本场考试结束还有3分钟”提示，考生误称“考生开始回答第三第四题”，随后完成作答；考官询问是否还有需要补充的内容，考生表示没有要补充的。 |
+| 岗位匹配度 | 良 | 第一题提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第三题承认工作有失职之处，希望媒体给予改进机会；第四题提出将政府各种举措公正公开透明表达出来以获得市民理解和支持。 |
+| 面试表现 | 良 | 四题均作答完毕，第一题、第二题、第三题、第四题均以“考生作答完毕”结束；第三题以现场模拟方式完成答复；第四题因时间提示未进一步展开。 |
+| 潜在风险点 | 中 | 第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”。 |
+# 综合素质
+突出亮点：第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省、权利与责任、连轴转的动力，并引用“吾日三省吾身”，提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第二题提出先补课充实AI知识储备、学习兄弟城市调研经验、查阅国务院及中央办公厅人工智能发展指导意见与省厅相关举措，制定包含客观（企业发展现状）和主观（政府应提供的服务需求）两方面的工作方案，分市场状况、服务需求、管理措施三部分调研，方案呈报领导审阅后按意见修改实施；第三题现场模拟中承认工作有失职之处，希望媒体给予改进机会，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题区分主要矛盾（时间上过去、现在和未来的诉求和需求不满足）和次要矛盾（噪音污染、出行问题、舆论问题），提出防噪墙、洒水降尘、交通广播推荐路线、引导市民多使用公交、以公告形式在网络上发布等具体措施。潜在风险点：第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”，且因时间提示（离本场考试结束还有3分钟）未对第四题作进一步展开。推进建议：原文未提及。</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>5808/1866</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="13.5" customHeight="1" s="9">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:11
 您早点过来排队，排队检票这个地方就是午门，这过去可不是斩首的地方，明朝皇帝在这杖打那些犯了错的大臣，清朝皇帝在这颁发第二年的历书，也叫颁朔之礼。从这个角度看，午门有三个门洞，进门之后您能看到，哎，变成五个门洞了，这就是我们常说的明三暗五，故宫跟天坛不一样，在这呢，皇帝是老大，所以中间那个正门。
 发言人 1  00:00:40
 只能皇上走，也有例外啊。皇上大婚的时候，皇后可以从这个门进一次。殿试考中前三名的，也就是状元、榜眼、探花，这哥仨可以从这门出去一次。旁边那两门走的是皇亲国戚和文武百官。进来之后，咱们现在的位置就是。这是太和门广场，眼前有五座金水桥。想过皇帝引的走中间，黄金国器走挨着中间这两座桥，文武百官走最边上。
@@ -5009,9 +6275,57 @@
 第二条游览路线是进门之后沿着中轴线往后走，看完了坤宁宫，咱们去看景仁宫和延禧宫，紧接着去逛钟表馆和珍宝馆。出来之后直奔御花园，完事呢从神武门就出去了，大概半天的时间就能逛完。最后一条路线比较适合那些时间有限，不想走太多路的朋友们，还是进门沿着中轴线往后走，看完了坤宁宫之后去储秀宫，出来去御花园，然后呢从神武门出，这条最省力的路线，预计2个小时左右就能逛完。
 发言人 1  00:12:49
 对于那些喜欢盖章的朋友们，我也给大家标注了七个可以免费盖章的位置，有需要的章友们可以截图保存。行了啊朋友们，关于故宫的。保姆级游览攻略到这就讲完了。如果您觉得这期视频对您有所帮助，求关注、求点赞、求转发，您的支持就是我最大的。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:15
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>参观游览</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t># 参观概况
+本次讲解沿故宫中轴线及东西六宫展开，依次介绍午门、太和门广场、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、东筒子夹道、延禧宫、景仁宫、御花园、神武门等景点。午门为排队检票处，明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官；太和门广场五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。太和门为明朝御门听政处，门口铜狮为故宫六对铜狮中最大一对；太和殿即金銮殿，用于皇帝登基、皇后册封等盛大典礼，文武百官文东武西，西边弘义阁为皇帝银库，东边体仁阁为缎库。中和殿为典礼时皇帝休息室，保和殿自乾隆五十四年起为科举殿试考场。乾清门为皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边为军机处；乾清宫为皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。交泰殿放25块传国玉玺，坤宁宫住皇后，明朝所有皇后都住此。储秀宫为慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，其子在此出生；慈宁宫为康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真；珍宝馆也是宁寿全宫，为乾隆给自己修建的养老院，退休后没放权仍照常上朝，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室。神武门为紫禁城北门，出门左手边有两个盖章点。讲解者总结三条游览路线，并标注七个可以免费盖章的位置。
+# 核心看点与讲解
+## 午门与太和门广场
+午门是排队检票处，明朝皇帝在此杖打犯错大臣，清朝在此颁朔；午门明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官。太和门广场有五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。
+## 太和门与太和殿
+太和门是明朝皇帝御门听政处，门口铜狮子是故宫六对铜狮中最大一对，建议不要站在底下合影。太和殿即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封；文武百官在太和殿广场朝拜，文东武西。西边弘义阁是皇帝银库，东边体仁阁是缎库。
+## 中和殿、保和殿与汉字馆
+中和殿是盛大典礼时皇帝休息室。保和殿从乾隆五十四年起为科举殿试考场。保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章；故宫不止一处可买紫禁城100，每家店印章不同，买了之后不能去其他店铺盖章，汉字馆印章数量据说最多，可邮寄或自背。
+## 乾清门与后宫区域
+乾清门是皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边是军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫不该看不该听。进门后乾清宫是皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。门口铜鹤铜龟旁有设计江山金殿，是紫禁城最小宫殿。
+## 交泰殿、坤宁宫与御花园
+交泰殿放25块传国玉玺。坤宁宫住皇后，明朝所有皇后都住此。坤宁宫东北角文创店有5枚免费印章。御花园有钦安殿，供奉真武大帝。
+## 储秀宫、慈宁宫与冰窖书吧
+储秀宫是慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，她儿子在此出生；旁边文创店有3枚免费印章。往南是翊坤宫和永寿宫，永寿宫西边太极殿是东西六宫唯一被称为殿的。慈宁宫是康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。冰窖书吧有3枚免费印章，印章造型好，讲解者在此买了冰嬉图。
+## 断虹桥、武英殿与文华殿
+断虹桥是网红打卡地，石狮子形态各异，最有名的是武当狮。断虹桥往西是武英殿，后改陶瓷馆，目前关闭只能在门口看。往东穿过太和门广场到文华殿，讲解者去时未开，据说现在有展览。
+## 箭亭、钟表馆与珍宝馆
+箭亭是清朝皇帝及子孙练习骑马射箭处，旁边商店可买文创雪糕。钟表馆展示各年代钟表。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真。珍宝馆不是单独展厅，院子周围屋子都可进；游客太多，看凤冠没点技术挤不进去。珍宝馆也是宁寿全宫，乾隆给自己修建的养老院，退休后没放权仍照常上朝。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室，有二龙仙楼设计。再往后是珍妃井，井口石小眼不是珍妃进去的地方。珍宝馆出口右手边商店有3枚免费印章。
+## 东筒子夹道、延禧宫与景仁宫
+东筒子夹道是很多小姐姐喜欢来的拍照出片地。往南拐弯到网红打卡地延禧宫，旁边景仁宫是甄嬛被封熹妃时住处，珍妃也住过。逛完景仁宫可去御花园。
+## 神武门与盖章点
+神武门是故宫紫禁城北门。出门左手边有两个盖章点：角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
+# 互动与体验
+讲解中介绍了多处盖章体验：保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章，讲解者称这感觉真是盖了帽了，并提到故宫里不止一处可以买到紫禁城100，每家店里的印章有所不同，买了之后不能去其他店铺盖章，据说汉字馆印章数量最多，盖完可选择邮寄到家或背着走。坤宁宫东北角文创店有5枚免费印章。储秀宫旁边文创店有3枚免费印章。冰窖书吧有3枚免费印章，讲解者称盖章时有批折子的感觉，并在此买了一个冰嬉图。珍宝馆出口右手边商店有3枚免费印章。神武门出门左手边角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。讲解者还提到箭亭旁边商店可买文创雪糕，并询问雪糕上的人物是谁。讲解者建议不要站在太和门铜狮子底下合影，单独给它拍张照即可。
+# 收获与建议
+讲解者总结三条游览路线：第一条走完视频内所有景点，早起排队一进门沿中轴线往后走，可错开旅游团，适合打算待一整天的朋友，一天走了3万步，注意休息补水；第二条进门沿中轴线往后走，看完坤宁宫去景仁宫和延禧宫，再逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天；第三条适合时间有限不想走太多路，进门沿中轴线往后走，看完坤宁宫去储秀宫，出来去御花园，从神武门出，预计2小时左右。视频标注了七个可以免费盖章的位置，有需要的章友可截图保存。讲解者强烈建议来珍宝馆，并提醒珍宝馆游客太多，看凤冠没点技术挤不进去。</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>4497/2520</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="13.5" customHeight="1" s="9">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:15
 随着刚需房的推广，留守儿童问题逐步缓解，而留守老人的困境
 发言人 2  00:00:22
 却还
@@ -5139,9 +6453,40 @@
 在社区举办的送春联活动中，老书法家写下的福字，由孩子们传承，又传递给千家万户的留守老人。这大红的福字，承载着社工们为社区和谐付出的辛劳与汗水，连接着孩子、家长和留守老人，接续着尊老爱幼的中华传统，也象征着每一位国人对和谐社会的。解决养老问题绝非易事。这不仅需要政府的关心和重视，也离不开子女、社区乃至更专业的养老服务机构的耐心陪伴与关怀。
 发言人 1  00:41:08
 视频的最后，祝每一位老人都能安享晚年，病有所医，老有所养，住有所居，弱有所扶。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:30
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>调研访谈</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概况
+本次访谈走访了农村老人、村干部与民政局干部、城市社区社工等对象，目的是了解农村养老制度与城市社区养老经验，探讨解决乡村养老问题的启示。核心议题包括留守老人与独居现状、农村养老政策与困境、城市社区志愿者制度与养老服务中心、社工制度困境。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住；农村方面2021年公安数据为73万多、占比约17.8%，预计老龄化程度会越来越严重。受访者普遍反映独居老人存在无人照料、无人慰藉、就医困难等问题，农村空巢老人面临无亲人陪伴、经济困难、子女不在身边、生病住院麻烦、娱乐方式少等困境，城市社区则以志愿者一对一帮扶和养老服务中心应对，但社工制度面临需求大而供给不足、资金有限、专业人才欠缺的困境。整体反馈基调为如实陈述现状与困难，并呼吁政府、子女、社区及专业养老服务机构共同关怀。
+# 核心反馈
+**独居老人无人照料、无人慰藉、就医困难**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住，独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自一人在家中发生意外。典型场景包括：黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认因一个人在家太寂寞、想找个人聊聊天才报了警；上海一名67岁独居老人在家中去世，直到多日之后家中满出刺鼻气味才被邻居发现；杭州一小区一名67岁独居老人不幸在家中去世，数天之后才被发现。
+**农村空巢老人经济困难、子女不在身边、生病住院麻烦、娱乐方式少**：村干部与民政局干部反映，空巢老人可能面临的问题第一是没有很多亲人来陪伴，第二是经济比较困难，这个地方经济不太发达，生病、锻炼等都受影响，子女不在身边一旦生病住院就比较麻烦，娱乐方式少，只能坐在一起聊聊天、打打牌。有受访者说：&gt; 现在80%都是都提醒这个在外面做做这些事的，年轻人都卖出去了。
+**农村养老公共设施运营经费后续没有支持**：干部介绍，之前其实也探索过在一些农村建养老公共设施，提供日托、休闲娱乐、沟通交友的平台，但不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的。
+**城市小区留守老人社交机会更少、易孤独抑郁**：相比之下，城市小区中的留守老人们与外界社交的机会更少，更容易产生孤独、抑郁等情绪。社工谈到曾帮助一位存在心理问题的老人，其与邻里关系处理不和谐、半夜摔门，社区派志愿者上门但老人出现抗拒，觉得周围的人都是陌生的、没有关心他的人，内心可能有一点仇恨式的；经日复一日关心照料后，现在与邻里关系还算好了，能够理解一些、也可以接受一些意见，之前是不接受任何人的建议的，他今天都打来电话说寂寞空虚、得不到人关注。
+**社工制度需求大而供给不足、资金有限、专业人才欠缺**：社工姐姐认为，目前社工制度的困境主要在于社会需求量大而供给不足，由于政府和社区资金有限，难以承担长期的专业社工服务费用，人民的需求得不到满足，大量社工迫于生计选择转行，这同时也阻碍着社工行业的长期发展。每个街道和乡镇派了两名社工驻点，主要围绕老人、小孩这一类去服务，但说实在话也很难能够走下来；社工行业工资都比较低，会影响就业率，基本上很多同学没做多久就垮了，可能不超过一年。服务需要花钱购买，不一定能够今年服务了、明年又能服务，要看领导能不能争取到这样的项目，一年的服务成效并不是那么的明显；资金拨不下来了，项目也结束了，但服务成效不一定就达到了。整个湖南省有这么大，这个街道也要花十来万块钱，省里还是拨了钱的，但很多社工并不是专业的、学社工专业出来的，在专业上其实还是很欠缺的。
+# 关键洞察与建议
+核心洞察：农村与城市留守老人问题均突出，农村空巢老人受经济困难、子女不在身边、娱乐方式少等多重因素叠加影响，城市小区留守老人社交机会更少、更易孤独抑郁；农村养老公共设施建设存在只考虑建设、不考虑后续持续运营经费的问题；社工制度面临社会需求量大而供给不足、资金有限、专业人才欠缺、服务成效不易显现的困境。受访者提出的建议与偏好：一是请专业施工人进行陪伴；二是尽量倡导在外务工的子女多跟他们联系；三是丰富他们的文化生活，能够有更多的娱乐方式；四是希望老年协会能够专项执行、专门建养老设施，有一个固定的场地，定期可以有一些施工人员或宣传，如板报宣传或健康知识讲座，并要给一个持续运营的经费，不管考虑建设还要考虑后续的持续运营，才能更好地发挥作用。城市社区方面的做法与倾向：志愿者制度实行一对一帮扶，通过定期表彰、志愿者积分兑换、雷锋超市兑换礼品让志愿者长期坚持；今年做小手拉大手，从儿童青少年着手拉动家长加入；周四准备开展送春联活动，邀请书法老师写对联让孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴，让大家感觉社区就是一个大家庭；2023年的目标是家长他们自己来组织，社区作为一个协助者。受访者还表示，解决养老问题绝非易事，不仅需要政府的关心和重视，也离不开子女、社区乃至更专业的养老服务机构的耐心陪伴与关怀。</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>5309/2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13.5" customHeight="1" s="9">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:30
 睡觉。
 发言人 2  00:00:38
 不是。做了这个水费险啊，你卫生不具备啊，不是200元啊，当然喝够喝完了的话不够了啊，我们再讲啊，大家讲的话是每周每周是每两周，是每个月是2块钱一块，
@@ -5731,9 +7076,38 @@
 这点我觉得
 发言人 2  00:49:14
 我们他们也会非常关注啊，都会主动问老师吧。今年是预报预报一些非常好了啊，比如我一包板子的话。一般都会说出来这个今年应该是我们的，但是他们他们教育这一块。大家如果没写的话，可以写。大家可以坐下，你看呃，如果有什么没听懂，然后各位家长如果有什么要补充的，也可以。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:16
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>家校沟通</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t># 沟通概况
+本次372班家长会由班主任林瑞主持，面向全体家长，围绕费用与反诈、班级基本情况、教师团队、班级存在问题及解决思路、给家长的建议等板块展开。费用方面，书费预交11000元尚未结算，书箱未购买部分将退费，相关费用约100元或70元、4000元购买、700元、120元、123元等；明确不在微信群收取家长任何费用，费用由学生交给生活委员，并提醒家长和学生注意反诈。班级共60人，男生25人、女生35人，整体时间观念执行力强、班风关系良好、班风纪律好，少数同学周末玩游戏、懒散、思考能力差、自习课纪律差。家长代表张宇波校长分享家庭教育经验，家委会建议至少三人自愿报名，保险、电子学生证、学校资助等事项一并沟通。
+# 沟通内容
+**亮点**：整体来看，第一个月时间观念执行力加强，班风关系全部良好，班风纪律非常好，地面干净，卫生良好；写字还是不错的，学生手册可查看；老师多数是老教师、优秀教师、师范院校毕业，有3年以上经验，部分6年以上，各科老师认真备课、用心上课、关爱每一位学生。**需关注之处**：少数同学周末玩游戏、懒散，思考能力比较差，自习课纪律差，班主任在时较乖、不在时乱哄哄；个别学生行动时间方面有问题，书写需练字，建议家长买字帖；自习课效率比较低；存在玩手机、看小说、镜子、微信、网瘾、打游戏充值400元、直播、不健康内容、谈恋爱、QQ、抖音、快手等情况；手机管理要求每个手机贴名字，家长处理掉多余手机，周一到周五不定时打电话检查手机是否开机；班主任将加强人员管理和班委培训，自习时给10分钟讨论，继续加强思想教育，制定详细班规，严格请假制度，定期沟通。
+# 家长反馈
+家长代表张宇波校长分享家庭教育经验：要控制孩子的身体健康和心理健康，高中阶段仍是长身体的关键时期；先做人，让孩子学会做人，千万不能带上不良风气；家长对待孩子要有平常心，孩子面临的学习压力很大，对挫折和失败要帮助孩子重新定位；要尊重孩子，给孩子自由空间，不轻易下消极评价；多倾听、多交流，把更多关爱与理解给孩子；遵守学校制度，配合老师工作。张宇波校长原话：&gt; 无论怎样，那你都是爸爸妈妈心里最优秀的儿子。班主任林瑞反馈家长需配合支持占30%，建议避免过分关注孩子、认为孩子不需要学习、过分期望、放任不管、给过多钱等误区，关注心理健康、交通安全（未满16周岁骑电动车非常危险，可能载两三个）、运动安全、饮食安全、防诈骗、防溺水、防校园欺凌，学习上不懂就问、不与他人比较，创造良好环境、和睦家庭气氛、制定小目标、多鼓励少指责。
+# 共识与配合事项
+[明确家校达成的共识、后续配合措施及跟进计划，用 `- [ ]` 待办格式列出双方分工；课程名、作业名、工具名可用 `具体内容` 标注]</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>17334/1136</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="13.5" customHeight="1" s="9">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:16
 哦，已经开始录像了，刚开始录像。我发现这个录像得提前一点。Yeah. 哦，我应该先开始录像，然后再说话。好，现在我问一下，大家能听到声音吗？嗯。你开始录制应该就能听到，我这边就不打字问了。下面我说明一下本次会议的性质和定位。本次会议是一个周会，10月28号周。
 发言人 1  00:00:53
 然后周会的主题是总结工作，你看一下会议的等级是一个自愿级。嗯目前就这定义为这样子就可以。然后会议资料是这三个，然后我念一下吧，会议资料是工作报告，这班看法，还有这班型社区介绍，然后会议目标是初步统一成员意见，你要通过这次会议统一。我们对这个社区的认识。然后那个更好看，然后美观一点，然后。
@@ -5797,9 +7171,46 @@
 然后换7028上的屏幕。这个就是最后的讨论。因为我自己学自己学也可以，我想和大家一起学。那多长时间一个小时了，那我们要不就继续在线下继续吧，我们一起学，这个时间也长了。我会。我们要下一个。看一下我们的会议目标啊。会议目标是。通过统一。对，一直听不到。邀请同事会邀请同事在村村的队。
 发言人 1  00:55:28
 音乐放的什么？如果一个人。地图。退货完成。开完了会，回到班级，我背后的同学叫我的名字，把我叫到走廊里，说。放歌，我还要最后放歌。都不想出去。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:08
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>团队例会</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t># 例会概况
+本次为10月28日周会，主题是总结工作，会议等级为自愿级，会议资料为工作报告、这班看法、这班型社区介绍，会议目标是初步统一成员意见、统一对社区的认识。会上讨论了工作报告与下周工作安排，提到项目创建学习资料并分为多个算术，服务定价权交给消费者，公司以前用传统方法现在用AI效率高质量好，需在实践中探索改进；还提到参加互联网加创业大赛、根据学校学习所需技能、实现教师改革，以及需要政府报告并符合要求、组建教育团队、确定路线、修订纲领章程。任务方面目前有四个任务，课程开发是其中之一，最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；大运发放需要调试，任务分配需安排，需招聘20多位师傅；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。学习介绍修改方面，把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号，服务时间还有工具需要改一下。待遇与角色方面，按照角色分为学生、教师、家长、学校、教育主管，待遇有上班5000、额外有奖励、还会有提成，周五半天加周末两天休假，需要公开的及时向当事人说明理由。会议时间已一个小时，决定会后线下继续一起学习；确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
+# 工作进展
+- 学习介绍修改：🔄进行中。已把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号；服务时间还有工具需要改一下。
+- 任务分配与课程开发：🔄进行中。目前有四个任务，课程开发是其中之一；任务分配需安排；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。
+- 组建执法队伍：🔄进行中。最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；需招聘20多位师傅。
+- 大运发放：🔄进行中。需要调试。
+- 待遇与角色：🔄进行中。按照角色分为学生、教师、家长、学校、教育主管；待遇有上班5000、额外有奖励、还会有提成；周五半天加周末两天休假；需要公开的及时向当事人说明理由。
+- 下一步：确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊；会后线下继续一起学习。
+# 协作需求
+- 邀请同事加入：先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
+- 组建教育团队：需要政府报告并符合要求，组建教育团队，确定路线，修订纲领章程。
+- 任务分配：任务分配需安排，任务第一步确定路线、修订纲领章程，然后安排任务。
+- 招聘师傅：需招聘20多位师傅。
+- 大运发放：需要调试。
+- 学习介绍：服务时间还有工具需要改一下。</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>4999/1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="13.5" customHeight="1" s="9">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:08
 你好，呃我姓严，是这里消化内科的医生，嗯我想了解一下你的病情，先核实一下你的名字好吗？
 发言人 2  00:00:16
 我叫张春和。
@@ -6239,9 +7650,44 @@
 没有什么问题了哈。那你就先休息，好吧？
 发言人 2  00:25:24
 好的。谢谢。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:14
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>就医咨询</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t># 就诊概况
+患者张春和，48岁，因上腹反复不适3个月到消化内科就诊，由严医生接诊。患者4年来每年春天多发，心窝处烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大；疼痛可忍受、白天发作、无夜间痛醒，3个月中有完全不痛的时候。曾出现两次黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近两个月出现几次呕吐，为酸味食物，晚上吐后舒服，有隔夜食物吐出，呕吐物无红色或黑色；最近3个月无黑便，大便黄色正常，小便正常，睡眠可。医生提出需留大便检查以了解有无出血，并安排后天做胃镜，待向上一级医生张医生汇报后再商定下一步处理意见。
+# 诊断与检查结果
+医生尚未给出明确诊断结论，表示需等检查资料更全面后再判断是否需要手术，若药物能控制病情则不用手术。患者曾两次出现黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近3个月无黑便，大便黄色正常。患者16岁时得过甲肝，在三医院住院一个月，出院时肝功能完全恢复，以后体检肝功正常。患者本人有低血压（90/60），父亲76岁有低血压，母亲75岁诊断过冠心病、吃药控制较好。医生提出需留大便检查以了解有无出血，并安排后天做胃镜。
+# 治疗方案与医嘱
+治疗计划：医生提出需留大便检查以了解有无出血，并安排后天做胃镜；将总结病情向上一级医生张医生（指导教授、权威）汇报后，再与患者商定下一步处理意见；关于手术，等检查资料更全面后再判断，若药物能控制则不用手术，如需手术再商量。生活注意事项：医生指出经常加班熬夜对疾病有影响，以后需注意；抽烟对身体不好，应尽量少抽或不抽，患者现把抽烟限制在10支以内并考虑戒烟；酒对胃肠道疾病影响大，需注意，患者应酬时少喝一点。重点禁忌：患者小时候因扁桃体炎在儿童医院吃华安药后左手起红疹、约半个月才好，医生告知对药物过敏，**不能吃该药**。
+| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
+| --- | --- | --- | --- | --- |
+| 斯达舒 | 最初一天两次，每次一颗；后加量至每天四五次 | 最初一天两次，后每天四五次 | 口服 | 最初有效，后效果不好，加量后仍效果不好 |
+| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉药厂，国产 |
+| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
+| 胃炎合剂 | 未提及 | 未提及 | 口服 | 所里医务室自己配置 |
+# 复诊与预警信号
+复诊时间：胃镜预约在后天进行，因患者爱人后天可请假陪同；后天张大夫查房。医生将总结病情向上一级医生张医生汇报后，再与患者商定下一步处理意见。预警信号：原文未提及需立即就医的预警症状。</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>10297/1145</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="13.5" customHeight="1" s="9">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:14
 开宗明义的讲，就是大家关心的这些问题，其实啊并不是我们关心的问题，也不是我们正在研究的问题。啊这个里面呢，其实我要是讲的是包含两层意思。那第一层意思就是首先从我从投资者的角度去出发，就就他者的角度去出发。啊我要讲的就是其实大部分人关心的类似的这种就What happen next的这样的问题呢。
 发言人 1  00:00:37
 就是说你其实你听到的这个答案呢，对你来说其实没有太大的这个用处。为什么这样说呢？比如说比方讲我看好一个板块，我看好哪个个股，啊然后我告诉你我很看好，这个对我来说呢，我看好这个东西呢是基于相关的知识，对我来说这个东西叫knowledge，但是对于你来说，你得到的仅仅只是一条肖楠看好某某这个信息。
@@ -6563,9 +8009,63 @@
 大家。
 发言人 2  01:09:22
 谢谢。嗯，下面我们有请第二位分享嘉宾蔡荣成总，简单介绍一下蔡总。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:14
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次汇报由基金经理肖楠面向投资者进行，主题为过去一段时间的研究布局、研究认知成果以及投资理念与框架的反思与更新。肖楠首先明确反对市场上流行的抱团与均值回归两个观点，随后汇报过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向，并分享围绕四大领域的重要认知，最后用五点反思梳理对投资框架的更新：对商业模式的反思、对终局判断的反思、对长期隐性变量的反思、深度价值可能长期无效（打问号，未得结论）、小企业X factor。汇报后进入客户提问交流环节，肖楠就终局判断与格局演进、伟大公司判断标准、全市场基金选股逻辑、血制品行业壁垒、农林牧渔行业提升、商增商减分析、伟大企业增长曲线、财富管理行业、企业家精神观察心得等问题逐一作答。
+# 核心观点与论证
+**论点一：反对抱团与均值回归两种流行观点。** 肖楠认为抱团定义不本质，基金经理之间是竞争关系，主观上不具备抱团意愿，同一公司研究员推荐被广泛认可买入也不叫抱团，且抱团只是截面数据忽略了时间维度；均值回归是特别不本质的局部正确，90%时间正确但10%错误代价惨重，举例某商学院老师在海螺水泥上做波段十年赚两三倍，2016至2017年卖出后该股约两年涨五六倍再未买回，并指出收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。
+**论点二：四大研究布局方向。** 过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向。互联网：全球仅中美能做成巨大产业，中国十几年迭代出流量、运营管理、算法三代企业，港股通开通后可投；财富管理：中国进入小康，人均收入中位数前移带来巨额剩余财富待专业机构管理，行业空间远超想象；新消费：富裕年代诞生的消费公司从CEO理念、组织架构到生产方式与匮乏年代企业完全不同；高端制造：中国几乎是唯一拥有全产业链的国家，很多细分领域已占据主导地位，欧美日企业份额已是中国企业碗里的肉。
+**论点三：研究认知成果。** 新消费领域看起来产品差不多的公司收入利润差距巨大，企业眼中产品差异在三年五年十年维度被放大；传统消费龙头赚钱龙二龙三也赚钱，新消费同一行业一家赚很多钱另一家完全不挣钱；从`商增`角度理解企业商业模式，商增过快导致企业走向失败，成长企业靠什么吸收熵增是关键。
+**论点四：投资框架五点反思。** 一是对商业模式，世界上没有一劳永逸坐地收钱的生意、极端稀缺，单一维度出发可能错失机会，商增角度理解商业模式更本质，企业家精神是否值得定价存疑并与张坤争论过；二是对终局判断，因终局判断不清晰或悲观而放弃中期十倍机会，需在坚持终局判断基础上争取研究格局演进阶段性特征；三是对长期隐性变量，为什么日本德国没有出巴菲特索罗斯，中国基金经理放到日本韩国不一定有好收益率，国运等长期变量解释相当部分收益率来源，并研究奢侈品和白酒文化强势案例；四是深度价值可能长期无效（打问号，未得结论），深度价值只是结果，去年投的深度价值标的result非常差；五是小企业X factor，经典`DCF`/`DDM`都是线性假设，企业发展是曲线，曲率因素无法定价但长期起作用，超额认知来自这些方面。
+# 金句总结
+「知识和信息之间是有着巨大的鸿沟的。」——背景：肖楠在开场说明投资者关心的What happen next类问题对提问者用处不大，看好某板块对本人是knowledge，对他人只是一条信息。
+「务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。」——背景：肖楠以巴菲特代表的极端务实派与索罗斯代表的极端务虚派说明基金经理理念处于两个极端中间，强调理念没有好坏。
+「均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。」——背景：肖楠反对均值回归观点，以海螺水泥波段操作案例说明。
+「收益率是幂律分布的，不是正态分布的。」——背景：肖楠论证均值回归不本质，指出美国股市200年价值增量由4%的公司贡献。
+「长期看所有的企业都要死去，就是我们不能够抱着就是抱定说我我们要买一个千秋万代的这种企业。」——背景：肖楠反思对商业模式的理解，指出没有一劳永逸坐地收钱的生意。
+「我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价，它不能被定价。」——背景：肖楠回答企业家精神观察心得，强调不乱归因、不轻易定价。
+# Q&amp;A 环节
+问：您刚刚讲到在对于终局结果的重视的过程中，也更加去关注格局演进的过程中阶段性的特征、中期投资机会，请问您能对这一点再详细描述一下吗？
+→ 答：肖楠表示不太好说具体标的，这个想法最早来自过去错过了一些特别大的机会，之所以错过是因为判断这些行业终局可能不大行，但明明判断对了却在两三年时间里深深错过了十几倍的涨幅。复盘看当时完全可以在既考虑终局可能没那么好的前提下依然做出漂亮投资。这类企业的重要特征是做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。后来在一些投资中，对终局可能没那么强的标的，依然能够做出好的投资，希望未来不要再去错过类似机会。
+问：您在年报中也讲到过，坚定持有优秀乃至伟大的公司。请问您能否对优秀乃至伟大的公司的判断标准，有一些具体的财务指标？
+→ 答：肖楠称伟大公司是在财务指标里面看不出来的。举例A、B两家同属一个大行业但不同细分子行业的国企，投资逻辑非常像，都在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于B公司没有太多研发、靠精益求精的管理做到成本极低；A公司每年有高额研发支出，关键技术指标以非常强速度迭代，还有很多特别前沿的研发项目，这些方向上的技术目前掌握在德国人、日本人手里。A公司在发展初期被德国人、日本人坑过，从董事长到总经理到技术骨干都有强烈的产业报国、技术报国理想，从跟着日本人学、跟着德国人学，到越做越强、超越对手，再到对手跑过来跟他们学、开始做全产业链布局，这种企业堪称伟大的企业。
+问：我们是全市场基金，能否介绍一下这个产品的投资逻辑呢？对于消费以外的行业的选股，主要是基于什么逻辑呢？
+→ 答：肖楠称很难分消费内消费外，选股逻辑都是一样的，都是不可能三角、企业三阶段、三种商业模式这一类的，消费行业只许买消费所以只能在消费行业里面选，两者选股逻辑完全一样。
+问：您是怎么看待血制品行业的竞争壁垒呢？
+→ 答：肖楠称血制品行业初初研究过，觉得壁垒不是特别的强，不是想要的那种强壁垒，研究不是特别多，相比之下买了另外一些强壁垒的公司，还有一些基金经理买了血制品行业，可以请教他们。
+问：农林牧渔行业是有所提升，请问您对这个行业的观点能够给我们讲一下吗？
+→ 答：肖楠称这行业太大了，农林牧渔行业的提升是因为牧原股份那一只股票，不是因为先看好农林牧渔行业再去选了牧原股份，就是牧原股份的比例提高了。
+问：您能够再具体讲一下生意模式里边商增和商减的这个分析吗？
+→ 答：肖楠用直白例子说明：企业从小到大，部门越来越多，中层干部一大堆，上面要分领导、还有副总裁，传达效率变低、效率开始变差，内部腐败开始出现，企业为解决供应商利益关联问题又要设置巡视检查部门，部门人员要加工资、提级别，多部门老总今年提哪个明年提哪个；企业要扩张，往下游或上游多做业务，又要多一个副总裁、多个部门。有些生意模式收入10个亿跟100个亿时没多多少机构、没多几个部门，有些企业是商增把自己拖死的。行业里剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，差别在于做得不好的公司从一开始就没考虑好企业大了以后商增怎么处理效率问题和人员问题。建议读一读党史，看组织如何保持活力，很多政府或企业确实是处理商增的高手。
+问：您讲到伟大的企业的增长曲线，您能否对于这个曲线的情况再具体跟大家讲一下呢？
+→ 答：肖楠称每年看企业今年增长20、明年15、后年17.5都是线性的，站10年周期看企业跟竞争对手之间拉开极大差距。举例快递行业疫情时只有顺丰能送，一下子把竞争对手甩出一大截；家电领域过去格力一直是老大，美的做渠道扁平化、T加三一直没看到成果，疫情来了美的占有率一下子超过格力。当企业在埋头做一些事情、还没体现到报表时，我们往往忽略其未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，就像平时走在路上大家都走得好好的，突然来一场雨，发现有一个人带伞了，别人都淋成了落汤鸡。
+问：您刚刚有讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会呢？
+→ 答：肖楠称财富管理行业话题特别大且分层，顶级富豪、普通中产阶级、中低收入人员的财富管理都有不同的公司和商业模式。最早关注这个行业是研究保险时发现，某些保险公司一个保险员一单能签七八千的首次保费，有些公司平均一个业务员大概三千多、有些两千多，差距巨大，背后是结构设置、机构设置、激励机制、文化等差异。发基金时也发现同样渠道经理，有的问的问题超级专业，有的永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司一口气拿掉行业增量的绝大部分，有些公司拿掉70%、80%，剩下的第二名只能拿到剩下的20%的80%，这种特别偏激、密分布特别偏激的行业里有可能诞生特别大的企业。因监管和法律规则原因有些标的不能投，未来合同设置更清晰时可能会在投资上有所体现。
+问：您刚刚讲到曲线的方面，第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标的方面会有什么心得和把握呢？
+→ 答：肖楠称第一个心得是评判这个因素时要特别小心谨慎，不要乱归因，不要因为一个企业成功就说企业家特别厉害，就像不要因为一个基金经理过去业绩很好就说他特别厉害，一定要把所有能够被归因到数据里的客观指标因素全部归因完，再特别谨慎地评价比较虚的因素。第二个心得是不要轻易给这些因素定价，绝对不要说因为这个企业家在所以公司就能值多少多少。始终强调的是避免错误的归因，避免因为对企业家的认可去犯投资上的错误，一定要把底线的风险搞好。这些因素不可被定价，只能在有限范围内做两两比较，比如两个公司做同样生意、同样产品，可以比较两个企业家的水平高低、理念先后，仅此而已，不要跨行业、跨业务、跨产品去比较，一定要非常谨慎地使用所谓企业家精神、伟大企业这些说法。</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>26252/4226</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="9">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:14
 正方四辩王新峰，正方 RUC棒辩论队向大家问好。下面有请反方做自我介绍。嗯嗯，这是介绍了半天，我们就不讲了，我们作为这个城市，在这个城市，那我爸爸就是直接从地方的公司换成了，就是也是整个。首先是不是爱他，你说爱是。王老师对我们的理想对象有更大的要求，刚刚说的，当他出现的时候，我就没有希望要求他。
 发言人 1  00:01:08
 他会说，你什么？他就会尽量，就是，但是在之前，他是不觉得，他会让我去爱上去，去不爱上去的。所以说，他。第二个我们来是安全的，安全的，同时告诉大家，这个是成绩确实是一个配方，一个配方是高的，是对于过去的这个时间的地点。都会怎么样？可能某一天春光正好，你穿着白衬衫出去穿越了阳光洒在沙滩上，你突然就爱上了他。
@@ -6713,9 +8213,48 @@
 多少人终其一生连这个迷药的味道都没有尝过，他只能清醒，会用自己的理智去判断，找一个。过日子，这才是最美好的一个精神。并且去去精心的熬制这款秘药给你的那个名字，并小心的使用它，守护这个后院通道的医生和战士。我要把这个，我要把这个桌子给放平。你爱的人会爱上谁，可是他会爱上谁，那个人对他好还是坏，爱他还是不爱他，你都不知道啊，你这么爱他的人，你怎么放心把他交给一个未知的某某某呢？
 发言人 1  00:53:11
 你受得了吗？好吧。你重新先试一下。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:10
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>辩论会</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t># 辩论内容概述
+本场辩论赛围绕「是否应拥有让所爱之人爱上自己的超能力」展开，正方为RUC棒辩论队，反方为对方辩友。正方认为爱本身并非自由意志的产物，以「坠入爱河」而非「跳入爱河」说明爱是情非得已，并援引丘脑分泌多巴胺产生爱的感觉、但科学无法解释为何偏偏对某人有感觉，故归于玄学；正方还认为红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方认为打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸，并认为通过洗脑获取爱更像变态的占有，不是爱；反方还认为月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。双方就爱到底是不是自由意志的产物、超能力发挥的机制究竟是洗脑还是其他方式、爱是玄学还是可被科学解释均未达成一致，本场辩论未形成统一结论。
+# 核心论点
+正方观点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制，若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方观点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
+| 阵营 | 立论框架 | 核心论点 | 支撑论据 |
+| --- | --- | --- | --- |
+| 正方 | 爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已 | 超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好 | 丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学；若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从 |
+| 反方 | 打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸 | 通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱 | 这个人原来不爱你的，但是你打了响指，他就一定爱上你了，这个和很多有必要的强奸犯讲的道理是一样的 |
+# 自由辩论环节
+争议点一：超能力是否剥夺对方自由意志。反方攻：打响指让对方爱上自己，是违背对方意志强行介入亲密关系，类比强奸。正方防：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已。
+争议点二：超能力是否等同于洗脑与占有。反方攻：通过洗脑获取爱更像变态的占有，不是爱。正方防：若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从。
+争议点三：爱是玄学还是可被科学解释。正方攻：丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学。反方防：质疑对方未论证爱是玄学。
+争议点四：放手的爱与是否应使用超能力。反方攻：追问相处后发现不合适是否再用超能力。正方防：若无法在一起会选择放手。反方再攻：一旦用过超能力，今后面对新感情会永远留下遗憾。
+争议点五：月老丘比特与红线掌握在谁手里。正方攻：红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方防：月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
+&gt; 正方：「我们说的是坠入爱河，而不是说去跳入爱河。」
+&gt; 反方：「这个人原来不爱你的，但是你打了响指，他就一定爱上你了。这个和很多有必要的强奸犯讲的道理是一样的。」
+# 结辩与评委点评
+正方结辩核心升华点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方结辩核心升华点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。评委点评意见：未提及。获胜方：正方。</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>12403/1626</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1" s="9">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:10
 所以做了这个手术之后做了八期的化疗，在复查的时候就发现有肝转移，从老家又来到北京做了个派的CT，
 发言人 2  00:00:19
 发现有
@@ -7055,9 +8594,43 @@
 觉得现在挺好的。对，他就觉得挺好。嗯。嗯。愿意提升。嗯。提升免疫力靠自己啊。是。面对是有限的，大夫也是有限的啊，咱手术也做了，现在就是。怎么帮助他用这个事，这个把责任啊放到自己，我跟他说了，他要给你做免疫评估，但是你方案你来定，看人家对不对。
 发言人 1  00:16:35
 他咋做免疫评估，是问一个问的，今天早上查了一个。早上查了个血。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:45
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>就医咨询</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t># 就诊概况
+患者于23年9月因腹痛一晚上确诊结肠癌，行结肠癌切除手术及8期化疗，复查发现肝转移，从老家到北京做PET-CT。去年9月行肝消融及乳腺结节切除，当时已有腹膜转移，切肠时可能切得不干净；术后行紫杉化疗，仅第一次有效，后续因肝功能不行停用靶向，至3月底复查发现肝、肺、腹膜又有转移。本次就诊为家属代述病史并咨询后续治疗，医生建议以全身系统治疗（化疗、靶向、免疫）为主，介入不是当前主要问题，并建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍。
+# 诊断与检查结果
+医生指出患者为结肠癌术后多发转移，累及肝、肺、腹膜及肠壁。PET-CT显示肝、肺、腹膜有转移；肠镜显示没事但PET显示有问题，今天说可能是肠镜做得不好。4月份做的检查。医生强调现在化疗是否有效并不清楚，基因检测推荐或不推荐都需参考；免疫细胞状态很重要，数量不足需创造。
+# 治疗方案与医嘱
+治疗计划以全身系统治疗为主，包括化疗、靶向、免疫，需选靶向、选免疫；靶向和免疫治疗与原来化疗机制不同、可能协同。建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍，第一次、第二次、第三次切片可对比，从对讲中找可用信息。生活注意事项：让患者把状态调整好，提升免疫力靠自己，大夫和手术有限；要做免疫评估，但方案由家属定。**若涨幅到10公分则要命，需先系统治疗**。
+| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
+| --- | --- | --- | --- | --- |
+| 紫杉化疗 | 未提及 | 未提及 | 化疗 | 仅第一次有效，后续因肝功能不行停用靶向 |
+| 靶向药 | 未提及 | 未提及 | 靶向治疗 | 后续因肝功能不行停用 |
+| 四联康 | 未提及 | 未提及 | 口服 | 肚子不好时用 |
+# 复诊与预警信号
+复诊时间未提及。⚠️ 若涨幅到10公分则要命，需立即就医。</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>7063/797</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="13.5" customHeight="1" s="9">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:45
 大哥。欢迎来到海尔洗机创新
 发言人 2  00:01:06
 发布会，
@@ -7203,9 +8776,52 @@
 浴巾暖烘烘，贴身衣物温软亲肤。洗衣不打扰，夜晚也能安静洗。一体集成，我家的阳台洗衣房。
 发言人 3  00:37:39
 我不喜欢湿漉漉的夏天。妈妈说她有一个好办法。哇，这就是。我们的新阳台吗？这些新朋友们好像都会魔法，让阳台变得整洁明亮，再也不用挂满衣服。我的小熊朋友也变得干干净净，家里飞舞的毛毛消失不见了，空气都那么清爽。以后这里就是我们的秘密基地了。yeah.</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:13
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>产品发布</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t># 产品概况
+本次发布会由海尔洗衣机用户研发中心主办，围绕洗干集成新物种迭代H2展开，主题为体验海尔洗衣机的科技创新之路、共同见证洗干集成新物种的诞生。发布背景源于全球家庭洗护需求洞察：欧洲作为滚筒洗衣机发源地，许多家庭有独立洗衣房、洗烘套装并排摆放；而在中国，80%的用户把洗烘套装放在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便，正是这些问题孕育了洗干集成新物种的诞生。迭代H2定位为客阳一体空间的黄金选择，是海尔为中国家庭打造的原创之作，目标是让每一个向往整洁有序新阳台的用户都能体验这种生活方式。
+# 市场定位与目标用户
+迭代H2专为客阳一体空间设计，面向中国当下最流行的客阳一体家居风格，是希望拥有整洁有序新阳台用户的黄金选择。典型使用场景为年轻人最喜欢的阳台风格之一，他们在阳台休闲、娱乐、健身、社交，悬挂晾衣既不美观又占空间，H2帮助其彻底告别晾晒。目标人群包括：渴望从漫长家务中解放出来的年轻人、对残留泡沫敏感的人、养宠物的人群，以及有宝宝的家庭。差异化竞争力方面，与洗烘套装的貌合神离不同，H2独有的灵犀洗烘联动可实现数据共享，让烘干和洗涤无缝连接；一体集成机身解决了洗烘套叠放带来的震动等安全隐患。
+# 核心卖点与技术参数
+**🏠 客阳一体设计与集成机身**：专为客阳一体空间设计，一体集成机身解决洗烘套叠放带来的震动等安全隐患；高度降为 `167厘米`，不用踮脚尖即可轻松操作；超薄机身完美嵌入 `60厘米` 标准橱柜，纯平不突出；同向开门尊重使用习惯，取放衣物流畅自如；采用无水盒设计，无需手动倒水。
+**🧠 智慧大脑与灵犀洗烘联动**：以屏幕为核心可全面操控洗涤、烘干和护理等多种模式；H2全新升级智慧大脑，利用中枢神经式智能网络让上下桶默契配合；H2独有灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接；洗涤结束前上桶提前 `15分钟` 主动预热，进一步缩短烘干时长。
+**🌀 烘干与洗涤技术**：搭载原创双擎热泵技术，大件烘干不缠绕；首次引入行业领先黑科技3D透视烘干，羽绒服或水洗被均可一次烘透，免去二次晾晒烦恼；升级精华洗2.0，能够激活洗衣液，`39分钟` 洗净一周衣物；新鲜净水漂洗减少洗衣液残留。
+**🐾 居家健康与静音**：搭载空净过滤系统，轻松去除衣物线屑和毛絮，更适合养宠物人群；洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭；搭载三台变频电机，洗涤、甩干、烘干全过程噪音都很低。
+| 维度 | 本产品 | 上代/竞品 | 提升 |
+| --- | --- | --- | --- |
+| 机身高度 | 167厘米 | 洗烘套装叠放 | 降低高度，不用踮脚尖即可操作 |
+| 机身嵌入 | 超薄机身，完美嵌入60厘米标准橱柜，纯平不突出 | 洗烘套装叠放 | 全平不突出，阳台更美观整洁 |
+| 开门方式 | 同向开门 | 洗烘套装开门方向相反 | 尊重使用习惯，取放衣物流畅自如 |
+| 水盒 | 无水盒设计 | 水盒太高太沉 | 无需手动倒水 |
+| 洗烘联动 | 灵犀洗烘联动，数据共享，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离 | 烘干和洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术、3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透 |
+| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 减少洗衣液残留 |
+| 过滤系统 | 空净过滤系统 | 未提及 | 去除衣物线屑和毛絮 |
+| 电机 | 三台变频电机 | 未提及 | 洗涤、甩干、烘干全过程噪音都很低 |
+# 定价与发售信息
+海尔为这款平嵌超薄产品公布诚意满满的定价：10kg 3D透视烘干款12998元，10kg双擎热泵款10998元。发售时间、购买渠道及预售政策未提及。</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>7311/1601</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="13.5" customHeight="1" s="9">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:13
 好吧。同志们，先把手机调成静音，我们今天开会。同志们，今天召开中共巢湖市银屏镇白母山村芦塘支部党员大会，改选中共巢湖市银屏镇白母山村芦塘支部委员会，支部共有党员8名，其中正式党员8名，有选举权的。应是因病请假一名，迟到会有选举权的党员7名，符合法定人数，可以开会。
 发言人 1  00:00:58
 应邀参加今天会议的有。银坪镇党委组织委员钱小丽同志，让我们以热烈的掌声表示欢迎。现在我宣布，中共巢湖市银屏镇白母山村芦塘支部委员会换届选举党员大会现在开始，请全体起立，奏
@@ -7391,9 +9007,37 @@
 服务基层服务群众。最后我代表新一届党支部希希望大家对我们如何开展工作提出建议和意见，更希望大家能够对我们工作中的不足提出批评。再一次感谢各位领导及公司的对我们的信任和支持。好同志们，巢湖市银屏镇白母山村卢塘党支部党员大会经过全体党员的共同努力，已完成了大会的任务。
 发言人 1  00:29:56
 现在我宣布中共巢湖市银屏镇白母山村。堂支部委员会换届选举大会圆满结束，请全体起立奏国际歌。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:05
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议为改选中共巢湖市银屏镇白母山村芦塘支部委员会，支部共有党员8名（正式党员8名），有选举权的应到8名，因病请假1名，实到会有选举权党员7名，符合法定人数，会议可以召开；应邀参加的有银屏镇党委组织委员钱小丽同志。会议依次通过上届支部委员会工作报告、党员大会选举办法草案、支委候选人名单、监票人及计票人名单，四位候选人依次进行竞职演说，随后进行支部委员会委员选举和书记选举。上届支部委员会工作报告经讨论无意见、鼓掌通过，报告回顾3年来支部落实党建工作要求、加强思想政治建设和理论学习、抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告同时指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。选举办法草案明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。银屏镇党委批复（2019年10月12日）同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选卢燕娇，委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。随后召开第一次支部委员会全体会议，支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准；会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言表示将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。
+## 大会审议与选举办法通过
+- 上届支部委员会向会议做工作报告，请同志们审议；报告回顾3年来支部落实党建工作各项要求，加强思想政治建设和理论学习，抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。报告经讨论无意见，鼓掌通过。杜军晓同志宣读党员大会选举办法草案，明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。选举办法草案一致通过。
+- 杜军晓同志宣读银屏镇党委关于同意中共巢湖市银屏镇白母山村芦塘支部委员会组成人员候选人预备人选的批复（2019年10月12日），委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇；委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。会议对候选人名单无不同意见，鼓掌通过。会议提议由贾淑玲同志担任监票人，经酝酿无意见，表决一致通过；宣布大会计票人员名单为黄婷丽、刘彩云。四位候选人依次进行竞职演说：卢燕娇表示如当选将加强支部建设、落实三会一课、推动村集体经济发展、抓好民生工程落实；杜军强表示如成为支部委员可更好担当纽带角色为党员和群众服务；辛东升表示严格要求自己、做合格党员干部、圆满完成上级党组织分配的各项任务；秦磊表示有较强责任心和较高思想觉悟，配合上级工作，当一名合格的支部委员。
+## 选举结果与委员分工
+- 选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，可以进行选举；发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，根据选举办法，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。随后召开第一次支部委员会全体会议，宣读选举办法草案，介绍书记候选人建议名单卢燕娇，经鼓掌通过；提议由辛东升同志担任监票人和计票人，表决一致通过；支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准。会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言，代表新当选的三位支部委员感谢信任和支持，表示下一步将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。会议宣布换届选举大会圆满结束。</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>8414/2327</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="9">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:05
 各位代表。现在我代表国务院向大会报告政府工作，请予审议，并请全国政协委员提出意见。2023年工作回顾，过去一年是全面贯彻党的二十大精神的开局之年，是本届政府依法履职的第一年。面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务。以习近平同志为核心的党中央团结带领全国各族人民顶住外部压力，克服内部困。
 发言人 1  00:01:00
 共同啊，付出艰辛努力，新冠疫情防控实现平稳转段。全年经济社会发展主要目标任务圆满完成。高质量发展，扎实推进社会大局保持稳定，全面建设社会主义现代化国家迈出坚实步伐。经济总体回升向好。国内生产总值超过126万亿元，增长5.2%，增速居世界主要经济体前列。城镇新增就业1244万人。
@@ -7513,9 +9157,40 @@
 我们要坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略。中国愿同国际社会一道落实全球发展战略。全球安全战略，全球文明战略，全球发展战，倡议全球安全战略，全球文明战略，推动构建人类命运共同体。各位代表，使命重在担当，奋斗创造未来，我们要更加紧密的团结在。
 发言人 1  00:51:00
 以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，坚定信心，开拓进取，努力完成全年经济社会发展目标任务。为以中国式现代化全面推进强国建设、民族复兴伟业不懈奋斗。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:16
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>政府报告</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t># 报告概况
+国务院向大会报告政府工作，请予审议，并请全国政协委员提出意见。报告回顾2023年工作：全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，城镇调查失业率平均5.2%，居民消费价格上涨0.2%；国产大飞机C919投入商业运营，新能源汽车产销量占全球比重超过60%；粮食产量1.39万亿斤再创历史新高，居民人均可支配收入增长6.1%，脱贫地区农村居民收入增长8%。报告明确2024年经济社会发展总体要求和政策取向：今年是中华人民共和国成立75周年、实现十四五规划目标任务的关键一年，坚持稳中求进工作总基调，统筹扩大内需和深化供给侧结构性改革、统筹新型城镇化和乡村全面振兴、统筹高质量发展和高水平安全。报告部署2024年十项政府工作任务，并指出面临的困难和挑战。
+# 核心政策
+2024年主要预期目标：国内生产总值增长**5%左右**，城镇新增就业**1120万人以上**，城镇调查失业率**5.5%左右**，居民消费价格涨幅**3%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量**1.3万亿斤以上**，单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善。财政政策：积极的财政政策要适度加力、提质增效，赤字率按**3%**安排，赤字规模**4.06万亿元**，一般公共预算支出规模**28.5万亿元**，安排地方政府专项债券**3.9万亿元**；为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**。货币政策：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。民生指标：居民医保人均财政补助标准提高**30元**，城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金。
+# 重点工作
+经济领域：大力推进现代化产业体系建设，加快发展新质生产力，推动产业链供应链优化升级，实施制造业重点产业链高质量发展，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展，打造更多有影响力的中国制造品牌；促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划；深入推进数字经济创新发展，开展人工智能加行动，实施制造业数字化转型行动。着力扩大国内需求，促进消费稳定增长，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；积极扩大有效投资，发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施十四五规划重大工程项目。坚定不移深化改革，激发各类经营主体活力，深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，加快全国统一大市场建设，谋划新一轮财税体制改革。扩大高水平对外开放，推动外贸质升量稳，促进跨境电商等新业态健康发展，全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，推动高质量共建一带一路走深走实。更好统筹发展和安全，优化房地产政策，促进房地产市场平稳健康发展，统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
+民生领域：多措并举稳就业促增收，突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模。提高医疗卫生服务能力，居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，促进中医药传承创新。加强社会保障，城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，健全分层分类的社会救助体系。丰富人民群众精神文化生活，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。维护国家安全和社会稳定，提高公共安全治理水平，坚决遏制重特大事故发生，坚持和发展新时代枫桥经验，建设更高水平的平安中国。
+三农与城乡区域领域：坚持不懈抓好三农工作，扎实推进乡村全面振兴，学习运用千村示范、万村整治工程经验，稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；毫不放松巩固拓展脱贫攻坚成果，加强防止返贫监测帮扶，确保不发生规模性返贫；启动第二轮土地承包到期后再延长30年整省试点。推动城乡融合和区域协调发展，积极推进新型城镇化，把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用。
+生态环保领域：加强生态文明建设，推进绿色低碳发展，深入践行绿水青山就是金山银山的理念，协同推进降碳、减污、扩绿、增长；深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，组织打好三北工程三大标志性战役；大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展，建设美丽中国先行区；积极稳妥推进碳达峰碳中和，扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系。
+&gt; 使命重在担当，奋斗创造未来，我们要更加紧密地团结在以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，坚定信心，开拓进取，努力完成全年经济社会发展目标任务。</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>9903/2479</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="13.5" customHeight="1" s="9">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:16
 嗯。我们的节目正在通过b站微博和抖音同步推出，如果您在观看的过程中有任何的问题，都可以用不同的方式在我们的弹幕区进行留言，稍后呢也会有今天的嘉宾的点评答疑解惑，为了帮助广大考生全面了解2026年。研究生的招生情况，今天全天来到我们直播间的是杭州医学院。本场直播呢是杭州医学院检验医学院、生物工程学院的专场，那么今天也特地的邀请到了学校的一位中。
 发言人 1  00:01:00
 让我们的嘉宾来做客我们直播间，那么就是来自杭州医学院检验医学院生物工程学院党委书记。副院长宋宋宝峰副教授。主持人你好。
@@ -8333,9 +10008,51 @@
 也要感谢到场的呃宋书记带来的精彩的直播，啊，那么如果说前面的直播没有看到的同学呢，也没有关系啊，我们在本场直播的结束以后的24小时之内呢，就会将我们的回回看上传到 B 站，所以也是欢迎我们的考生能够随时来搜索。我们的本场的直播内容，那么如果说想要了解更多的报考信息呢，可以持续关注杭州医学院的官网和杭州医学院的官网，那么我们本场直播到这里就要结束了，各位考生，各位家长再见。
 发言人 2  00:57:53
 再见再见。好。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:13
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沟通交流会</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t># 沟通背景与目的
+本次直播为杭州医学院检验医学院、生物工程学院专场，由学院党委书记、副院长宋宝峰副教授介绍2026年医学技术专业硕士点招生情况。该学位点为2024年获批的新学位点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，其中检验技术细分为医检和卫检两个方向。2025年录取64位考生，检验方向38人、影像方向11人、康复方向13人、智能方向24人。2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。
+# 信息同步
+**学位点基本情况**：2024年获得医学技术专业硕士点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养工作，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，检验技术细分为医检和卫检两个方向。
+**2025年招生情况**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能方向24人。
+**学科建设情况**：医学技术2023年获批省一流学科B类；近五年获国家级基金项目19项、省部级项目1项，纵向科研经费1300万，横向合作课题经费2200多万；获省科技进步一等奖2项、二等奖1项、三等奖2项；建成国家级一流本科课程2门、国家级一流本科专业建设点2个；拥有省生物标志物与器官诊断转化重点实验室、省神经系统疾病数字化装备研发重点实验室等多个省级平台。
+**学科优势**：体外诊断领域优势显著，疫情时期与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品并获NMPA注册；医学影像技术方向在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优质方向；康复治疗方向依托省人民医院康复医学科；智能医学工程方向聚焦阿尔茨海默病智能预警生物标志物，居国际领跑水平。
+**主要研究方向**：医学检验技术方向负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制等五大块；卫生检验检疫方向负责人金大志教授，聚焦新发突发传染病病原体检测检验新技术方法开发及卫生检验技术研究；医学影像技术方向负责人徐秀芳教授，含多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；康复治疗方向负责人倪湘明教授，含技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五个方向；智能医学工程方向负责人李海教授，聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断五个方面。
+**师资队伍与领军人物**：专任教师90人，高级职称占30%以上共53人，博士55人；硕导69人，其中正高35人，博士占比46人；有省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。领军人物包括学位点负责人吕建新教授、徐秀芳教授、叶小明教授、金大志研究员、李凯教授等。
+**硕士培养与毕业去向**：培养目标为面向健康中国发展需要、服务区域行业产业发展的高层次应用型人才；全日制专业学位学制三年，最长不超过五年；课程学习实行学分制，毕业前要求取得不少于24个学分，其中专业必修课不少于12个学分，专业选修课不少于5-6个学分；就业方向包括医院相关科室、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等。
+**2026年招考计划**：2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准；初试科目为思想政治理论、英语及对应方向专业综合（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；专业综合满分300分，考试时长180分钟；检验综合中卫生生物学检验占40%、生物化学检验占30%、微生物学检验占30%；参考书及考试大纲以杭州医学院研究生招生网公布为准。
+**复试安排**：复试采用线上线下结合、目前以线下为主；初试占60%、复试占40%；复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%；复试具体形式和内容以学校当年复试录取办法为基础，可参考2025年复试办法。
+**考生问答**：就业前景方面，宋宝峰表示就业优先，专业就业前景非常好，可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等；跨专业报考方面，允许非该专业本科考生跨专业自主报考；交通方面，学校有三个校区，主城区黄路校区交通便利；竞赛方面，学校重视竞赛，以赛促学、以赛促教、以赛促改。
+# 达成共识
+**2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。**
+**初试科目为思想政治理论、英语及对应方向专业综合，专业综合满分300分，考试时长180分钟。**
+**复试采用线上线下结合、目前以线下为主，初试占60%、复试占40%，复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%。**
+**允许非该专业本科考生跨专业自主报考医学技术专业。**
+&gt; 允许非该专业的考生跨专业来报考我们这个医学技术。
+# 待协调事项
+无</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>23026/2233</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="13.5" customHeight="1" s="9">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:13
 好，那我们现在就上课了，那我们先思考一下，我们作为一个小部门，首先呢。观点。
 发言人 2  00:00:31
 对。
@@ -8875,9 +10592,63 @@
 是的。
 发言人 1  00:33:53
 想一下啊，好，我们先把这个先思考一下，我们做一个小图啊，涉及到我们的电视。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:01:21
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课为历史小论文写作讲评课，围绕自命题类、观点提示类、图表信息类三类题型讲解解题步骤与方法，并逐一分析学生作答。总体要求是观点必须明确亮出，不能只是简单陈述或加个名词；论证写两到三条，不宜太多，要能支撑论点；先打开学术背景再引出自己的观点；可用序号也可直接罗列，但逻辑要清晰，按时间脉络（如700时期、明清时期）或国内外等维度罗列清楚；最后论述要升华观点，不能简单照抄观点。自命题类以武汉长江大桥为例，学生作答涉及新中国成立、改革开放、对内改革对外开放的时间顺序，老师指出按顺序应先写对内改革再写对外开放，并强调要写清时间和重大国家利益。观点提示类以1940年抗战时期某材料为例，学生分析四个观点并选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。图表信息类以中国历代民德等级变化图表为例，涉及春秋、东汉、宋明等时期，讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系。
+# 核心知识点梳理
+**一、小论文写作总体要求**
+- **观点必须明确亮出**：不能只是简单陈述或加个名词，要把自己的观点亮出来，观点还要有凝聚力。
+- **论证写两到三条**：不宜太多，要能支撑论点；先打开学术背景，再引出自己的观点。
+- **逻辑清晰**：可用序号，也可不用序号直接罗列，但要让老师看清写了几条；可按时间脉络（如700时期、明清时期）或国内外、内衣外衣等维度罗列清楚。
+- **最后论述要升华**：不能简单把观点抄一遍，要说明写这个东西是为了什么。
+**二、自命题类解题步骤**
+1. 先审题：看要求，注意「小红帽」的要求及形成标准。
+2. 认真读材料：先抓主要信息，再细看它们之间的关系。
+3. 题目先写好，再罗列事实：事实要与材料相关，不要乱罗列。
+4. 最后进行升华。
+案例：武汉长江大桥。学生作答涉及新中国成立、改革开放；老师指出按时间顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
+**三、观点提示类解题方法**
+- 先看有哪些观点，按选择和观点的关系处理。
+- 选择核心观点，清晰表明自己认为正确或错误，把不同观点在论点中详细表述。
+- 注意不能照抄。
+- 最后简单总结观点并升华。
+案例：1940年抗战时期某材料，四个观点分别为：国民对本国历史应略有所知；了解本国利益会有威胁和利益；对本国历史有敬意则不会偏激；经济方面观点。学生选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。
+**四、图表信息类解题方法**
+- 迅速看图表关键信息，包括题头、横向纵向信息。
+- 注意信息之间的关系变化，提取有效信息再分析。
+案例：中国历代民德等级变化图表，涉及春秋、东汉、宋明等时期；讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
+# 课堂互动与答疑
+问 → 答：学生就武汉长江大桥一题作答，涉及新中国成立、改革开放、对内改革对外开放的时间顺序。老师指出按顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
+问 → 答：学生就1940年抗战时期材料分析四个观点并选择第二条作答。老师追问为什么在这个时期写这个东西，提醒学生写的时候要想清楚写作背景。
+问 → 答：学生就中国历代民德等级变化图表作答，涉及春秋、东汉、宋明等时期。老师引导讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
+&gt; 观点必须明确亮出，不能只是简单陈述或加个名词。
+&gt; 论证写两到三条，不宜太多，要能支撑论点。
+&gt; 最后论述要升华，不能简单把观点抄一遍。
+# 课后任务与学习建议
+未提及</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>12357/1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="13.5" customHeight="1" s="9">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:01:21
 各位代表。第14届全国人民代表大会第三次会议。出席代表2929人。今天的会议出席2880人，缺席49人，出席人数符合法定人数。现在我宣布，中华人民共和国第十四届全国人民代表大会第三次会议开幕。请全体起立，
 发言人 2  00:02:10
 唱国歌。
@@ -9017,9 +10788,36 @@
 各位代表，信心凝聚力量，实干谱写华章，我们要更加紧密的团结在以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，迎难而上，锐意。进取，努力完成全年经济社会发展目标任务，确保十四五规划圆满收官，为以中国式。
 发言人 2  00:49:00
 现代化，全面推进强国建设，民族复兴伟业，不懈奋斗。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:10
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>政府报告</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t># 报告概况
+国务院总理李强代表国务院向第十四届全国人民代表大会第三次会议作政府工作报告，请代表审议并请全国政协委员提出意见。报告回顾2024年工作，指出过去一年我国发展历程很不平凡，党的二十届三中全会对进一步全面深化改革、推进中国式现代化作出部署，我们隆重庆祝中华人民共和国成立75周年；面对外部压力加大、内部困难增多的复杂严峻形势，经济运行总体平稳、稳中有进，全年经济社会发展主要目标任务顺利完成，高质量发展扎实推进，新质生产力稳步发展。报告同时指出面临的困难与挑战，明确2025年经济社会发展总体要求和政策取向，并部署2025年政府工作任务。报告强调，今年是十四五规划收官之年，要高质量完成十四五规划目标任务，为实现十四五良好开局打牢基础，并开展十五规划编制工作。
+# 核心政策
+2025年主要预期目标：国内生产总值增长**5%左右**；城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**；居民消费价格涨幅**2%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.4万亿斤左右**；单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。财政政策方面，实施更加积极的财政政策，今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；发行超长期特别国债**1.3万亿元**；发行特别国债**5000亿元**，支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。货币政策方面，实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配。政策取向强调强化宏观政策民生导向，经济政策着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生；打好政策组合拳，健全和用好宏观政策取向一致性评估工作机制。
+# 重点工作
+经济领域：大力提振消费、提高投资效益，全方位扩大国内需求，实施提振消费专项行动，安排超长期特别国债**3000亿元**支持消费品以旧换新，今年中央预算内投资已安排**7350亿元**；因地制宜发展新质生产力，加快建设现代化产业体系，培育生物制造、量子科技、具身智能、6G等未来产业，持续推进人工智能加行动；推动标志性改革举措加快落地，高质量完成国有企业改革深化提升行动，纵深推进全国统一大市场建设，综合整治内卷式竞争；扩大高水平对外开放，稳外贸、稳外资，扩大电信、医疗、教育等领域开放试点，推动高质量共建一带一路走深走实。民生领域：更大力度稳定和扩大就业，实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；强化基本医疗卫生服务，深化以公益性为导向的公立医院改革，优化药品集采政策；完善社会保障和服务政策，城乡居民基本养老金最低标准再提高**20元**，适当提高退休人员基本养老金，制定促进生育政策、发放育儿补贴；加强精神文明建设，推进群众身边运动场地设施建设。科教领域：深入实施科教兴国战略，制定实施教育强国建设三年行动计划，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科、加快双一流建设；推进高水平科技自立自强，加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合。三农与区域领域：着力抓好三农工作，稳定粮食播种面积，严守耕地红线，有序推进第二轮土地承包到期后再延长30年试点、扩大整省试点范围；推进新型城镇化和区域协调发展，科学有序推进农业转移人口市民化，支持经济大省挑大梁。环保领域：协同推进降碳、减污、扩绿、增长，持续深入推进蓝天碧水净土保卫战，建立一批零碳园区、零碳工厂，加快建设沙戈荒新能源基地。风险防范领域：有效防范化解重点领域风险，持续用力推动房地产市场止跌回稳，稳妥化解地方政府债务风险，积极防范金融领域风险。&gt; 报告强调，确保十四五规划圆满收官，为以中国式现代化全面推进强国建设、民族复兴伟业不懈奋斗。</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>10273/1661</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="13.5" customHeight="1" s="9">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:10
 各位业主大家各位专家大家好，就是说大家有什么疑问的话呢可以来提问。我来这个答疑，谢谢大家。
 发言人 2  00:00:31
 我这里有几个问题啊，呃第一
@@ -9215,9 +11013,37 @@
 不知道吧？你说。
 发言人 2  00:35:33
 本第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。那么通过我们今天的评标，呃第一名。正标人，候选人为呃深圳市资平物业发展有限公司，提交完毕。好，那么恭喜我们的深圳市林业发展有限公司今天的招标活动圆满结束，谢谢大家。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:05
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议为景城苑项目物业管理服务招标答辩与评审，三家投标单位依次陈述并回答评委提问。长沙富佳物业答辩称改造项目已在标书117页列明共12大改造点、预计一年内完成，针对车辆乱停将先分析原因再增加停车位或派保安客服现场劝阻，承接查验方面提出提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先私下沟通、再请业委会或街道社区组织协调会、仍无法解决则在业委会及业主大会和街道社区许可下采取强制措施，并针对监控门禁失效提出增设人行门禁、升级大堂报到系统、地面增设隔离墩、建设外围停车场、增设电动车停车场五方面改善。深圳资平物业介绍公司成立于04年、总部深圳、全国367个项目其中127个业委会项目、创始人陈志平为万科物业创始人，提出洗理静音、疏金活选、疑难杂症、有效提升四步计划，计划半年到八个月内完成、一年以内保证小区有序，团队编制16人、薪酬福利高于同类项目、一线人员直招不外包；包干制方面称湖南11个项目中10个为包干制，强调财务透明和业主知情权，公益服务包括居家上门免费、家政、24小时业主护送服务等有偿和无偿业务；承接查验方面提出与社区街道派出所沟通、与现有物业及业委会明确设备设施和债务债权、按专业线分组并调动集团工程师协助查验、在16人团队基础上增派150%人员；安保方面提出关键岗位用老员工、来访人员车辆登记核实后放行、收集业主车辆信息制定停车管理方案和公约、升级道闸识别外来人员和业主；针对楼层顶层堆放杂物和乱搭乱晒提出宣传引导、联合社区应急管理部门、给业主时间段处理杂物、设集中晾晒区并提供免费上门拉送增值服务，强调要疏而不是强制。评标环节评委打分去掉一个最高分和一个最低分，品牌质量需三人签名，打分环节全程保密、暂停会场网络直播、录像材料不予公开。公布排名为第二名长沙富佳物业管理有限公司72.91分、第三名湖南恒居恒基居业物业管理有限公司60.73分、第四名重庆新东源物业管理有限公司54.48分，第一名中标候选人为深圳市资平物业发展有限公司。
+## 富佳物业答辩
+- 评委问中标后从哪些方面改善小区现状及预计时间，富佳回应改造项目已在标书117页详细说明，共12大改造点，预计一年内完成。针对车辆停放不规范、电动车乱停现象，富佳回应先分析乱停原因（停车场地不够、业主觉得远、不自觉），再针对性制定措施：车位不够则增加停车位，不自觉则派保安和客服现场说服劝阻纠正。承接查验方面，富佳称有丰富二手小区交接经验，提前两周项目负责人入场摸底，提前一周服务人员到位培训；交接分顺利和不顺利两种情况，不顺利时先与县物业私下沟通，公司间无法解决则请业委会或街道社区组织协调会，仍无法解决则在业委会、业主大会及街道社区许可下采取强制措施。针对监控门禁失效与停车管理混乱，富佳提出五方面改善：大门口增设人行门禁系统（微信、卡、密码进出）；升级大堂大门报到系统，录入业主车辆信息统一管理，临时车辆由安保登记放行；地面增设隔离墩禁止公共场所停车，保证消防和人行通道畅通；建设外围停车场并安装停车管理系统；增设电动车停车场。关于类似项目管理经验与满意度收费率，富佳称没有很相似的小区，采取用心倾听、如实记录、马上处理、及时反馈的方法处理业主投诉和反馈。
+- 评委问包干制经验及中标后公益性福利拓展服务，资平称湖南11个项目中10个为包干制，强调财务透明和业主知情权，团队直招，管理干部30%来自现有、60%左右来自现有物业优秀员工及招聘，公益服务包括居家上门免费（材料费业主自买或代购）、家政、24小时业主护送服务等有偿和无偿业务。承接查验方面，资平提出前期准备要充足，与社区街道派出所沟通，与现有物业及业委会明确设备设施和债务债权；按专业线分专业组，调动集团工程师协助查验；在现有16人团队基础上增派150%人员；成立成熟小组，建立标准，确保查出问题不遗留不明事项。安保方面，资平回应关键岗位（门岗、门勤岗、车务）用老员工，对来访人员和车辆管控登记核实后放行；收集业主车辆信息，制定停车管理方案和公约，升级道闸识别外来人员和业主；监控方面利用自有设备公司和技术手段解决关键岗位和部位监控。针对楼层顶层堆放杂物与乱搭乱晒，资平提出宣传引导，上门宣传和海报，让业主明白风险和法律责任；联合社区应急管理部门；全面沟通；给业主时间段处理杂物；物业可提供闲置区域临时堆放但限期解决；针对晾晒，设集中晾晒区，物业可提供免费上门拉送增值服务，强调要疏而不是强制。
+## 评标结果公布
+- 评委打分去掉最高最低分，品牌质量需三人签名。公布排名：第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。第一名中标候选人为深圳市资平物业发展有限公司。打分环节全程保密，暂停会场网络直播，录像材料不予公开。</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>11743/1996</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="13.5" customHeight="1" s="9">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:05
 三观正直一把尺，扎扎实实讲历史。我是李正，欢迎来到正直讲史。我们本期要讲的人是康熙朝文渊阁大学士陈廷敬。在康熙王朝的影视剧中啊，比起党同伐异的索额图与明珠，陈廷敬仿佛永远忠诚老练。在影视剧中，他既支持撤藩，又毛遂自荐招抚台湾，甚至征剿格尔丹时，他还全力维护过康熙的后勤粮草。
 发言人 1  00:00:29
 不过我们要说以上这些事，历史上的陈廷敬都没有做过。但这并不是说陈廷敬他不重要，恰恰相反，历史上的陈廷敬直到临终前，康熙依然在询问着他说，朕的大臣中是否还有其他像你一样的人。康熙的原话叫，朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？
@@ -9323,9 +11149,48 @@
 像《论语》中讲，叫苟正其身矣，于从政乎何有？意思说一个人只要自身品。行端正，那么治理正义就没有什么是困难的。那这句话或许是陈廷敬在3岁时就听他妈妈张氏讲过，可陈廷敬帅就帅在他儿时学过的那些道理，直到死他都没有违背过。好了，那关于陈廷敬的故事我们就讲到这里吧，内容可能有些琐碎和平淡，没有大开大合的那些波澜壮阔的事情，也不知道有多少小伙伴会一直看到最后啊，那也希望看到最后的小伙伴能给 up 来个一键三连，这是对我更新的最大鼓励。
 发言人 1  00:25:31
 感谢感谢。另外想了解更多。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:03
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本期由李正主讲，讲述康熙朝总理南书房大臣、文渊阁大学士陈廷敬的一生。讲座分三个阶段：母亲张氏的开蒙、圣祖康熙的讲师、至公无私的落幕。主讲人首先澄清影视剧中陈廷敬支持撤藩、招抚台湾、维护征剿噶尔丹粮草等情节历史上均未做过，但康熙临终前仍询问大臣中是否有像陈廷敬一样的人。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第六代读书为官，母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》，14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
+# 核心观点与论证
+第一阶段「妈妈张氏的开蒙」：论点为陈廷敬童年学习一大半在母亲张氏关照与注视下展开。论据包括：母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，嫁入陈家后每日干完家务即读书背诵，半夜不睡继续看书；陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》；9岁作《咏牡丹》诗，母亲夸其为天才；14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
+第二阶段「圣祖康熙的讲师」：论点为康熙重用陈廷敬主要因其课教得好、专业过硬、教学风格外放狠辣。论据包括：陈廷敬入翰林时与直隶通州同届进士陈敬重名，因对方不习清书被顺治点名批评并罚俸一年，22岁的陈廷敬主动上书改名廷敬，传说廷字为顺治所赐；顺治18年庶吉士毕业考试获同届第一，授秘书院检讨；顺治驾崩、母亲病倒后请假归乡三年；康熙六年考察一等称职，32岁升国子监司业，整顿国子监拒收学生见面礼，两年内连升三级，34岁官居翰林院侍讲学士，35岁被19岁康熙任为日讲官；康熙15年九月以内阁学士兼礼部侍郎充经筵讲官，时年39岁；康熙16年正月任翰林院长院学士教习庶吉士，同年母亲张氏去世，终年59岁，康熙令满汉一体遣大臣往祭，礼部以封号不合规反对，康熙追封按学士品级官方祭奠。
+第三阶段「至公无私的落幕」：论点为陈廷敬21岁入官场，75岁去世，宦海浮沉50年声名清白、恪守初心。论据包括：康熙20年守孝三年后重返官场执掌翰林院；康熙23年47岁升从一品左都御史，上奏要求捐纳买官者正式上岗前追加考试，吏部反对，康熙支持并令各地督府详查已任命官员，凡不识字义者查参修治；此后连续出任工部、户部、吏部三部尚书。康熙26年50岁时湖广巡抚张谦贪污案发，张谦为陈廷敬老乡兼亲家，口供称曾贿赂陈廷敬、徐乾学、高士奇，证据为三人劝其好好当官的信件；康熙传旨主审官马齐只处理张谦一人，不得扩大株连，其他人事后密查；51岁陈廷敬主动上书辞官，康熙准许辞官但留京修书；康熙29年53岁重新启用为左都御史，后一年刑部尚书、六年户部尚书、四年吏部尚书；康熙42年66岁升文渊阁大学士兼总理南书房；康熙46年70岁起连续三次申请退休被拒，康熙49年73岁第四次申请获准，康熙赐匾额五亭山村及楹联；两年后病逝，终年75岁，谥号文贞。
+争议点：张谦案真相至今没有公开定论，康熙一时间无法确定徐乾学、高士奇、陈廷敬三人谁干净谁不干净；主讲人个人倾向陈廷敬无辜，理由为李光地称张谦案始终皆徐乾学所为、徐乾学贪污事迹多且热衷结党、徐乾学与高士奇后均因贪污被罢官而陈廷敬仅辞官一年即被康熙重新启用为左都御史。
+# 金句总结
+「朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？」——背景：康熙临终前仍询问陈廷敬，体现康熙对陈廷敬的念念不忘。
+「无鼠相存，譬犹唇齿，不必智者而知之。全记上书以讨荆州自效，明年全破斩云长传其手，全其屯权也哉。」——背景：陈廷敬在文集中指责孙权背刺关羽，体现其教学风格外放狠辣、三观坚定。
+「以平靖世将握秦而恩福待，吾何以劝劳臣乎？」——背景：礼部反对官方祭奠陈廷敬母亲，康熙以此表态，最终追封按学士品级祭奠。
+「自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。」——背景：陈廷敬任左都御史时上奏要求捐纳买官者追加考试。
+「临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治。」——背景：康熙支持陈廷敬并令各地督府详查已任命官员。
+「臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节，所以臣之心迹极此可白，而臣之自处虚实所疑，唯当隐退田间，永衔恩于高厚。」——背景：陈廷敬因张谦案主动上书辞官。
+「朕特殊匾联赐卿，自此不与人写字矣。」——背景：康熙49年准陈廷敬退休，赐匾额五亭山村及楹联。
+「苟正其身矣，于从政乎何有？」——背景：主讲人引《论语》总结陈廷敬一生，称其儿时学过的道理直到死都没有违背过。
+# Q&amp;A 环节
+未提及</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>9132/2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13.5" customHeight="1" s="9">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:03
 有的美感。
 发言人 2  00:00:05
 因为他是这样，就是中国的这个在宋明这两。
@@ -9929,9 +11794,91 @@
 我们。
 发言人 1  00:32:29
 强强3</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:04
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>采访记录</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本次对话由马先生与当年明月参与，围绕刚播完的日本历史剧《大奥》与《明朝那些事》展开。当年明月指出《大奥》三部跨越日本晚清至明治维新前，吸引他的是严谨精神，剧中演员认真、片头将军出场时众人呈45度鞠躬的场面令他印象深刻；马先生补充大奥即后宫之意，日本话中“奥”指屋子最深处，大奥规矩严谨、后宫不许进人。当年明月由此引申日本文化核心是极端精神，即所有事情做到尽头，并以日本战后用30年成为世界第二经济强国、且是强国中唯一没有资源的国家为例。马先生则从多次赴日经历谈到日本人的坚韧不拔与忠诚，称日本是忠诚文化的典型国家，并举例日本豆腐厂规定当天做当天卖、夜里11点45分所有人坐着看表、12点整才开始干活。话题转向明朝历史与《明朝那些事》，当年明月表示自己写明朝是因为明史最熟、资料最多，历史研究两大难点是先秦与明清，明清资料如明实录几千万字、明通鉴、明史记事本末、明会典等堆得比山高，但一个说法可能有七个不同。当年明月表示推崇朱元璋，因为他是历史上唯一由最底层乞丐坐上皇位的人，刘邦好歹是村长，朱元璋要过饭、知道每一层猫腻所以疑心重，推翻元朝当上皇帝并定下明朝规章制度、基本没有太大改动。当年明月还称“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因为史书只留下照片、而古人的生活是录像，不知道当时的前因后果，不能套用。
+# 访谈详细记录
+一、《大奥》与日本文化
+- 当年明月指出《大奥》三部大概前两部相当于中国的晚清到清初这个时段，后来还有一部是在明治维新之前的一段时间，是一个有跨越性的历史剧。
+- 当年明月称吸引他的是觉得有一种严谨的精神，回头看三国演义会看到很多群众演员会笑，但看日本剧看不到笑的，每一个人非常认真、特别有专业精神，而且都像大腕跟那演。他看第一集一个片头就被震了：将军出场的时候，所有的人呈45度开始鞠躬，依次那个场面之华丽，包括色彩，一看就不一样。
+- 马先生称大奥就是咱们的普通话叫后宫，日本话的这个奥是指很深的地方，就是屋子最里处叫奥，比如咱们现在还保留这种痕迹，就是说这个道理，深奥，奥是很深的地方。
+- 当年明月称从大奥那个剧可以看出来，一个日本文化，其实他从头到尾没有变，就是日本人一种精神，叫极端精神，所有的事情要做到尽头。
+- 马先生称日本战后1945年以后，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然，就是他全民族的这种极端精神，是一个国家在战后这样一个不利的局面下，只需要30年的时间，他进入世界第二经济强国，是以绝对量，不是人均量，绝对量，他是一个世界上这个强国里唯一没有资源的国家。
+- 当年明月称日本的文化跟中国的文化存在一个极大的不同，中国的文化精神是中庸，讲究这个世界上有一种道，不是对也不是错，不是黑也不是白，不是真理也不是谬误，就是太极，但是这条路可以走得通，叫融合。他以马先生家具店中拿了一番木头，特别硬的木头，上面刻的是云彩为例，说这么硬的一个东西能做的这么柔软，这就是中庸。
+- 当年明月称日本的精神就恰恰相反，他坚持一个原则，假如一个炮手开炮的时候，当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。
+- 马先生称我们文化中有很多东西可以从电视剧里去看，他实际上看很大程度是看日本文化，我们的文化跟他的差异性非常大，所以导致很多民族的这个观念性的冲突。他去过、多次去过日本，在日本中没有感受到很难过的时候，也没有谁对你非礼。文化上的差异从这个电视剧看得清清楚楚，比如日本人的坚韧不拔，他说的做到极致，再有他的一个忠诚，它是一个忠诚文化的典型国家。
+- 马先生称日本人的跳槽率是最高的，每一次跳槽都是社会资源的浪费，你刚把这个人培养好了，能给你为你工作了吧，他跳槽了。当年明月称这是经济学上的一个奇迹，西方经济学还是不能理解，为什么他们有一个原则，经济学原理可以讲，叫终身雇佣制，就是这个缺乏竞争，日本可能公司终身雇佣，不会解雇你的，一定会导致工作效率的极低效，但是日本不对，日本是终身雇用了，人家还是基金特别高。
+- 马先生举例日本豆腐厂规定当天做当天卖，夜里11:45，所有人都在那做好不动手，在那坐着看着表，那表到12点，夜里12点一整，所有人都赶紧开车，最后那秒是8一到那所有人开始干活，然后到4点多钟干完，然后就开始上市。当年明月称这叫一丝不苟。
+- 当年明月称日本没有资源，什么都没有，还经常火山地震，说难听点你跑都没地方跑，所以人本身对这个世界有一种极强的求生欲望，或者说他对于这个世界是悲观的，必须努力求生存的，所以他就学会了一点，人只有融入到那个团体之内，按照一个固定的规则去做事，于是我们才能往前走，才能生存下来。
+- 马先生称日本的这种聪明人都没有生存环境，他社会的那种文化的抵制是非常难过的。他举例日本原来做绳子，可能一根绳子能做到全日本第一的人，他在长达几年的时间内是不赚钱的，他是从这个地把什么批发出来给那个人送去1分钱都不赚，那所有人跟他竞争是竞争不过，因为他是不赚钱为代价的，等他全部把市场都铺平了以后，他会把两张单子给你看，你看我是这个钱进的，就是这个钱卖的，你怎么也得让我挣一点钱吧，你能不能让给我2%，然后这时候是不好意思再给你加个2%，拿这张单子跟这边说，你看我卖了以后这个也不挣，所以你再给我加2%，那全国的东西它就4%就是不得了的一个数，它就挣那么大钱。
+- 当年明月称慢慢来才是最快的方法，所有人按照自己的角度去做自己的，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走，我是商人就做商人事，我是奶妈就做奶妈的事，我是王后就做王后的事，我什么都可以做自己的事，就是不管别人的事，但这种情况下，形成合力就非常可怕。
+- 当年明月称说实话这是很不愿意做日本人，因为他很多时候就像你说盲从，他们本身还有一个特点，有一种寻死的那种潜在欲望，看樱花开的时候不看，发芽都不看，就是落那一天就看，他们总觉得由于常年以来生活在岛国上，确实生态环境太恶劣了，所以他对于死亡他不是说藐视死亡，他是应该说是有点向往的感觉，或者说不惧怕。他称二战日军到中国会有那么暴行，他是一种藐视生命。
+- 马先生称日本民族不是藐视生命，他是重视，是翻着的，日本人在经济危机的时候，很多身家万贯的跳楼。
+二、明朝历史与《明朝那些事》
+- 当年明月称自己写明朝是因为明史最熟，因为明史的资料最多，历史界研究有两个难点，第一个是先秦，第二个难点就是明清，明清没法说，明实录几千万明代史官的记录，明通鉴、明史记事本末、明会典等堆的比山还高，但一个说法可能有七个不同，一个事件可能有七个不同的说法，就好像罗生门，一件事五个人看，个个都不同。
+- 马先生称明朝本身260多年的过程本身就跌宕起伏，从某种意义上讲，明朝几次都要死没死了，土木堡之变、夺门之变就是各种之变特别多，皇上已经被瓦剌军给抓起来了，要把弟弟扶起来，这类事完全构成一个现代版的电视剧，因为只有电视剧才能捏造出来这种极为离奇的情节，但生活中不幸就发生了。
+- 当年明月称推崇朱元璋，因为一个乞丐，历史上由最底层的人坐在位上，叫他独此一个，刘邦好歹是个村长，朱元璋要过饭，他因为知道每一层的猫腻，他就疑心重，但他全知道，这种人才上。他称朱元璋从一起干，一直到最后，推翻元朝，当上了皇帝，定了多少规章制度，明朝的规章制度是由他定下来的，基本上没有什么太大的改动，这个人是多了不起的人才。
+- 马先生称人的因素最大，就是改变时势一定是出现一个人，是英雄史观。
+- 当年明月以亮剑中李云龙没上过军事院校能打仗为例，称会打仗的人打，不用看兵书，一个人到战场上死死生生多少年，没死，最后积累下来经验，然后一上战场就知道敌人会往哪走，我该怎么打。
+- 当年明月称历史最重要的是你要明白它是发生过的，很多人看历史会觉得这个故事好玩，他不好玩，旁观者你看的多好玩，一跺脚就去参加起义去了，那不可能，你想他掉脑袋的。他称你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
+- 马先生称明朝还是有很多时期非常不错，比如明朝的仁宣盛世，现在不怎么提，时间因为太短，晚明的时候尽管过去史书上一代说政治如何如何黑暗，皇帝如何如何不上朝，但老百姓生活很好。
+- 当年明月称明末那段时间很多真相都被掩盖了，那个市民生活特别特别轻松，想去哪去哪，当时连那个皇册都不用了，到处走，而且当时去给人打工，当年江浙一带兴起的工商业，就是给人当雇工，那活得很滋润，就像三言二拍这种市民小说，娱乐产品出现才说明它是有能够养活自己的资本了。后来李自成那个时候闹起义，那是因为那个时候陕西那一带发生了大规模的灾荒。
+- 马先生称当时江南的也比电影中很多当时的器皿中就可以看到人的那个生活的乐趣，比如一个瓷器，我们的工艺品到了明末的时候彻底改观，变得非常精细，有点像日本的工艺，非常精细，日本有很多东西学我们明末的，派了大量的工匠跟中国交流。
+- 当年明月称看到的史料就是穿什么都有，至少江南那一带他确实非常富裕。马先生称吴门画派像文征明、唐寅，都是那个时期的，他如果生活不好，这些人就也画不出那个东西来，他画的一定都是兵荒马乱的。一到朱耷的时候，八大山人，他默了，你看他画的都是那翻白眼，为什么呀？就他对这社会有点愤愤不平了。他前面这部分人，吴门画派的那些人都能画的都是那个小桥流水，画一个风雨归舟图都是充满了欣赏的感觉。
+- 当年明月称我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训，因为这事儿不是你办的，你总觉得那个以往人就该怎么办，都是聪明的，错误的，我们没有意识到一个问题，历史他那个事儿发生的时候是有背景的，当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。他称我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像，在史书上下来的只是一个照片咔嚓，但你不知道为那一幕之前和之后是什么，你就不知道他当时为什么要做这个选择，所以很多人对历史有误解，他总觉得从中可以得到什么经验教训，那千万不能套用。
+- 当年明月称明代这个朝代很有趣，什么都有，宦官专政魏忠贤，文官专政张居正，皇帝专政朱元璋，而且什么都能发生，皇帝出去了还能回来，回来了还能做皇帝。
+- 当年明月称晚明时期就更可笑了，吴三桂要跟满清合作要入关，陈圆圆，但是还有个原因，他认为崇祯死了，当时人家的说法，我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝，崇祯皇帝当然可以不死，早点跑应该不跑。还有包括1644年就是明朝灭亡那一年，为什么你们曾经打到京城没有人抵抗呢？因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天你看疙瘩瘟就什么天花。
+- 马先生称中国的历史王朝300年都是大限，你一逼近300年的时候，你自己就没了，和人一样，这人一到八九十岁的时候，你的大限就快到了。他称中国历史上如果严格的讲，超过300年大限的只有宋朝，南北宋接上以后，因为他好在是接上的，汉朝中间往往隔断14年是彻底空的，那么他呢是退让了大半个国土，保证了他延续了300年，剩下的唐朝、明朝、清朝都没他。
+- 当年明月称你说你今天数世界上公司超过279人有几家？没有几家，人家公司多容易管呐，当年刚成立的时候可能三五个人，你说明朝做多大多大摊子啊？几千万人。
+- 马先生称中国在宋明这两个朝代是典型的汉人政权，汉人是文人政权，文人肯定是欣赏的审美都比较高，所以他对美的判断不是表象的，但是满族因为他毕竟是个异族，他进来以后呢，他对你的判断都是表象的。他称今天凡是那种非常外在的直观能看到的都卖的非常贵，但是在100年前的时候，就是晚清到民国初年的时候，这个东西值钱的一定是素雅的。
+- 当年明月称明朝皇帝九五至尊，想干什么干什么，但皇上说我要去一趟江南，皇上当然不行，真不行就不行，咱就是不让你去，明武宗要去，不让去不让去，跪金水桥前门，就是全部跪了，跪着抗议，后来气坏了，就到锦衣卫去打，打死了十几个。
+- 马先生称这种文化的力量，我们一直过去有时候老忽略这种力量，我们现在是没这种文化的力量，他文化的力量是一个超出我们想象的。
+- 当年明月称明武宗正德到扬州说我要什么东西，这时候没有啊东西没有了，有也不给，然后就说什么，那行，那我就回去，他让人准备酒席，他说那个吃不了，说怎么办呢？这样吧，把你们那个酒席折合的银两我带回去，我这皇帝他打这个秋风。
+- 马先生称正德皇帝在明朝的整个皇帝不是一个最最特殊的行为，最鬼怪个性，我们对他的过去的评价是非常低的，说他荒淫，报房是他闹的。他称爱当木匠的是天启，最后了直接干活，干完活了他干的乐就更更有意思，他干完活以后，他拆大盆去卖，卖完回来还打听，卖的怎么样？他说卖的很好，他成就感特大。
+- 马先生称他从侧面去反映了当时社会的一种时尚，他绝对不是凭空，当时这个家具在每个人心里边地位高，为什么我们明式家具现在在国际上那么高的地位，这绝对不是偶然的，所有的偶然中一定有个必然的因素，当时皇帝能下那么大力气去做，可见这个东西对他的影响之深。
+- 当年明月称明神宗几十年不上朝，但他不出去，包括明武宗正德，但凡是明朝皇帝，一般说来后人是不会说乾隆自己朝代的呀，我都是明朝人，我怎么会说我朝的皇帝多差呢？为什么他特别差？因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以他不能够把他写的太好，所以说像正德皇帝为什么说他特别荒淫？我们都来报房，其实就玩，报房，他那个有动物园，他真是有动物园，他里边养了豹子，后宫也是女人嘛，爆房也是女人，放哪都是一样的，不影响其他什么问题。
+- 马先生称正德皇帝是有定论的，说清朝明朝最荒淫的皇帝，那清朝最荒淫的是咸丰，咸丰干的那个事都很过分，但咸丰还留了个种，这正德不留种，这事很奇怪，就他这个人没少找女人，但他不留种。当年明月称不好说。马先生称他有没有生育，有记载他怀过吗？但反正他就是没有正宗的传下来，到嘉靖这是拐弯嘛。
+- 马先生称正德皇帝对东平以外的那个女人确实没兴趣，那女人是被训练过的，禁忌多，太保守了，再说这人是王丽一去就自个就先睡了半边，那个民女不知他是谁，不是圆了干，他就不一样，关键是野花不知道他是。
+- 当年明月称据说是去过，但是这个没有具体的史料能够去，哪个史官说皇上今天出去嫖娼，我要打死了，不能记的。他称这个人绝不是史料上所写的那么那么蠢，他从江南回来，他没有进京城，他在通州先停了半年，为什么呢？先派人打探里边有没有人带，这是史料记载，通州停了半年或一天，先停在这，你们先给我把情况看清楚，京城里有没有人想搞埋伏，搞圈套。马先生称很有城府。
+- 当年明月称这个人还真的是被写坏的，就是嘉靖那个时候因为明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般来说，他都有某些程度的偏颇，因为如果你把他说太好，嘉靖上台先搞了个叫什么大礼仪事件，为这事死了很多人，也折腾了很多人，就会给自己父亲真的明白，因为他父亲是王，他又把他追封为皇帝。所以说历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
+- 马先生称看很多人专家写历史，就觉得现在不爱聊什么西方傲慢与偏见嘛，实际很多人研究历史就有傲慢与偏见，就是你没有设身处地，你老觉得你自个聪明，我判断他昏庸无能。
+# 关键引语与金句
+&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+&gt; 慢慢来才是最快的方法。
+&gt; 历史最重要的是你要明白它是发生过的。
+&gt; 你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
+&gt; 我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像。
+&gt; 中国的文化精神是中庸。
+&gt; 日本的精神就恰恰相反，他坚持一个原则。
+&gt; 日本战后以后呢，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然。
+&gt; 他是一个世界上这个强国里唯一没有资源的国家。
+&gt; 这叫一丝不苟。
+&gt; 所有的偶然中一定有个必然的因素。
+&gt; 历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
+&gt; 原话引语……</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>17496/6601</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="13.5" customHeight="1" s="9">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:04
 说当年的感觉已经远去，这是很痛苦的，我已经把那个40多最好的一段时间浪费了，就拖了2个多月，活着也蛮认真的。
 发言人 2  00:00:14
 我这还忍着。
@@ -10285,9 +12232,97 @@
 那也
 发言人 1  00:25:42
 那也是勉强吹进来的。假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。是当年的感觉，这是很痛苦的。我已经把那个40多岁到50岁最好。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>采访记录</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本次访谈围绕作家余华的写作历程、创作状态与面对批评和网络关注的心态展开。余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段：第一阶段逼自己坐下来写，让屁股和椅子建立友谊；第二阶段受卡夫卡启发，写内心动荡不安的人物；第三阶段受威廉·福克纳启发，用视觉描写替代心理描写，如《狂人日记》中赵家的狗看人一眼。3.0之后没再升级，他认为《活着》可能是4.0版但已不是难题，3.0版本已经是大海，够了。他自述最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品；2006年开始写的一部长篇小说，现在身体状态可能还能维持激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来，他估计能好好写作的时间可能只剩十年左右。他回应《第七天》出来时有教授说他变得仁慈了，说自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。面对批评，他形成的方式是：第一不要去看，第二有些批评要重视；他在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期，但自媒体时代会把几十年前的事情和以前说过的话翻出来，互联网上关于他的话有一半不是他说的。被问及希望以什么姿态留在历史长河，他回答“遗忘的姿态”，假如历史长河里有主题，主题就是一个世界、一个一个人。
+# 访谈详细记录
+一、自学游泳与文学创作的三阶段
+- 余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段。
+- 第一阶段：逼着自己坐下来写，“让屁股和椅子建立友谊”，这是年轻时候最重要的；如果离开写字桌躺到床上幻想作品多牛逼，可能就不会去写它。
+- 第二阶段：受卡夫卡启发，写内心动荡不安的人物；写一个人物内心平静没有意思，内心动荡不安的话写1万个字。
+- 第三阶段：受威廉·福克纳启发，福克纳写一个穷白人把一个富白人杀了之后的内心状态，采用“让心脏停止跳动，让眼睛睁开”，心理描写没有心理，是视觉描写；如《狂人日记》中赵家的狗看人一眼，就知道这个人精神状态。余华去过精神病医院，认为精神病人说话逻辑是清晰的，只是方向不同。
+- 3.0版本之后没再升级，他认为《活着》可能是4.0版，但对他来说已不是难题，写作已经很成熟；写一个没什么文化的农民讲述自己的故事，要用最朴素的语言。他认为3.0版本已经是大海，够了。
+二、写作状态与身体、感觉的流失
+- 余华认为最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品。
+- 2006年开始写的一部长篇小说，时间跨度与《兄弟》一样，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写；现在身体状态可能还能维持这种激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来。
+- 他估计能好好写作的时间可能只剩十年左右。
+- 他提到《十八岁出门远行》一天就写完，有6000字，对写字较慢的他来说是奇迹。
+三、《兄弟》的创作与时代变化
+- 《兄弟》1996年动笔，当时中国社会变化复杂；2003、2004年重新拿回来写时，庆幸1996年没写完，因为从2004年看，1996年的变化不算什么，那才是真正大的变化。
+四、作品出版间隔与下一步计划
+- 从《在细雨中呼喊》到《兄弟》隔了十年，《兄弟》到《第七天》隔了八年，《第七天》到《文城》又隔了八年。
+- 余华希望快一点，已把这边整理完，开学时要去和学生们见一下，学校还有一些事情要处理，完了以后回三亚继续往前，安安静静把感觉找回来。
+- 被问下一步长篇是否在2029年，余华未明确确认。
+五、童年看海与人生感受
+- 余华童年第一次看到大海，感受到人生是宽广的。
+- 小时候每年夏天在海盐游泳，有一次进入海流，不能挣扎只能跟着海流走，一直漂到40里外才爬上来，赤脚沿海边走回来，天快亮了。海流把他带回海岸线，没有带到太平洋。
+- 在三亚看到童年星空，发现月光是金色的，不是银色的。
+六、《第七天》的仁慈与悲剧/喜剧转向
+- 有教授说《第七天》出来时余华变得仁慈了。余华回应自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。
+- 已确认：余华决定先完成一部喜剧作品。
+七、追求宽度而非高度
+- 余华表示对高度已经不追求了，现在追求宽度。认为作为作家，写作能走到的高度已经是现在的高度，允许自己下滑一下但不要下滑太多。
+- 年纪大了，知道自己的能力、长处和还有多少潜力，不再像年轻时充满野心。
+八、文学理想与马尔克斯的影响
+- 余华认为这一代中国作家很大程度上被马尔克斯误导，都想在一本书里写一个世纪的故事，但其实没有必要。
+- 托尔斯泰、狄更斯、莎士比亚、巴尔扎克、福楼拜、司汤达、契诃夫等都没有这样做。马尔克斯写拉丁美洲最混乱的世界所以能写出来，别人不一定写得出来。
+- 余华现在知道自己要什么，就是把所处的时代通过更多方式表现出来。
+九、莫言与莎士比亚故居之行
+- 余华说莫言小说对话精彩，想写话剧，20多年前就开始写话剧，但写了没拿出来。
+- 余华、苏童、莫言三人一起去莎士比亚故居，莫言在雕塑前发誓要成为剧作家，余华认为那是瞎扯，莫言当时在挑帽子，帽子钱还是余华付的，三人买了三顶一模一样的深蓝色帽子，上面有莎士比亚名字，后来找不着了。
+十、面对批评与网络时代的心态
+- 《兄弟》出版时余华以为会是一片赞扬，结果一片骂声，他接受很多采访努力解释。
+- 《第七天》出来时只接收一个采访，告诉朋友们做好思想准备，果然一片骂声。《文城》出来时骂声还有但少一点。
+- 余华找到对待批评的方式：第一不要去看，第二有些批评要重视。批评宋凡平写得太完美没有道理，因为宋凡平不是贯穿全书的人物；但批评《第七天》中社会底层人未必都善良，这句话很好，以后写小人物会考虑进去。
+- 已确认：余华形成对待批评的方式，有道理的批评会在以后作品中考虑。
+十一、网络热度与一年冷静期
+- 余华在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期。
+- 按过去经验一年后就在媒体上消失，但自媒体时代不是这样，几十年前的事情都被翻出来，以前说过的话也被翻出来。
+- 互联网上关于他的话有一半不是他说的，比如“精神内耗”“想要命好”等都不是他说的。
+- 他不担心喜欢会消散，因为他的工作是写作，不是靠说话。
+十二、中年危机与自我调节
+- 余华34岁时在年终总结中说成年人每到年底都会发现一种虚无，对生活充满信心的人变成面试者。
+- 当时感觉生活每天在呼吸，人口增加、孩子来了，空间没有变得宽敞。只有写作能得到新的东西，虚构世界带来新东西，现实世界每天都是。
+- 面对年轻人巨大的不安和焦虑，余华认为只有自我调节：发生的事情无法选择让它发生或不发生，但可以选择让自己知道什么、不知道什么，负面消息太多就屏蔽掉，选择积极的。
+十三、希望以遗忘的姿态留在历史长河
+- 被问及希望以什么姿态留在历史长河，余华回答“遗忘的姿态”，就是一个遗忘的人。
+- 那些能够勉强被微风吹进耳朵的人，也是勉强吹进来的。假如历史长河里有主题，主题就是一个世界、一个一个人。
+# 关键引语与金句
+&gt; 坐下来让屁股和椅子建立友谊，这是很重要的。
+&gt; 假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的。
+&gt; 让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视觉描写。
+&gt; 我觉得我活着也蛮仁慈的。
+&gt; 把悲伤留给虚构，把欢乐留给现实。
+&gt; 第一，你就不要去看就行了。第二，有些批评你要重视。
+&gt; 发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。
+&gt; 遗忘的姿态。就是一个遗忘的人。
+&gt; 假如那个历史的长河里边有一个主题的话，这个主题就是一个世界，一个一个人。
+&gt; 我已经把那个40多岁到50岁最好的一段时间浪费掉了。
+&gt; 那个过去那个时代那个感觉没有了。我写到那个80年代的和90年代那个感觉，也在，感觉都在远去。
+&gt; 原话引语……</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>11212/3364</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="13.5" customHeight="1" s="9">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 战役柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，同时也是苏德战争期间苏联和德国进行的最后一场大规模战役。1945年，同盟国和苏俄已经相继从不同方向攻入的德国本土。此时，对于德国来说，他的纳粹政权的覆灭只是一个时间问题。对于苏联来说，占领柏林可以获得至高无上的荣誉，毕竟柏林也是法西斯德国大本营以及纳粹最大的巢穴。谁要是能占领了柏林，谁在。二次世界大战结束之后，可以获得至高无上的一个地位。所以这一次苏联的从上到下，从高层到基层，大家。突奇团结一致，然后以柏林为目标进行了一次不惜代价的强攻。
 发言人 1  00:01:15
 此时苏军已经进抵到奥德河、尼斯河一线，也就是今天德国和波兰的边境地区，距离柏林只有60公里。同时，英美联军才刚刚到达易北河一带，距离柏林还有一百到一百二十公里。显而易见，从其当前部署的位置来看的话，苏联已经获得了先发制人的一次机会。此时对于纳粹德国来说可以说是丧钟敲响的开始此次行动由。
@@ -10381,9 +12416,63 @@
 好，那咱们时间差不多了，咱可以。
 发言人 1  00:16:03
 OK下一个下一个章节，大家准备一下。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:02
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次研讨会围绕第二次世界大战欧洲战场最后一次大规模战役——柏林战役展开，由发言人1主讲，系统梳理了战役背景、双方部署、进攻过程、希特勒自杀、德军投降及战后格局。1945年同盟国与苏俄从不同方向攻入德国本土，苏军已进抵奥德河、尼斯河一线，距柏林仅60公里，英美联军刚到达易北河一带，距柏林100至120公里，苏联获得先发制人机会。苏军由朱可夫元帅和克列夫元帅指挥，白俄罗斯第一方面军从奥德河一线北部突击包围，乌克兰第一方面军从南部绕到波斯坦地区实施西部包围，苏军两个方面军总计约250万人形成合围；德军防守约100万人，以从东线撤离的中央集团军群残兵为主力，另有柏林卫戍部队及由老人和16岁以下孩子组成的国民制弹兵部队。战役第一阶段于1945年4月16日开始，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击；因德军在桑多梅日桥头堡之前修筑防线，苏军拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日突进柏林市区，德军温克第十二集团军与苏军周旋。4月30日柏林被围死，苏联红军离希特勒地堡只有两条街，希特勒与夫人艾娃·布劳恩一起举枪自尽，其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据。4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束，战役从4月16日持续到5月2日。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
+# 核心观点与论证
+论点一：苏联不惜代价强攻柏林，源于占领柏林可获至高无上的荣誉与战后地位。论据：1945年同盟国和苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题；柏林是法西斯德国大本营及纳粹最大巢穴，谁占领柏林谁在二战后可获得至高无上的地位，因此苏联从上到下团结一致，以柏林为目标进行不惜代价的强攻。
+论点二：苏联在部署上已获得先发制人机会。论据：苏军已进抵奥德河、尼斯河一线，即今天德国和波兰的边境地区，距柏林只有60公里；英美联军才刚刚到达易北河一带，距柏林还有100到120公里。
+论点三：苏军以两个方面军形成合围，兵力占优。论据：白俄罗斯第一方面军指挥官为朱可夫元帅，从奥德河一线、奥德法兰克福方向北部对柏林进行突击与包围；乌克兰第一方面军指挥官为克列夫元帅，由克拉科夫以及德雷斯顿方向前出，从南部绕到柏林前突至波斯坦地区，对柏林实施西部包围。苏军两个方面军总计约250万人，从北部石切清一直到南部德雷斯顿形成合围网。德军主要防守部队为从东线撤离的中央集团军群残缺部队、柏林卫戍部队以及国民制弹兵部队（由年纪较大的老人及16岁以下孩子组成的民兵），总共有约100万人，以中央集团军群残兵为主力。
+论点四：战役进程受德军防线修筑影响而延迟。论据：第一阶段1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河突击，乌克兰第一方面军越过尼斯河突击；但由于德军在桑多梅日桥头堡之前修筑防线，一直拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日才突进柏林市区，由白俄罗斯第一方面军进行突击，此时乌克兰第一方面军还在艰难摸索向柏林边缘靠近。德军温克第十二集团军与苏军一直周旋。
+论点五：城市作战与野外作战存在明显区别。论据：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
+论点六：希特勒自杀及遗体争议。论据：1945年4月30日柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽；其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据；除少数亲信外，大部分人坚信纳粹没有覆灭，自欺欺人继续战斗，导致谣言盛起。
+论点七：英美未进攻柏林的原因。论据：丘吉尔想抢占柏林，但盟国已达成协议柏林战后属于苏联，会分出一半区域给西方盟国即西柏林；艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤回去，得不偿失，不如占领更多德国精华地带如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，盟军还有求于苏联一起对日本战斗。
+论点八：战役结束与战后格局。论据：4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队在其将领温克率领下渡过易北河向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
+# 金句总结
+「谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。」——背景：主讲人分析苏联不惜代价强攻柏林的动机，指出柏林是法西斯德国大本营及纳粹最大巢穴，占领柏林可获至高无上的荣誉与战后地位。
+「城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。」——背景：主讲人回答听众关于城市作战与野外作战区别的提问，说明城市作战的困难与危险。
+「希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了，就和他的夫人艾娃·布劳恩一起。」——背景：主讲人回答听众关于希特勒是否自杀的提问，说明希特勒自杀的原因与方式。
+「除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以说各种流传到民间的说法褒贬不一，导致很多后时候谣言还在盛起。」——背景：主讲人解释希特勒自杀细节为何引人关注，指出遗体被焚烧后无确切证据，导致谣言盛起。
+「与其这样，还不如说是尽可能去占领更多德国的精华地带，比如说慕尼黑、斯图加特以及纽伦堡，还有就是汉堡、法兰克福这些地方，柏林就让给苏联吧。」——背景：主讲人分析艾森豪威尔认为美军攻占柏林得不偿失，不如占领更多德国精华地带。
+「那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。」——背景：发言人5补充红旗插上国会大厦的细节，说明旗帜是士兵临时用床单和颜料绘制。
+# Q&amp;A 环节
+问：城市作战跟野外作战有什么明显的区别？
+答：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
+问：是不是这个战役里面希特勒自杀了？
+答：是的。1945年4月30日，德国离兵败之日不远，柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽。
+问：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么引关注？
+答：因为在他自尽之后，他的部下用汽油把尸体焚烧了，到今天为止也没有见到希特勒遗体全貌，只是获得一堆烧焦的焦炭，外界说法各种不一，也没有确切证据证明。实际上他自杀后尸体被焚烧，除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以各种流传到民间的说法褒贬不一，导致很多谣言还在盛起。
+问：如果想了解更多这个战役，有什么影视推荐吗？
+答：苏联有拍柏林战役，德国有《帝国的毁灭》。德国角度更多是希特勒最后生平以及关于柏林防守上的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
+问：主要进攻柏林的是苏联方面的部队，那为什么英美他不打柏林呢？
+答：丘吉尔当时想抢占柏林，但盟国事先已在战后德国地盘划分占领上达成协议，柏林战后属于苏联，会分出一半区域给西方盟国即后来的西柏林。美军统帅艾森豪威尔认为美军去攻占柏林会增加不必要伤亡，同时占领柏林后还是要撤回去，得不偿失，不如尽可能占领更多德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，柏林就让给苏联。毕竟打完德国之后，盟军还有求于苏联一起跟日本进行战斗。
+问：这场战役大概持续了多久？
+答：从4月16号开始，一直进行到了5月2号。
+问：有什么书可以看的吗？
+答：可以看朱可夫自传、崔可夫自传，以及斯大林传记里面写到的关于柏林战役后苏俄和西方的博弈，涉及西柏林地区划分以及德国边境重新划定。</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>4609/3614</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="13.5" customHeight="1" s="9">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:02
 嗯，你买房不是生活中哪些约定俗成的规则其实很不合理，比如必须结婚。
 发言人 2  00:00:13
 必须买房，还有必须结婚生子。
@@ -10515,9 +12604,37 @@
 够了，行。
 发言人 2  00:10:56
 ok停吧，ok，哎，停。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+会议围绕生活中约定俗成的规则是否合理以及AI/机器人未来展开自由讨论，并测试多人同时说话的语音标注效果。与会者就买房、结婚生子、工作等规则交换意见，认为经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对；工作方面提出工作可能是合理的，但工作状态应合理，即干自己想做的、不要跟钱太保密，并讨论理想工作状态是每天起来想干啥就干啥、参考自己兴趣干活，举例宠物博主发宠物日常剪视频赚钱、游戏高手，同时提出脏活累活没人愿意承担的问题。在AI与机器人议题上，提出应让AI去做苦活累活而不是搞创作艺术，设想机器人负责生产、人负责享受，提到扫地机器人及未来可打扫家、做饭的机器人，并讨论AI普及普惠到实体、机器人有自己思维后人类能否控制；进一步讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影，提到机器人可能成为犯罪代理人、职业杀手、超级战士，以及智能与思想可能无法分开、思想可能带来不好影响。讨论还涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。
+## 约定俗成规则与理想工作状态讨论
+- 讨论买房、结婚生子、工作等约定俗成规则是否合理；提到经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对。
+- 讨论理想工作状态，提到每天起来想干啥就干啥、参考自己兴趣干活；举例宠物博主发宠物日常剪视频赚钱、游戏高手；提出脏活累活没人愿意承担的问题。
+## AI与机器人替代及失控风险讨论
+- 提出应让AI去做苦活累活而不是搞创作艺术；设想机器人负责生产、人负责享受；提到扫地机器人及未来可打扫家、做饭的机器人；讨论AI普及普惠到实体、机器人有自己思维后人类能否控制。讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影；提到机器人可能成为犯罪代理人、职业杀手、超级战士；讨论智能与思想可能无法分开，思想可能带来不好影响。涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>3931/1305</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="13.5" customHeight="1" s="9">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 我问呢，我感觉刚才才是才是会议的这个场景。对，开始了，接着争论吧，接着争论吧。我怎么记得啊，开始了。对，开始。
 发言人 1  00:00:10
 哥斯拉这个电影呢，大家耳熟能详，在上个世纪的1954年的时候，就第一部哥斯拉题材的电影就诞生了。迄今为止已经差不多70多年了，然后不管是日本还是美国，翻拍出了不同版本的哥斯拉。但是最早的一个哥斯拉的起源就是在海底的一个生物，由于吸食了核废料、核废水之后啊，然后变变异成了一个庞然大物，然后对人类世界展开一次报复和攻击。然后。
@@ -10595,9 +12712,37 @@
 当时前几年好像还还有个电视剧还是看。好像有电影都跟音乐，这个游戏好像也有类似于这种，使命召唤4，然后那一关，在那个就是反派，当时就是车臣派。军要去那个切尔诺贝利去那个挖核废料的时候，被那个英国 SAS 特种部队那个主角，然后狙杀，结果没狙杀成功，打断一条胳膊，就是那个双狙人那一关。
 发言人 2  00:15:17
 这一条差不多了。大家可以关一下啊。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:01
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议围绕哥斯拉系列电影起源、各版本剧情及怪兽设定展开自由讨论，并延伸至核废水、核污染与生物变异话题。1954年第一部哥斯拉电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物并对人类展开报复攻击；哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验破坏生态。美国版剧情方面，2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版方面，人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。关于哥斯拉与奥特曼的关系，两者最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。
+## 哥斯拉电影起源与设定
+- 1954年第一部哥斯拉题材电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+- 哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验、破坏大自然生态；相关扩展题材涉及人类频繁搞战争和核试验后唤醒沉睡生物及招致外星生物入侵。
+## 哥斯拉各版本剧情梳理
+- 美国版：2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版：人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。哥斯拉与奥特曼最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>5319/1287</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="13.5" customHeight="1" s="9">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:01
 然后咱们这一场大家来分享一下，18岁以前有没有什么特别印呃深刻的印象和记忆？就比如说以前逃课，要么去网吧打游戏，要么去追星，然后还有要么就是去那个是什么呢？去呃谁的哪个音乐会，就是现场或者说有个乐队什么的这一块，然后大家都可以分享一下。
 发言人 2  00:00:27
 我我十八岁之前还真真真没逃过课我上了大学之后啊他有个逃过逃过一次课。
@@ -10821,9 +12966,38 @@
 就是外导。
 发言人 4  00:14:53
 嗯像小会吃的。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:02
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议为一场围绕18岁以前特别深刻的印象和记忆展开的自由分享会，由发言人1发起并主持，参与者包括发言人1至发言人6。核心探讨问题为18岁前是否有逃课、去网吧打游戏、追星、参加音乐会或乐队等经历，并延伸至小说漫画阅读、电脑游戏与单机游戏、第一人称射击与僵尸题材游戏、游戏与影视改编先后、塔防游戏与使命召唤等话题。发言人1回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐。发言人2称18岁前没逃过课，上大学后逃过一次；发言人3认为逃课是正常现象；发言人4称上大学就不算。
+# 发言要点
+发言人1作为主要发起者，回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐；其称穿越火线抄袭，自己曾在贴吧和QQ空间写文章骂穿越火线被封禁，后成为CS铁杆粉，喜欢僵尸模式，并介绍求生之路第二部有东洋刀、电锯、砍刀砍丧尸，很暴力，后来有年龄限制，未成年人不能注册Steam账号，需18岁以上，还称求生之路精准预测美国政府在灾难中的表现，2020年新冠疫情后游戏重新火起来。发言人2称18岁前没逃过课，上大学后逃过一次；称看郭敬明小说挺难受、挺扭曲，并提到《梦里花落知多少》，还提到《意林》《读者》《故事会》并称意林讲得特别好；提到穿越火线、地下城与勇士、魔兽争霸，称欧美玩家爱玩打僵尸游戏，称植物大战僵尸有特别变态的版本，后期满屏子弹，电脑都卡，称使命召唤这游戏太男性了。发言人3认为逃课是正常现象，称小时候经常玩塔防游戏，现在还在玩植物大战僵尸和Kindle rush。发言人4称上大学就不算逃课，称班里特别流行看柯南，提到摩尔庄园、赛尔号，提到仙剑三最火且有电视剧。发言人5提到特别喜欢郭敬明的小说，提到当时还有一些杂志，提到萌化三国，提到仙剑四、仙辕剑、古剑四，质疑当时游戏没有年龄限制、内容暴力，小孩能否玩。发言人6提到生活杂志、柯南、老夫子、仙剑、Steam图标、僵尸题材，称艺术源于生活。观点交锋点包括：逃课是否正常及上大学后是否算逃课；郭敬明小说是否令人难受扭曲；穿越火线是否抄袭及游戏暴力与年龄限制；求生之路与生化危机、惊变48小时的影视游戏先后关系；变形金刚先有玩具还是电影；英雄联盟与DOTA的鄙视链及王者荣耀处于鄙视链最低端。
+# 共识形成
+小组未形成正式决议或统一意见，讨论以自由分享与回忆为主。形成的共同认知包括：**逃课在初中高中阶段被视为正常现象，但上大学后逃课一般不算**；**郭敬明小说、柯南、老夫子、意林读者故事会等是当时流行的阅读内容**；**穿越火线、CS、求生之路、仙剑、魔兽、摩尔庄园、赛尔号、植物大战僵尸等是当时流行的游戏**；**求生之路第二部因暴力内容后来设有年龄限制，未成年人不能注册Steam账号，需18岁以上**；**生化危机先有游戏后有电影，求生之路是在惊变48小时、生化危机基础上先有电影后有游戏**；**变形金刚先有玩具，后有MV和电影**；**英雄联盟与DOTA存在鄙视链，王者荣耀处于鄙视链最低端**。
+# 未决事项与分工
+需进一步探讨的问题包括：发言人5质疑当时游戏没有年龄限制、内容暴力，小孩能否玩，该问题未形成结论；发言人2问游戏和电影谁先有，讨论中仅就生化危机、求生之路、变形金刚等具体作品给出先后关系，未形成一般性结论；发言人1称求生之路精准预测美国政府在灾难中的表现，该观点未获其他成员明确回应。后续任务分工未在原文中明确。</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>6453/1554</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="13.5" customHeight="1" s="9">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:02
 啊，然后大家讨论一下，待会儿说啥吧。
 发言人 2  00:00:05
 就是不是红楼了继续吧，梦婷，还没说完，他那个。
@@ -11081,9 +13255,38 @@
 等一下那个咱们时间差不多了咱们再起一条好吧好的好大家现在暂停就是。
 发言人 2  00:14:17
 说一下ok那下一个场景是啥你接。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:02
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论为闲聊式交流，开场由发言人1提议大家讨论待会儿说啥，并确定继续聊《红楼梦》及相关古典小说话题，随后依次展开红楼官场暗线与四大家族、红楼细节与版本差异、金瓶梅与水浒传关系及人物、西游记佛教描写、三国孙权二宫之争等话题。参与讨论的成员包括发言人1、发言人2、发言人3、发言人4，围绕四大家族兴衰、人物结局版本差异、小说朝代背景及佛教描写等核心问题交换看法。讨论中未形成明确结论，多处内容为参与者凭印象回忆，部分细节表示记不清或未看过。会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。
+# 发言要点
+发言人3提出红楼梦还有一条官场上的线，即朝堂政权变化，四大家族如王熙凤娘家在官场上的地位与其前期、后期地位及结局相关，其兄长先死也影响其结局，并表示对暗线很好奇；还提到四大家族整体在走下坡路，是王朝家族衰败，并介绍冷香丸配方需雨水、小雪及白牡丹、白荷花、白芙蓉、白梅花，以及120回版本中薛宝钗嫁贾宝玉后为无性婚姻、贾宝玉出家，另有版本称其怀有孩子。发言人4认为四大家族感觉没几个人，每家两家人多一点，薛宝钗家没什么靠山，并回忆小时候看红楼梦对吃螃蟹讲究印象深刻，还提到金瓶梅中潘金莲有心机、西门庆有十个老婆。发言人1补充四大家族形容诗句「丰年好大雪，珍珠如土金如铁」「白玉为堂金作马」「东海缺少白玉床，龙王来请金陵王」，并说明金瓶梅从武松杀武大郎之后写起，武松报仇时西门庆翻窗逃脱、武松后被发配，西门庆霸凌武大郎并攀附权贵，其结局在水浒中被砍头、在金瓶梅中纵欲过度而死，还提到西游记中如来佛祖收300两黄金。发言人2询问四大家族如何形容、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件，并提到孙权二宫之争中王夫人和孙鲁班有心机、反杀搅乱东吴政局。分歧点在于薛宝钗结局版本差异、西门庆结局版本差异及红楼梦是否有真实历史事件，各方均未达成一致。
+# 共识形成
+小组未形成统一意见或明确解决方案，讨论中确认的共识性内容为：**金瓶梅与水浒传为北宋时期平行故事线，红楼梦为单独故事线**；**红楼梦没有明确朝代，是写得很虚的故事，映射明末清初及曹雪芹经历**；**四大家族整体在走下坡路，是王朝家族衰败**。
+# 未决事项与分工
+需进一步探讨的问题包括：四大家族具体如何形容、薛宝钗结局版本差异、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件。后续任务分工未明确，会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>5893/1087</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="13.5" customHeight="1" s="9">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:02
 行，那我们就提前聊一聊，嗯，你们小时候也不看小说吗？
 发言人 2  00:00:10
 没有，不怎么看小说，可能刷短剧多一点吧。
@@ -11353,9 +13556,37 @@
 还电量不足了。
 发言人 1  00:13:02
 哎，那这些都没填啊，这几个呢，那个好像。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议为轻松对话与录制调度，前半段围绕小说阅读、综艺剧集偏好、专业背景与洗发水等生活话题闲聊，后半段转入日本现代化转型主题并协调八爪鱼、金融、中央会等录制安排。发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。
+## 小说阅读与综艺剧集偏好
+- 发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。
+- 关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。
+## 专业背景与生活话题
+- 发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>5310/1279</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="13.5" customHeight="1" s="9">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 北部的高丽以及南部的百地与新罗，从分裂到统一的一个整合，然后再到二次世界大战结束之后的一次再次分裂的一个状态。1945年第二次世界大战结束之后，尤其是在亚洲这边，日本投降之后，美国和苏联的军队单独开进了朝鲜北。北部和南部的不同地域，双方以北纬38度为基准，形成了后来广为人知的三八线这一带。尤其在一九四九年，当新中国建立之后，然后我们这边宣布要废除列强在华的一切租界以及特权之后，其中也包含了苏联的利益在里边，尤其是苏联当时在东北建立的中长铁路以及。大连旅顺就是特区的一个存在，然后要中国这边要收回苏联在这一地区的主权。然后当时苏联比较不甘心吧，然后他鼓动当时就是朝鲜去进攻韩国，希望朝鲜能把韩国统一之后能以朝鲜半岛的。相同的，以仁川或者釜山这一块类似的城市来代替，就是旅顺和大连的这样一个地位。然后苏联还要继续在亚洲发挥它该有的一个影响力。
 发言人 1  00:01:37
 就这样，在一九五零年六月的时候，呃，由北朝鲜军队率先越过三八线向南进攻之后，然后朝鲜战争爆发，然后各方有不同的称谓在这场战争中。朝鲜方面称为祖国统一解放战争然后中国这边称为抗美援朝韩国称。为625事件，然后美国以及西方国家称之为朝鲜战争，或者说是韩战。这主要是台湾地区的一个称谓，在战争开始的时候，朝鲜人民军从三八线一直打到了洛东江环形防御圈，差不多也就是今天大邱到釜山一带，就是韩国的这个城市地区。然后后来是美国下场，并于1950年9月15号的时候在仁川。登陆成功之后，将深入到韩国境内的朝鲜人民军分割包围，逐次歼灭，然后以此来收复整个三八线以南的韩国领土。
@@ -11495,9 +13726,78 @@
 但是由于美国后期又越过三八线，向朝鲜以及中朝边境进发，然后触动了咱们的一个敏感神经，唇亡齿寒这么一个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争，因为台湾那个事儿已经让咱们已经很被动了，朝鲜半岛这一场，既然。要就是争取战略。主动，那就索性就是解放军的陆军当时就很强，就是在陆地上进行战斗。既然海上没办法进行战斗，那就只能在陆地上进行战斗。所以说这也是后来咱们当时就是一种战斗意志的体现，就是在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。就这样。
 发言人 2  00:24:27
 OK好，那咱们差不多大家可以关一下，这个录的比较久，已经25min。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:03
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次研讨会由主讲人（发言人1）围绕朝鲜半岛从分裂到朝鲜战争爆发、停战及今日朝韩格局展开分享。主讲人梳理了1945年日本投降后美苏军队分别进入朝鲜南北、以北纬38度为基准形成三八线的由来，并指出1949年新中国宣布废除列强在华租界与特权、涉及苏联在东北的中长铁路及大连旅顺利益后，苏联鼓动朝鲜进攻韩国，希望以仁川或釜山类似城市替代旅顺大连地位并继续在亚洲发挥影响力。战争进程方面，1950年6月北朝鲜军队率先越过三八线南进，朝鲜人民军一度打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，麦克阿瑟任联合国军总司令，美军以联合国军身份参战，另有十六个国家共同出兵；美军越过三八线招致中国强烈不满，中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束，此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带并扩展至三七线，第五次战役为最后一次大规模战役，1953年7月27日双方正式达成停战协定，朝韩名义上停战，未实现真正和平。问答环节还涉及朝鲜战争的影响与评价、越南统一、朝韩旅游与朝鲜现状、朝鲜半岛文明与历史沿革、南北割裂的历史渊源、美国对朝鲜的态度、朝韩统一前景、中俄朝关系与图们江出海口、韩国军队在朝鲜战争中的作用，以及中国选择抗美援朝而非收复台湾的原因等议题，会议未形成决议。
+# 核心观点与论证
+**论点一：三八线是美苏分区受降的产物，朝鲜半岛分裂源于冷战格局。** 论据：1945年二战结束、日本投降后，美苏军队分别进入朝鲜南北，以北纬38度为基准形成三八线；最初设想不同占领区受降后像奥地利那样普选建立统一民选政府，但美苏关系急转直下，扶植领导人各有心思，意识形态不同，最终建立两个国家。美国在三八线以南单独建立韩国以保护日本免遭苏联及共产主义势力影响，苏联在朝鲜北部建立卫星附属国。
+**论点二：朝鲜战争爆发与各方称谓不同。** 论据：1950年6月北朝鲜军队率先越过三八线向南进攻；朝鲜称祖国统一解放战争，中国称抗美援朝，韩国称625事件，美国及西方国家称朝鲜战争或韩战，台湾地区称韩战。
+**论点三：战争进程经历多次战役，最终在三八线附近形成今日边境。** 论据：朝鲜人民军从三八线打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，分割包围并逐次歼灭朝鲜人民军，收复三八线以南韩国领土；中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束；此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带，扩展至三七线（北纬37度）；后期美军反攻，双方鏖战于三七线和三八线之间；第五次战役为最后一次大规模战役，结束后双方在三八线基础上互有攻防，形成今日朝韩边境。西部中朝方面向南占领开城、延安半岛和望京半岛一带；东部美军向北占领今韩国襄阳地区及金刚山地区。1953年7月27日双方正式达成停战协定，延续至今。
+**论点四：朝鲜战争对中国具有战略意义。** 论据：从中国角度奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期中国警告美国不得越过北纬17度线，美国未敢越过；美国称此战为被遗忘的战争，联合国军最后一任司令官马克克拉克承认是美国历史上第一次未取得胜利情况下签署停战协议的司令官；伤害最深的是朝鲜和韩国，一脉相承的血肉同胞分裂成两个国家。
+**论点五：中国选择抗美援朝而非收复台湾，因海军实力不足与战略主动考量。** 论据：台湾和大陆之间有一道约100公里海峡，中共刚建国没有相应海军实力；1950年朝鲜战争爆发，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾；美国后期越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，唇亡齿寒深入人心，解放军陆军很强，海上没办法战斗就只能在陆地上战斗；长津湖和上甘岭接连让美军惨败。
+**论点六：韩国军队在朝鲜战争中的作用与战斗力演变。** 论据：韩国军队一开始瞎指挥，差点被朝鲜团灭；6月25日朝鲜战争爆发，7月10日以后朝鲜南部地面战斗主要是美军和朝鲜人民军进行，韩军负责冲人头角色；1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力；此前韩军对美军类似猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每次兵败都是韩国军队战线崩溃引起；第五次战役中志愿军从朝鲜半岛东部形成反包围突击，打崩韩国军队前线，美国把韩国第三军团全部撤销；韩军以二战时期日本扶植的伪军和傀儡部队军官为骨干，士兵类似国民党抓壮丁强征农村青年；一直贯彻二战昭和日军武士道精神管理体制，老兵欺负新兵，军队霸凌事件蔓延至今。
+**论点七：朝韩统一前景与中俄朝关系。** 论据：若当时美国未下场救援韩国，今日朝鲜可能是苏联卫星国附属，用来牵制中国并威胁美国在亚洲尤其日本的不稳定定时炸弹；现在若朝韩统一，大概率是韩国兼并朝鲜，因经济影响和综合实力；北方有充足优质兵源及核武器和导弹等尖端武器，若统一对整个东北亚都是不稳定定时炸弹；越南统一时宣布继承法国在中南半岛所有地盘和疆域，统一第二年进攻柬埔寨和泰国，导致1979年中国出兵对越南自卫反击战。中俄朝各怀鬼胎；中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落；图们江是俄罗斯和朝鲜的界江，是日本海出海口，在中朝俄边境，国际水域航道可通行，但俄罗斯和朝鲜建了一座小桥，大船无法通过；俄罗斯和朝鲜都不希望中国过分强大，不想过多依附中国，把图们江出海口封死。
+# 金句总结
+&gt; “朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的一个状态。”
+背景：主讲人在讲述美军越过三八线后中国决定出兵时提出，用以说明中国以志愿军形式出兵的战略考量。
+&gt; “美国再也不敢小瞧我们了。”
+背景：主讲人在回答朝鲜战争影响时提出，指出此战从中国角度奠定了强国地位，并提及1967年越南战争时期中国警告美国不得越过北纬17度线。
+&gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
+背景：主讲人引述联合国军最后一任司令官马克克拉克的承认，说明美国称此战为被遗忘的战争。
+&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。”
+背景：主讲人在评价朝鲜战争影响时提出，指出朝韩名义上停战，未实现真正和平。
+&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
+背景：主讲人在回答中国选择抗美援朝而非收复台湾的原因时提出，指出解放军陆军很强，台湾海峡约100公里且当时没有海军实力。
+&gt; “各怀鬼胎。”
+背景：主讲人在回答中俄朝关系时提出，指出中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落。
+# Q&amp;A 环节
+问：战争开始和结束，韩国和朝鲜他们作战的势力有很大的差别吗？这个战争的改变大吗？
+→ 答：主要从中国的角度来说，奠定了我们一个强国的一个地位。美国再也不敢小瞧我们了，导致在一九六七年的越南战争时期，中国这边向美国发出的警告，绝对不允许越过北纬十七度线。那个时候就是南越和北越的一个边境线，如果说美国胆敢越过北纬十七度线的话，那中国必将出兵越南，导致美国在越战的时候未敢越过北纬十七度线，然后奠定了我们的一个地位。同时这场战役在美国被称为被遗忘的战争，因为联合国军，也就美军当时在朝鲜的最后一任司令官马克克拉克，他自己就说了一句他承认了，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官，然后伤害最深的其实还是朝鲜和韩国。
+问：现在越南还分南北吗？
+→ 答：没有。越南它还是统一的，因为美国最终还是放弃了南越，然后北越趁这个机会把南越给统一了。
+问：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
+→ 答：当然是韩国更好玩一点的。因为朝鲜他那边旅游就有点就是没有人身自由。当我们如果说是进入朝鲜的境内，第一件事就是什么呢？没有对搜手机检查，然后没有无线网，就没有网络。然后只有平壤，不就他们自己的网络运营商，而且就是类似于咱们国家八九十年代的那样的一个状态。然后他们的手机就是很落后、很慢，然后国际漫游和网络就非常的贵。然后那几天就是就是参观他们的，就是所谓的伟大的今日成员在的感召之下的各种主体思想和社会主义的辉煌建设成就。然后就类似于像以前我们的文革时期的那种，就是呃无产阶级，就是就是高于一切那样的一个思想，然后就活在一种就是异次元的世界当中。
+问：他们普通人可以上网吗？
+→ 答：不行啊，普通人不能上网。对，普通人是一般的。就是他那个，就局域网都已经很有限。然后普通人连电脑和就是咱们的，就是这些5G手机都用不起，他们怎么上网啊？因为主要是外部有韩国，然后光是韩国用韩剧作为意识形态的宣传武器，老百姓都会就是起来，要是知道真相之后也会颠覆他们的政权。否则的话，为什么那么多朝鲜就是老百姓，不管是吃不饱肚子，还是受意识形态的公式的关宣传之下，都往韩国跑？鲜有韩呃韩国人会去朝鲜的。对，脱北者。
+问：朝鲜那边有啥好玩的？
+→ 答：也就平壤那边看看志愿军的那些抗美援朝那些功绩，还有就是开城嘛，毕竟是朝鲜半岛三千年古都，然后就那边特产小人参。
+问：朝鲜是不是和什么我们北京或者是俄罗斯利亚有一个很大的一个广场，就是平壤的金日成广场？
+→ 答：以领导人来命名，就他们大将军、大元帅这样的啊。战争类的也可以用吧。
+问：它这个南北之间的割裂，是有什么历史渊源吗？为什么它会成为两个政权？
+→ 答：主要一开始的时候，美国和苏联都希望在朝鲜半岛建立一个缓冲区。然后美国主要是为了在建，在分出三八线以南的领土，单建单独建立一个韩国，是为了保护日本免遭苏联以及共产主义势力的一个影响，然后。在韩国形成一个缓冲区，而苏联也需要在亚洲建立一个卫星附属国，所以说就在朝鲜北部，在韩国独立的一个建国的一个基础之上，然后也宣布北朝鲜独。鼓励奉行的就是呃，对苏联马首是瞻的一个指示。所以说就是两边最开始的一个诉求，本来是一开始就是说，在就是不同的占领区受降，日本人的投降之后，像奥地利那样形成一个普选，然后建建立一个统一的民选政府。可谁都没想到，当时美国和苏联的关系恶化的非常快，急转直下的关系可以说是。然后，同时所扶植的领导人也各自有各自的心思。由于意识形态的不同，然后最终就是建立了不同的两个国家。所以说这也是朝鲜战争爆发的缘由。
+问：当时美国没有打败朝鲜嘛，然后你觉得现在美国对朝鲜的态度是怎样的？
+→ 答：因为就是什么呢？因为美国是因为惧怕朝鲜背后的中国和俄罗斯这么一个因素在里面。因为朝鲜战争爆发的时候，呃，当时朝鲜已经快被美国完全占领了，然后中国这边出动了志愿军部队，然后帮着朝鲜把美国打回去，而苏联当时也是提供了空军掩护和武器的一个后勤支持，所以说是中国和苏联联手，可以说是把美国给打回到三八线以南这么一个状态。所以说美国就比较忌惮这一块的因素，所以说就是没有，就是主动进攻朝鲜，也没有再次挑起这个朝鲜半岛的武装冲突，然后同时朝鲜当前的一个状态，金家也担心他们的那个江山，呃。在一旦贸然发动战争了之后，重新被颠覆了，所以说也不敢贸然发动战争，就这样的。
+问：现在的朝韩对立这个局面，可以认为是现在韩国还有还有还有西方国家在背后支撑嘛，可以认为它是一个微妙的平衡。如果不妨畅想一下，如果当时没有形成这种这个冷战布局，就是互相争夺这个半岛的控制权的话。这个大一统的朝鲜半岛会是一个什么形态？会是一个大号的朝鲜，还是一个平衡的韩朝？
+→ 答：如果当时朝鲜战争爆发的时候，美国没有下场去救援韩国，今日朝鲜可能会是呃一个就是苏联的卫星国附属之下的，然后当时用来牵制咱们国家的一颗钉子，也要也是威胁美国在亚洲，尤其是日本那一块的一个就是不稳定的定时炸弹，就这样的一个状态。但是现在如果说是。朝韩要是统一，大概率应该是韩国兼并朝鲜。毕竟经济影响和综合实力摆在这儿，然后北方，然后也有就是就是充足的优质兵源以及核武器和导弹这一块的一些尖端武器的话，今日朝韩如果统一的话，那对于整个东北亚地区来说，都是一颗不稳定的定时炸弹。毕竟当年越南当时统一的时候，他当时说要宣布继承法国在中南半岛的所有地盘和疆域。越南统一的第二年就去进攻柬埔寨和泰国，然后被咱们也被逼到79年出兵对越南发动自卫反击战。所以说越南尚且如此，朝鲜半岛统一之后局势更加不可控。
+问：你感觉现在中国俄罗斯和朝鲜之间关系其实怎么样？
+→ 答：各怀鬼胎。咱们和朝鲜的问题，还有俄罗斯的问题，主要就是图们江出海口的那个问题，到现在今天还拖着这个事没有着落。图们江就是俄罗斯和朝鲜就是那个，就是有一条有一条界江，但是那个地方是日本海的出海口，然后咱们在，就是在中朝俄边境那一块。就是图们江，就国际水域航道是可以通行，但是俄罗斯和朝鲜在那建了一座小桥。大船没法从那过去，所以说就俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了，然后都不想把那个出海口让给我们。
+问：你觉得就是朝鲜战争中那个朝鲜的军队，那韩国的军队有没有发挥什么作用？
+→ 答：好像在刚开始就差点让人发挥。一开始的时候，因为韩国的军队当时瞎指挥，就是什么呢？差点被朝鲜团灭，然后差不多在6月25号朝鲜战争爆发，可是从7月10号以后，朝鲜的南部的地面战斗主要是美军和朝鲜人民军进行战斗，然后韩军一开始就是负责一个冲人头的一个角色，就是，然后差不多是在1952年之后，美国把韩国重新整军训练备战之后，韩军才形成了一个基本的一个战斗力。在此之前，呃，韩国的军队对于美军来说一直有点类似于像猪队友的一个存在，就是接连被美国不被。中朝的军队给接连打败，然后美国每一次战役里边就是什么呢？志愿军跟美军占不到便宜的时候，都从韩国军队的那个战线那边进行突击，然后导致美军每一次的兵败都是韩国军队的战线崩溃所引起的。然后最后是呃，在第五次战役，也就是朝鲜战争最大的一次运动战的里面，呃，志愿军当时从韩国军队的就。朝鲜半岛的东部那一块就是形成一次反包围突击，然后把整个韩国军队前线都给打崩。然后美国当时把韩国第三军团全部给撤销，然后是美国人在韩国的领土上把韩国军队给撤销了。所以说关于韩国军队的战斗力，在一九五二年之前我不敢恭维，在一九五二年之后还是不可小视，毕竟韩军的主。要形成，他还是以军官的主体，是二战时期日本人扶植起来的伪军和傀儡部队的为骨干。然后士兵就是有点类似于像国民党时期抓壮丁的一个形式，强征来的一些就是呃农村青年这么一个形式。然后韩国的军队，他从朝鲜战争成军的时候一直到现在，他一直贯慢贯彻的。以前二战时期昭和日军的那套武士道精神的那种管理体制，就是就是关西兵，然后老兵欺负新兵，军队的霸凌事件一直蔓延到今天都屡见不鲜，所以说他就是一支充满着昭和军国主义时期那种思想余孽的，就是旧日军部队的一种延伸。
+问：就是他不是五零年五零年去援那个汉明嗯然后四九年国呃中国刚成立。然后他当时好像没找到选择，一个是受服台湾，一个是去抗美援朝。因为当时他自己的实力不是很强的，所以他选这个。他为什么选择了抗美援朝，而不是选择受服台湾？
+→ 答：首先，台湾和大陆之间有一道漫长的海峡，这个距离差不多得有个就是100公里左右。当时的中共刚刚建国，也没有相应的一个海军实力。然后50年的时候，朝鲜当时爆发了战争，在美国的参众两院普遍看来，这是共产主义世界对自由世界的一次全面进攻，然后连带着就是把台湾和韩国共同纳入到了美国的亚太实力圈。保护圈里面然后。连带的影响的就是美军的陆军，就是出兵朝鲜半岛，海军第七舰队进驻台湾。一来防止就是就是解放军解放台湾，二来说是防止国民党反攻大陆。然后因为当时解放军当时建军的时候没有相应的海军实力，所以说没办法进行。解放台湾的战斗。但是由于美国后期又越过三八线，向朝鲜以及中朝边境进发，然后触动了咱们的一个敏感神经，唇亡齿寒这么一个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争，因为台湾那个事儿已经让咱们已经很被动了，朝鲜半岛这一场，既然。要就是争取战略。主动，那就索性就是解放军的陆军当时就很强，就是在陆地上进行战斗。既然海上没办法进行战斗，那就只能在陆地上进行战斗。所以说这也是后来咱们当时就是一种战斗意志的体现，就是在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>7464/6822</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="13.5" customHeight="1" s="9">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:03
 还有一个问题是出门必带的三样东西是什么？
 发言人 2  00:00:08
 手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。
@@ -11669,9 +13969,42 @@
 那个妹子好像没买大雨，她一大早就早上可能就送给孩子，然后就去。
 发言人 4  00:10:13
 好，这一条时间差不多了，我们先停吧。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:03
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>对话记录</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t># 对话概况
+本次对话为多人围绕出门与上班随身物品展开的闲聊，参与者包括发言人1、发言人2、发言人3、发言人4、发言人5。发言人2提出出门必带手机、充电宝、指甲刀，称指甲刀为多功能可磨手掌，并已用电子锁多年、以指甲刀平替钥匙；发言人3提出钥匙、纸巾、伞；发言人1强调必须带钥匙，自家为指纹锁、手机充电线够用；发言人4提到家钥匙及必带绑头发的皮圈；发言人5提出手机、耳机和工卡。上班随身物品方面，发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒。话题还延伸至长发打理与北京下雨，发言人3提到每年下雨园区门口都是水、李博之前开幕的地方被淹。会议未形成正式结论，发言人4在时间差不多时提议先停。
+# 交流内容
+出门必带物品话题：发言人2提出手机、充电宝、指甲刀，称指甲刀是多重指甲刀，可刮指甲、磨手掌；发言人3提出钥匙；发言人1强调必须带钥匙，并称自家门是指纹锁、手机充电线够用；发言人4提到家钥匙；发言人2称已用电子锁多年，用指甲刀平替钥匙；发言人4提到必带绑头发的皮圈；发言人3提到纸巾、伞。
+上班随身物品话题：发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒；发言人5提出手机、耳机和工卡；发言人2称耳机和工卡放单位、刷脸进入；发言人1提到打卡用手机、领夜宵需工卡，出差肯定不带手机卡；发言人2认为充电宝既能充电也能防身，最好带一块砖重量。
+长发打理话题：发言人2好奇初中男生为何喜欢薅女生头发圈，称若自己是女生会披发显脑袋小；发言人1称绑的没有散头发好看；发言人4提到女生披肩发；发言人2称高中时想留长发留大胡子学民谣吉他，后因不好打理打消念头，曾留胡子被误认为新疆少数民族。
+北京下雨话题：发言人1称北京下雨很少、没季节性、秋天容易下雨；发言人2质疑往常是春天容易下雨；发言人4认为北京夏天容易下雨；发言人1称夏天容易暴雨；发言人3提到每年下雨园区门口都是水，李博之前开幕的地方被淹、去年也有；发言人2提出住三楼以上远离水淹；发言人3提到一个妹子没买大雨、一早送孩子。
+# 共识与分歧
+共识：**出门与上班随身物品因人而异，未形成统一清单**；**发言人2以指甲刀平替钥匙、上班必带充电宝、手机、刮胡刀**；**发言人1打卡用手机、领夜宵需工卡**。
+分歧：出门必带的三样东西到底是什么，未达成一致；为什么初中很多男生喜欢薅女生后边的头发圈，未解决；为什么秋天容易下雨而不是春天容易下雨，未解决；字节员工不录工卡会有什么样的惩罚，未解决。
+# 后续规划
+未提及</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>3851/1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="13.5" customHeight="1" s="9">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:03
 咱们刚才那个就先说这个手机里最常用的三个A P P.
 发言人 2  00:00:08
 知乎小红书，然后还有那个就是谷歌。
@@ -11851,9 +14184,38 @@
 但是他的确全球的影响力。
 发言人 2  00:10:13
 其实都对，然后那个就是亚洲，十分钟了，十分钟了，挺好的。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论由发言人1至发言人5共同参与，围绕各自手机中最常用的APP及使用习惯展开交流，核心探讨问题包括常用APP类别、AI助手与浏览器的取舍、视频平台付费方式、音乐APP选择与听歌场景，以及歌手与乐队偏好。讨论中涉及的具体APP包括知乎、小红书、谷歌、微信、抖音、淘宝、京东、B站、YouTube、豆包、百度、千问、吉米、重庆元宝、腾讯视频、爱奇艺、优酷、芒果TV、网易云、酷狗、酷我、虾扎、苹果music等。微信是否算最常用APP、大家为什么不喜欢用浏览器、Taylor Swift为什么重新火起来成为讨论中的开放问题。
+# 发言要点
+发言人2提到常用知乎、小红书、谷歌，并表示仍停留在浏览器加地图测绘用尺子标注的年代，不太喜欢用AI软件，不确定其是否正确，还提到欧美音乐平台虾扎、欧美演唱会版本更多、小众翻唱多、大版权有纠纷播不出来，并疑惑Taylor Swift为何重新火起来，提到她中学时火、后因绯闻消沉、对九零后和零零后影响深，以及Love Story、猫头鹰之城、亚当杨、绯闻、表白。发言人3提到微信、抖音、淘宝、京东，表示已下载豆包，提到重庆元宝，认为AI小助手更全面、回答更精准、总结性更强，还提到腾讯视频、爱奇艺、优酷、芒果TV等播放器APP，开VIP、看广告获得VIP时长，以及谢霆锋、Taylor Swift、玉蝴蝶。发言人4提到微信、小红书，提到用小布小布代替浏览器，提到通勤路上听歌、要降噪耳机，提到歌名有英文、Taylor Swift的全球影响力。发言人5提到B站、YouTube，指出小布小布是豆包，常用网易云，提到单框架手机网易云不适配、用卓翼通，提到APP太多不知道开哪个。发言人1提到百度、千问、吉米等，提到苹果music，发现国内付费电视剧在YouTube上不要钱，提到五月天、周杰伦。观点交锋点包括微信是否算常用APP、AI助手能否判断对错、视频平台广告与付费方式、音乐APP选择与适配问题。
+# 共识形成
+小组未形成统一意见或解决方案，讨论中提出的主要观点包括：AI小助手更全面、回答更精准、总结性更强；视频平台广告时间长，可用B站直接看或开VIP、看广告获得VIP时长；小网站不用花钱，因平台大才有版权纠纷需付费；欧美音乐平台演唱会版本更多、小众翻唱多；听歌场景包括上班、通勤路上、地铁，降噪耳机可提升体验。
+# 未决事项与分工
+需进一步探讨的问题包括：微信是否算最常用APP、大家为什么不喜欢用浏览器了、Taylor Swift为什么重新火起来。后续任务分工未提及。</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>4259/1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="13.5" customHeight="1" s="9">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 这一章啊，咱们就具体讲一下2022年以来俄罗斯进攻乌克兰之后，俄军在战场上所进行的表现。众所周知，不管是在美国还是在我们国家，还是在西欧国家的认知里面，从苏联时期开始，俄军就一直是给人一种钢铁洪流的一种印象。然后在各国的很多游戏里面，不管是苏联还是俄罗斯，一直是作为电影和游戏中的一种反派的呃那个角色诞生于此。然后呢，呃呃古代也有一种说法，就把俄军称为什么灰色牲口？就是啥呢？它是耗材，因为就是俄罗斯比很多欧洲国家更承受得了更多的、更惨烈的伤亡和那种就是死亡人数，反而所以。这一系列的这种代价是西方国家所不能承受的。
 发言人 1  00:01:04
 可是呢，当2022年俄乌战争爆发的时候，俄军刚进攻乌克兰的时候，全世界都会认为战争天平会向俄罗斯一边倒，然后基辅会很快占领。呃，乌克兰会被消灭，泽连斯基会流亡。可是剧情超出各位的反转和认知，泽连斯基不但扛住了俄罗斯的进攻，反而还把俄军从基辅打回了白俄罗斯和乌克兰的边境。所以说今天。就想和大家探讨一下，关于俄罗斯在俄乌战争的表现是否是俄军它真正应有的一种状态，然后大家发表一下看法，谢谢。
@@ -12013,9 +14375,38 @@
 嗯，明白了。 OK 那咱们录的时间差不多了，咱先停一下，然后让你们。行。
 发言人 1  00:17:22
 好，好。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:01
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论围绕2022年俄乌战争爆发后俄军战场表现是否为其真正应有状态展开，由发言人1主持并主讲，发言人2、发言人3、发言人4参与讨论。发言人1指出，战前外界普遍认为俄罗斯会一边倒取胜、基辅很快被占领、泽连斯基会流亡，但泽连斯基扛住进攻并把俄军从基辅打回白俄罗斯和乌克兰边境。与会者从腐败、基层官兵、游戏影视形象、直观战斗力、欧洲认知及俄罗斯旅行见闻等多个角度发表了看法。讨论认为俄军单兵素质很厉害但总体拉垮，主要问题在后勤和指挥上；欧洲人把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，乌克兰被称为欧洲之门。
+# 核心观点与论证
+核心论点一：俄军腐败问题突出。支撑论据为情报官员把用于策反乌克兰官员的经费全部贪污瓜分，导致乌克兰高官未收到策反经费；2014年俄罗斯占领克里米亚后乌克兰上下迸发民族仇恨，对政府无能与腐败不满。核心论点二：俄军基层官兵与战争初期情况。支撑论据为俄军基层官兵不知道2022年会进攻乌克兰，好多部队收到命令还以为是去演习，第一批部队进入乌克兰时遭遇民兵自发抵抗而非军队有组织进攻，闪电战变成持久战。核心论点三：游戏与影视中的俄军/苏联形象。支撑论据为从苏联时期开始俄军给人钢铁洪流印象，在各国游戏里苏联或俄罗斯常作为反派；红警等游戏被指为黑苏联，把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。核心论点四：对俄军的直观印象与战斗力评价。支撑论据为俄军单兵素质很厉害但总体拉垮，主要后勤和指挥上，像矮脚巨人、柯基腿短支撑不起庞大身子；俄乌战场打得跟二战没啥进步，多了点无人机，双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸，从钢铁洪流变成菜鸡互啄；俄罗斯无人机靠伊朗给，乌克兰由北约持续输血，类似越战形式；车臣、格鲁吉亚、瓦格纳、库尔德武装等地方武装战斗力挺强。核心论点五：欧洲对俄罗斯的认知与乌克兰的地缘意义。支撑论据为乌克兰在欧洲人认知里被称为欧洲之门，欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待；俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳；欧洲自发支援乌克兰，不让俄罗斯打赢，要把俄罗斯挡在亚洲之外；乌克兰死活不能向俄罗斯妥协。核心论点六：俄罗斯旅行与东宫藏品。支撑论据为出俄罗斯后签证上会写、办美签可能被拒；发言人1因去过好几次俄罗斯，在美国边境入口被拦下询问去俄罗斯干嘛，差点被怀疑是间谍；东宫是世界四大艺术博物馆之一，连续去了三次不同区域都没逛完，圣彼得堡夏天不错；东宫藏品来源包括列强殖民、探险队名义、俄国东扩、二战后从德国运回，以及王室联姻赠送品，涉及欧洲、中东、东亚、西夏王陵、敦煌、中亚、埃及、北非、奥斯曼帝国等地。核心论点七：俄罗斯地域与民族构成。支撑论据为讨论俄罗斯欧洲部分与亚洲部分差别是否很大，远东地区风格和欧洲那头；提到境内好多共和国，但总的来说以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。
+# 金句总结
+发言人1："俄军他总的来说，给我看来，他就是单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，然后就是矮脚巨人的感觉是不是就有点像柯基的感觉，就是腿特别短，支撑不起他庞大的身子的那种感觉。"——背景为讨论俄军在乌克兰的表现时对俄军整体战斗力的评价。发言人1："从一种钢铁洪流变成了最后的菜鸡互啄。"——背景为描述双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸的战场状态。发言人1："乌克兰在欧洲人的认知里面是被称为欧洲之门。"——背景为阐述欧洲对俄罗斯的认知与乌克兰的地缘意义。发言人1："欧洲的边界是在乌克兰，所以说一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。"——背景为解释欧洲自发支援乌克兰、不让俄罗斯打赢的原因。
+# Q&amp;A 环节
+问：俄罗斯在俄乌战争的表现是否是俄军真正应有的一种状态？→ 答：发言人1提出该问题供讨论，与会者从腐败、基层官兵、游戏形象、直观战斗力、欧洲认知等角度发表看法，未形成明确结论。问：大家对于游戏里的俄军是一个什么样的印象？→ 答：发言人2、发言人4认为红警等游戏是西方主导为黑苏联而做，苏联形象多为反面、很猛很变态、研究非常邪乎的武器、大规模夸张；发言人1指出把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。问：对于俄罗斯被西欧称半兽人这种印象，大家怎么看？→ 答：发言人1解释欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳。问：俄罗斯欧洲那边跟亚洲这边差别很大吗，远东地区的风格和欧洲那头？→ 答：发言人1表示总的来说还是以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>6103/1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="13.5" customHeight="1" s="9">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:01
 贝姐啊，咱们主要讲一下那个前段时间那个热播的南京照相馆这部电影。首先还是想问一下大家，关于大家对这场电影的印象是个什么样子的？来吧。
 发言人 3  00:00:18
 我我我看的好像是那个片段，在抖音上看的切片那些。但是切片好像看着还行啊，不知道是什么样。
@@ -12101,9 +14492,44 @@
 你看问的那应该是ok了吧，咱们这一段先结束，然后大家可以暂停那个停止了。
 发言人 1  00:13:48
 13分钟够吧，够10~25min。那下一场我当配角了，大家谁当主角？</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次讨论围绕电影《南京照相馆》展开，由发言人1介绍历史背景并辨析影片虚构与真实。发言人3在抖音看过切片、也去电影院看过，觉得挺好看；发言人4认为是灾难电影，印象最深的是几个人在地下室吃喝睡觉、最后老弱妇孺还活着；发言人2觉得深刻、好看；发言人5表示题材不太习惯、没看过。发言人1介绍：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据。发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
+# 核心观点与论证
+发言人1首先介绍历史背景：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。
+在虚构与真实之辨上，发言人4问片中日本军官及主角与其建立友谊是否虚构，发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据，而非电影人物所拍摄留存。
+发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
+关于日军暴行成因与指挥更替，发言人1解释上海抗战介绍多是因为中日第一场大规模战斗在上海；日军到南京进行大屠杀，因其自九一八以来未遭大规模战争，认为遭受前所未有的侮辱及战场应激创伤，结合日本攻破敌方城镇以屠城狂欢麻痹的历史，以及自上而下高压武士道精神下的欺凌霸凌宣泄；原指挥官松井石根因生病被临时替换，他曾发布命令避免日军在上海至南京沿线烧杀抢掠，以免招致中国军民反感、增强抵抗意志；替换为裕仁亲王的叔叔朝香宫鸠彦亲王，其追随脱亚入欧思想，上任后第一道命令是不留俘虏、格杀无论，导致日军军纪失控，蔓延至对老百姓群体，最终导致南京大屠杀。
+# 金句总结
+发言人1在介绍日军暴行成因时指出：“从他们的角度来说，就是我也去过什么日本当时的那些个博物馆……觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”其背景是解释日军攻破南京城后为何进行大屠杀。
+发言人1在说明指挥更替时指出：朝香宫鸠彦亲王“上任之后发布的第一道命令就是不留俘虏，格杀无论”，随后“蔓延到了对老百姓群体的一种发生，然后最终导致了南京大屠杀”。
+发言人1在辨析影片真实与虚构时指出：“电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。”
+# Q&amp;A 环节
+问（发言人4）：电影里面虚构的，它里面有一个日本的军方关系叫什么？就是主角一度好像和他建立一次友谊吧？不知道这个是虚构的，就是有没有这个日本军官是是不是真实？
+→ 答（发言人1）：电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。真实的一个历史是，当时是两个美国的传教士，然后当时是拍摄的当时日军的这一块相关的一个暴行。然后同时期也有咱们国家当时就是负责给日本人冲洗照片的一个，就是那个我不能说是摄影师，他应该是后期，就类似于就照片冲洗这样一个状态吧。然后他无意间发现了这一些个，就是日本所拍摄这些暴行，在日本当时是属于禁文，他偷偷拷贝了下来，藏起来了之后，然后是于抗战之后把这个递交给当时国民政府的军事法庭，就是作为审判日本战犯的一个证据，而不是当时就是南京照相馆里面的那些电影人物所就是拍摄留存下来的这么个情况。</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>4228/1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="13.5" customHeight="1" s="9">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 这一章咱们关于对于日本进行一下探讨啊，首先呢，日本对于咱们中，广大的中国人的印象中，就是一个比较复杂的国家。第一是因为历史原因的时候，对，中英混说，历史原因的时候，就是中日关系确实也发生过战争，然后也发生过一些悲剧。但是另一方面的话，在今天我们国家当时主要的很多外部投资，日本也占。呃，很大的一个比重。然后中日也是主要的一个贸易伙伴吧？所以说这也很复杂。当然今天咱们有很多呃，就是不管是上学的还是上班的，都喜欢去日本旅游。然后日本的服务业和购物体验确实在很多国家之间比起来也是首屈一指。啊，所以说今天咱们谈一谈日本这个国家的一个概况，还有大家对日本的一个印象，还有以及对这个国家的一个了解是什么样的，然后大家都可以自由发言一下，开始吧。/.
 发言人 2  00:01:13
 sil 嗯，我之前还挺喜欢日本，包括我读研的时候我还上了一课，就是去讲日本文化，然后后来我读了一部一部，就。小说就是那个四代同堂，余老舍嗯嗯。
@@ -12175,9 +14601,38 @@
 方法国意大利都是女生买的法国意大利还有就像什么那个韩国买的都很多的对化妆品对男生买就是名牌还有化妆品巧克力然后那个白色链子。对，然后感觉去欧洲他们也是买巧克力，然后去日韩也买巧克力，怎么感觉哪的巧克力都比国内的巧克力好？呃，去日本我最喜欢干的事还是什么呢？去爬，去登山还是，哈哈。就是还是爬山，然后去爬富士山，然后还有去看古城，去逛博物馆，就是这样，去什么镰仓，呃，卡马库拉喽。然后还有那个京都 kod，还有那个就是，呃，对，关西那边是，还有那个丽子雅，就名古屋那边就是有那个独特的那种，就是自己那种，就本土化改良那种，就是文化场景，就古城这样的一个状态。所以说我是比较喜欢那个镰仓那边那种气候，夏天去呢比较舒服。
 发言人 1  00:15:37
 剑科对就建科道口那里在卡玛库拉楼接下来了。是差不多了还有觉可以改成中日。了我我了中日然后是大会场大会场咱们就觉得的。墙边上做的好的。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:01
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议围绕日本国家概况、对日本的印象与了解展开自由讨论，由发言人1主持并引导，发言人2参与发言。发言人1提出日本在国人印象中较为复杂：历史原因导致中日曾发生战争与悲剧，但今天日本在中国外部投资中占很大比重，中日也是主要贸易伙伴；上学、上班人群喜欢去日本旅游，日本服务业和购物体验在各国中首屈一指。发言人2提到读研时上过讲日本文化的课，读《四世同堂》后觉得民族仇恨还是应该有一点影响。讨论涉及日本文化的来源与历史分期、天皇制度与君主立宪、旅游购物与中古店、日本民族性格与岛国环境等话题。
+# 发言要点
+发言人1主张日本文化没有原创，属外来接收后本土化改进，经历三次转折：古代大化改新（向中国、朝鲜半岛学习，形成和服、制茶、漆器等传统）、近代明治维新（对标清朝、向欧美列强学习，学英国和德国法度利器）、二战后和平宪法转型（美国制定和平宪法，社会结构大规模调整，向美国看齐）；并谈到古代日本君臣关系与中国差别大，天皇对各地封建君主而言更像吉祥物，被当神灵供奉以精神层面控制百姓，1945年二战结束后美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，推动社会转型；现今天皇如君主立宪制下英国、西班牙那样的象征性存在，不能参与政治和国家事务，政治由国会和内阁选出首相执政，美国把日本改造成英美海洋法系国家结构，天皇没有实权，靠政府养着，存在感不如英国国王。发言人1还谈到旅游购物：长崎、东京、大阪、秋叶原等城市，秋叶原可买数码宝贝、铁甲小宝等原装手办以及美妆、护肤品、玩具；日本奢侈品便宜，有Vintage中古店，广场协议后日本经济急剧恶化、泡沫经济崩溃，上班族失业后把原先买的高档大衣、西装、皮具、皮鞋等通过二手回收寄卖，催生中古二手店产业，上海也有很多这类店，能买到LV、Burberry、古奇等上个世纪知名大牌，男性款式相对少；其本人喜欢去日本爬山、爬富士山、看古城、逛博物馆，如镰仓、京都、名古屋，喜欢镰仓夏天舒服的气候。发言人2提到日本传统文化如漆艺、茶艺以及现代文化艺术，并提到听过一种评论：日本是岛国，气候非常不稳定，发展农业可能遇海啸导致收成没了，所以民族性格比较容易极端。双方分歧点在于：发言人1追问日本文化具体指哪一个历史阶段，发言人2未明确；发言人1认为日本民众现在对天皇没有崇拜，发言人2则追问是否还有崇拜，未达成一致。
+# 共识形成
+小组未形成明确统一意见或解决方案，讨论中形成的共同认识包括：日本在国人印象中较为复杂，中日既有历史战争与悲剧，也是主要贸易伙伴；日本文化属外来接收后本土化改进，经历大化改新、明治维新、二战后和平宪法转型三次转折；现今天皇为君主立宪制下的象征性存在，无实权；日本有Vintage中古店产业，上海也有这类店。
+# 未决事项与分工
+需进一步探讨的问题：日本文化具体指哪一个历史阶段的日本文化，尚未明确；日本民众现在对天皇是否还有崇拜，未达成一致。后续任务分工未提及。</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>4892/1239</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="13.5" customHeight="1" s="9">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:01
 好，这回咱们再继续刚才那个所谈论的文学啊，咱们聊了西游记了，然后咱们接下来进行一个延伸，然后大家对于三国是一个什么样的一个印象，主要就是。
 发言人 2  00:00:15
 三国。
@@ -12373,9 +14828,38 @@
 大家先停一下吧，下一个话题。那下一个咱们说点什么呢？
 发言人 3  00:19:17
 下一个。咱们可以继续。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次会议承接此前西游记的文学话题，延伸讨论大家对三国与红楼梦的印象与看法，参与者为发言人1至发言人5。三国部分围绕整体印象与阵营偏好、刘备与孙刘联盟、白衣渡江与吕蒙评价、东吴大都督与陆逊、蜀汉内斗与姜维魏延、三顾茅庐与隆中对展开；红楼梦部分围绕版本与作者、判词与人物结局、后四十回官方地位及曹雪芹小道等北京地点展开。核心探讨问题包括：对三国印象最深刻的章节与阵营偏好、正史中刘备与孙刘联盟的演变、白衣渡江的评价、东吴大都督的结局、蜀汉内斗与姜维魏延、三顾茅庐与隆中对战略，以及红楼梦前八十回与后四十回的作者差异、判词与人物结局、后四十回为何成为官方结尾。
+# 发言要点
+发言人2表示三国没看完，看到诸葛亮去世就不想看了，认为后面没意思；印象最深刻的是赤壁，认为前面比后面有意思；受三国演义影响一般偏向蜀汉刘备阵营；认为白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好；对陆逊印象是火烧连营，认为东吴后期政治斗争严重、内斗狠；提到蜀汉也内斗、魏延被砍；红楼梦方面提到四个丫鬟、袭人、晴雯，提到解读说林黛玉代表明、薛宝钗代表清，问为何最终选高鄂后四十回作为官方结尾，提到植物园有曹雪芹小道。发言人1补充正史后续姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴；认为刘备晚年若未称汉中王，孙权可能不会彻底决裂，称王引发吕蒙白衣渡江、刘备伐吴夷陵惨败等连锁反应；讲述刘备入川占成都后不还南郡、孙权派兵夺荆南三郡、曹操取汉中迫使刘备回师并签订湘水之盟，单刀赴会实为鲁肃与关羽各不带兵士在中立区谈判被罗贯中美化；认同白衣渡江开坏头，称吕蒙被后世与小偷鼠辈等价；称正史上周瑜被曹人射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；称刘禅自知能力不行完全放权诸葛亮，诸葛亮去世后姜维难力挽狂澜，刘禅轻信黄浩谗言，姜维是魏国降将靠诸葛亮提拔才有说服力；称正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，若非姜维断后挡住司马懿军队后果不敢想象，其行为与谋反无实质区别，实为与杨仪个人矛盾；补充隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾，诸葛亮北伐目标在关中平原和陇西，第一次北伐赢面大但因马谡兵败街亭而破产。发言人3称红楼梦只写了前八十回，后面是别人写的；称第五回贾宝玉梦游太虚幻境已把结局交代，以判词形式；称北苑所旁边村子有曹雪芹小道，爬山时看到过。发言人4称红楼梦有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；称第一遍读高鄂续版本时觉得合理，后来知道后四十回不是同一作者，反复读前八十回后再接触后四十回，发现林黛玉性格变了很多；称判词没点那么明确，探春、史湘云结局都是猜的，最后谁和贾宝玉在一起也是猜的；称林黛玉死不是原作写的，但原作意图肯定是悲剧；称晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；称第五回贾宝玉在秦可卿床上做梦到太虚幻境，看到判词，十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；称最终选高鄂后四十回因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及；称北京植物园底下有他的工具。发言人5讲述三顾茅庐：刘备中原屡战屡败，深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次前往拜访，前两次未见到，第三次见到诸葛亮，诸葛亮被打动提出隆中对战略，联合孙权，最终同意辅佐刘备；问悲剧原因，如贾宝玉与林黛玉真心相爱却被迫娶薛宝钗。
+# 共识形成
+小组未形成正式决议，讨论中形成的共同认识包括：三国方面，大家印象最深刻的是赤壁，受三国演义影响一般偏向蜀汉刘备阵营；白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好，吕蒙被后世与小偷鼠辈等价；东吴后期政治斗争严重，周瑜正史中被射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，其行为与谋反无实质区别，实为与杨仪个人矛盾；隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，但白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾；诸葛亮第一次北伐赢面大但因马谡兵败街亭而破产，此后只能拖延魏国灭蜀。红楼梦方面，大家认为其有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；只写了前八十回，后面是别人写的；第五回贾宝玉梦游太虚幻境已以判词形式交代结局，但判词没点那么明确；晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；最终选高鄂后四十回作为官方结尾，因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及。
+# 未决事项与分工
+未决事项包括：红楼梦后四十回到底是谁写的、什么版本，真正意义是否与当时朝代社会有关；探春、史湘云的结局以及最后谁和贾宝玉在一起，都是猜的，没有明确答案；为什么最终选高鄂的后四十回作为官方结尾。后续任务分工未提及。</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>6453/2163</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="13.5" customHeight="1" s="9">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 好，刚才咱们讲完那个《红楼梦》、还有《三国》、《水浒》、《西游记》和《金瓶梅》，然后咱们继续延伸着三国那个接下来的故事线走。然后咱们从那个兵法和战法角度来考虑，大家认为赤壁之战的影响主要是体现在哪一方面？就是这样的。
 发言人 2  00:00:22
 这咋说呀，也不好说吧。
@@ -12475,9 +14959,38 @@
 这地盘太小了。
 发言人 1  00:15:15
 差不多了差不多了差不多了。行，咱们这一条先停一下。下一张是什么。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论由发言人1主导串场，发言人2、发言人3参与，从兵法和战法角度延伸三国故事线，核心探讨赤壁之战的影响、合肥之战与孙权北伐、白衣渡江与火烧连营、陆逊与孙家关系、北伐方向与孙权早期败仗、蜀汉曹魏印象与武将战力、魏延守街亭假设等议题。讨论认为赤壁之战不是曹军实力不行，而是骑兵没法打水战；合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下。
+# 发言要点
+发言人1主张：曹操军队以虎豹骑为主擅长陆战，刚收服荆州无像样水军，江东以水军为主，曹军无法打水战而败；后期东吴北伐如合肥之战，吴军擅长划船、摇橹、打水战、游泳，上岸后无法与曹军对抗，双方僵持。合肥像钉子钉在东吴北伐路线上，从建业过长江到江北、经小河到巢湖上岸，打下合肥才能靠近淮河继续北伐；公元215年合肥之战，曹军主力在汉中，合肥只有张辽、李典、乐进三将且矛盾重，张辽率800死士骑马冲锋大败吴军，孙权差点被张辽抓住，张辽问俘虏骑马好、箭准、上长下短、小胡子的人是谁，得知是孙权后后悔没抓住。刘备体恤下属让士兵在密林扎营抵御酷暑，陆逊抓住秋季干燥、树叶飘落时机在秋老虎时期一口气放火，连营七百里的营地被烧，刘备只身逃回白帝城。陆逊是江东四杰，孙策孙坚是外来户，孙策被称为小霸王，过于冒失后被刺杀，曹操说生子当如孙仲谋，孙权开疆拓土能力不行但能守住家业。对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家；刘备汉中之战打得好，夷陵之战被仇恨冲昏头脑冒进，汉中之战有法正和黄权辅佐，靠地势地利耗出汉中；关羽水淹七军、斩颜良诛文丑，阵中斩将历史第一人；黄忠阵斩夏侯渊；张飞长坂坡、和马超大战五百回合；五子良将有曹仁、张辽、夏侯渊、张郃、徐晃、于禁，于禁被关羽生擒；曹操人多血厚能耗得起。如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，不会像马谡轻易丢掉街亭，第一次北伐可能成功，魏延想法大胆但不太符合蜀汉当时实际支撑，地盘太小。发言人2提出：小时候觉得生子当如孙仲谋，孙权厉害，长大感觉反转厉害；并问陆逊和孙家是否有仇。发言人3提出：除朱元璋从南往北打，其余都是来首都就不错，北伐南、南下容易；孙权在孙十万之前也打过一场坑仗，好几万人去打人家，被几千几百人追着打；关羽只知水淹七军，张飞只知长坂坡。分歧点在于孙权早期败仗的对手是谁，是刘表、刘琦还是曹仁时期，未确认。
+# 共识形成
+小组未形成正式决议，讨论中形成的统一意见包括：**赤壁之战不是曹军实力不行，而是骑兵没法打水战**；**张八百大破孙十万是长期划船游泳的人不擅长陆地冲锋，双方僵持**；**合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下**；**孙权开疆拓土能力不行但能守住家业**；**对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家**；**如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，第一次北伐可能成功，但魏延想法不太符合蜀汉当时实际支撑，地盘太小**。
+# 未决事项与分工
+需进一步探讨的问题：孙权早期被几千几百人追着打的败仗对手是谁，是刘表、刘琦还是曹仁时期，未确认。后续任务分工未提及。</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>4899/1301</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="13.5" customHeight="1" s="9">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 咱们讲一下阿富汗战争，也就是1979年到1989年的苏联入侵阿富汗战争，史称苏阿战争。阿富汗在亚洲的中部，也就是今天呃的差不多新疆往西再出去瓦汉走廊之后到达阿富汗腹地，其国家东接中国，北邻塔吉克斯坦，南接。巴基斯坦、锡林、伊朗，也被称为亚洲的中间走廊地带，是名副其实的兵家必争之地。在历史上，各大列强都对阿富汗有一个觊觎之心，但是其国土纵深百分之九十都为高原山地地带，也是名副其实的。易守难攻的地带从历史上列强入侵哈。阿富汗以及后来的结果来看，阿富汗多次获得其帝国坟场的称号。第一次大英帝国入侵了之后，短暂的时期被阿富汗给反推回巴基斯坦地区；第二次，也就是我们今天要说的苏联入侵阿富汗这么一个状态。
 发言人 1  00:01:26
 阿富汗当时在一二十世纪50年代的时候，它是同时与苏联以及西方国家保持一个友好交往的一个状态。它主要实行的一个制度就还是以那个就是君主立宪制为基准模板进行的，同时就是其国内精英阶层和知识界阶层也是奉行着亲英与亲苏两头政策的，进并行。在文化上，积极向英国这一块的靠拢。就比如说是英国的议会制度、君主立宪制度以及大学现代科学的承办，师从英国；但是国家建设和工业方面又向苏联看齐，然后由地缘上引发的原因。导致这个国家，它跟西方国家和苏联的关系都不差。
@@ -12523,9 +15036,58 @@
 下一个问题。
 发言人 2  00:11:25
 雨翔，你刚才说了吗？说了说了是吧？第一个问题，ok那咱咱们差不多了，我一直在说行，咱们差不多了，可以关上了。11分钟够不够够10到15分钟都行，然后下一场是啥？下一场是女生说。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>专题讲座</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t># 讲座概况
+本次研讨会围绕1979至1989年苏联入侵阿富汗战争（苏阿战争）展开讲解并组织提问讨论。讲解指出阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带和兵家必争之地，国土纵深90%为高原山地，易守难攻，被称为帝国坟场，谁控制了阿富汗谁就控制住了亚洲的咽喉。讲解梳理了战前国情与苏联出兵过程：20世纪50年代阿富汗实行君主立宪制，同时与苏联和西方保持友好交往，精英与知识界奉行亲英与亲苏两头政策，文化上向英国靠拢、国家建设和工业向苏联看齐，基辛格评价阿明用苏联的火柴点美国的香烟。因阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入，1979年12月24日平安夜趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营，此举招致阿拉伯国家、中国、西方盟国不满。讨论环节分析了苏联出兵原因与阿富汗难打的原因：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克，加上阿富汗是特殊战略要地及苏联错判，导致大的战略性失误，同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。阿富汗90%为高原山地，是天然游击战地区，除喀布尔、坎大哈等主要城市外大部分乡村实行部落长老制、各自为政，政府无控制力；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助毒刺防空火箭筒等先进单兵武器，有效压制苏联雌鹿武装直升机，坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机，苏联基层官兵厌战、士气一落千丈，1989年从上到下扛不住压力最终撤军。关于各国援助，讲解说明阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契，中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+# 核心观点与论证
+论点一：阿富汗地理位置关键，是亚洲咽喉要地，易守难攻。论据：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带，兵家必争之地；国土纵深90%为高原山地，易守难攻，被称为帝国坟场；谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+论点二：20世纪50年代阿富汗同时与苏联和西方保持友好交往，实行君主立宪制，精英与知识界奉行亲英与亲苏两头政策。论据：文化上向英国靠拢，如英国议会制度、君主立宪制度及大学现代科学的承办师从英国；国家建设和工业方面向苏联看齐；基辛格评价阿明用苏联的火柴点美国的香烟，获得墙头草称号。
+论点三：苏联出兵阿富汗的决策与过程。论据：阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入；1979年12月24日平安夜，苏联趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法强行派兵，从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营；此举招致阿拉伯国家、中国、西方盟国不满。
+论点四：苏联出兵是冷战思维与战略错判共同导致。论据：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克；阿富汗是特殊战略要地，加上苏联错判，导致大的战略性失误；同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。
+论点五：圣战者含义。论据：圣战者指狂烈激进的伊斯兰圣战思想，从上到下宗教式洗脑，导致阿富汗圣战者具备像二战日本军国主义荼毒下日本军民那样不顾一切、抱着同归于尽思想进行圣战。
+论点六：阿富汗难打的原因与游击战。论据：阿富汗90%为高原山地，是天然游击战地区；除喀布尔、坎大哈等主要城市外，大部分乡村实行部落长老制，各自为政，政府无控制力，列强及城市政府无法有力控制高原山地；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助先进单兵武器如毒刺防空火箭筒，有效压制苏联雌鹿武装直升机；坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机；苏联基层官兵厌战，士气一落千丈，1989年从上到下扛不住压力最终撤军。
+论点七：各国对阿富汗的援助。论据：阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契；中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+# 金句总结
+「谁控制了阿富汗，谁就控制住了亚洲的咽喉。」——背景：在回答听众提问“阿富汗到底有啥好、为啥都想打它”时，主讲人以此说明阿富汗地理位置的关键性。
+「他是用的苏联的火柴在点的美国的香烟。」——背景：主讲人引述基辛格对阿明的评价，说明阿富汗当时同时从苏联和西方两边获取好处、被称为墙头草的外交状态。
+「阿富汗多次获得其帝国坟场的称号。」——背景：主讲人梳理历史上列强入侵阿富汗的结果，指出阿富汗国土纵深90%为高原山地、易守难攻，因而得名帝国坟场。
+「苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。」——背景：主讲人分析阿富汗高原山地地形使苏联坦克和步兵战车无法形成有效战斗力，加上基层官兵厌战、士气一落千丈，最终苏联于1989年撤军。
+# Q&amp;A 环节
+问：阿富汗到底有啥好，为啥都想打它？
+答：地理位置的原因，因为谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+问：是不是阿富汗有石油啊？
+答：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如说是西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+问：为什么苏联要出兵阿富汗？
+答：用当时的冷战思维来看，阿富汗当时被苏联化为苏联势力，就是苏联大家庭中的一员，根据勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，所以加上苏联这个错判，导致苏联的大的战略性失误。同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人的进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
+问：阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
+答：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式那种洗脑，然后导致了其阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民的那样一样，不顾一切的就是抱着一种同归于尽的思想进行一种圣战的方式。
+问：为什么阿富汗这个位置这么难打？
+答：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。它除了以喀布尔和坎大哈那几个主要城市为首的城市地区以外，剩下大部分百分之九十的地区都是乡村部落长老制的那种制度。你到乡村，政府没有任何的控制力，都是由部落的长老控制的该部落，然后各个村落与部落各自为政，然后导致了任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。
+问：中国对阿富汗提供了哪些援助？
+答：也是给了一些枪炮，比如说像咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，也是通过这个援助的一个形式，然后我把咱们国家就是已经饱和的军工业这个产业给它稀释掉，同时也是大家为了抵抗苏联的霸权主义和西方盟国达成了一种就是秘而不宣的默契。专家派的主要就教一些兵法、地道战、地雷战这一块的，只提供军火，但是没有派人。</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>3129/3273</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="13.5" customHeight="1" s="9">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 唠呗，就刚才继续呗。
 发言人 2  00:00:02
 中间唠一个哥斯拉的这个讲完了，咱们再讲讲日本其他阴暗的东西，就比如说是那个东野圭吾的白夜行吧。
@@ -12701,9 +15263,38 @@
 可以提问。
 发言人 2  00:15:55
 下一个由主。</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>小组讨论</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t># 讨论议题与背景
+本次讨论以闲聊方式围绕多国文学及《西游记》相关话题展开，参与发言的有发言人1、发言人2、发言人3、发言人4。核心探讨问题包括：日本文学（东野圭吾《白夜行》）的叙事手法与阴暗结局、法国文学（雨果《悲惨世界》）的抗争精神与浪漫理想主义、俄国文学（契诃夫、列夫·托尔斯泰、格罗斯曼、《古拉格群岛》《命运与生活》）对人性丑恶的揭露与批判、英国文学（狄更斯《圣诞欢歌》《雾都孤儿》《简爱》）对底层民众的描写、美国文学（马克·吐温、海明威、《了不起的盖茨比》）的现代叙事风格，以及中国文学与影视（《平凡的世界》、台湾电影《假如我是真的》）和《西游记》狮驼岭章节的讨论。讨论未形成明确结论，最后转入练习环节。
+# 发言要点
+发言人1提到《白夜行》是悬疑小说，叙事手法隐藏、每个人都有嫌疑，结局非常阴暗；认为法国文学有抗争精神，法国革命多，英国小说多写贵族生活；提到国内《平凡的世界》写底层也深刻，但受政策原因很多作品不让看；认为英国狄更斯的《圣诞欢歌》《雾都孤儿》讲底层人，贵族与穷人之间有鸿沟，穷人把希望寄托宗教或虚无；提到美国历史短、美洲大陆相对幸福，并提及《了不起的盖茨比》；提到《一九四二》讲大饥荒和战乱；提到《西游记》狮驼岭章节吓人，认为黑神话悟空没有设计那一章，因太血腥不好过审。发言人2提到《菊与刀》描绘日本人性格特点，认为《白夜行》符合日本形象；提到雨果《悲惨世界》体现浪漫的理想主义精神；提到契诃夫、列夫·托尔斯泰、格罗斯曼，认为俄国文学戏剧性更明显、更多揭露批判人性丑恶，《古拉格群岛》最早为法语版、俄语版在苏联解体后发行；提到台湾电影《假如我是真的》改编自俄国小说并结合文革真实事件，涉及知青上山下乡；提到英国土地承载不了人口膨胀，很多人移民美国；提到美国农业资源广阔、从不缺粮食、从未发生大饥荒；提到高尔基《海燕》体现被压迫后的反抗；详细讲述《西游记》狮驼岭章节，青狮、白象、大鹏三魔头吃掉全城人、尸骸遍地、人皮做地毯、头骨做装饰，距灵山约500公里，与普度众生大相径庭，认为大鹏精是唯一能遛猴子的反派。发言人3提到哈利波特、俄国文学，询问《假如我是真的》讲什么，最后提议停止讨论转入练习。发言人4提到法国只读过《悲惨世界》，英国只看了《简爱》，认为法国小说描绘底层民众多一些、英国都是贵族生活，认为俄国文学更曲折、戏剧性更明显，询问狮驼岭是什么、是否没有拍到电视剧。观点交锋点主要在于法国与俄国文学对底层民众描写的生动性比较，以及各国文学主题特点的差异。
+# 共识形成
+讨论未形成明确的统一意见或解决方案，各方主要分享了对各国文学及《西游记》狮驼岭章节的个人看法与阅读体验，未进行表决或达成共识。
+# 未决事项与分工
+需进一步探讨的问题包括：法国和俄国文学哪一个对底层民众的描写更生动；各国文学主题特点的具体比较。后续任务分工未明确，发言人3提议停止讨论并转入练习环节，发言人2回应OK，随后进入提问环节。</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>5886/1222</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="13.5" customHeight="1" s="9">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 各位好，咱们今天开个二十分钟的短会，主要是过一下手机图库项目目前的整体进展，顺便对齐下接下来的排期和潜在风险。老规矩，先听下产品侧的交互迭代和用户反馈，然后开发两位同步下技术实现和性能优化的情况，最后我总结一下接下来的重点工作。产品这边先开始吧
 发言人 2  00:00:36
 好的，我这边先同步下。最近两周咱们重点在推智能分类和相册推荐的改版，目前高保真原型已经出了V1.5版，主要调整了网格视图的交互逻辑，把长按手势做了更自然的微动效反馈。不过测试那边反馈说部分低端机上滑列表的时候偶尔会有掉帧的情况，我已经跟开发2沟通过了，看能不能通过降低预览图缩放级别来换帧。另外，用户调研那边收到不少关于‘隐私相册’入口太深的吐槽，我建议下一版直接把入口提到首部顶部二级菜单，产品经理看这个范围变更会不会太大
@@ -12759,9 +15350,37 @@
 好嘞，我十一点半前发你。大家效率拉满，咱们月底见分晓
 发言人 1  00:12:18
 好，那就这样，散会。辛苦各位，有问题随时在飞书上同步</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次短会围绕手机图库项目整体进展、排期与潜在风险展开。产品侧同步智能分类与相册推荐改版高保真原型已出V1.5版，调整网格视图交互逻辑并为长按手势加入微动效反馈，测试反馈部分低端机上滑列表偶尔掉帧，用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。开发侧同步AI智能标签接口已跑起V2版识别模型，准确率比上一代提升约88%，因新增视频帧提取功能单次请求耗时从800毫秒涨到约1.5秒，产品侧否决异步推送、确定采用本地缓存策略，开发1下午拉分支改逻辑预计三天联调完，并讨论端侧轻量级预过滤可平均压耗时一半。云相册同步模块弱网环境下断点续传出现状态机紊乱，同步队列积压到一千张以上时部分机型OOM崩溃，开发2已加分片加载机制每次只拉五十张但会拖慢整体同步进度，后台静默同步权限审核严大概率下不了。缩略图渲染改用新图片解码库后内存占用降约30%、CPU占用上升，已在主流三款机型灰度帧率稳定60帧、低端机约50帧，批量删除照片同时触发回收站重建索引时数据库偶尔锁死、已用消息队列排队临时规避、正式修复排到下下周版本。时间轴视图测试提三个高优Bug，滑动到二十年前老照片时页面卡死三秒以上，准备加本地索引预加载。会议确定调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化；里程碑按原定计划月底封版，内测包暂定下周三发。
+## 产品侧交互迭代与用户反馈
+- 智能分类和相册推荐改版，高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势做微动效反馈；测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通，考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。
+- 隐私相册入口提上去没问题，不算大改动，需出交互方案供评审；掉帧问题得抓紧，下周进性能压测。
+## AI智能标签接口与多模态识别模型部署
+- 后端已跑起V2版识别模型，准确率比上一代提升约88%；因加视频帧提取功能，单次请求耗时从800毫秒涨到约1.5秒；产品侧认为异步推送不行，提出本地缓存策略，开发1确认可加CQLite缓存层，下午拉分支改逻辑，预计三天联调完，缓存命中率低仍需回溯；讨论端侧轻量级预过滤，过滤gif或截图后再走全量云端识别，可平均压耗时一半，需评估模型体积和端侧推理开销，可能需申请两百兆本地缓存空间；安装包加两三百兆问题不大，但首次使用下载体验做成按需加载，用现有资源下发模块约两天搞定。</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>3605/1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="13.5" customHeight="1" s="9">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 好了，大家都到齐了，手机都放一下啊。今天咱们这个月度研讨会，就定在下午两点到两点四十，一共四十分钟。时间不长，但内容得扎实。上个月的市场波动挺大，咱们这个项目虽然整体去化还行，但有些数据我不满意。组长，你先从整体数据起个头，把核心指标过一遍
 发言人 2  00:00:35
 行，总监。我这边拉了后台的完整数据。上一个月咱们案场总到访是三百二十组，环比增加了百分之十五，这个数据是达标的。但是转化率低了点，成交七十六套，转化率是百分之二十三，比上个月的百分之二十七掉了一个点。渠道带看占比是百分之六十五，自然来访只有百分之三十五。蓄客量目前在三千二百组左右，认购到成交的流失率大概在百分之十八。整体来说，量是够的，但卡在逼定和转化环节
@@ -12831,9 +15450,37 @@
 明白，马上梳理客户
 发言人 5  00:15:07
 好的，我去改话术和准备物料</t>
-  </si>
-  <si>
-    <t>发言人 1  00:00:00
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次月度研讨会围绕上月案场数据复盘与下月去化目标展开。上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面。会议确认工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干；周末办业主答谢会，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练，每人必须参加、课后现场抽考，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房；财务和法务周六日轮流值班、在案场外围待命。下月总去化目标120套，拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。散会后半小时内，销售组长把会议纪要和任务分解表发到工作群；销冠下周晨会分享逼定案例。
+## 上月案场数据复盘与客户流失抗性分析
+- 上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。
+- 流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面；客户怕买错，需把工地实时进展、材料样板拉到面前看。
+## 下月去化目标与执行动作
+- 下月总去化目标120套，按人员配置和上月产出权重拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干，组长带销售A和销售B回访上周未成交三百多组，销冠梳理二十几个高意向客户周末逼定；周末办业主答谢会，销冠带人协助、销售B主抓流程、销售A负责邀约和逼定记录，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练（竞品对比与抗性化解、逼定时机与谈判心理学），每人必须参加、课后现场抽考、过不了加练，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房，再出问题直接问责；财务和法务周六日轮流值班、在案场外围待命；散会后半小时内，销售组长把会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例。</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>4211/1165</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="13.5" customHeight="1" s="9">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>发言人 1  00:00:00
 好了，人都齐了，咱们直接开。今天主要是过一下上周ASR模型的迭代进度，还有线上推理延迟和那个长音频卡死的问题。A和B先分别同步下各自负责板块的现状，有什么卡点或者需要协调的资源，现在直接提，别留到后面
 发言人 2  00:00:19
 嗯嗯，收到。组长，我先从数据和模型训练这块汇报。上周咱们定好的混合语料库，数据清洗流水线已经跑完了第二轮。我把那些长尾噪音、极端口音和背景人声重叠的片段单独做了分流，现在数据集里有效的语音时长占比从之前的89%提到了94%左右。另外，标注对齐这块，我重新校对了CTC的blank token分布，发现之前多音字和连读场景的切分点确实有点偏，这周打算用新基准跑一轮消融
@@ -12893,1688 +15540,149 @@
 没了，我这边就是模型训练、数据对齐和自动化评估，按节奏走就行。周三前把CI脚本和测试用例发群里评审
 发言人 3  00:11:57
 也没问题，推理优化、VAD消融、热修复和监控文档我盯着。组长，那咱们今天先到这？辛苦大家</t>
-  </si>
-  <si>
-    <t>MOS分</t>
-  </si>
-  <si>
-    <t>模板准确性</t>
-  </si>
-  <si>
-    <t>竞品对比</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>自定义模板</t>
-  </si>
-  <si>
-    <t>智能识别</t>
-  </si>
-  <si>
-    <t>新闻发布</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>沟通交流会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>总结复盘会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用纪要</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作研讨会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>庭审记录</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目进度会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>课堂记录</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>知识笔记</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>只是笔记</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>采访记录</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>就医咨询</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>面试报告</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>参观游览</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>调研访谈</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>家校沟通</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>团队例会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>专题讲座</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>辩论会</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品发布</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>政府报告</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>小组讨论</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话记录</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>文本</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="55.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="56.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="9" style="5"/>
-    <col min="4" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="4"/>
-    </row>
-    <row r="32" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="4"/>
-    </row>
-    <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="4"/>
-    </row>
-    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" s="4"/>
-    </row>
-    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="4"/>
-    </row>
-    <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="4"/>
-    </row>
-    <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="4"/>
-    </row>
-    <row r="41" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="4"/>
-    </row>
-    <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="4"/>
-    </row>
-    <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="4"/>
-    </row>
-    <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="4"/>
-    </row>
-    <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="4"/>
-    </row>
-    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="4"/>
-    </row>
-    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>70</v>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>通用纪要</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本次会议围绕上周ASR模型迭代进度、线上推理延迟与长音频解码卡死问题展开，A与B分别同步数据训练与推理侧现状。数据侧混合语料库清洗流水线跑完第二轮，长尾噪音、极端口音与背景人声重叠片段单独分流，有效语音时长占比从89%提升到94%左右，重新校对CTC blank token分布后发现多音字与连读场景切分点偏，本周用新基准跑消融；验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时易吞过渡音或重复解码。模型侧计划将全纯Transformer换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练，RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线与压测数据未跑完，明天下午发压力测试日志和截图。推理侧现有队列切分导致首字延迟波动在150ms到300ms之间，计划改为静态分段加流式解码组合方案，音频按2秒切块、前端VAD预过滤、后端RNN-T增量解码，首字延迟控制在80ms以内、吞吐量稳在120路并发，VAD阈值卡在-25dB并结合能量与谱熵双模型判断，下周拉线上流量回放做端到端对比。长音频卡死问题方面，线上用户输入超长连续且带方言口音音频导致解码loop卡死、解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题。组长提出三点要求：流式架构切换不能影响现有非流式离线批处理，双线都要保、测试用例覆盖全；VAD阈值由B做消融实验，误切率与漏切率画曲线找最优解；A的模型训练算力下周一开始划拨三块A100做增量训练，注意别和NLP组项目撞车、排队看调度面板错峰跑。会议明确稳定性优先、精度次之，下周先出热修复版本上灰度，专业术语后续做词表扩展和热词注入；CI/CD自动评估流水线由A负责评估脚本与流水线配置、预计三天周四前出V1版本，B配合把压测数据输出成标准JSON格式；监控面板接Prometheus和Grafana，B出监控指标定义文档明天下班前发组长转发运维负责人，告警分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。
+## 数据与模型训练进展
+- 混合语料库数据清洗流水线跑完第二轮，长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提到94%左右；重新校对CTC blank token分布，发现多音字和连读场景切分点偏，本周用新基准跑消融。验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时模型易吞过渡音或重复解码，排查为CTC对齐阶段跨语言边界和轻声尾音处理不够平滑。
+- 计划把全纯Transformer换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练；数据增强加时间偏移，对背景白噪声和混响鲁棒性差，准备引入MixUp和Cut再迭代。RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线和压测数据未跑完，明天下午发压力测试日志和截图。
+## 推理优化与线上稳定性
+- 现有队列切分导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯；计划改成静态分段加流式解码组合方案，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，首字延迟控制在80ms以内，吞吐量稳在120路并发；VAD阈值卡在-25dB，结合能量和谱熵双模型判断，下周拉线上流量回放做端到端对比。线上用户输入超长连续且带方言口音音频导致解码loop卡死，解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，日志显示RNN-T attention权重一直震荡没收敛；建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题，同时加超时熔断和降级返回。前端SDK采样率仍为16k而新模型为32k输入，前端不升级上采样会引入高频伪影影响识别率，前端对接人称排期推到下个月，32k模型在长尾词上比16k好0.5%的WER。</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>3912/1826</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B3:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="D3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>60</v>
+    <row r="3">
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>准确性</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>相关性</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>通顺性</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>其它问题</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>MOS分</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>模板准确性</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="e">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>竞品对比</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" s="0">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E4" t="e">
+        <v/>
+      </c>
+      <c r="E4" s="0">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F4" t="e">
+        <v/>
+      </c>
+      <c r="F4" s="0">
         <f>AVERAGE(竞品对比!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G4" s="3" t="e">
+        <v/>
+      </c>
+      <c r="G4" s="3">
         <f>COUNTIF(竞品对比!#REF!,-5)/COUNTIF(竞品对比!#REF!,"&lt;&gt;")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H4" t="e">
+        <v/>
+      </c>
+      <c r="H4" s="0">
         <f>AVERAGE((竞品对比!#REF!+竞品对比!#REF!+竞品对比!#REF!)/3+竞品对比!#REF!)</f>
-        <v>#REF!</v>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B5" s="8"/>
-      <c r="C5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="3"/>
+    <row r="5">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B6" s="8"/>
-      <c r="C6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="3"/>
+    <row r="6">
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B7" s="1" t="s">
-        <v>65</v>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>自定义模板</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" t="e">
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>智能识别</t>
+        </is>
+      </c>
+      <c r="I8" s="0">
         <f>COUNTIF(#REF!,“可用”)</f>
-        <v>#REF!</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="1">
     <mergeCell ref="B4:B6"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="6"/>
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="4"/>
-  <pixelatorList sheetStid="5"/>
-  <pixelatorList sheetStid="3"/>
-  <pixelatorList sheetStid="7"/>
-  <pixelatorList sheetStid="9"/>
-  <pixelatorList sheetStid="10"/>
-  <pixelatorList sheetStid="11"/>
-  <pixelatorList sheetStid="12"/>
-  <pixelatorList sheetStid="14"/>
-  <pixelatorList sheetStid="16"/>
-  <pixelatorList sheetStid="18"/>
-  <pixelatorList sheetStid="19"/>
-</pixelators>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <woSheetsProps>
-    <woSheetProps sheetStid="6" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="4" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="5" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="3" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="7" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="9" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="10" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="11" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="12" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="14" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="16" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-    <woSheetProps sheetStid="18" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-  </woSheetsProps>
-  <woBookProps>
-    <bookSettings isFilterShared="0" coreConquerUserId="" isAutoUpdatePaused="0" filterType="user" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
-  </woBookProps>
-</woProps>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<autofilters xmlns="https://web.wps.cn/et/2018/main">
-  <sheetItem sheetStid="1">
-    <filterData filterID="AK20210901JXNSXO8261057">
-      <hiddenRange rowFrom="1" rowTo="9"/>
-      <hiddenRange rowFrom="11" rowTo="22"/>
-      <hiddenRange rowFrom="24" rowTo="35"/>
-      <hiddenRange rowFrom="37" rowTo="48"/>
-      <hiddenRange rowFrom="50" rowTo="55"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO15104038">
-      <hiddenRange rowFrom="1" rowTo="1"/>
-      <hiddenRange rowFrom="3" rowTo="3"/>
-      <hiddenRange rowFrom="5" rowTo="14"/>
-      <hiddenRange rowFrom="16" rowTo="16"/>
-      <hiddenRange rowFrom="18" rowTo="27"/>
-      <hiddenRange rowFrom="29" rowTo="29"/>
-      <hiddenRange rowFrom="31" rowTo="40"/>
-      <hiddenRange rowFrom="42" rowTo="42"/>
-      <hiddenRange rowFrom="44" rowTo="53"/>
-      <hiddenRange rowFrom="55" rowTo="56"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO2962640"/>
-    <filterData filterID="AK20210901JXNSXO16551897"/>
-    <filterData filterID="AK20210901JXNSXO14573183"/>
-    <filterData filterID="AK20210901JXNSXO14760968"/>
-    <filterData filterID="AK20210901JXNSXO16981454"/>
-    <filterData filterID="AK20210901JXNSXO15978846">
-      <hiddenRange rowFrom="1" rowTo="12"/>
-      <hiddenRange rowFrom="14" rowTo="25"/>
-      <hiddenRange rowFrom="27" rowTo="38"/>
-      <hiddenRange rowFrom="40" rowTo="51"/>
-      <hiddenRange rowFrom="53" rowTo="55"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO12102127">
-      <hiddenRange rowFrom="1" rowTo="10"/>
-      <hiddenRange rowFrom="12" rowTo="23"/>
-      <hiddenRange rowFrom="25" rowTo="36"/>
-      <hiddenRange rowFrom="38" rowTo="49"/>
-      <hiddenRange rowFrom="51" rowTo="55"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO17933749">
-      <hiddenRange rowFrom="5" rowTo="5"/>
-      <hiddenRange rowFrom="15" rowTo="15"/>
-      <hiddenRange rowFrom="17" rowTo="18"/>
-      <hiddenRange rowFrom="28" rowTo="28"/>
-      <hiddenRange rowFrom="30" rowTo="31"/>
-      <hiddenRange rowFrom="41" rowTo="41"/>
-      <hiddenRange rowFrom="43" rowTo="44"/>
-      <hiddenRange rowFrom="54" rowTo="54"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO18734464">
-      <hiddenRange rowFrom="1" rowTo="4"/>
-      <hiddenRange rowFrom="6" rowTo="7"/>
-      <hiddenRange rowFrom="9" rowTo="17"/>
-      <hiddenRange rowFrom="19" rowTo="20"/>
-      <hiddenRange rowFrom="22" rowTo="30"/>
-      <hiddenRange rowFrom="32" rowTo="33"/>
-      <hiddenRange rowFrom="35" rowTo="43"/>
-      <hiddenRange rowFrom="45" rowTo="46"/>
-      <hiddenRange rowFrom="48" rowTo="55"/>
-    </filterData>
-    <autofilterInfo filterID="AK20210901JXNSXO14573183">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO16551897">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO16981454">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO14760968">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO15104038">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="段功宸"/>
-            <customFilter operator="equal" val="江涛"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO2962640">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO17933749">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="4">
-          <filters>
-            <filter val="1"/>
-            <filter val="2"/>
-            <filter val="3"/>
-            <filter val="4"/>
-            <filter val="5"/>
-            <filter val="3.5"/>
-            <filter val="4.5"/>
-          </filters>
-        </filterColumn>
-        <filterColumn colId="11">
-          <filters>
-            <filter val="2"/>
-            <filter val="3"/>
-            <filter val="4"/>
-            <filter val="5"/>
-            <filter val="3.5"/>
-            <filter val="4.5"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO18734464">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="李腾飞"/>
-            <customFilter operator="equal" val="石晓华"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO12102127">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="余瑞芳"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO15978846">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="钟婉婷"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO8261057">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC57">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="武思华"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-  </sheetItem>
-  <sheetItem sheetStid="4">
-    <filterData filterID="AK20210901JXNSXO8261057">
-      <hiddenRange rowFrom="1" rowTo="9"/>
-      <hiddenRange rowFrom="11" rowTo="22"/>
-      <hiddenRange rowFrom="24" rowTo="35"/>
-      <hiddenRange rowFrom="37" rowTo="48"/>
-      <hiddenRange rowFrom="50" rowTo="61"/>
-      <hiddenRange rowFrom="63" rowTo="74"/>
-      <hiddenRange rowFrom="76" rowTo="81"/>
-      <hiddenRange rowFrom="83" rowTo="84"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO15104038">
-      <hiddenRange rowFrom="1" rowTo="1"/>
-      <hiddenRange rowFrom="3" rowTo="3"/>
-      <hiddenRange rowFrom="5" rowTo="14"/>
-      <hiddenRange rowFrom="16" rowTo="16"/>
-      <hiddenRange rowFrom="18" rowTo="27"/>
-      <hiddenRange rowFrom="29" rowTo="29"/>
-      <hiddenRange rowFrom="31" rowTo="40"/>
-      <hiddenRange rowFrom="42" rowTo="42"/>
-      <hiddenRange rowFrom="44" rowTo="53"/>
-      <hiddenRange rowFrom="55" rowTo="55"/>
-      <hiddenRange rowFrom="57" rowTo="66"/>
-      <hiddenRange rowFrom="68" rowTo="68"/>
-      <hiddenRange rowFrom="70" rowTo="85"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO14573183">
-      <hiddenRange rowFrom="1" rowTo="5"/>
-      <hiddenRange rowFrom="7" rowTo="18"/>
-      <hiddenRange rowFrom="20" rowTo="31"/>
-      <hiddenRange rowFrom="33" rowTo="44"/>
-      <hiddenRange rowFrom="46" rowTo="57"/>
-      <hiddenRange rowFrom="59" rowTo="70"/>
-      <hiddenRange rowFrom="72" rowTo="84"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO16551897">
-      <hiddenRange rowFrom="1" rowTo="8"/>
-      <hiddenRange rowFrom="10" rowTo="21"/>
-      <hiddenRange rowFrom="23" rowTo="34"/>
-      <hiddenRange rowFrom="36" rowTo="47"/>
-      <hiddenRange rowFrom="49" rowTo="60"/>
-      <hiddenRange rowFrom="62" rowTo="73"/>
-      <hiddenRange rowFrom="75" rowTo="80"/>
-      <hiddenRange rowFrom="82" rowTo="84"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO17933749"/>
-    <filterData filterID="AK20210901JXNSXO18734464"/>
-    <filterData filterID="AK20210901JXNSXO14760968">
-      <hiddenRange rowFrom="1" rowTo="11"/>
-      <hiddenRange rowFrom="13" rowTo="24"/>
-      <hiddenRange rowFrom="26" rowTo="37"/>
-      <hiddenRange rowFrom="39" rowTo="50"/>
-      <hiddenRange rowFrom="52" rowTo="63"/>
-      <hiddenRange rowFrom="65" rowTo="76"/>
-      <hiddenRange rowFrom="78" rowTo="82"/>
-      <hiddenRange rowFrom="84" rowTo="84"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO16981454"/>
-    <filterData filterID="AK20210901JXNSXO12102127">
-      <hiddenRange rowFrom="1" rowTo="10"/>
-      <hiddenRange rowFrom="12" rowTo="23"/>
-      <hiddenRange rowFrom="25" rowTo="36"/>
-      <hiddenRange rowFrom="38" rowTo="49"/>
-      <hiddenRange rowFrom="51" rowTo="62"/>
-      <hiddenRange rowFrom="64" rowTo="75"/>
-      <hiddenRange rowFrom="77" rowTo="84"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO15978846">
-      <hiddenRange rowFrom="1" rowTo="12"/>
-      <hiddenRange rowFrom="14" rowTo="25"/>
-      <hiddenRange rowFrom="27" rowTo="38"/>
-      <hiddenRange rowFrom="40" rowTo="51"/>
-      <hiddenRange rowFrom="53" rowTo="64"/>
-      <hiddenRange rowFrom="66" rowTo="77"/>
-      <hiddenRange rowFrom="79" rowTo="83"/>
-    </filterData>
-    <autofilterInfo filterID="AK20210901JXNSXO15104038">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="段功宸"/>
-            <customFilter operator="equal" val="江涛"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO16551897">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="王俊凯"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO14573183">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="潘奕利"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO17933749">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO18734464">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO14760968">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="翟雨实"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO16981454">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO12102127">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="余瑞芳"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO15978846">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="钟婉婷"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO8261057">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="武思华"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-  </sheetItem>
-  <sheetItem sheetStid="3">
-    <filterData filterID="AK20210901JXNSXO15104038">
-      <hiddenRange rowFrom="1" rowTo="1"/>
-      <hiddenRange rowFrom="3" rowTo="3"/>
-      <hiddenRange rowFrom="5" rowTo="14"/>
-      <hiddenRange rowFrom="16" rowTo="16"/>
-      <hiddenRange rowFrom="18" rowTo="27"/>
-      <hiddenRange rowFrom="29" rowTo="29"/>
-      <hiddenRange rowFrom="31" rowTo="40"/>
-      <hiddenRange rowFrom="42" rowTo="42"/>
-      <hiddenRange rowFrom="44" rowTo="53"/>
-      <hiddenRange rowFrom="55" rowTo="55"/>
-      <hiddenRange rowFrom="57" rowTo="66"/>
-      <hiddenRange rowFrom="68" rowTo="68"/>
-      <hiddenRange rowFrom="70" rowTo="79"/>
-      <hiddenRange rowFrom="81" rowTo="81"/>
-      <hiddenRange rowFrom="83" rowTo="85"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO8261057"/>
-    <filterData filterID="AK20210901JXNSXO14760968"/>
-    <filterData filterID="AK20210901JXNSXO18734464">
-      <hiddenRange rowFrom="1" rowTo="3"/>
-      <hiddenRange rowFrom="5" rowTo="16"/>
-      <hiddenRange rowFrom="18" rowTo="29"/>
-      <hiddenRange rowFrom="31" rowTo="42"/>
-      <hiddenRange rowFrom="44" rowTo="55"/>
-      <hiddenRange rowFrom="57" rowTo="68"/>
-      <hiddenRange rowFrom="70" rowTo="81"/>
-      <hiddenRange rowFrom="83" rowTo="85"/>
-    </filterData>
-    <filterData filterID="AK20210901JXNSXO17933749"/>
-    <filterData filterID="AK20210901JXNSXO15978846"/>
-    <filterData filterID="AK20210901JXNSXO16981454"/>
-    <filterData filterID="AK20210901JXNSXO12102127"/>
-    <filterData filterID="AK20210901JXNSXO14573183"/>
-    <filterData filterID="AK20210901JXNSXO16551897"/>
-    <autofilterInfo filterID="AK20210901JXNSXO15104038">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="段功宸"/>
-            <customFilter operator="equal" val="江涛"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO18734464">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L86">
-        <filterColumn colId="1">
-          <customFilters>
-            <customFilter operator="equal" val="江涛"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-  </sheetItem>
-  <sheetItem sheetStid="12">
-    <filterData filterID="AK20210901JXNSXO17933749">
-      <hiddenRange rowFrom="3" rowTo="3"/>
-      <hiddenRange rowFrom="6" rowTo="9"/>
-      <hiddenRange rowFrom="16" rowTo="19"/>
-      <hiddenRange rowFrom="24" rowTo="28"/>
-      <hiddenRange rowFrom="30" rowTo="31"/>
-      <hiddenRange rowFrom="34" rowTo="39"/>
-      <hiddenRange rowFrom="42" rowTo="42"/>
-      <hiddenRange rowFrom="44" rowTo="47"/>
-      <hiddenRange rowFrom="51" rowTo="52"/>
-      <hiddenRange rowFrom="54" rowTo="57"/>
-      <hiddenRange rowFrom="68" rowTo="69"/>
-      <hiddenRange rowFrom="71" rowTo="71"/>
-      <hiddenRange rowFrom="74" rowTo="74"/>
-      <hiddenRange rowFrom="77" rowTo="81"/>
-      <hiddenRange rowFrom="86" rowTo="86"/>
-      <hiddenRange rowFrom="88" rowTo="91"/>
-      <hiddenRange rowFrom="93" rowTo="94"/>
-      <hiddenRange rowFrom="97" rowTo="103"/>
-      <hiddenRange rowFrom="105" rowTo="105"/>
-      <hiddenRange rowFrom="107" rowTo="110"/>
-      <hiddenRange rowFrom="112" rowTo="116"/>
-      <hiddenRange rowFrom="118" rowTo="118"/>
-      <hiddenRange rowFrom="121" rowTo="123"/>
-    </filterData>
-    <autofilterInfo filterID="AK20210901JXNSXO17933749">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F125">
-        <filterColumn colId="5">
-          <filters>
-            <filter val="1.1：候选人概况中&quot;面试官主要来自权哥、帅总、郑总等&quot;中&quot;郑总&quot;在原文中未明确出现，原文仅出现&quot;权哥&quot;&quot;帅总&quot;及&quot;另一个面试官&quot;，&quot;郑总&quot;为模型推测；2.1：原文中发言者4也参与了部分技术提问（如数据库优化、Nginx跨域），模型未在面试官介绍中体现其角色"/>
-            <filter val="2.1:对'家庭氛围压抑'这一背景信息提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="识别模板为家校沟通,原文为沟通交流会但内容为家长会,家校沟通可适用但与沟通交流会模板略有偏差。2.1:对'青春期沟通'核心话题提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="1.1 提取错误：原文，公司写的12-17k，候选人要15K，公司最高给12，如果13候选人可接受继续后续面试&#10;2.1 细节遗漏：遗漏候选人对自动化测试缺点、动态元素定位的细节描述，做了整体总结"/>
-            <filter val="1.3：摘要中“候选人自称目前是应届生身份”与原文不符，发言者2在自我介绍中明确表示“目前是22岁”，但并未自称“应届生”，而是直接以应聘者身份参与面试，且面试官也未就“应届生”身份进行追问，该表述属于实体提取错误。摘要中“性能测试（最高20万并发）”的描述存在歧义，原文中发言者2在回答“你做过最高的并发是做到多少？”时回答“最高的是最后20万”，可能是指测试中的并发用户数，但摘要未明确单位（如“20万并发用户”），表述不够精确。1.4：摘要将“职业规划表述不够清晰，最初回答‘做老板’，后改称‘踏踏实实干活’”作为风险点，但原文中面试官询问“你写的职业规划是做老板是啥意思？”时，发言者2回答“这个其实是我瞎写的，因为我目前没有什么大的规划，我就想踏踏实实干活”，该回答并非“改称”，而是对“做老板”这一规划的直接解释和澄清，摘要的因果逻辑表述不准确。2.1：摘要缺失了面试中最核心的结论性信息——面试官最终给出的“最高给到12k，15k给不到，如果13k可以接受则安排复试，否则不再考虑”这一关键薪资谈判结果，这是整场面试的实质性结论，属于全局核心遗漏.2.3：摘要中的“能力评估”表格内容多为对面试问答的概括性复述，如“能清晰描述测试用例设计规范”“掌握接口测试（正向/异常）”等，缺乏对候选人表现优劣的深入评判，且部分描述（如“沟通协作”维度）未结合具体面试互动细节，冗余约30%"/>
-            <filter val="1.1：'提议学唱《水手》作为情绪调节尝试'与原文不符，原文中《水手》是来访者此前已学会的歌曲（'你上次放的水手我会唱了'），并非咨询师新提议的任务；2.1：遗漏了来访者关于欧文亚隆存在主义心理学四大终极问题（死亡、自由、孤独、无意义）的讨论内容，这是原文中较重要的哲学探讨环节；2.1：遗漏了来访者明确表达的'未来梦想当一个歌手'的具体职业向往，仅概括为'对音乐有强烈兴趣'"/>
-            <filter val="2.1 核心遗漏：对于住宿的部分没有提及&#10;3.2 小标题合理性：互动与体验部分分类不合理，马队体验可以并入千问的那拉提景区介绍，美食单独作为一个分类呈现&#10;自驾部分应该单独作为一个分类"/>
-            <filter val="1.2：摘要将部分受访者身份归属错误。原文中发言者2明确表示自己是“做当代艺术的”（艺术家），发言者3是“做设计的”，而摘要将其合并归为“当代艺术家/策展人”，未准确区分二人身份；发言者4并非“自由职业设计师”，原文中其称“我是做摄影的”，摘要归纳有偏差；发言者12并非“互联网平台618搞的朋友”，而是电商从业者，发言者13是与其聊工作的同行，摘要将二人合并表述为“与这位互联网平台618搞的朋友”，导致身份混淆。2.1：本次街头采访的核心主题是“深夜工作日外出的原因”，受访者的个人故事和独特回答（如“多邻国打卡1000多天”“阿森纳是冠军”“南昌路最帅调酒师之争”等）是本视频的重要看点，但摘要仅以表格形式概括职业和作息，缺失了这些富有趣味性和个性化的内容，降低了访谈摘要的可读性和传播价值"/>
-            <filter val="2.1 核心遗漏：只分析了候选人的相关信息，面试结果未提及，公司方的信息也没有&#10;2.2 比例失调：对于候选人亮点和风险点的分析都抓住的不算核心矛盾"/>
-            <filter val="2.1 核心遗漏：只分析了候选人的相关信息，面试结果未提及，公司方的信息也没有&#10;关于薪资、学历等关键面试信息都没有提及&#10;2.2 比例失调：对于候选人亮点和风险点的分析都抓住的不算核心矛盾"/>
-            <filter val="1.1: 幻觉，摘要中'情绪反应持续时间：分手后立即产生强烈情绪，持续约1个月'，原文中来访者未明确提及分手到咨询的具体时长，仅提及'最近跟我相处5年的男朋友分手了'，'持续约1个月'为模型自行添加的具体时间数据.。2.1: 全局核心遗漏，原文咨询的核心结论为'靠时间疗愈'和'容易被情绪绑架'，摘要虽提及但未充分强调咨询师对来访者'靠时间''时间还不够'这一核心判断，以及来访者对'时间够不够'的追问（'那多久算时间够'）这一互动关键点，略有遗漏"/>
-            <filter val="2.1 核心遗漏：没有介绍来访的基本背景&#10;3.2 小标题合理性：心理症状是整个核心困扰中所有部分都涉及的，不应该单拎成一个小部分&#10;情绪疏导和共情与支持有概念重叠"/>
-            <filter val="2.1 核心遗漏：没有介绍来访的基本背景&#10;2.2 比例失调：对于咨询干预后来访的改善篇幅过小&#10;3.2 小标题合理性：心理支持和共情与支持有概念重叠"/>
-            <filter val="2.1 核心遗漏：教师对提出问题的解决建议基本未提及&#10;2.3 冗余：家长反馈部分不需要引用家长原话&#10;3.3 分段不合理：对于解决方案的分类太多、太碎，主次结构也不清晰&#10;3.4 内容重复多次：家长反馈没有必要用两个分类提两次"/>
-            <filter val="1.3：摘要中提到“提出需高薪聘请技术骨干但未明确招聘进度”，原文发言者6确实提及“高薪聘用几个作为招牌”，但同时也提到“招收新学员”，摘要仅提及聘请技术骨干，遗漏了“招收新学员”这一并列计划，属于部分实体提取不完整.1.4：摘要中“积分兑换制度（10元=1积分）及消费积分有效期管理方案”表述基本准确，但原文中积分规则由发言者1和发言者6等共同讨论，且明确消费积分每年清零、预存积分永久有效，摘要未区分两类积分，简化了逻辑细节，但未严重扭曲。2.1：全文最核心的讨论成果（开业套餐方案、会员活动、老带新机制、装修风格、积分制度等）在“进度追踪”模块中有所覆盖，但缺少对“男性休息区保留与否”、“VIP客户随行人员免费体验”等几项关键决策的明确记录，且未提炼出任何明确的最终决议或共识，例如套餐是否最终确定、装修风格是否定调等，全局核心结论缺失。2.2：摘要将原文内容结构化呈现，但部分模块（如“营销推广策略”）内容单薄，仅简单罗列，而原文中有大量关于具体套餐细节、促销活动（如398元拉新方案、进店送礼等）的详细讨论，被过度简略，导致比例失调。2.3：全文摘要中“进度追踪”表格内容多为对原文发言的概括，但部分描述仍偏列举式，例如“提出19.9元体验套餐（含...）”、“制定线上线下结合方案：...”等，保留了较多罗列细节，缺乏对核心策略的提炼，冗余约30%。"/>
-            <filter val="2.1 核心遗漏：对于自驾、住宿的部分没有提及&#10;3.2 小标题合理性：与马队互动怎么会属于行程调整呢"/>
-            <filter val="1.3：摘要中“投资公司于2016年5月10日提交再审答辩状时附带7份附件”表述准确，但原文中发言者1明确说明附件二、三、六、七为“不作为新证据提交，只是供法院参考”，摘要未区分哪些是证据哪些是参考资料，存在轻微实体提取不完整。2.1：摘要缺失了法庭辩论环节中最核心的法律争点——即“雇佣救助合同是否适用海商法183条按比例分摊规则”这一双方交锋最激烈的焦点，仅以表格形式简单罗列双方观点，未体现投资公司关于“人命救助应扣减50%报酬”的关键抗辩，也未体现南海救助局关于“海商法但书条款仅适用于人命酬金”的核心辩论意见，属于全局核心遗漏.2.2：摘要将大量篇幅用于罗列“证据提交情况”“质证意见”“法官询问要点”等程序性内容，而法庭辩论阶段的法律争议内核被压缩为简表，比例略有失调"/>
-            <filter val="识别模板正确。2.1:对'社工与社区协调困难'细节提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="识别模板正确。2.1:对'线上线下融合'核心议题提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="识别模板正确。2.1:对面试具体问答细节提炼略浅,部分技术问题未充分呈现；3.1:个别标点略不规范"/>
-            <filter val="2.1 核心遗漏：没有把问题的关键现状和解决措施列完整&#10;3.2 小标题合理性：归类业主提出的问题不应该概括为信息同步&#10;4.3 层级逻辑极其混乱：每个问题都应该按照问题现状-物业回应-解决措施的逻辑排列，现在的整个顺序是乱的"/>
-            <filter val="1.1：事实错误，跨课程联合宣传是发言者1提的，摘要中写的发言者3和4&#10;2.1：细节遗漏：招生策略中缺少“先抓住孩子，再抓父母”，舞蹈班缺少对不同需求的区分"/>
-            <filter val="2.1 核心遗漏：没有把当前产品类型的所有阻塞问题列出来&#10;没有把管理层对于问题处理方案的决策列出来&#10;4.3 层级逻辑极其混乱：不同产品类型的格式不一样"/>
-            <filter val="1.1 幻觉：编造原文不存在的具体参数，略微严重&#10;2.1 比例失调：原文虽然归类产品发布但主要是纪录片内容，摘要侧重了产品，倒也没什么问题"/>
-            <filter val="1.1：'5年测试伪装应届生'为原文标题/摘要性描述，候选人实际自述为应届生，模型未在概况中说明这一身份争议的来源（标题描述 vs 候选人自述），可能造成误解；1.3：候选人期望薪资原文仅记录为'20'，模型直接解读为'20K'，原文未明确单位，存在数值单位推断；2.1：遗漏面试官对候选人'真的是应届生吗'的质疑及候选人'可能我长得有点显老'的回应这一关键互动细节（虽在综合素质中提及但未在概况中体现）；2.1：遗漏候选人'不行，这是原则性问题'的完整语境（针对薪资20K被压低后的回应），模型在沟通协作维度仅简略提及"/>
-            <filter val="2.1 细节遗漏，遗漏部分受访者观点的细节&#10;2.2 从100万到7位数（百万）不等 表述不通顺"/>
-            <filter val="2.1 核心遗漏：提取金句时没头没尾的，只看截取部分不明白想表达什么&#10;3.2 小标题合理性：童年早于车祸残疾的经历怎么能属于人生选择和创作态度呢&#10;关于电影创作和对人生的理解，与第一个大分类有重叠&#10;4.3 层级逻辑极其混乱：不理解是以什么逻辑顺序呈现的，不同部分之间的界限不清晰，重叠部分也很多"/>
-            <filter val="1.1: 幻觉，摘要中'改进计划'第3条'财务与人力资源部门需解决薪酬问题：优先解决员工工资拖欠问题，确保当月工资按时发放'等表述，原文总经理明确表示资金紧张，但并未承诺'确保当月工资按时发放'，而是提出'会向董事长反应资金问题'，此措辞属于过度承诺.摘要中'改进计划'第3条'建立资金使用审批绿色通道'，原文完全未提及此概念，属于凭空捏造。1.3: 实体提取错误，摘要中'酒店已拖欠员工工资达半年'，原文后勤保障部发言人5提到'半年没开工资啦'，但总经理并未确认该时长，且可能为特定部门情况，摘要将其作为全局事实陈述，存在归因偏差。1.4: 逻辑错乱，摘要中'责任推诿现象：各部门存在将问题上交推卸责任的情况'，原文仅总经理提到'别把问题甩给我'，但后勤部门发言人5明确表示已多次打报告申请资金未获批准，并非推诿而是流程受阻，摘要将其简单归为'推诿'与原文语境不符。2.1: 全局核心遗漏，会议核心为酒店停业整顿原因分析及责任追究，原文总经理强调了消防、食品、服务等多方面问题，且后勤部门回应了资金不足导致整改困难，但摘要的'改进计划'完全未提及如何协调资金短缺这一根本矛盾（总经理承认资金紧张，后勤强调无钱整改），缺失核心症结讨论。2.2: 比例失调，摘要中'改进计划'部分占篇幅较大，但原文后半部分讨论的核心'资金短缺与工资拖欠'仅在'不足事项'中一笔带过，未充分体现后勤部门对无钱整改的反驳及双方争论，重点略偏"/>
-            <filter val="识别模板错误：应为'采访记录'，模型识别为'心理咨询'。原文为采访对话，受访者疑似姜思达（发言者2提及'下面请姜思达发言'），非心理咨询关系；1.1：咨询小结中'布置的家庭作业是记录一周内在不同社交场景中的自我评价内容'、'下次咨询将重点讨论如何区分自我保护与自我限制的界限'均为模型捏造，原文未提及任何家庭作业或下次咨询计划；1.1：'来访者承认通过回避社交活动可以缓解不适'与原文不符，原文是发言者1提到'通过不参加任何活动得到了全然的改变'，且这是作为歌手保护嗓子的客观原因，非回避社交的应对策略；2.1：因模板选错，未按采访记录模板（访谈概述、访谈详细记录、关键引语与金句）组织内容，遗漏了原文中具有传播价值的关键引语，如'如果没有什么关系是永恒的，你还敢投入吗？'、'如果太大声会显得我太冒进，太小声，别人会听不见'等；2.1：未识别出受访者身份（姜思达）及采访背景"/>
-            <filter val="识别模板错误：应为'总结复盘会'，模型识别为'团队例会'，导致整体结构（复盘目标与结果概况、亮点事项、不足事项、改进计划）缺失；1.1：协作需求中'计划在12月中旬前完成初步沟通'、'确保宣传覆盖率达100%'为模型捏造，原文未提及具体时间节点和覆盖率指标；2.1：遗漏事故科核心数据（事故率同比下降7.5%、酒驾肇事占1%、突发事故占22.3%、车辆故障占17.5%、高峰期事故占40%多）；2.1：遗漏事故科提出的4点改进建议具体内容（加大打击惩罚力度、偏僻路口增加投入、高峰期增加人力辅助、与安全科合作）；2.1：遗漏二大队关于开发区超速、闯红灯、工程车超载等核心问题的具体分析"/>
-            <filter val="2.1：遗漏了发言者1关于歌手身份与保护嗓子的内容、在朋友群聊中&quot;没有什么原因坐在那就是很想哭&quot;的具体例子、&quot;安静不是一个选择，安静是你唯一的能力&quot;等关键表述；关键引语准确无误，访谈结构清晰"/>
-            <filter val="2.1:对'青春期沟通'这一核心话题提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="2.1:对'社工与社区协调困难'这一细节提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="2.1:对'线上线下融合'这一核心议题提炼略显不足；3.1:个别标点略不规范"/>
-            <filter val="1.1：发布会日期&quot;2020年7月23日&quot;在原文中未明确提及，原文仅提及该日期为许某某被刑事拘留时间，模型将其作为发布会日期属推断/捏造；2.1：遗漏了许某某&quot;自1987年开始先后在绍兴、上海等地从事鱼粉和养殖生意&quot;的背景信息；整体案件时间线、侦查数据、当事人信息梳理准确完整"/>
-            <filter val="1.1: 幻觉，摘要中'最终决议'部分将多个讨论中的提议直接定性为'确定'或'实施'的决议，例如'确定19.9元体验套餐'、'实施满1000元办卡政策'、'采用粉色/紫色主色调'等，但原文为多人发言的商讨场景，发言者1多次以'可以''也行'等词汇表示认可，并未明确宣布最终决议，摘要将讨论内容转化为正式决策属于过度确定性表述.1.3: 实体提取错误，摘要中'韩国冰醇小气泡'原文为'韩国冰韩韩国冰醇小气包儿'（应为'韩国冰醇小气泡'，但原文有口误），模型提取为'韩国冰醇小气泡'基本正确，但'PTD电子光疗'原文为'P T D电子光疗'，提取无大问题；但摘要将'外延排毒刮痧'写为'外延排毒刮痧'（原文为'外延排毒刮痧'）摘要中'充值500元赠100积分、充值1000元赠200积分'，原文发言人2表述为'充五百赠一百''充一千赠两百'，但发言人3提到'充三百赠一百充五百赠两百'，摘要只取部分发言者提议并未区分来源，且将'赠金额'误解为'赠积分'，原文积分与赠金为两套体系（积分按消费金额累积，赠金为充值赠送），摘要混淆。1.4: 逻辑错乱，摘要'遗留问题第5条：促销活动的时间范围（如365元/年方案的具体有效期）需确定'，原文发言人5提出365元/年方案时明确为'全年美容'，时间范围本身已明确（一年），摘要将其列为'需确定'的逻辑与实际不符。2.1: 全局核心遗漏，会议开场明确讨论议题包括'优惠政策、套餐内容、员工工资、装修风格'，摘要虽涵盖了套餐、会员、装修、积分等，但遗漏了员工工资讨论（发言人1开头提及），且对'装修风格'的讨论较简略（未提及灯具、布帘等细节）2.3: 冗余，摘要中'方案陈述'表格和'最终决议'、'遗留问题'存在大量重复内容（同一套餐、活动在多个部分重复描述），冗余内容超过30%"/>
-            <filter val="1.2 事实错误：缺货的是低档烟，不是高档烟&#10;2.1 核心遗漏：工作内容部分没有囊括所有的问题&#10;没有把管理层对于问题处理方案的决策列出来"/>
-            <filter val="1.2：摘要将“后勤保障部”负责人（发言者5）的强烈反驳意见简单归为“反馈”，并称其“申请资金解决工资发放问题”，但原文中发言者5明确表示“半年没开工资”、“我是没告你们”，态度激烈，摘要弱化了这种对抗性，且未体现其对总经理批评的直接反驳，属于观点提取不准确。1.3：摘要中“总经理需要各部门提交详细的整改方案和时间节点”属于捏造，原文中总经理并未提出此要求；同时，“餐饮部需要检查厨房用具安全，特别是天然气使用安全”是总经理在会议后期提出的，并非餐饮部自己反馈的计划，摘要错误地将该要求归为餐饮部的“后续计划”，属于归属错误。1.4：摘要将停业整顿的主要原因归为“消防器材过期、电路老化、食材采购及厨房安全”，但原文中总经理明确指出“主要还是一些咱们酒店内部处理的这一些问题”，涵盖消防、设备、客户投诉、员工消极怠工等多个方面，且后勤保障部负责人指出根本原因是资金短缺导致设备无法更换，摘要未准确反映这一核心因果关系，简化了复杂的责任归属。2.1：整场会议最核心的议题是总经理追责、各部门自我辩护与相互指责，以及因资金短缺导致的整改困境，但摘要完全缺失“各部门责任推诿”这一核心矛盾，也未提及总经理“该撤的撤、该降的降”等严厉表态，以及后勤保障部对资金问题的直接挑战，导致核心冲突与会议性质被严重弱化，属于全局核心遗漏。2.2：摘要将大量篇幅用于罗列各部门“问题-现状-后续计划”的表格，但这些内容多为对原文发言的机械拆分，而真正关键的互动交锋（如后勤保障部对总经理的当面反驳、餐饮部与后勤部关于食材质量的争执）被一笔带过或完全忽略，比例严重失调。2.3：摘要中的表格内容多为对原文口语的复述式概括，例如“消防通道堆放杂物、消防器材过期生锈”、“半年未发工资”等，缺乏更高层次的提炼，冗余超过50%"/>
-            <filter val="1.2：摘要中“咨询师指出来访者可能存在‘撒娇’倾向”描述不够准确，原文中咨询师说的是“你别从这个世界撒娇”、“你快点哄哄我就不哄我”，是咨询师对来访者反复说“但是”这一行为的解读，并非直接指出来访者存在撒娇倾向，表述略有偏差。2.1：摘要整体覆盖了咨询的核心议题和咨询师的主要干预技术，但遗漏了部分重要细节：咨询师明确指出来访者“脑子极混乱”、“容易被情绪绑架，被感觉绑架”、“感觉不加验证”，这些对来访者思维模式的描述是咨询师做出“靠时间”结论的关键依据，摘要未充分提取"/>
-            <filter val="2.1：遗漏了咨询师分享自身19岁经历（山东卫视首席主持人）、萨老师哥伦比亚大学心理学硕士背景、具体合唱歌曲《水手》、录有声书建议等细节；整体内容准确，干预技术归纳合理"/>
-            <filter val="1.2：销售技巧探讨中&quot;发言者6指出需通过细节服务（如送小礼品、递茶水）提升客户好感度&quot;实际为发言者3所述（原文发言者3提到&quot;送小礼品递茶水等细节部分&quot;）；2.1：&quot;达成共识与解决方案&quot;和&quot;未决分歧与后续探索&quot;部分内容为模型自行归纳，原文为开放式讨论，未明确达成共识或列出后续探索事项，属轻度拔高"/>
-            <filter val="1.1 事实错误，口才班需求支持与原文不一致；1.2 待协调事项负责人、对接人原文并未明确。2.1 细节遗漏，遗漏学生匹配度、先转孩子再抓父母的策略；"/>
-            <filter val="1.1 部分对接人、负责人幻觉，但还好；2.1 待协调事项部分内容与前文重复"/>
-            <filter val="2.1 核心遗漏：没有把问题的关键现状和解决措施列完整&#10;3.2 小标题合理性：归类业主提出的问题不应该概括为信息同步&#10;物业对于问题的回应和解决方案不应该概括为达成共识&#10;4.3 层级逻辑极其混乱：每个问题都应该按照问题现状-物业回应-解决措施的逻辑排列，现在要对应问题和相应的方案很困难"/>
-            <filter val="2.1：遗漏嫌疑人作案动机（因家庭生活矛盾对来某某产生不满，于7月5日凌晨在家中趁来某某熟睡之际将其杀害、分尸后分散抛弃）这一关键案件事实；2.1：遗漏化粪池筛查的具体时间（7月22日下午）、恶劣工作条件（40度高温、连续奋战25小时）等关键侦查细节；2.1：遗漏被害人基本信息（51岁、杭州某公司保洁员）；2.1：遗漏嫌疑人背景（1987年起在绍兴、上海从事鱼粉和养殖生意，2018年到杭州工作）；2.1：遗漏对小区1075户人家开展询问走访的规模信息"/>
-            <filter val="识别模板正确。2.1:对'家庭氛围压抑'背景信息提炼略浅；3.1:个别标点略不规范"/>
-            <filter val="1.4 逻辑错乱：净化器需求增加应该属于家电区的工作内容&#10;2.1 核心遗漏：工作内容部分没有囊括所有的问题&#10;没有把管理层对于问题处理方案的决策列出来"/>
-            <filter val="1.4：综合素质中&quot;对技术问题有持续学习的态度&quot;与原文候选人表达&quot;再久我真的要废了，搞不动了&quot;、&quot;不想搞了，累了累了&quot;的疲惫态度不符，存在逻辑判断偏差；2.1：原文为40+分钟长面试，模型遗漏了UniApp多端编译、Docker部署、Nacos服务注册发现、Sharding JDBC分库分表、CPU 100%事故（序列号写错入库几百亿）、本地压测QPS 1500、银信通项目对接第三方支付等多个技术话题讨论；项目经验评估过于简略"/>
-            <filter val="2.1 核心遗漏：双方的共识没有提及&#10;4.3 层级逻辑极其混乱：应该按照核心论点-立论框架-支撑论据的逻辑顺序排列"/>
-            <filter val="2.1 核心遗漏：对于论据的概括避重就轻，比如出现平台，没有强调主要出现在非权利中心这一关键论据&#10;双方的共识没有强调&#10;没有论述为什么反方胜利&#10;4.3 层级逻辑极其混乱：应该按照核心论点-立论框架-支撑论据的逻辑顺序排列"/>
-            <filter val="1.1 幻觉：：只有一个原告&#10;1.2 事实错误：要求追加被告的是法院方，不是原告&#10;2.1 核心遗漏：只写了第一、第二被告，这些分别代表什么人和公司没有提及&#10;出庭情况没有提及&#10;只有质证，没有提及被质疑的证据具体是什么"/>
-            <filter val="1.1：改进计划中&quot;19:00-23:00时段增派警力&quot;在原文中未提及，原文仅说&quot;晚上&quot;，具体时段属捏造；1.1：&quot;每月至少开展一次中小学交通安全公开课&quot;的频率原文未提及；1.1：&quot;结合测速设备强化夜间管控&quot;原文未明确提及测速设备；2.1：遗漏了事故科关于事故原因的具体数据（酒驾占1%、突发事故22.3%、车辆故障17.5%、高峰期40%+）及事故科提出的三点改进建议（加大酒驾打击力度、偏僻路口增加投入、高峰期增加人力辅助）"/>
-            <filter val="2.1：遗漏了关键背景信息&quot;5年测试伪装应届生，面试官质疑是不是应届王&quot;，这是整个面试的核心语境和疑点；2.1：遗漏了候选人&quot;可能我长得有点显老&quot;的回应、视频面试形式（&quot;面试官可以看见到我吗&quot;）；2.1：遗漏了SQL优化中&quot;避免使用不等于号、索引不超过6个&quot;等具体细节；候选人OSI模型回答存在ASR错误但模型未予纠正说明"/>
-            <filter val="2.1 核心遗漏：只写了国际公司作为第二被告，其他被告的身份没有提及&#10;出庭情况没有提及&#10;只有质证，没有提及被质疑的证据具体是什么&#10;4.3 层级逻辑极其混乱：被告没有按照第一被告往下的顺序排列，可读性比较差"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
-    </autofilterInfo>
-  </sheetItem>
-  <sheetItem sheetStid="14">
-    <filterData filterID="AK20210901JXNSXO17933749"/>
-    <autofilterInfo filterID="AK20210901JXNSXO17933749">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N168"/>
-    </autofilterInfo>
-  </sheetItem>
-  <sheetItem sheetStid="16">
-    <filterData filterID="AK20210901JXNSXO17933749"/>
-    <filterData filterID="AK20210901JXNSXO16981454"/>
-    <autofilterInfo filterID="AK20210901JXNSXO16981454">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S168"/>
-    </autofilterInfo>
-    <autofilterInfo filterID="AK20210901JXNSXO17933749">
-      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S168"/>
-    </autofilterInfo>
-  </sheetItem>
-</autofilters>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品对比" sheetId="1" state="visible" r:id="rId1"/>
@@ -93,7 +93,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -120,6 +120,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -467,10 +470,11 @@
     <col width="55.375" customWidth="1" style="5" min="1" max="1"/>
     <col width="56.125" customWidth="1" style="5" min="2" max="2"/>
     <col width="9" customWidth="1" style="5" min="3" max="3"/>
-    <col width="9" customWidth="1" style="4" min="4" max="16384"/>
+    <col width="9" customWidth="1" style="4" min="4" max="4"/>
+    <col width="9" customWidth="1" style="4" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="9">
+    <row r="1" ht="13.5" customHeight="1" s="10">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>文本</t>
@@ -481,23 +485,23 @@
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>纪要</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>消耗时间</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>文本长度</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" s="9">
+    <row r="2" ht="13.5" customHeight="1" s="10">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:21
@@ -568,27 +572,25 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表讲话，围绕多极化世界、国际秩序及热点问题阐述中方立场，提出四点主张：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，多极化是历史必然并正在成为现实，中国主张推动平等有序的世界多极化，中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。王毅还就中欧关系表示，欧洲是多极世界的重要一极，中欧是伙伴而不是对手，今年是中欧建交50周年，中方愿同欧方用好这一契机，深化战略沟通和互利合作。在回答提问时，王毅就联合国与国际秩序规则、乌克兰问题、中美关系分别作出回应。
+2025年慕尼黑安全会议期间，中共中央政治局委员、外交部长王毅发表演讲并接受主持人提问，阐述中国对世界多极化的立场。王毅指出世界走向多极化是历史必然，中国主张推动平等有序的世界多极化，并提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。他强调中国是现行国际秩序的受益者和维护者，愿提供公共产品，并回应了关于国际秩序、乌克兰危机和中美关系等热点问题。整体基调坚定务实，展现中国作为多极体系中确定性因素和建设性力量的定位。
 # 核心信息
-王毅提出四点主张：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，强调联合国宪章宗旨和原则是国际关系根本遵循，国家不论大小强弱都是国际法治利益攸关方，大国要带头讲诚信讲法治，摒弃言行不一、零和博弈，遵守国际法不能搞双重标准，应支持中国实现完全统一；三是践行多边主义，表示联合国是践行多边主义、推进全球治理的核心平台，应固本强基而非拆梁毁柱，中国承担超过**20%**的联合国会费，履行`巴黎协定`，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，指出保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己，应坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化。关键数据：去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**；中国加入了几乎所有普遍性的政府间国际组织和**600多项**国际公约；联合国成立时只有**51个**会员国，今天是**193个**国家。中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接。
+王毅在慕尼黑安全会议上发表演讲，核心信息包括：世界走向多极化是历史必然，中国主张推动平等有序的世界多极化，并提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。关键数据：联合国成立时51个会员国，至今193个国家；中国承担超过**20%**的联合国会费；去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**；中国加入几乎所有普遍性政府间国际组织和**600多项**国际公约；中国建成世界上最大的清洁发电体系。王毅强调中国是现行国际秩序的受益者和维护者，愿提供公共产品，包括全球发展倡议、全球安全倡议、全球文明倡议。
 # 官方表态
-关于多极化：王毅表示，多极化的世界既是历史的必然，也正在成为现实，中国给出的答案是应当推动平等有序的世界多极化，这是习近平主席提出的又一个重大主张。关于国际法治：王毅表示，联合国宪章宗旨和原则是处于国际关系的根本遵循，也是建设多极世界的重要基石，国家不论大小强弱都是国际法治的利益攸关方，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈，在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。关于多边主义：王毅表示，联合国是践行多边主义、推进全球治理的核心平台，对于这座大厦应该固本强基，而不是拆梁毁柱，中国坚持真正的多边主义，倡导共商共建共享的全球治理观。关于开放共赢：王毅表示，保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。关于中欧关系：王毅表示，中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手，今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。关于联合国与国际秩序规则：王毅表示，中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展，需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。关于乌克兰问题：王毅表示，中国同俄罗斯是两大邻国，有着漫长的边界，两国建立了结盟不对抗、不针对第三方的睦邻友好关系，进而建立了全面战略伙伴关系，中国同俄罗斯之间的交往是正常的国与国之间的交往；中国历来主张一切争端和冲突都应该通过对话寻求政治解决，乌克兰问题上同样如此，从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释，任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识，所有当事方包括利益攸关方都应该适时的参与到和谈的进程当中，欧洲更有必要为此发挥重要的作用。关于中美关系：王毅表示，中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢，中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底。
+关于国际秩序与规则：王毅回应称中国是现行国际秩序的受益者，主张维护以联合国为核心的国际体系，遵守联合国宪章宗旨和原则，反对双重标准，推动秩序朝着更加公正合理的方向发展。关于乌克兰危机：王毅表示中国从俄罗斯购买油气是正常贸易，满足民众需求，不可能不买；中国主张通过对话政治解决，提出四点主张，派特使斡旋，发起和平之友，乐见一切致力于和平的努力。关于中美关系：王毅表示中国对美政策保持连续性和稳定性，遵循相互尊重、和平共处、合作共赢三原则，愿构建稳定健康可持续的双边关系，但若美方打压遏制，中方将奉陪到底。
 # Q&amp;A环节
-问（发言者2）：你提到国际秩序，也提到需要尊重联合国宪章，现在有很多质疑，我们看到俄罗斯入侵乌克兰，我们看到美国总统威胁使用武力入侵格陵兰和巴拿马，以及巴勒斯坦人流离失所，你的国家也被指控违反海洋法或世界人权宣言。你现在从这里前往纽约参加安理会，你是否继续相信联合国？你是否相信联合国宪章？你是否也会为联合国改革而努力？联合国宪章在你的优先事项中排多高？ → 答（王毅）：说到秩序，这几年总有人说中国要改变秩序，中国要另起炉灶，但现在再说这种话的人可能不会太多了，因为真正要挑战秩序、在毁约退群的国家出现了；中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展。谈到规则，我们需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则，这应该是我们的最大的公约数。
-问（发言者2）：自2022年以来慕安会的一个话题就是俄罗斯入侵乌克兰，在俄罗斯入侵前几天你曾说过主权、独立和领土完整应该得到尊重和保障，乌克兰也不例外，你确认了联合国宪章。今天俄罗斯已成为中国的加油站，这意味着你对乌克兰有很大影响力。你是否看到现在有更多压力来结束这场战争，你能否减少俄罗斯向你国供应天然气的可能性或降低价格，或停止一些双用途物资，以便对俄罗斯施加更多压力来结束这场战争？ → 答（王毅）：中国同俄罗斯是两大邻国，有着漫长的边界，两国关系过去经历过一番曲折的经历，之后我们双方吸取教训，建立了结盟不对抗、不针对第三方的睦邻友好关系，进而增进了战略互信，建立了全面战略伙伴关系。中国同俄罗斯之间的交往是正常的国与国之间的交往。如果中国不从俄罗斯买油气，哪个国家能够提供如此巨量的油气来满足中国民众的需求呢？那是不可能的，也是不保险的。中国在对待地区热点问题上是有我们的立场的，我们历来主张一切争端和冲突都应该通过对话寻求政治解决，因为武力和制裁不可能真正和彻底的解决问题，乌克兰问题上同样如此。从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决。习近平主席提出的4点主张是中国立场的最权威的阐释。我们派出的特使去各国斡旋，我们同巴西等南方国家发起了和平之友。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识。所有当事方包括利益攸关方，都应该适时的参与到这个和谈的进程当中。这场战事发生在欧洲大地上，欧洲更有必要为此发挥重要的作用。
-问（发言者2）：我们时间不多了，但至少请你简要预览一下你认为我们和中国之间的关系将如何发展？ → 答（王毅）：中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，这体现了作为大国的战略定力和国际信誉。我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢。中国和美国制度确实不一样，这是我们各自人民做出的选择，如果想改造或者颠覆对方的话，那是不切实际的，正确的态度就是相互尊重。中美两个大国总不能冲突起来吧，因为那将殃及整个世界，所以还是要开展对话，加强交往，增进了解，建立信任。合作共赢，这是因为国际社会期待中美开展合作，全球性的挑战也需要中美携手来应对。中方已经准备好了，我们愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。我们当然希望美方能够相向而行，但是如果美方不愿意，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，我们必将坚定的维护中国的主权、中国的国家的尊严和我们的正当发展权利，必将坚决的回击美方的单边和霸凌的这种行径。</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>7004/3331</t>
+问：中国是否遵守国际法和联合国宪章？是否支持联合国改革？答：王毅表示中国是现行国际秩序的受益者，主张维护以联合国为核心的国际体系，遵守联合国宪章宗旨和原则，反对双重标准，愿推动秩序朝着更加公正合理的方向发展。问：中国能否减少从俄罗斯购买油气以施压俄罗斯结束战争？答：王毅表示中国从俄罗斯购买油气是正常贸易，满足民众需求，不可能不买；中国主张通过对话政治解决乌克兰危机，提出四点主张，派特使斡旋，发起和平之友，乐见一切致力于和平的努力。问：中美关系将如何发展？答：王毅表示中国对美政策保持连续性和稳定性，遵循相互尊重、和平共处、合作共赢三原则，愿构建稳定健康可持续的双边关系，但若美方打压遏制，中方将奉陪到底。</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7004/1085</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="9">
+    <row r="3" ht="13.5" customHeight="1" s="10">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 01:35
@@ -751,36 +753,29 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次沟通为电子科学与工程学院面向考生和家长的直播介绍会，由三位老师及学生代表分别介绍学院整体情况与各研究方向，并解答夏令营相关问题。段院介绍学院历史沿革、学科布局、师生规模、科研经费与平台情况；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术和电路与系统方向；李天明教授介绍物理电子学方向；2023级博士研究生田雨桐从学生视角分享择校理由与建议。互动答疑环节，段院回复今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。
+本次宣讲会由电子科学与工程学院主办，面向考生和家长介绍学院整体情况及专业方向。学院历史可追溯至1956年建校时的无线电系，历经4次院系调整，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设5个二级学科方向及3个国防特色学科。学院现有本科生1545人、研究生1975人，教师302人（含两院院士2人、领军人才19人、青年人才28人），近5年科研经费稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，拥有两个国家级平台。各专业方向负责人分别介绍了学科情况：电子信息材料与元器件方向以材料为基础、器件为核心、应用为目标，指出中国2021年集成电路进口额达2.8万亿元（约为原有进口量的1.7倍），先进电子材料元器件是卡脖子问题，研究团队包括邓龙江院士团队（19人）和张怀武教授团队（17人），依托两个国家级平台，科研面积2万余平米，拥有大型设备500余台套，毕业生去向包括英特尔、中芯国际、华为等；电磁场与微波技术学科始于1956年，由林卫干和谢楚芳创建，所属一级学科入选双一流A类，介绍了杨世文、樊勇、李恩、延波等教授团队的研究成果（如四维天线阵列、毫米波平面集成天线、太赫兹雷达成像等），电路与系统学科1981年开始招收研究生，拥有国家级人才4人，连续三年获全国大学生集成电路创新创业大赛奖项；物理电子学是物理学与电子科学技术交叉学科，起源于1956年电子控器件专业，1979年成立高能电子学研究所，2018年并入电子科学与工程学院，团队共9个，每年科研经费接近2亿元，是国际最大真空器件研究中心。博士生田雨桐从学生视角分享了选择电子学院的8个理由，包括成都的产业优势、学校电子信息学科群、电子科学与技术学科评估A+、研究团队实力、奖助体系等，建议学生先选团队再选导师，利用文献检索网站了解导师情况。关于夏令营，段院回应今年计划举办，时间待定，相关信息将通过QQ群发布（群号978499108）。
 # 信息同步
-**段院（学院整体情况）**：介绍学院历史沿革，1956年建校成立无线电系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科；本科生1545人，招生专业为工科试验班电子工程类，含电子科学技术、电磁场与无线技术；硕士博士研究生1975人；教师302人，教师总数269人，两院院士2人、领军人才19人、青年人才28人；近5年科研到账经费稳定在3~4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利授权1300余件；20个科研团队，年度经费过千万团队15个、过亿元团队1个；拥有2个国家级平台、4个国际合作平台、7个省部级科研平台，共建国际姊妹院系2个，主办高水平国际会议13场。
-**柳教授（电子信息材料与元器件方向）**：该方向以材料为基础、器件为核心、应用为目标导向，2021年中国集成电路电子产品进口额度达2.8万元（原文），为原有进口量1.7倍，属卡脖子问题之一，应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域；研究队伍含国家级人才10余人，两个团队——邓龙江院士电磁辐射控制材料与技术团队（研究人员19人，正高13、副高15，论文300余篇，课题130余项，年均到账经费3000多万元，授权发明专利100余项，国家科技进步或技术发明二等奖共3项）和张怀武教授磁电薄膜与微型器件团队（研究人员17人，正高15、副高2，课题100余项，科技进步二等奖共3项，SCI论文400余篇，年均到账经费2000余万元）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室；科研面积2万余平米，超精尖3000平，两条国家重大任务试验生产线，大型设备500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
-**张教授（电磁场与微波技术和电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，始于1956年由林卫干先生和谢楚芳先生创建，有6个团队，拥有中国高校最先进的微波暗室群体及微波毫米波太Hz仿真测试平台；研究成果包括杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵应用于中电14所某大型机载相控阵雷达，樊勇教授团队毫米波平面集成天线、太Hz雷达成像系统（0.22太Hz、0.34太Hz、0.42太Hz，分辨率小于1厘米）并于2023年成都大运会田径项目示范应用，李恩教授团队微波毫米波测量技术、生物医学电磁学及成像，延波教授团队微波毫米波太Hz芯片、三毫米导引头前端等；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，81年招收研究生，88年成立首批博士后流动站，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人，康凯教授团队毫米波CMOS芯片，连续三年获全国大学生集成电路创新创业大赛奖项。
-**李天明教授（物理电子学方向）**：该学科为物理学与电子科学技术交叉学科，典型如微波电子学、光电子学，特点为基础性与前沿性、学科边界不清晰；学校物理电子学起源于1956年建校时前苏联专家帮助下成立的电子控器件专业，1979年刘成刚院士带领下成立高能电子学研究所，2018年成立电子科学与工程学院；经过近70年发展，纵向向上游仿真设计数字模拟材料、下游系统应用发展，横向向毫米波到太赫兹频段及与医学交叉发展；拥有自主知识产权商用软件MMST和切皮克；团队共9个；每年到校科研经费接近2亿元，为学院最多；是世界上最大的真空器件研究中心；2023年成功举办行业内顶级会议；学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-**学生代表田雨桐（择校分享）**：2023级电子科学与技术专业博士研究生，分享选择电子学院的8个理由：城市成都（新一线城市、电子信息产业前端，英特尔华为京东方等汇聚）；电子科大为电子信息人才培育代名词；电子科学与技术学科第四轮学科评估A+全国第一；研究团队实力（所在毫米波技术与系统应用团队由樊勇老师带领，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向，团队硕博毕业生百分百就业率）；奖助体系全覆盖高额度长周期；建议先选研究团队再选导师，借助文献检索网站了解导师。
-**互动答疑**：有考生和家长询问夏令营具体时间和形式，段院回复今年计划举办夏令营活动，时间待定，感兴趣的同学可加入QQ群（群号978499108），相关信息会及时发布；直播尾声进行抽奖，口令为“一生一世，逐梦未来”，奖品为学校马克杯套装。
+**学院整体情况（段院）**：学院历史沿革，1956年建校成立无线电系，历经4次院系调整，2023年成立电子科学与工程学院与集成电路学院。电子科学与技术为国家重点一级学科，下设5个二级学科方向（电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构）及3个国防特色学科（电磁场与微波军用关键材料、电子元器件）。本科生1545人，研究生1975人。教师302人，其中两院院士2人、领军人才19人、青年人才28人。近5年科研经费稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利申请1600余件、授权1300余件。拥有两个国家级平台（国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室）。
+**电子信息材料与元器件方向（柳教授）**：该方向以材料为基础、器件为核心、应用为目标，涉及电子材料与器件设计研制。指出中国是电子产品生产大国但非强国，2021年集成电路进口额达2.8万亿元（约为原有进口量的1.7倍），先进电子材料元器件是卡脖子问题。研究团队包括邓龙江院士团队（19人，正高13人、副高15人）和张怀武教授团队（17人，正高15人、副高2人），依托两个国家级平台（国家电磁辐射控制材料工程技术研究中心、电磁薄膜与集成器件全国重点实验室），科研面积2万余平米，拥有大型设备500余台套。毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
+**电磁场与微波技术和电路与系统方向（张教授）**：电磁场与微波技术包含4个细分方向（微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术），电路与系统包含3个方向（非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统）。电磁场与微波技术学科始于1956年，由林卫干和谢楚芳创建，所属一级学科入选双一流A类。介绍杨世文、樊勇、李恩、延波等教授团队的研究成果，包括四维天线阵列、毫米波平面集成天线、太赫兹雷达成像（0.22THz、0.34THz、0.42THz，分辨率小于1厘米）等。电路与系统学科1981年开始招收研究生，拥有国家级人才4人。人才培养方面连续三年获全国大学生集成电路创新创业大赛奖项。
+**物理电子学方向（李天明教授）**：物理电子学是物理学与电子科学技术交叉学科，典型应用包括微波电子学、光电子学。学校物理电子学起源于1956年电子控器件专业，1979年成立高能电子学研究所，2018年并入电子科学与工程学院。经过近70年发展，内涵不断扩展，纵向发展包括仿真设计、人工智能引入，横向发展包括频段上移和学科交叉。团队共9个，每年科研经费接近2亿元，是国际最大真空器件研究中心。
+**学生视角分享（博士生田雨桐）**：分享选择电子学院的8个理由，包括成都的产业优势、学校电子信息学科群、电子科学与技术学科评估A+、研究团队实力、奖助体系等。建议学生先选团队再选导师，利用文献检索网站了解导师情况。
 # 达成共识
-各方确认的信息：段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍各研究方向，学生代表田雨桐分享择校理由与建议。
-达成的共识：**今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。**
-段院原话：
-&gt; 我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会唉到时会及时的发布。
+各方确认的信息与共识：学院计划今年举办夏令营，时间待定，相关信息将通过QQ群发布（群号978499108）。段院承诺：**感兴趣的同学可加入QQ群，相关信息届时会及时发布**。
 # 待协调事项
-事项：夏令营具体时间和形式尚未确定，需后续明确并发布。
-对接人：未明确
-负责人：段院
-预计完成时间：待定，相关信息通过QQ群（978499108）及时发布。</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>13887/2555</t>
+**夏令营时间与形式**：事项描述：夏令营的具体时间和形式待定，需学院确定后发布。对接人：无。负责人：段院。预计完成时间或后续沟通计划：时间待定，相关信息将通过QQ群（978499108）发布。</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13887/2282</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1" s="9">
+    <row r="4" ht="13.5" customHeight="1" s="10">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:01
@@ -1312,26 +1307,25 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t># 复盘目标与结果概况
-本次复盘会围绕2023年公司发展数据、年终奖发放标准、各部门与个人评价及颁奖抽奖展开。预期目标是通报全年经营状况并明确年终奖发放口径，实际结果是年终奖转账总额226,000元，人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27；最高工资含年终奖两三人拿到手20万多，平均到手1万多；2023年平均人工支出相对提高，平时工资提高约25万，年终奖比去年多1312万多；干满一年从去年四五人到今年12人；公司总量提升但成本往上跑，结余到账往下跑，还有百来万没收回来；老板每人比去年少拿约10万，承担亏100万风险。老板称成本控制非常差，是最大的癌症、根源问题，归因于老板关心关注不够、不够雷厉风行、出现问题没及时解决，成本控制问题明年开会时再说。年终奖发放标准为：入职两三个月或半年以内发红包，去年600、800，今年可能1000左右；满一年以一个月基本工资为基准，无大披露无大问题会更高；超过一年不过多考虑年限，看当年表现；干得久又非常满意的有高预算，实际拿到可能两三万，预算可给大几万但需给理由。部门评价方面，对短视频部门整体满意并认可，明年期待账号开始变现；对执行部门表示认可，今年项目没做砸过；商务部门从结果看基本达到预期，整个部门拿到的活约300万左右。颁奖共6人5项奖，最佳新人奖颁给红叶子和张扬，最佳进步奖颁给欧阳小元，最佳员工奖颁给游腾宇，特别贡献奖颁给李海腾。
-# 亮点事项
-短视频账号运营超出预期：视频号从3月1日700多粉涨到8万，小红书2000加涨到6.4万，抖音2000加涨到5.7万，B站3.1万涨到7.6万，6月20日外出拍摄视频后起色；直播在视频号4、5场，平均在线5000人加，前100人平均在线50分钟以上。促成成功的关键动作是郭东辉在6月20日前潘老师多次提醒其出去找工作、项目不想干了的情况下坚持不放弃，并破釜沉舟说服潘老师到外面去拍摄，加上forty到来后继续坚持；其所有内容决策均有数据支撑，晚上8:00~9:00抽一小时刷侃哥、巧克力、克瑞斯金等英语老师直播间，研究内容与互动。**最具复用价值的经验是：面对项目可能被放弃时，先说服自己坚持，再以数据支撑内容决策，并找到破壳的点逐个击破。** 个人评价方面，刘腾宇职业性专业性纪律性最好，年终奖在既定标准上再拉一档，可能翻倍；张文倩表现高出老板期待，宁波等难活也完成了；宋俊逸第一次安排活即效率不错，监狱、财经等项目未出问题；张扬基本达到期待，老板认为2023年干到最有价值的一件事就是把他招进来；张启表现高于预期，有主观能动性，主动联系客户打电话。
-# 不足事项
-成本控制非常差 → 根因是老板关心关注不够、不够雷厉风行、出现问题没及时解决，是最大的癌症、根源问题；若今年没有增量、成本控制又是今年状况就不开这个会。公司结余到账往下跑，还有百来万没收回来，稍微缩水；老板每人比去年少拿约10万，承担亏100万风险。郭东辉克服本不应面对的困难，公司限制其发挥，应表示歉意；6月20日前潘老师多次提醒郭东辉出去找工作，项目不想干了；账号目前没有变现，直播现在没有课程无法变现；郭东辉一人负责多个平台，精力不充沛。张文倩在法院项目上与同学沟通吃力，对方踢皮球，不知道标准怎么做。钱德峰后半年拍摄密集，两个月连轴转没有一天休息。外援成本高，公司内部可搞定的简单机位却凑不出人。后期人员加班严重，后半年基本都在加班，很少正常休息；人不够是加班最大的因素，是老板判断失误。商务给活断断续续，造成不需要招这么多人的错觉。张启项目少，老板给的支持比较少；张启自评2023年没达到自己预期，效率、时间、项目沟通和甲方做得不太好。
-# 改进计划
-成本控制问题明年开会时再说，责任人无，时间明年开会。短视频部门明年期待账号开始变现，老板会投入更大精力，责任人老板，时间明年。执行部门明年期待老板更多组织协调、减少侵占休息时间，责任人老板，时间明年。商务部门明年会给予更多支持和帮助，责任人老板，时间明年。张扬的具体问题明年再说，责任人无，时间明年。李国宇的具体问题明年再说，责任人无，时间明年。徐艺玲更高的期待明年再说，责任人无，时间明年。年终奖具体数额不公布，以发到手的为准，责任人无，时间无。</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>24562/1759</t>
+          <t># 年终总结与表彰大会
+年终总结与表彰大会
+会议要点：公司召开年终总结会，老板公布年度经营数据：年终奖总额226,000元，成本控制差，支出390万，利润率24%或27%，最高工资20万，平均工资1万多，2023年总量提升但结余缩水，有百来万未收回。年终奖发放标准为：入职不满半年发红包约1000元，满一年以一个月基本工资为基准，超过一年考虑年度表现，个人数额不公布。；老板逐一点评员工，肯定优点并提出期待，短视频部门满意，期待变现；执行部门认可辛苦，期待老板更多组织协调；商务部门基本达标，实打实项目约300万，期待更多支持。；颁发最佳新人奖给红叶子和张扬，最佳进步奖给欧阳小元，后期独当一面奖给刘腾宇，最佳员工奖给游腾宇，特别贡献奖给李海腾，随后抽奖结束。
+关键决策：年终奖总额226,000元，个人数额不公布。；年终奖发放标准：入职不满半年发红包约1000元，满一年以一个月基本工资为基准，超过一年考虑年度表现。；颁发最佳新人奖给红叶子和张扬，最佳进步奖给欧阳小元，后期独当一面奖给刘腾宇，最佳员工奖给游腾宇，特别贡献奖给李海腾。；抽奖奖品包括一等奖、二等奖、三等奖等，现场发放。
+风险与阻塞：成本控制非常差，利润率低。；公司结余缩水，有百来万未收回。；加班严重，人员不足。；外援成本高，内部人员参与拍摄不足。
+未决问题：明年成本控制问题待开会讨论。；明年年终奖额度待定。；账号变现的具体计划未明确。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24562/612</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="9">
+    <row r="5" ht="13.5" customHeight="1" s="10">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:10
@@ -1870,24 +1864,24 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕小区物业服务缺失、业主大会召开与业委会成立、物业费欠费及双方拟走法律程序等矛盾进行协调。业主方称已有200来户业主接龙要求召开业主大会，业委会工作组有6个群、准业主分5个群，最早业主群已建5、6年，建议尽快召开业主大会由全体业主表决；物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主代表列举11项服务缺失问题，包括入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏且上个月进贼未获数据、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重、北边围墙用烂铁皮挡着且有缺口不安全、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员从办公室近10人减至4人、维修从5人减至2人。物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。
-## 业主大会召开与业委会成立
-- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早业主群已建5、6年。业主方建议尽快召开业主大会由全体业主表决，物业方称未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
-- 业主代表列举11项服务缺失问题：入户庭院门柱灯从未开启；内部水系从未开启；售楼处门口迎宾水系从未开启；监控几乎全部损坏，上个月进贼未获数据；监控室24小时值班及一键直达服务自王艳芳上任后荒废；绿化死亡严重，物业管家称等明年发芽；北边围墙用烂铁皮挡着，有缺口不安全，物业承诺定制围挡未兑现；快递柜、直饮水机、宽带、暖气开户等民生附属问题无进展；雨水倒灌自2019年造成财产损失未解决；物业人员配备严重不足，办公室从近10人减至4人，维修从5人减至2人。
-## 物业方回应与经营困难
-- 物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题，属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>21511/1505</t>
+本次会议为小区业委会与物业就长期服务问题（门柱灯、水系、监控、绿化、围墙、雨水倒灌、物业人员配备不足等）进行协调的专项讨论会。业委会列举了小区存在的11项问题，要求召开业主大会表决是否更换物业；物业方逐条回应，称部分属地产责任、费用不足或红线外问题，双方未达成一致。物业方宣布已与高级人民法院、滨城区人民法院沟通，将于本月起诉业委会，并称诉讼期间业主大会无法召开；业委会表示将反诉，并计划集体起诉物业要求返还部分物业费。双方就物业费欠费与服务顺序争执不下，会议未达成实质和解。
+## 业主大会召开与物业去留
+- 业委会成员提出小区存在11项问题，要求召开业主大会表决是否更换物业；物业方表示已与集团法务沟通，将于本月起诉业委会，并称诉讼期间业主大会无法召开；双方就物业费欠费、服务缺失等问题激烈争论，未达成一致。
+- 业委会成员列举了门柱灯不亮、水系从未开启、监控损坏、监控室无人值班、绿化死亡、北围墙缺失、民生配套未解决、雨水倒灌、物业人员配备不足等10条问题；物业方逐条回应，称部分属地产责任、费用不足或红线外问题。
+## 物业费欠费与法律诉讼
+- 物业方称业主欠费170多万，公司连年亏损，人工成本超100万，无力承担维修费用；业委会认为物业服务不应以先收费为前提，双方就缴费与服务顺序争执不下。物业方宣布已与高级人民法院、滨城区人民法院沟通，将于本月起诉业委会；业委会表示将反诉，并计划集体起诉物业要求返还部分物业费。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21511/620</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="9">
+    <row r="6" ht="13.5" customHeight="1" s="10">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 02:06
@@ -2131,26 +2125,23 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t># 研讨背景与议题
-本次圆桌由主持人（多模态大模型与具身智能融合方向）主持，参与讨论的包括于洋老师的博士生雄辉（强化学习）、卢策吾老师的博士生薛寒（数据收集与柔性物体操作）、于洋老师的博士生志龙（具身模型与世界模型）以及赵浩、王岳等老师。研讨围绕具身智能的模型形态、硬件期待、世界模型定义、模仿与强化学习路线及数据scaling五个议题展开。核心痛点在于：具身智能究竟收敛为统一端到端模型还是分层形态、硬件如何支撑真机evaluation的scale up、世界模型是否需要3D inductive bias、模仿学习与强化学习如何取舍，以及真机数据与仿真数据如何配比。
-# 核心观点
-模型形态议题：主持人提出大脑大模型、小脑大模型、端到端模型等形态，并以派灵收集6000多小时数据训出端到端模型为例，询问是统一模型还是前段固定加Action refiner；王岳认为大模型直通底层会消除硬件迭代可能性，至少应分上下层，大脑不变、小脑适应肢体；发言者6认为当前大模型不是终极形态，世界模型可能更接近人脑水平，但也不是最终形态。硬件形态议题：发言者3从机械与传感器角度反问具身身体会收敛成人形还是非人形，并提到机械智能、软手抓取；薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up，现有工业机械臂并非为此设计，需要柔顺硬件结构；主持人认为具身是软硬件协同优化范式，以松龄二代和凝胶夹爪为例，认为协同进化；发言者6认为人形机器人和特种机器人将来都会存在，特斯拉花一半精力做22自由度灵巧手。世界模型议题：主持人介绍赵浩从computer vision角度评价世界模型，涉及是否需重构所有pixel和3D，并提到4D world model投稿；志龙从强化学习角度认为世界模型第一要素是可交互，回溯到Dyna Q和杨乐坤的表征与转移，当前世界模型物理规律欠缺明显；赵浩认为CV界追求重建物理世界动态，可作为RL世界模型的工具，但三维计算机视觉技术栈长，RL博士生难完全学习，并讨论inductive bias随数据规模变化；王岳以游戏跳楼例子认为世界模型可能做不到统一，policy可能是一个；发言者9提出不同物理结构可能有统一表征，讨论condition与M个模型复杂度。策略学习路线议题：主持人提出强化学习与模仿学习两大流派，派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈，语言模型有RLHF和o1思维链、MCTS；发言者10介绍公司采用模型强化加机理融合，监督学习动作空间大、数据分布不足，强化学习强依赖仿真环境、sim-to-real迁移难，需限定决策空间和任务分层；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化都不行；王岳认为pid有反馈就可作为reward，强化必然走得成；发言者11认为IL和RL没有本质冲突，只是想要一个latent状态。数据采集与scaling议题：主持人请杨立新和薛寒分享真机数据收集经验，赵浩和主持人代表仿真生成数据流派；杨立新强调视角控制和标定重要，open X等数据集相机视角不固定，且缺少物体运动信息，其团队采集刚体和关节体；薛寒all in真机采集，认为柔性体仿真需先进图形学技术如IPC、算力要求高、人才少，真机数据是更低成本方案，终极形态可能是脑机接口或可穿戴设备无感采集，互联网视频与机器人所需数据差异大；主持人提到ego4d数据清洗三个月，仿真数据加少量真机数据可显著提升成功率；赵浩认为真实还是仿真看成本，提出2025年应推广大规模利用无标注真实数据，国产仿真系统是产业问题。
-# 达成共识与解决方案
-研讨未形成正式决议，但各方在以下认知上趋于一致：**具身智能是软硬件协同优化的范式**，硬件需具备高寿命、高可靠性与柔顺结构以支撑真机evaluation的scale up；**模型形态至少应分上下层**，大脑保持稳定、小脑适应肢体与硬件变化，而非单一端到端直通底层；**世界模型与强化学习的关系上**，CV界重建物理世界动态的成果可作为RL世界模型的工具，但RL更关注可交互性与策略学习；**策略学习路线上**，复杂任务宜先模仿后强化，单独模仿或单独强化均难以覆盖，混合多种方式是目前较实际的解；**数据路线上**，真机数据与仿真数据并非相斥，仿真数据加少量真机数据可显著提升成功率，真实还是仿真应case by case看成本。
-# 未决分歧与后续探索
-未决分歧包括：具身智能最终会收敛成统一端到端模型，还是前段固定加Action refiner的分层形态；具身的身体会收敛成人形机器人还是非人形形态；世界模型是否需要3D inductive bias，还是由数据规模决定；世界模型最终是一个还是多个，policy是否可能统一；模仿学习和强化学习最终路线是单独一种还是混合；未来是否强依赖英伟达生态，还是会有国产仿真产品支持。后续探索方向包括：赵浩提出2025年应推广大规模利用无标注真实数据；薛寒提出可穿戴式设备或脑机接口作为无感采集的终极形态；主持人提出仿真数据与少量真机数据结合的训练方法；国产仿真系统作为产业问题需business by business讨论。</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>21458/2146</t>
+          <t># 具身智能圆桌论坛：技术路线与数据策略探讨
+具身智能圆桌论坛：技术路线与数据策略探讨
+会议要点：本次圆桌论坛围绕具身智能领域的关键技术问题展开，重点讨论了大模型与硬件协同、世界模型定义、强化学习与模仿学习路线、数据采集与仿真等议题。关于大模型是否端到端，王岳认为不应从上到下完全贯通，硬件变化会导致重新训练，应分层；薛寒提出硬件需高寿命、高可靠性以支持大规模真机评估；穆老师强调软硬件协同优化。关于世界模型，赵浩从CV角度强调3D、物理规律、可交互，志龙从RL角度认为可交互是首要，王岳提出世界模型可能无法统一，存在歧义问题，policy可能统一，薛寒认为CV世界模型对强化任务不必要。；关于强化学习与模仿学习，业界嘉宾介绍其公司采用模型强化加机理融合的方式，薛寒认为复杂任务应先模仿后强化，单独模仿或强化都不行，王岳认为PID反馈可作为reward，静波认为两者不冲突，可获取运动先验。关于数据采集与仿真，杨立新强调视角和标定对数据质量的影响，薛寒认为真机数据是低成本方案，可穿戴设备是终极形态，穆老师认为仿真数据可弥补真机数据不足，赵浩提出加入无标注真实数据。赵浩还提到梦想写一篇关于data bias trade off的论文，并认为2025年应推广大规模利用无标注数据。
+未决问题：具身智能大模型是否应端到端？；世界模型是否需要3D inductive bias？；强化学习与模仿学习最终路线如何？；仿真数据与真实数据比例如何？
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21458/628</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1" s="9">
+    <row r="7" ht="13.5" customHeight="1" s="10">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:10
@@ -2645,37 +2636,29 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系国家开发银行（上诉人）与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司（被上诉人）金融借款合同纠纷二审，国开行不服云南省高级人民法院2018云民初88号民事判决向本院提起上诉。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。经核对，各方出庭人员身份均符合法律规定，东源煤电、东源煤业、曲靖电力三方委托共同诉讼代理人合并发表意见，各方确认已收到诉讼文书及开庭传票。庭审围绕三个争议焦点调查辩论：抵押权与融资租赁所有权冲突及善意取得、罚息复利计算及起算日期、东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案，各方均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，国家开发银行不服云南省高级人民法院（2018）云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，于2019年公开开庭审理。庭审围绕三个争议焦点展开：国开行抵押权是否构成善意取得、罚息复利计算及起算日期、违约金承担。经合议庭组织调解，各方当事人自愿达成调解协议，法院予以确认并出具调解书。
 # 原告诉称与被告辩称
-国开行主张其抵押权完整无瑕疵，已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，尽到审慎义务构成善意取得；招银租赁主张国开行未在抵押时点查询融资租赁登记，不构成善意，东源煤电出资系无权处分，招银租赁2012年已取得设备所有权。
+各方当事人对调解方案均无异议，同意签署调解协议。确定国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元。确定招银租赁对涉案6项设备享有所有权，国开行对93项设备有抵押权。招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用各担50%。本案调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序。若司法变现不能，国开行和招银租赁权益通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营。案涉设备上的管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置。一审诉讼费用中对于国开行诉请部分按一审判决执行，对于招银租赁诉请部分由二审法院按规定计算后由国开行承担。二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%。本协议签订后，各方之间就本案涉及的问题不再存在任何争议。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利及违约金 | 已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，已尽审慎义务；利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源煤电东源煤业应按借款合同第24条第3项支付千分之一违约金 |
-| 被上诉人东源煤电、东源煤业、曲靖电力 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意；罚息不应作为复利计算基数；不应连带给付违约金 | 招银租赁2012年已取得设备所有权，东源煤电出资系无权处分；2018年6月13日宣布提前到期未给合理期限；复利再计算复利无合同依据；国开行未举证证明违约行为且未按合同约定先行限期纠正 |
-| 被上诉人招银租赁 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意 | 国开行应提供2015年12月操作抵押时点在人行征信中心的查询结果；东源煤电出资系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得设备所有权 |
+| 上诉人（原审原告） | 请求撤销一审判决，改判支持其抵押权、罚息复利及违约金主张 | 已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，审查义务仅限于抵押人曲靖电力公司，构成善意取得；利息计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；东源煤电、东源煤业违约，应支付违约金，依据合同第24条第3项 |
+| 被上诉人（原审被告） | 请求驳回上诉，维持原判 | 2015年12月2日邮件已告知设备情况，且用红色标注，国开行应尽注意义务；国开行宣布贷款提前到期未给合理期限，罚息不应计收复利，复利不应再计复利；国开行未举证证明违约，且未按合同约定先行限期纠正 |
 # 举证与法庭调查
-**一、举证与质证**
-国开行提交2018年9月对曲靖电力公司的融资租赁查询证书、证据第54页和第58页东源煤电公司曲靖电力公司对设备权属的证明材料和股东会决议、证据第108页核查表；招银租赁提交2015年12月2日邮件及东源公司融资情况统计表、回租设备清单（证据第7页）、2013年和2015年审计报告（证据第82页、第95页）。
-**二、法官询问要点**
-合议庭就中国人民银行征信中心融资租赁登记的性质及法律后果、融资租赁登记系统查询方式、案涉5套设备是否登记唯一识别码、国开行贷款前风控是否要求保留查询记录、融资租赁司法解释第9条第2款举证责任分担、不同登记机构信息冲突如何处理等问题进行询问。
-**三、双方辩论的争议焦点**
-1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已按央行规定查询融资租赁系统且无记录、设备为通用设备无唯一标识码、构成善意取得；招银租赁主张国开行未在抵押时点查询、不构成善意、东源煤电出资系无权处分、其2012年已取得设备所有权。
-2. 罚息复利计算及起算日期：国开行主张利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源方主张2018年6月13日宣布提前到期未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
-3. 东源煤电东源煤业是否应连带给付违约金：国开行主张按借款合同第24条第3项支付千分之一违约金、东源方未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约行为且未按合同约定先行限期纠正。
+本案系国家开发银行与东源煤电、东源煤业、曲靖电力、招银租赁金融借款合同纠纷二审，围绕三个争议焦点展开：国开行抵押权是否善意取得、罚息复利计算、违约金承担。经调解，各方达成一致，确认债权数额及设备处置方案。国开行主张已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备有融资租赁登记，且设备为通用设备无唯一标识码，审查义务仅限于抵押人曲靖电力公司，构成善意取得。东源煤电反驳称2015年12月2日邮件已告知设备情况，且用红色标注，国开行应尽注意义务。招银租赁认为国开行未在抵押时点查询，不构成善意，且东源煤电出资行为系无权处分。合议庭询问融资租赁登记性质、查询方式、举证责任等，各方意见不一。国开行主张利息计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算，并给出具体金额。东源煤电认为国开行宣布贷款提前到期未给合理期限，且罚息不应计收复利，复利不应再计复利。招银租赁表示非合同当事人，尊重合议庭审查。国开行主张东源煤电、东源煤业违约，应支付违约金，依据合同第24条第3项。东源煤电反驳称国开行未举证证明违约，且未按合同约定先行限期纠正。招银租赁表示非合同当事人，尊重合议庭审查。
 # 庭审结果
-合议庭归纳三个争议焦点：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息复利计算及起算日期；三是东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案：国开行对东源煤电债权利息罚息复利共计6474.4513万元；确认招银租赁对涉案6项设备享有所有权、对应债权数额1377.4137万元，确认国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置程序，变现价款双方各得50%、实现费用双方各担50%；未实现债权按破产重整计划预留方案实现；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；各方对一审判决第2项第4项无争议按其判项内容在调解书中确认；一审诉讼费用中国开行诉请部分按一审判决执行、招银租赁诉请部分诉讼费用由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%；本协议签订后各方就本案涉及问题不再存在任何争议。各方对调解方案均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>28485/2240</t>
+本案经调解，各方当事人自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：确定国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元；确定招银租赁对涉案6项设备享有所有权，国开行对93项设备有抵押权；招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用各担50%；本案调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序；若司法变现不能，国开行和招银租赁权益通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营；案涉设备上的管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置；一审诉讼费用中对于国开行诉请部分按一审判决执行，对于招银租赁诉请部分由二审法院按规定计算后由国开行承担；二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%；本协议签订后，各方之间就本案涉及的问题不再存在任何争议。</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28485/1976</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="9">
+    <row r="8" ht="13.5" customHeight="1" s="10">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:11
@@ -2828,80 +2811,39 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18号19号提前介入前期摸排，20号召开首次会议，分内业检查和外业检查，按建筑工程、安装工程、机电设备专业方向开展。截止今天已完成卢萨卡点除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收工作，姆皮卡点现场验收工作尚未开展；因带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。内业方面，管理组技术组基本能够按照项目合同从开工到过程中组建项目执行团队并按流程程序开展工作，受疫情及项目特殊情况影响主要人员基本能保证在前方岗位，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求，但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。外业方面，建筑部分原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准，因资料完整整理结果没出来今天不下最后结论；安装部分以钢结构为主，所有材料从国内定制发货到现场，设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。财务验收专家对本项目财务资料进行查阅并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准；不可预见费方面，检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+原占比二玉米面加工厂项目中期验收会议于近期召开，验收组已完成卢萨卡点除带料调试外的所有验收工作，蒙泽点已全部完成并顺带完成带料调试流程试生产，姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展。内业检查涵盖人员履约、程序性文件、过程性检查文件等，基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善。外业检查分建筑、安装、设备三部分：建筑部分整体品质良好，但存在局部损伤、排水需清理、混凝土路面开裂等问题；安装部分结构无问题，但监控管线接头脱落；设备部分运行正常，产能符合设计指标。验收组提出人员履约、内业资料、现场整改等要求，管理组田组长表示会后与技术组细化检查并制定方案处理，技术组龚总汇报三点整改计划。合作局领导强调资料补充沟通、路面开裂原因分析及整改闭环、成品保护；公司林总强调按合同标准仔细验收、提醒当地用户建议、注意交通安全和防疫。验收组发现项目有动用不可预见费情况，需完善依据证据和数据，后续将专门对接。
 # 进度追踪
-各模块进展如下：
-- **卢萨卡点验收**：已完成除弹料加工调试以外的所有验收工作。
-- **蒙泽点验收**：已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程。
-- **姆皮卡点验收**：现场验收工作尚未开展，内业资料已提前拿到卢萨卡点。
-- **内业资料**：管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，验收组查阅资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。
-- **建筑部分**：原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论。
-- **安装部分**：钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底。
-- **机电设备**：验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。
-- **财务**：财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。
-- **不可预见费**：检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+验收工作总体进展：卢萨卡点除带料调试外所有验收工作已完成，蒙泽点已全部完成并顺带完成带料调试流程试生产，姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展。内业检查：人员履约、程序性文件、过程性检查文件基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善。外业检查：建筑部分整体品质良好，但存在局部损伤、排水需清理、混凝土路面开裂等问题；安装部分结构无问题，但监控管线接头脱落；设备部分运行正常，产能符合设计指标。
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程 | ✅已完成 |
-| 姆皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | ⛔阻塞 |
-| 内业资料 | 管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，基本评价为满足项目有关标准和规范要求；分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善 | 🔄进行中 |
-| 建筑部分 | 原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论 | 🔄进行中 |
-| 安装部分 | 钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底 | 🔄进行中 |
-| 机电设备 | 验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准 | ✅已完成 |
-| 财务 | 财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准 | ✅已完成 |
-| 不可预见费 | 检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接 | 🔄进行中 |
+| 验收工作总体进展 | 卢萨卡点除带料调试外所有验收工作已完成，蒙泽点已全部完成并顺带完成带料调试流程试生产，姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展 | 🔄进行中 |
+| 内业检查 | 人员履约、程序性文件、过程性检查文件基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善 | 🔄进行中 |
+| 外业检查-建筑 | 整体品质良好，但存在局部损伤、排水需清理、混凝土路面开裂等问题 | 🔄进行中 |
+| 外业检查-安装 | 结构无问题，但监控管线接头脱落 | 🔄进行中 |
+| 外业检查-设备 | 运行正常，产能符合设计指标 | ✅已完成 |
 # 风险预警
-整体健康度：🟡低风险。主要风险与瓶颈如下：
-- 人员履约方面，个别同志进出场时间以及护照还需施工部和管理组进一步完善，个别岗位人员因各种原因有申请更换流程，个别特种人员证件有效期可能因出国后国内延期或更新未及时到位。
-- 人员统计数量尤其是技术组对厂家服务人员可能没有计算进去，投标和合同文件对数量有要求。
-- 内业资料分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散。
-- 某厂区非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，若移交外方投入使用后再出现大面积开裂，对外影响不太好。
-- 监控管线因设备启动震动，管线接头处有脱落。
-- 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌。
-- 卢萨卡点廊墙最端头横向分布只有三个竖条，可能影响巡检和维护人员安全保障。
-- 不可预见费使用有关依据证据和数据还需进一步完善，必须做到充分无误。
-- 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方。
-- 赞比亚雨季路况不好，去姆皮卡路途遥远，交通安全风险；新冠疫情防控风险。
+混凝土路面开裂可能影响项目移交后使用，存在大面积开裂隐患，等级中，责任人为管理组和总包单位，应对计划为分析原因并制定科学合理的整改方案，在出报告前完成整改并形成闭环。监控管线接头脱落可能引起机械故障，等级低，责任人为施工组，应对计划为全面检查并保证有效性和安全性。雨季来临，厂区排水可能阻塞，需清理排查，等级低，责任人为施工方，应对计划为做最后的清理和排查工作。姆皮卡点路途遥远，路况不好，存在交通安全风险，等级中，责任人为验收组，应对计划为注意交通安全和防疫。疫情及雨季可能影响验收工作，等级中，责任人为验收组，应对计划为做好防控并合理安排行程。
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 人员履约：个别同志进出场时间以及护照资料需完善，个别岗位人员有更换申请流程 | 🟡低风险 | 影响验收报告闭合条件 | 管理组、技术组 | 在形成验收报告之前完善进出场时间及护照资料，达到闭合条件 |
-| 人员统计数量尤其是技术组对厂家服务人员可能未计入 | 🟡低风险 | 投标和合同文件对数量有要求，影响履约统计 | 技术组 | 完善人员统计，将厂家服务人员等EPC项目团队人员计入 |
-| 个别特种人员证件有效期可能因出国后国内延期或更新未及时到位 | 🟡低风险 | 影响人员履约合规性 | 执行单位 | 与国内人力资源对接，确认延期或更新情况并完善 |
-| 内业资料分类整理及少量质检和管理机构验收签字规范性不足 | 🟡低风险 | 影响竣工文件组卷成册 | 执行单位、技术组 | 按项目执行有关标准和规范及国家有关规范，及时汇总卢萨卡、分类成册、按竣工文件归档要求组卷 |
-| 竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散 | 🟡低风险 | 影响资料集中归档进度 | 执行单位 | 抓紧将三个厂区资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码 |
-| 某厂区非主要通道范围内混凝土路面有少量开裂现象 | 🔴高风险 | 若移交外方投入使用后再出现大面积开裂，对外影响不太好 | 管理组、总包单位 | 共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，在末次会之前、最迟出报告之前完成整改，验收组复核形成闭环 |
-| 监控管线因设备启动震动，管线接头处有脱落 | 🟡低风险 | 影响监控有效性和安全性，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌 | 🟡低风险 | 影响设备运行与成品保护 | 施工组 | 检查并考虑增加覆盖面积或通过技术措施解决 |
-| 卢萨卡点廊墙最端头横向分布只有三个竖条 | 🟢正常 | 可能影响巡检和维护人员安全保障 | 施工组 | 建议中间加两个竖条，从视觉上更安全，为巡检和维护人员提供安全保障 |
-| 不可预见费使用有关依据证据和数据还需进一步完善 | 🟡低风险 | 影响费用动用合规性与验收报告表述 | 验收组、施工单位 | 后续利用时间做专门对接，确保依据证据和数据充分无误 |
-| 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方 | 🟡低风险 | 影响交付前成品状态 | 管理组、总包单位 | 交给外方之前继续做好成品保护，破损地方及时修补 |
-| 赞比亚雨季路况不好，去姆皮卡路途遥远 | 🟡低风险 | 交通安全风险 | 验收组 | 注意交通安全，争取安安全全平平安安完成任务 |
-| 新冠疫情防控风险 | 🟡低风险 | 影响人员健康与验收进度 | 验收组、参建单位 | 注意新冠疫情防控 |
+| 混凝土路面开裂 | 中 | 可能影响项目移交后使用，存在大面积开裂隐患 | 管理组和总包单位 | 分析原因并制定科学合理的整改方案，在出报告前完成整改并形成闭环 |
+| 监控管线接头脱落 | 低 | 可能引起机械故障 | 施工组 | 全面检查并保证有效性和安全性 |
+| 雨季排水阻塞 | 低 | 厂区排水可能阻塞，需清理排查 | 施工方 | 做最后的清理和排查工作 |
+| 姆皮卡点交通安全 | 中 | 路途遥远，路况不好，存在交通安全风险 | 验收组 | 注意交通安全和防疫 |
+| 疫情及雨季影响 | 中 | 可能影响验收工作 | 验收组 | 做好防控并合理安排行程 |
 # 后续计划
-下一周期核心交付物与关键时间节点如下：
-- **在末次会之前、最迟在出报告之前完成混凝土路面开裂整改**，由管理组和总包单位共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，整改完成后由验收组进行复核，在报告中形成闭环。
-- **在验收完成第一时间将三个厂区资料全部汇总于卢萨卡**，包括竣工图进行分类汇总、分类组卷及编码，由技术组按验收组专家要求及援外项目执行手册管理办法规定执行。
-- **在形成验收报告之前完善个别同志进出场时间以及护照资料**，达到闭合条件，由管理组和技术组负责。
-- **与国内人力资源对接完善个别特种人员证件有效期延期或更新问题**，由执行单位负责。
-- **全面检查监控管线接头脱落问题**，保证有效性和安全性，由施工组负责。
-- **检查卢萨卡点加工提升桶往上位置雨水倒灌问题**，考虑增加覆盖面积或通过技术措施解决。
-- **建议卢萨卡点廊墙最端头中间加两个竖条**，为巡检和维护人员提供安全保障。
-- **交给外方之前继续做好成品保护**，破损地方及时修补。
-- 会后及时安排接下来的工作情况，通过适当渠道向后方的领导汇报整个工作进展情况。
-*依赖前提：姆皮卡点现场验收工作尚未开展，需在会后安排并注意雨季路况与交通安全；不可预见费有关依据证据和数据需进一步完善，后续专门对接。*</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>11110/4902</t>
+下一周期核心交付物包括：**完成姆皮卡点现场验收**，**完成三个厂区资料汇总至卢萨卡并分类组卷编码**，**完成现场实体整改并形成闭环**。验收标准为满足项目合同及援外项目执行手册管理办法规定，验收组复核确认。关键时间节点为路面开裂问题在出报告前完成整改，验收组复核；资料汇总在验收完成后第一时间完成。存在依赖前提或外部假设的计划：*姆皮卡点现场验收依赖交通和天气条件，需注意安全*；*不可预见费使用依据证据和数据需完善，待专门对接*。</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11110/1880</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="9">
+    <row r="9" ht="13.5" customHeight="1" s="10">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:02
@@ -3108,25 +3050,25 @@
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-本次中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性三大宏观热点展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就反内卷与光伏、人形机器人、游戏板块进行行业更新。会议核心信息包括：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年。整体基调为：大美丽法案对信用周期中长期有利但三季度有流动性波折，美股美债波动提供再配置机会、不悲观；关税大概率是谈判技巧、市场逐渐脱敏；港股三季度流动性边际收紧、指数在23000~24000区间震荡；反内卷政策有望夯实光伏行业底部；人形机器人三季度是二季度迷茫期到商业兑现的过渡阶段；游戏板块在消费、政策和新品周期三重利好下有望在调整后再次实现戴维斯双击。
+本次中金宏观策略周会由中金公司策略组主办，策略分析师刘刚凯文主持，围绕大美丽法案、关税更新、港股流动性、光伏反内卷、人形机器人及游戏板块等热点议题展开。会议核心信息包括：大美丽法案提高债务上限5万亿美元、延长减税并取消899条款，对美股美债中长期有利但三季度存在流动性波折；关税大概率作为谈判技巧，有效税率维持10-12%水平；港股流动性边际收紧但基本面可盖过影响；光伏反内卷政策升级，硅料整合最迫切；人形机器人三季度关注华为云生态、本土企业技术闭环及特斯拉硬件替代三条主线；游戏板块在政策、消费、新品周期三重利好下有望实现戴维斯双击。整体基调偏积极，建议投资者在合适位置布局长期正确板块。
 # 核心信息
-大美丽法案三大块：第一，解决债务上限，提高约**5万亿美元**，违约风险消除；第二，延长2017年减税，新增支出**3.4万亿**、一年**3400亿**，同时减掉其他支出**1.4万**（包括减少对新能源补贴）；第三，取消899条款，避免对海外投资者持有美债利息征税。关税收入每年**3000~4000亿**可对冲支出，赤字率基本维持**5~6%**。7~9月发债约**1万亿**带来流动性抽水，2023年三季度曾发1万亿债推高美债利率从**3.8~5%**、美元走强、美股小幅下跌**4~5%**。关税四点信息：一定会做以支撑收入、需维持**10~12%**有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到**18%**，通胀年底抬升至**3.3~3.4%**但不改变路径。光伏2025年需求**650~700GW**，电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**，产业链价格跌**70~90%**；反内卷政策级别提升：2月国常会、6月29日起人民日报发声、7月1日中财委第六次会议、7月3日工信部座谈会；多晶硅期货反弹至**40元/公斤**、硅片报价涨**10%**、电池涨**2分**。人形机器人二季度A股板块跌约**9%**、跑输机械**12个百分点**，特斯拉供应商回调**30~40%**；智元机器人收购上市、宇树科技年收入破**10亿**、两家中标中国移动**1.2亿**订单。游戏6月单月版号**158个**创2018年以来新高，1~5月游戏市场规模同比增长**17%**多、手游增长**20%**，吉比特《仗剑传说》首月流水**2亿多**、巨人网络《超自然行动组》6月流水**过亿**，当前TTM PE约**30倍**、2025年静态PE约**20倍**。
+大美丽法案三大块：提高债务上限5万亿美元，延长2017年减税法案（新增支出3.4万亿美元，年3400亿），取消899条款。财政赤字率维持5-6%，关税收入可覆盖支出。三季度7-9月美债供给约1万亿美元，可能推高利率但幅度或不及2023年。关税有效税率测算10-12%，极端18%，通胀年底3.3-3.4%，关注8月1日和其他市场谈判、8月12日中美谈判及转口限制（越南40%）。港股流动性三季度不如二季度，港币7.85，IPO融资多。光伏行业2020-2024年装机CAGR 42%，2025-26年增速回落至10%左右，产能过剩：电池1.5倍、硅片组件2倍、硅料2.5倍，价格下跌70-90%。反内卷政策：6月29日人民日报发声、7月1日中财委会议、7月3日工信部座谈会。多晶硅期货价格反弹至40元/公斤，硅片涨10%，电池涨2分。人形机器人二季度板块跌9%，跑输机械12个百分点，特斯拉标签股回调30-40%，智元收购上市、宇树年收入破10亿、两家中标中国移动1.2亿订单。游戏板块6月版号单月158个创新高，1-5月市场规模同比增长17%，手游增长20%，吉比特仗剑传说首月流水2亿多，巨人网络超自然行动组年化20亿流水，估值TTM PE 30倍、2025年静态PE 20倍。
 # 官方表态
-刘刚凯文：&gt; 我们并不是完全的认同，去美元化这个观点的。现在这个预期基本成了一个非常拥挤的共识，而且主要是基于宏大趋势。把美元弱当成去美元化，把美元弱和美股弱直接划等号，是市场两个最大的误区。&gt; 大美丽法案对信用周期中长期有利，但三季度有流动性波折；美股美债波动提供再配置机会，不悲观。&gt; 关税大概率是谈判技巧，市场逐渐脱敏，但需关注8月1日谈判和8月12日中美谈判及转口限制。&gt; 港股三季度流动性边际收紧，指数在23000~24000区间震荡，建议低迷时介入、亢奋时锁定利润。刘佳妮：&gt; 反内卷政策有望夯实行业底部，硅料整合最迫切，头部一体化组件企业穿越周期能力较强。郭文秀：&gt; 三季度是二季度迷茫期到商业兑现的过渡阶段，建议关注华为云生态接入、头部企业出货量跨越500/1000台、电机硬件优化三类信号。张雪琴：&gt; 游戏板块在消费、政策和新品周期三重利好下，有望在调整后再次实现戴维斯双击。
+刘刚凯文对大美丽法案表态：提高债务上限消除违约风险，延长减税避免大幅加税，取消899条款维护美元体系根基，认为信用周期改善，财政赤字率不会大幅增加，三季度流动性有波折但波动提供再配置机会，对美股美债不悲观。对关税表态：关税一定会做，需维持一定税率（10-12%有效税率），不能太高，市场逐渐脱敏，大概率是谈判技巧，对通胀影响有限，美联储仍可降息。对港股流动性表态：三季度不如二季度，但基本面强可盖过影响，建议在合适位置拿长期正确板块。刘佳妮对光伏反内卷表态：政策力度升级，价格恶性竞争有望告一段落，行业底部夯实，硅料整合最迫切，头部一体化组件企业穿越周期能力强。郭文秀对人形机器人表态：三季度是迷茫期到商业兑现的过渡阶段，关注华为云生态接入、头部企业出货量跨越500/1000台、电机硬件优化三类信号。张雪琴对游戏板块表态：在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击，当前是配置时间点。
 # Q&amp;A环节
-问：大美丽法案对美股美债和美元流动性有什么影响？ → 答：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年，信用周期框架下美国下半年环比改善，四季度美元可能小幅走强、美股可能反弹跑赢。问：关税谈判最新变化及对市场影响？ → 答：关税四点信息为一定会做以支撑收入、需维持10~12%有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到18%，通胀年底抬升至3.3~3.4%但不改变路径，需关注8月1日谈判和8月12日中美谈判及转口限制。问：反内卷对光伏行业的影响？ → 答：光伏2025年需求650~700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍，产业链价格跌70~90%；反内卷政策级别提升，硅料环节最易切入，多晶硅期货反弹至40元/公斤、硅片报价涨10%、电池涨2分，组件跟涨意愿但受136号文电价不确定性影响。问：人形机器人三季度核心趋势和投资逻辑？ → 答：二季度A股机器人板块跌约9%、跑输机械12个百分点，特斯拉供应商回调30~40%；三季度三条主线为华为云生态开放、本土企业技术闭环、特斯拉延期带来硬件替代窗口；关注物流端场景、电机和轻量化方向。问：游戏板块最近状态及投资机会？ → 答：政策端友好度空前，6月单月版号158个创2018年以来新高，1~5月游戏市场规模同比增长17%多、手游增长20%；中型厂商新品成为核心催化，当前TTM PE约30倍、2025年静态PE约20倍，新品利润有滞后性、明年兑现，有望在调整后再次实现戴维斯双击。</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>22868/2459</t>
+问：大美丽法案对美股美债和美元流动性有何影响？答：刘刚凯文指出，法案提高债务上限、延长减税、取消899条款，对中长期信用周期有利，但三季度7-9月有流动性抽水效应，美债供给约1万亿美元，可能推高利率但幅度或不及2023年，波动提供再配置机会，四季度美元可能小幅走强。问：关税升级市场为何反应冷静？答：刘刚凯文表示，关税大概率作为谈判技巧，有效税率维持10-12%水平，对通胀影响有限，市场逐渐脱敏，关注8月1日和其他市场谈判、8月12日中美谈判及转口限制。问：港股流动性前景如何？答：刘刚凯文指出，三季度流动性不如二季度，美元流动性供给压力、港币未完全回来、IPO融资多，但基本面强可盖过影响，建议在合适位置布局长期正确板块。问：光伏反内卷政策对行业有何影响？答：刘佳妮表示，政策升级强化，价格恶性竞争有望告一段落，行业底部夯实，硅料整合最迫切，组件价格跟涨需观望招标情况。问：人形机器人三季度有哪些投资主线？答：郭文秀指出，关注华为云生态开放、本土企业技术闭环、特斯拉延期带来的硬件替代窗口三条主线，建议关注物流场景、电机优化、轻量化方向。问：游戏板块调整后是否值得配置？答：张雪琴表示，在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击，当前是配置时间点。</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22868/1807</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="9">
+    <row r="10" ht="13.5" customHeight="1" s="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:10
@@ -3436,42 +3378,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t># 课程概况
-本次课程为以「梦想」为主题的班会课，教师先提问班会主题名称并邀请同学分享梦想，有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手，教师提到有同学想当歌手并让其上来唱了两首歌，鼓励自愿为原则在结束前再唱一首。教师随后分享自己的梦想是成为受学生喜爱、有名望的优秀人民教师，并讲述自己曾想考中国美术学院、单考通过但因离家远和没钱未去，最终去了广东技术师范大学（原民族学院，后改名广师大），自己是定向生、免学费、需回龙川县教书，当时哭了三天但后来越来越喜爱教师行业。教师播放航模少年和想成为歌手的普通人的视频，组织4个大组作为梦想观察团讨论实现梦想需要的条件，并以马云中考考两次、高考多次、现成为中国首富为例说明坚持的重要。最后教师请同学们写下自己的梦想清单并分组分享，收齐每个同学的梦想。
-# 核心知识点梳理
-**丑小鸭的梦想**：想变成白天鹅。
-**教师的梦想**：成为受学生喜爱、有名望的优秀人民教师；此前愿望清单包括考中国美术学院（单考通过，因离家远和没钱未去）、加入学生会、参加各种比赛、保持专业排名第一（专业41人）、考教师资格证。
-**定向生**：免学费，需回龙川县教书；定向不能考研，只能在职考研，且学费自交。
-**实现梦想的条件**：学生提到坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结 `学习`、`坚持`、`行动` 是梦想必不可少的三个条件，机会留给有准备的人。
-**马云案例**：中考考两次才考上高中，高考多次，现成为中国首富，说明起点高低不重要、坚持才重要；马云的新梦想是希望未来15年世界因他们而改变，享受改变他人的乐趣。
-**梦想的调整**：梦想可以一步步立高，如先考进年级前百再定前50，实现不了可以调整。
-⭐ 难点：理解定向生不能考研、只能在职考研且学费自交的限制；理解梦想可以调整、一步步立高。
-*易混点*：定向生与普通师范生的区别；梦想实现不了与放弃梦想的区别。
-# 课堂互动与答疑
-问：班会主题叫什么？→ 答：梦想。
-问：同学们有什么梦想？→ 答：有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手。
-问：老师的梦想是什么？→ 答：成为受学生喜爱、有名望的优秀人民教师。
-问：实现梦想需要具备哪些条件？→ 答：坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结学习、坚持、行动是必不可少的三个条件。
-问：如果缺少一个条件，梦想还会实现吗？→ 答：具备某一个条件梦想都有可能实现，都具备则会更快实现。
-问：马云的新梦想是什么？→ 答：希望未来15年世界因他们而改变，享受改变他人的乐趣。
-&gt; 不被嘲笑的梦想就是梦想。
-&gt; 机会都是留给有准备的人。
-&gt; 梦想还是要有的，万一实现了呢？
-&gt; 每一个梦想都是值得我们尊重的。
-# 课后任务与学习建议
-教师请同学们拿出纸写下自己的梦想清单，可列第1个、第2个、第3个，实现之后可以打勾，并思考实现梦想需要的时间和收获。写完后各小组第1个同学分享梦想，教师收齐每个同学的梦想。教师强调写梦想要实在一点、诚恳一点，梦想可以制定多个，先定小目标再定大目标，实现不了可以调整。复习重点为实现梦想的条件（学习、坚持、行动）及梦想可以一步步立高、可以调整。</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>9362/1348</t>
+          <t># 梦想主题班会：分享与讨论
+梦想主题班会：分享与讨论
+会议要点：本次班会以“梦想”为主题，老师先询问学生梦想，学生回答想当太空人、世界冠军、主角、歌手等。老师分享自己的梦想是成为受学生喜爱的有名望的优秀人民教师，并讲述个人经历：曾梦想考中国美术学院，单考通过但未就读，后入读广东技术师范大学（原民族学院），因离家远和家庭经济原因选择定向师范，毕业后回龙川教书。老师还分享大学期间的梦想：加入学生会、参加比赛、保持专业排名第一、考教师资格证等。；班会播放视频展示航模爱好者何宗发和普通歌手追梦的故事，引导学生讨论实现梦想的条件。老师总结条件包括坚持努力、天赋、勇敢、机会、兴趣、能力和学习，并强调不要嘲笑任何人的梦想，机会留给有准备的人。；老师展示自己的梦想之路，从读书到考大学历时11年，获得国家励志奖学金用一年，成为优秀人民教师待定。学生写下梦想清单，老师分享部分学生的梦想，如考试不犯糊涂、考上重本、成为画家、攒20万、成为创业者等。老师总结梦想可以分阶段制定，先小目标后大目标，量力而行，适时调整。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9362/462</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="9">
+    <row r="11" ht="13.5" customHeight="1" s="10">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:00
@@ -3642,24 +3564,24 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次内容为新闻联播式综合报道，涵盖新思想引领新时代改革开放的文化建设、赵乐际对俄罗斯正式友好访问并出席中俄议会合作委员会第九次会议、夏粮产量创历史新高、6月国家铁路货运指标增长、上半年快递业发展提速、油气管网建设提速、渝川皖等地应对降雨天气，以及国内国际联播快讯等议题。文化建设方面，报道围绕文化兴国运兴、文化强民族强展开，强调党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展，坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议；今年是中俄建交75周年，双方表示从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障，沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政，访问期间赵乐际向俄无名烈士墓敬献花圈。经济民生方面，今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加主因，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金，小麦质量为近年来最好水平；6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，化肥农药运量增幅最大，同比增长26.2%，中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%；上半年我国快递业务量超800亿件，快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件；油气管网建设提速，预计全年新增管道里程超4000公里，西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米，目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米，按照规划到2025年初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。防汛方面，7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区内涝、滑坡，消防救援人员紧急出动转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来洪峰流量45000立方米每秒量级洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群减小三峡水库入库洪峰流量。国内联播快讯方面，北京上半年计划新开工的320个市区重大项目全部实现开工，总投资超过4000亿元；燕矶长江大桥北岸主塔封顶，下一步转入主缆施工阶段，大桥连接湖北鄂州和黄冈，主跨1860米；第二十三届环青海湖国际公路自行车赛在海北州门源县收官，22支车队154名运动员决出5个奖项冠军；内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底；“中非儿童手拉手”活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。国际联播快讯方面，美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，枪击造成一名观众死亡、两名观众重伤，枪手被特勤局狙击手打死，动机有待查明；以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明谴责；以军袭击黎巴嫩多个边境村镇，黎真主党武装称打击以军集结地；叙利亚大马士革卡夫苏萨地区等遭空袭，造成1名政府军士兵死亡、3人受伤；俄称打击乌军列车点，乌称击退俄军进攻；加拿大东北部林火蔓延，拉布拉多城9600人被疏散，加拿大正在应对500多起活跃林火，其中超400起处于失控状态。
-## 新思想引领新时代改革开放：以文化自信筑牢强国复兴精神之基
-- 报道围绕文化兴国运兴、文化强民族强展开，强调没有高度文化自信就没有中华民族伟大复兴；党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。
-- 习近平总书记就弘扬和发展中华文化提出一系列重要论述，在孔子故里翻看《孔子家语通解》《论语诠解》，在岳麓书院凝望“实事求是”匾额，在三苏祠强调从中华优秀传统文化中汲取治国理政的理念和思维，在武夷山朱熹园提出以时代精神激活中华优秀传统文化的生命力。从深入实施中华文明探源工程到高标准推进国家文化公园建设，从中国共产党历史展览馆、国家版本馆等文化地标落成到《复兴文库》、“中国历代绘画大系”出版，中华优秀传统文化与革命文化、社会主义先进文化融会贯通。深化国有文艺院团改革、树立以人民为中心的创作导向，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
-## 赵乐际对俄罗斯进行正式友好访问并出席中俄议会合作委员会第九次会议
-- 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科的邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。赵乐际向普京转达了习近平主席的亲切问候和良好祝愿，指出今年是中俄建交75周年，中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献。普京请赵乐际转达对习近平主席的亲切问候，表示俄中立法机构始终保持高水平合作。与马特维延科、沃洛金分别会谈时，赵乐际表示要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持，两国立法机构要立足职能职责，用好中俄议会合作委员会、双边友好小组等机制和平台，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障。马特维延科表示发展对华关系得到俄社会的广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，指出两国立法机构要密切战略协作，服务中俄关系发展大局；交流治国理政经验，助力各自国家发展振兴；发挥立法机构职能作用，以法治方式促进务实合作；传承弘扬传统友谊，不断夯实国家关系的社会和民意基础；加强多边协作，从立法机构层面团结壮大“全球南方”力量。访问期间，赵乐际在莫斯科向俄无名烈士墓敬献了花圈。</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>7755/3290</t>
+会议围绕文化自信与中华民族现代文明建设展开，回顾了党的十八大以来文化体制改革成就，强调坚持把社会效益放在首位、社会效益和经济效益相统一。赵乐际于7月9日至13日对俄罗斯进行正式友好访问，会见普京，与马特维延科、沃洛金会谈，出席中俄议会合作委员会第九次会议，双方强调立法机构要深化多层级、多领域、多渠道交流合作，互学互鉴立法经验。今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，单产375.2公斤/亩，小麦单产399.1公斤；6月国家铁路发送货物3.32亿吨，货运周转量2665亿吨公里，同比分别增长6.1%、5.3%；上半年快递业务量超800亿件；预计全年新增管道里程超4000公里，输气能力从2020年2230亿立方米增加到3290亿立方米。
+## 文化自信与中华民族现代文明建设
+- 习近平总书记强调文化自信，提出‘两个结合’，首次提出习近平文化思想。文化体制改革推进，实施《深化文化体制改革实施方案》和《关于实施中华优秀传统文化传承发展工程的意见》。文化领域供给侧结构性改革，文旅融合，非遗保护，公共文化服务体系建设。
+- 坚持把社会效益放在首位，社会效益和经济效益相统一。
+## 外交与多领域发展成就
+- 赵乐际访俄并出席中俄议会合作委员会第九次会议，双方强调立法机构合作；夏粮产量创历史新高；6月铁路货运多项指标增长；上半年快递业务量超800亿件；油气管网建设提速；渝川皖等地应对降雨天气；国内联播快讯及国际新闻。</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7755/624</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="9">
+    <row r="12" ht="13.5" customHeight="1" s="10">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:03
@@ -3894,46 +3816,25 @@
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课为三讲光学中的第一讲，部分同学是新学、部分是复习，内容涵盖光的直线传播、光的反射（平面镜、凸面镜、凹面镜即球面镜）、光的折射（凸透镜、凹透镜）及透镜应用（显微镜、望远镜），初中光学统称几何光学，高中不再讲几何光学而讲干涉、衍射。光源定义为自身能够发光的物体，分自然光源（太阳、萤火虫）与人造光源（火把、蜡烛、煤油灯、电灯），光线用带箭头直线表示、是物理模型并非真实存在。光在均匀介质中沿直线传播，实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成；小孔成像一定成倒立实像、放大缩小不一定、与孔形状无关。光在真空中传播速度为3×10^8米每秒即3×10^5千米每秒，约每秒绕地球赤道7圈半，水中约为真空中的3/4、玻璃中约为2/3。光的反射定律为反射光线、入射光线和法线在同一平面内，反射光线与法线、入射光线分居法线两侧，反射角等于入射角；平面镜成正立、等大的虚像；凸面镜对光线起发散作用、成正立缩小的虚像，凹面镜对光线起会聚作用、有焦点F。
+本讲为初中物理光学复习课，系统复习光的直线传播、光速、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。光源分为自然光源（太阳、萤火虫）与人造光源（电灯等），光线是带箭头的直线，为物理模型；光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。光速在真空中为3×10^8米/秒，空气中略慢，水中为真空中的3/4，玻璃中为2/3。光的反射定律为三线共面、分居两侧、反射角等于入射角，法线为辅助线且垂直镜面，垂直入射时入射角为0度；作图步骤为先画法线，再按反射角等于入射角画光线。镜面反射发生在光滑表面，反射光线平行，可能造成反光问题；漫反射发生在凹凸不平表面，反射光线射向各个方向，生活中大多数反射为漫反射，如黑板、电影银幕，两者均遵守反射定律。平面镜成像原理是光的反射，成正立、等大的虚像；实验用玻璃板代替平面镜以确定像的位置，用刻度尺比较像与物到镜面的距离，用两段相同蜡烛比较大小；玻璃板有厚度会导致两个像，玻璃板不垂直会导致测量误差。凸面镜对光起发散作用，成缩小虚像，用于汽车后视镜、丁字路口镜；凹面镜对光起会聚作用，用于手电筒、太阳灶、耳鼻喉科检查；玻璃幕墙凹面可能造成光污染，烧死树木或引燃电线。
 # 核心知识点梳理
-**几何光学**：初中光学（直线传播、反射、折射）统称几何光学，2000多年前古希腊哲学家已发现相关规律；高中不再讲几何光学，转而讲干涉、衍射。
-**光源**：自身能够发光的物体。自然光源如太阳、萤火虫；人造光源从火把、蜡烛、煤油灯到电灯。
-**光线**：用带箭头的直线表示，是物理模型，并非真实存在。光源按形状可分点光源（如蜡烛）和平行光源（如太阳）。
-**光在均匀介质中沿直线传播**：可用玻璃罩加熏香或点香、激光笔照射证明；吸管弯折后激光打不到墙上同一点。实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成。
-⭐ **小孔成像**：一定成倒立实像，放大缩小不一定，与孔形状无关，如树荫下光斑。
-⭐ **日食月食**：日食为太阳、月球、地球同一直线且月球在中间，分日全食、日偏食、日环食；月食为太阳、地球、月球同一直线且地球在中间，月偏食是月球部分在1号区域、部分在2或3区域。
-**光速**：真空中 `3×10^8米每秒` 即 `3×10^5千米每秒`，约每秒绕地球赤道7圈半；空气中约 `2.99×10^8米每秒`，近似取 `3×10^8`；水中约为真空中的3/4，玻璃中约为2/3。练习中激光从地球到月球1.25秒，距离为 `3.75×10^8米`；雷电先见闪电后闻雷声因光速比声速快，15度时声速340米每秒。
-**光的反射定律**：通过硬纸壳、透明胶带、平面镜和激光笔的探究实验验证。定义入射光线AO、入射点O、反射光线OB、法线OP（垂直于镜面、是角AOB的角平分线）、入射角与反射角；法线不存在、画虚线。三句话：反射光线、入射光线和法线在同一平面内（共面）；反射光线与法线、入射光线分居法线两侧；反射角等于入射角。垂直入射时入射角和反射角均为0度，反射光线与平面镜夹角40度时入射角为50度；作图先画法线、保留作图痕迹、利用对称找点。
-**镜面反射与漫反射**：镜面反射是平行光射到光滑镜面后反射光线仍平行、只在特定方向看到反射光；漫反射是表面凹凸不平时反射光线射向各个方向、生活中大多数反射是漫反射。黑板、电影银幕、投影幕布发生漫反射，黑板反光看不清字是镜面反射；无论镜面反射还是漫反射都遵守光的反射定律。雨后夜晚迎着月光走亮处是水潭、背着月光走暗处是水潭；光路可逆。
-**平面镜成像**：实验用玻璃板代替平面镜以便移动蜡烛找像，用刻度尺比较像与物到镜面的距离，选两段完全相同蜡烛比较像与物大小；平面镜成正立、等大的虚像，不能用光屏承接，像与物连线与镜面垂直、像到镜面距离与物到镜面距离相等；玻璃板与水平面不垂直或玻璃板有厚度（两面反射成像）会导致数据不相等或看到两个像；平静水面、光滑金属表面可充当平面镜。
-**球面镜**：凸面镜对光线起发散作用、成正立缩小的虚像，用于汽车后视镜、丁字路口拐弯处；凹面镜对光线起会聚作用、有焦点F，用于手电筒、汽车前大灯、探照灯、耳鼻喉科医生头镜、西藏太阳灶；作图可用以直代曲方法。
+**光源**：自身能够发光的物体，分为自然光源（太阳、萤火虫）与人造光源（电灯等）。**光线**：带箭头的直线，是物理模型，非真实存在。**光在均匀介质中沿直线传播**：实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。小孔成像成倒立实像，放大缩小不一定，与孔形状无关。日食时月球在中间，月食时地球在中间。**光速**：真空中为3×10^8米/秒（每秒绕地球赤道7圈半），空气中略慢，水中为真空中的3/4，玻璃中为2/3。**光的反射定律**：三线共面、分居两侧、反射角等于入射角；法线为辅助线，垂直镜面，垂直入射时入射角为0度。作图步骤：先画法线，再按反射角等于入射角画光线。**镜面反射与漫反射**：镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向，两者均遵守反射定律。**平面镜成像**：成正立、等大的虚像，原理是光的反射；实验用玻璃板代替平面镜，用刻度尺比较距离，用两段相同蜡烛比较大小。**球面镜**：凸面镜发散，成缩小虚像，用于汽车后视镜、丁字路口镜；凹面镜会聚，用于手电筒、太阳灶、耳鼻喉科检查。⭐难点：日食月食的区域划分（日全食、日偏食、日环食；月全食、月偏食）。易混点：*小孔成像成倒立实像，平面镜成像成正立虚像*。
 # 课堂互动与答疑
-问 → 答：为什么用玻璃板代替平面镜做实验？→ 因为若用镜子虽有反射，但无法移动后面的蜡烛来找像，故用玻璃板代替平面镜。
-问 → 答：实验为什么选用刻度尺？→ 为了便于比较像与物相对镜面的距离。
-问 → 答：为什么选取两段完全相同的蜡烛？→ 为了比较像与物的大小。
-问 → 答：光屏能否接收到蜡烛的烛焰的像？→ 不能，因为实际光线没有到达后面，成的是虚像。
-问 → 答：记录数据中蜡烛到玻璃板的距离与像到玻璃板的距离有几组不相等，原因可能是什么？→ 一是玻璃板与水平面不垂直，二是玻璃板有厚度、它的两个面发生反射成像。
-问 → 答：在玻璃板同一侧看到同一个蜡烛的两个像，原因是什么？→ 玻璃板有厚度，它的两个面发生反射成像的结果。
-问 → 答：为什么引进法线？→ 主要是为后面讲折射作准备，法线真实不存在，画虚线。
-&gt; 光线是真实存在的吗？我画一个写上它实际上是一个物理模型。
-&gt; 三点一线实际上原理是什么？就是这个光在均匀介质中沿直线传播。
-&gt; 光在真空中传播速度是3×10^8米每秒，基本上一秒钟绕地球赤道7圈半。
-&gt; 无论哪种反射都要遵守光的反射定律。
-&gt; 作图一定是先去做一条法线，作图痕迹要留下。
+问：萤火虫算不算光源？答：算，它自身能发光。问：光线是真实存在的吗？答：不是，是物理模型。问：为什么光在均匀介质中沿直线传播，但穿过大气层会偏折？答：因为大气层不均匀，光发生偏折，所以太阳看起来像越出地平线，星星会眨眼睛。问：为什么小孔成像的像与孔形状无关？答：因为光沿直线传播，像的形状由物体决定。问：为什么平面镜成像实验中用玻璃板代替平面镜？答：因为玻璃板透明，便于确定像的位置。问：为什么玻璃板有厚度会看到两个像？答：因为玻璃板两个面都能发生反射成像。问：为什么垂直入射时入射角是0度而不是90度？答：因为入射角是入射光线与法线的夹角，垂直入射时夹角为0度。&gt; 教师提醒：光在均匀介质中沿直线传播，这句话要写全。
 # 课后任务与学习建议
-教师布置的课堂练习为练习第1至5题、第10和第11题、第13至24题等，要求当堂完成并讲解答案。复习重点为：光在均匀介质中沿直线传播及其实例、光的反射定律三句话、镜面反射与漫反射的区别、平面镜成像特点（正立、等大的虚像）、凸面镜与凹面镜的作用与应用。学习建议：可在家用纸杯底部用针扎小孔、蒙塑料布、点蜡烛做小孔成像实验；用硬纸壳、透明胶带、平面镜和激光笔做反射定律实验；用白纸和小镜子配合手电筒观察镜面反射与漫反射；建议购买激光笔辅助研究直线传播与反射实验。教师提醒注意保护眼睛，长时间看屏幕、判卷等最费眼睛，视力下降后矫正视力约0.7，应重视用眼健康。</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>25691/2518</t>
+完成讲义练习第1至第6题（光的直线传播部分）、第7至第17题（光的反射定律、镜面反射与漫反射）、第18至第24题（平面镜成像、球面镜）。复习重点：光的直线传播实例、光的反射定律、平面镜成像特点及实验、镜面反射与漫反射的区别。建议：可在家用激光笔、硬纸壳、平面镜等做反射实验，用纸杯、针、蜡烛做小孔成像实验，用玻璃板、蜡烛做平面镜成像实验。</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25691/1582</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="9">
+    <row r="13" ht="13.5" customHeight="1" s="10">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:14
@@ -4039,38 +3940,22 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t># 课程概况
-本次课为《电气工程基础》课程导论，该课是进入专业课接触的第一门课，也是专业入门课。教学目的有两个：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程要求对电路理论和电机学知识有一定了解，特别是变压器和同步电机相关知识要求较高，有欠缺的同学需下去补充；后续最重要的四门课程为电力系统分析、电力系统继电保护、电力系统自动化和高电压技术。第一章涉及电力系统基本概念最多、最重要，要求掌握电力系统、电力网、动力系统和变电站等基本概念，理解电力系统特点及由此引起的最基础理论，理解对电力系统提出的要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中心点接地方式特点。课程还梳理了电力发展简史、三相交流输电优势，以及电力系统形成与定义、电网分类与变电站分类。
-# 核心知识点梳理
-**一、课程定位与目标**：电气工程基础是进入专业课接触的第一门课、专业入门课。教学目的：①掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；②掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程：电路理论、电机学，特别是变压器和同步电机相关知识要求较高。后续最重要的四门课程：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
-**二、第一章重点内容**：①学习和掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站；②理解电力系统的特点及由这些特点引起的设计运行等方面最基础的理论；③理解对电力系统提出的要求，涉及运行、设计和维护各方面；④掌握电力系统的电能质量指标，包括国家标准对这些指标规定的范围；⑤了解电力系统常用的接地方式，特别是工作接地即中心点接地方式的不同特点。
-⭐**三个学习难点**：①由电力系统特点引出的最基本原理，如电能不能大量储存，决定了电力系统的有功功率和无功功率的动态平衡问题；②电力系统额定电压的规定非常繁杂，要注意把这些规定搞清楚；③各种中心点的接地方式，直接影响后面所学习的多个章节内容，学习起来也比较困难。
-**三、学习方法建议**：对基本概念注意其内涵和外延，并适当结合实际；思考方法上从电力系统的特点要求出发，注意从最基础的原理去推导，不要去记结论，因为结论性东西在使用条件变化时就会发生变化；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。
-**四、电力发展简史**：电力发展从直流开始。福泰勒使用2000米导线连接瓦斯发电机，拖动直流发电机和电动机，证明直流远距离两公里输电可行。1874年俄国工程师在彼得堡建立4.5公里直流输电线路，功率4.5千瓦。1882年法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端343伏、末端850伏，输送功率200瓦，损耗78%。1883年德普勒进行14公里输电试验，输送功率1.1千瓦，损耗55%。1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展为五线制。19世纪末法国方剑将多台直流发电机串联提高电压，将75千瓦电力送75千米。20世纪初瑞典科学家在串联直流发电机上装短路器，之后20多年建15条直流输电线路，最大为1906年投运的法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦线路，1927年改建为260公里、125千伏、19000千瓦。直流输电受制约因素多、设备复杂、运行方式复杂、造价高、可靠性差。
-交流方面：1876年俄国科学家发明单相变压器，主要用于照明；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行；威斯汀豪斯与爱迪生进行交直流电力战争，爱迪生和凯尔文主张直流，威斯汀豪斯和特斯拉主张交流；1886年威斯汀豪斯在麻省进行1000米、30千伏交流输电示范，又在意大利建成17英里高压输电线路；1886年俄国科学家发明三相交流电和三相异步电动机；法国到德国的交流输电线路被认为是第一条交流输电线路。交流输电随高电压技术和绝缘技术发展：1898年发明真实绝缘子，美国加利福尼亚输电电压提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，首次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压1150千伏线路投运后降压到500千伏运行。国内：220千伏1941年投运，330千伏1972年投运，500千伏1981年投运，2009年1000千伏交流特高压投运。直流用于联网：1954年瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆，100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。中国第一个直流输电工程连接舟山群岛与浙江定海电网；第二个是1989年葛上直流，葛洲坝电厂到上海，±500千伏；今年6月投运云广直流±800千伏特高压直流工程。
-**五、三相交流输电优势**：交流指ABC三相对称系统，优点：①易于产生旋转磁场，三相电动机容易做驱动；②瞬时功率恒定，不随时间变化；③输电线路导线量即金属消耗量最少。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流。国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小。
-**六、电力系统的形成与定义**：最早单台发电机孤立向附近负荷供电，可靠性差。后将多台发电机连接起来提高可靠性，但导线有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离不能太长。解决办法是升高电压，电压升高后电流减小，有功功率损耗和电压降落减小，输电距离变长，采用变压器升压降压。这样构成电力系统雏形，多台发电机共同向负荷供电，可装大机组，供电范围越来越大，带来经济效益。输电距离很长时，中间装设变电站用降压变压器向当地供电，并解决稳定问题。现代电力系统：发电机发出电，通过升压变压器升压，经输电线路传输到负荷中心，再降压给用电设备使用。**电力系统**定义为变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能，由发电、输电、配电、用电四个环节组成。**电力网**是变压器和输电线路构成的网络，即电力系统去掉发电机和用电设备的部分。**动力系统**是电力系统基础上加上发电厂动力部分（如火电厂锅炉、汽机、煤炭输送处理系统，水电厂水轮机、水坝、水库等）。
-**七、电网分类与变电站分类**：按规模将电网分为地方电力网、区域电力网、超高压远距离输送网络。地方电力网向固定地方供电，电压等级早期35千伏及以下，现在常为110千伏及以下，供电半径20~50公里；区域电力网电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心；超高压远距离输送网络电压等级500千伏或1000千伏，东北有330千伏，主要任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统，如特高压系统从山西晋东南到湖北荆门，跨三省，连接华北电网和华中电网。举例：武汉电网属地方电力网，主要供电电压110千伏和35千伏，少数220千伏；华中网是典型区域网；葛上直流、三峡到上海输电线路属超高压远距离输电网络。变电站分类常见三种：按电压等级分类，按最高电压等级称为多少千伏变电站，如华工变电站10千伏、关山变电站220千伏、凤凰山变电站500千伏；按主要功率流通方向分为升压变电站和降压变电站，大部分功率从高压侧向低压侧传输为降压变电站，从低压侧向高压侧为升压变电站。
-# 课堂互动与答疑
-问：我们国家为什么采用交流、为什么采用三相三线制？→ 答：交流指ABC三相对称系统，至少具有三个方面的优点：第一，易于产生旋转磁场，因此三相电动机很容易做驱动；第二，瞬时功率是恒定的，不随时间变化；第三，输电线路所采用的导线量即金属消耗量最少。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此三相三线制输电系统在交流输电领域得到广泛应用。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。
-&gt; 对基本概念，我们要注意它的内涵和外延，并且适当地结合实际。
-&gt; 对于思考的方法，我们要从电力系统的特点要求出发，注意从最基础的原理去进行推导，不要去记一些结论。
-&gt; 这些结论性的东西，往往当它的使用条件变化的时候就将发生变化。
-&gt; 关于这方面的内容，我希望大家下去做一些进一步的阅读，作为电气专业的学生，我们应该了解我们电力发展的一个基本的发展史。
-# 课后任务与学习建议
-教师推荐三本书，供大家下去阅读。教师强调第一章为重点内容，要求大家以重点内容进行掌握，并提醒学完章节后仔细体会学习方法：注意基本概念的内涵和外延并适当结合实际；从电力系统的特点要求出发，从最基础的原理去推导，不记结论；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。教师要求对电路理论和电机学知识有欠缺的同学下去把相关内容做一定的补充，特别是变压器和同步电机的相关知识。教师希望学生下去对电力发展史方面的内容做进一步的阅读，了解电力发展的基本发展史。原文未提及具体作业提交要求。</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>11163/4089</t>
+          <t># 电气工程基础课程：电力系统概念与发展史
+电气工程基础课程：电力系统概念与发展史
+会议要点：本课程为电气工程基础入门课，旨在使学生掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及整体关系，并掌握分析、设计、运行、管理的基础理论、技术与计算方法。前修课程要求电路理论和电机学知识，特别是变压器和同步电机；后续课程包括电力系统分析、电力系统继电保护、电力系统自动化和高电压技术。第一章概念最多最重要，学习内容包括基本概念、电力系统特点、要求、电能质量指标和接地方式；三个难点为电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）、额定电压规定、中性点接地方式；学习方法包括注意概念内涵外延、从原理推导、寻找额定电压规律、比较接地方式特点。；电力发展史从直流输电开始：福泰勒用2000米导线连接瓦斯发电机拖动直流电动机和水泵，证明直流输电可行；1874年俄国工程师建成4.5公里直流线路；1882年法国德普勒架设57公里直流试验线路，首端电压343伏、末端850伏，输送功率200瓦，损耗78%；1883年德普勒进行14公里输电试验，输送功率1.1千瓦，损耗55%。直流输电受电压等级限制，难以远距离大容量输电；交流输电因变压器升压降压优势逐渐占主导，1886年威斯汀豪斯在麻省进行交流输电示范，1898年发明绝缘子，电压等级逐步提高至110千伏、220千伏、380千伏、735千伏、765千伏、1150千伏。中国1941年投运220千伏，1972年330千伏，1981年500千伏，2009年1000千伏。直流输电在联网中重新受关注，1954年瑞典建成世界首个工业海底电缆直流工程，1972年加拿大投运首个晶闸管换流阀背靠背直流工程；中国首个直流工程连接舟山群岛与浙江定海，1989年葛上直流±500千伏，今年6月云广直流±800千伏投运。；电力系统由发电机、变压器、输电线路和用电设备组成，完成电能生产、输送、分配和消耗；电力网是去除发电机和用电设备的部分，动力系统则包含发电厂动力部分。电网按规模分为地方电力网（电压等级110千伏及以下，供电半径20-50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，跨省跨地区）。变电站按最高电压等级分类（如10千伏、220千伏、500千伏变电站），按主要功率流向分为升压变电站和降压变电站。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11163/1030</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="9">
+    <row r="14" ht="13.5" customHeight="1" s="10">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:05
@@ -4147,29 +4032,44 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本笔记围绕调和级数收敛与发散这一经典问题展开，核心议题是评论 Stack Exchange（MSE）上网友对该问题的多种证明思路。UP主皮卡从高中数学讲起，先给出级数收敛与发散的简化定义：序列 `an=1/n`，前n项和 `sn`，若所有 `sn` 都小于某个固定实数 `a` 则收敛，若 `sn` 大于某个无界递增的 `bn` 则发散。随后评论了网友的分组求和证明，并补充柯西凝聚判别法，指出其证明过程与分组求和一模一样，对非负不增序列，收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1。UP主还联想到高斯求和 `1+2+…+100` 时用 `1+100`、`2+99` 等分组，每组 `101`，说明分组求和思路普遍。第二个证明用调和数 `hn` 大于 `log(n+1)` 证明发散，涉及积分估计与差分两种流派；网友取对数将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`，UP主认为这与差分方法本质相同，是故弄玄虚。第三个流派用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+本笔记围绕调和级数收敛性的证明方法展开，源自皮卡在视频中对Stack Exchange上相关帖子的评论。皮卡首先介绍了级数收敛与发散的定义，随后逐一评论了网友的证明方法，包括分组求和、柯西凝聚判别法、积分估计、对数差分等，并指出某些证明是事后凑出来的，不自然。他批评了其中一种证明的故弄玄虚，认为其本质与更直观的方法相同。皮卡计划根据本期视频的反响决定是否继续该系列，若反响不错，将出下一期继续评论网友的数学问题解答。
 # 核心概念
-**级数收敛与发散的定义**：序列 `an=1/n`，前n项和 `sn=1+1/2+…+1/n`。若所有 `sn` 都小于某个固定实数 `a`，则收敛；若 `sn` 大于某个明显递增且无界的 `bn`，则发散。
-**分组求和证明**：将 `1/2+1/3` 分为一组，`1/4` 至 `1/7` 为一组，`1/8` 至 `1/15` 为一组，每组和都大于 `1/2`，任意多组相加无上界，故发散。
-**柯西凝聚判别法**：证明过程与分组求和一模一样，对非负不增序列，其收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1，便于判断增长缓慢的序列。
-**高斯求和**：`1+2+…+100` 用 `1+100`、`2+99`、`3+98` 等分组，每组 `101`，只需数有多少个 `101`，体现分组求和思路的普遍性。
-**调和数 `hn` 与 `log(n+1)`**：第二个证明用 `hn` 大于 `log(n+1)` 证明发散，`log` 无上界故 `hn` 无上界；有积分估计流派和差分流派，积分估计用矩形面积近似 `hn` 并放缩。
-**取对数与连乘积**：网友两边取对数，利用 `e^(a+b)=e^a·e^b` 将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`。
-**Stolz 定理**：第三个流派试图证明 `hn` 与 `log n` 同增长级别，用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+### 级数收敛与发散的定义
+- **收敛**：对于正向级数，若存在固定实数 `a`，使得所有部分和 `s_n` 均小于 `a`，则级数收敛。
+- **发散**：若部分和 `s_n` 大于某个无界递增的 `b_n`，即无论给定多大的数，总能通过增大 `n` 使 `b_n` 超过它，则级数发散。
+### 调和级数
+- 调和级数定义为 `1 + 1/2 + 1/3 + ... + 1/n`，其部分和记为 `h_n`。
+- 调和级数是发散的，即部分和没有上界。
+### 证明方法
+- **分组求和**：将调和级数分组，每组和均大于 `1/2`，从而证明发散。
+- **柯西凝聚判别法**：其证明思路与分组求和完全一致，通过分组估计部分和，适用于增长缓慢的序列。
+- **积分估计**：利用积分曲线面积近似 `h_n`，通过放缩证明 `h_n &gt; log(n+1)`，从而说明发散。
+- **对数差分**：利用 `e^x &gt; 1+x` 不等式，将 `e^{h_n}` 放缩为连乘积，最终得到 `n+1`，证明发散。
+- **Stolz定理**：通过比较 `h_n` 与 `log n` 的差分极限，证明二者同阶，从而说明发散。
+### 观点与批评
+- 皮卡认为某些证明（如对数差分）是事后凑出来的，不自然，本质与更直观的方法相同。
+- 他批评其中一种证明故弄玄虚，认为其本质是简单的分组求和思想，却用复杂形式呈现，妨碍理解。
 # 核心结论
-核心结论：调和级数发散，网友的分组求和证明、柯西凝聚判别法、`hn&gt;log(n+1)` 证明、取对数连乘积证明以及 Stolz 定理求极限均指向这一结论。易混淆点：**分组求和与柯西凝聚判别法证明过程一模一样**；**取对数连乘积方法与差分方法本质相同**；**Stolz 定理求 `hn/log n` 极限为1是先知道结果再凑，不自然**。待澄清问题：UP主表示后面还有很多方法，有机会再评论；下次是否出下一期取决于反响。</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>7465/1391</t>
+**核心结论**：调和级数是发散的，其部分和 `h_n` 无上界。
+**易混淆点**：
+- 收敛与发散的定义需明确：收敛要求所有部分和小于某个固定上界，发散则要求部分和无界。
+- 柯西凝聚判别法与分组求和本质相同，但适用于更广泛的非负不增序列。
+- 对数差分证明看似巧妙，但本质与积分估计或对数不等式相同，是事后凑出的结果。
+**待澄清问题**：
+- 皮卡提到“dialectic分解”思路，但未详细展开，留待后续视频。
+- 后续视频是否继续取决于本期反响，尚未确定。</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7465/1086</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1" s="9">
+    <row r="15" ht="13.5" customHeight="1" s="10">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:05
@@ -4228,47 +4128,54 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本笔记围绕 GitHub 作为资源库的知识主题展开，核心议题包括 GitHub 上的实用热门项目、国内访问加速方法、页面汉化与搜索技巧，以及项目主页功能与热门项目跟踪方式。主要观点为：GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到，涵盖麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂面试题与面试经验，Google、阿里等大公司最新开源大模型，以及用 AI 搞副业赚钱的教程和 AI 学习资料等。整体逻辑框架为：先介绍正经与不正经的实用项目，再逐一解决访问、汉化、搜索等使用问题，最后说明文档整理与领取方式。
+本次会议为工作室视频录制，由老李介绍GitHub上的实用热门项目及访问技巧。老李首先介绍了多个热门项目，包括评估工作性价比的“b班值不值得上”、表情包博物馆、健康活到150岁指南、一键证件照、自重健身教练、免费PDF教材、全自动视频生成项目、声音克隆模型chat box TTS、AI学习资源库、awesome AI apps等。针对国内访问GitHub存在的网络不通、页面全英文、搜索功能不好用等问题，老李提供了解决方案：使用watch tool Kit加速软件、GitHub镜像站（如gh proxy）、浏览器翻译插件（谷歌翻译、沉浸式翻译）、汉化插件等。老李指出GitHub原生搜索功能不好用，分享了更丝滑的搜索方法，推荐使用AI工具（如ChatGPT）搜索项目，并介绍了项目页面的功能：star、watch、fork、about、release、read me文件、最近更新日期等，以及explore和trending查看热门项目。
 # 核心概念
-## **GitHub 资源库定位**
-GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。正经资源包括麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂的面试题和面试经验，Google、阿里等大公司最新的开源大模型，用 AI 搞副业赚钱的教程，AI 学习资料等；不正经资源包括国内这些年全网火爆的表情包大合集、活到 150 岁养生指南、国内 996 最严重的大厂黑名单等。
-## **实用热门项目**
-- **B 班值不值得上**：评估工作性价比，输入年薪、工作地区、年假、通勤时长、学历、工作年限及领导同事是否 SB 等因素，综合给出工作性价比分数和评级。
-- **表情包博物馆**：国内过去这些年全网爆火的表情包大合集，包含甄嬛传、罗翔老师、特朗普、马保国等表情包。
-- **活到 150 岁指南**：分享经过科学研究证实的健康知识，如间歇性进食对身体有好处，会促进胆汁代谢、炎症自愈；吃天然发酵类食品可以改善肠道菌群生态等。
-- **一键做证件照**：上传一张大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
-- **丐版健身教练**：可选择自重、哑铃、弹力带、长凳等，选择要练习的肌肉群后给出用身体自重练习的参考动画。
-- **PDF 教材合集**：收集国内所有小学、初中、高中一部分大学的 PDF 教材，全部免费用。
-- **全自动视频生成项目** `Morning Printer Turbo`。
-- **声音克隆模型** `ChatTTS`：零样本语言克隆，情感控制非常到位，克隆的声音就像真人说话一样。
-- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，教程内容整理成一份 500 多页的 PDF 文档，含大量示意图。
-- **awesome AI apps**：收录大模型最新的 agent 应用，如医学影像数据分析的 agent、AI 投资的 agent、竞争对手情报分析 agent 等。
-## **GitHub 访问加速方法**
-- **Watt Toolkit 加速软件**：进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速，即可流畅上 GitHub。
-- **GitHub 镜像站**：如 `gh proxy`，浏览器点开就直接上 GitHub，默认是镜像的项目地址，搜其他项目也没问题。
-- **魔法**：个人最推荐的方法。
-## **GitHub 页面汉化**
-给浏览器装翻译插件，推荐谷歌 `Translate` 或 `沉浸式翻译`，装好后可直接把网页翻译成中文；动手能力强的还可给浏览器安装汉化插件。
-## **GitHub 搜索技巧**
-- **原生搜索**：按搜索词精准匹配，搜 `screen record` 和 `screen recording` 按星标排序结果不一样。
-- **AI 搜索**：推荐用 ChatGPT 等工具，用中文指令如“在 github 上帮我找好用的录屏软件”，能搜全热门录屏工具并总结成表格。
-## **项目主页功能与热门项目跟踪**
-- **项目主页功能**：`star` 相当于收藏和点赞，`watch` 是关注项目，`fork` 是复制项目，`about` 是项目简介，`release` 是软件安装包，`readme` 是项目说明书，`commit` 日期可理解为最近更新时间。
-- **跟踪热门项目**：点开左侧 `explore`，在 `trending` 里能看到全站当天、本周、本月最热门的项目；也可用 ChatGPT 找 `github daily`。
+**GitHub热门项目**
+- **工作性价比评估**：项目“b班值不值得上”可评估工作性价比，输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事是否SB等因素，综合给出性价比分数和评级。
+- **表情包博物馆**：收集国内过去几年全网爆火的表情包大合集，包括甄嬛传、罗翔、特朗普、马保国等主题。
+- **健康活到150岁指南**：分享经科学研究的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群生态。
+- **一键证件照**：上传大头照即可一键抠图换背景，生成不同标准的证件照和打印模板。
+- **自重健身教练**：选择肌肉群（如腹肌）后提供身体自重练习的参考动画，适合请不起真人教练的用户。
+- **免费PDF教材**：收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费。
+- **全自动视频生成项目**：名为morning printer Turbo，近期超火。
+- **声音克隆模型**：`chat box TTS`，零样本语音克隆，情感控制到位，克隆声音像真人说话。
+- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
+- **awesome AI apps**：收录大模型最新的agent应用，如医学影像数据分析agent、AI投资agent、竞争对手情报分析agent等。
+**GitHub访问问题及解决方案**
+- **网络不通**：使用`watch tool Kit`加速软件，进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可流畅访问。
+- **镜像站**：如`gh proxy`，浏览器点开直接访问GitHub，默认是镜像项目地址，也可搜索其他项目，但速度和稳定性较差。
+- **魔法（VPN）**：个人最推荐的方法。
+- **页面全英文**：安装浏览器翻译插件，谷歌浏览器推荐`谷歌翻译`或`沉浸式翻译`，可将网页翻译成中文；动手能力强的可安装汉化插件。
+**GitHub搜索与项目页面使用**
+- **原生搜索局限**：按搜索词精准匹配，如搜“screen record”和“screen recording”结果不同，导致不全面。
+- **AI搜索**：推荐用ChatGPT等AI工具，用中文描述需求，AI可总结成表格，找齐热门项目。
+- **项目页面功能**：`star`相当于收藏点赞，`watch`是关注项目，`fork`是复制项目到自己的账号；`about`是项目简介；`release`是软件安装包；`read me`文件是项目说明书，默认在项目最下面展开显示。
+- **更新日期**：每个文件最近的`commit`日期可理解为最近更新时间，若更新日期是好几年前，大概率是没人维护的僵尸项目。
+- **热门项目跟踪**：点开左侧`explore`，在`trending`里可看到全站当天、本周、本月最热门的项目；也可用ChatGPT找GitHub daily，及时分享最新热门项目。
 # 核心结论
-GitHub 是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。国内访问 GitHub 卡顿难，可用 Watt Toolkit 加速软件、gh proxy 等镜像站或魔法解决，其中 Watt Toolkit 更流畅，镜像站速度稳定性较差，个人最推荐魔法。页面满屏英文可装谷歌 Translate 或沉浸式翻译插件汉化。原生搜索按精准匹配，搜 `screen record` 与 `screen recording` 结果不一致，推荐用 ChatGPT 等 AI 工具以中文指令搜索。项目主页的 `star`、`watch`、`fork`、`about`、`release`、`readme`、`commit` 日期等功能需了解；跟踪热门项目可看 `explore` 的 `trending`，或用 ChatGPT 找 `github daily`。所有开源项目、教程及视频未提到的项目都整理在文档里，需要的可以三连关注免费领取。</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>4014/2303</t>
+**核心结论**：
+- GitHub是巨大的宝藏资源库，能找到名校公开课、大厂面试题、开源大模型、AI学习资料等正经资源，也有表情包、养生指南等不正经内容。
+- 国内访问GitHub推荐使用`watch tool Kit`加速软件，镜像站速度和稳定性较差，个人最推荐用魔法（VPN）。
+- GitHub原生搜索按精准匹配，结果不全面，推荐用AI工具（如ChatGPT）搜索项目。
+- 通过`explore`和`trending`可跟踪最新热门项目。
+**易混淆点**：
+- `star`是收藏点赞，`watch`是关注，`fork`是复制项目，三者功能不同。
+- `commit`日期是最近更新时间，不是创建时间。
+- 镜像站可访问GitHub，但速度和稳定性不如加速软件。
+**待澄清问题**：
+- 未提及。</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4014/2100</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="9">
+    <row r="16" ht="13.5" customHeight="1" s="10">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:07
@@ -4634,110 +4541,22 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t># 访谈概述
-本次对话由窦文涛主持，嘉宾为马先生与《明朝那些事》作者当年明月，从刚播完的日本电视剧《大奥》谈起，认为它是《大长今》之后最有影响的外国剧，三部剧时间跨度约相当于中国晚明到清初，另有一部在明治维新之前。对话认为日本文化核心是极端精神与忠诚文化，凡事做到尽头、发自内心，与中国讲中庸、讲融合的文化差异极大，并举例战后日本用30年成为世界第二经济强国、跳槽率最低、终身雇佣制、豆腐厂按点开工、做绳子的人几年不赚钱铺市场等。关于生死观，对话提到日本人重视死亡而非单纯藐视生命，剖腹自杀、看樱花只看落的那一天，被认为源于岛国生存条件恶劣。关于明史，当年明月表示写明朝是因为明史资料最多、自己最熟，但明清史料说法不一如罗生门，明朝本身跌宕起伏，朱元璋从乞丐到皇帝被推崇为人才，历史经验教训难以套用。对话还提到正德皇帝被写坏、豹房实为动物园、晚明江南市民生活富足、明末灾荒与瘟疫导致李自成起义和明朝灭亡，以及中国王朝约300年大限。
-# 访谈详细记录
-一、《大奥》与日本文化
-- 发言者3认为《大奥》是大长今以后可能最有影响的外国电视剧，拍得非常好。
-- 发言者3介绍该剧三部，前两部大概相当于中国晚明到清初，发言者2补充后来还有一部在明治维新之前，是一部有跨越性的历史剧。
-- 发言者2表示吸引他的是严谨的精神，看日本剧看不到群众演员笑场。
-- 发言者3称听人说这是大长今以后最重要的外国剧，第1集片头将军出场时所有人呈45度开始鞠躬，依次鞠躬，场面之华丽包括色彩，一看就不一样。
-- 发言者3介绍大奥就是普通话说的后宫，日本话的奥指很深的地方，屋子最里处叫奥，一般人不准进去。
-- 发言者2说明日本天皇一直是摆设，实际掌管权力的是幕府将军，德川家康开创德川幕府后日本所有权力掌握在一个人手上。
-- 发言者2称从实际上看幕府将军对天皇一点都不崇拜，天皇没钱办活动找将军要钱，将军不给，活动没办，后来还有为表示对幕府抗议而退位的。
-- 发言者2认为日本文化从头到尾没有变，核心是极端精神，所有事情要做到尽头。
-- 发言者3称日本是发自内心的，战后1945年以后用30年成为世界第二经济强国，是必然不是偶然，是唯一没有资源的国家。
-- 发言者2认为中国文化精神是中庸，讲究融合，是一条最适合的路；日本精神恰相反，坚持一个原则。
-- 发言者3称日本是忠诚文化的典型国度，坚韧不拔，做到极致。
-- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
-- 发言者3称日本跳槽率最低，每一次跳槽都是社会资源的浪费。
-- 发言者2称西方经济学家一直不能理解日本终身雇佣制，认为缺乏竞争会导致效率极低下，但日本终身雇佣了人家还是积极性特别高。
-- 发言者3举例去日本参观最底层工厂，豆腐规定当天做当天卖，夜里11:45所有人坐好看着表，12点整所有人站起来开始工作，四点多钟干完，然后上市，今天的豆腐今天卖。
-- 发言者2认为日本是岛国，没有资源，经常火山地震，人对世界有极强求生欲望，必须融入团体按固定规则做事才能生存。
-- 发言者3称日本投机取巧的人没有生存环境，社会文化的鄙视非常难过，所以不能生存。
-- 发言者3举例日本做绳子做到全日本第一的人，长达几年不赚钱，从批发处进货一分钱不赚送给客户，等把市场铺平后，拿单子跟两边各加2%，全国4%就是不得了的一个数。
-- 发言者2称慢慢走或者不偷奸耍滑，是一条更快到达成功的道路。
-- 发言者3称在这种文化中你愿意也做不成，你的文化不允许这种现象生存；强调忠诚最终一定要落到一个好处，所以这个民族才团结。
-- 发言者2称很不愿意做日本人，因为很多时候像盲从，而且他们有一种寻死的潜在欲望。
-二、日本生死观与忠诚
-- 发言者2称日本人看樱花不看发芽的时候，只看落那一天，由于常年以来生活在岛国上，生存条件太恶劣，对死亡不是藐视，是有点向往或者说不惧怕。
-- 发言者2称二战时日军到中国有那么多暴行，是一种藐视生命的行为。
-- 发言者3认为日本民族不是藐视生命，是重视死亡，是翻着的；剖腹自杀不是藐视生命，是重视死亡；经济危机时日本很多身家万贯的人剖腹自杀。
-- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
-- 发言者3称我们不能再用另外一个标准去评判它。
-三、明朝历史与明史研究
-- 发言者2表示写明朝是因为明史最熟，明史资料最多；历史界研究有两个难点，第一是先秦春秋，没史料，史记就那么一两篇，都是编的；第二是明清，明实录几千万字，明代史官的记录，明通鉴、明史纪事本末、明会典、纲目三编这些书堆得比山还高，但一个说法可能有7个不同，一个事件可能有7个不同说法，就好像罗生门。
-- 发言者3称明朝本身260多年的过程跌宕起伏，几次都要死没死了，土木堡之变、夺门之变各种之变特别多，皇上已经被瓦剌军抓起来了，哥几个一攒吧说那不算，又把弟弟扶起来了，完全构成一个现代版的电视剧。
-- 发言者1提到当年明月对朱元璋好像很推崇。
-- 发言者3称一个乞丐坐到最上面独此一份，刘邦好歹是个村长亭长。
-- 发言者2称推崇朱元璋因为他太不容易了，从一乞丐一直到最后推翻元朝当上了皇帝，定了多少规章制度，明朝的规章制度由他定下来，基本上没有什么太大的改动。
-- 发言者3认为人的因素最大，改变时势一定是出现一个人。
-- 发言者2称朱元璋天分相当高，举例李云龙没上过军事院校能打仗，会打仗的人打仗，不用看兵书，天赋。
-- 发言者1提到朱元璋的选择有点逼上梁山的性质，好友汤和让他去参加起义军，他在庙里犹豫，怕被杀头，后来因为信差送信被人告发，没办法只能去起义。
-- 发言者2称历史最重要的是你一定要弄明白它是发生过的，当年那是造反，于他而言是非常有风险的事儿。
-- 发言者3称历史你回过头看谁都是一个聪明人，你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
-- 发言者3称明朝有仁宣盛世，晚明时尽管史书上一再说政治如何黑暗、皇帝如何不上朝，但老百姓生活很好。
-- 发言者4提到金瓶梅写的西门庆是一个阶层。
-- 发言者2称明末那段时间很多真相是被掩盖的，市民生活特别轻松舒服，想去哪去哪，连皇册都不用了，到处走，去给人打工；当年江浙一带兴起了工商业，给人当雇工活得很滋润；三言二拍这种娱乐产品的出现说明有能够养活自己的资本；后来李自成闹起义是因为陕西那一带发生了大规模的灾荒。
-- 发言者3称从当时器皿可以看到人的生活乐趣，明末工艺变得非常精细，有点像日本的工艺，日本派了大量工匠跟中国交流。
-- 发言者2称看到的史料穿什么都有，至少江南那一带确实非常富足。
-- 发言者3称文征明、唐寅、董其昌都是那个时期的人。
-- 发言者3称一到朱搭的时候，八大山人明末了，画的都是翻白眼，前面无文化派的人画的都是小桥流水。
-- 发言者2称历史经验教训说多少次了，我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-- 发言者2称历史那个事儿发生的时候是有背景的，你不比前人聪明，甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
-- 发言者2称史书上记载下来是照片，而实际上古人的生活都是录像，你不知道为那一幕之前跟之后是什么，不知道当时为什么要做这个选择，所以千万不能套用，套用那一定要倒霉。
-- 发言者2称明代这个朝代很有趣，什么事都有，宦官专政魏忠贤、刘瑾，文官专政张居正，皇帝专政朱元璋、朱棣，谁都可能当老大，而且什么都能发生，皇帝出去了还能回来了，还能做皇帝。
-- 发言者2称晚明时期吴三桂跟满清合作要入关，陈圆圆是一个原因，还有一个原因是他认为崇祯死了，当时说法是我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝。
-- 发言者2称1644年明朝灭亡那一年，李自成军打到京城没有人抵抗，因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天看疙瘩瘟就是天花。
-- 发言者3称中国的历史王朝300年都是大限，一逼近300年的时候你自己就没就完了。
-- 发言者3称中国历史上如果严格讲跨过300年大限的只有宋朝，南北宋接上以后，退让了大半个国土，保证了它延续了319年；汉朝中间隔断14年是彻底空的；唐朝明朝清朝都没跨过这个界限。
-- 发言者2称今天数世界上公司超过276人的有几家呢，没有几家，明朝做公司多大摊子几千万人。
-四、明朝皇帝与晚明社会
-- 发言者1提到一种观点说明朝和清朝在美这方面，故宫金碧辉煌大红大紫是满族人的趣味，真正明朝不是这样。
-- 发言者3称宋明两个朝代是典型的汉人政权，汉人是文人政权，对美的判断不是表象的；满族是异族，对美的判断都是表象的；今天凡是那种非常外在美直观能看到美的都卖得非常贵，但在100年前晚清到民国初年的收藏，这种东西都不值钱，一定是素雅的。
-- 发言者2称明朝皇帝是九五至尊，但皇上说要去一趟江南，大臣说不行就不行，明武宗正德皇帝要去，不让去，全跪金水桥前面，后来气坏了到锦衣卫去打，打死了十几个，还是不让去。
-- 发言者1提到明朝有些史官就是要跟皇帝说点难听的，让你砍我的头，这样我青史留名，冒死就为了个名。
-- 发言者3称这就是文化的力量，文化的力量是一个超出我们想象的力量。
-- 发言者2称明武宗正德后来打服了一批人，非要去不去不行，到扬州说我要什么东西，政府说没有东西没有了，有也不给，皇帝不生气，说那我就回去，还让人准备酒席，然后说吃不了，你们把酒席折合成银两，我带回去。
-- 发言者3称正德皇帝是明朝整个皇帝中最特殊、最鬼怪的一个个性，过去对他的评价非常低，说他荒淫，豹房是他弄的。
-- 发言者1提到一个爱当木匠的皇帝，发言者3称那是天启，直接干活，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好，他成就感特大。
-- 发言者3称这从侧面反映了当时社会的一种时尚，当时家具在每个人心目中地位高，明式家具现在在国际上那么高的地位绝对不是偶然的。
-- 发言者2称明代皇帝本身确实也没什么事干，明神宗几十年不上朝，但他不出去。
-- 发言者2称但凡是明朝的皇帝，后人不会说前朝自己朝代的皇帝多差，正德特别差是因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以不能够把他写得太好。
-- 发言者2称正德皇帝被说特别荒淫，豹房其实就是玩的地方，里边养了豹子，有动物园，女人肯定是有的，但在后宫也是女人，不影响其他什么问题。
-- 发言者3称正德皇帝是有定论的说明朝最荒淫的皇帝，清朝最荒淫的是咸丰，咸丰还留了个种，正德不留种，没少找女人但没有生育能力。
-- 发言者3称正德皇帝对宫廷以外的女人都有兴趣，宫廷内的女人确实没兴趣，因为宫廷内的女人被训练过，禁忌太多，太保守。
-- 发言者2称据说正德去过，但没有具体的史料能够确实，史料没法记。
-- 发言者2称正德从江南回来，没有进京城，在通州先停了半天，先派人打探，这是史料记载的，先停在这儿，你们先给我把情况看清楚了，京城里有没有人想搞埋伏搞圈套，非常有城府。
-- 发言者2称明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般都有某些程度的偏颇，因为嘉靖上台先搞了个大礼仪事件，为这事死了很多人，为给自己父亲争个名分，他父亲是王爷，他要把他追封为皇帝。
-- 发言者1称很多人研究历史就有傲慢与偏见，没有设身处地，老觉得自己聪明，判断他昏庸无能。
-# 关键引语与金句
-&gt; 慢慢来才是最快的方法。
-&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 历史最重要的是什么呢？就是你一定要弄明白它是发生过的。
-&gt; 史书上记载下来是什么。照片，我打个比方是照片照片，而我们实际上我们的生活，古人的生活都是录像。
-&gt; 你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
-&gt; 文化的力量是一个超出我们想象的力量。
-&gt; 所有人按照自己的角色去做自己的事情，最节省成本了，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
-&gt; 我是商人就做商人的事儿，我是奶妈就做奶妈的事儿，我是王后就是王后的事，我什么都可以做自己的事，就是不管别人的事。
-&gt; 中国的文化精神是什么？是中庸。
-&gt; 日本的精神就恰相反，他坚持一个原则。
-&gt; 一个乞丐对有这个历史上有这种最底层的人坐到最上面独此一份。
-&gt; 他太不容易了，我们今天说你做个什么事能做成呢？这人从一乞丐一直到最后推翻元朝当上了皇帝。
-&gt; 历史你回过头看谁都是一个聪明人，你当时都不聪明。
-&gt; 原话引语……</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>14719/5104</t>
+          <t># 《大奥》与明史：中日文化差异及明朝兴亡探讨
+《大奥》与明史：中日文化差异及明朝兴亡探讨
+会议要点：本期锵锵三人行围绕日剧《大奥》与《明朝那些事儿》展开，嘉宾马先生、当年明月及主持人共同探讨了日本文化中的极端精神、忠诚文化、中日文化差异，以及明朝历史的魅力、朱元璋评价、明朝兴亡经验与明式家具等话题。当年明月认为《大奥》吸引他的是其中体现的严谨精神，并指出日本文化与中国文化存在极大不同，中国文化精神是中庸，而日本文化讲究做到极致。马先生提到《大奥》是继《大长今》之后最有影响的外国电视剧，并指出日本战后用30年时间成为世界第二经济强国（绝对量），这是全民族极端精神的体现。；关于明朝历史，当年明月表示明史资料最多是其写作原因，并认为朱元璋从乞丐到皇帝，其天分与不易值得推崇。马先生补充说明朝历史跌宕起伏，如土木堡之变、夺门之变等，本身就像现代版电视剧。讨论还涉及明朝兴亡的经验教训，当年明月提出“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，并指出明末市民生活轻松富足，江南工商业兴起，而李自成起义源于陕西大规模灾荒。；关于明式家具与皇帝评价，马先生认为明式家具在国际上地位高并非偶然，天启皇帝爱当木匠反映了当时社会对家具的重视。当年明月指出正德皇帝被嘉靖指派杨廷和编的《明武宗实录》写坏，其真实形象并非史料所载那么蠢，例如他从江南回来先在通州停留打探京城情况，显示其有城府。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>14719/608</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="9">
+    <row r="17" ht="13.5" customHeight="1" s="10">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>• 发言者 1 00:05
@@ -5070,31 +4889,30 @@
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者张学恒，48岁，成都人，在成都轻工研究所从事科研工作，本次就诊于消化专科。主诉上腹反复疼痛3个月，4年来经常发作、每年春天较多，心窝处有烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大，疼痛可忍受、白天发作、无夜间痛醒；曾出现两次黑大便，一次一年前、一次三个月前，均查大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后转黄；最近两个月吐过几次黄水样酸的东西，晚上胀想吐、吐后舒服。既往16岁得过甲肝、在三医院住院一个月、出院各项指标正常，对磺胺药过敏，无手术史。医生表示等检查资料更全面后再判断是否需要手术，能药物控制治好就不用手术；要求患者留大便做检查，胃镜预约在后天进行，并将在总结情况后向上级医生张医生汇报再讨论治疗。
+48岁男性患者张学恒，因上腹心窝处反复烧灼样疼痛4年、近3个月加重，就诊于消化专科。疼痛与进食冷硬食物、工作紧张劳累相关，刺激性食物可诱发，近3个月存在完全不痛时段；曾于一年前和三个月前两次出现黑便，均住院确诊为大便出血，住院两三天后大便转黄；近两个月呕吐数次，吐出黄水样酸味物，无呕血。既往有甲肝史（16岁，已愈）、磺胺药过敏史，家族中婶婶（无血缘关系）患胃癌。医生初步考虑消化道出血及胃部病变可能，建议留大便检查并预约后天胃镜，待向上级张医生汇报后商定治疗方案。
 # 诊断与检查结果
-医生本次未给出明确诊断结论，表示等检查资料都更加全面以后再判断是否需要做手术，临床上有很多药物对消化系统疾病有很好的治疗效果，若能用药控制病情治好就不用做手术。关键检查方面，患者曾两次因黑大便查大便提示大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后大便转黄；最近三个月大便均为黄色、无灰色大便，小便正常。患者自述有低血压约90/60，父亲76岁也有低血压；母亲75岁诊断冠心病、吃药控制较好。本次就诊尚未做检查，医生要求留大便做检查以了解有无相关出血，并安排胃镜及活检。
+本次就诊未进行胃镜及大便检查，医生根据病史初步判断需排查消化道出血及恶性病变可能。患者曾于一年前和三个月前两次黑便，住院检查均确诊为大便出血，住院两三天后大便转黄；近三个月无黑便，大便黄色正常。既往16岁患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；对磺胺药过敏（左手起红疹，持续半个月）。医生建议留大便样本检查出血，并预约后天行胃镜及活检。
 # 治疗方案与医嘱
-用药方案：患者自述最近一直吃药，先服“大叔”，刚开始一天两次、每次一颗有效，后效果越来越差、量加至每天四五次仍不好；又开过武汉药厂国产`奥美拉唑`和`阿莫西林`，还吃所里医务室配制的胃炎合剂，反复用药反复发作。治疗计划：医生要求患者留大便做检查，因曾两次黑便需了解有无相关出血；胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结情况向上级医生张医生汇报后再商量下一步处理意见，是否需要手术待检查资料更全面后判断。生活注意事项：医生指出经常熬夜对疾病有一定影响，**以后还是得注意**；**抽烟对疾病有影响，应尽量少抽或不抽**，患者已限制在10支以内并想慢慢戒；**酒对胃上的疾病影响挺大**，患者有便血情况，以后需注意；医生建议尽量少喝酒、若能戒烟对疾病有好处。
+患者近期自行服药情况：最初服用某药（可能为“达喜”类）有效，后效果变差并加量至每日4-5次仍不佳；后加用国产奥美拉唑（武汉药厂）和阿莫西林，以及单位医务室自配胃炎合剂，效果短暂，停药后复发。医生建议戒烟、少饮酒，注意休息，避免劳累熬夜。**重点禁忌：磺胺药过敏，禁用磺胺类药物**。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 大叔 | 最初每次一颗，后加量 | 最初一天两次，后加至每天四五次 | 口服 | 刚开始有效，后效果越来越差，加量后效果仍不好 |
-| 奥美拉唑 | 未明确 | 未明确 | 口服 | 武汉药厂国产；刚开始吃有些效果，停药后反复出现疼痛 |
-| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同开，具体剂量频次未明确 |
-| 胃炎合剂 | 未明确 | 未明确 | 口服 | 所里医务室自己配制，效果反复 |
+| 奥美拉唑（国产，武汉药厂） | 未明确 | 未明确 | 口服 | 效果短暂，停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑联用 |
+| 胃炎合剂（单位医务室自配） | 未明确 | 未明确 | 口服 | 效果短暂，停药后复发 |
 # 复诊与预警信号
-复诊时间：胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结患者情况后向上级医生张医生汇报，再回来与患者商量下一步处理意见。需立即就医的预警信号：原文未明确列出具体预警症状，医生要求患者留大便做检查，因曾出现两次黑便，需了解有无相关出血。</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>8519/1371</t>
+胃镜预约在后天进行，以便患者爱人陪同，胃镜活检后正好张大夫查房。医生将总结病情后向上级张医生汇报，再商定下一步处理意见。⚠️ 若再次出现黑便、呕血、剧烈腹痛等预警症状，需立即就医。</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8519/884</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="9">
+    <row r="18" ht="13.5" customHeight="1" s="10">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:05
@@ -6045,54 +5863,30 @@
       <c r="C18" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系国家开发银行因与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，对本案公开开庭审理，各方当事人均已到庭，法庭准备工作就绪。庭审围绕三个争议焦点展开调查辩论：一是抵押权与融资租赁所有权冲突及善意取得，二是罚息、复利计算，三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，依据《中华人民共和国民事诉讼法》第一百三十四条第一款、第一百六十九条的规定公开开庭审理。庭审围绕抵押权与融资租赁所有权冲突、罚息复利计算、违约金三个争议焦点展开法庭调查与辩论。合议庭休庭评议后提出调解方案，各方当事人均无异议并签署调解协议，本院予以确认并出具调解书。
 # 原告诉称与被告辩称
-见下表。
+各方主张对照如下：
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利计算及违约金请求 | 已按人民银行规定程序完成贷款抵押刑事审查、资料审查、法律审查；2018年9月查询曲靖电力公司租赁情况无融资租赁登记；2018年核查表（证据108页）显示曲靖电力公司名下仍无融资租赁登记；评估报告明确曲靖电力公司在建工程价值5.7亿、机械设备价值5.1亿；设备为通用设备无唯一标识，只能对抵押人名下信息调查；抵押设备金额、使用上均明确为曲靖电力公司；借款合同第24条第三项约定千分之一违约金，东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约 |
-| 被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司 | 主张2018年6月13日宣布贷款提前到期不符合合同约定，未给合理期限；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金，应予驳回 | 2015年12月2日邮件发送时间与2015年12月20日签订抵押合同时间吻合；统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务；借款合同第24条第二款第二项约定宣布提前到期应发通知并限期偿还，限期偿还与立即偿还概念不同；人民币利率管理规定第21条针对贷款期内不能按期支付的利息计收复利，不包括逾期罚息；东源公司以煤炭开采为主营业务，2015年下半年资金链断裂，2019年2月19日破产重整受理时负债76.2亿元，2016年去产能安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠 |
-| 被上诉人招银金融租赁有限公司 | 主张国开行未查询人行征信中心融资租赁登记，不构成善意；东源煤电出资行为系无权处分；招银租赁2012年即取得租赁设备所有权 | 2012年8月对东源煤电相关设备进行物权确权审查，要求提供六项设备买卖合同、大部分发票及到货确认单；设备交付到货即取得所有权，招银租赁同时获得租赁设备所有权；国开行2015年办理抵押登记，时间在后且未进行相应审查义务；融资租赁登记系统初始登记附件清单载明设备名称、数量、进场时间、生产厂商及存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台；设备唯一标识码非必填项，暗设五套设备当时刚交付无唯一识别码故未登记 |
+| 原告（上诉人：国家开发银行） | 请求确认对案涉设备享有抵押权，主张罚息自2018年6月13日起算，复利按合同约定计算，东源煤电应支付违约金。 | 已按人民银行规定查询曲靖电力公司名下融资租赁登记信息，未发现登记；设备为通用设备无唯一标识，已尽合理审慎义务，构成善意取得；合同第六条第四款约定罚息计收复利；合同第24条第三项约定违约应支付千分之一违约金。 |
+| 被告（被上诉人：云南东源电力、曲靖电力） | 主张国开行未履行告知义务，罚息不应计收复利，宣布贷款提前到期应给合理期限，违约金无合同依据。 | 2015年12月2日邮件已履行告知义务，抵押设备名称以红色标注；人民币利率管理规定第21条仅规定贷款期内利息计收复利；合同约定限期偿还而非立即偿还；国开行未举证违约行为且未履行限期纠正程序。 |
+| 第三人（招银租赁） | 主张对案涉六项设备享有所有权，国开行不构成善意取得。 | 2012年已取得设备所有权，国开行2015年办理抵押时未查询融资租赁登记系统，不构成善意；东源煤电出资行为系无权处分。 |
 # 举证与法庭调查
-## 一、举证与质证
-### （一）国开行举证
-1. 2018年9月对曲靖电力公司租赁情况的查询证书（第五组证据第一项），用以证明已对融资租赁登记信息进行核查。招银租赁质证认为该查询证书不符合要求，根据201493号中国人民银行关于融资租赁登记系统规定，国开行在操作抵押时点未查询人行征信中心结果，无论以设备名义还是以电力公司名义查询，均未进行相应查询。
-2. 证据四冶合成58亿，含东源煤电公司、曲靖电力公司对案涉设备的权属证明，用以证明设备所有权确属曲靖电力公司。
-3. 2018年核查表（证据108页），用以证明2018年再次核查曲靖电力公司名下仍无融资租赁登记信息。
-4. 2015年12月2日邮件及统计表，东源方用以证明已告知设备融资租赁情况。国开行质证认为该邮件正文及附表均无设备存在融资租赁的文字，统计表中招银租赁一栏记载的融资额度及抵押类型为不动产抵押，看不出东源方履行过告知义务。
-### （二）东源方举证
-1. 2015年12月2日邮件及融资情况表，主张邮件发送时间与2015年12月20日签订抵押合同时间吻合，统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务。
-2. 东源公司经营困难情况说明：以煤炭开采为主营业务，2015年下半年出现资金链断裂，2019年2月19日人民法院受理破产重整时点负债高达76.2亿元，2016年响应去产能政策安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠。
-### （三）招银租赁举证
-1. 一审提交证据7页回租设备清单，载明设备名称和生产厂家，未提及设备型号。国开行质证认为即便提交该清单，开行角度亦无法对设备进行同一性测试；清单提示2012年3月1日，而抵押设备铭牌记载生产日期均在2013年以后，部分为2013年11月、2013年12月、2014年3月，看不出是同一设备。
-2. 2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4个亿且已实缴。国开行认为招银租赁有理由知道或应当知道设备出资情况。
-3. 融资租赁登记系统初始登记附件清单，含设备名称、数量、进场时间、生产厂商及存放地点，显示存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台。
-## 二、法官询问要点
-1. 合议庭询问各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果。国开行认为系行业强制性规范，目的是防范动产设备多处抵押或融资冲突；招银租赁认为系行业性质、非物权法定登记，仅强化动产权利外观、可能产生对抗效力，不影响所有权设立转移；东源方认为系行业指导性规范文件，非强制性，不当然产生物权后果。
-2. 合议庭询问央行金融租赁查询方式能否保证查询到登记结果。国开行称能使用的查询方式就是查询单位；招银租赁称可通过公司名称或设备两种方式查询，以设备查询涉及种类物区分问题。
-3. 合议庭询问设备唯一标识码是否为必填项。招银租赁称不是必填项，发电机组铭牌只有型号和参数，无发动机号类唯一标识；暗设五套设备当时刚交付、无唯一识别码，故未登记。
-4. 合议庭询问国开行内部风控是否规定必须查询、未查到是否需将未查到单据作为风控材料。国开行称办理动产抵押时需调查该系统并筛查，因无表现故未保留筛查记录，内部无此规定。
-5. 合议庭询问国开行认为未查到登记结果即可免责的逻辑。国开行称按央行规定查询融资租赁系统，抵押人为曲靖电力公司，查询后系统无记载，2018年6月截图亦无显示，至今无结果，说明行为无过失。
-6. 合议庭询问若通过其他渠道知道抵押设备存在租赁是否仍需查询。招银租赁称仍需通过央行系统查询，央行规定出台背景是实践中大量存在此类案例，只有确定标准才能衡量双方是否善意。
-7. 合议庭询问各方如何看待因不同登记机构产生登记瑕疵。国开行认为涉及人民银行融资租赁登记系统与动产抵押登记的冲突，系统信息不完整、体系相互隔离、信息不流畅，未形成相互联通，可能带来交易风险；东源方称非专业机构，提供不了相关建议；招银租赁认为规范不统一、登记机构不统一、信息不对称，建议从立法层面统一对金融主体和市场主体要求，发挥行业协会作用，从操作和技能方面推动登记平台统一化。
-## 三、双方辩论的争议焦点
-1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已尽合理审慎义务、构成善意取得；东源方主张邮件已告知且设备名称相同并用红色标注、国开行应尽注意义务；招银租赁主张2012年即取得设备所有权、国开行2015年办理抵押时未查询登记、不构成善意。
-2. 罚息、复利计算：国开行主张利息自2017年12月21日至2018年6月12日合计2179万5727.08元、罚息自2018年6月13日至2019年2月19日合计4105万零579.57元、复利自2018年3月21日至2019年2月19日合计191万8206元；东源方主张2018年6月13日宣布贷款提前到期不符合合同约定、未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
-3. 违约金连带责任：国开行主张依借款合同第24条第三项约定应支付千分之一违约金、东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约；东源方主张国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金、应予驳回。
+一、举证与质证情况。国开行提交证据包括：2015年12月2日邮件及附表、工商部门出资证明、设备权属证明、人民银行征信中心查询结果、2018年核查表（证据108页）等，用以证明已尽审查义务、构成善意取得抵押权。招银租赁提交证据包括：回租设备清单（证据7页）、2013年和2015年审计报告（证据82页、95页）等，用以证明其2012年已取得设备所有权、国开行未查询融资租赁登记系统不构成善意。东源公司提交2015年12月2日邮件及截屏，主张已履行告知义务。质证中，国开行认为邮件及统计表不能证明告知义务已履行，统计表中招银租赁抵押类型记载为不动产抵押，与融资租赁概念不同；招银租赁认为国开行2018年9月查询证书不符合2014年93号文要求，且抵押时点未进行查询；东源公司认为邮件发送时间（2015年12月2日）与抵押合同签订时间（2015年12月20日）吻合，且抵押设备名称以红色标注，国开行应尽注意义务。二、法庭询问要点。合议庭询问各方对中国人民银行征信中心融资租赁登记性质及法律后果的理解；询问国开行贷款前审查是否内部规定必须查询融资租赁系统并保留未查询结果单证；询问招银租赁融资租赁登记系统中设备唯一标识码是否必填项；询问国开行与招银租赁查询方式能否保证查询到登记结果；询问各方对因不同登记机构产生登记瑕疵的意见。三、双方辩论焦点。关于抵押权与所有权冲突，国开行主张已按人民银行规定查询曲靖电力公司名下融资租赁登记信息，未发现登记，且设备为通用设备无唯一标识，已尽合理审慎义务，构成善意取得；招银租赁主张国开行未在抵押时点查询融资租赁登记系统，不构成善意，且东源煤电出资行为系无权处分；东源公司主张已通过邮件履行告知义务。关于罚息复利计算，国开行主张罚息自2018年6月13日起算，复利按合同第六条第四款约定计算；东源公司主张罚息不应计收复利，且宣布贷款提前到期应给合理期限。关于违约金，国开行主张依合同第24条第三项约定，东源煤电未配合办理账户管理及柜台签约手续构成违约，应支付千分之一违约金；东源公司主张国开行未举证违约行为，且未履行限期纠正程序。
 # 庭审结果
-本案争议焦点为三项：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息、复利计算；三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字。经本院主持调解，各方当事人自愿达成调解协议，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。调解方案主要内容：确定国开行对东源公司债权扣除破产中已清偿本金外，利息2017年12月21日至2018年6月12日合计2179万5727.08元、罚息2018年6月13日至2019年2月19日合计4105万零579.57元、复利2018年3月21日至2019年2月19日合计191万8206元，三项共计6474万4513元；确定招银租赁对涉案六项设备享有所有权、对应债权数额1377万4137万元，确定国开行对93项设备有抵押权，双方对案涉全部发电设备整体盘活处置并从变现款中实现各自债权，生效20日内由国开行向一审法院提出执行申请启动司法变现，变现价格双方各50%、实现费用双方各担50%；变现款不足清偿债务或变现后招银租赁未实现债权，在执行法院处具体本裁定后按破产重整计划中预留方案实现债权，破产管理人对招银租赁债权予以纳入预留方案，由东源煤电按此前招银租赁在东源煤电破产重组程序中有担保清偿方案予以清偿；如司法变现不能实现国开行和招银租赁权益，通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营；各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认；一审诉讼费用中对于国开行诉请部分按一审判决执行，对于招银租赁诉请部分诉讼费由二审法院按规定根据证据确定，二审诉讼费由本院依法确定。合议庭指出本案涉及生产设备的动产抵押权与融资租赁物所有权冲突是司法实践中普遍性难题，金融风险防控还有较大空间，根本原因在于国家还未建立统一的动产登记制度，现有动产融资租赁登记系统和动产抵押登记系统缺乏有效衔接，将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议，共同推进国家治理现代化。</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t>30731/4434</t>
+本案争议焦点为：一、国开行对案涉设备是否享有抵押权及是否构成善意取得；二、一审判决对案涉借款罚息、复息的计算是否正确；三、东源煤电、东源煤业是否应连带给付违约金。经合议庭评议并征求各方意见，提出调解方案：确定国开行对93项设备有抵押权，招银租赁对6项设备有所有权；招银租赁和国开行对案涉全部发电设备整体盘活处置，并从变现款中实现各自债权，变现价格双方各50%，实现费用双方各担50%；若司法变现不能，双方放弃对案涉设备权益，由东源曲靖电力自主生产经营；各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认；一审诉讼费中国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定确定，二审诉讼费由本院依法确定。各方对调解方案均无异议，签署调解协议，本院出具调解书。</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30731/2011</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1" s="9">
+    <row r="19" ht="13.5" customHeight="1" s="10">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:25
@@ -6194,33 +5988,22 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t># 候选人概况与面试岗位
-本次为公务员面试模拟，面试共20分钟、回答4个问题，考生确认准备好后由计时员计时，题纸和草稿纸可用但不得在题纸上做任何记录。考生依次作答四题：第一题围绕骏马、风筝、陀螺三句绳子意象谈对公务员工作的启示；第二题以市政府办公室工作人员小王身份谈如何组织本市AI相关企业调研；第三题以市级服务标兵小王身份现场模拟答复记者关于地下排水管道返堵的质疑；第四题从公共服务角度谈道路改造与雨污分流工程扰民矛盾的处理思路。四题均作答完毕，考官询问是否还有需要补充的内容，考生表示没有要补充的，面试到此结束。
-# 能力评估
-按专业/技术能力、项目经验、沟通协作三个维度评估，评级与依据见下表。
-| 评估维度 | 推荐评级 | 评估依据（具体事例） |
-| --- | --- | --- |
-| 专业/技术能力 | 良 | 第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省（吾日三省吾身）、权利与责任（权利清单、责任清单）、连轴转的动力（基层与机关加班加点、材料撰写中的责任感与成就感）；第二题提出查阅国务院、中央办公厅人工智能发展指导意见及省厅相关举措，制定包含客观与主观两方面、分市场状况、服务需求、管理措施三部分的调研方案；第四题区分主要矛盾与次要矛盾并提出防噪墙、洒水降尘等具体措施。 |
-| 项目经验 | 中 | 第二题以市政府办公室工作人员小王身份提出AI相关企业调研的组织实施思路：先补课充实AI知识储备、学习兄弟城市调研经验、摸清上级领导和中央部门指示要求；与企业对接阅读发展报告、制定调查问卷并请单位AI专家学者修改完善、以座谈会形式听取企业意见，询问人才对口引进、政策倾斜、用地审批、人才吸引机制和长效培养机制等具体服务需求。 |
-| 沟通协作 | 良 | 第三题现场模拟答复记者时先询问记者姓氏并自称片区负责人小王，说明管道为上世纪90年代社区集中整治时所修建、城区属老城区改造难度大、夏天用水高峰问题集中出现，表示已联系维修师傅正赶往现场维修，长久管道硬件问题已汇报上级部门，将通过城市综合保障工程完善硬件、改善基础设施，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题提出通过交通广播推荐出行路线、加强宣传引导市民多使用公交、以公告形式在网络上发布政府举措。 |
-| 应变与时间管理 | 中 | 面试共20分钟、回答4个问题，考生确认准备好后由计时员计时；第四题作答中收到“离本场考试结束还有3分钟”提示，考生误称“考生开始回答第三第四题”，随后完成作答；考官询问是否还有需要补充的内容，考生表示没有要补充的。 |
-| 岗位匹配度 | 良 | 第一题提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第三题承认工作有失职之处，希望媒体给予改进机会；第四题提出将政府各种举措公正公开透明表达出来以获得市民理解和支持。 |
-| 面试表现 | 良 | 四题均作答完毕，第一题、第二题、第三题、第四题均以“考生作答完毕”结束；第三题以现场模拟方式完成答复；第四题因时间提示未进一步展开。 |
-| 潜在风险点 | 中 | 第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”。 |
-# 综合素质
-突出亮点：第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省、权利与责任、连轴转的动力，并引用“吾日三省吾身”，提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第二题提出先补课充实AI知识储备、学习兄弟城市调研经验、查阅国务院及中央办公厅人工智能发展指导意见与省厅相关举措，制定包含客观（企业发展现状）和主观（政府应提供的服务需求）两方面的工作方案，分市场状况、服务需求、管理措施三部分调研，方案呈报领导审阅后按意见修改实施；第三题现场模拟中承认工作有失职之处，希望媒体给予改进机会，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题区分主要矛盾（时间上过去、现在和未来的诉求和需求不满足）和次要矛盾（噪音污染、出行问题、舆论问题），提出防噪墙、洒水降尘、交通广播推荐路线、引导市民多使用公交、以公告形式在网络上发布等具体措施。潜在风险点：第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”，且因时间提示（离本场考试结束还有3分钟）未对第四题作进一步展开。推进建议：原文未提及。</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>5808/1866</t>
+          <t># 公务员面试：四题综合能力考察
+公务员面试：四题综合能力考察
+会议要点：本次面试围绕四道题目展开，考察考生的综合分析、计划组织、应急处理和公共服务能力。第一题要求考生从骏马、风筝、陀螺的绳子比喻中提炼对公务员工作的启示，考生分别联想到自我反省、权利与责任平衡、工作动力，并联系公务员实际工作展开论述。第二题模拟市政府办公室工作人员小王调研本市AI企业，考生提出前期准备（补课、学习兄弟城市经验、查阅上级文件）、制定方案、实施调研（企业对接、问卷、座谈会）及管理措施调研等步骤。第三题模拟答复记者关于管道问题的投诉，考生解释管道为90年代老城区建设、已联系维修并汇报上级，同时承认工作失职并请求媒体解释。第四题从公共服务角度分析道路改造矛盾，考生区分主要矛盾（时间）与次要矛盾（噪音、出行、舆论），提出加快工程、降噪降尘、建议便道、交通广播、宣传公交、公告沟通等措施。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5808/393</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="9">
+    <row r="20" ht="13.5" customHeight="1" s="10">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:11
@@ -6284,45 +6067,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t># 参观概况
-本次讲解沿故宫中轴线及东西六宫展开，依次介绍午门、太和门广场、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、东筒子夹道、延禧宫、景仁宫、御花园、神武门等景点。午门为排队检票处，明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官；太和门广场五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。太和门为明朝御门听政处，门口铜狮为故宫六对铜狮中最大一对；太和殿即金銮殿，用于皇帝登基、皇后册封等盛大典礼，文武百官文东武西，西边弘义阁为皇帝银库，东边体仁阁为缎库。中和殿为典礼时皇帝休息室，保和殿自乾隆五十四年起为科举殿试考场。乾清门为皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边为军机处；乾清宫为皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。交泰殿放25块传国玉玺，坤宁宫住皇后，明朝所有皇后都住此。储秀宫为慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，其子在此出生；慈宁宫为康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真；珍宝馆也是宁寿全宫，为乾隆给自己修建的养老院，退休后没放权仍照常上朝，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室。神武门为紫禁城北门，出门左手边有两个盖章点。讲解者总结三条游览路线，并标注七个可以免费盖章的位置。
-# 核心看点与讲解
-## 午门与太和门广场
-午门是排队检票处，明朝皇帝在此杖打犯错大臣，清朝在此颁朔；午门明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官。太和门广场有五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。
-## 太和门与太和殿
-太和门是明朝皇帝御门听政处，门口铜狮子是故宫六对铜狮中最大一对，建议不要站在底下合影。太和殿即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封；文武百官在太和殿广场朝拜，文东武西。西边弘义阁是皇帝银库，东边体仁阁是缎库。
-## 中和殿、保和殿与汉字馆
-中和殿是盛大典礼时皇帝休息室。保和殿从乾隆五十四年起为科举殿试考场。保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章；故宫不止一处可买紫禁城100，每家店印章不同，买了之后不能去其他店铺盖章，汉字馆印章数量据说最多，可邮寄或自背。
-## 乾清门与后宫区域
-乾清门是皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边是军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫不该看不该听。进门后乾清宫是皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。门口铜鹤铜龟旁有设计江山金殿，是紫禁城最小宫殿。
-## 交泰殿、坤宁宫与御花园
-交泰殿放25块传国玉玺。坤宁宫住皇后，明朝所有皇后都住此。坤宁宫东北角文创店有5枚免费印章。御花园有钦安殿，供奉真武大帝。
-## 储秀宫、慈宁宫与冰窖书吧
-储秀宫是慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，她儿子在此出生；旁边文创店有3枚免费印章。往南是翊坤宫和永寿宫，永寿宫西边太极殿是东西六宫唯一被称为殿的。慈宁宫是康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。冰窖书吧有3枚免费印章，印章造型好，讲解者在此买了冰嬉图。
-## 断虹桥、武英殿与文华殿
-断虹桥是网红打卡地，石狮子形态各异，最有名的是武当狮。断虹桥往西是武英殿，后改陶瓷馆，目前关闭只能在门口看。往东穿过太和门广场到文华殿，讲解者去时未开，据说现在有展览。
-## 箭亭、钟表馆与珍宝馆
-箭亭是清朝皇帝及子孙练习骑马射箭处，旁边商店可买文创雪糕。钟表馆展示各年代钟表。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真。珍宝馆不是单独展厅，院子周围屋子都可进；游客太多，看凤冠没点技术挤不进去。珍宝馆也是宁寿全宫，乾隆给自己修建的养老院，退休后没放权仍照常上朝。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室，有二龙仙楼设计。再往后是珍妃井，井口石小眼不是珍妃进去的地方。珍宝馆出口右手边商店有3枚免费印章。
-## 东筒子夹道、延禧宫与景仁宫
-东筒子夹道是很多小姐姐喜欢来的拍照出片地。往南拐弯到网红打卡地延禧宫，旁边景仁宫是甄嬛被封熹妃时住处，珍妃也住过。逛完景仁宫可去御花园。
-## 神武门与盖章点
-神武门是故宫紫禁城北门。出门左手边有两个盖章点：角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
-# 互动与体验
-讲解中介绍了多处盖章体验：保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章，讲解者称这感觉真是盖了帽了，并提到故宫里不止一处可以买到紫禁城100，每家店里的印章有所不同，买了之后不能去其他店铺盖章，据说汉字馆印章数量最多，盖完可选择邮寄到家或背着走。坤宁宫东北角文创店有5枚免费印章。储秀宫旁边文创店有3枚免费印章。冰窖书吧有3枚免费印章，讲解者称盖章时有批折子的感觉，并在此买了一个冰嬉图。珍宝馆出口右手边商店有3枚免费印章。神武门出门左手边角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。讲解者还提到箭亭旁边商店可买文创雪糕，并询问雪糕上的人物是谁。讲解者建议不要站在太和门铜狮子底下合影，单独给它拍张照即可。
-# 收获与建议
-讲解者总结三条游览路线：第一条走完视频内所有景点，早起排队一进门沿中轴线往后走，可错开旅游团，适合打算待一整天的朋友，一天走了3万步，注意休息补水；第二条进门沿中轴线往后走，看完坤宁宫去景仁宫和延禧宫，再逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天；第三条适合时间有限不想走太多路，进门沿中轴线往后走，看完坤宁宫去储秀宫，出来去御花园，从神武门出，预计2小时左右。视频标注了七个可以免费盖章的位置，有需要的章友可截图保存。讲解者强烈建议来珍宝馆，并提醒珍宝馆游客太多，看凤冠没点技术挤不进去。</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>4497/2520</t>
+          <t># 故宫保姆级游览攻略讲解
+故宫保姆级游览攻略讲解
+会议要点：本次讲解围绕故宫游览攻略展开，覆盖午门、太和门广场、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、寿康宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、九龙壁、宁寿宫、珍妃井、东筒子夹道、延禧宫、景仁宫、御花园、神武门等主要景点，并介绍各处的历史背景与看点。；讲解中介绍了故宫内七个免费盖章点：坤宁宫东北角文创店5枚、储秀宫旁文创店3枚、冰窖书吧3枚、珍宝馆出口商店3枚、角楼咖啡2枚、故宫文创2枚，以及保和殿东北角汉字馆4枚。；讲解最后总结三条游览路线：第一条适合全天游览，早起排队沿中轴线走完所有景点，约3万步；第二条半天路线，中轴线后看景仁宫、延禧宫、钟表馆、珍宝馆，御花园后神武门出；第三条最省力，约2小时，中轴线后看储秀宫、御花园，神武门出。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4497/379</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="9">
+    <row r="21" ht="13.5" customHeight="1" s="10">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:15
@@ -6463,27 +6223,23 @@
       <c r="C21" s="4" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈走访了农村老人、村干部与民政局干部、城市社区社工等对象，目的是了解农村养老制度与城市社区养老经验，探讨解决乡村养老问题的启示。核心议题包括留守老人与独居现状、农村养老政策与困境、城市社区志愿者制度与养老服务中心、社工制度困境。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住；农村方面2021年公安数据为73万多、占比约17.8%，预计老龄化程度会越来越严重。受访者普遍反映独居老人存在无人照料、无人慰藉、就医困难等问题，农村空巢老人面临无亲人陪伴、经济困难、子女不在身边、生病住院麻烦、娱乐方式少等困境，城市社区则以志愿者一对一帮扶和养老服务中心应对，但社工制度面临需求大而供给不足、资金有限、专业人才欠缺的困境。整体反馈基调为如实陈述现状与困难，并呼吁政府、子女、社区及专业养老服务机构共同关怀。
+本次访谈对象包括农村留守老人、村政府和民政局干部、城市社区养老社工等，访谈目的是了解农村留守老人养老现状、政策困境及城市社区养老服务经验。核心议题涵盖独居老人无人照料、就医困难、意外风险，农村养老政策实施情况，以及城市社区志愿者制度、养老服务中心和社工服务。整体反馈基调呈现农村养老资源不足、政策覆盖有限，城市社区服务相对完善但社工供给不足，受访者普遍表达对改善养老服务的期待。
 # 核心反馈
-**独居老人无人照料、无人慰藉、就医困难**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住，独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自一人在家中发生意外。典型场景包括：黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认因一个人在家太寂寞、想找个人聊聊天才报了警；上海一名67岁独居老人在家中去世，直到多日之后家中满出刺鼻气味才被邻居发现；杭州一小区一名67岁独居老人不幸在家中去世，数天之后才被发现。
-**农村空巢老人经济困难、子女不在身边、生病住院麻烦、娱乐方式少**：村干部与民政局干部反映，空巢老人可能面临的问题第一是没有很多亲人来陪伴，第二是经济比较困难，这个地方经济不太发达，生病、锻炼等都受影响，子女不在身边一旦生病住院就比较麻烦，娱乐方式少，只能坐在一起聊聊天、打打牌。有受访者说：&gt; 现在80%都是都提醒这个在外面做做这些事的，年轻人都卖出去了。
-**农村养老公共设施运营经费后续没有支持**：干部介绍，之前其实也探索过在一些农村建养老公共设施，提供日托、休闲娱乐、沟通交友的平台，但不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的。
-**城市小区留守老人社交机会更少、易孤独抑郁**：相比之下，城市小区中的留守老人们与外界社交的机会更少，更容易产生孤独、抑郁等情绪。社工谈到曾帮助一位存在心理问题的老人，其与邻里关系处理不和谐、半夜摔门，社区派志愿者上门但老人出现抗拒，觉得周围的人都是陌生的、没有关心他的人，内心可能有一点仇恨式的；经日复一日关心照料后，现在与邻里关系还算好了，能够理解一些、也可以接受一些意见，之前是不接受任何人的建议的，他今天都打来电话说寂寞空虚、得不到人关注。
-**社工制度需求大而供给不足、资金有限、专业人才欠缺**：社工姐姐认为，目前社工制度的困境主要在于社会需求量大而供给不足，由于政府和社区资金有限，难以承担长期的专业社工服务费用，人民的需求得不到满足，大量社工迫于生计选择转行，这同时也阻碍着社工行业的长期发展。每个街道和乡镇派了两名社工驻点，主要围绕老人、小孩这一类去服务，但说实在话也很难能够走下来；社工行业工资都比较低，会影响就业率，基本上很多同学没做多久就垮了，可能不超过一年。服务需要花钱购买，不一定能够今年服务了、明年又能服务，要看领导能不能争取到这样的项目，一年的服务成效并不是那么的明显；资金拨不下来了，项目也结束了，但服务成效不一定就达到了。整个湖南省有这么大，这个街道也要花十来万块钱，省里还是拨了钱的，但很多社工并不是专业的、学社工专业出来的，在专业上其实还是很欠缺的。
+农村留守老人核心痛点：**无人照料**，65.5%的老人子女长期不在身边，独居老人存在无人照料、就医困难、意外风险等问题；**精神孤独**，黑龙江绥滨独居老人因寂寞报警，杭州67岁独居老人去世多日才被发现；**经济困难**，农村养老金118元/月，与工人养老金差距大，五保户分散供养生活费475元/月，残疾人低保分160、270、380元三档；**就医不便**，视障老人反映就医障碍。城市社区老人痛点：**社交机会少**，更易产生孤独、抑郁情绪；**心理问题**，社工帮助过一位与邻里关系不和谐、抗拒外界关心的老人。对现有解决方案的不满：农村养老公共设施运营经费缺乏后续支持，地方财政困难；社工工资低、转行率高，专业能力欠缺，项目资金不稳定，服务成效难以持续。
 # 关键洞察与建议
-核心洞察：农村与城市留守老人问题均突出，农村空巢老人受经济困难、子女不在身边、娱乐方式少等多重因素叠加影响，城市小区留守老人社交机会更少、更易孤独抑郁；农村养老公共设施建设存在只考虑建设、不考虑后续持续运营经费的问题；社工制度面临社会需求量大而供给不足、资金有限、专业人才欠缺、服务成效不易显现的困境。受访者提出的建议与偏好：一是请专业施工人进行陪伴；二是尽量倡导在外务工的子女多跟他们联系；三是丰富他们的文化生活，能够有更多的娱乐方式；四是希望老年协会能够专项执行、专门建养老设施，有一个固定的场地，定期可以有一些施工人员或宣传，如板报宣传或健康知识讲座，并要给一个持续运营的经费，不管考虑建设还要考虑后续的持续运营，才能更好地发挥作用。城市社区方面的做法与倾向：志愿者制度实行一对一帮扶，通过定期表彰、志愿者积分兑换、雷锋超市兑换礼品让志愿者长期坚持；今年做小手拉大手，从儿童青少年着手拉动家长加入；周四准备开展送春联活动，邀请书法老师写对联让孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴，让大家感觉社区就是一个大家庭；2023年的目标是家长他们自己来组织，社区作为一个协助者。受访者还表示，解决养老问题绝非易事，不仅需要政府的关心和重视，也离不开子女、社区乃至更专业的养老服务机构的耐心陪伴与关怀。</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>5309/2110</t>
+核心洞察：农村养老问题受多重因素叠加影响，包括子女外出务工、老人适应能力降低、城市对农村老人存在无形歧视；农村养老政策覆盖有限，五保户和残疾人保障标准较低，养老设施运营经费不足。建议：请专业施工人员进行陪伴，倡导在外务工子女多与老人联系，丰富老人文化生活，建立老年协会专项执行养老设施并保障持续运营经费；城市社区志愿者制度、一对一帮扶、积分兑换礼品、送春联、做月饼、百家宴等活动可借鉴，养老服务中心提供理疗、按摩、老年大学、心理咨询等服务；社工制度需解决供给不足、工资低、专业欠缺问题，政府应加大资金支持，保障项目持续性。受访者倾向性表达：老人需要关爱和陪伴，社区应成为大家庭，志愿者制度需长期坚持并发展新志愿者。</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5309/854</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="9">
+    <row r="22" ht="13.5" customHeight="1" s="10">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:30
@@ -7085,26 +6841,26 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t># 沟通概况
-本次372班家长会由班主任林瑞主持，面向全体家长，围绕费用与反诈、班级基本情况、教师团队、班级存在问题及解决思路、给家长的建议等板块展开。费用方面，书费预交11000元尚未结算，书箱未购买部分将退费，相关费用约100元或70元、4000元购买、700元、120元、123元等；明确不在微信群收取家长任何费用，费用由学生交给生活委员，并提醒家长和学生注意反诈。班级共60人，男生25人、女生35人，整体时间观念执行力强、班风关系良好、班风纪律好，少数同学周末玩游戏、懒散、思考能力差、自习课纪律差。家长代表张宇波校长分享家庭教育经验，家委会建议至少三人自愿报名，保险、电子学生证、学校资助等事项一并沟通。
-# 沟通内容
-**亮点**：整体来看，第一个月时间观念执行力加强，班风关系全部良好，班风纪律非常好，地面干净，卫生良好；写字还是不错的，学生手册可查看；老师多数是老教师、优秀教师、师范院校毕业，有3年以上经验，部分6年以上，各科老师认真备课、用心上课、关爱每一位学生。**需关注之处**：少数同学周末玩游戏、懒散，思考能力比较差，自习课纪律差，班主任在时较乖、不在时乱哄哄；个别学生行动时间方面有问题，书写需练字，建议家长买字帖；自习课效率比较低；存在玩手机、看小说、镜子、微信、网瘾、打游戏充值400元、直播、不健康内容、谈恋爱、QQ、抖音、快手等情况；手机管理要求每个手机贴名字，家长处理掉多余手机，周一到周五不定时打电话检查手机是否开机；班主任将加强人员管理和班委培训，自习时给10分钟讨论，继续加强思想教育，制定详细班规，严格请假制度，定期沟通。
-# 家长反馈
-家长代表张宇波校长分享家庭教育经验：要控制孩子的身体健康和心理健康，高中阶段仍是长身体的关键时期；先做人，让孩子学会做人，千万不能带上不良风气；家长对待孩子要有平常心，孩子面临的学习压力很大，对挫折和失败要帮助孩子重新定位；要尊重孩子，给孩子自由空间，不轻易下消极评价；多倾听、多交流，把更多关爱与理解给孩子；遵守学校制度，配合老师工作。张宇波校长原话：&gt; 无论怎样，那你都是爸爸妈妈心里最优秀的儿子。班主任林瑞反馈家长需配合支持占30%，建议避免过分关注孩子、认为孩子不需要学习、过分期望、放任不管、给过多钱等误区，关注心理健康、交通安全（未满16周岁骑电动车非常危险，可能载两三个）、运动安全、饮食安全、防诈骗、防溺水、防校园欺凌，学习上不懂就问、不与他人比较，创造良好环境、和睦家庭气氛、制定小目标、多鼓励少指责。
-# 共识与配合事项
-[明确家校达成的共识、后续配合措施及跟进计划，用 `- [ ]` 待办格式列出双方分工；课程名、作业名、工具名可用 `具体内容` 标注]</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>17334/1136</t>
+          <t># 372班家长会：家校沟通与班级管理
+372班家长会：家校沟通与班级管理
+会议要点：本次家长会由班主任林瑞主持，介绍372班基本情况（共60人，男生25人，女生35人），指出学生处于青春期不稳定时期，班级优点为时间观念执行力强、班风良好，缺点为少数同学周末玩手机、自习课效率低。教师团队多为老教师和优秀教师，班主任林瑞教地理，联系方式将发在群里。；针对存在问题，提出加强思想教育、严格班规管理、定期与家长沟通、制定班规、严格请假制度等计划，并给出家长建议，包括关注孩子心理、合理期望、多鼓励少批评。强调安全教育（未满16周岁骑电动车危险、防溺水、防诈骗、防校园欺凌）和心理健康关注。；费用方面，说明水费险、书费预交11000元未结算、书箱退款等，强调不在微信群收取费用，由学生交生活委员，提醒防诈骗。成立家长委员会，至少三人自愿报名。保险购买哪一家尚未确定，电子学生证办理的具体方案待定。
+关键决策：费用由学生交给生活委员，不在微信群转账。；要求收掉手机和镜子。；成立家长委员会，至少三人自愿报名。
+全员执行要点：班主任林瑞介绍班级情况、存在问题及解决思路，要求家长配合收掉手机和镜子，并强调费用由学生交生活委员。；有家长分享家庭教育经验，强调尊重孩子、多倾听、配合学校。
+风险与阻塞：少数同学周末玩手机、有网瘾。；个别学生书写差。；自习课效率低。；学生带镜子等违禁品。；学生看不良内容、谈恋爱。；未满16周岁骑电动车危险。；防溺水、防诈骗风险。；防校园欺凌风险。
+未决问题：保险购买哪一家尚未确定。；电子学生证办理的具体方案待定。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17334/676</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="9">
+    <row r="23" ht="13.5" customHeight="1" s="10">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:16
@@ -7181,33 +6937,35 @@
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t># 例会概况
-本次为10月28日周会，主题是总结工作，会议等级为自愿级，会议资料为工作报告、这班看法、这班型社区介绍，会议目标是初步统一成员意见、统一对社区的认识。会上讨论了工作报告与下周工作安排，提到项目创建学习资料并分为多个算术，服务定价权交给消费者，公司以前用传统方法现在用AI效率高质量好，需在实践中探索改进；还提到参加互联网加创业大赛、根据学校学习所需技能、实现教师改革，以及需要政府报告并符合要求、组建教育团队、确定路线、修订纲领章程。任务方面目前有四个任务，课程开发是其中之一，最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；大运发放需要调试，任务分配需安排，需招聘20多位师傅；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。学习介绍修改方面，把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号，服务时间还有工具需要改一下。待遇与角色方面，按照角色分为学生、教师、家长、学校、教育主管，待遇有上班5000、额外有奖励、还会有提成，周五半天加周末两天休假，需要公开的及时向当事人说明理由。会议时间已一个小时，决定会后线下继续一起学习；确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
+本次会议为10月28日周会，主题为总结工作，等级为自愿级，会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会议讨论了教育网站建设，计划将算术分为多个部分，并希望将服务定价权交给消费者，转变为代购模式。会议指出工作方向可能偏了，需要考虑工作量，需完成两个活动，下周工作安排，需要政府报告，组建教育团队，确定路线，修订纲领章程。目前有四个任务，其中最大任务是组建执法队伍，下个月主要任务即为此，大运发放需要调试，任务分配需讨论，招聘20多位师傅。待遇方面，上班5000元，额外有奖励和提成，休假为周五半天加周末两天。会议决定下个月主要任务是组建执法队伍，学习介绍已经弄完。下一步将邀请同事加入，并讨论是否修改会议纲要，是否报上上等问题。
 # 工作进展
-- 学习介绍修改：🔄进行中。已把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号；服务时间还有工具需要改一下。
-- 任务分配与课程开发：🔄进行中。目前有四个任务，课程开发是其中之一；任务分配需安排；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。
-- 组建执法队伍：🔄进行中。最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；需招聘20多位师傅。
-- 大运发放：🔄进行中。需要调试。
-- 待遇与角色：🔄进行中。按照角色分为学生、教师、家长、学校、教育主管；待遇有上班5000、额外有奖励、还会有提成；周五半天加周末两天休假；需要公开的及时向当事人说明理由。
-- 下一步：确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊；会后线下继续一起学习。
+### 工作进展
+- **教育网站建设**：🔄 进行中，计划将算术分为多个部分，希望将服务定价权交给消费者，转变为代购模式。
+- **学习介绍**：✅ 已完成，已将“我们是谁”提到最上面，并修改了参数。
+- **任务分配**：🔄 进行中，目前有四个任务，包括课程开发，最大任务是组建执法队伍，下个月主要任务即为此。
+- **执法队伍组建**：🔄 进行中，需招聘20多位师傅，第一步确定路线，修订纲领章程，修订303等。
+- **大运发放**：🔄 进行中，需要调试。
+- **待遇与休假**：🔄 进行中，上班5000元，额外有奖励和提成，休假为周五半天加周末两天。
+- **下周工作安排**：🔄 进行中，需完成两个活动，需要政府报告，组建教育团队。
+### 关键阻塞与风险
+- **工作方向可能偏了**，需考虑工作量。
+- **活动不是特别重要**，但需互相理解。
+- **任务分配条件可能不同**，菜品条件可能不太一样。
+- **服务时间与工具需要修改**，东西不太好，太奇怪。
 # 协作需求
-- 邀请同事加入：先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
-- 组建教育团队：需要政府报告并符合要求，组建教育团队，确定路线，修订纲领章程。
-- 任务分配：任务分配需安排，任务第一步确定路线、修订纲领章程，然后安排任务。
-- 招聘师傅：需招聘20多位师傅。
-- 大运发放：需要调试。
-- 学习介绍：服务时间还有工具需要改一下。</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>4999/1098</t>
+邀请同事加入，共同制作解决方案。学习介绍已弄完，下一步邀请同事加入。讨论是否修改会议纲要，是否报上上。</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4999/855</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="9">
+    <row r="24" ht="13.5" customHeight="1" s="10">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:08
@@ -7660,31 +7418,31 @@
       <c r="C24" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者张春和，48岁，因上腹反复不适3个月到消化内科就诊，由严医生接诊。患者4年来每年春天多发，心窝处烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大；疼痛可忍受、白天发作、无夜间痛醒，3个月中有完全不痛的时候。曾出现两次黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近两个月出现几次呕吐，为酸味食物，晚上吐后舒服，有隔夜食物吐出，呕吐物无红色或黑色；最近3个月无黑便，大便黄色正常，小便正常，睡眠可。医生提出需留大便检查以了解有无出血，并安排后天做胃镜，待向上一级医生张医生汇报后再商定下一步处理意见。
+患者张春和，男，48岁，因反复上腹心窝处烧灼痛4年、近3个月加重，伴两次黑便及近两个月呕吐，就诊于消化内科。严医生接诊并采集病史，初步考虑消化道溃疡或出血可能，需进一步检查明确诊断。医生建议留大便做潜血检查，并预约后天行胃镜检查，待向上级张医生汇报后商定治疗方案。
 # 诊断与检查结果
-医生尚未给出明确诊断结论，表示需等检查资料更全面后再判断是否需要手术，若药物能控制病情则不用手术。患者曾两次出现黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近3个月无黑便，大便黄色正常。患者16岁时得过甲肝，在三医院住院一个月，出院时肝功能完全恢复，以后体检肝功正常。患者本人有低血压（90/60），父亲76岁有低血压，母亲75岁诊断过冠心病、吃药控制较好。医生提出需留大便检查以了解有无出血，并安排后天做胃镜。
+医生初步诊断考虑上消化道疾病可能，需排除消化道出血及恶性病变。关键检查安排：大便潜血检查（排查出血）、胃镜检查（预约后天）。既往史：16岁曾患甲肝（三医院住院一个月治愈），磺胺药过敏（左手红疹，持续半个月），双眼近视400度，偶发口腔溃疡。家族史：父亲低血压，母亲冠心病，婶婶（无血缘关系）患胃癌。
 # 治疗方案与医嘱
-治疗计划：医生提出需留大便检查以了解有无出血，并安排后天做胃镜；将总结病情向上一级医生张医生（指导教授、权威）汇报后，再与患者商定下一步处理意见；关于手术，等检查资料更全面后再判断，若药物能控制则不用手术，如需手术再商量。生活注意事项：医生指出经常加班熬夜对疾病有影响，以后需注意；抽烟对身体不好，应尽量少抽或不抽，患者现把抽烟限制在10支以内并考虑戒烟；酒对胃肠道疾病影响大，需注意，患者应酬时少喝一点。重点禁忌：患者小时候因扁桃体炎在儿童医院吃华安药后左手起红疹、约半个月才好，医生告知对药物过敏，**不能吃该药**。
+患者既往用药：斯达舒（初有效后效果不佳，加量至每日四五次仍不佳）、奥美拉唑（武汉产）和阿莫西林、单位医务室胃炎合剂（有效但停药后复发）。治疗计划：留大便做潜血检查，后天行胃镜检查，待检查结果后由上级张医生商定治疗方案。生活注意事项：**戒烟限酒**，避免熬夜劳累，注意饮食（避免冷、硬、辛辣食物）。重点禁忌：**磺胺药过敏**，用药需避免。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 斯达舒 | 最初一天两次，每次一颗；后加量至每天四五次 | 最初一天两次，后每天四五次 | 口服 | 最初有效，后效果不好，加量后仍效果不好 |
-| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉药厂，国产 |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
-| 胃炎合剂 | 未提及 | 未提及 | 口服 | 所里医务室自己配置 |
+| 斯达舒 | 未明确 | 最初每日两次，每次1颗；后加至每日四五次 | 口服 | 初有效后效果不佳，加量后仍不佳 |
+| 奥美拉唑（武汉产） | 未明确 | 未明确 | 口服 | 有效但停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同用 |
+| 胃炎合剂（单位医务室配制） | 未明确 | 未明确 | 口服 | 有效但停药后复发 |
 # 复诊与预警信号
-复诊时间：胃镜预约在后天进行，因患者爱人后天可请假陪同；后天张大夫查房。医生将总结病情向上一级医生张医生汇报后，再与患者商定下一步处理意见。预警信号：原文未提及需立即就医的预警症状。</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>10297/1145</t>
+复诊时间：后天行胃镜检查，胃镜后赶上张大夫查房，之后由严医生向上级张医生汇报病情，再商定治疗意见。预警信号：⚠️ 若再次出现黑便、呕血、剧烈腹痛、头晕乏力等症状，需立即就医。</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10297/829</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1" s="9">
+    <row r="25" ht="13.5" customHeight="1" s="10">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:14
@@ -8019,50 +7777,50 @@
       <c r="C25" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次汇报由基金经理肖楠面向投资者进行，主题为过去一段时间的研究布局、研究认知成果以及投资理念与框架的反思与更新。肖楠首先明确反对市场上流行的抱团与均值回归两个观点，随后汇报过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向，并分享围绕四大领域的重要认知，最后用五点反思梳理对投资框架的更新：对商业模式的反思、对终局判断的反思、对长期隐性变量的反思、深度价值可能长期无效（打问号，未得结论）、小企业X factor。汇报后进入客户提问交流环节，肖楠就终局判断与格局演进、伟大公司判断标准、全市场基金选股逻辑、血制品行业壁垒、农林牧渔行业提升、商增商减分析、伟大企业增长曲线、财富管理行业、企业家精神观察心得等问题逐一作答。
+本次讲座由基金经理肖楠主讲，面向机构投资者汇报其过去一年的研究布局、投资框架反思与认知升级，并回答投资者提问。肖楠首先指出投资者普遍关心的“What happen next”类问题因知识鸿沟而用处有限，并基于自身研究框架将问题分为重要不重要、可研究及难以研究四类，强调真正关心的是标的基本面变化、投资逻辑更新、认知深入及投资框架修正。他明确反对市场上“抱团”与“均值回归”两个流行观点，认为抱团定义不本质，均值回归仅是局部正确，长期看收益率呈幂律分布，投资核心在于寻找长线超级大牛股。随后他介绍过去一年在互联网、财富管理、新消费和高端制造四个方向的研究布局，并分享五点投资框架反思，包括商业模式分类的不完备性、从商增角度理解商业模式、长期变量对收益率的影响、深度价值可能长期无效（存疑）以及小企业X factor的重要性。最后，肖楠就投资者关于终局判断、伟大公司标准、全市场基金选股逻辑、血制品行业、农林牧渔行业、商增商减分析、增长曲线、财富管理行业及企业家精神等问题逐一作答。
 # 核心观点与论证
-**论点一：反对抱团与均值回归两种流行观点。** 肖楠认为抱团定义不本质，基金经理之间是竞争关系，主观上不具备抱团意愿，同一公司研究员推荐被广泛认可买入也不叫抱团，且抱团只是截面数据忽略了时间维度；均值回归是特别不本质的局部正确，90%时间正确但10%错误代价惨重，举例某商学院老师在海螺水泥上做波段十年赚两三倍，2016至2017年卖出后该股约两年涨五六倍再未买回，并指出收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。
-**论点二：四大研究布局方向。** 过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向。互联网：全球仅中美能做成巨大产业，中国十几年迭代出流量、运营管理、算法三代企业，港股通开通后可投；财富管理：中国进入小康，人均收入中位数前移带来巨额剩余财富待专业机构管理，行业空间远超想象；新消费：富裕年代诞生的消费公司从CEO理念、组织架构到生产方式与匮乏年代企业完全不同；高端制造：中国几乎是唯一拥有全产业链的国家，很多细分领域已占据主导地位，欧美日企业份额已是中国企业碗里的肉。
-**论点三：研究认知成果。** 新消费领域看起来产品差不多的公司收入利润差距巨大，企业眼中产品差异在三年五年十年维度被放大；传统消费龙头赚钱龙二龙三也赚钱，新消费同一行业一家赚很多钱另一家完全不挣钱；从`商增`角度理解企业商业模式，商增过快导致企业走向失败，成长企业靠什么吸收熵增是关键。
-**论点四：投资框架五点反思。** 一是对商业模式，世界上没有一劳永逸坐地收钱的生意、极端稀缺，单一维度出发可能错失机会，商增角度理解商业模式更本质，企业家精神是否值得定价存疑并与张坤争论过；二是对终局判断，因终局判断不清晰或悲观而放弃中期十倍机会，需在坚持终局判断基础上争取研究格局演进阶段性特征；三是对长期隐性变量，为什么日本德国没有出巴菲特索罗斯，中国基金经理放到日本韩国不一定有好收益率，国运等长期变量解释相当部分收益率来源，并研究奢侈品和白酒文化强势案例；四是深度价值可能长期无效（打问号，未得结论），深度价值只是结果，去年投的深度价值标的result非常差；五是小企业X factor，经典`DCF`/`DDM`都是线性假设，企业发展是曲线，曲率因素无法定价但长期起作用，超额认知来自这些方面。
+讲座围绕“知识与信息的鸿沟”展开，肖楠指出投资者获得的仅是信息而非知识，知识更新会迅速改变判断，因此“What happen next”类答案对投资者用处不大。他基于自身研究框架将问题分为重要不重要、可研究及难以研究四类，强调关心标的基本面变化、投资逻辑更新、认知深入及投资框架修正。
+肖楠明确反对“抱团”与“均值回归”两个流行观点。关于抱团，他认为该定义不本质，基金经理之间是竞争关系，主观上不可能抱团；同一公司买同一板块是研究员推荐被广泛认可的结果，而非合谋。关于均值回归，他指出其仅是局部正确，长期看收益率呈幂律分布，并以美国股市200年增量由4%公司贡献为例，强调投资核心是找到长线超级大牛股。
+他介绍过去一年在互联网、财富管理、新消费和高端制造四个方向的研究布局。互联网产业是富矿，中国和美国能诞生巨大公司；财富管理行业空间巨大，因中国收入中位数提升将带来巨额剩余财富；新消费公司从CEO到组织架构完全不同于传统企业；高端制造中国在众多细分领域已占据主导地位，未来空间可见。
+肖楠分享五点投资框架反思：第一，商业模式分类不完备，没有一劳永逸的坐地收钱生意，长期看所有企业都会死去；第二，从商增角度理解商业模式更本质，企业成长过程中需吸收熵增，商增过快会导致失败；第三，长期变量如国运、文化背景影响收益率，需保持谦卑但大胆思考；第四，深度价值可能长期无效（打问号），因深度价值只是结果，若导致原因不变，最好结果也只是不输；第五，小企业的X factor，即驱动企业增长且不被线性描述的因子，无法定价但必须承认存在，否则会陷入估值与基本面的两难。
 # 金句总结
-「知识和信息之间是有着巨大的鸿沟的。」——背景：肖楠在开场说明投资者关心的What happen next类问题对提问者用处不大，看好某板块对本人是knowledge，对他人只是一条信息。
-「务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。」——背景：肖楠以巴菲特代表的极端务实派与索罗斯代表的极端务虚派说明基金经理理念处于两个极端中间，强调理念没有好坏。
-「均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。」——背景：肖楠反对均值回归观点，以海螺水泥波段操作案例说明。
-「收益率是幂律分布的，不是正态分布的。」——背景：肖楠论证均值回归不本质，指出美国股市200年价值增量由4%的公司贡献。
-「长期看所有的企业都要死去，就是我们不能够抱着就是抱定说我我们要买一个千秋万代的这种企业。」——背景：肖楠反思对商业模式的理解，指出没有一劳永逸坐地收钱的生意。
-「我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价，它不能被定价。」——背景：肖楠回答企业家精神观察心得，强调不乱归因、不轻易定价。
+“知识和信息之间有着巨大的鸿沟。”——肖楠以此说明投资者获得的“看好某板块”等信息对其决策用处有限，因为知识更新会迅速改变判断。
+“务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”——他强调投资理念无好坏，关键在于执行。
+“均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”——他以商学院老师在海螺水泥上做波段、最终错过两年五六倍涨幅为例，说明均值回归的局限性。
+“收益率是幂律分布的，不是正态分布的。”——他以此强调投资核心是找到长线超级大牛股，美国股市200年增量由4%公司贡献。
+“我们一定要对市场保持谦卑。”——他提醒投资者注意长期变量对收益率的影响，避免过度归因于个人能力。
+“驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”——他以此引出X factor概念，强调超额认知的来源。
 # Q&amp;A 环节
-问：您刚刚讲到在对于终局结果的重视的过程中，也更加去关注格局演进的过程中阶段性的特征、中期投资机会，请问您能对这一点再详细描述一下吗？
-→ 答：肖楠表示不太好说具体标的，这个想法最早来自过去错过了一些特别大的机会，之所以错过是因为判断这些行业终局可能不大行，但明明判断对了却在两三年时间里深深错过了十几倍的涨幅。复盘看当时完全可以在既考虑终局可能没那么好的前提下依然做出漂亮投资。这类企业的重要特征是做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。后来在一些投资中，对终局可能没那么强的标的，依然能够做出好的投资，希望未来不要再去错过类似机会。
-问：您在年报中也讲到过，坚定持有优秀乃至伟大的公司。请问您能否对优秀乃至伟大的公司的判断标准，有一些具体的财务指标？
-→ 答：肖楠称伟大公司是在财务指标里面看不出来的。举例A、B两家同属一个大行业但不同细分子行业的国企，投资逻辑非常像，都在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于B公司没有太多研发、靠精益求精的管理做到成本极低；A公司每年有高额研发支出，关键技术指标以非常强速度迭代，还有很多特别前沿的研发项目，这些方向上的技术目前掌握在德国人、日本人手里。A公司在发展初期被德国人、日本人坑过，从董事长到总经理到技术骨干都有强烈的产业报国、技术报国理想，从跟着日本人学、跟着德国人学，到越做越强、超越对手，再到对手跑过来跟他们学、开始做全产业链布局，这种企业堪称伟大的企业。
-问：我们是全市场基金，能否介绍一下这个产品的投资逻辑呢？对于消费以外的行业的选股，主要是基于什么逻辑呢？
-→ 答：肖楠称很难分消费内消费外，选股逻辑都是一样的，都是不可能三角、企业三阶段、三种商业模式这一类的，消费行业只许买消费所以只能在消费行业里面选，两者选股逻辑完全一样。
-问：您是怎么看待血制品行业的竞争壁垒呢？
-→ 答：肖楠称血制品行业初初研究过，觉得壁垒不是特别的强，不是想要的那种强壁垒，研究不是特别多，相比之下买了另外一些强壁垒的公司，还有一些基金经理买了血制品行业，可以请教他们。
-问：农林牧渔行业是有所提升，请问您对这个行业的观点能够给我们讲一下吗？
-→ 答：肖楠称这行业太大了，农林牧渔行业的提升是因为牧原股份那一只股票，不是因为先看好农林牧渔行业再去选了牧原股份，就是牧原股份的比例提高了。
-问：您能够再具体讲一下生意模式里边商增和商减的这个分析吗？
-→ 答：肖楠用直白例子说明：企业从小到大，部门越来越多，中层干部一大堆，上面要分领导、还有副总裁，传达效率变低、效率开始变差，内部腐败开始出现，企业为解决供应商利益关联问题又要设置巡视检查部门，部门人员要加工资、提级别，多部门老总今年提哪个明年提哪个；企业要扩张，往下游或上游多做业务，又要多一个副总裁、多个部门。有些生意模式收入10个亿跟100个亿时没多多少机构、没多几个部门，有些企业是商增把自己拖死的。行业里剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，差别在于做得不好的公司从一开始就没考虑好企业大了以后商增怎么处理效率问题和人员问题。建议读一读党史，看组织如何保持活力，很多政府或企业确实是处理商增的高手。
-问：您讲到伟大的企业的增长曲线，您能否对于这个曲线的情况再具体跟大家讲一下呢？
-→ 答：肖楠称每年看企业今年增长20、明年15、后年17.5都是线性的，站10年周期看企业跟竞争对手之间拉开极大差距。举例快递行业疫情时只有顺丰能送，一下子把竞争对手甩出一大截；家电领域过去格力一直是老大，美的做渠道扁平化、T加三一直没看到成果，疫情来了美的占有率一下子超过格力。当企业在埋头做一些事情、还没体现到报表时，我们往往忽略其未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，就像平时走在路上大家都走得好好的，突然来一场雨，发现有一个人带伞了，别人都淋成了落汤鸡。
-问：您刚刚有讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会呢？
-→ 答：肖楠称财富管理行业话题特别大且分层，顶级富豪、普通中产阶级、中低收入人员的财富管理都有不同的公司和商业模式。最早关注这个行业是研究保险时发现，某些保险公司一个保险员一单能签七八千的首次保费，有些公司平均一个业务员大概三千多、有些两千多，差距巨大，背后是结构设置、机构设置、激励机制、文化等差异。发基金时也发现同样渠道经理，有的问的问题超级专业，有的永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司一口气拿掉行业增量的绝大部分，有些公司拿掉70%、80%，剩下的第二名只能拿到剩下的20%的80%，这种特别偏激、密分布特别偏激的行业里有可能诞生特别大的企业。因监管和法律规则原因有些标的不能投，未来合同设置更清晰时可能会在投资上有所体现。
-问：您刚刚讲到曲线的方面，第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标的方面会有什么心得和把握呢？
-→ 答：肖楠称第一个心得是评判这个因素时要特别小心谨慎，不要乱归因，不要因为一个企业成功就说企业家特别厉害，就像不要因为一个基金经理过去业绩很好就说他特别厉害，一定要把所有能够被归因到数据里的客观指标因素全部归因完，再特别谨慎地评价比较虚的因素。第二个心得是不要轻易给这些因素定价，绝对不要说因为这个企业家在所以公司就能值多少多少。始终强调的是避免错误的归因，避免因为对企业家的认可去犯投资上的错误，一定要把底线的风险搞好。这些因素不可被定价，只能在有限范围内做两两比较，比如两个公司做同样生意、同样产品，可以比较两个企业家的水平高低、理念先后，仅此而已，不要跨行业、跨业务、跨产品去比较，一定要非常谨慎地使用所谓企业家精神、伟大企业这些说法。</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>26252/4226</t>
+问：您刚刚讲到在重视终局结果的过程中，也更加关注格局演进的阶段性特征和中期投资机会，能否再详细描述一下？
+答：这个想法源于我们过去错过了一些特别大的机会，我们判断这些行业的终局可能不大行，但明明判断对了，却在两三年的时间里错过了十几倍的涨幅。复盘发现，这些企业虽然某一代产品被追上，但做出了第二增长曲线，且壁垒更深。所以我们开始承认终局可能没那么强，但依然能做出好的投资，希望未来不再错过类似机会。
+问：您在年报中讲到坚定持有优秀乃至伟大的公司，请问判断标准是否有具体财务指标？
+答：伟大公司在财务指标里看不出来。我举例两家公司，A和B都在自己领域把成本做到行业最低，市场份额稳固提升。但B公司不怎么做研发，靠精细化管理；A公司每年高额研发，关键技术指标快速迭代，且从董事长到技术骨干都有强烈的产业报国精神，从跟着日本人、德国人学到超越对手，堪称伟大企业。
+问：全市场基金的选股逻辑是什么？消费以外的行业选股基于什么逻辑？
+答：我们很难分消费内消费外，选股逻辑都一样，都是基于不可能三角、企业三阶段、三种商业模式等。消费行业只许买消费，所以只能在消费里选，两者逻辑完全一样。
+问：您怎么看血制品行业的竞争壁垒？
+答：我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒，所以没有深入，我们买了另外一些强壁垒的公司。
+问：农林牧渔行业持仓有所提升，您对这个行业怎么看？
+答：农林牧渔行业提升是因为牧原股份，就那一只股票。不是先看好行业再选牧原，而是牧原比例提高了，就这么简单。
+问：能否具体讲一下生意模式里商增和商减的分析？
+答：用直白的话讲，企业从小到大，部门越来越多，传达效率变低，内部腐败出现，为解决这些问题又增设部门，导致效率进一步下降。有些生意收入从10亿到100亿，机构没多几个部门；有些企业则被商增拖死。我建议大家读党史，看组织如何保持活力，很多国家和企业都是被商增拖死的。
+问：您讲到伟大企业的增长曲线，能否再具体讲一下？
+答：有些企业每年看是线性增长，但拉长到10年，会在关键节点突然甩开竞争对手。比如疫情时只有顺丰能送，一下子拉开差距；家电领域美的做渠道扁平化，疫情时占有率突然超过格力。这些企业平时直线发展，但在特殊时刻拐上去，就像下雨时有人带了伞。
+问：您讲到财富管理行业，能否具体展开投资逻辑和机会？
+答：财富管理行业话题很大，且分层，顶级富豪、中产阶级、中低收入者的财富管理方式不同，商业模式也不同。我们最早研究保险时发现，不同保险公司业务员单均保费差距巨大，背后是结构设置、激励机制、文化的差异。财富分布极不均匀，头部公司可能拿走行业增量的绝大部分，这种偏激分布可能诞生特别大的企业。但受监管和法律限制，我们有些产品暂时不能投类似标的，未来合同设置更清晰时可能会有所体现。
+问：您讲到第二第三增长曲线需要卓越的企业家精神，请问观察这个指标有什么心得？
+答：第一，评判时要特别小心谨慎，不要乱归因，把所有能归因到客观指标的都归因完，再谨慎评价虚的因素。第二，不要轻易给这些因素定价，绝对不要说因为企业家在，公司就值多少。我们一致同意它不可被定价。这些虚的因素在客观归因穷尽后再考虑，且只能在两两比较中比较企业家水平，不要跨行业比较。要谨慎使用“企业家精神”“伟大企业”等词，避免错误归因。</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>26252/2922</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="9">
+    <row r="26" ht="13.5" customHeight="1" s="10">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:14
@@ -8222,36 +7980,23 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t># 辩论内容概述
-本场辩论赛围绕「是否应拥有让所爱之人爱上自己的超能力」展开，正方为RUC棒辩论队，反方为对方辩友。正方认为爱本身并非自由意志的产物，以「坠入爱河」而非「跳入爱河」说明爱是情非得已，并援引丘脑分泌多巴胺产生爱的感觉、但科学无法解释为何偏偏对某人有感觉，故归于玄学；正方还认为红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方认为打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸，并认为通过洗脑获取爱更像变态的占有，不是爱；反方还认为月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。双方就爱到底是不是自由意志的产物、超能力发挥的机制究竟是洗脑还是其他方式、爱是玄学还是可被科学解释均未达成一致，本场辩论未形成统一结论。
-# 核心论点
-正方观点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制，若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方观点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
-| 阵营 | 立论框架 | 核心论点 | 支撑论据 |
-| --- | --- | --- | --- |
-| 正方 | 爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已 | 超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好 | 丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学；若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从 |
-| 反方 | 打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸 | 通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱 | 这个人原来不爱你的，但是你打了响指，他就一定爱上你了，这个和很多有必要的强奸犯讲的道理是一样的 |
-# 自由辩论环节
-争议点一：超能力是否剥夺对方自由意志。反方攻：打响指让对方爱上自己，是违背对方意志强行介入亲密关系，类比强奸。正方防：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已。
-争议点二：超能力是否等同于洗脑与占有。反方攻：通过洗脑获取爱更像变态的占有，不是爱。正方防：若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从。
-争议点三：爱是玄学还是可被科学解释。正方攻：丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学。反方防：质疑对方未论证爱是玄学。
-争议点四：放手的爱与是否应使用超能力。反方攻：追问相处后发现不合适是否再用超能力。正方防：若无法在一起会选择放手。反方再攻：一旦用过超能力，今后面对新感情会永远留下遗憾。
-争议点五：月老丘比特与红线掌握在谁手里。正方攻：红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方防：月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
-&gt; 正方：「我们说的是坠入爱河，而不是说去跳入爱河。」
-&gt; 反方：「这个人原来不爱你的，但是你打了响指，他就一定爱上你了。这个和很多有必要的强奸犯讲的道理是一样的。」
-# 结辩与评委点评
-正方结辩核心升华点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方结辩核心升华点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。评委点评意见：未提及。获胜方：正方。</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>12403/1626</t>
+          <t># 超能力之爱是否美好辩论赛
+超能力之爱是否美好辩论赛
+会议要点：本次辩论赛围绕“拥有让任何人爱上自己的超能力是否美好”展开，正方RUC棒辩论队主张超能力客观存在，且掌握在爱你的人手里比交给蒙眼小孩更好，月老丘比特是浪漫象征；反方则认为爱是自由意志的产物，超能力抹杀对方决定，类似洗脑和占有。；正方指出爱非意志可控，用“坠入爱河”等例证反驳，并质疑对方未论证爱是玄学，指出科学无法解释爱的特殊性；反方坚持洗脑不是爱，并质疑超能力剥夺对方选择空间，是自私的占有。；正方最终获胜，获得4分钟小结时间。
+未决问题：爱是否与自由意志相关？；超能力发动机制是洗脑还是其他？；放手的爱是否成立？
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12403/300</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1" s="9">
+    <row r="27" ht="13.5" customHeight="1" s="10">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:10
@@ -8604,30 +8349,29 @@
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者于23年9月因腹痛一晚上确诊结肠癌，行结肠癌切除手术及8期化疗，复查发现肝转移，从老家到北京做PET-CT。去年9月行肝消融及乳腺结节切除，当时已有腹膜转移，切肠时可能切得不干净；术后行紫杉化疗，仅第一次有效，后续因肝功能不行停用靶向，至3月底复查发现肝、肺、腹膜又有转移。本次就诊为家属代述病史并咨询后续治疗，医生建议以全身系统治疗（化疗、靶向、免疫）为主，介入不是当前主要问题，并建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍。
+患者为结肠癌术后患者，2023年9月因结肠癌行切除手术，术后完成8期化疗，后出现肝转移，去年9月行肝消融和乳腺结节切除，因肝功能不佳停用部分化疗药，3月底复查发现肝、肺、腹膜转移。患者主诉为肚子疼，疼了一晚上，既往有吃海鲜后上吐下泻史。初步诊断为结肠癌术后多发转移（肝、肺、腹膜）。医生建议优先进行全身系统治疗（化疗、靶向、免疫），而非局部介入，并建议进行基因检测和免疫评估以指导后续治疗。
 # 诊断与检查结果
-医生指出患者为结肠癌术后多发转移，累及肝、肺、腹膜及肠壁。PET-CT显示肝、肺、腹膜有转移；肠镜显示没事但PET显示有问题，今天说可能是肠镜做得不好。4月份做的检查。医生强调现在化疗是否有效并不清楚，基因检测推荐或不推荐都需参考；免疫细胞状态很重要，数量不足需创造。
+诊断结论：结肠癌术后多发转移，累及肝脏、肺、腹膜。关键检查结果：PET-CT显示肝转移、肺转移、腹膜转移；肠镜显示未见异常，但PET-CT显示有转移，医生认为可能肠镜做得不好；基因检测提示存在基因突变，但具体类型未明确。异常指标：肝功能不佳，导致停用部分化疗药。
 # 治疗方案与医嘱
-治疗计划以全身系统治疗为主，包括化疗、靶向、免疫，需选靶向、选免疫；靶向和免疫治疗与原来化疗机制不同、可能协同。建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍，第一次、第二次、第三次切片可对比，从对讲中找可用信息。生活注意事项：让患者把状态调整好，提升免疫力靠自己，大夫和手术有限；要做免疫评估，但方案由家属定。**若涨幅到10公分则要命，需先系统治疗**。
+治疗计划：优先进行全身系统治疗，包括化疗、靶向治疗和免疫治疗。建议进行基因检测和免疫评估，以指导后续用药选择。生活注意事项：注意饮食，避免食用海鲜等可能引起肠胃不适的食物；可服用四联康调节肠道菌群。重点提醒：肝功能不佳时需调整化疗方案，避免使用肝毒性药物。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 紫杉化疗 | 未提及 | 未提及 | 化疗 | 仅第一次有效，后续因肝功能不行停用靶向 |
-| 靶向药 | 未提及 | 未提及 | 靶向治疗 | 后续因肝功能不行停用 |
-| 四联康 | 未提及 | 未提及 | 口服 | 肚子不好时用 |
+| 四联康 | 未明确 | 未明确 | 口服 | 用于调节肠道菌群，改善肠胃不适 |
+| 化疗药（具体药名未明确） | 未明确 | 未明确 | 静脉给药 | 因肝功能不佳，已停用其中一种药物 |
 # 复诊与预警信号
-复诊时间未提及。⚠️ 若涨幅到10公分则要命，需立即就医。</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>7063/797</t>
+复诊时间：未明确。预警症状：⚠️ 若出现剧烈腹痛、持续呕吐、便血、呼吸困难或意识改变，需立即就医。</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7063/708</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="9">
+    <row r="28" ht="13.5" customHeight="1" s="10">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:45
@@ -8786,39 +8530,37 @@
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t># 产品概况
-本次发布会由海尔洗衣机用户研发中心主办，围绕洗干集成新物种迭代H2展开，主题为体验海尔洗衣机的科技创新之路、共同见证洗干集成新物种的诞生。发布背景源于全球家庭洗护需求洞察：欧洲作为滚筒洗衣机发源地，许多家庭有独立洗衣房、洗烘套装并排摆放；而在中国，80%的用户把洗烘套装放在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便，正是这些问题孕育了洗干集成新物种的诞生。迭代H2定位为客阳一体空间的黄金选择，是海尔为中国家庭打造的原创之作，目标是让每一个向往整洁有序新阳台的用户都能体验这种生活方式。
+海尔叠黛H2洗干集成机是海尔为中国家庭打造的原创之作，定位为洗干集成新物种。发布会背景源于中国80%用户将洗烘套装叠放阳台带来的操作不便，产品专为客阳一体空间设计，以一体集成机身解决洗烘套叠放带来的震动等安全隐患。产品高度167厘米，超薄机身可嵌入60厘米标准橱柜，采用同向开门与无水盒设计。核心目标是为向往整洁有序新阳台的用户提供一体化洗护体验，让用户享受家的整洁有序。
 # 市场定位与目标用户
-迭代H2专为客阳一体空间设计，面向中国当下最流行的客阳一体家居风格，是希望拥有整洁有序新阳台用户的黄金选择。典型使用场景为年轻人最喜欢的阳台风格之一，他们在阳台休闲、娱乐、健身、社交，悬挂晾衣既不美观又占空间，H2帮助其彻底告别晾晒。目标人群包括：渴望从漫长家务中解放出来的年轻人、对残留泡沫敏感的人、养宠物的人群，以及有宝宝的家庭。差异化竞争力方面，与洗烘套装的貌合神离不同，H2独有的灵犀洗烘联动可实现数据共享，让烘干和洗涤无缝连接；一体集成机身解决了洗烘套叠放带来的震动等安全隐患。
+目标人群覆盖多类中国家庭：一是追求客阳一体家居风格的年轻用户，他们在阳台休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间；二是养宠家庭，居家环境漂浮的毛屑多来自衣物家纺；三是有宝宝的家庭，需要洗衣无残留、干衣无毛絮的健康守护。产品针对中国80%用户将洗烘套装叠放阳台的痛点，对比欧洲家庭独立洗衣房并排摆放洗烘套装的使用习惯，以一体集成设计解决屏幕过高、开门方向相反、水盒太高太沉等不便，形成差异化竞争力。
 # 核心卖点与技术参数
-**🏠 客阳一体设计与集成机身**：专为客阳一体空间设计，一体集成机身解决洗烘套叠放带来的震动等安全隐患；高度降为 `167厘米`，不用踮脚尖即可轻松操作；超薄机身完美嵌入 `60厘米` 标准橱柜，纯平不突出；同向开门尊重使用习惯，取放衣物流畅自如；采用无水盒设计，无需手动倒水。
-**🧠 智慧大脑与灵犀洗烘联动**：以屏幕为核心可全面操控洗涤、烘干和护理等多种模式；H2全新升级智慧大脑，利用中枢神经式智能网络让上下桶默契配合；H2独有灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接；洗涤结束前上桶提前 `15分钟` 主动预热，进一步缩短烘干时长。
-**🌀 烘干与洗涤技术**：搭载原创双擎热泵技术，大件烘干不缠绕；首次引入行业领先黑科技3D透视烘干，羽绒服或水洗被均可一次烘透，免去二次晾晒烦恼；升级精华洗2.0，能够激活洗衣液，`39分钟` 洗净一周衣物；新鲜净水漂洗减少洗衣液残留。
-**🐾 居家健康与静音**：搭载空净过滤系统，轻松去除衣物线屑和毛絮，更适合养宠物人群；洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭；搭载三台变频电机，洗涤、甩干、烘干全过程噪音都很低。
+**一体集成设计**：专为客阳一体空间设计，一体集成机身解决洗烘套叠放带来的震动等安全隐患，高度167厘米，超薄机身嵌入60厘米标准橱柜，纯平不突出，同向开门，采用无水盒设计无需手动倒水。
+**智慧互联**：搭载全新升级的智慧大脑，利用中枢神经式智能网络让上下桶默契配合；独有的灵犀洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长。
+**烘干技术**：搭载原创双擎热泵技术，大件烘干不缠绕；首次引入行业领先黑科技3D透视烘干，羽绒服、水洗被均可一次烘透，免去二次晾晒。
+**洗护功能**：升级精华洗2.0，39分钟洗净一周衣物；新鲜净水漂洗减少洗衣液残留，对残留泡沫敏感人群友好。
+**健康与静音**：搭载空净过滤系统，去除衣物线屑和毛絮；搭载三台变频电机，洗涤、甩干、烘干全过程噪音低。
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 机身高度 | 167厘米 | 洗烘套装叠放 | 降低高度，不用踮脚尖即可操作 |
-| 机身嵌入 | 超薄机身，完美嵌入60厘米标准橱柜，纯平不突出 | 洗烘套装叠放 | 全平不突出，阳台更美观整洁 |
-| 开门方式 | 同向开门 | 洗烘套装开门方向相反 | 尊重使用习惯，取放衣物流畅自如 |
-| 水盒 | 无水盒设计 | 水盒太高太沉 | 无需手动倒水 |
-| 洗烘联动 | 灵犀洗烘联动，数据共享，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离 | 烘干和洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术、3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透 |
-| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 减少洗衣液残留 |
-| 过滤系统 | 空净过滤系统 | 未提及 | 去除衣物线屑和毛絮 |
-| 电机 | 三台变频电机 | 未提及 | 洗涤、甩干、烘干全过程噪音都很低 |
+| 机身设计 | 一体集成机身，高度167厘米，嵌入60厘米标准橱柜 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
+| 洗烘联动 | 灵犀洗烘联动，上桶提前15分钟预热 | 洗烘套装貌合神离 | 数据共享，烘干与洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵+3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透 |
+| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物 | 未提及 | 高效洗净，新鲜净水漂洗减少洗衣液残留 |
+| 健康功能 | 空净过滤系统 | 未提及 | 去除线屑毛絮，适合养宠及有宝宝家庭 |
+| 静音表现 | 三台变频电机 | 未提及 | 洗涤、甩干、烘干全过程噪音低 |
 # 定价与发售信息
-海尔为这款平嵌超薄产品公布诚意满满的定价：10kg 3D透视烘干款12998元，10kg双擎热泵款10998元。发售时间、购买渠道及预售政策未提及。</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>7311/1601</t>
+发布会公布两款定价：10kg 3D透视烘干款12998元，10kg净净双擎热泵款10998元。发售时间、购买渠道及预售政策原文未提及。</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7311/1265</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="9">
+    <row r="29" ht="13.5" customHeight="1" s="10">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:13
@@ -9016,25 +8758,24 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次会议为改选中共巢湖市银屏镇白母山村芦塘支部委员会，支部共有党员8名（正式党员8名），有选举权的应到8名，因病请假1名，实到会有选举权党员7名，符合法定人数，会议可以召开；应邀参加的有银屏镇党委组织委员钱小丽同志。会议依次通过上届支部委员会工作报告、党员大会选举办法草案、支委候选人名单、监票人及计票人名单，四位候选人依次进行竞职演说，随后进行支部委员会委员选举和书记选举。上届支部委员会工作报告经讨论无意见、鼓掌通过，报告回顾3年来支部落实党建工作要求、加强思想政治建设和理论学习、抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告同时指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。选举办法草案明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。银屏镇党委批复（2019年10月12日）同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选卢燕娇，委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。随后召开第一次支部委员会全体会议，支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准；会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言表示将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。
-## 大会审议与选举办法通过
-- 上届支部委员会向会议做工作报告，请同志们审议；报告回顾3年来支部落实党建工作各项要求，加强思想政治建设和理论学习，抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。报告经讨论无意见，鼓掌通过。杜军晓同志宣读党员大会选举办法草案，明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。选举办法草案一致通过。
-- 杜军晓同志宣读银屏镇党委关于同意中共巢湖市银屏镇白母山村芦塘支部委员会组成人员候选人预备人选的批复（2019年10月12日），委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇；委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。会议对候选人名单无不同意见，鼓掌通过。会议提议由贾淑玲同志担任监票人，经酝酿无意见，表决一致通过；宣布大会计票人员名单为黄婷丽、刘彩云。四位候选人依次进行竞职演说：卢燕娇表示如当选将加强支部建设、落实三会一课、推动村集体经济发展、抓好民生工程落实；杜军强表示如成为支部委员可更好担当纽带角色为党员和群众服务；辛东升表示严格要求自己、做合格党员干部、圆满完成上级党组织分配的各项任务；秦磊表示有较强责任心和较高思想觉悟，配合上级工作，当一名合格的支部委员。
-## 选举结果与委员分工
-- 选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，可以进行选举；发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，根据选举办法，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。随后召开第一次支部委员会全体会议，宣读选举办法草案，介绍书记候选人建议名单卢燕娇，经鼓掌通过；提议由辛东升同志担任监票人和计票人，表决一致通过；支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准。会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言，代表新当选的三位支部委员感谢信任和支持，表示下一步将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。会议宣布换届选举大会圆满结束。</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>8414/2327</t>
+          <t># 芦塘支部换届选举党员大会
+芦塘支部换届选举党员大会
+会议要点：中共巢湖市银屏镇白母山村芦塘支部召开党员大会，改选支部委员会。支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。镇党委组织委员钱小丽到会讲话，提出三点意见：充分认识大会意义、正确行使选举权、服从大局遵守纪律。；上届支部委员会作工作报告，总结三年工作：加强思想政治建设、抓好支部建设、开展主题教育、党务公开、党风党纪教育，新发展党员一名，按规定收缴党费2640元上交上级党组织；同时指出存在不足：党建工作制度不完善、党员主体意识不高、教育管理监督不深入。报告经讨论无意见，鼓掌通过。；大会依次通过选举办法、支委候选人名单（卢燕娇、辛东升、杜军强、秦磊）、监票人贾淑玲及计票人黄婷丽、刘彩云名单。经无记名投票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员；随后召开第一次支委会，卢燕娇当选支部书记，辛东升负责组织宣传工作，杜军强负责纪检工作。
+关键决策：通过上届支部委员会工作报告；通过党员大会选举办法；通过支委候选人名单：卢燕娇、辛东升、杜军强、秦磊；通过监票人贾淑玲，计票人黄婷丽、刘彩云；选举卢燕娇、辛东升、杜军强为新一届支部委员会委员；选举卢燕娇为支部书记；辛东升负责组织宣传工作，杜军强负责纪检工作
+全员执行要点：卢燕娇当选支部书记，负责主持支部全面工作，并代表新一届支委表态将抓好学习、制度建设和服务型支部建设。；辛东升负责组织宣传工作，并在第一次支委会中担任监票人和计票人。；杜军强负责纪检工作。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8414/658</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="9">
+    <row r="30" ht="13.5" customHeight="1" s="10">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:05
@@ -9167,27 +8908,23 @@
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t># 报告概况
-国务院向大会报告政府工作，请予审议，并请全国政协委员提出意见。报告回顾2023年工作：全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，城镇调查失业率平均5.2%，居民消费价格上涨0.2%；国产大飞机C919投入商业运营，新能源汽车产销量占全球比重超过60%；粮食产量1.39万亿斤再创历史新高，居民人均可支配收入增长6.1%，脱贫地区农村居民收入增长8%。报告明确2024年经济社会发展总体要求和政策取向：今年是中华人民共和国成立75周年、实现十四五规划目标任务的关键一年，坚持稳中求进工作总基调，统筹扩大内需和深化供给侧结构性改革、统筹新型城镇化和乡村全面振兴、统筹高质量发展和高水平安全。报告部署2024年十项政府工作任务，并指出面临的困难和挑战。
+《政府工作报告》由国务院总理代表国务院向全国人民代表大会报告，报告期间为2023年工作回顾与2024年工作部署。报告核心主题是坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，着力推动高质量发展，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全，以中国式现代化全面推进强国建设、民族复兴伟业。整体基调积极进取，既肯定2023年成绩来之不易，又直面外部环境复杂性上升、经济恢复基础不稳固、有效需求不足、社会预期偏弱等困难挑战，强调要巩固和增强经济回升向好态势，持续推动经济实现质的有效提升和量的合理增长。
 # 核心政策
-2024年主要预期目标：国内生产总值增长**5%左右**，城镇新增就业**1120万人以上**，城镇调查失业率**5.5%左右**，居民消费价格涨幅**3%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量**1.3万亿斤以上**，单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善。财政政策：积极的财政政策要适度加力、提质增效，赤字率按**3%**安排，赤字规模**4.06万亿元**，一般公共预算支出规模**28.5万亿元**，安排地方政府专项债券**3.9万亿元**；为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**。货币政策：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。民生指标：居民医保人均财政补助标准提高**30元**，城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金。
+2024年主要预期目标：**国内生产总值增长5%左右**，**城镇新增就业1120万人**，**城镇调查失业率5.5%左右**，**居民消费价格涨幅3%左右**，**居民收入增长和经济增长同步**，**国际收支保持基本平衡**，**粮食产量1.3万亿斤以上**，**单位国内生产总值能耗降低2.5%左右**，生态环境质量持续改善。宏观政策取向：积极的财政政策适度加力、提质增效，**赤字率按3%安排**，**一般公共预算支出规模28.5万亿元**，**地方政府专项债券3.9万亿元**，**发行超长期特别国债10000亿元**，专项用于国家重大战略实施和重点领域安全能力建设；稳健的货币政策灵活适度、精准有效，保持流动性合理充裕，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。核心政策包括：大力推进现代化产业体系建设，加快发展新质生产力；深入实施科教兴国战略；着力扩大国内需求；坚定不移深化改革；扩大高水平对外开放；更好统筹发展和安全；坚持不懈抓好三农工作；推动城乡融合和区域协调发展；加强生态文明建设；切实保障和改善民生。
 # 重点工作
-经济领域：大力推进现代化产业体系建设，加快发展新质生产力，推动产业链供应链优化升级，实施制造业重点产业链高质量发展，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展，打造更多有影响力的中国制造品牌；促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划；深入推进数字经济创新发展，开展人工智能加行动，实施制造业数字化转型行动。着力扩大国内需求，促进消费稳定增长，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；积极扩大有效投资，发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施十四五规划重大工程项目。坚定不移深化改革，激发各类经营主体活力，深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，加快全国统一大市场建设，谋划新一轮财税体制改革。扩大高水平对外开放，推动外贸质升量稳，促进跨境电商等新业态健康发展，全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，推动高质量共建一带一路走深走实。更好统筹发展和安全，优化房地产政策，促进房地产市场平稳健康发展，统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
-民生领域：多措并举稳就业促增收，突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模。提高医疗卫生服务能力，居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，促进中医药传承创新。加强社会保障，城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，健全分层分类的社会救助体系。丰富人民群众精神文化生活，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。维护国家安全和社会稳定，提高公共安全治理水平，坚决遏制重特大事故发生，坚持和发展新时代枫桥经验，建设更高水平的平安中国。
-三农与城乡区域领域：坚持不懈抓好三农工作，扎实推进乡村全面振兴，学习运用千村示范、万村整治工程经验，稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；毫不放松巩固拓展脱贫攻坚成果，加强防止返贫监测帮扶，确保不发生规模性返贫；启动第二轮土地承包到期后再延长30年整省试点。推动城乡融合和区域协调发展，积极推进新型城镇化，把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用。
-生态环保领域：加强生态文明建设，推进绿色低碳发展，深入践行绿水青山就是金山银山的理念，协同推进降碳、减污、扩绿、增长；深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，组织打好三北工程三大标志性战役；大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展，建设美丽中国先行区；积极稳妥推进碳达峰碳中和，扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系。
-&gt; 使命重在担当，奋斗创造未来，我们要更加紧密地团结在以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，坚定信心，开拓进取，努力完成全年经济社会发展目标任务。</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>9903/2479</t>
+**一、现代化产业体系建设**：实施制造业重点产业链高质量发展行动，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展；巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划；深入推进数字经济创新发展，开展`人工智能+`行动，实施制造业数字化转型行动。**二、科教兴国战略**：制定实施教育强国建设规划纲要，开展基础教育扩优提质行动，加快建设中国特色世界一流的大学和优势学科；强化基础研究系统布局，推进关键核心技术协同攻关，强化企业科技创新主体地位；实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度。**三、扩大国内需求**：培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；发挥政府投资带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳等领域，着力稳定扩大民间投资。**四、深化改革**：深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制；加快全国统一大市场建设，专项治理地方保护、市场分割、招商引资不当竞争等突出问题；谋划新一轮财税体制改革。**五、扩大高水平对外开放**：推动外贸稳规模优结构，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点；**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入；推动高质量共建`一带一路`走深走实，抓好八项行动落实落地。**六、统筹发展和安全**：优化房地产政策，促进房地产市场平稳健康发展，加快构建房地产发展新模式，加大保障性住房建设和供给；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；稳妥推进中小金融机构风险处置；全方位夯实粮食安全根基，强化能源资源安全保障。**七、三农工作**：学习运用`千村示范、万村整治`工程经验，稳定粮食播种面积，严守耕地红线，提高高标准农田建设投资补助水平；毫不放松巩固拓展脱贫攻坚成果，确保不发生规模性返贫；**启动第二轮土地承包到期后再延长30年整省试点**。**八、城乡融合和区域协调发展**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，推动未落户常住人口平等享受城镇基本公共服务；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区发挥高质量发展动力源作用。**九、生态文明建设**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，组织打好`三北`工程三大标志性战役；大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构绿色转型；积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`。**十、保障和改善民生**：突出就业优先导向，强化促进青年就业政策，预计今年高校毕业生超过1170万人；**居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层；**城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金；健全生育支持政策，减轻家庭生育养育教育负担；维护国家安全和社会稳定，坚决遏制重特大事故发生。</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9903/2116</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="9">
+    <row r="31" ht="13.5" customHeight="1" s="10">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:16
@@ -10017,39 +9754,22 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t># 沟通背景与目的
-本次直播为杭州医学院检验医学院、生物工程学院专场，由学院党委书记、副院长宋宝峰副教授介绍2026年医学技术专业硕士点招生情况。该学位点为2024年获批的新学位点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，其中检验技术细分为医检和卫检两个方向。2025年录取64位考生，检验方向38人、影像方向11人、康复方向13人、智能方向24人。2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。
-# 信息同步
-**学位点基本情况**：2024年获得医学技术专业硕士点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养工作，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，检验技术细分为医检和卫检两个方向。
-**2025年招生情况**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能方向24人。
-**学科建设情况**：医学技术2023年获批省一流学科B类；近五年获国家级基金项目19项、省部级项目1项，纵向科研经费1300万，横向合作课题经费2200多万；获省科技进步一等奖2项、二等奖1项、三等奖2项；建成国家级一流本科课程2门、国家级一流本科专业建设点2个；拥有省生物标志物与器官诊断转化重点实验室、省神经系统疾病数字化装备研发重点实验室等多个省级平台。
-**学科优势**：体外诊断领域优势显著，疫情时期与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品并获NMPA注册；医学影像技术方向在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优质方向；康复治疗方向依托省人民医院康复医学科；智能医学工程方向聚焦阿尔茨海默病智能预警生物标志物，居国际领跑水平。
-**主要研究方向**：医学检验技术方向负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制等五大块；卫生检验检疫方向负责人金大志教授，聚焦新发突发传染病病原体检测检验新技术方法开发及卫生检验技术研究；医学影像技术方向负责人徐秀芳教授，含多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；康复治疗方向负责人倪湘明教授，含技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五个方向；智能医学工程方向负责人李海教授，聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断五个方面。
-**师资队伍与领军人物**：专任教师90人，高级职称占30%以上共53人，博士55人；硕导69人，其中正高35人，博士占比46人；有省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。领军人物包括学位点负责人吕建新教授、徐秀芳教授、叶小明教授、金大志研究员、李凯教授等。
-**硕士培养与毕业去向**：培养目标为面向健康中国发展需要、服务区域行业产业发展的高层次应用型人才；全日制专业学位学制三年，最长不超过五年；课程学习实行学分制，毕业前要求取得不少于24个学分，其中专业必修课不少于12个学分，专业选修课不少于5-6个学分；就业方向包括医院相关科室、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等。
-**2026年招考计划**：2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准；初试科目为思想政治理论、英语及对应方向专业综合（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；专业综合满分300分，考试时长180分钟；检验综合中卫生生物学检验占40%、生物化学检验占30%、微生物学检验占30%；参考书及考试大纲以杭州医学院研究生招生网公布为准。
-**复试安排**：复试采用线上线下结合、目前以线下为主；初试占60%、复试占40%；复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%；复试具体形式和内容以学校当年复试录取办法为基础，可参考2025年复试办法。
-**考生问答**：就业前景方面，宋宝峰表示就业优先，专业就业前景非常好，可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等；跨专业报考方面，允许非该专业本科考生跨专业自主报考；交通方面，学校有三个校区，主城区黄路校区交通便利；竞赛方面，学校重视竞赛，以赛促学、以赛促教、以赛促改。
-# 达成共识
-**2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。**
-**初试科目为思想政治理论、英语及对应方向专业综合，专业综合满分300分，考试时长180分钟。**
-**复试采用线上线下结合、目前以线下为主，初试占60%、复试占40%，复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%。**
-**允许非该专业本科考生跨专业自主报考医学技术专业。**
-&gt; 允许非该专业的考生跨专业来报考我们这个医学技术。
-# 待协调事项
-无</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t>23026/2233</t>
+          <t># 杭州医学院医学技术硕士点招生宣讲
+杭州医学院医学技术硕士点招生宣讲
+会议要点：本次直播为杭州医学院医学技术专业硕士点招生宣讲，由检验医学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养工作，聚焦四个主要专业方向：检验技术（细分为医检和卫检）、医学影像技术、康复治疗、智能医学工程。2025年录取64人，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。；学科建设方面，医学技术学科2023年获批省一流学科B类，近五年获国家级基金项目19项，纵向科研经费1300万，横向合作课题经费2200多万，获省科技进步一等奖2项、二等奖1项、三等奖2项；建有国家级一流本科课程2门、国家级一流本科专业建设点2个及多个省级科研平台。师资队伍方面，专任教师90人，高级职称53人（占30%以上），博士55人，硕导69人，其中正高35人，博士占比46人。；2026年招考计划以教育部正式下达为准，初试科目为思想政治理论、英语（统考）及按方向自主命题的专业课（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合），实践分值300分、考试时长180分钟；复试初试占60%、复试占40%，复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%，形式以线下为主。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23026/572</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1" s="9">
+    <row r="32" ht="13.5" customHeight="1" s="10">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:13
@@ -10602,50 +10322,34 @@
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课为历史小论文写作讲评课，围绕自命题类、观点提示类、图表信息类三类题型讲解解题步骤与方法，并逐一分析学生作答。总体要求是观点必须明确亮出，不能只是简单陈述或加个名词；论证写两到三条，不宜太多，要能支撑论点；先打开学术背景再引出自己的观点；可用序号也可直接罗列，但逻辑要清晰，按时间脉络（如700时期、明清时期）或国内外等维度罗列清楚；最后论述要升华观点，不能简单照抄观点。自命题类以武汉长江大桥为例，学生作答涉及新中国成立、改革开放、对内改革对外开放的时间顺序，老师指出按顺序应先写对内改革再写对外开放，并强调要写清时间和重大国家利益。观点提示类以1940年抗战时期某材料为例，学生分析四个观点并选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。图表信息类以中国历代民德等级变化图表为例，涉及春秋、东汉、宋明等时期，讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系。
+本次课程为历史小论文写作指导课，围绕观点明确、论证条理、材料运用等展开。教师通过例题讲解自命题、观点提示、图表信息等题型，并分析学生答案，强调审题、罗列事实、升华观点。课程指出观点必须明确，不能只是陈述形式；论证一般写两到三条，不宜过多；内容需支撑论点；写作顺序可先写背景学术报告再写观点；可用序号或直接列出，但逻辑要清晰，如按时间脉络或国内外分类；最后需进行总结升华，不能简单重复观点。
 # 核心知识点梳理
-**一、小论文写作总体要求**
-- **观点必须明确亮出**：不能只是简单陈述或加个名词，要把自己的观点亮出来，观点还要有凝聚力。
-- **论证写两到三条**：不宜太多，要能支撑论点；先打开学术背景，再引出自己的观点。
-- **逻辑清晰**：可用序号，也可不用序号直接罗列，但要让老师看清写了几条；可按时间脉络（如700时期、明清时期）或国内外、内衣外衣等维度罗列清楚。
-- **最后论述要升华**：不能简单把观点抄一遍，要说明写这个东西是为了什么。
-**二、自命题类解题步骤**
-1. 先审题：看要求，注意「小红帽」的要求及形成标准。
-2. 认真读材料：先抓主要信息，再细看它们之间的关系。
-3. 题目先写好，再罗列事实：事实要与材料相关，不要乱罗列。
-4. 最后进行升华。
-案例：武汉长江大桥。学生作答涉及新中国成立、改革开放；老师指出按时间顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
-**三、观点提示类解题方法**
-- 先看有哪些观点，按选择和观点的关系处理。
-- 选择核心观点，清晰表明自己认为正确或错误，把不同观点在论点中详细表述。
-- 注意不能照抄。
-- 最后简单总结观点并升华。
-案例：1940年抗战时期某材料，四个观点分别为：国民对本国历史应略有所知；了解本国利益会有威胁和利益；对本国历史有敬意则不会偏激；经济方面观点。学生选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。
-**四、图表信息类解题方法**
-- 迅速看图表关键信息，包括题头、横向纵向信息。
-- 注意信息之间的关系变化，提取有效信息再分析。
-案例：中国历代民德等级变化图表，涉及春秋、东汉、宋明等时期；讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
+**小论文写作基本要求**：观点必须明确，不能只是陈述形式；论证一般写两到三条，不宜过多；内容需支撑论点；写作顺序可先写背景学术报告再写观点；可用序号或直接列出，但逻辑要清晰，如按时间脉络或国内外分类；最后需进行总结升华，不能简单重复观点。
+**自命题类题型解题步骤**：先审题，注意要求如世界史知识、范围限制、小红帽要求及形成标准；再读材料，抓主要信息，细看关系；最后控制，先写题目，罗列事实，再论述升华。以武汉长江大桥为例，分析学生答案，指出背景、措施、影响等，强调时间顺序如先对内改革后对外开放。
+**观点提示类题型**：需先看观点，选择核心观点，明确表达自己的判断，不能照抄材料。以1940年抗战时期材料为例，分析四个观点，学生选择第二条，论证中华文化优越性，如丝绸之路、四大发明等，强调敬畏祖国历史。
+**图表信息类题型**：需迅速查看图表关键信息，如题头、横向纵向信息，注意关系变化，提取有效信息进行分析。以中国历代民德变化图为例，讨论不同时期民德高低与政治、思想的关系，如唐朝国力强盛但民德较低，宋朝民德繁盛等，并参考官方答案。
 # 课堂互动与答疑
-问 → 答：学生就武汉长江大桥一题作答，涉及新中国成立、改革开放、对内改革对外开放的时间顺序。老师指出按顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
-问 → 答：学生就1940年抗战时期材料分析四个观点并选择第二条作答。老师追问为什么在这个时期写这个东西，提醒学生写的时候要想清楚写作背景。
-问 → 答：学生就中国历代民德等级变化图表作答，涉及春秋、东汉、宋明等时期。老师引导讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
-&gt; 观点必须明确亮出，不能只是简单陈述或加个名词。
-&gt; 论证写两到三条，不宜太多，要能支撑论点。
-&gt; 最后论述要升华，不能简单把观点抄一遍。
+问：武汉长江大桥的题目如何审题？
+答：要审题看要求，注意是否限定世界史知识或范围，先写题目再罗列事实，按时间顺序如先对内改革后对外开放。
+问：观点提示类题目如何选择观点？
+答：先看观点，选择核心观点，明确表达自己的判断，不能照抄材料，要结合史实论证。
+问：图表信息类题目如何分析？
+答：迅速查看图表关键信息，如题头、横向纵向信息，注意关系变化，提取有效信息进行分析。
+&gt; 教师提醒：观点要明确，论证两三条，逻辑清晰，最后升华。
 # 课后任务与学习建议
 未提及</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>12357/1540</t>
+      <c r="D32" s="11" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12357/926</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1" s="9">
+    <row r="33" ht="13.5" customHeight="1" s="10">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:01:21
@@ -10798,23 +10502,27 @@
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t># 报告概况
-国务院总理李强代表国务院向第十四届全国人民代表大会第三次会议作政府工作报告，请代表审议并请全国政协委员提出意见。报告回顾2024年工作，指出过去一年我国发展历程很不平凡，党的二十届三中全会对进一步全面深化改革、推进中国式现代化作出部署，我们隆重庆祝中华人民共和国成立75周年；面对外部压力加大、内部困难增多的复杂严峻形势，经济运行总体平稳、稳中有进，全年经济社会发展主要目标任务顺利完成，高质量发展扎实推进，新质生产力稳步发展。报告同时指出面临的困难与挑战，明确2025年经济社会发展总体要求和政策取向，并部署2025年政府工作任务。报告强调，今年是十四五规划收官之年，要高质量完成十四五规划目标任务，为实现十四五良好开局打牢基础，并开展十五规划编制工作。
+十四届全国人大三次会议于2025年开幕，出席代表2880人，缺席49人，符合法定人数。会议共有四项议程，第一项为审议政府工作报告，由国务院总理李强代表国务院作报告。报告回顾2024年工作，指出经济运行总体平稳，国内生产总值达134.9万亿元，增长5%；城镇新增就业1256万人，居民消费价格上涨0.2%；粮食产量首次跃上1.4万亿斤新台阶，新能源汽车年产量突破1300万辆；嫦娥六号实现人类首次月球背面采样返回。同时指出外部环境复杂严峻，内需不振、预期偏弱等问题交织叠加。报告提出2025年经济社会发展总体要求，部署十大工作任务，整体基调为稳中求进、迎难而上，高质量完成十四五规划目标任务。
 # 核心政策
-2025年主要预期目标：国内生产总值增长**5%左右**；城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**；居民消费价格涨幅**2%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.4万亿斤左右**；单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。财政政策方面，实施更加积极的财政政策，今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；发行超长期特别国债**1.3万亿元**；发行特别国债**5000亿元**，支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。货币政策方面，实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配。政策取向强调强化宏观政策民生导向，经济政策着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生；打好政策组合拳，健全和用好宏观政策取向一致性评估工作机制。
+2025年主要预期目标：**国内生产总值增长5%左右**，**城镇调查失业率5.5%左右**，**城镇新增就业1200万人以上**，**居民消费价格涨幅2%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，**粮食产量1.4万亿斤左右**，**单位国内生产总值能耗降低3%左右**。实施更加积极的财政政策，**赤字率拟按4%左右安排**，**赤字规模5.66万亿元**，发行超长期特别国债1.3万亿元，拟发行特别国债5000亿元支持国有大型商业银行补充资本，安排地方政府专项债券4.4万亿元，合计新增政府债务总规模11.86万亿元。实施适度宽松的货币政策，适时降准降息。安排超长期特别国债3000亿元支持消费品以旧换新，中央预算内投资安排7350亿元。
 # 重点工作
-经济领域：大力提振消费、提高投资效益，全方位扩大国内需求，实施提振消费专项行动，安排超长期特别国债**3000亿元**支持消费品以旧换新，今年中央预算内投资已安排**7350亿元**；因地制宜发展新质生产力，加快建设现代化产业体系，培育生物制造、量子科技、具身智能、6G等未来产业，持续推进人工智能加行动；推动标志性改革举措加快落地，高质量完成国有企业改革深化提升行动，纵深推进全国统一大市场建设，综合整治内卷式竞争；扩大高水平对外开放，稳外贸、稳外资，扩大电信、医疗、教育等领域开放试点，推动高质量共建一带一路走深走实。民生领域：更大力度稳定和扩大就业，实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；强化基本医疗卫生服务，深化以公益性为导向的公立医院改革，优化药品集采政策；完善社会保障和服务政策，城乡居民基本养老金最低标准再提高**20元**，适当提高退休人员基本养老金，制定促进生育政策、发放育儿补贴；加强精神文明建设，推进群众身边运动场地设施建设。科教领域：深入实施科教兴国战略，制定实施教育强国建设三年行动计划，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科、加快双一流建设；推进高水平科技自立自强，加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合。三农与区域领域：着力抓好三农工作，稳定粮食播种面积，严守耕地红线，有序推进第二轮土地承包到期后再延长30年试点、扩大整省试点范围；推进新型城镇化和区域协调发展，科学有序推进农业转移人口市民化，支持经济大省挑大梁。环保领域：协同推进降碳、减污、扩绿、增长，持续深入推进蓝天碧水净土保卫战，建立一批零碳园区、零碳工厂，加快建设沙戈荒新能源基地。风险防范领域：有效防范化解重点领域风险，持续用力推动房地产市场止跌回稳，稳妥化解地方政府债务风险，积极防范金融领域风险。&gt; 报告强调，确保十四五规划圆满收官，为以中国式现代化全面推进强国建设、民族复兴伟业不懈奋斗。</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>10273/1661</t>
+**经济领域**：大力提振消费、提高投资效益，全方位扩大国内需求，实施提振消费专项行动，安排超长期特别国债3000亿元支持消费品以旧换新，扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展；因地制宜发展新质生产力，培育壮大新兴产业、未来产业，培育生物制造、量子科技、具身智能、6G等未来产业，推动传统产业改造升级，激发数字经济创新活力；扩大高水平对外开放，稳定对外贸易发展，促进跨境电商发展，大力鼓励外商投资，推动高质量共建一带一路走深走实。
+**民生领域**：更大力度稳定和扩大就业，实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；强化基本医疗卫生服务，深化以公益性为导向的公立医院改革，优化药品集采政策；完善社会保障和服务政策，**城乡居民基本养老金最低标准再提高20元**，适当提高退休人员基本养老金，制定促进生育政策并发放育儿补贴，大力发展托幼一体服务；深入实施科教兴国战略，制定实施教育强国建设三年行动计划，逐步推行免费学前教育，推进高水平科技自立自强。
+**环保领域**：协同推进降碳、减污、扩绿、增长，持续深入推进蓝天碧水净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，加快发展绿色低碳经济，积极稳妥推进碳达峰碳中和，建立零碳园区、零碳工厂，开展煤电低碳化改造试点示范。
+**改革与风险防范**：推动标志性改革举措加快落地，高质量完成国有企业改革深化提升行动，开展规范涉企执法专项行动，纵深推进全国统一大市场建设；有效防范化解重点领域风险，持续用力推动房地产市场止跌回稳，稳妥化解地方政府债务风险，积极防范金融领域风险。
+**三农与城镇化**：着力抓好三农工作，稳定粮食播种面积，严守耕地红线，高质量推进高标准农田建设，巩固拓展脱贫攻坚成果；推进新型城镇化和区域协调发展，科学有序推进农业转移人口市民化，持续推进城市更新和城镇老旧小区改造。</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10273/1456</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1" s="9">
+    <row r="34" ht="13.5" customHeight="1" s="10">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:10
@@ -11023,24 +10731,24 @@
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为景城苑项目物业管理服务招标答辩与评审，三家投标单位依次陈述并回答评委提问。长沙富佳物业答辩称改造项目已在标书117页列明共12大改造点、预计一年内完成，针对车辆乱停将先分析原因再增加停车位或派保安客服现场劝阻，承接查验方面提出提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先私下沟通、再请业委会或街道社区组织协调会、仍无法解决则在业委会及业主大会和街道社区许可下采取强制措施，并针对监控门禁失效提出增设人行门禁、升级大堂报到系统、地面增设隔离墩、建设外围停车场、增设电动车停车场五方面改善。深圳资平物业介绍公司成立于04年、总部深圳、全国367个项目其中127个业委会项目、创始人陈志平为万科物业创始人，提出洗理静音、疏金活选、疑难杂症、有效提升四步计划，计划半年到八个月内完成、一年以内保证小区有序，团队编制16人、薪酬福利高于同类项目、一线人员直招不外包；包干制方面称湖南11个项目中10个为包干制，强调财务透明和业主知情权，公益服务包括居家上门免费、家政、24小时业主护送服务等有偿和无偿业务；承接查验方面提出与社区街道派出所沟通、与现有物业及业委会明确设备设施和债务债权、按专业线分组并调动集团工程师协助查验、在16人团队基础上增派150%人员；安保方面提出关键岗位用老员工、来访人员车辆登记核实后放行、收集业主车辆信息制定停车管理方案和公约、升级道闸识别外来人员和业主；针对楼层顶层堆放杂物和乱搭乱晒提出宣传引导、联合社区应急管理部门、给业主时间段处理杂物、设集中晾晒区并提供免费上门拉送增值服务，强调要疏而不是强制。评标环节评委打分去掉一个最高分和一个最低分，品牌质量需三人签名，打分环节全程保密、暂停会场网络直播、录像材料不予公开。公布排名为第二名长沙富佳物业管理有限公司72.91分、第三名湖南恒居恒基居业物业管理有限公司60.73分、第四名重庆新东源物业管理有限公司54.48分，第一名中标候选人为深圳市资平物业发展有限公司。
-## 富佳物业答辩
-- 评委问中标后从哪些方面改善小区现状及预计时间，富佳回应改造项目已在标书117页详细说明，共12大改造点，预计一年内完成。针对车辆停放不规范、电动车乱停现象，富佳回应先分析乱停原因（停车场地不够、业主觉得远、不自觉），再针对性制定措施：车位不够则增加停车位，不自觉则派保安和客服现场说服劝阻纠正。承接查验方面，富佳称有丰富二手小区交接经验，提前两周项目负责人入场摸底，提前一周服务人员到位培训；交接分顺利和不顺利两种情况，不顺利时先与县物业私下沟通，公司间无法解决则请业委会或街道社区组织协调会，仍无法解决则在业委会、业主大会及街道社区许可下采取强制措施。针对监控门禁失效与停车管理混乱，富佳提出五方面改善：大门口增设人行门禁系统（微信、卡、密码进出）；升级大堂大门报到系统，录入业主车辆信息统一管理，临时车辆由安保登记放行；地面增设隔离墩禁止公共场所停车，保证消防和人行通道畅通；建设外围停车场并安装停车管理系统；增设电动车停车场。关于类似项目管理经验与满意度收费率，富佳称没有很相似的小区，采取用心倾听、如实记录、马上处理、及时反馈的方法处理业主投诉和反馈。
-- 评委问包干制经验及中标后公益性福利拓展服务，资平称湖南11个项目中10个为包干制，强调财务透明和业主知情权，团队直招，管理干部30%来自现有、60%左右来自现有物业优秀员工及招聘，公益服务包括居家上门免费（材料费业主自买或代购）、家政、24小时业主护送服务等有偿和无偿业务。承接查验方面，资平提出前期准备要充足，与社区街道派出所沟通，与现有物业及业委会明确设备设施和债务债权；按专业线分专业组，调动集团工程师协助查验；在现有16人团队基础上增派150%人员；成立成熟小组，建立标准，确保查出问题不遗留不明事项。安保方面，资平回应关键岗位（门岗、门勤岗、车务）用老员工，对来访人员和车辆管控登记核实后放行；收集业主车辆信息，制定停车管理方案和公约，升级道闸识别外来人员和业主；监控方面利用自有设备公司和技术手段解决关键岗位和部位监控。针对楼层顶层堆放杂物与乱搭乱晒，资平提出宣传引导，上门宣传和海报，让业主明白风险和法律责任；联合社区应急管理部门；全面沟通；给业主时间段处理杂物；物业可提供闲置区域临时堆放但限期解决；针对晾晒，设集中晾晒区，物业可提供免费上门拉送增值服务，强调要疏而不是强制。
-## 评标结果公布
-- 评委打分去掉最高最低分，品牌质量需三人签名。公布排名：第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。第一名中标候选人为深圳市资平物业发展有限公司。打分环节全程保密，暂停会场网络直播，录像材料不予公开。</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>11743/1996</t>
+本次会议为景城苑小区物业招标答疑及评标会，两家物业公司（富家物业、资平物业）分别回答业主关于改造计划、停车管理、承接查验、安防整改等问题。富家物业提出具体改造项目在标书117页，预计一年内完成；停车管理方面提出分析乱停原因、增加停车位、保安劝阻、增设隔离墩、建设外围停车场、增设电动车停车场；承接查验方面提出提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先私下沟通，再请业委会或街道协调，必要时采取强制措施；安防方面提出增设人行门禁系统、升级大堂报到系统、登记临时车辆、增设隔离墩、建设外围停车场；业主满意度方面提出四句话：用心倾听、如实记录、马上处理、及时反馈。资平物业提出四步举措：进场一个月集中资源整改环境绿化，半年内排查设备设施，八个月内完成重大改造，一年内保证小区有序；停车管理方面提出收集业主车辆信息、制定停车管理方案、升级道闸系统、技术手段监控；承接查验方面提出前期准备充分，与社区街道派出所沟通，分专业组查验，增派150%人员；安防方面提出关键岗位用老员工、登记核实外来车辆、升级道闸、技术手段监控；业主满意度方面提出财务透明、管理透明、导入顾客管理系统、大数据管理投诉、开展社区文化活动；包干制经验方面介绍在湖南有11个项目，其中10个包干制，强调财务透明、团队直招、管理干部选拔，提供居家上门免费服务、家政、24小时护送等；楼层杂物与晾晒问题方面提出宣传引导、联合社区应急部门、上门沟通、设置临时堆放区、集中晾晒区、免费上门晾晒服务，强调疏导而非强制。评标委员会打分，去掉最高最低分，全程保密。最终评标结果：第一名（中标候选人）为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒基恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。
+## 改造计划与时间
+- 富家物业称具体改造项目在标书117页，预计一年内完成。资平物业提出四步举措：进场一个月集中资源整改环境绿化，半年内排查设备设施，八个月内完成重大改造，一年内保证小区有序。
+- 富家物业提出分析乱停原因，增加停车位、保安劝阻、增设隔离墩、建设外围停车场、增设电动车停车场。资平物业提出收集业主车辆信息、制定停车管理方案、升级道闸系统、技术手段监控。
+## 承接查验与安防整改
+- 富家物业提出提前两周项目负责人入场摸底，提前一周服务人员到位培训，交接不畅时先私下沟通，再请业委会或街道协调，必要时采取强制措施。资平物业提出前期准备充分，与社区街道派出所沟通，分专业组查验，增派150%人员。安防方面，富家物业提出增设人行门禁系统、升级大堂报到系统、登记临时车辆、增设隔离墩、建设外围停车场；资平物业提出关键岗位用老员工、登记核实外来车辆、升级道闸、技术手段监控。</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11743/1173</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1" s="9">
+    <row r="35" ht="13.5" customHeight="1" s="10">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:05
@@ -11159,35 +10867,25 @@
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本期由李正主讲，讲述康熙朝总理南书房大臣、文渊阁大学士陈廷敬的一生。讲座分三个阶段：母亲张氏的开蒙、圣祖康熙的讲师、至公无私的落幕。主讲人首先澄清影视剧中陈廷敬支持撤藩、招抚台湾、维护征剿噶尔丹粮草等情节历史上均未做过，但康熙临终前仍询问大臣中是否有像陈廷敬一样的人。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第六代读书为官，母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》，14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
+本期视频由主讲人李正（正直讲史）讲述康熙朝文渊阁大学士陈廷敬的一生，分为母亲张氏开蒙、圣祖康熙的讲师、至公无私的落幕三个阶段。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第，六代读书人。影视剧中支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但康熙临终前仍询问是否有类似陈廷敬的大臣。陈廷敬童年由母亲张氏开蒙，6岁前已背诵《论语》《孟子》《大学》《中庸》《诗经》，14岁以全省第一考中秀才，20岁中举，21岁中进士入翰林。入翰林后因与直隶通州陈敬重名，主动上书改名，顺治赐“廷”字。顺治18年庶吉士毕业考试获第一，授秘书院检讨，同年顺治驾崩，康熙元年母亲病倒，请假归乡三年。重返官场后，康熙六年考察一等，两年后升国子监司业，整顿收礼陋习。康熙11年充日讲起居注官，康熙15年充经筵讲官，教学风格外放。康熙16年任翰林院掌院学士，同年母亲去世，康熙破例派大臣祭奠，礼部反对后康熙坚持追封。康熙23年任左都御史，上奏捐纳者需考试，获康熙支持并扩大至已任官员。康熙26年亲家张谦贪污案牵连陈廷敬，康熙令密查不蔓延，陈廷敬主动辞官，一年后复任左都御史。康熙42年任文渊阁大学士，总理南书房，70岁起四次申请退休，康熙49年准奏并赐匾联。75岁病逝，谥号文贞。
 # 核心观点与论证
-第一阶段「妈妈张氏的开蒙」：论点为陈廷敬童年学习一大半在母亲张氏关照与注视下展开。论据包括：母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，嫁入陈家后每日干完家务即读书背诵，半夜不睡继续看书；陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》；9岁作《咏牡丹》诗，母亲夸其为天才；14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
-第二阶段「圣祖康熙的讲师」：论点为康熙重用陈廷敬主要因其课教得好、专业过硬、教学风格外放狠辣。论据包括：陈廷敬入翰林时与直隶通州同届进士陈敬重名，因对方不习清书被顺治点名批评并罚俸一年，22岁的陈廷敬主动上书改名廷敬，传说廷字为顺治所赐；顺治18年庶吉士毕业考试获同届第一，授秘书院检讨；顺治驾崩、母亲病倒后请假归乡三年；康熙六年考察一等称职，32岁升国子监司业，整顿国子监拒收学生见面礼，两年内连升三级，34岁官居翰林院侍讲学士，35岁被19岁康熙任为日讲官；康熙15年九月以内阁学士兼礼部侍郎充经筵讲官，时年39岁；康熙16年正月任翰林院长院学士教习庶吉士，同年母亲张氏去世，终年59岁，康熙令满汉一体遣大臣往祭，礼部以封号不合规反对，康熙追封按学士品级官方祭奠。
-第三阶段「至公无私的落幕」：论点为陈廷敬21岁入官场，75岁去世，宦海浮沉50年声名清白、恪守初心。论据包括：康熙20年守孝三年后重返官场执掌翰林院；康熙23年47岁升从一品左都御史，上奏要求捐纳买官者正式上岗前追加考试，吏部反对，康熙支持并令各地督府详查已任命官员，凡不识字义者查参修治；此后连续出任工部、户部、吏部三部尚书。康熙26年50岁时湖广巡抚张谦贪污案发，张谦为陈廷敬老乡兼亲家，口供称曾贿赂陈廷敬、徐乾学、高士奇，证据为三人劝其好好当官的信件；康熙传旨主审官马齐只处理张谦一人，不得扩大株连，其他人事后密查；51岁陈廷敬主动上书辞官，康熙准许辞官但留京修书；康熙29年53岁重新启用为左都御史，后一年刑部尚书、六年户部尚书、四年吏部尚书；康熙42年66岁升文渊阁大学士兼总理南书房；康熙46年70岁起连续三次申请退休被拒，康熙49年73岁第四次申请获准，康熙赐匾额五亭山村及楹联；两年后病逝，终年75岁，谥号文贞。
-争议点：张谦案真相至今没有公开定论，康熙一时间无法确定徐乾学、高士奇、陈廷敬三人谁干净谁不干净；主讲人个人倾向陈廷敬无辜，理由为李光地称张谦案始终皆徐乾学所为、徐乾学贪污事迹多且热衷结党、徐乾学与高士奇后均因贪污被罢官而陈廷敬仅辞官一年即被康熙重新启用为左都御史。
+讲座按时间顺序分三阶段展开。第一阶段“妈妈张氏的开蒙”：陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第，六代读书人。母亲张氏自幼随父张弘毅读书，精通儒家经典，婚后仍勤学不辍，陈廷敬6岁前已背诵《论语》《孟子》《大学》《中庸》《诗经》。9岁作诗《咏牡丹》获母亲称赞。14岁以全省第一考中秀才，20岁中举，21岁中进士入翰林。入翰林后因与直隶通州陈敬重名，对方不习满文被顺治罚俸，陈廷敬主动上书改名，顺治赐“廷”字。顺治18年庶吉士毕业考试获第一，授秘书院检讨。同年顺治驾崩，康熙元年母亲病倒，请假归乡三年。第二阶段“圣祖康熙的讲师”：重返官场后，康熙六年考察一等，两年后升国子监司业，整顿收礼陋习。康熙11年充日讲起居注官，康熙15年充经筵讲官，教学风格外放，曾痛骂孙权背刺关羽。康熙16年任翰林院掌院学士，同年母亲去世，康熙破例派大臣祭奠，礼部反对后康熙坚持追封。第三阶段“至公无私的落幕”：康熙23年任左都御史，上奏捐纳者需考试，获康熙支持并扩大至已任官员。后历任工部、户部、吏部尚书，整顿各领域。康熙26年亲家张谦贪污案牵连陈廷敬，康熙令密查不蔓延，陈廷敬主动辞官，一年后复任左都御史。康熙42年任文渊阁大学士，总理南书房，70岁起四次申请退休，康熙49年准奏并赐匾联。75岁病逝，谥号文贞。
 # 金句总结
-「朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？」——背景：康熙临终前仍询问陈廷敬，体现康熙对陈廷敬的念念不忘。
-「无鼠相存，譬犹唇齿，不必智者而知之。全记上书以讨荆州自效，明年全破斩云长传其手，全其屯权也哉。」——背景：陈廷敬在文集中指责孙权背刺关羽，体现其教学风格外放狠辣、三观坚定。
-「以平靖世将握秦而恩福待，吾何以劝劳臣乎？」——背景：礼部反对官方祭奠陈廷敬母亲，康熙以此表态，最终追封按学士品级祭奠。
-「自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。」——背景：陈廷敬任左都御史时上奏要求捐纳买官者追加考试。
-「临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治。」——背景：康熙支持陈廷敬并令各地督府详查已任命官员。
-「臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节，所以臣之心迹极此可白，而臣之自处虚实所疑，唯当隐退田间，永衔恩于高厚。」——背景：陈廷敬因张谦案主动上书辞官。
-「朕特殊匾联赐卿，自此不与人写字矣。」——背景：康熙49年准陈廷敬退休，赐匾额五亭山村及楹联。
-「苟正其身矣，于从政乎何有？」——背景：主讲人引《论语》总结陈廷敬一生，称其儿时学过的道理直到死都没有违背过。
+“朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？”——康熙在陈廷敬临终前询问是否有类似大臣，体现对其学问人品的极高信任。“自古未有不晓文艺之人可以为民父母者也”——陈廷敬主张捐纳者需考试，强调父母官必须有文化。“苟正其身矣，于从政乎何有？”——出自《论语》，陈廷敬一生践行，自身品行端正则治理政事无困难。
 # Q&amp;A 环节
 未提及</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>9132/2003</t>
+      <c r="D35" s="11" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9132/1318</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="13.5" customHeight="1" s="9">
+    <row r="36" ht="13.5" customHeight="1" s="10">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:03
@@ -11804,78 +11502,61 @@
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本次对话由马先生与当年明月参与，围绕刚播完的日本历史剧《大奥》与《明朝那些事》展开。当年明月指出《大奥》三部跨越日本晚清至明治维新前，吸引他的是严谨精神，剧中演员认真、片头将军出场时众人呈45度鞠躬的场面令他印象深刻；马先生补充大奥即后宫之意，日本话中“奥”指屋子最深处，大奥规矩严谨、后宫不许进人。当年明月由此引申日本文化核心是极端精神，即所有事情做到尽头，并以日本战后用30年成为世界第二经济强国、且是强国中唯一没有资源的国家为例。马先生则从多次赴日经历谈到日本人的坚韧不拔与忠诚，称日本是忠诚文化的典型国家，并举例日本豆腐厂规定当天做当天卖、夜里11点45分所有人坐着看表、12点整才开始干活。话题转向明朝历史与《明朝那些事》，当年明月表示自己写明朝是因为明史最熟、资料最多，历史研究两大难点是先秦与明清，明清资料如明实录几千万字、明通鉴、明史记事本末、明会典等堆得比山高，但一个说法可能有七个不同。当年明月表示推崇朱元璋，因为他是历史上唯一由最底层乞丐坐上皇位的人，刘邦好歹是村长，朱元璋要过饭、知道每一层猫腻所以疑心重，推翻元朝当上皇帝并定下明朝规章制度、基本没有太大改动。当年明月还称“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因为史书只留下照片、而古人的生活是录像，不知道当时的前因后果，不能套用。
+本期《锵锵三人行》由主持人窦文涛与嘉宾马未都、当年明月围绕日本历史剧《大奥》与明朝历史展开对谈。节目先讨论《大奥》所反映的日本历史阶段与文化精神，认为其严谨、极端、忠诚的文化特质与中国的“中庸”精神形成鲜明对比，并以日本战后三十年成为世界第二经济强国、终身雇佣制、跳槽率、豆腐厂凌晨作业等事例佐证。随后话题转向明朝历史，当年明月解释自己写明史是因为明史资料最多但说法不一，并讨论朱元璋的崛起、明朝制度、明末市民生活、正德与天启等皇帝的个性行为，以及明式家具在国际上的地位。
 # 访谈详细记录
-一、《大奥》与日本文化
-- 当年明月指出《大奥》三部大概前两部相当于中国的晚清到清初这个时段，后来还有一部是在明治维新之前的一段时间，是一个有跨越性的历史剧。
-- 当年明月称吸引他的是觉得有一种严谨的精神，回头看三国演义会看到很多群众演员会笑，但看日本剧看不到笑的，每一个人非常认真、特别有专业精神，而且都像大腕跟那演。他看第一集一个片头就被震了：将军出场的时候，所有的人呈45度开始鞠躬，依次那个场面之华丽，包括色彩，一看就不一样。
-- 马先生称大奥就是咱们的普通话叫后宫，日本话的这个奥是指很深的地方，就是屋子最里处叫奥，比如咱们现在还保留这种痕迹，就是说这个道理，深奥，奥是很深的地方。
-- 当年明月称从大奥那个剧可以看出来，一个日本文化，其实他从头到尾没有变，就是日本人一种精神，叫极端精神，所有的事情要做到尽头。
-- 马先生称日本战后1945年以后，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然，就是他全民族的这种极端精神，是一个国家在战后这样一个不利的局面下，只需要30年的时间，他进入世界第二经济强国，是以绝对量，不是人均量，绝对量，他是一个世界上这个强国里唯一没有资源的国家。
-- 当年明月称日本的文化跟中国的文化存在一个极大的不同，中国的文化精神是中庸，讲究这个世界上有一种道，不是对也不是错，不是黑也不是白，不是真理也不是谬误，就是太极，但是这条路可以走得通，叫融合。他以马先生家具店中拿了一番木头，特别硬的木头，上面刻的是云彩为例，说这么硬的一个东西能做的这么柔软，这就是中庸。
-- 当年明月称日本的精神就恰恰相反，他坚持一个原则，假如一个炮手开炮的时候，当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。
-- 马先生称我们文化中有很多东西可以从电视剧里去看，他实际上看很大程度是看日本文化，我们的文化跟他的差异性非常大，所以导致很多民族的这个观念性的冲突。他去过、多次去过日本，在日本中没有感受到很难过的时候，也没有谁对你非礼。文化上的差异从这个电视剧看得清清楚楚，比如日本人的坚韧不拔，他说的做到极致，再有他的一个忠诚，它是一个忠诚文化的典型国家。
-- 马先生称日本人的跳槽率是最高的，每一次跳槽都是社会资源的浪费，你刚把这个人培养好了，能给你为你工作了吧，他跳槽了。当年明月称这是经济学上的一个奇迹，西方经济学还是不能理解，为什么他们有一个原则，经济学原理可以讲，叫终身雇佣制，就是这个缺乏竞争，日本可能公司终身雇佣，不会解雇你的，一定会导致工作效率的极低效，但是日本不对，日本是终身雇用了，人家还是基金特别高。
-- 马先生举例日本豆腐厂规定当天做当天卖，夜里11:45，所有人都在那做好不动手，在那坐着看着表，那表到12点，夜里12点一整，所有人都赶紧开车，最后那秒是8一到那所有人开始干活，然后到4点多钟干完，然后就开始上市。当年明月称这叫一丝不苟。
-- 当年明月称日本没有资源，什么都没有，还经常火山地震，说难听点你跑都没地方跑，所以人本身对这个世界有一种极强的求生欲望，或者说他对于这个世界是悲观的，必须努力求生存的，所以他就学会了一点，人只有融入到那个团体之内，按照一个固定的规则去做事，于是我们才能往前走，才能生存下来。
-- 马先生称日本的这种聪明人都没有生存环境，他社会的那种文化的抵制是非常难过的。他举例日本原来做绳子，可能一根绳子能做到全日本第一的人，他在长达几年的时间内是不赚钱的，他是从这个地把什么批发出来给那个人送去1分钱都不赚，那所有人跟他竞争是竞争不过，因为他是不赚钱为代价的，等他全部把市场都铺平了以后，他会把两张单子给你看，你看我是这个钱进的，就是这个钱卖的，你怎么也得让我挣一点钱吧，你能不能让给我2%，然后这时候是不好意思再给你加个2%，拿这张单子跟这边说，你看我卖了以后这个也不挣，所以你再给我加2%，那全国的东西它就4%就是不得了的一个数，它就挣那么大钱。
-- 当年明月称慢慢来才是最快的方法，所有人按照自己的角度去做自己的，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走，我是商人就做商人事，我是奶妈就做奶妈的事，我是王后就做王后的事，我什么都可以做自己的事，就是不管别人的事，但这种情况下，形成合力就非常可怕。
-- 当年明月称说实话这是很不愿意做日本人，因为他很多时候就像你说盲从，他们本身还有一个特点，有一种寻死的那种潜在欲望，看樱花开的时候不看，发芽都不看，就是落那一天就看，他们总觉得由于常年以来生活在岛国上，确实生态环境太恶劣了，所以他对于死亡他不是说藐视死亡，他是应该说是有点向往的感觉，或者说不惧怕。他称二战日军到中国会有那么暴行，他是一种藐视生命。
-- 马先生称日本民族不是藐视生命，他是重视，是翻着的，日本人在经济危机的时候，很多身家万贯的跳楼。
-二、明朝历史与《明朝那些事》
-- 当年明月称自己写明朝是因为明史最熟，因为明史的资料最多，历史界研究有两个难点，第一个是先秦，第二个难点就是明清，明清没法说，明实录几千万明代史官的记录，明通鉴、明史记事本末、明会典等堆的比山还高，但一个说法可能有七个不同，一个事件可能有七个不同的说法，就好像罗生门，一件事五个人看，个个都不同。
-- 马先生称明朝本身260多年的过程本身就跌宕起伏，从某种意义上讲，明朝几次都要死没死了，土木堡之变、夺门之变就是各种之变特别多，皇上已经被瓦剌军给抓起来了，要把弟弟扶起来，这类事完全构成一个现代版的电视剧，因为只有电视剧才能捏造出来这种极为离奇的情节，但生活中不幸就发生了。
-- 当年明月称推崇朱元璋，因为一个乞丐，历史上由最底层的人坐在位上，叫他独此一个，刘邦好歹是个村长，朱元璋要过饭，他因为知道每一层的猫腻，他就疑心重，但他全知道，这种人才上。他称朱元璋从一起干，一直到最后，推翻元朝，当上了皇帝，定了多少规章制度，明朝的规章制度是由他定下来的，基本上没有什么太大的改动，这个人是多了不起的人才。
-- 马先生称人的因素最大，就是改变时势一定是出现一个人，是英雄史观。
-- 当年明月以亮剑中李云龙没上过军事院校能打仗为例，称会打仗的人打，不用看兵书，一个人到战场上死死生生多少年，没死，最后积累下来经验，然后一上战场就知道敌人会往哪走，我该怎么打。
-- 当年明月称历史最重要的是你要明白它是发生过的，很多人看历史会觉得这个故事好玩，他不好玩，旁观者你看的多好玩，一跺脚就去参加起义去了，那不可能，你想他掉脑袋的。他称你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
-- 马先生称明朝还是有很多时期非常不错，比如明朝的仁宣盛世，现在不怎么提，时间因为太短，晚明的时候尽管过去史书上一代说政治如何如何黑暗，皇帝如何如何不上朝，但老百姓生活很好。
-- 当年明月称明末那段时间很多真相都被掩盖了，那个市民生活特别特别轻松，想去哪去哪，当时连那个皇册都不用了，到处走，而且当时去给人打工，当年江浙一带兴起的工商业，就是给人当雇工，那活得很滋润，就像三言二拍这种市民小说，娱乐产品出现才说明它是有能够养活自己的资本了。后来李自成那个时候闹起义，那是因为那个时候陕西那一带发生了大规模的灾荒。
-- 马先生称当时江南的也比电影中很多当时的器皿中就可以看到人的那个生活的乐趣，比如一个瓷器，我们的工艺品到了明末的时候彻底改观，变得非常精细，有点像日本的工艺，非常精细，日本有很多东西学我们明末的，派了大量的工匠跟中国交流。
-- 当年明月称看到的史料就是穿什么都有，至少江南那一带他确实非常富裕。马先生称吴门画派像文征明、唐寅，都是那个时期的，他如果生活不好，这些人就也画不出那个东西来，他画的一定都是兵荒马乱的。一到朱耷的时候，八大山人，他默了，你看他画的都是那翻白眼，为什么呀？就他对这社会有点愤愤不平了。他前面这部分人，吴门画派的那些人都能画的都是那个小桥流水，画一个风雨归舟图都是充满了欣赏的感觉。
-- 当年明月称我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训，因为这事儿不是你办的，你总觉得那个以往人就该怎么办，都是聪明的，错误的，我们没有意识到一个问题，历史他那个事儿发生的时候是有背景的，当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。他称我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像，在史书上下来的只是一个照片咔嚓，但你不知道为那一幕之前和之后是什么，你就不知道他当时为什么要做这个选择，所以很多人对历史有误解，他总觉得从中可以得到什么经验教训，那千万不能套用。
-- 当年明月称明代这个朝代很有趣，什么都有，宦官专政魏忠贤，文官专政张居正，皇帝专政朱元璋，而且什么都能发生，皇帝出去了还能回来，回来了还能做皇帝。
-- 当年明月称晚明时期就更可笑了，吴三桂要跟满清合作要入关，陈圆圆，但是还有个原因，他认为崇祯死了，当时人家的说法，我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝，崇祯皇帝当然可以不死，早点跑应该不跑。还有包括1644年就是明朝灭亡那一年，为什么你们曾经打到京城没有人抵抗呢？因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天你看疙瘩瘟就什么天花。
-- 马先生称中国的历史王朝300年都是大限，你一逼近300年的时候，你自己就没了，和人一样，这人一到八九十岁的时候，你的大限就快到了。他称中国历史上如果严格的讲，超过300年大限的只有宋朝，南北宋接上以后，因为他好在是接上的，汉朝中间往往隔断14年是彻底空的，那么他呢是退让了大半个国土，保证了他延续了300年，剩下的唐朝、明朝、清朝都没他。
-- 当年明月称你说你今天数世界上公司超过279人有几家？没有几家，人家公司多容易管呐，当年刚成立的时候可能三五个人，你说明朝做多大多大摊子啊？几千万人。
-- 马先生称中国在宋明这两个朝代是典型的汉人政权，汉人是文人政权，文人肯定是欣赏的审美都比较高，所以他对美的判断不是表象的，但是满族因为他毕竟是个异族，他进来以后呢，他对你的判断都是表象的。他称今天凡是那种非常外在的直观能看到的都卖的非常贵，但是在100年前的时候，就是晚清到民国初年的时候，这个东西值钱的一定是素雅的。
-- 当年明月称明朝皇帝九五至尊，想干什么干什么，但皇上说我要去一趟江南，皇上当然不行，真不行就不行，咱就是不让你去，明武宗要去，不让去不让去，跪金水桥前门，就是全部跪了，跪着抗议，后来气坏了，就到锦衣卫去打，打死了十几个。
-- 马先生称这种文化的力量，我们一直过去有时候老忽略这种力量，我们现在是没这种文化的力量，他文化的力量是一个超出我们想象的。
-- 当年明月称明武宗正德到扬州说我要什么东西，这时候没有啊东西没有了，有也不给，然后就说什么，那行，那我就回去，他让人准备酒席，他说那个吃不了，说怎么办呢？这样吧，把你们那个酒席折合的银两我带回去，我这皇帝他打这个秋风。
-- 马先生称正德皇帝在明朝的整个皇帝不是一个最最特殊的行为，最鬼怪个性，我们对他的过去的评价是非常低的，说他荒淫，报房是他闹的。他称爱当木匠的是天启，最后了直接干活，干完活了他干的乐就更更有意思，他干完活以后，他拆大盆去卖，卖完回来还打听，卖的怎么样？他说卖的很好，他成就感特大。
-- 马先生称他从侧面去反映了当时社会的一种时尚，他绝对不是凭空，当时这个家具在每个人心里边地位高，为什么我们明式家具现在在国际上那么高的地位，这绝对不是偶然的，所有的偶然中一定有个必然的因素，当时皇帝能下那么大力气去做，可见这个东西对他的影响之深。
-- 当年明月称明神宗几十年不上朝，但他不出去，包括明武宗正德，但凡是明朝皇帝，一般说来后人是不会说乾隆自己朝代的呀，我都是明朝人，我怎么会说我朝的皇帝多差呢？为什么他特别差？因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以他不能够把他写的太好，所以说像正德皇帝为什么说他特别荒淫？我们都来报房，其实就玩，报房，他那个有动物园，他真是有动物园，他里边养了豹子，后宫也是女人嘛，爆房也是女人，放哪都是一样的，不影响其他什么问题。
-- 马先生称正德皇帝是有定论的，说清朝明朝最荒淫的皇帝，那清朝最荒淫的是咸丰，咸丰干的那个事都很过分，但咸丰还留了个种，这正德不留种，这事很奇怪，就他这个人没少找女人，但他不留种。当年明月称不好说。马先生称他有没有生育，有记载他怀过吗？但反正他就是没有正宗的传下来，到嘉靖这是拐弯嘛。
-- 马先生称正德皇帝对东平以外的那个女人确实没兴趣，那女人是被训练过的，禁忌多，太保守了，再说这人是王丽一去就自个就先睡了半边，那个民女不知他是谁，不是圆了干，他就不一样，关键是野花不知道他是。
-- 当年明月称据说是去过，但是这个没有具体的史料能够去，哪个史官说皇上今天出去嫖娼，我要打死了，不能记的。他称这个人绝不是史料上所写的那么那么蠢，他从江南回来，他没有进京城，他在通州先停了半年，为什么呢？先派人打探里边有没有人带，这是史料记载，通州停了半年或一天，先停在这，你们先给我把情况看清楚，京城里有没有人想搞埋伏，搞圈套。马先生称很有城府。
-- 当年明月称这个人还真的是被写坏的，就是嘉靖那个时候因为明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般来说，他都有某些程度的偏颇，因为如果你把他说太好，嘉靖上台先搞了个叫什么大礼仪事件，为这事死了很多人，也折腾了很多人，就会给自己父亲真的明白，因为他父亲是王，他又把他追封为皇帝。所以说历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
-- 马先生称看很多人专家写历史，就觉得现在不爱聊什么西方傲慢与偏见嘛，实际很多人研究历史就有傲慢与偏见，就是你没有设身处地，你老觉得你自个聪明，我判断他昏庸无能。
+议题一：日本历史剧《大奥》与文化差异
+- 当年明月认为《大奥》是一部非常优秀的剧，反映日本历史阶段：前两部相当于中国晚清到清初，第三部在明治维新之前，具有跨越性。
+- 当年明月指出《大奥》吸引他的是严谨精神，日本历史剧中群众演员不会笑，每个人都认真、有专业精神。
+- 马未都解释“大奥”即后宫，日本话“奥”指很深的地方，如“深奥”。
+- 当年明月提到日本天皇是摆设，实际权力在幕府将军，德川家康开创德川幕府后权力集中；曾有一段天皇没钱办活动，找将军要钱被拒，最后活动没办，天皇以退位抗议。
+- 当年明月认为日本文化体现“极端精神”，所有事情做到尽头；战后1945年日本用30年成为世界第二经济强国（绝对量），是必然，源于全民族极端精神，且日本是世界上强国中唯一没有资源的国家。
+- 当年明月对比中日文化：中国文化精神是“中庸”，讲究融合，不是对错黑白之间，而是最适合的路；日本精神坚持一个原则，如炮手忘记一切只记得开炮即达最高境界。
+- 马未都强调日本是忠诚文化的典型国家，多次去日本未感到难过或非礼；日本跳槽率最高，但终身雇佣制下效率仍高，是经济学奇迹。
+- 马未都以《大奥》中阿福为例：25岁进大奥当奶妈，65岁去世，40年做事不处私心，完全公心，被所有人认为楷模。
+- 当年明月指出“慢慢来才是最快的方法”，所有人按自己角度做事最节省成本，形成合力非常可怕。
+- 马未都举例日本豆腐厂规定当天做当天卖，夜里11:45所有人坐等，12点整开始干活，4点多干完上市，体现一丝不苟。
+- 当年明月认为日本民族因岛国环境恶劣、资源匮乏、火山地震，对世界悲观，必须努力求生存，融入团体按规则做事才能生存；日本聪明人没有生存环境，文化抵制强烈。
+- 马未都举例日本做绳子的人几年不赚钱，以不赚钱代价铺开市场，最后加价4%赚大钱。
+- 当年明月表示不愿做日本人，因其常盲从，且有寻死的潜在欲望，看樱花只看落的那天，对死亡不惧怕甚至向往，藐视生命，二战日军暴行源于此。马未都则认为日本民族不是藐视生命，而是重视，是“翻着的”。
+议题二：明朝历史与明史研究
+- 当年明月解释为何写明史：明史资料最多，他最熟；历史研究有两个难点，一是先秦（如孙武事迹在史记中仅一两篇，多为编造），二是明清，因史料说法不一，一个事件可能有七个不同说法，如“罗生门”。
+- 马未都补充明朝260多年过程跌宕起伏，如土木堡之变、夺门之变，皇上被瓦剌军抓走，情节离奇如现代电视剧。
+- 当年明月推崇朱元璋：从乞丐到皇帝，历史上由最底层人坐上位仅此一个；刘邦好歹是村长/乡长；朱元璋因知道每层猫腻而疑心重，但定下明朝规章制度，基本无大改动，是了不起的人才。
+- 马未都认为人的因素最大，改变时势一定出现一个人，是英雄史观。
+- 当年明月以朱元璋被汤和劝参加起义军、因信差送信被告发而被迫起义为例，强调历史最重要的是明白它是发生过的，旁观者觉得好玩，但当事人面临掉脑袋风险。
+- 马未都认为明朝经验体现在兴亡上，如仁宣盛世、晚明市民生活好，有文徵明、金瓶梅、三言二拍等娱乐产品，江浙工商业兴起，市民生活轻松；李自成起义因陕西灾荒。
+- 马未都指出明末工艺品变得精细，日本派大量工匠交流学习；吴门画派如文徵明、唐寅画小桥流水，心态轻松；八大山人朱耷画翻白眼，因对社会愤愤不平。
+- 当年明月说“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因历史发生时有背景，你不比前人聪明，甚至可能更笨；史书是照片，生活是录像，不能简单套用经验教训。
+- 当年明月认为明朝有趣：宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去还能回来做皇帝；吴三桂入关为崇祯复仇，崇祯本可早跑；1644年北京有瘟疫（疙瘩瘟，可能天花），导致无人抵抗。
+- 马未都提到中国王朝300年大限，超过300年的只有宋朝（南北宋接上，退让大半个国土），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
+议题三：明代皇帝与明式家具
+- 马未都对比宋明汉人政权与满清异族政权审美：汉人政权是文人政权，审美高，对美判断非表象；满族是异族，判断表象，如故宫大红大紫是满族趣味；今天外在直观的东西卖得贵，100年前晚清民国初值钱的是素雅的。
+- 当年明月举例明朝皇帝受限制：明武宗要去江南，大臣跪金水桥抗议，皇帝打锦衣卫打死十几个；到扬州要东西没有，准备酒席吃不了，折合银两带回，皇帝“打秋风”。
+- 马未都提到正德皇帝是明朝最荒淫皇帝（清朝最荒淫是咸丰），但正德不留种，没有正宗传下来，到嘉靖拐弯；正德对宫内女人没兴趣，因女人被训练过、禁忌多，他乔装改扮找民女。
+- 当年明月为正德翻案：明武宗实录是嘉靖朝杨廷和等人编的，有偏颇，因嘉靖上台搞大礼仪事件，追封自己父亲为皇帝，若把正德写太好则不利；正德从江南回来在通州停半年，先派人打探京城有无埋伏，说明有城府，被写坏了。
+- 马未都提到天启皇帝爱当木匠，干完活拆大盆去卖，卖完打听卖得怎么样，成就感特大；反映当时社会时尚，明式家具在国际上地位高，所有偶然中必有必然因素。
 # 关键引语与金句
-&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 慢慢来才是最快的方法。
-&gt; 历史最重要的是你要明白它是发生过的。
-&gt; 你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
-&gt; 我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像。
-&gt; 中国的文化精神是中庸。
-&gt; 日本的精神就恰恰相反，他坚持一个原则。
-&gt; 日本战后以后呢，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然。
-&gt; 他是一个世界上这个强国里唯一没有资源的国家。
-&gt; 这叫一丝不苟。
-&gt; 所有的偶然中一定有个必然的因素。
-&gt; 历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
+&gt; “慢慢来才是最快的方法。”
+&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
+&gt; “你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。”
+&gt; “所有的偶然中一定有个必然的因素。”
+&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是中庸。”
+&gt; “他（朱元璋）太不容易。我们今天说你做个什么事，能做能做什么，这人从一起干，一直到最后，推翻元朝，当上了皇帝，定了多少规章制度。”
+&gt; “历史最重要的是什么？就是你要明白它是发生过的。”
+&gt; “史书上记载下来是什么？照片。而我们实际上我们的生活古人的生活都是录像。”
 &gt; 原话引语……</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>17496/6601</t>
+      <c r="D36" s="11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17496/2640</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="13.5" customHeight="1" s="9">
+    <row r="37" ht="13.5" customHeight="1" s="10">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:04
@@ -12242,84 +11923,29 @@
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本次访谈围绕作家余华的写作历程、创作状态与面对批评和网络关注的心态展开。余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段：第一阶段逼自己坐下来写，让屁股和椅子建立友谊；第二阶段受卡夫卡启发，写内心动荡不安的人物；第三阶段受威廉·福克纳启发，用视觉描写替代心理描写，如《狂人日记》中赵家的狗看人一眼。3.0之后没再升级，他认为《活着》可能是4.0版但已不是难题，3.0版本已经是大海，够了。他自述最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品；2006年开始写的一部长篇小说，现在身体状态可能还能维持激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来，他估计能好好写作的时间可能只剩十年左右。他回应《第七天》出来时有教授说他变得仁慈了，说自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。面对批评，他形成的方式是：第一不要去看，第二有些批评要重视；他在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期，但自媒体时代会把几十年前的事情和以前说过的话翻出来，互联网上关于他的话有一半不是他说的。被问及希望以什么姿态留在历史长河，他回答“遗忘的姿态”，假如历史长河里有主题，主题就是一个世界、一个一个人。
+本次采访中，作家余华回顾了其文学创作历程，将创作分为1.0、2.0、3.0三个阶段：1.0是逼自己坐下来写，2.0受卡夫卡启发，3.0受福克纳影响，用视觉描写心理。他认为3.0版本已是大海，不再追求高度，转而追求宽度。余华坦言最好的写作状态在40多岁到50岁，即《兄弟》到《第七天》期间，但那段时光被浪费，只出了两部作品。他提到2006年开始写的一部长篇小说因感觉远去而搁置，现在身体状态还能维持激烈，但感觉找不回来。余华对《兄弟》的期望是好评如潮，结果批评如潮，后来学会什么都不看，但重视有道理的批评，如《第七天》中关于小人物善良的批评，会在以后作品中考虑。他建议年轻人通过选择知道什么来隔离负面消息，进行自我调节。
 # 访谈详细记录
-一、自学游泳与文学创作的三阶段
-- 余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段。
-- 第一阶段：逼着自己坐下来写，“让屁股和椅子建立友谊”，这是年轻时候最重要的；如果离开写字桌躺到床上幻想作品多牛逼，可能就不会去写它。
-- 第二阶段：受卡夫卡启发，写内心动荡不安的人物；写一个人物内心平静没有意思，内心动荡不安的话写1万个字。
-- 第三阶段：受威廉·福克纳启发，福克纳写一个穷白人把一个富白人杀了之后的内心状态，采用“让心脏停止跳动，让眼睛睁开”，心理描写没有心理，是视觉描写；如《狂人日记》中赵家的狗看人一眼，就知道这个人精神状态。余华去过精神病医院，认为精神病人说话逻辑是清晰的，只是方向不同。
-- 3.0版本之后没再升级，他认为《活着》可能是4.0版，但对他来说已不是难题，写作已经很成熟；写一个没什么文化的农民讲述自己的故事，要用最朴素的语言。他认为3.0版本已经是大海，够了。
-二、写作状态与身体、感觉的流失
-- 余华认为最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品。
-- 2006年开始写的一部长篇小说，时间跨度与《兄弟》一样，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写；现在身体状态可能还能维持这种激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来。
-- 他估计能好好写作的时间可能只剩十年左右。
-- 他提到《十八岁出门远行》一天就写完，有6000字，对写字较慢的他来说是奇迹。
-三、《兄弟》的创作与时代变化
-- 《兄弟》1996年动笔，当时中国社会变化复杂；2003、2004年重新拿回来写时，庆幸1996年没写完，因为从2004年看，1996年的变化不算什么，那才是真正大的变化。
-四、作品出版间隔与下一步计划
-- 从《在细雨中呼喊》到《兄弟》隔了十年，《兄弟》到《第七天》隔了八年，《第七天》到《文城》又隔了八年。
-- 余华希望快一点，已把这边整理完，开学时要去和学生们见一下，学校还有一些事情要处理，完了以后回三亚继续往前，安安静静把感觉找回来。
-- 被问下一步长篇是否在2029年，余华未明确确认。
-五、童年看海与人生感受
-- 余华童年第一次看到大海，感受到人生是宽广的。
-- 小时候每年夏天在海盐游泳，有一次进入海流，不能挣扎只能跟着海流走，一直漂到40里外才爬上来，赤脚沿海边走回来，天快亮了。海流把他带回海岸线，没有带到太平洋。
-- 在三亚看到童年星空，发现月光是金色的，不是银色的。
-六、《第七天》的仁慈与悲剧/喜剧转向
-- 有教授说《第七天》出来时余华变得仁慈了。余华回应自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。
-- 已确认：余华决定先完成一部喜剧作品。
-七、追求宽度而非高度
-- 余华表示对高度已经不追求了，现在追求宽度。认为作为作家，写作能走到的高度已经是现在的高度，允许自己下滑一下但不要下滑太多。
-- 年纪大了，知道自己的能力、长处和还有多少潜力，不再像年轻时充满野心。
-八、文学理想与马尔克斯的影响
-- 余华认为这一代中国作家很大程度上被马尔克斯误导，都想在一本书里写一个世纪的故事，但其实没有必要。
-- 托尔斯泰、狄更斯、莎士比亚、巴尔扎克、福楼拜、司汤达、契诃夫等都没有这样做。马尔克斯写拉丁美洲最混乱的世界所以能写出来，别人不一定写得出来。
-- 余华现在知道自己要什么，就是把所处的时代通过更多方式表现出来。
-九、莫言与莎士比亚故居之行
-- 余华说莫言小说对话精彩，想写话剧，20多年前就开始写话剧，但写了没拿出来。
-- 余华、苏童、莫言三人一起去莎士比亚故居，莫言在雕塑前发誓要成为剧作家，余华认为那是瞎扯，莫言当时在挑帽子，帽子钱还是余华付的，三人买了三顶一模一样的深蓝色帽子，上面有莎士比亚名字，后来找不着了。
-十、面对批评与网络时代的心态
-- 《兄弟》出版时余华以为会是一片赞扬，结果一片骂声，他接受很多采访努力解释。
-- 《第七天》出来时只接收一个采访，告诉朋友们做好思想准备，果然一片骂声。《文城》出来时骂声还有但少一点。
-- 余华找到对待批评的方式：第一不要去看，第二有些批评要重视。批评宋凡平写得太完美没有道理，因为宋凡平不是贯穿全书的人物；但批评《第七天》中社会底层人未必都善良，这句话很好，以后写小人物会考虑进去。
-- 已确认：余华形成对待批评的方式，有道理的批评会在以后作品中考虑。
-十一、网络热度与一年冷静期
-- 余华在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期。
-- 按过去经验一年后就在媒体上消失，但自媒体时代不是这样，几十年前的事情都被翻出来，以前说过的话也被翻出来。
-- 互联网上关于他的话有一半不是他说的，比如“精神内耗”“想要命好”等都不是他说的。
-- 他不担心喜欢会消散，因为他的工作是写作，不是靠说话。
-十二、中年危机与自我调节
-- 余华34岁时在年终总结中说成年人每到年底都会发现一种虚无，对生活充满信心的人变成面试者。
-- 当时感觉生活每天在呼吸，人口增加、孩子来了，空间没有变得宽敞。只有写作能得到新的东西，虚构世界带来新东西，现实世界每天都是。
-- 面对年轻人巨大的不安和焦虑，余华认为只有自我调节：发生的事情无法选择让它发生或不发生，但可以选择让自己知道什么、不知道什么，负面消息太多就屏蔽掉，选择积极的。
-十三、希望以遗忘的姿态留在历史长河
-- 被问及希望以什么姿态留在历史长河，余华回答“遗忘的姿态”，就是一个遗忘的人。
-- 那些能够勉强被微风吹进耳朵的人，也是勉强吹进来的。假如历史长河里有主题，主题就是一个世界、一个一个人。
+一、文学创作阶段与理念：余华将文学创作分为3.0阶段：1.0是逼自己坐下来写，让屁股和椅子建立友谊；2.0受卡夫卡启发，写作越写越难，遇到对心理表现的障碍；3.0受威廉·福克纳影响，用视觉描写心理，如福克纳写穷白人杀富白人时让心脏停止跳动、让眼睛睁开，通过视觉精确表达杀人后的状态。余华认为3.0版本已足够，不再升级，因为写作已成熟，知道写农民要用最朴素的语言。二、写作状态与遗憾：余华认为最好的写作状态在40多岁到50岁，即《兄弟》到《第七天》期间，但那段时光被浪费，只出了两部作品。他提到2006年开始写的一部长篇小说，实践跨度与《兄弟》一样，但从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写，现在身体状态还能维持激烈，但感觉没了，过去时代的感觉在远去，很难找回来。他估计能好好写作的时间可能只剩十年左右。三、未来写作计划：余华希望尽快完成一部喜剧，改变读者对他悲观印象。他计划开学时与学生见面，处理学校事务后回三亚继续写作，找回感觉。四、对批评的态度：余华分享《兄弟》出版时遭遇批评的经历，当时期望好评如潮，结果批评如潮，他努力解释但效果不佳。后来他学会不看批评，但重视有道理的批评，如《第七天》中关于小人物善良的批评，会在以后作品中考虑。五、网络热度与公众人物：余华谈到网络走红后曾停一年活动，发现自媒体时代会翻旧账，互联网上关于他的话有一半不是他说的。他不担心热度消散，因为他的工作是写作，不是说话。六、中年危机与自我调节：余华分享面对中年危机的感受，认为只有写作能带来新东西，现实世界每天重复。他建议年轻人通过选择知道什么来隔离负面消息，屏蔽网上负面消息，选择让自己知道什么、不知道什么。七、历史长河中的姿态：余华希望以遗忘的姿态留在历史长河中，认为历史长河的主题是一个个世界、一个个的人。
 # 关键引语与金句
-&gt; 坐下来让屁股和椅子建立友谊，这是很重要的。
-&gt; 假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的。
-&gt; 让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视觉描写。
-&gt; 我觉得我活着也蛮仁慈的。
-&gt; 把悲伤留给虚构，把欢乐留给现实。
-&gt; 第一，你就不要去看就行了。第二，有些批评你要重视。
-&gt; 发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。
-&gt; 遗忘的姿态。就是一个遗忘的人。
-&gt; 假如那个历史的长河里边有一个主题的话，这个主题就是一个世界，一个一个人。
-&gt; 我已经把那个40多岁到50岁最好的一段时间浪费掉了。
-&gt; 那个过去那个时代那个感觉没有了。我写到那个80年代的和90年代那个感觉，也在，感觉都在远去。
+&gt; “假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。”
+&gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
+&gt; “把悲伤留给虚构，把欢乐留给现实。”
+&gt; “我已经找到了一一个方式，就如何去对待那种批评呢？就第一，你就不要去看就行了。第二，有些批评你要重视。”
+&gt; “我们可以选择什么让自己去知道，什么让自己去不知道。”
+&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。”
 &gt; 原话引语……</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>11212/3364</t>
+      <c r="D37" s="11" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11212/1349</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="13.5" customHeight="1" s="9">
+    <row r="38" ht="13.5" customHeight="1" s="10">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -12425,51 +12051,22 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次研讨会围绕第二次世界大战欧洲战场最后一次大规模战役——柏林战役展开，由发言人1主讲，系统梳理了战役背景、双方部署、进攻过程、希特勒自杀、德军投降及战后格局。1945年同盟国与苏俄从不同方向攻入德国本土，苏军已进抵奥德河、尼斯河一线，距柏林仅60公里，英美联军刚到达易北河一带，距柏林100至120公里，苏联获得先发制人机会。苏军由朱可夫元帅和克列夫元帅指挥，白俄罗斯第一方面军从奥德河一线北部突击包围，乌克兰第一方面军从南部绕到波斯坦地区实施西部包围，苏军两个方面军总计约250万人形成合围；德军防守约100万人，以从东线撤离的中央集团军群残兵为主力，另有柏林卫戍部队及由老人和16岁以下孩子组成的国民制弹兵部队。战役第一阶段于1945年4月16日开始，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击；因德军在桑多梅日桥头堡之前修筑防线，苏军拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日突进柏林市区，德军温克第十二集团军与苏军周旋。4月30日柏林被围死，苏联红军离希特勒地堡只有两条街，希特勒与夫人艾娃·布劳恩一起举枪自尽，其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据。4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束，战役从4月16日持续到5月2日。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
-# 核心观点与论证
-论点一：苏联不惜代价强攻柏林，源于占领柏林可获至高无上的荣誉与战后地位。论据：1945年同盟国和苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题；柏林是法西斯德国大本营及纳粹最大巢穴，谁占领柏林谁在二战后可获得至高无上的地位，因此苏联从上到下团结一致，以柏林为目标进行不惜代价的强攻。
-论点二：苏联在部署上已获得先发制人机会。论据：苏军已进抵奥德河、尼斯河一线，即今天德国和波兰的边境地区，距柏林只有60公里；英美联军才刚刚到达易北河一带，距柏林还有100到120公里。
-论点三：苏军以两个方面军形成合围，兵力占优。论据：白俄罗斯第一方面军指挥官为朱可夫元帅，从奥德河一线、奥德法兰克福方向北部对柏林进行突击与包围；乌克兰第一方面军指挥官为克列夫元帅，由克拉科夫以及德雷斯顿方向前出，从南部绕到柏林前突至波斯坦地区，对柏林实施西部包围。苏军两个方面军总计约250万人，从北部石切清一直到南部德雷斯顿形成合围网。德军主要防守部队为从东线撤离的中央集团军群残缺部队、柏林卫戍部队以及国民制弹兵部队（由年纪较大的老人及16岁以下孩子组成的民兵），总共有约100万人，以中央集团军群残兵为主力。
-论点四：战役进程受德军防线修筑影响而延迟。论据：第一阶段1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河突击，乌克兰第一方面军越过尼斯河突击；但由于德军在桑多梅日桥头堡之前修筑防线，一直拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日才突进柏林市区，由白俄罗斯第一方面军进行突击，此时乌克兰第一方面军还在艰难摸索向柏林边缘靠近。德军温克第十二集团军与苏军一直周旋。
-论点五：城市作战与野外作战存在明显区别。论据：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
-论点六：希特勒自杀及遗体争议。论据：1945年4月30日柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽；其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据；除少数亲信外，大部分人坚信纳粹没有覆灭，自欺欺人继续战斗，导致谣言盛起。
-论点七：英美未进攻柏林的原因。论据：丘吉尔想抢占柏林，但盟国已达成协议柏林战后属于苏联，会分出一半区域给西方盟国即西柏林；艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤回去，得不偿失，不如占领更多德国精华地带如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，盟军还有求于苏联一起对日本战斗。
-论点八：战役结束与战后格局。论据：4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队在其将领温克率领下渡过易北河向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
-# 金句总结
-「谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。」——背景：主讲人分析苏联不惜代价强攻柏林的动机，指出柏林是法西斯德国大本营及纳粹最大巢穴，占领柏林可获至高无上的荣誉与战后地位。
-「城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。」——背景：主讲人回答听众关于城市作战与野外作战区别的提问，说明城市作战的困难与危险。
-「希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了，就和他的夫人艾娃·布劳恩一起。」——背景：主讲人回答听众关于希特勒是否自杀的提问，说明希特勒自杀的原因与方式。
-「除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以说各种流传到民间的说法褒贬不一，导致很多后时候谣言还在盛起。」——背景：主讲人解释希特勒自杀细节为何引人关注，指出遗体被焚烧后无确切证据，导致谣言盛起。
-「与其这样，还不如说是尽可能去占领更多德国的精华地带，比如说慕尼黑、斯图加特以及纽伦堡，还有就是汉堡、法兰克福这些地方，柏林就让给苏联吧。」——背景：主讲人分析艾森豪威尔认为美军攻占柏林得不偿失，不如占领更多德国精华地带。
-「那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。」——背景：发言人5补充红旗插上国会大厦的细节，说明旗帜是士兵临时用床单和颜料绘制。
-# Q&amp;A 环节
-问：城市作战跟野外作战有什么明显的区别？
-答：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
-问：是不是这个战役里面希特勒自杀了？
-答：是的。1945年4月30日，德国离兵败之日不远，柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽。
-问：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么引关注？
-答：因为在他自尽之后，他的部下用汽油把尸体焚烧了，到今天为止也没有见到希特勒遗体全貌，只是获得一堆烧焦的焦炭，外界说法各种不一，也没有确切证据证明。实际上他自杀后尸体被焚烧，除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以各种流传到民间的说法褒贬不一，导致很多谣言还在盛起。
-问：如果想了解更多这个战役，有什么影视推荐吗？
-答：苏联有拍柏林战役，德国有《帝国的毁灭》。德国角度更多是希特勒最后生平以及关于柏林防守上的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
-问：主要进攻柏林的是苏联方面的部队，那为什么英美他不打柏林呢？
-答：丘吉尔当时想抢占柏林，但盟国事先已在战后德国地盘划分占领上达成协议，柏林战后属于苏联，会分出一半区域给西方盟国即后来的西柏林。美军统帅艾森豪威尔认为美军去攻占柏林会增加不必要伤亡，同时占领柏林后还是要撤回去，得不偿失，不如尽可能占领更多德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，柏林就让给苏联。毕竟打完德国之后，盟军还有求于苏联一起跟日本进行战斗。
-问：这场战役大概持续了多久？
-答：从4月16号开始，一直进行到了5月2号。
-问：有什么书可以看的吗？
-答：可以看朱可夫自传、崔可夫自传，以及斯大林传记里面写到的关于柏林战役后苏俄和西方的博弈，涉及西柏林地区划分以及德国边境重新划定。</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>4609/3614</t>
+          <t># 柏林战役历史背景与过程研讨会
+柏林战役历史背景与过程研讨会
+会议要点：本次研讨会由主讲人介绍柏林战役的历史背景、过程与影响。1945年苏军进抵奥德河-尼斯河一线，距柏林60公里，英美联军距柏林100-120公里；苏军白俄罗斯第一方面军（朱可夫）与乌克兰第一方面军（科涅夫）共约250万人，德军中央集团军群残部及国民掷弹兵约100万人。战役于1945年4月16日开始，苏军炮击并突击，4月20日进抵柏林城区，4月24日突入市区；希特勒于4月30日与妻子艾娃·布劳恩自杀，尸体被焚烧；5月2日柏林德军投降，5月9日德国无条件投降。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4609/274</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1" s="9">
+    <row r="39" ht="13.5" customHeight="1" s="10">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:02
@@ -12614,24 +12211,24 @@
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-会议围绕生活中约定俗成的规则是否合理以及AI/机器人未来展开自由讨论，并测试多人同时说话的语音标注效果。与会者就买房、结婚生子、工作等规则交换意见，认为经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对；工作方面提出工作可能是合理的，但工作状态应合理，即干自己想做的、不要跟钱太保密，并讨论理想工作状态是每天起来想干啥就干啥、参考自己兴趣干活，举例宠物博主发宠物日常剪视频赚钱、游戏高手，同时提出脏活累活没人愿意承担的问题。在AI与机器人议题上，提出应让AI去做苦活累活而不是搞创作艺术，设想机器人负责生产、人负责享受，提到扫地机器人及未来可打扫家、做饭的机器人，并讨论AI普及普惠到实体、机器人有自己思维后人类能否控制；进一步讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影，提到机器人可能成为犯罪代理人、职业杀手、超级战士，以及智能与思想可能无法分开、思想可能带来不好影响。讨论还涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。
-## 约定俗成规则与理想工作状态讨论
-- 讨论买房、结婚生子、工作等约定俗成规则是否合理；提到经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对。
-- 讨论理想工作状态，提到每天起来想干啥就干啥、参考自己兴趣干活；举例宠物博主发宠物日常剪视频赚钱、游戏高手；提出脏活累活没人愿意承担的问题。
-## AI与机器人替代及失控风险讨论
-- 提出应让AI去做苦活累活而不是搞创作艺术；设想机器人负责生产、人负责享受；提到扫地机器人及未来可打扫家、做饭的机器人；讨论AI普及普惠到实体、机器人有自己思维后人类能否控制。讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影；提到机器人可能成为犯罪代理人、职业杀手、超级战士；讨论智能与思想可能无法分开，思想可能带来不好影响。涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>3931/1305</t>
+会议围绕结婚、买房、工作等社会约定俗成规则的合理性展开讨论，认为这些规则是否合理取决于个人能力、经济条件和遇到的人，经济条件影响可行性。讨论延伸到理想工作形态，认为理想工作是按兴趣干活，如宠物博主、游戏高手等，但指出脏活累活无人承担的问题，进而探讨由AI和机器人承担苦活累活的可能性，认为应让AI做苦活累活而非创作，但存在阶级阻力和实现难度。讨论机器人拥有思想意识后可能不受控制、罢工、反抗人类的风险，引用终结者、人工智能电影、数码宝贝等例子，认为后果灾难性。最后提及语音分离标注测试，讨论两人同时说话时的标注问题，需要认识声音的人标注，单人麦克风效果较强。
+## 社会规则与理想工作讨论
+- 讨论结婚、买房、工作等社会规则的合理性，认为取决于个人能力和遇到的人，经济条件影响可行性。
+- 讨论理想工作为按兴趣干活，提到宠物博主、游戏高手等例子，也指出脏活累活无人承担的问题。
+## AI机器人影响与风险讨论
+- 认为应让AI做苦活累活而非创作，讨论机器人负责生产、人类享受的可能性，但存在阶级阻力和实现难度。讨论机器人拥有思想后可能不受控制、罢工、反抗人类，引用终结者、人工智能电影、数码宝贝等例子，认为后果灾难性。最后提及语音分离标注测试，讨论两人同时说话时的标注问题，需要认识声音的人标注，单人麦克风效果较强。</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3931/565</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1" s="9">
+    <row r="40" ht="13.5" customHeight="1" s="10">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -12722,24 +12319,24 @@
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕哥斯拉系列电影起源、各版本剧情及怪兽设定展开自由讨论，并延伸至核废水、核污染与生物变异话题。1954年第一部哥斯拉电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物并对人类展开报复攻击；哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验破坏生态。美国版剧情方面，2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版方面，人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。关于哥斯拉与奥特曼的关系，两者最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。
-## 哥斯拉电影起源与设定
-- 1954年第一部哥斯拉题材电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
-- 哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验、破坏大自然生态；相关扩展题材涉及人类频繁搞战争和核试验后唤醒沉睡生物及招致外星生物入侵。
-## 哥斯拉各版本剧情梳理
-- 美国版：2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版：人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。哥斯拉与奥特曼最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>5319/1287</t>
+会议围绕哥斯拉系列电影剧情展开讨论，梳理了美日两版哥斯拉的起源、各代剧情及怪兽设定。哥斯拉起源于1954年首部电影，为海底生物吸食核废料变异而成，在日本神话中作为大自然守护神存在，因人类核试验破坏生态而报复人类。美国版剧情包括2014年《哥斯拉》中与雾托的战斗、《哥斯拉怪兽之王》中与基多拉的战斗，以及《哥斯拉大战金刚》中与金刚联手击败机械基多拉；日本版剧情更为复杂，2016年《新哥斯拉》中哥斯拉最终被无人机投放炸弹耗尽能量并以冷冻剂封印。讨论延伸至哥斯拉与奥特曼的关联，指出两者导演均为圆谷英二，但属于不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星，均为正面形象，未直接战斗；拉顿（翼龙）在两者作品中均作为反派出现。由哥斯拉题材引申讨论核废水危害，提及日本排放核废水、切尔诺贝利核事故导致生物畸形、普里皮亚季成为鬼城，以及日本进口食品问题。发言人2分享在日本留学时购买中国进口鱼类的经历，并指出日本国产产品因民族自信而价格昂贵。
+## 哥斯拉系列电影剧情梳理
+- 哥斯拉起源于1954年首部电影，为海底生物吸食核废料变异而成，在日本神话中作为大自然守护神，因人类核试验破坏生态而报复人类。美国版剧情包括2014年《哥斯拉》中与雾托的战斗、《哥斯拉怪兽之王》中与基多拉的战斗，以及《哥斯拉大战金刚》中与金刚联手击败机械基多拉。日本版剧情更为复杂，2016年《新哥斯拉》中哥斯拉最终被无人机投放炸弹耗尽能量并以冷冻剂封印。
+- 哥斯拉与奥特曼的关联：两者导演均为圆谷英二，但属于不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星，均为正面形象，未直接战斗；拉顿（翼龙）在两者作品中均作为反派出现。
+## 核废水危害与切尔诺贝利事件讨论
+- 由哥斯拉题材引申讨论核废水对身体的危害，提及日本排放核废水、切尔诺贝利核事故导致生物畸形、普里皮亚季成为鬼城，以及日本进口食品问题。发言人2分享在日本留学时购买中国进口鱼类的经历，并指出日本国产产品因民族自信而价格昂贵。</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5319/841</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1" s="9">
+    <row r="41" ht="13.5" customHeight="1" s="10">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:01
@@ -12975,26 +12572,22 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议为一场围绕18岁以前特别深刻的印象和记忆展开的自由分享会，由发言人1发起并主持，参与者包括发言人1至发言人6。核心探讨问题为18岁前是否有逃课、去网吧打游戏、追星、参加音乐会或乐队等经历，并延伸至小说漫画阅读、电脑游戏与单机游戏、第一人称射击与僵尸题材游戏、游戏与影视改编先后、塔防游戏与使命召唤等话题。发言人1回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐。发言人2称18岁前没逃过课，上大学后逃过一次；发言人3认为逃课是正常现象；发言人4称上大学就不算。
-# 发言要点
-发言人1作为主要发起者，回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐；其称穿越火线抄袭，自己曾在贴吧和QQ空间写文章骂穿越火线被封禁，后成为CS铁杆粉，喜欢僵尸模式，并介绍求生之路第二部有东洋刀、电锯、砍刀砍丧尸，很暴力，后来有年龄限制，未成年人不能注册Steam账号，需18岁以上，还称求生之路精准预测美国政府在灾难中的表现，2020年新冠疫情后游戏重新火起来。发言人2称18岁前没逃过课，上大学后逃过一次；称看郭敬明小说挺难受、挺扭曲，并提到《梦里花落知多少》，还提到《意林》《读者》《故事会》并称意林讲得特别好；提到穿越火线、地下城与勇士、魔兽争霸，称欧美玩家爱玩打僵尸游戏，称植物大战僵尸有特别变态的版本，后期满屏子弹，电脑都卡，称使命召唤这游戏太男性了。发言人3认为逃课是正常现象，称小时候经常玩塔防游戏，现在还在玩植物大战僵尸和Kindle rush。发言人4称上大学就不算逃课，称班里特别流行看柯南，提到摩尔庄园、赛尔号，提到仙剑三最火且有电视剧。发言人5提到特别喜欢郭敬明的小说，提到当时还有一些杂志，提到萌化三国，提到仙剑四、仙辕剑、古剑四，质疑当时游戏没有年龄限制、内容暴力，小孩能否玩。发言人6提到生活杂志、柯南、老夫子、仙剑、Steam图标、僵尸题材，称艺术源于生活。观点交锋点包括：逃课是否正常及上大学后是否算逃课；郭敬明小说是否令人难受扭曲；穿越火线是否抄袭及游戏暴力与年龄限制；求生之路与生化危机、惊变48小时的影视游戏先后关系；变形金刚先有玩具还是电影；英雄联盟与DOTA的鄙视链及王者荣耀处于鄙视链最低端。
-# 共识形成
-小组未形成正式决议或统一意见，讨论以自由分享与回忆为主。形成的共同认知包括：**逃课在初中高中阶段被视为正常现象，但上大学后逃课一般不算**；**郭敬明小说、柯南、老夫子、意林读者故事会等是当时流行的阅读内容**；**穿越火线、CS、求生之路、仙剑、魔兽、摩尔庄园、赛尔号、植物大战僵尸等是当时流行的游戏**；**求生之路第二部因暴力内容后来设有年龄限制，未成年人不能注册Steam账号，需18岁以上**；**生化危机先有游戏后有电影，求生之路是在惊变48小时、生化危机基础上先有电影后有游戏**；**变形金刚先有玩具，后有MV和电影**；**英雄联盟与DOTA存在鄙视链，王者荣耀处于鄙视链最低端**。
-# 未决事项与分工
-需进一步探讨的问题包括：发言人5质疑当时游戏没有年龄限制、内容暴力，小孩能否玩，该问题未形成结论；发言人2问游戏和电影谁先有，讨论中仅就生化危机、求生之路、变形金刚等具体作品给出先后关系，未形成一般性结论；发言人1称求生之路精准预测美国政府在灾难中的表现，该观点未获其他成员明确回应。后续任务分工未在原文中明确。</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>6453/1554</t>
+          <t># 青春记忆与游戏文化分享会
+青春记忆与游戏文化分享会
+会议要点：本次会议围绕18岁以前的深刻印象和记忆展开分享，涵盖逃课、网吧游戏、追星、乐队、小说漫画等经历。发言人1回忆初中走读时每周一下午4点放学后去游戏厅、网吧玩穿越火线、CS online等游戏，高中因高考压力不敢逃课，转而追星、搞乐队，喜欢朋克金属音乐；发言人5提到喜欢郭敬明小说，发言人2认为其小说扭曲，发言人4提到流行看柯南和老夫子，发言人5提到萌化三国，发言人2提到意林读者和故事会。；在电脑游戏讨论中，发言人4提到摩尔庄园、赛尔号，发言人1提到劲舞团，发言人2提到穿越火线、地下城与勇士，发言人1提到单机游戏求生之路，发言人5提到仙剑四，发言人2提到魔兽争霸，发言人5提到英雄联盟和DOTA的鄙视链，发言人2认为王者荣耀在鄙视链底端。；关于第一人称射击游戏与暴力，发言人1分享自己因骂穿越火线被平台封禁，成为CS铁杆粉丝，喜欢僵尸模式；发言人5质疑游戏暴力且无年龄限制，发言人1解释求生之路第二部血腥暴力，Steam账号需18岁以上注册，并详细讲述求生之路剧情，认为制作团队精准预测美国政府疫情表现，导致疫情后游戏重新火爆；发言人2提到欧洲玩家喜欢打僵尸游戏，发言人1提到生化危机。；在游戏与电影关系讨论中，发言人2询问游戏和电影先后，发言人1回答生化危机先有游戏后有电影，求生之路先有电影后有游戏；发言人4提到变形金刚先有玩具，发言人1补充绿日乐队出过MV。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6453/624</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1" s="9">
+    <row r="42" ht="13.5" customHeight="1" s="10">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:02
@@ -13265,25 +12858,25 @@
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论为闲聊式交流，开场由发言人1提议大家讨论待会儿说啥，并确定继续聊《红楼梦》及相关古典小说话题，随后依次展开红楼官场暗线与四大家族、红楼细节与版本差异、金瓶梅与水浒传关系及人物、西游记佛教描写、三国孙权二宫之争等话题。参与讨论的成员包括发言人1、发言人2、发言人3、发言人4，围绕四大家族兴衰、人物结局版本差异、小说朝代背景及佛教描写等核心问题交换看法。讨论中未形成明确结论，多处内容为参与者凭印象回忆，部分细节表示记不清或未看过。会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。
+本次会议围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的情节、人物、版本差异及历史背景展开闲聊式讨论。与会者谈及《红楼梦》中四大家族（贾、史、王、薛）的兴衰与官场暗线，王熙凤地位与其娘家官场沉浮相关，四大家族整体走下坡路；并提及冷香丸的制作需对应各节气雨水、小雪等，以及江南吃螃蟹的讲究。讨论《金瓶梅》与《水浒传》的关系，指出西门庆在《水浒传》中被武松所杀，而在《金瓶梅》中因重病而亡；武松报仇线在《金瓶梅》中被压制，西门庆作为小人物在官场发迹，有十个老婆，其中潘金莲最有心机。另讨论《西游记》中佛教虚伪的体现，如如来佛祖收300两黄金、寺院住持贪图袈裟自焚等情节。关于历史背景，与会者认为《红楼梦》无明确朝代，可能映射曹雪芹经历，且因是禁书而不写明朝代；《金瓶梅》与《水浒传》为北宋时期。会议无明确决策，仅提出若干未决问题。
 # 发言要点
-发言人3提出红楼梦还有一条官场上的线，即朝堂政权变化，四大家族如王熙凤娘家在官场上的地位与其前期、后期地位及结局相关，其兄长先死也影响其结局，并表示对暗线很好奇；还提到四大家族整体在走下坡路，是王朝家族衰败，并介绍冷香丸配方需雨水、小雪及白牡丹、白荷花、白芙蓉、白梅花，以及120回版本中薛宝钗嫁贾宝玉后为无性婚姻、贾宝玉出家，另有版本称其怀有孩子。发言人4认为四大家族感觉没几个人，每家两家人多一点，薛宝钗家没什么靠山，并回忆小时候看红楼梦对吃螃蟹讲究印象深刻，还提到金瓶梅中潘金莲有心机、西门庆有十个老婆。发言人1补充四大家族形容诗句「丰年好大雪，珍珠如土金如铁」「白玉为堂金作马」「东海缺少白玉床，龙王来请金陵王」，并说明金瓶梅从武松杀武大郎之后写起，武松报仇时西门庆翻窗逃脱、武松后被发配，西门庆霸凌武大郎并攀附权贵，其结局在水浒中被砍头、在金瓶梅中纵欲过度而死，还提到西游记中如来佛祖收300两黄金。发言人2询问四大家族如何形容、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件，并提到孙权二宫之争中王夫人和孙鲁班有心机、反杀搅乱东吴政局。分歧点在于薛宝钗结局版本差异、西门庆结局版本差异及红楼梦是否有真实历史事件，各方均未达成一致。
+发言人3（梦婷）提出《红楼梦》中存在官场暗线，四大家族兴衰与朝堂变化相关，王熙凤地位及结局与其兄长在官场的地位相关，并提及冷香丸制作需对应各节气雨水、小雪等。发言人4对四大家族人数提出疑问，认为每家仅两三人，感觉不厉害；发言人3回应薛宝钗家是做生意的，有钱但无靠山。发言人1补充四大家族诗句：贾家“白玉为堂金作马”，史家“阿房宫三百里，住不下金陵一个史”，王家“东海缺少白玉床，龙王来请金陵王”，薛家“丰年好大雪，珍珠如土金如铁”。发言人4回忆小时候看《红楼梦》对吃螃蟹的讲究印象深刻。关于《金瓶梅》，发言人1指出其与《水浒传》的差异：武松报仇时西门庆在楼上喝茶，仆人报信后翻窗逃走，武松被发配，报仇线被压制；西门庆作为小人物在官场发迹，有十个老婆，潘金莲最有心机。发言人3补充西门庆有老婆因迷信和尚而病亡，并提及书中佛教收灯油钱。发言人2询问西门庆结局，发言人3称在《金瓶梅》中因重病而亡，与《水浒传》中被杀不同。发言人2提出《水浒传》与《金瓶梅》为北宋时期，与《红楼梦》不同；发言人3指出《红楼梦》无明确朝代，是禁书，可能映射曹雪芹经历。发言人2还提及孙权二宫之争中王夫人与孙鲁班搅乱东吴政局，但未深入。
 # 共识形成
-小组未形成统一意见或明确解决方案，讨论中确认的共识性内容为：**金瓶梅与水浒传为北宋时期平行故事线，红楼梦为单独故事线**；**红楼梦没有明确朝代，是写得很虚的故事，映射明末清初及曹雪芹经历**；**四大家族整体在走下坡路，是王朝家族衰败**。
+与会者就《红楼梦》四大家族兴衰与官场暗线达成共识，认为四大家族整体走下坡路，王熙凤地位与娘家官场相关。关于《金瓶梅》，一致认为其与《水浒传》为平行故事线，西门庆在《金瓶梅》中因重病而亡，武松报仇线被压制，西门庆作为小人物在官场发迹。关于历史背景，共识为《红楼梦》无明确朝代，可能映射曹雪芹经历，且因是禁书而不写明朝代；《金瓶梅》与《水浒传》为北宋时期。
 # 未决事项与分工
-需进一步探讨的问题包括：四大家族具体如何形容、薛宝钗结局版本差异、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件。后续任务分工未明确，会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>5893/1087</t>
+未决问题包括：《金瓶梅》中西门庆的结局具体如何；《红楼梦》是否映射曹雪芹经历；孙权二宫之争的具体细节。后续任务分工未提及。</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5893/1148</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1" s="9">
+    <row r="43" ht="13.5" customHeight="1" s="10">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:02
@@ -13566,24 +13159,24 @@
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为轻松对话与录制调度，前半段围绕小说阅读、综艺剧集偏好、专业背景与洗发水等生活话题闲聊，后半段转入日本现代化转型主题并协调八爪鱼、金融、中央会等录制安排。发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。
-## 小说阅读与综艺剧集偏好
-- 发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。
-- 关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。
-## 专业背景与生活话题
-- 发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>5310/1279</t>
+本次会议前半段为闲聊，涉及个人阅读习惯、综艺喜好、专业背景（数学、统计、软件工程、俄语）及洗发水使用等生活话题。后半段转向日本现代化转型主题的播客录制安排，计划采用中英混播形式，讨论人员分工（如八爪鱼、小辉等）和场地安排（三楼会议室）。
+## 闲聊话题
+- 讨论个人阅读习惯、综艺喜好、专业背景（俄语、数学、软件工程）及洗发水使用等生活话题。
+- 未提及
+## 日本现代化转型播客录制安排
+- 计划录制关于日本现代化转型的播客，涉及中英混播形式，讨论人员分工（如八爪鱼、小辉等）和场地安排（三楼会议室）。</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5310/259</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="13.5" customHeight="1" s="9">
+    <row r="44" ht="13.5" customHeight="1" s="10">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -13735,66 +13328,22 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次研讨会由主讲人（发言人1）围绕朝鲜半岛从分裂到朝鲜战争爆发、停战及今日朝韩格局展开分享。主讲人梳理了1945年日本投降后美苏军队分别进入朝鲜南北、以北纬38度为基准形成三八线的由来，并指出1949年新中国宣布废除列强在华租界与特权、涉及苏联在东北的中长铁路及大连旅顺利益后，苏联鼓动朝鲜进攻韩国，希望以仁川或釜山类似城市替代旅顺大连地位并继续在亚洲发挥影响力。战争进程方面，1950年6月北朝鲜军队率先越过三八线南进，朝鲜人民军一度打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，麦克阿瑟任联合国军总司令，美军以联合国军身份参战，另有十六个国家共同出兵；美军越过三八线招致中国强烈不满，中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束，此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带并扩展至三七线，第五次战役为最后一次大规模战役，1953年7月27日双方正式达成停战协定，朝韩名义上停战，未实现真正和平。问答环节还涉及朝鲜战争的影响与评价、越南统一、朝韩旅游与朝鲜现状、朝鲜半岛文明与历史沿革、南北割裂的历史渊源、美国对朝鲜的态度、朝韩统一前景、中俄朝关系与图们江出海口、韩国军队在朝鲜战争中的作用，以及中国选择抗美援朝而非收复台湾的原因等议题，会议未形成决议。
-# 核心观点与论证
-**论点一：三八线是美苏分区受降的产物，朝鲜半岛分裂源于冷战格局。** 论据：1945年二战结束、日本投降后，美苏军队分别进入朝鲜南北，以北纬38度为基准形成三八线；最初设想不同占领区受降后像奥地利那样普选建立统一民选政府，但美苏关系急转直下，扶植领导人各有心思，意识形态不同，最终建立两个国家。美国在三八线以南单独建立韩国以保护日本免遭苏联及共产主义势力影响，苏联在朝鲜北部建立卫星附属国。
-**论点二：朝鲜战争爆发与各方称谓不同。** 论据：1950年6月北朝鲜军队率先越过三八线向南进攻；朝鲜称祖国统一解放战争，中国称抗美援朝，韩国称625事件，美国及西方国家称朝鲜战争或韩战，台湾地区称韩战。
-**论点三：战争进程经历多次战役，最终在三八线附近形成今日边境。** 论据：朝鲜人民军从三八线打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，分割包围并逐次歼灭朝鲜人民军，收复三八线以南韩国领土；中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束；此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带，扩展至三七线（北纬37度）；后期美军反攻，双方鏖战于三七线和三八线之间；第五次战役为最后一次大规模战役，结束后双方在三八线基础上互有攻防，形成今日朝韩边境。西部中朝方面向南占领开城、延安半岛和望京半岛一带；东部美军向北占领今韩国襄阳地区及金刚山地区。1953年7月27日双方正式达成停战协定，延续至今。
-**论点四：朝鲜战争对中国具有战略意义。** 论据：从中国角度奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期中国警告美国不得越过北纬17度线，美国未敢越过；美国称此战为被遗忘的战争，联合国军最后一任司令官马克克拉克承认是美国历史上第一次未取得胜利情况下签署停战协议的司令官；伤害最深的是朝鲜和韩国，一脉相承的血肉同胞分裂成两个国家。
-**论点五：中国选择抗美援朝而非收复台湾，因海军实力不足与战略主动考量。** 论据：台湾和大陆之间有一道约100公里海峡，中共刚建国没有相应海军实力；1950年朝鲜战争爆发，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾；美国后期越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，唇亡齿寒深入人心，解放军陆军很强，海上没办法战斗就只能在陆地上战斗；长津湖和上甘岭接连让美军惨败。
-**论点六：韩国军队在朝鲜战争中的作用与战斗力演变。** 论据：韩国军队一开始瞎指挥，差点被朝鲜团灭；6月25日朝鲜战争爆发，7月10日以后朝鲜南部地面战斗主要是美军和朝鲜人民军进行，韩军负责冲人头角色；1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力；此前韩军对美军类似猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每次兵败都是韩国军队战线崩溃引起；第五次战役中志愿军从朝鲜半岛东部形成反包围突击，打崩韩国军队前线，美国把韩国第三军团全部撤销；韩军以二战时期日本扶植的伪军和傀儡部队军官为骨干，士兵类似国民党抓壮丁强征农村青年；一直贯彻二战昭和日军武士道精神管理体制，老兵欺负新兵，军队霸凌事件蔓延至今。
-**论点七：朝韩统一前景与中俄朝关系。** 论据：若当时美国未下场救援韩国，今日朝鲜可能是苏联卫星国附属，用来牵制中国并威胁美国在亚洲尤其日本的不稳定定时炸弹；现在若朝韩统一，大概率是韩国兼并朝鲜，因经济影响和综合实力；北方有充足优质兵源及核武器和导弹等尖端武器，若统一对整个东北亚都是不稳定定时炸弹；越南统一时宣布继承法国在中南半岛所有地盘和疆域，统一第二年进攻柬埔寨和泰国，导致1979年中国出兵对越南自卫反击战。中俄朝各怀鬼胎；中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落；图们江是俄罗斯和朝鲜的界江，是日本海出海口，在中朝俄边境，国际水域航道可通行，但俄罗斯和朝鲜建了一座小桥，大船无法通过；俄罗斯和朝鲜都不希望中国过分强大，不想过多依附中国，把图们江出海口封死。
-# 金句总结
-&gt; “朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的一个状态。”
-背景：主讲人在讲述美军越过三八线后中国决定出兵时提出，用以说明中国以志愿军形式出兵的战略考量。
-&gt; “美国再也不敢小瞧我们了。”
-背景：主讲人在回答朝鲜战争影响时提出，指出此战从中国角度奠定了强国地位，并提及1967年越南战争时期中国警告美国不得越过北纬17度线。
-&gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
-背景：主讲人引述联合国军最后一任司令官马克克拉克的承认，说明美国称此战为被遗忘的战争。
-&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。”
-背景：主讲人在评价朝鲜战争影响时提出，指出朝韩名义上停战，未实现真正和平。
-&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
-背景：主讲人在回答中国选择抗美援朝而非收复台湾的原因时提出，指出解放军陆军很强，台湾海峡约100公里且当时没有海军实力。
-&gt; “各怀鬼胎。”
-背景：主讲人在回答中俄朝关系时提出，指出中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落。
-# Q&amp;A 环节
-问：战争开始和结束，韩国和朝鲜他们作战的势力有很大的差别吗？这个战争的改变大吗？
-→ 答：主要从中国的角度来说，奠定了我们一个强国的一个地位。美国再也不敢小瞧我们了，导致在一九六七年的越南战争时期，中国这边向美国发出的警告，绝对不允许越过北纬十七度线。那个时候就是南越和北越的一个边境线，如果说美国胆敢越过北纬十七度线的话，那中国必将出兵越南，导致美国在越战的时候未敢越过北纬十七度线，然后奠定了我们的一个地位。同时这场战役在美国被称为被遗忘的战争，因为联合国军，也就美军当时在朝鲜的最后一任司令官马克克拉克，他自己就说了一句他承认了，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官，然后伤害最深的其实还是朝鲜和韩国。
-问：现在越南还分南北吗？
-→ 答：没有。越南它还是统一的，因为美国最终还是放弃了南越，然后北越趁这个机会把南越给统一了。
-问：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
-→ 答：当然是韩国更好玩一点的。因为朝鲜他那边旅游就有点就是没有人身自由。当我们如果说是进入朝鲜的境内，第一件事就是什么呢？没有对搜手机检查，然后没有无线网，就没有网络。然后只有平壤，不就他们自己的网络运营商，而且就是类似于咱们国家八九十年代的那样的一个状态。然后他们的手机就是很落后、很慢，然后国际漫游和网络就非常的贵。然后那几天就是就是参观他们的，就是所谓的伟大的今日成员在的感召之下的各种主体思想和社会主义的辉煌建设成就。然后就类似于像以前我们的文革时期的那种，就是呃无产阶级，就是就是高于一切那样的一个思想，然后就活在一种就是异次元的世界当中。
-问：他们普通人可以上网吗？
-→ 答：不行啊，普通人不能上网。对，普通人是一般的。就是他那个，就局域网都已经很有限。然后普通人连电脑和就是咱们的，就是这些5G手机都用不起，他们怎么上网啊？因为主要是外部有韩国，然后光是韩国用韩剧作为意识形态的宣传武器，老百姓都会就是起来，要是知道真相之后也会颠覆他们的政权。否则的话，为什么那么多朝鲜就是老百姓，不管是吃不饱肚子，还是受意识形态的公式的关宣传之下，都往韩国跑？鲜有韩呃韩国人会去朝鲜的。对，脱北者。
-问：朝鲜那边有啥好玩的？
-→ 答：也就平壤那边看看志愿军的那些抗美援朝那些功绩，还有就是开城嘛，毕竟是朝鲜半岛三千年古都，然后就那边特产小人参。
-问：朝鲜是不是和什么我们北京或者是俄罗斯利亚有一个很大的一个广场，就是平壤的金日成广场？
-→ 答：以领导人来命名，就他们大将军、大元帅这样的啊。战争类的也可以用吧。
-问：它这个南北之间的割裂，是有什么历史渊源吗？为什么它会成为两个政权？
-→ 答：主要一开始的时候，美国和苏联都希望在朝鲜半岛建立一个缓冲区。然后美国主要是为了在建，在分出三八线以南的领土，单建单独建立一个韩国，是为了保护日本免遭苏联以及共产主义势力的一个影响，然后。在韩国形成一个缓冲区，而苏联也需要在亚洲建立一个卫星附属国，所以说就在朝鲜北部，在韩国独立的一个建国的一个基础之上，然后也宣布北朝鲜独。鼓励奉行的就是呃，对苏联马首是瞻的一个指示。所以说就是两边最开始的一个诉求，本来是一开始就是说，在就是不同的占领区受降，日本人的投降之后，像奥地利那样形成一个普选，然后建建立一个统一的民选政府。可谁都没想到，当时美国和苏联的关系恶化的非常快，急转直下的关系可以说是。然后，同时所扶植的领导人也各自有各自的心思。由于意识形态的不同，然后最终就是建立了不同的两个国家。所以说这也是朝鲜战争爆发的缘由。
-问：当时美国没有打败朝鲜嘛，然后你觉得现在美国对朝鲜的态度是怎样的？
-→ 答：因为就是什么呢？因为美国是因为惧怕朝鲜背后的中国和俄罗斯这么一个因素在里面。因为朝鲜战争爆发的时候，呃，当时朝鲜已经快被美国完全占领了，然后中国这边出动了志愿军部队，然后帮着朝鲜把美国打回去，而苏联当时也是提供了空军掩护和武器的一个后勤支持，所以说是中国和苏联联手，可以说是把美国给打回到三八线以南这么一个状态。所以说美国就比较忌惮这一块的因素，所以说就是没有，就是主动进攻朝鲜，也没有再次挑起这个朝鲜半岛的武装冲突，然后同时朝鲜当前的一个状态，金家也担心他们的那个江山，呃。在一旦贸然发动战争了之后，重新被颠覆了，所以说也不敢贸然发动战争，就这样的。
-问：现在的朝韩对立这个局面，可以认为是现在韩国还有还有还有西方国家在背后支撑嘛，可以认为它是一个微妙的平衡。如果不妨畅想一下，如果当时没有形成这种这个冷战布局，就是互相争夺这个半岛的控制权的话。这个大一统的朝鲜半岛会是一个什么形态？会是一个大号的朝鲜，还是一个平衡的韩朝？
-→ 答：如果当时朝鲜战争爆发的时候，美国没有下场去救援韩国，今日朝鲜可能会是呃一个就是苏联的卫星国附属之下的，然后当时用来牵制咱们国家的一颗钉子，也要也是威胁美国在亚洲，尤其是日本那一块的一个就是不稳定的定时炸弹，就这样的一个状态。但是现在如果说是。朝韩要是统一，大概率应该是韩国兼并朝鲜。毕竟经济影响和综合实力摆在这儿，然后北方，然后也有就是就是充足的优质兵源以及核武器和导弹这一块的一些尖端武器的话，今日朝韩如果统一的话，那对于整个东北亚地区来说，都是一颗不稳定的定时炸弹。毕竟当年越南当时统一的时候，他当时说要宣布继承法国在中南半岛的所有地盘和疆域。越南统一的第二年就去进攻柬埔寨和泰国，然后被咱们也被逼到79年出兵对越南发动自卫反击战。所以说越南尚且如此，朝鲜半岛统一之后局势更加不可控。
-问：你感觉现在中国俄罗斯和朝鲜之间关系其实怎么样？
-→ 答：各怀鬼胎。咱们和朝鲜的问题，还有俄罗斯的问题，主要就是图们江出海口的那个问题，到现在今天还拖着这个事没有着落。图们江就是俄罗斯和朝鲜就是那个，就是有一条有一条界江，但是那个地方是日本海的出海口，然后咱们在，就是在中朝俄边境那一块。就是图们江，就国际水域航道是可以通行，但是俄罗斯和朝鲜在那建了一座小桥。大船没法从那过去，所以说就俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了，然后都不想把那个出海口让给我们。
-问：你觉得就是朝鲜战争中那个朝鲜的军队，那韩国的军队有没有发挥什么作用？
-→ 答：好像在刚开始就差点让人发挥。一开始的时候，因为韩国的军队当时瞎指挥，就是什么呢？差点被朝鲜团灭，然后差不多在6月25号朝鲜战争爆发，可是从7月10号以后，朝鲜的南部的地面战斗主要是美军和朝鲜人民军进行战斗，然后韩军一开始就是负责一个冲人头的一个角色，就是，然后差不多是在1952年之后，美国把韩国重新整军训练备战之后，韩军才形成了一个基本的一个战斗力。在此之前，呃，韩国的军队对于美军来说一直有点类似于像猪队友的一个存在，就是接连被美国不被。中朝的军队给接连打败，然后美国每一次战役里边就是什么呢？志愿军跟美军占不到便宜的时候，都从韩国军队的那个战线那边进行突击，然后导致美军每一次的兵败都是韩国军队的战线崩溃所引起的。然后最后是呃，在第五次战役，也就是朝鲜战争最大的一次运动战的里面，呃，志愿军当时从韩国军队的就。朝鲜半岛的东部那一块就是形成一次反包围突击，然后把整个韩国军队前线都给打崩。然后美国当时把韩国第三军团全部给撤销，然后是美国人在韩国的领土上把韩国军队给撤销了。所以说关于韩国军队的战斗力，在一九五二年之前我不敢恭维，在一九五二年之后还是不可小视，毕竟韩军的主。要形成，他还是以军官的主体，是二战时期日本人扶植起来的伪军和傀儡部队的为骨干。然后士兵就是有点类似于像国民党时期抓壮丁的一个形式，强征来的一些就是呃农村青年这么一个形式。然后韩国的军队，他从朝鲜战争成军的时候一直到现在，他一直贯慢贯彻的。以前二战时期昭和日军的那套武士道精神的那种管理体制，就是就是关西兵，然后老兵欺负新兵，军队的霸凌事件一直蔓延到今天都屡见不鲜，所以说他就是一支充满着昭和军国主义时期那种思想余孽的，就是旧日军部队的一种延伸。
-问：就是他不是五零年五零年去援那个汉明嗯然后四九年国呃中国刚成立。然后他当时好像没找到选择，一个是受服台湾，一个是去抗美援朝。因为当时他自己的实力不是很强的，所以他选这个。他为什么选择了抗美援朝，而不是选择受服台湾？
-→ 答：首先，台湾和大陆之间有一道漫长的海峡，这个距离差不多得有个就是100公里左右。当时的中共刚刚建国，也没有相应的一个海军实力。然后50年的时候，朝鲜当时爆发了战争，在美国的参众两院普遍看来，这是共产主义世界对自由世界的一次全面进攻，然后连带着就是把台湾和韩国共同纳入到了美国的亚太实力圈。保护圈里面然后。连带的影响的就是美军的陆军，就是出兵朝鲜半岛，海军第七舰队进驻台湾。一来防止就是就是解放军解放台湾，二来说是防止国民党反攻大陆。然后因为当时解放军当时建军的时候没有相应的海军实力，所以说没办法进行。解放台湾的战斗。但是由于美国后期又越过三八线，向朝鲜以及中朝边境进发，然后触动了咱们的一个敏感神经，唇亡齿寒这么一个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争，因为台湾那个事儿已经让咱们已经很被动了，朝鲜半岛这一场，既然。要就是争取战略。主动，那就索性就是解放军的陆军当时就很强，就是在陆地上进行战斗。既然海上没办法进行战斗，那就只能在陆地上进行战斗。所以说这也是后来咱们当时就是一种战斗意志的体现，就是在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>7464/6822</t>
+          <t># 朝鲜战争历史讲解与答疑纪要
+朝鲜战争历史讲解与答疑纪要
+会议要点：本次会议围绕朝鲜战争历史展开，主讲人从朝鲜半岛分裂讲起，涵盖1945年美苏分占、三八线形成、1950年朝鲜战争爆发、各方称谓、主要战役（仁川登陆、长津湖、第三次战役等）、停战协定及战后边界变化。；主讲人阐述朝鲜战争对中国国际地位的影响，提及越南战争中北纬十七度线警告，以及美国称其为'被遗忘的战争'，克拉克将军承认未胜利签署停战协议。；主讲人解释朝鲜半岛分裂原因是意识形态不同导致建立两个国家，并分析当前朝韩关系、中俄朝关系及图们江问题，评价韩军战斗力，解释中国出兵朝鲜原因。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7464/282</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="13.5" customHeight="1" s="9">
+    <row r="45" ht="13.5" customHeight="1" s="10">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:03
@@ -13979,29 +13528,24 @@
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t># 对话概况
-本次对话为多人围绕出门与上班随身物品展开的闲聊，参与者包括发言人1、发言人2、发言人3、发言人4、发言人5。发言人2提出出门必带手机、充电宝、指甲刀，称指甲刀为多功能可磨手掌，并已用电子锁多年、以指甲刀平替钥匙；发言人3提出钥匙、纸巾、伞；发言人1强调必须带钥匙，自家为指纹锁、手机充电线够用；发言人4提到家钥匙及必带绑头发的皮圈；发言人5提出手机、耳机和工卡。上班随身物品方面，发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒。话题还延伸至长发打理与北京下雨，发言人3提到每年下雨园区门口都是水、李博之前开幕的地方被淹。会议未形成正式结论，发言人4在时间差不多时提议先停。
+本次会议为一场围绕出门必带物品的闲聊，场景为通用日常对话，共五位发言人参与。发言人2提出出门必带手机、充电宝、指甲刀，并解释指甲刀用于刮指甲、磨手掌等；发言人1强调必须带钥匙，并提到家中使用指纹锁；发言人4提到带皮圈绑头发；发言人2提到上班必带充电宝、手机、刮胡刀，平均每三天带一次；发言人5提到每天带手机、耳机和工卡；发言人3提到带纸巾和伞。讨论延伸至头发打理与个人形象，发言人2认为披发显头小，发言人3建议弄公分；发言人2分享曾想留长发大胡子的梦想，但因打理困难放弃。随后讨论北京下雨季节，发言人4认为夏天易下雨，发言人1认为无季节性；发言人3提到园区门口积水及李博家被淹，发言人2建议住三楼以上。会议无明确结论。
 # 交流内容
-出门必带物品话题：发言人2提出手机、充电宝、指甲刀，称指甲刀是多重指甲刀，可刮指甲、磨手掌；发言人3提出钥匙；发言人1强调必须带钥匙，并称自家门是指纹锁、手机充电线够用；发言人4提到家钥匙；发言人2称已用电子锁多年，用指甲刀平替钥匙；发言人4提到必带绑头发的皮圈；发言人3提到纸巾、伞。
-上班随身物品话题：发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒；发言人5提出手机、耳机和工卡；发言人2称耳机和工卡放单位、刷脸进入；发言人1提到打卡用手机、领夜宵需工卡，出差肯定不带手机卡；发言人2认为充电宝既能充电也能防身，最好带一块砖重量。
-长发打理话题：发言人2好奇初中男生为何喜欢薅女生头发圈，称若自己是女生会披发显脑袋小；发言人1称绑的没有散头发好看；发言人4提到女生披肩发；发言人2称高中时想留长发留大胡子学民谣吉他，后因不好打理打消念头，曾留胡子被误认为新疆少数民族。
-北京下雨话题：发言人1称北京下雨很少、没季节性、秋天容易下雨；发言人2质疑往常是春天容易下雨；发言人4认为北京夏天容易下雨；发言人1称夏天容易暴雨；发言人3提到每年下雨园区门口都是水，李博之前开幕的地方被淹、去年也有；发言人2提出住三楼以上远离水淹；发言人3提到一个妹子没买大雨、一早送孩子。
+话题一：出门必带物品。发言人2提出出门必带手机、充电宝、指甲刀，并解释指甲刀用途：'指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。'发言人1强调必须带钥匙，并提到家中使用指纹锁：'我家那个门是那个指纹锁的。'发言人4提到带皮圈绑头发：'我一定会带一个那个皮圈就绑头发的。'发言人2提到上班必带充电宝、手机、刮胡刀，平均每三天带一次：'上班必带三件套，充电宝、手机、刮胡刀。'发言人5提到每天带手机、耳机和工卡：'我现在每天就是手机、耳机和工卡。'发言人3提到带纸巾和伞。话题二：头发打理与个人形象。发言人2认为披发显头小：'我要是姑娘的话，我肯定得把头发披着，显得自己脑袋小一点。'发言人3建议弄公分：'弄个公分两边都补点点小点。'发言人2分享曾想留长发大胡子的梦想，但因打理困难放弃：'后来发现留胡子不太好打理还是算的，然后那个头发更不好打理，我就打消这样的想法和念头了。'话题三：下雨季节与居住安全。发言人4认为北京夏天易下雨：'我觉得北京是夏天能易下雨的。'发言人1认为无季节性：'北京倒是下雨很少，也没个季节性。'发言人3提到园区门口积水及李博家被淹：'每年的下雨，都那个园区门口都是水。李博还之前不是还就是开幕的那个地方还被淹了吗？'发言人2建议住三楼以上：'还是得远离，三楼以下还是得三楼以上？那么住着。'
 # 共识与分歧
-共识：**出门与上班随身物品因人而异，未形成统一清单**；**发言人2以指甲刀平替钥匙、上班必带充电宝、手机、刮胡刀**；**发言人1打卡用手机、领夜宵需工卡**。
-分歧：出门必带的三样东西到底是什么，未达成一致；为什么初中很多男生喜欢薅女生后边的头发圈，未解决；为什么秋天容易下雨而不是春天容易下雨，未解决；字节员工不录工卡会有什么样的惩罚，未解决。
-# 后续规划
-未提及</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>3851/1105</t>
+共识：多位发言人认同出门必带物品因人而异，且均分享个人习惯；发言人2与发言人1均认为钥匙或电子锁替代钥匙是常见做法；发言人2与发言人3均认为长发打理困难。分歧：关于下雨季节，发言人4认为北京夏天易下雨，发言人1认为无季节性；关于头发绑与披的观感，发言人2认为披发显头小，发言人1认为绑发不如散发好看。未解决的分歧：初中男生为什么喜欢薅女生头发圈、为什么秋天容易下雨，均无定论。
+# 后续规划</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3851/1101</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="13.5" customHeight="1" s="9">
+    <row r="46" ht="13.5" customHeight="1" s="10">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:03
@@ -14193,26 +13737,22 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次讨论由发言人1至发言人5共同参与，围绕各自手机中最常用的APP及使用习惯展开交流，核心探讨问题包括常用APP类别、AI助手与浏览器的取舍、视频平台付费方式、音乐APP选择与听歌场景，以及歌手与乐队偏好。讨论中涉及的具体APP包括知乎、小红书、谷歌、微信、抖音、淘宝、京东、B站、YouTube、豆包、百度、千问、吉米、重庆元宝、腾讯视频、爱奇艺、优酷、芒果TV、网易云、酷狗、酷我、虾扎、苹果music等。微信是否算最常用APP、大家为什么不喜欢用浏览器、Taylor Swift为什么重新火起来成为讨论中的开放问题。
-# 发言要点
-发言人2提到常用知乎、小红书、谷歌，并表示仍停留在浏览器加地图测绘用尺子标注的年代，不太喜欢用AI软件，不确定其是否正确，还提到欧美音乐平台虾扎、欧美演唱会版本更多、小众翻唱多、大版权有纠纷播不出来，并疑惑Taylor Swift为何重新火起来，提到她中学时火、后因绯闻消沉、对九零后和零零后影响深，以及Love Story、猫头鹰之城、亚当杨、绯闻、表白。发言人3提到微信、抖音、淘宝、京东，表示已下载豆包，提到重庆元宝，认为AI小助手更全面、回答更精准、总结性更强，还提到腾讯视频、爱奇艺、优酷、芒果TV等播放器APP，开VIP、看广告获得VIP时长，以及谢霆锋、Taylor Swift、玉蝴蝶。发言人4提到微信、小红书，提到用小布小布代替浏览器，提到通勤路上听歌、要降噪耳机，提到歌名有英文、Taylor Swift的全球影响力。发言人5提到B站、YouTube，指出小布小布是豆包，常用网易云，提到单框架手机网易云不适配、用卓翼通，提到APP太多不知道开哪个。发言人1提到百度、千问、吉米等，提到苹果music，发现国内付费电视剧在YouTube上不要钱，提到五月天、周杰伦。观点交锋点包括微信是否算常用APP、AI助手能否判断对错、视频平台广告与付费方式、音乐APP选择与适配问题。
-# 共识形成
-小组未形成统一意见或解决方案，讨论中提出的主要观点包括：AI小助手更全面、回答更精准、总结性更强；视频平台广告时间长，可用B站直接看或开VIP、看广告获得VIP时长；小网站不用花钱，因平台大才有版权纠纷需付费；欧美音乐平台演唱会版本更多、小众翻唱多；听歌场景包括上班、通勤路上、地铁，降噪耳机可提升体验。
-# 未决事项与分工
-需进一步探讨的问题包括：微信是否算最常用APP、大家为什么不喜欢用浏览器了、Taylor Swift为什么重新火起来。后续任务分工未提及。</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>4259/1069</t>
+          <t># 手机常用APP与音乐偏好闲聊
+手机常用APP与音乐偏好闲聊
+会议要点：本次会议围绕手机常用APP及音乐偏好展开闲聊。与会者分别提及常用APP：发言人2常用知乎、小红书、谷歌；发言人3常用微信、抖音、淘宝、京东；发言人4常用微信、小红书；发言人5常用B站、YouTube。大家提到AI助手如小布、豆包、百度千问等，认为AI助手更全面精准，但发言人2表示不信任AI，仍用浏览器和纸质地图。；在视频与播放器方面，发言人3提到腾讯视频、爱奇艺、优酷、芒果TV等，发言人2抱怨广告时间长，用B站直接看；发言人5提到单框架手机无法下载YouTube；发言人1发现国内付费剧在YouTube免费，但发言人2指出小网站可免费看，因平台大有版权纠纷需付费。音乐方面，发言人5常用网易云，但单框架手机不适配，用卓翼通；发言人2以前用酷狗、酷我，提到欧美音乐平台虾扎；发言人1用苹果音乐。听歌时间包括上班、通勤、地铁等，发言人2提到柏林地铁安静听歌有代入感。；歌手与乐队偏好方面，发言人3提到喜欢谢霆锋，提到Taylor Swift；发言人1认为五月天以前好，新发唱不上去了；发言人2疑惑Taylor Swift为何重新火起来，提到中学时期（2010年代）火过，因绯闻消沉，现在对九零后和零零后都有影响；发言人4认为她全球影响力大。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4259/566</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1" s="9">
+    <row r="47" ht="13.5" customHeight="1" s="10">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -14385,25 +13925,30 @@
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论围绕2022年俄乌战争爆发后俄军战场表现是否为其真正应有状态展开，由发言人1主持并主讲，发言人2、发言人3、发言人4参与讨论。发言人1指出，战前外界普遍认为俄罗斯会一边倒取胜、基辅很快被占领、泽连斯基会流亡，但泽连斯基扛住进攻并把俄军从基辅打回白俄罗斯和乌克兰边境。与会者从腐败、基层官兵、游戏影视形象、直观战斗力、欧洲认知及俄罗斯旅行见闻等多个角度发表了看法。讨论认为俄军单兵素质很厉害但总体拉垮，主要问题在后勤和指挥上；欧洲人把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，乌克兰被称为欧洲之门。
+本次讲座围绕2022年俄乌战争以来俄军战场表现展开讨论，主讲人及机构未明确提及。发言人1提出俄军传统钢铁洪流印象与2022年实际表现形成反差，基辅未被占领，俄军被击退；发言人3提及腐败、国防部长问题；发言人4认为俄军被动时战斗力强，主动进攻表现差。发言人1分析普京信息茧房、情报经费贪污、基层官兵误以为演习、民兵自发抵抗导致闪电战变持久战。讨论还涉及游戏与媒体中的俄军形象、俄军战斗力与战争形态、乌克兰地缘战略与欧洲认知，并延伸至俄罗斯历史文化与旅游见闻。
 # 核心观点与论证
-核心论点一：俄军腐败问题突出。支撑论据为情报官员把用于策反乌克兰官员的经费全部贪污瓜分，导致乌克兰高官未收到策反经费；2014年俄罗斯占领克里米亚后乌克兰上下迸发民族仇恨，对政府无能与腐败不满。核心论点二：俄军基层官兵与战争初期情况。支撑论据为俄军基层官兵不知道2022年会进攻乌克兰，好多部队收到命令还以为是去演习，第一批部队进入乌克兰时遭遇民兵自发抵抗而非军队有组织进攻，闪电战变成持久战。核心论点三：游戏与影视中的俄军/苏联形象。支撑论据为从苏联时期开始俄军给人钢铁洪流印象，在各国游戏里苏联或俄罗斯常作为反派；红警等游戏被指为黑苏联，把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。核心论点四：对俄军的直观印象与战斗力评价。支撑论据为俄军单兵素质很厉害但总体拉垮，主要后勤和指挥上，像矮脚巨人、柯基腿短支撑不起庞大身子；俄乌战场打得跟二战没啥进步，多了点无人机，双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸，从钢铁洪流变成菜鸡互啄；俄罗斯无人机靠伊朗给，乌克兰由北约持续输血，类似越战形式；车臣、格鲁吉亚、瓦格纳、库尔德武装等地方武装战斗力挺强。核心论点五：欧洲对俄罗斯的认知与乌克兰的地缘意义。支撑论据为乌克兰在欧洲人认知里被称为欧洲之门，欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待；俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳；欧洲自发支援乌克兰，不让俄罗斯打赢，要把俄罗斯挡在亚洲之外；乌克兰死活不能向俄罗斯妥协。核心论点六：俄罗斯旅行与东宫藏品。支撑论据为出俄罗斯后签证上会写、办美签可能被拒；发言人1因去过好几次俄罗斯，在美国边境入口被拦下询问去俄罗斯干嘛，差点被怀疑是间谍；东宫是世界四大艺术博物馆之一，连续去了三次不同区域都没逛完，圣彼得堡夏天不错；东宫藏品来源包括列强殖民、探险队名义、俄国东扩、二战后从德国运回，以及王室联姻赠送品，涉及欧洲、中东、东亚、西夏王陵、敦煌、中亚、埃及、北非、奥斯曼帝国等地。核心论点七：俄罗斯地域与民族构成。支撑论据为讨论俄罗斯欧洲部分与亚洲部分差别是否很大，远东地区风格和欧洲那头；提到境内好多共和国，但总的来说以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。
+讲座按逻辑结构逐层展开。首先，发言人1提出俄军传统钢铁洪流印象与2022年实际表现反差，基辅未被占领，俄军被击退，并分析原因：普京活在自己信息茧房，情报官员贪污策反乌克兰官员经费，基层官兵误以为演习，民兵自发抵抗导致闪电战变持久战。其次，讨论游戏与媒体中的俄军形象，发言人4指出西方主导游戏，苏联形象多为反面，如红警将共产主义思想扭曲为心灵控制器。再次，发言人1总结俄军单兵素质强但后勤指挥拉垮，比喻为矮脚巨人；发言人4认为俄乌战场与二战相比进步有限，仅多无人机，双方重装备耗尽，转为战壕手雷和无人机互炸，形容为菜鸡互啄。最后，发言人1阐述乌克兰为欧洲之门，欧洲视俄罗斯为亚洲半兽人，因蒙古统治历史不被接纳，欧洲支援乌克兰以阻挡俄罗斯。
 # 金句总结
-发言人1："俄军他总的来说，给我看来，他就是单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，然后就是矮脚巨人的感觉是不是就有点像柯基的感觉，就是腿特别短，支撑不起他庞大的身子的那种感觉。"——背景为讨论俄军在乌克兰的表现时对俄军整体战斗力的评价。发言人1："从一种钢铁洪流变成了最后的菜鸡互啄。"——背景为描述双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸的战场状态。发言人1："乌克兰在欧洲人的认知里面是被称为欧洲之门。"——背景为阐述欧洲对俄罗斯的认知与乌克兰的地缘意义。发言人1："欧洲的边界是在乌克兰，所以说一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。"——背景为解释欧洲自发支援乌克兰、不让俄罗斯打赢的原因。
+发言人1："俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，矮脚巨人的感觉，就像柯基，腿特别短，支撑不起庞大的身子。"（背景：总结俄军在俄乌战争中的表现，强调单兵与整体反差）
+发言人1："从一种钢铁洪流变成了最后的菜鸡互啄。"（背景：描述双方重装备耗尽后，战场转为战壕手雷和无人机互炸的形态）
+发言人1："没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。"（背景：阐述乌克兰对俄罗斯的地缘战略意义，欧洲视乌克兰为欧洲之门）
 # Q&amp;A 环节
-问：俄罗斯在俄乌战争的表现是否是俄军真正应有的一种状态？→ 答：发言人1提出该问题供讨论，与会者从腐败、基层官兵、游戏形象、直观战斗力、欧洲认知等角度发表看法，未形成明确结论。问：大家对于游戏里的俄军是一个什么样的印象？→ 答：发言人2、发言人4认为红警等游戏是西方主导为黑苏联而做，苏联形象多为反面、很猛很变态、研究非常邪乎的武器、大规模夸张；发言人1指出把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。问：对于俄罗斯被西欧称半兽人这种印象，大家怎么看？→ 答：发言人1解释欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳。问：俄罗斯欧洲那边跟亚洲这边差别很大吗，远东地区的风格和欧洲那头？→ 答：发言人1表示总的来说还是以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t>6103/1947</t>
+问：游戏里俄军是什么印象？
+答：发言人4指出西方主导游戏，苏联形象多为反面，很猛、很变态，研究邪乎武器，规模夸张；发言人1补充红警将共产主义思想扭曲为心灵控制器，把毛子形容为暴力美学形象代言。
+问：俄罗斯东西部差异大吗？
+答：发言人1表示总的来说以俄罗斯族为主，俄国东扩像美国西进，源源不断淘金移民。</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6103/950</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="13.5" customHeight="1" s="9">
+    <row r="48" ht="13.5" customHeight="1" s="10">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:01
@@ -14502,31 +14047,25 @@
       <c r="C48" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论围绕电影《南京照相馆》展开，由发言人1介绍历史背景并辨析影片虚构与真实。发言人3在抖音看过切片、也去电影院看过，觉得挺好看；发言人4认为是灾难电影，印象最深的是几个人在地下室吃喝睡觉、最后老弱妇孺还活着；发言人2觉得深刻、好看；发言人5表示题材不太习惯、没看过。发言人1介绍：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据。发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
+会议围绕电影《南京照相馆》展开讨论，由发言人1主导介绍历史背景。发言人3看过抖音切片，发言人4看过电影，印象是灾难电影，老弱妇孺存活，地下室场景；发言人2觉得深刻好看；发言人5因题材不习惯未看。发言人1介绍1937年8月13日八一三淞沪抗战后，国军从上海撤退，日军追击至南京，因缺乏军纪约束导致南京大屠杀。电影主要人物虚构，但照片拍摄真实，实际由美国传教士拍摄，中国冲洗人员偷拷并提交军事法庭作为证据；电影中中华门战斗、挹江门惨案、战犯审判为真实历史。发言人2提到沈阳伪满洲国博物馆、唐山大地震纪念馆参观人多需预约；发言人3提到上海抗战纪念馆人多，南京大屠杀纪念馆难抢；发言人4多年前去过。
 # 核心观点与论证
-发言人1首先介绍历史背景：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。
-在虚构与真实之辨上，发言人4问片中日本军官及主角与其建立友谊是否虚构，发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据，而非电影人物所拍摄留存。
-发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
-关于日军暴行成因与指挥更替，发言人1解释上海抗战介绍多是因为中日第一场大规模战斗在上海；日军到南京进行大屠杀，因其自九一八以来未遭大规模战争，认为遭受前所未有的侮辱及战场应激创伤，结合日本攻破敌方城镇以屠城狂欢麻痹的历史，以及自上而下高压武士道精神下的欺凌霸凌宣泄；原指挥官松井石根因生病被临时替换，他曾发布命令避免日军在上海至南京沿线烧杀抢掠，以免招致中国军民反感、增强抵抗意志；替换为裕仁亲王的叔叔朝香宫鸠彦亲王，其追随脱亚入欧思想，上任后第一道命令是不留俘虏、格杀无论，导致日军军纪失控，蔓延至对老百姓群体，最终导致南京大屠杀。
+发言人1首先介绍历史背景：1937年8月13日八一三淞沪抗战，国军与日军在上海激战，因实力原因撤退，日军追击至南京。更深层原因是自1931年九一八事变以来，日军占领东北、华北均未遭遇成规模抵抗，八一三淞沪抗战是日军首次遭受迎头痛击，伤亡惨重，加上长达四个月战斗，日军缺乏军纪约束，攻破南京后导致南京大屠杀。电影中主要人物虚构，但照片拍摄真实，实际由两名美国传教士拍摄日军暴行，同时期中国冲洗照片人员无意发现后偷偷拷贝，抗战后提交国民政府军事法庭作为审判日本战犯证据。电影中中华门城墙战斗、挹江门撤退惨案、战犯审判（谷寿夫、第六师团师团长等被枪决）均为真实历史。发言人1还分析日军暴行原因：日军遭受前所未有的侮辱及战场应激创伤，结合日本屠城传统、高压武士道精神，以及指挥官更换——松井石根因病被替换，朝香宫鸠彦亲王上任后发布不留俘虏命令，导致军纪失控。
 # 金句总结
-发言人1在介绍日军暴行成因时指出：“从他们的角度来说，就是我也去过什么日本当时的那些个博物馆……觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”其背景是解释日军攻破南京城后为何进行大屠杀。
-发言人1在说明指挥更替时指出：朝香宫鸠彦亲王“上任之后发布的第一道命令就是不留俘虏，格杀无论”，随后“蔓延到了对老百姓群体的一种发生，然后最终导致了南京大屠杀”。
-发言人1在辨析影片真实与虚构时指出：“电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。”
+发言人1指出：“从他们当时那样的心态来说，觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”此句关联日军在南京暴行的心理动因。另一金句：“攻破了敌方的城镇，都要以屠城来进行自己那种狂欢与麻痹。”此句解释日军屠城的历史传统。
 # Q&amp;A 环节
-问（发言人4）：电影里面虚构的，它里面有一个日本的军方关系叫什么？就是主角一度好像和他建立一次友谊吧？不知道这个是虚构的，就是有没有这个日本军官是是不是真实？
-→ 答（发言人1）：电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。真实的一个历史是，当时是两个美国的传教士，然后当时是拍摄的当时日军的这一块相关的一个暴行。然后同时期也有咱们国家当时就是负责给日本人冲洗照片的一个，就是那个我不能说是摄影师，他应该是后期，就类似于就照片冲洗这样一个状态吧。然后他无意间发现了这一些个，就是日本所拍摄这些暴行，在日本当时是属于禁文，他偷偷拷贝了下来，藏起来了之后，然后是于抗战之后把这个递交给当时国民政府的军事法庭，就是作为审判日本战犯的一个证据，而不是当时就是南京照相馆里面的那些电影人物所就是拍摄留存下来的这么个情况。</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t>4228/1960</t>
+问：电影里面虚构的，它里面有一个日本的军方关系叫什么？就是主角一度好像和他建立一次友谊吧，不知道这个是虚构的，有没有这个日本军官是不是真实？答：电影里的主要人物是虚构，但照片的拍摄是真实的，但不是以电影里所描述的方式进行的。真实历史是当时两个美国传教士拍摄日军暴行，同时期中国负责冲洗照片的人无意发现后偷偷拷贝，抗战后提交国民政府军事法庭作为审判证据。</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4228/1003</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="13.5" customHeight="1" s="9">
+    <row r="49" ht="13.5" customHeight="1" s="10">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -14611,25 +14150,25 @@
       <c r="C49" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议围绕日本国家概况、对日本的印象与了解展开自由讨论，由发言人1主持并引导，发言人2参与发言。发言人1提出日本在国人印象中较为复杂：历史原因导致中日曾发生战争与悲剧，但今天日本在中国外部投资中占很大比重，中日也是主要贸易伙伴；上学、上班人群喜欢去日本旅游，日本服务业和购物体验在各国中首屈一指。发言人2提到读研时上过讲日本文化的课，读《四世同堂》后觉得民族仇恨还是应该有一点影响。讨论涉及日本文化的来源与历史分期、天皇制度与君主立宪、旅游购物与中古店、日本民族性格与岛国环境等话题。
+本次会议围绕日本国家概况、文化历史阶段、社会转型、天皇制度及旅游购物等话题展开自由讨论，参会成员为发言人1和发言人2。发言人1指出日本文化缺乏原创，是外来接收的本土化改进，并列举三次转折：大化改新、明治维新、和平宪法转型，分别对应向中国、欧美、美国学习。发言人2提及民族仇恨应有一定影响，并认为日本文化对自身影响较多，同时提到喜欢漆艺、茶艺等传统文化。发言人1补充天皇在古代是吉祥物般存在，二战后麦克阿瑟迫使天皇公开露面，打破神格，推动社会转型，现在天皇无实权，类似英国、西班牙君主立宪制。发言人2提及民族性格极端源于岛国气候不稳定。发言人1还提及东京、大阪、镰仓、京都、名古屋等城市，以及秋叶原、富士山等地点和购物体验，包括奢侈品、中古店、手办等，发言人2提到化妆品、美妆。
 # 发言要点
-发言人1主张日本文化没有原创，属外来接收后本土化改进，经历三次转折：古代大化改新（向中国、朝鲜半岛学习，形成和服、制茶、漆器等传统）、近代明治维新（对标清朝、向欧美列强学习，学英国和德国法度利器）、二战后和平宪法转型（美国制定和平宪法，社会结构大规模调整，向美国看齐）；并谈到古代日本君臣关系与中国差别大，天皇对各地封建君主而言更像吉祥物，被当神灵供奉以精神层面控制百姓，1945年二战结束后美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，推动社会转型；现今天皇如君主立宪制下英国、西班牙那样的象征性存在，不能参与政治和国家事务，政治由国会和内阁选出首相执政，美国把日本改造成英美海洋法系国家结构，天皇没有实权，靠政府养着，存在感不如英国国王。发言人1还谈到旅游购物：长崎、东京、大阪、秋叶原等城市，秋叶原可买数码宝贝、铁甲小宝等原装手办以及美妆、护肤品、玩具；日本奢侈品便宜，有Vintage中古店，广场协议后日本经济急剧恶化、泡沫经济崩溃，上班族失业后把原先买的高档大衣、西装、皮具、皮鞋等通过二手回收寄卖，催生中古二手店产业，上海也有很多这类店，能买到LV、Burberry、古奇等上个世纪知名大牌，男性款式相对少；其本人喜欢去日本爬山、爬富士山、看古城、逛博物馆，如镰仓、京都、名古屋，喜欢镰仓夏天舒服的气候。发言人2提到日本传统文化如漆艺、茶艺以及现代文化艺术，并提到听过一种评论：日本是岛国，气候非常不稳定，发展农业可能遇海啸导致收成没了，所以民族性格比较容易极端。双方分歧点在于：发言人1追问日本文化具体指哪一个历史阶段，发言人2未明确；发言人1认为日本民众现在对天皇没有崇拜，发言人2则追问是否还有崇拜，未达成一致。
+发言人1：指出日本文化缺乏原创，是外来接收的本土化改进，列举三次转折——大化改新向中国和朝鲜半岛学习，明治维新向欧美列强学习，和平宪法转型向美国看齐；补充天皇在古代是吉祥物般存在，二战后麦克阿瑟迫使天皇公开露面打破神格，现在天皇无实权，类似英国、西班牙君主立宪制；提及东京、大阪、镰仓、京都、名古屋等城市，以及秋叶原、富士山等地点和购物体验，包括奢侈品、中古店、手办等。发言人2：提及民族仇恨应有一定影响，认为日本文化对自身影响较多，提到喜欢漆艺、茶艺等传统文化；认为日本民族性格极端源于岛国气候不稳定；提到化妆品、美妆。观点交锋点：发言人1强调日本文化是外来接收的本土化改进，发言人2则更关注日本文化对自身的影响和民族性格成因。
 # 共识形成
-小组未形成明确统一意见或解决方案，讨论中形成的共同认识包括：日本在国人印象中较为复杂，中日既有历史战争与悲剧，也是主要贸易伙伴；日本文化属外来接收后本土化改进，经历大化改新、明治维新、二战后和平宪法转型三次转折；现今天皇为君主立宪制下的象征性存在，无实权；日本有Vintage中古店产业，上海也有这类店。
+小组未形成明确的统一意见或解决方案，讨论停留在自由交流层面。发言者就日本文化历史阶段、天皇制度、旅游购物等话题分享了个人印象和知识，但未达成具体共识或产出。
 # 未决事项与分工
-需进一步探讨的问题：日本文化具体指哪一个历史阶段的日本文化，尚未明确；日本民众现在对天皇是否还有崇拜，未达成一致。后续任务分工未提及。</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>4892/1239</t>
+未提及需进一步探讨的问题及后续任务分工。</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4892/791</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1" s="9">
+    <row r="50" ht="13.5" customHeight="1" s="10">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:01
@@ -14837,26 +14376,22 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议承接此前西游记的文学话题，延伸讨论大家对三国与红楼梦的印象与看法，参与者为发言人1至发言人5。三国部分围绕整体印象与阵营偏好、刘备与孙刘联盟、白衣渡江与吕蒙评价、东吴大都督与陆逊、蜀汉内斗与姜维魏延、三顾茅庐与隆中对展开；红楼梦部分围绕版本与作者、判词与人物结局、后四十回官方地位及曹雪芹小道等北京地点展开。核心探讨问题包括：对三国印象最深刻的章节与阵营偏好、正史中刘备与孙刘联盟的演变、白衣渡江的评价、东吴大都督的结局、蜀汉内斗与姜维魏延、三顾茅庐与隆中对战略，以及红楼梦前八十回与后四十回的作者差异、判词与人物结局、后四十回为何成为官方结尾。
-# 发言要点
-发言人2表示三国没看完，看到诸葛亮去世就不想看了，认为后面没意思；印象最深刻的是赤壁，认为前面比后面有意思；受三国演义影响一般偏向蜀汉刘备阵营；认为白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好；对陆逊印象是火烧连营，认为东吴后期政治斗争严重、内斗狠；提到蜀汉也内斗、魏延被砍；红楼梦方面提到四个丫鬟、袭人、晴雯，提到解读说林黛玉代表明、薛宝钗代表清，问为何最终选高鄂后四十回作为官方结尾，提到植物园有曹雪芹小道。发言人1补充正史后续姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴；认为刘备晚年若未称汉中王，孙权可能不会彻底决裂，称王引发吕蒙白衣渡江、刘备伐吴夷陵惨败等连锁反应；讲述刘备入川占成都后不还南郡、孙权派兵夺荆南三郡、曹操取汉中迫使刘备回师并签订湘水之盟，单刀赴会实为鲁肃与关羽各不带兵士在中立区谈判被罗贯中美化；认同白衣渡江开坏头，称吕蒙被后世与小偷鼠辈等价；称正史上周瑜被曹人射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；称刘禅自知能力不行完全放权诸葛亮，诸葛亮去世后姜维难力挽狂澜，刘禅轻信黄浩谗言，姜维是魏国降将靠诸葛亮提拔才有说服力；称正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，若非姜维断后挡住司马懿军队后果不敢想象，其行为与谋反无实质区别，实为与杨仪个人矛盾；补充隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾，诸葛亮北伐目标在关中平原和陇西，第一次北伐赢面大但因马谡兵败街亭而破产。发言人3称红楼梦只写了前八十回，后面是别人写的；称第五回贾宝玉梦游太虚幻境已把结局交代，以判词形式；称北苑所旁边村子有曹雪芹小道，爬山时看到过。发言人4称红楼梦有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；称第一遍读高鄂续版本时觉得合理，后来知道后四十回不是同一作者，反复读前八十回后再接触后四十回，发现林黛玉性格变了很多；称判词没点那么明确，探春、史湘云结局都是猜的，最后谁和贾宝玉在一起也是猜的；称林黛玉死不是原作写的，但原作意图肯定是悲剧；称晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；称第五回贾宝玉在秦可卿床上做梦到太虚幻境，看到判词，十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；称最终选高鄂后四十回因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及；称北京植物园底下有他的工具。发言人5讲述三顾茅庐：刘备中原屡战屡败，深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次前往拜访，前两次未见到，第三次见到诸葛亮，诸葛亮被打动提出隆中对战略，联合孙权，最终同意辅佐刘备；问悲剧原因，如贾宝玉与林黛玉真心相爱却被迫娶薛宝钗。
-# 共识形成
-小组未形成正式决议，讨论中形成的共同认识包括：三国方面，大家印象最深刻的是赤壁，受三国演义影响一般偏向蜀汉刘备阵营；白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好，吕蒙被后世与小偷鼠辈等价；东吴后期政治斗争严重，周瑜正史中被射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，其行为与谋反无实质区别，实为与杨仪个人矛盾；隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，但白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾；诸葛亮第一次北伐赢面大但因马谡兵败街亭而破产，此后只能拖延魏国灭蜀。红楼梦方面，大家认为其有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；只写了前八十回，后面是别人写的；第五回贾宝玉梦游太虚幻境已以判词形式交代结局，但判词没点那么明确；晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；最终选高鄂后四十回作为官方结尾，因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及。
-# 未决事项与分工
-未决事项包括：红楼梦后四十回到底是谁写的、什么版本，真正意义是否与当时朝代社会有关；探春、史湘云的结局以及最后谁和贾宝玉在一起，都是猜的，没有明确答案；为什么最终选高鄂的后四十回作为官方结尾。后续任务分工未提及。</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>6453/2163</t>
+          <t># 三国与红楼梦文学讨论纪要
+三国与红楼梦文学讨论纪要
+会议要点：会议围绕三国演义与红楼梦展开文学讨论。三国部分，发言人2表示三国未看完，诸葛亮去世后便不再看，印象最深刻章节为赤壁，阵营偏好受演义影响倾向蜀汉。发言人1补充正史后续：姜维北伐、孙权二宫之争、邓艾偷渡阴平、姜维反间计、刘禅投降、西晋灭吴。发言人1分析刘备称汉中王引发连锁反应，包括吕蒙白衣渡江、夷陵惨败；正史中刘备借荆州不还，孙权派兵夺荆南三郡，后湘水划界；鲁肃与关羽单刀赴会，被演义美化为关云长单刀赴会；白衣渡江被指突破底线，吕蒙后世印象不佳；陆逊因二宫之争被孙权逼死，东吴大都督结局多不佳；魏延正史无谋反，但烧栈道行为与谋反无异。发言人5讲述三顾茅庐与隆中对，发言人1分析隆中对在白衣渡江后失效，诸葛亮北伐目标为凉州，因马谡失街亭失败，后期北伐为绝望抗争。；红楼梦部分，发言人4提出多角度解读，讨论前八十回与后四十回作者差异，高鹗续写版本合理性。第五回判词预示结局，探春、史湘云结局为猜测。晴雯为林黛玉替身，袭人像薛宝钗。晴雯之死为曹雪芹原作。讨论林黛玉、薛宝钗影射明朝清朝的说法，秦可卿被解读为前朝公主。高鹗后四十回被选为官方结尾，因其总体合理且基于残稿梳理。
+（生成可能有误）</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6453/524</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="13.5" customHeight="1" s="9">
+    <row r="51" ht="13.5" customHeight="1" s="10">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -14969,25 +14504,25 @@
       <c r="C51" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人1主导串场，发言人2、发言人3参与，从兵法和战法角度延伸三国故事线，核心探讨赤壁之战的影响、合肥之战与孙权北伐、白衣渡江与火烧连营、陆逊与孙家关系、北伐方向与孙权早期败仗、蜀汉曹魏印象与武将战力、魏延守街亭假设等议题。讨论认为赤壁之战不是曹军实力不行，而是骑兵没法打水战；合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下。
+会议围绕三国赤壁之战、合肥之战、火烧连营等战役展开讨论，从兵法和战法角度分析各方军事特点与将领能力。成员包括发言人1、发言人2、发言人3，核心探讨问题包括赤壁之战的影响、孙权北伐合肥的失败、火烧连营的经过，以及对关羽、张飞、黄忠、五子良将等武将能力的评价。
 # 发言要点
-发言人1主张：曹操军队以虎豹骑为主擅长陆战，刚收服荆州无像样水军，江东以水军为主，曹军无法打水战而败；后期东吴北伐如合肥之战，吴军擅长划船、摇橹、打水战、游泳，上岸后无法与曹军对抗，双方僵持。合肥像钉子钉在东吴北伐路线上，从建业过长江到江北、经小河到巢湖上岸，打下合肥才能靠近淮河继续北伐；公元215年合肥之战，曹军主力在汉中，合肥只有张辽、李典、乐进三将且矛盾重，张辽率800死士骑马冲锋大败吴军，孙权差点被张辽抓住，张辽问俘虏骑马好、箭准、上长下短、小胡子的人是谁，得知是孙权后后悔没抓住。刘备体恤下属让士兵在密林扎营抵御酷暑，陆逊抓住秋季干燥、树叶飘落时机在秋老虎时期一口气放火，连营七百里的营地被烧，刘备只身逃回白帝城。陆逊是江东四杰，孙策孙坚是外来户，孙策被称为小霸王，过于冒失后被刺杀，曹操说生子当如孙仲谋，孙权开疆拓土能力不行但能守住家业。对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家；刘备汉中之战打得好，夷陵之战被仇恨冲昏头脑冒进，汉中之战有法正和黄权辅佐，靠地势地利耗出汉中；关羽水淹七军、斩颜良诛文丑，阵中斩将历史第一人；黄忠阵斩夏侯渊；张飞长坂坡、和马超大战五百回合；五子良将有曹仁、张辽、夏侯渊、张郃、徐晃、于禁，于禁被关羽生擒；曹操人多血厚能耗得起。如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，不会像马谡轻易丢掉街亭，第一次北伐可能成功，魏延想法大胆但不太符合蜀汉当时实际支撑，地盘太小。发言人2提出：小时候觉得生子当如孙仲谋，孙权厉害，长大感觉反转厉害；并问陆逊和孙家是否有仇。发言人3提出：除朱元璋从南往北打，其余都是来首都就不错，北伐南、南下容易；孙权在孙十万之前也打过一场坑仗，好几万人去打人家，被几千几百人追着打；关羽只知水淹七军，张飞只知长坂坡。分歧点在于孙权早期败仗的对手是谁，是刘表、刘琦还是曹仁时期，未确认。
+发言人1认为赤壁之战并非曹军实力不济，而是骑兵无法打水战；东吴擅长水战但陆战弱，在合肥之战中失利。发言人2表示小时候认为孙权厉害，长大后看法反转，认为其战绩不佳。发言人3补充孙权在孙策刚死时也曾被刘表等势力击败，几万人被几千人追着打。关于武将能力，发言人1认为关羽阵中斩将改变战局，张飞长坂坡，黄忠斩夏侯渊；发言人3提到关羽水淹七军，并认为刘备汉中之战打得还行。
 # 共识形成
-小组未形成正式决议，讨论中形成的统一意见包括：**赤壁之战不是曹军实力不行，而是骑兵没法打水战**；**张八百大破孙十万是长期划船游泳的人不擅长陆地冲锋，双方僵持**；**合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下**；**孙权开疆拓土能力不行但能守住家业**；**对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家**；**如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，第一次北伐可能成功，但魏延想法不太符合蜀汉当时实际支撑，地盘太小**。
+会议达成共识：赤壁之战体现双方各自优势与局限，曹军败于缺乏水军，东吴败于陆战能力弱；孙权一生未能攻克合肥，合肥之战成为其军事生涯败笔；刘备因体恤士兵在密林扎营，被陆逊火攻连营七百里，逃回白帝城。
 # 未决事项与分工
-需进一步探讨的问题：孙权早期被几千几百人追着打的败仗对手是谁，是刘表、刘琦还是曹仁时期，未确认。后续任务分工未提及。</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>4899/1301</t>
+未提及</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4899/449</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="13.5" customHeight="1" s="9">
+    <row r="52" ht="13.5" customHeight="1" s="10">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -15046,45 +14581,34 @@
       <c r="C52" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次研讨会围绕1979至1989年苏联入侵阿富汗战争（苏阿战争）展开讲解并组织提问讨论。讲解指出阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带和兵家必争之地，国土纵深90%为高原山地，易守难攻，被称为帝国坟场，谁控制了阿富汗谁就控制住了亚洲的咽喉。讲解梳理了战前国情与苏联出兵过程：20世纪50年代阿富汗实行君主立宪制，同时与苏联和西方保持友好交往，精英与知识界奉行亲英与亲苏两头政策，文化上向英国靠拢、国家建设和工业向苏联看齐，基辛格评价阿明用苏联的火柴点美国的香烟。因阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入，1979年12月24日平安夜趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营，此举招致阿拉伯国家、中国、西方盟国不满。讨论环节分析了苏联出兵原因与阿富汗难打的原因：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克，加上阿富汗是特殊战略要地及苏联错判，导致大的战略性失误，同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。阿富汗90%为高原山地，是天然游击战地区，除喀布尔、坎大哈等主要城市外大部分乡村实行部落长老制、各自为政，政府无控制力；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助毒刺防空火箭筒等先进单兵武器，有效压制苏联雌鹿武装直升机，坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机，苏联基层官兵厌战、士气一落千丈，1989年从上到下扛不住压力最终撤军。关于各国援助，讲解说明阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契，中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+本次研讨会围绕1979年至1989年苏联入侵阿富汗的苏阿战争展开，主讲人系统介绍了阿富汗的地理位置、历史背景、苏联出兵原因、战争过程及各方援助情况。阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、伊朗，被称为亚洲的中间走廊地带，是兵家必争之地；其国土百分之九十为高原山地，易守难攻，历史上多次获得“帝国坟场”称号。主讲人详细讲述了苏联出兵的过程：1979年12月24日平安夜，苏联以兵变政变形式，借口阿富汗请求救援，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜之间控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营。此举招致阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗抵抗组织，阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，支持阿富汗进行长达十年的游击战争，最终苏联于1989年撤军。问答环节中，主讲人解答了听众关于阿富汗战略价值、石油资源、圣战者含义及帝国坟场原因等问题。
 # 核心观点与论证
-论点一：阿富汗地理位置关键，是亚洲咽喉要地，易守难攻。论据：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带，兵家必争之地；国土纵深90%为高原山地，易守难攻，被称为帝国坟场；谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-论点二：20世纪50年代阿富汗同时与苏联和西方保持友好交往，实行君主立宪制，精英与知识界奉行亲英与亲苏两头政策。论据：文化上向英国靠拢，如英国议会制度、君主立宪制度及大学现代科学的承办师从英国；国家建设和工业方面向苏联看齐；基辛格评价阿明用苏联的火柴点美国的香烟，获得墙头草称号。
-论点三：苏联出兵阿富汗的决策与过程。论据：阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入；1979年12月24日平安夜，苏联趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法强行派兵，从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营；此举招致阿拉伯国家、中国、西方盟国不满。
-论点四：苏联出兵是冷战思维与战略错判共同导致。论据：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克；阿富汗是特殊战略要地，加上苏联错判，导致大的战略性失误；同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。
-论点五：圣战者含义。论据：圣战者指狂烈激进的伊斯兰圣战思想，从上到下宗教式洗脑，导致阿富汗圣战者具备像二战日本军国主义荼毒下日本军民那样不顾一切、抱着同归于尽思想进行圣战。
-论点六：阿富汗难打的原因与游击战。论据：阿富汗90%为高原山地，是天然游击战地区；除喀布尔、坎大哈等主要城市外，大部分乡村实行部落长老制，各自为政，政府无控制力，列强及城市政府无法有力控制高原山地；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助先进单兵武器如毒刺防空火箭筒，有效压制苏联雌鹿武装直升机；坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机；苏联基层官兵厌战，士气一落千丈，1989年从上到下扛不住压力最终撤军。
-论点七：各国对阿富汗的援助。论据：阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契；中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+主讲人首先阐述阿富汗的地理位置与战略价值：地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、伊朗，被称为“亚洲的中间走廊地带”，是兵家必争之地；其国土百分之九十为高原山地，易守难攻，历史上多次获得“帝国坟场”称号。接着介绍战前背景：20世纪50年代，阿富汗同时与苏联及西方国家保持友好，实行君主立宪制，精英阶层奉行亲英与亲苏两头政策，文化上师从英国，国家建设与工业方面向苏联看齐；基辛格评价当时的国王阿明“用苏联的火柴点美国的香烟”，两边要好处。苏联因阿明不满其干涉内政、过度导向美国，担心阿富汗脱离掌控影响中亚地区，遂决定武力介入。1979年12月24日平安夜，苏联以兵变政变形式，借口阿富汗请求救援，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台。此举招致阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗抵抗组织：阿富汗和穆斯林国家出动兵源，中国和西方盟国提供武器与情报资源，支持阿富汗进行长达十年的游击战争。主讲人分析阿富汗难打的原因：百分之九十的高原山地地形适合游击战，乡村由部落长老控制，政府无法有效统治；中国曾教授地道战、地雷战等战法，美国援助了毒刺导弹等单兵武器，有效压制苏联武装直升机；苏联基层官兵普遍厌战，士气低落，最终于1989年撤军。
 # 金句总结
-「谁控制了阿富汗，谁就控制住了亚洲的咽喉。」——背景：在回答听众提问“阿富汗到底有啥好、为啥都想打它”时，主讲人以此说明阿富汗地理位置的关键性。
-「他是用的苏联的火柴在点的美国的香烟。」——背景：主讲人引述基辛格对阿明的评价，说明阿富汗当时同时从苏联和西方两边获取好处、被称为墙头草的外交状态。
-「阿富汗多次获得其帝国坟场的称号。」——背景：主讲人梳理历史上列强入侵阿富汗的结果，指出阿富汗国土纵深90%为高原山地、易守难攻，因而得名帝国坟场。
-「苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。」——背景：主讲人分析阿富汗高原山地地形使苏联坦克和步兵战车无法形成有效战斗力，加上基层官兵厌战、士气一落千丈，最终苏联于1989年撤军。
+“谁控制了阿富汗，谁就控制住了亚洲的咽喉。”——主讲人回答听众关于阿富汗战略价值的问题时指出，地理位置是列强争夺阿富汗的根本原因。
+“它是用的苏联的火柴在点的美国的香烟。”——主讲人引用基辛格对阿富汗国王阿明的评价，说明阿富汗在苏联与西方之间两头要好处、左右逢源的“墙头草”状态。
+“苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。”——主讲人总结苏联在阿富汗的困境，指出其重装部队在高原山地无法形成有效战斗力。
 # Q&amp;A 环节
-问：阿富汗到底有啥好，为啥都想打它？
+问：阿富汗到底有啥好呀？为啥都想打它？
 答：地理位置的原因，因为谁控制了阿富汗，谁就控制住了亚洲的咽喉。
 问：是不是阿富汗有石油啊？
 答：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如说是西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
-问：为什么苏联要出兵阿富汗？
-答：用当时的冷战思维来看，阿富汗当时被苏联化为苏联势力，就是苏联大家庭中的一员，根据勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，所以加上苏联这个错判，导致苏联的大的战略性失误。同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人的进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
-问：阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
-答：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式那种洗脑，然后导致了其阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民的那样一样，不顾一切的就是抱着一种同归于尽的思想进行一种圣战的方式。
+问：之前看阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
+答：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致其阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样，不顾一切地抱着同归于尽的思想进行圣战。
 问：为什么阿富汗这个位置这么难打？
-答：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。它除了以喀布尔和坎大哈那几个主要城市为首的城市地区以外，剩下大部分百分之九十的地区都是乡村部落长老制的那种制度。你到乡村，政府没有任何的控制力，都是由部落的长老控制的该部落，然后各个村落与部落各自为政，然后导致了任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。
-问：中国对阿富汗提供了哪些援助？
-答：也是给了一些枪炮，比如说像咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，也是通过这个援助的一个形式，然后我把咱们国家就是已经饱和的军工业这个产业给它稀释掉，同时也是大家为了抵抗苏联的霸权主义和西方盟国达成了一种就是秘而不宣的默契。专家派的主要就教一些兵法、地道战、地雷战这一块的，只提供军火，但是没有派人。</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t>3129/3273</t>
+答：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，各个村落与部落各自为政，导致任何列强以及阿富汗的城市政府都无法对广大高原山地地区形成有力控制。</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3129/1635</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="13.5" customHeight="1" s="9">
+    <row r="53" ht="13.5" customHeight="1" s="10">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -15273,25 +14797,25 @@
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论以闲聊方式围绕多国文学及《西游记》相关话题展开，参与发言的有发言人1、发言人2、发言人3、发言人4。核心探讨问题包括：日本文学（东野圭吾《白夜行》）的叙事手法与阴暗结局、法国文学（雨果《悲惨世界》）的抗争精神与浪漫理想主义、俄国文学（契诃夫、列夫·托尔斯泰、格罗斯曼、《古拉格群岛》《命运与生活》）对人性丑恶的揭露与批判、英国文学（狄更斯《圣诞欢歌》《雾都孤儿》《简爱》）对底层民众的描写、美国文学（马克·吐温、海明威、《了不起的盖茨比》）的现代叙事风格，以及中国文学与影视（《平凡的世界》、台湾电影《假如我是真的》）和《西游记》狮驼岭章节的讨论。讨论未形成明确结论，最后转入练习环节。
+本次会议为一场关于各国文学的闲聊，成员包括发言人1、发言人2、发言人3和发言人4。讨论从日本小说《白夜行》谈起，发言人1认为其叙事手法新颖、结局阴暗，发言人2引用《菊与刀》说明日本性格特点。随后比较了法国、俄国、英国、美国文学的特点，涉及雨果、契诃夫、托尔斯泰、马克·吐温等作家，探讨底层描写、理想主义、讽刺性等主题。发言者还延伸讨论了《西游记》狮驼岭章节的黑暗描写及其对佛教虚伪的批判，并联系西藏历史。最后因时间关系结束，未形成正式决策。
 # 发言要点
-发言人1提到《白夜行》是悬疑小说，叙事手法隐藏、每个人都有嫌疑，结局非常阴暗；认为法国文学有抗争精神，法国革命多，英国小说多写贵族生活；提到国内《平凡的世界》写底层也深刻，但受政策原因很多作品不让看；认为英国狄更斯的《圣诞欢歌》《雾都孤儿》讲底层人，贵族与穷人之间有鸿沟，穷人把希望寄托宗教或虚无；提到美国历史短、美洲大陆相对幸福，并提及《了不起的盖茨比》；提到《一九四二》讲大饥荒和战乱；提到《西游记》狮驼岭章节吓人，认为黑神话悟空没有设计那一章，因太血腥不好过审。发言人2提到《菊与刀》描绘日本人性格特点，认为《白夜行》符合日本形象；提到雨果《悲惨世界》体现浪漫的理想主义精神；提到契诃夫、列夫·托尔斯泰、格罗斯曼，认为俄国文学戏剧性更明显、更多揭露批判人性丑恶，《古拉格群岛》最早为法语版、俄语版在苏联解体后发行；提到台湾电影《假如我是真的》改编自俄国小说并结合文革真实事件，涉及知青上山下乡；提到英国土地承载不了人口膨胀，很多人移民美国；提到美国农业资源广阔、从不缺粮食、从未发生大饥荒；提到高尔基《海燕》体现被压迫后的反抗；详细讲述《西游记》狮驼岭章节，青狮、白象、大鹏三魔头吃掉全城人、尸骸遍地、人皮做地毯、头骨做装饰，距灵山约500公里，与普度众生大相径庭，认为大鹏精是唯一能遛猴子的反派。发言人3提到哈利波特、俄国文学，询问《假如我是真的》讲什么，最后提议停止讨论转入练习。发言人4提到法国只读过《悲惨世界》，英国只看了《简爱》，认为法国小说描绘底层民众多一些、英国都是贵族生活，认为俄国文学更曲折、戏剧性更明显，询问狮驼岭是什么、是否没有拍到电视剧。观点交锋点主要在于法国与俄国文学对底层民众描写的生动性比较，以及各国文学主题特点的差异。
+发言人1认为《白夜行》叙事手法新颖，结局阴暗，并指出法国文学具有抗争精神，英国文学多写贵族与穷人的鸿沟，底层人将希望寄托于宗教。发言人2引用《菊与刀》说明日本性格，认为法国文学体现浪漫理想主义，俄国文学更侧重对人性丑恶的揭露与批判，讽刺性更强，并详细解读《西游记》狮驼岭章节，批判佛教虚伪，联系西藏历史。发言人4认为法国文学比英国文学更多描绘底层民众，俄国文学戏剧性更明显。发言人3主要参与提问和附和。分歧点在于法国与俄国文学对底层民众描绘的生动性，以及各国文学特点的侧重点。
 # 共识形成
-讨论未形成明确的统一意见或解决方案，各方主要分享了对各国文学及《西游记》狮驼岭章节的个人看法与阅读体验，未进行表决或达成共识。
+小组未形成统一意见或解决方案，讨论以分享观点为主。**关键产出**为对各国文学特点的比较，包括法国文学的抗争精神与理想主义、俄国文学的讽刺性、英国文学的贵族与底层对比、美国文学的现代性，以及对《西游记》狮驼岭章节的批判性解读。
 # 未决事项与分工
-需进一步探讨的问题包括：法国和俄国文学哪一个对底层民众的描写更生动；各国文学主题特点的具体比较。后续任务分工未明确，发言人3提议停止讨论并转入练习环节，发言人2回应OK，随后进入提问环节。</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
-        <is>
-          <t>5886/1222</t>
+未提及需进一步探讨的问题或后续任务分工。</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5886/631</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="13.5" customHeight="1" s="9">
+    <row r="54" ht="13.5" customHeight="1" s="10">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -15357,27 +14881,27 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C54" s="0" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t># 全文摘要
-本次短会围绕手机图库项目整体进展、排期与潜在风险展开。产品侧同步智能分类与相册推荐改版高保真原型已出V1.5版，调整网格视图交互逻辑并为长按手势加入微动效反馈，测试反馈部分低端机上滑列表偶尔掉帧，用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。开发侧同步AI智能标签接口已跑起V2版识别模型，准确率比上一代提升约88%，因新增视频帧提取功能单次请求耗时从800毫秒涨到约1.5秒，产品侧否决异步推送、确定采用本地缓存策略，开发1下午拉分支改逻辑预计三天联调完，并讨论端侧轻量级预过滤可平均压耗时一半。云相册同步模块弱网环境下断点续传出现状态机紊乱，同步队列积压到一千张以上时部分机型OOM崩溃，开发2已加分片加载机制每次只拉五十张但会拖慢整体同步进度，后台静默同步权限审核严大概率下不了。缩略图渲染改用新图片解码库后内存占用降约30%、CPU占用上升，已在主流三款机型灰度帧率稳定60帧、低端机约50帧，批量删除照片同时触发回收站重建索引时数据库偶尔锁死、已用消息队列排队临时规避、正式修复排到下下周版本。时间轴视图测试提三个高优Bug，滑动到二十年前老照片时页面卡死三秒以上，准备加本地索引预加载。会议确定调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化；里程碑按原定计划月底封版，内测包暂定下周三发。
-## 产品侧交互迭代与用户反馈
-- 智能分类和相册推荐改版，高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势做微动效反馈；测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通，考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。
-- 隐私相册入口提上去没问题，不算大改动，需出交互方案供评审；掉帧问题得抓紧，下周进性能压测。
-## AI智能标签接口与多模态识别模型部署
-- 后端已跑起V2版识别模型，准确率比上一代提升约88%；因加视频帧提取功能，单次请求耗时从800毫秒涨到约1.5秒；产品侧认为异步推送不行，提出本地缓存策略，开发1确认可加CQLite缓存层，下午拉分支改逻辑，预计三天联调完，缓存命中率低仍需回溯；讨论端侧轻量级预过滤，过滤gif或截图后再走全量云端识别，可平均压耗时一半，需评估模型体积和端侧推理开销，可能需申请两百兆本地缓存空间；安装包加两三百兆问题不大，但首次使用下载体验做成按需加载，用现有资源下发模块约两天搞定。</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>3605/1019</t>
+会议围绕手机图库项目进展、排期与潜在风险展开。产品侧推进智能分类和相册推荐改版，高保真原型V1.5版已调整网格视图交互与长按微动效，测试反馈低端机掉帧，已与开发沟通降低预览图缩放级别；用户反馈隐私相册入口太深，决定上提至首部顶部二级菜单，产品出交互方案评审。开发侧同步多项技术优化：AI识别V2模型准确率提升88%，但单次请求耗时从800ms涨至1.5s，决定采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完；端侧预过滤方案可行，需评估模型体积和端侧推理开销。云同步弱网下状态机紊乱，队列积压超一千张时部分机型OOM崩溃，采用分片加载方案每次拉五十张，后台同步权限申请大概率下不了，进度不能拖。缩略图渲染采用新解码库，内存占用降30%，主流机型帧率稳定60帧，低端机50帧；批量删除照片时数据库锁死，临时规避方案先稳住，正式修复排进V1.2迭代。时间轴滑动到老照片卡死三秒以上，采用本地索引预加载，预加载放主线程IO池，同步放子线程后台服务，需用户授权媒体和存储权限，产品设计引导弹窗。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块；非核心UI微调往后排，资源给到管线重构和AI标签优化；开发2评估管线重构工作量，今天下班前发；开发1排联调时间，尽量周五前跑通主干流程；周四性能压测需拿达标数据。
+## 产品交互迭代与用户反馈
+- 产品侧推进智能分类和相册推荐改版，高保真原型V1.5版调整网格视图交互和长按微动效。测试反馈低端机掉帧，已与开发沟通降低预览图缩放级别。用户反馈隐私相册入口太深，决定上提至首部顶部二级菜单，产品出交互方案评审。
+- 掉帧问题需抓紧，下周进入性能压测。
+## 技术实现与性能优化
+- AI识别V2模型准确率提升88%，但单次请求耗时从800ms涨至1.5s，采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完；端侧预过滤方案可行，需评估模型体积和端侧推理开销。云同步弱网下状态机紊乱，队列积压超一千张时部分机型OOM崩溃，采用分片加载方案每次拉五十张，后台同步权限申请大概率下不了。缩略图渲染采用新解码库，内存占用降30%，主流机型帧率稳定60帧，低端机50帧；批量删除照片时数据库锁死，临时规避方案先稳住，正式修复排进V1.2迭代。时间轴滑动到老照片卡死三秒以上，采用本地索引预加载，预加载放主线程IO池，同步放子线程后台服务，需用户授权媒体和存储权限，产品设计引导弹窗。</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3605/1033</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="13.5" customHeight="1" s="9">
+    <row r="55" ht="13.5" customHeight="1" s="10">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -15457,27 +14981,27 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C55" s="0" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t># 全文摘要
-本次月度研讨会围绕上月案场数据复盘与下月去化目标展开。上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面。会议确认工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干；周末办业主答谢会，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练，每人必须参加、课后现场抽考，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房；财务和法务周六日轮流值班、在案场外围待命。下月总去化目标120套，拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。散会后半小时内，销售组长把会议纪要和任务分解表发到工作群；销冠下周晨会分享逼定案例。
-## 上月案场数据复盘与客户流失抗性分析
-- 上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。
-- 流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面；客户怕买错，需把工地实时进展、材料样板拉到面前看。
-## 下月去化目标与执行动作
-- 下月总去化目标120套，按人员配置和上月产出权重拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干，组长带销售A和销售B回访上周未成交三百多组，销冠梳理二十几个高意向客户周末逼定；周末办业主答谢会，销冠带人协助、销售B主抓流程、销售A负责邀约和逼定记录，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练（竞品对比与抗性化解、逼定时机与谈判心理学），每人必须参加、课后现场抽考、过不了加练，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房，再出问题直接问责；财务和法务周六日轮流值班、在案场外围待命；散会后半小时内，销售组长把会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例。</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>4211/1165</t>
+本次月度研讨会聚焦上月转化率下滑问题，明确量够但转化不够、卡在逼定和转化环节的结论。上月案场总到访320组，环比增15%，成交76套，转化率23%，较上月降1个百分点；渠道带看占比65%，自然来访35%，蓄客量3200组，认购到成交流失率18%。销冠复盘流失客户集中在价格预期和交付信心两个抗性，销售A反馈工地开放日频率不够、流程繁琐，报备审批要半天。会议确定多项动作：工地开放日标准化，定在每周三，提前两天在CRM系统推送给意向客户；逼定权益可视化，替换旧版物料，制作'权益可视化'台卡；渠道带看实名制与质量考核，下月起执行，扣减渠道积分；周末举办业主答谢会，销冠协助，销售B主抓流程，销售A负责邀约和逼定记录；专项培训全员参加，课后现场抽考，过不了加练；销控必须实时同步，CRM系统锁房，出问题直接问责；财务和法务周末轮流值班，在案场外围待命。下月目标总去化120套，比上月多50%，按人员配置和产出权重拆分：销冠28套，销售A、销售B和组长三人共50套，剩余12套作为机动和渠道攻坚储备。总监强调跟进节奏必须提速，客户不过夜，分片包干回访上周未成交的300多组客户；渠道带看质量大于数量，总监亲自沟通渠道部。
+## 上月数据复盘与转化率问题分析
+- 上月案场总到访320组，环比增15%，成交76套，转化率23%，较上月降1个百分点。渠道带看占比65%，自然来访35%，蓄客量3200组，认购到成交流失率18%。销冠复盘流失客户集中在价格预期和交付信心两个抗性。销售A反馈工地开放日频率不够，流程繁琐，报备审批要半天。结论为量够但转化不够，卡在逼定和转化环节，需提升自主拓客和案场拦截能力。
+- 工地开放日标准化，定在每周三，提前两天在CRM系统推送给意向客户。逼定权益可视化，替换旧版物料，制作'权益可视化'台卡。渠道带看实名制与质量考核，下月起执行，扣减渠道积分。周末举办业主答谢会，销冠协助，销售B主抓流程，销售A负责邀约和逼定记录。专项培训全员参加，课后现场抽考，过不了加练。销控必须实时同步，CRM系统锁房，出问题直接问责。财务和法务周末轮流值班，在案场外围待命。
+## 下月目标分解与专项培训
+- 集团下月目标总去化120套，比上月多50%。组长按人员配置和产出权重拆分：销冠28套，销售A、销售B和组长三人共50套，剩余12套作为机动和渠道攻坚储备。总监安排两次专项演练：'竞品对比与抗性化解'和'逼定时机与谈判心理学'，每人必须参加，课后现场抽考，过不了加练。组长安排签到和考核表，结果挂钩下周绩效系数。</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4211/1070</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="13.5" customHeight="1" s="9">
+    <row r="56" ht="13.5" customHeight="1" s="10">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>发言人 1  00:00:00
@@ -15547,23 +15071,23 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C56" s="0" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕上周ASR模型迭代进度、线上推理延迟与长音频解码卡死问题展开，A与B分别同步数据训练与推理侧现状。数据侧混合语料库清洗流水线跑完第二轮，长尾噪音、极端口音与背景人声重叠片段单独分流，有效语音时长占比从89%提升到94%左右，重新校对CTC blank token分布后发现多音字与连读场景切分点偏，本周用新基准跑消融；验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时易吞过渡音或重复解码。模型侧计划将全纯Transformer换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练，RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线与压测数据未跑完，明天下午发压力测试日志和截图。推理侧现有队列切分导致首字延迟波动在150ms到300ms之间，计划改为静态分段加流式解码组合方案，音频按2秒切块、前端VAD预过滤、后端RNN-T增量解码，首字延迟控制在80ms以内、吞吐量稳在120路并发，VAD阈值卡在-25dB并结合能量与谱熵双模型判断，下周拉线上流量回放做端到端对比。长音频卡死问题方面，线上用户输入超长连续且带方言口音音频导致解码loop卡死、解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题。组长提出三点要求：流式架构切换不能影响现有非流式离线批处理，双线都要保、测试用例覆盖全；VAD阈值由B做消融实验，误切率与漏切率画曲线找最优解；A的模型训练算力下周一开始划拨三块A100做增量训练，注意别和NLP组项目撞车、排队看调度面板错峰跑。会议明确稳定性优先、精度次之，下周先出热修复版本上灰度，专业术语后续做词表扩展和热词注入；CI/CD自动评估流水线由A负责评估脚本与流水线配置、预计三天周四前出V1版本，B配合把压测数据输出成标准JSON格式；监控面板接Prometheus和Grafana，B出监控指标定义文档明天下班前发组长转发运维负责人，告警分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。
-## 数据与模型训练进展
-- 混合语料库数据清洗流水线跑完第二轮，长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提到94%左右；重新校对CTC blank token分布，发现多音字和连读场景切分点偏，本周用新基准跑消融。验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时模型易吞过渡音或重复解码，排查为CTC对齐阶段跨语言边界和轻声尾音处理不够平滑。
-- 计划把全纯Transformer换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练；数据增强加时间偏移，对背景白噪声和混响鲁棒性差，准备引入MixUp和Cut再迭代。RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线和压测数据未跑完，明天下午发压力测试日志和截图。
-## 推理优化与线上稳定性
-- 现有队列切分导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯；计划改成静态分段加流式解码组合方案，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，首字延迟控制在80ms以内，吞吐量稳在120路并发；VAD阈值卡在-25dB，结合能量和谱熵双模型判断，下周拉线上流量回放做端到端对比。线上用户输入超长连续且带方言口音音频导致解码loop卡死，解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，日志显示RNN-T attention权重一直震荡没收敛；建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题，同时加超时熔断和降级返回。前端SDK采样率仍为16k而新模型为32k输入，前端不升级上采样会引入高频伪影影响识别率，前端对接人称排期推到下个月，32k模型在长尾词上比16k好0.5%的WER。</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
-        <is>
-          <t>3912/1826</t>
+会议围绕ASR模型迭代进度、线上推理延迟和长音频卡死问题展开，确认了流式RNN-T混合架构、2秒切分方案、VAD阈值消融、热修复版本、监控面板及CI评估流水线等多项决策，并明确了各负责人和时间节点。数据清洗流水线完成第二轮，有效语音时长占比从89%提升至94%，WER下降0.8个点；低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音被吞或重复解码。计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，在20小时核心数据上训练，数据增强引入MixUp和Cut。推理侧动态Batching导致首字延迟波动150ms-300ms，计划改为静态分段加流式解码，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，首字延迟控制在80ms以内，吞吐量120路并发；VAD阈值卡在-25dB，需平衡误切率和漏切率，计划拉线上流量回放做端到端对比。线上出现超长连续带方言口音音频导致解码器loop卡死，服务器节点重启；默认max steps 2048，超时5秒，但解码序列超阈值时未优雅降级，报OOM；RNN-T attention权重震荡不收敛；确认加early stopping机制，连续30步置信度低于0.2强制截断，下周出热修复版本上灰度。
+## ASR模型迭代与数据优化
+- 数据清洗流水线完成第二轮，有效语音时长占比从89%提升至94%，WER下降0.8个点；低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音被吞或重复解码。计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，在20小时核心数据上训练，数据增强引入MixUp和Cut。
+- 推理侧动态Batching导致首字延迟波动150ms-300ms，计划改为静态分段加流式解码，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，首字延迟控制在80ms以内，吞吐量120路并发；VAD阈值卡在-25dB，需平衡误切率和漏切率，计划拉线上流量回放做端到端对比。
+## 长音频卡死与稳定性修复
+- 线上出现超长连续带方言口音音频导致解码器loop卡死，服务器节点重启；默认max steps 2048，超时5秒，但解码序列超阈值时未优雅降级，报OOM；RNN-T attention权重震荡不收敛；确认加early stopping机制，连续30步置信度低于0.2强制截断，下周出热修复版本上灰度。</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3912/1028</t>
         </is>
       </c>
     </row>
@@ -15587,17 +15111,17 @@
           <t>准确性</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>相关性</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>通顺性</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>其它问题</t>
         </is>
@@ -15624,15 +15148,15 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D4" s="0">
+      <c r="D4" s="9">
         <f>AVERAGE(竞品对比!#REF!)</f>
         <v/>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="9">
         <f>AVERAGE(竞品对比!#REF!)</f>
         <v/>
       </c>
-      <c r="F4" s="0">
+      <c r="F4" s="9">
         <f>AVERAGE(竞品对比!#REF!)</f>
         <v/>
       </c>
@@ -15640,7 +15164,7 @@
         <f>COUNTIF(竞品对比!#REF!,-5)/COUNTIF(竞品对比!#REF!,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="9">
         <f>AVERAGE((竞品对比!#REF!+竞品对比!#REF!+竞品对比!#REF!)/3+竞品对比!#REF!)</f>
         <v/>
       </c>
@@ -15674,7 +15198,7 @@
           <t>智能识别</t>
         </is>
       </c>
-      <c r="I8" s="0">
+      <c r="I8" s="9">
         <f>COUNTIF(#REF!,“可用”)</f>
         <v/>
       </c>

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -568,23 +568,23 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表讲话，围绕多极化世界、国际秩序及热点问题阐述中方立场，提出四点主张：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅表示，多极化是历史必然并正在成为现实，中国主张推动平等有序的世界多极化，中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。王毅还就中欧关系表示，欧洲是多极世界的重要一极，中欧是伙伴而不是对手，今年是中欧建交50周年，中方愿同欧方用好这一契机，深化战略沟通和互利合作。在回答提问时，王毅就联合国与国际秩序规则、乌克兰问题、中美关系分别作出回应。
+王毅在慕尼黑安全会议发表讲话并回答提问，围绕多极化世界阐述中方立场。王毅表示，多极化是历史必然并正在成为现实，中国主张推动平等有序的世界多极化，中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。他提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅还就中欧关系表示，欧洲是多极世界的重要一极，中欧是伙伴而不是对手，今年是中欧建交50周年。在答问环节，王毅就乌克兰问题、中美关系等阐明中方立场。
 # 核心信息
-王毅提出四点主张：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，强调联合国宪章宗旨和原则是国际关系根本遵循，国家不论大小强弱都是国际法治利益攸关方，大国要带头讲诚信讲法治，摒弃言行不一、零和博弈，遵守国际法不能搞双重标准，应支持中国实现完全统一；三是践行多边主义，表示联合国是践行多边主义、推进全球治理的核心平台，应固本强基而非拆梁毁柱，中国承担超过**20%**的联合国会费，履行`巴黎协定`，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，指出保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己，应坚持开放合作，以普惠包容的经济全球化支撑平等有序的世界多极化。关键数据：去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**；中国加入了几乎所有普遍性的政府间国际组织和**600多项**国际公约；联合国成立时只有**51个**会员国，今天是**193个**国家。中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接。
+王毅提出四点主张：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，联合国宪章宗旨和原则是国际关系根本遵循，国家不论大小强弱都是国际法治利益攸关方，大国要带头讲诚信讲法治，摒弃言行不一、零和博弈，遵守国际法不能搞双重标准，应支持中国实现完全统一；三是践行多边主义，联合国是推进全球治理的核心平台，应固本强基而非拆梁毁柱，中国承担超过**20%**的联合国会费，切实履行`巴黎协定`，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己，去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**，愿推动高质量共建`一带一路`同欧盟`全球门户`战略相互对接。中欧关系方面，今年是中欧建交**50周年**，中方愿同欧方用好这一契机深化战略沟通和互利合作。
 # 官方表态
-关于多极化：王毅表示，多极化的世界既是历史的必然，也正在成为现实，中国给出的答案是应当推动平等有序的世界多极化，这是习近平主席提出的又一个重大主张。关于国际法治：王毅表示，联合国宪章宗旨和原则是处于国际关系的根本遵循，也是建设多极世界的重要基石，国家不论大小强弱都是国际法治的利益攸关方，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈，在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。关于多边主义：王毅表示，联合国是践行多边主义、推进全球治理的核心平台，对于这座大厦应该固本强基，而不是拆梁毁柱，中国坚持真正的多边主义，倡导共商共建共享的全球治理观。关于开放共赢：王毅表示，保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。关于中欧关系：王毅表示，中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手，今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。关于联合国与国际秩序规则：王毅表示，中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展，需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。关于乌克兰问题：王毅表示，中国同俄罗斯是两大邻国，有着漫长的边界，两国建立了结盟不对抗、不针对第三方的睦邻友好关系，进而建立了全面战略伙伴关系，中国同俄罗斯之间的交往是正常的国与国之间的交往；中国历来主张一切争端和冲突都应该通过对话寻求政治解决，乌克兰问题上同样如此，从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释，任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识，所有当事方包括利益攸关方都应该适时的参与到和谈的进程当中，欧洲更有必要为此发挥重要的作用。关于中美关系：王毅表示，中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢，中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底。
+关于国际秩序与规则：中国是在现行国际秩序中发展起来的，是这个秩序的受益者，要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展；需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。关于乌克兰问题：中国同俄罗斯是两大邻国，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中国同俄罗斯之间的交往是正常的国与国之间的交往；&gt; 如果中国不从俄罗斯买，哪个国家能够提供如此巨量的油气来满足中国民众的需求呢？那是不可能的，也是不保险的。中方历来主张一切争端和冲突都应该通过对话寻求政治解决，从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决；习近平主席提出的4点主张是中国立场的最权威的阐释，即各国的主权领土完整应该得到尊重，联合国的宪章应该得到遵守，各国的合理安全关切应该得到重视，一切致力于和平的努力都应该得到支持；中方派出的特使去各国斡旋，同巴西等南方国家发起了和平之友；中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识；所有当事方包括利益攸关方，都应该适时参与到和谈进程当中，欧洲更有必要为此发挥重要作用。关于中美关系：中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼；对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢；中美制度不一样是各自人民做出的选择，如果想改造或者颠覆对方是不切实际的；中美两个大国总不能冲突起来，因为那将殃及整个世界；中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系；如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，必将坚定维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决回击美方的单边和霸凌行径。
 # Q&amp;A环节
-问（发言者2）：你提到国际秩序，也提到需要尊重联合国宪章，现在有很多质疑，我们看到俄罗斯入侵乌克兰，我们看到美国总统威胁使用武力入侵格陵兰和巴拿马，以及巴勒斯坦人流离失所，你的国家也被指控违反海洋法或世界人权宣言。你现在从这里前往纽约参加安理会，你是否继续相信联合国？你是否相信联合国宪章？你是否也会为联合国改革而努力？联合国宪章在你的优先事项中排多高？ → 答（王毅）：说到秩序，这几年总有人说中国要改变秩序，中国要另起炉灶，但现在再说这种话的人可能不会太多了，因为真正要挑战秩序、在毁约退群的国家出现了；中国是在现行国际秩序中发展起来的，是这个秩序的受益者，我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展。谈到规则，我们需要共同来维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则，这应该是我们的最大的公约数。
-问（发言者2）：自2022年以来慕安会的一个话题就是俄罗斯入侵乌克兰，在俄罗斯入侵前几天你曾说过主权、独立和领土完整应该得到尊重和保障，乌克兰也不例外，你确认了联合国宪章。今天俄罗斯已成为中国的加油站，这意味着你对乌克兰有很大影响力。你是否看到现在有更多压力来结束这场战争，你能否减少俄罗斯向你国供应天然气的可能性或降低价格，或停止一些双用途物资，以便对俄罗斯施加更多压力来结束这场战争？ → 答（王毅）：中国同俄罗斯是两大邻国，有着漫长的边界，两国关系过去经历过一番曲折的经历，之后我们双方吸取教训，建立了结盟不对抗、不针对第三方的睦邻友好关系，进而增进了战略互信，建立了全面战略伙伴关系。中国同俄罗斯之间的交往是正常的国与国之间的交往。如果中国不从俄罗斯买油气，哪个国家能够提供如此巨量的油气来满足中国民众的需求呢？那是不可能的，也是不保险的。中国在对待地区热点问题上是有我们的立场的，我们历来主张一切争端和冲突都应该通过对话寻求政治解决，因为武力和制裁不可能真正和彻底的解决问题，乌克兰问题上同样如此。从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决。习近平主席提出的4点主张是中国立场的最权威的阐释。我们派出的特使去各国斡旋，我们同巴西等南方国家发起了和平之友。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识。所有当事方包括利益攸关方，都应该适时的参与到这个和谈的进程当中。这场战事发生在欧洲大地上，欧洲更有必要为此发挥重要的作用。
-问（发言者2）：我们时间不多了，但至少请你简要预览一下你认为我们和中国之间的关系将如何发展？ → 答（王毅）：中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼，这体现了作为大国的战略定力和国际信誉。我们的对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢。中国和美国制度确实不一样，这是我们各自人民做出的选择，如果想改造或者颠覆对方的话，那是不切实际的，正确的态度就是相互尊重。中美两个大国总不能冲突起来吧，因为那将殃及整个世界，所以还是要开展对话，加强交往，增进了解，建立信任。合作共赢，这是因为国际社会期待中美开展合作，全球性的挑战也需要中美携手来应对。中方已经准备好了，我们愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。我们当然希望美方能够相向而行，但是如果美方不愿意，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，我们必将坚定的维护中国的主权、中国的国家的尊严和我们的正当发展权利，必将坚决的回击美方的单边和霸凌的这种行径。</t>
+问：你是否继续相信联合国？是否相信联合国宪章？是否会为联合国及其宪章改革而努力？这在你优先事项中排多高？ → 答：王毅表示，提问涉及秩序和规则两个关键词；真正要挑战秩序、毁约退群的国家出现了，而中国是在现行国际秩序中发展起来的，是受益者，要做的就是按照大多数国家的愿望推动这个秩序朝着更加公正合理的方向发展；需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。
+问：中国是否有可能对俄施压，如削减俄对华供气、降低价格或停止部分两用物资，以推动结束战争？ → 答：王毅表示，中国同俄罗斯是两大邻国，两国关系过去经历过曲折，之后双方吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中国同俄罗斯之间的交往是正常的国与国之间的交往；如果中国不从俄罗斯买，哪个国家能够提供如此巨量的油气来满足中国民众的需求，那是不可能的，也是不保险的；中方不会允许把经贸问题政治化、当做打压中国的工具，要为人民负责任；中方历来主张一切争端和冲突都应该通过对话寻求政治解决，乌克兰问题上同样如此，从2022年2月25号起中方就提出了对话协商解决，习近平主席提出的4点主张是中国立场的最权威阐释，中方不断推进劝和促谈，派出特使去各国斡旋，同巴西等南方国家发起了和平之友；中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识，认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要发挥重要作用。
+问：请简要预览一下中美关系将如何发展？ → 答：王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉；对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢；中美制度不一样是各自人民做出的选择，如果想改造或者颠覆对方是不切实际的，正确的态度就是相互尊重；中美两个大国总不能冲突起来，因为那将殃及整个世界，所以还是要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美开展合作，全球性挑战也需要中美携手应对；中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道；如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，必将坚定维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决回击美方的单边和霸凌行径。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>7004/3331</t>
+          <t>7004/2458</t>
         </is>
       </c>
     </row>
@@ -751,32 +751,28 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次沟通为电子科学与工程学院面向考生和家长的直播介绍会，由三位老师及学生代表分别介绍学院整体情况与各研究方向，并解答夏令营相关问题。段院介绍学院历史沿革、学科布局、师生规模、科研经费与平台情况；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术和电路与系统方向；李天明教授介绍物理电子学方向；2023级博士研究生田雨桐从学生视角分享择校理由与建议。互动答疑环节，段院回复今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。
+本次沟通交流会为电子科学与工程学院面向考生和家长的直播宣讲，由三位老师及学生代表介绍学院整体情况与各研究方向，并解答夏令营相关问题。段院介绍学院历史沿革、学科布局、师资与科研数据；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术、电路与系统方向；李天明教授介绍物理电子学方向；2023级博士研究生田雨桐分享择校理由与建议。段院就夏令营安排答复：今年计划举办夏令营活动，具体时间待定，相关信息通过QQ群978499108及时发布。直播最后进行抽奖互动，口令为“一生一世，逐梦未来”，奖品为学校马克杯套装。
 # 信息同步
-**段院（学院整体情况）**：介绍学院历史沿革，1956年建校成立无线电系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科；本科生1545人，招生专业为工科试验班电子工程类，含电子科学技术、电磁场与无线技术；硕士博士研究生1975人；教师302人，教师总数269人，两院院士2人、领军人才19人、青年人才28人；近5年科研到账经费稳定在3~4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利授权1300余件；20个科研团队，年度经费过千万团队15个、过亿元团队1个；拥有2个国家级平台、4个国际合作平台、7个省部级科研平台，共建国际姊妹院系2个，主办高水平国际会议13场。
-**柳教授（电子信息材料与元器件方向）**：该方向以材料为基础、器件为核心、应用为目标导向，2021年中国集成电路电子产品进口额度达2.8万元（原文），为原有进口量1.7倍，属卡脖子问题之一，应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域；研究队伍含国家级人才10余人，两个团队——邓龙江院士电磁辐射控制材料与技术团队（研究人员19人，正高13、副高15，论文300余篇，课题130余项，年均到账经费3000多万元，授权发明专利100余项，国家科技进步或技术发明二等奖共3项）和张怀武教授磁电薄膜与微型器件团队（研究人员17人，正高15、副高2，课题100余项，科技进步二等奖共3项，SCI论文400余篇，年均到账经费2000余万元）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室；科研面积2万余平米，超精尖3000平，两条国家重大任务试验生产线，大型设备500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
-**张教授（电磁场与微波技术和电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，始于1956年由林卫干先生和谢楚芳先生创建，有6个团队，拥有中国高校最先进的微波暗室群体及微波毫米波太Hz仿真测试平台；研究成果包括杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵应用于中电14所某大型机载相控阵雷达，樊勇教授团队毫米波平面集成天线、太Hz雷达成像系统（0.22太Hz、0.34太Hz、0.42太Hz，分辨率小于1厘米）并于2023年成都大运会田径项目示范应用，李恩教授团队微波毫米波测量技术、生物医学电磁学及成像，延波教授团队微波毫米波太Hz芯片、三毫米导引头前端等；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，81年招收研究生，88年成立首批博士后流动站，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人，康凯教授团队毫米波CMOS芯片，连续三年获全国大学生集成电路创新创业大赛奖项。
-**李天明教授（物理电子学方向）**：该学科为物理学与电子科学技术交叉学科，典型如微波电子学、光电子学，特点为基础性与前沿性、学科边界不清晰；学校物理电子学起源于1956年建校时前苏联专家帮助下成立的电子控器件专业，1979年刘成刚院士带领下成立高能电子学研究所，2018年成立电子科学与工程学院；经过近70年发展，纵向向上游仿真设计数字模拟材料、下游系统应用发展，横向向毫米波到太赫兹频段及与医学交叉发展；拥有自主知识产权商用软件MMST和切皮克；团队共9个；每年到校科研经费接近2亿元，为学院最多；是世界上最大的真空器件研究中心；2023年成功举办行业内顶级会议；学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-**学生代表田雨桐（择校分享）**：2023级电子科学与技术专业博士研究生，分享选择电子学院的8个理由：城市成都（新一线城市、电子信息产业前端，英特尔华为京东方等汇聚）；电子科大为电子信息人才培育代名词；电子科学与技术学科第四轮学科评估A+全国第一；研究团队实力（所在毫米波技术与系统应用团队由樊勇老师带领，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向，团队硕博毕业生百分百就业率）；奖助体系全覆盖高额度长周期；建议先选研究团队再选导师，借助文献检索网站了解导师。
-**互动答疑**：有考生和家长询问夏令营具体时间和形式，段院回复今年计划举办夏令营活动，时间待定，感兴趣的同学可加入QQ群（群号978499108），相关信息会及时发布；直播尾声进行抽奖，口令为“一生一世，逐梦未来”，奖品为学校马克杯套装。
+**段院（学院整体情况）**：介绍学院历史沿革，1956年建校成立无线电系等，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科；本科生1545人，招生专业为工科试验班电子工程类，含电子科学技术、电磁场与无线技术；研究生1975人；教师302人，两院院士2人，领军人才19人，青年人才28人；近5年科研到账经费稳定在3~4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利1600余件；20个科研团队，年度经费过千万团队15个，过亿团队1个；拥有2个国家级平台、4个国际合作平台、7个省部级科研平台；国际交流共建姊妹院系2个，主办国际会议13场。
+**柳教授（电子信息材料与元器件方向）**：该方向以电子材料与电子器件为核心，服务电路系统与电子装备；中国集成电路电子产品2021年进口额度达2.8万元（原文），是卡脖子问题之一；应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域；元器件向微型化、片式化、集成化、薄膜化、智能化发展；研究队伍含国家级人才10余人，两个团队：邓龙江院士电磁辐射控制材料与技术团队（19人，正高13、副高15，论文300余篇，课题130余项，年均经费3000多万元，授权专利100余项，国家科技进步/技术发明二等奖3项）、张怀武教授磁电薄膜与微型器件团队（17人，正高15、副高2，课题100余项，二等奖3项，SCI论文400余篇，年均经费2000余万元）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室；科研面积2万余平米，超精尖3000平，两条国家重大任务试验生产线，大型设备500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
+**张教授（电磁场与微波技术和电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向；电磁场与微波技术始于1956年，由林卫干先生和谢楚芳先生创建；有6个团队；拥有中国高校最先进的微波暗室群体；研究成果包括杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵应用于中电14所某大型机载相控阵雷达，樊勇教授团队毫米波平面集成天线、太Hz雷达成像系统（0.22/0.34/0.42太Hz，分辨率小于1厘米）2023年成都大运会示范应用，李恩教授团队微波毫米波测量技术、生物医学电磁学，延波教授团队微波毫米波太Hz芯片等；电路与系统81年招收研究生，88年成立首批博士后流动站，国家级人才4人，教授10人，副教授22人；人才培养连续三年获全国大学生集成电路创新创业大赛奖项等。
+**李天明教授（物理电子学方向）**：是物理学与电子科学技术交叉学科，研究微波与电子相互作用（微波电子学）、光与电子相互作用（光电子学）等；起源于1956年建校时前苏联专家帮助下成立的电子控器件专业，1979年刘成刚院士带领下成立高能电子学研究所；经过近70年发展，纵向向上游仿真设计数字模拟材料、下游系统应用发展，横向向毫米波到太赫兹频段及与医学交叉发展；拥有自主知识产权商用软件MMST和切皮克；每年到校科研经费接近两个亿，是学院最多；是世界上最大的真空器件研究中心；团队共9个；学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。
+**田雨桐（学生代表）**：2023级博士研究生，分享选择电子学院的8个理由：城市成都（新一线城市、电子信息产业前端，英特尔华为京东方等汇聚）、学校是电子信息人才培育代名词、专业电子科学与技术第4轮学科评估A+全国第一、研究团队实力、奖助体系全覆盖高额度长周期等；建议先选研究团队再选导师，可借助文献检索网站如HBO E和中国知网了解导师论文和指导研究生毕业情况，提前沟通交流。
+**夏令营答疑**：有朋友询问夏令营具体时间形式；段院回答今年计划夏令营活动时间还待定，感兴趣同学可加入QQ群978499108，相关信息会及时发布；主持人念QQ群号并邀请扫码加入。
 # 达成共识
-各方确认的信息：段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍各研究方向，学生代表田雨桐分享择校理由与建议。
-达成的共识：**今年计划举办夏令营活动，时间待定，相关信息通过QQ群（978499108）及时发布。**
-段院原话：
-&gt; 我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会唉到时会及时的发布。
+各方确认的信息：段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍各研究方向，田雨桐分享择校理由与建议。
+达成的共识：**今年计划举办夏令营活动，具体时间待定，相关信息通过QQ群978499108及时发布。**
+&gt; 段院：今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会唉到时会及时的发布。
 # 待协调事项
-事项：夏令营具体时间和形式尚未确定，需后续明确并发布。
-对接人：未明确
-负责人：段院
-预计完成时间：待定，相关信息通过QQ群（978499108）及时发布。</t>
+无</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>13887/2555</t>
+          <t>13887/2280</t>
         </is>
       </c>
     </row>
@@ -1313,21 +1309,21 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会围绕2023年公司发展数据、年终奖发放标准、各部门与个人评价及颁奖抽奖展开。预期目标是通报全年经营状况并明确年终奖发放口径，实际结果是年终奖转账总额226,000元，人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27；最高工资含年终奖两三人拿到手20万多，平均到手1万多；2023年平均人工支出相对提高，平时工资提高约25万，年终奖比去年多1312万多；干满一年从去年四五人到今年12人；公司总量提升但成本往上跑，结余到账往下跑，还有百来万没收回来；老板每人比去年少拿约10万，承担亏100万风险。老板称成本控制非常差，是最大的癌症、根源问题，归因于老板关心关注不够、不够雷厉风行、出现问题没及时解决，成本控制问题明年开会时再说。年终奖发放标准为：入职两三个月或半年以内发红包，去年600、800，今年可能1000左右；满一年以一个月基本工资为基准，无大披露无大问题会更高；超过一年不过多考虑年限，看当年表现；干得久又非常满意的有高预算，实际拿到可能两三万，预算可给大几万但需给理由。部门评价方面，对短视频部门整体满意并认可，明年期待账号开始变现；对执行部门表示认可，今年项目没做砸过；商务部门从结果看基本达到预期，整个部门拿到的活约300万左右。颁奖共6人5项奖，最佳新人奖颁给红叶子和张扬，最佳进步奖颁给欧阳小元，最佳员工奖颁给游腾宇，特别贡献奖颁给李海腾。
+本次复盘会围绕2023年度经营数据、年终奖发放标准、个人与部门评价及颁奖抽奖展开。老板通报年终奖转账总额226,000元，人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27；最高工资含年终奖两三人拿到手20万多，平均到手1万多；2023年平均人工支出相对提高，平时工资提高约25万，年终奖比去年多1312万多；干满一年从去年四五人到今年12人。总量提升但成本往上跑，公司结余到账往下跑，还有百来万没收回来；老板每人比去年少拿约10万，承担亏100万风险。年终奖发放标准为：入职两三个月或半年以内发红包，去年600、800，今年可能1000左右；满一年以一个月基本工资为基准；超过一年不过多考虑年限，看当年表现。老板逐人评价并颁奖，共6人5项奖，最佳新人奖颁给红叶子、张扬，最佳进步奖颁给欧阳小元，最佳员工奖颁给游腾宇，特别贡献奖颁给李海腾。老板明确对后期有所侧重，是唯一愿意解释的一点；成本控制问题、年终奖额度问题、张扬的具体问题、徐艺玲更高的期待均明年再说。
 # 亮点事项
-短视频账号运营超出预期：视频号从3月1日700多粉涨到8万，小红书2000加涨到6.4万，抖音2000加涨到5.7万，B站3.1万涨到7.6万，6月20日外出拍摄视频后起色；直播在视频号4、5场，平均在线5000人加，前100人平均在线50分钟以上。促成成功的关键动作是郭东辉在6月20日前潘老师多次提醒其出去找工作、项目不想干了的情况下坚持不放弃，并破釜沉舟说服潘老师到外面去拍摄，加上forty到来后继续坚持；其所有内容决策均有数据支撑，晚上8:00~9:00抽一小时刷侃哥、巧克力、克瑞斯金等英语老师直播间，研究内容与互动。**最具复用价值的经验是：面对项目可能被放弃时，先说服自己坚持，再以数据支撑内容决策，并找到破壳的点逐个击破。** 个人评价方面，刘腾宇职业性专业性纪律性最好，年终奖在既定标准上再拉一档，可能翻倍；张文倩表现高出老板期待，宁波等难活也完成了；宋俊逸第一次安排活即效率不错，监狱、财经等项目未出问题；张扬基本达到期待，老板认为2023年干到最有价值的一件事就是把他招进来；张启表现高于预期，有主观能动性，主动联系客户打电话。
+短视频部门整体表现超出预期：视频号粉丝从3月1日的700多人涨到8万，小红书从2000多涨到6.4万，抖音从2000多涨到5.7万，B站从3.1万涨到7.6万，整体转变从6月20日第一条外出拍摄视频开始。账号变现课程拍到十分满分达到7.05分，直播在视频号播了4到5场，平均每场在线5000人加，前100人平均在线50分钟以上。郭东辉在6月20日前被潘老师多次提醒出去找工作的情况下坚持不放弃，破釜沉舟说服潘老师外出拍摄，并一人负责多个平台运营，同时学习课程上架、开店、开企业店等琐碎事务，所有内容决策均有数据支撑，会抽时间刷同类英语老师直播间研究内容与互动。刘腾宇职业性、专业性、纪律性最好，无之一，沟通回复专业，几乎不迟到，请假严格按规定并提前告知工作安排，宁波罗峰反馈如果不是小姑娘做得好早就投诉，林海腾聊5分钟有4分钟在夸她，年终奖在既定标准上再拉一档。张扬作为请来的人才，来半年基本达到期待，职业态度和工作能力有目共睹，老板认为2023年干到最有价值的一件事就是把他招进来。宋俊逸10月来，编导岗位，第一次安排宁波两分钟宣传片文稿就让人觉得能干这个活，效率不错，监狱或财经项目没出现任何问题，段位较高。徐武安灵光、眼里有活，警察学院驻场孤苦伶仃但反馈不错，拍摄技术水平好于后期。张启商务表现高于预期，本以为害羞反而挺外向，有主观能动性，主动联系客户打电话。
 # 不足事项
-成本控制非常差 → 根因是老板关心关注不够、不够雷厉风行、出现问题没及时解决，是最大的癌症、根源问题；若今年没有增量、成本控制又是今年状况就不开这个会。公司结余到账往下跑，还有百来万没收回来，稍微缩水；老板每人比去年少拿约10万，承担亏100万风险。郭东辉克服本不应面对的困难，公司限制其发挥，应表示歉意；6月20日前潘老师多次提醒郭东辉出去找工作，项目不想干了；账号目前没有变现，直播现在没有课程无法变现；郭东辉一人负责多个平台，精力不充沛。张文倩在法院项目上与同学沟通吃力，对方踢皮球，不知道标准怎么做。钱德峰后半年拍摄密集，两个月连轴转没有一天休息。外援成本高，公司内部可搞定的简单机位却凑不出人。后期人员加班严重，后半年基本都在加班，很少正常休息；人不够是加班最大的因素，是老板判断失误。商务给活断断续续，造成不需要招这么多人的错觉。张启项目少，老板给的支持比较少；张启自评2023年没达到自己预期，效率、时间、项目沟通和甲方做得不太好。
+成本控制非常差，是最大的问题，现象是人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27，根因是老板对一些关心或关注不够，不够雷厉风行，出现问题没有及时解决。公司结余到账往下跑，还有百来万没收回来，稍微缩水，老板每人比去年少拿约10万，承担亏100万风险。郭东辉克服本不该面对的困难，公司限制其发挥，应该表示歉意。张文倩在法院项目上沟通吃力，对方踢皮球，不知道标准怎么做。钱德峰后半年拍摄密集，两个月连轴转没有一天休息。外援成本大，有些东西公司自己人内部就可以搞定但凑不出人。后期加班严重，后半年基本都在加班，很少正常休息，人不够是加班最大的因素，是老板判断失误。李国宇沟通能力有问题且很严重。张启项目上对同事沟通和甲方做得不太好。
 # 改进计划
-成本控制问题明年开会时再说，责任人无，时间明年开会。短视频部门明年期待账号开始变现，老板会投入更大精力，责任人老板，时间明年。执行部门明年期待老板更多组织协调、减少侵占休息时间，责任人老板，时间明年。商务部门明年会给予更多支持和帮助，责任人老板，时间明年。张扬的具体问题明年再说，责任人无，时间明年。李国宇的具体问题明年再说，责任人无，时间明年。徐艺玲更高的期待明年再说，责任人无，时间明年。年终奖具体数额不公布，以发到手的为准，责任人无，时间无。</t>
+成本控制问题明年开会再说，责任人无，时间明年。年终奖额度问题明年开会再说，责任人无，时间明年。张扬的具体问题明年再说，责任人无，时间明年。徐艺玲更高的期待明年再说，责任人无，时间明年。短视频部门期待账号开始变现，老板投入更大精力，责任人无，时间明年。执行部门期待老板更多组织协调，减少侵占休息时间，责任人无，时间明年。商务部门明年给予更多支持，责任人无，时间明年。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>26.7</v>
+        <v>22.9</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>24562/1759</t>
+          <t>24562/1571</t>
         </is>
       </c>
     </row>
@@ -1870,20 +1866,20 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕小区物业服务缺失、业主大会召开与业委会成立、物业费欠费及双方拟走法律程序等矛盾进行协调。业主方称已有200来户业主接龙要求召开业主大会，业委会工作组有6个群、准业主分5个群，最早业主群已建5、6年，建议尽快召开业主大会由全体业主表决；物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主代表列举11项服务缺失问题，包括入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏且上个月进贼未获数据、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重、北边围墙用烂铁皮挡着且有缺口不安全、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员从办公室近10人减至4人、维修从5人减至2人。物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。
+本次会议围绕小区物业服务缺失、业主大会召开与业委会成立等矛盾进行协调。业主方称已有200来户业主接龙要求召开业主大会，业委会工作组有6个群、准业主分5个群，最早的业主群已建5、6年，业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系；物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主代表逐条列举11项服务缺失问题，包括入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重、北边围墙用烂铁皮挡着且有缺口不安全、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员配备严重不足。物业方逐项回应称门柱灯因能耗成本无法运营、水系属地产维修责任、监控损坏已优先维修但费用超出运营承担、绿化死亡因业委会10月成立时已入冬、北边围墙属红线以外且涉违建、民生覆盖属地产前期配套、雨水倒灌属地产设计问题、人员配备不足因地产补亏款未结账，并称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称已无调解必要、将正常推进业主大会，物业方称诉讼期间无法换物业公司，会议未达成一致。
 ## 业主大会召开与业委会成立
-- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早业主群已建5、6年。业主方建议尽快召开业主大会由全体业主表决，物业方称未接到任何通知，质疑程序合法性，并称已与集团法务沟通本月起诉。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
-- 业主代表列举11项服务缺失问题：入户庭院门柱灯从未开启；内部水系从未开启；售楼处门口迎宾水系从未开启；监控几乎全部损坏，上个月进贼未获数据；监控室24小时值班及一键直达服务自王艳芳上任后荒废；绿化死亡严重，物业管家称等明年发芽；北边围墙用烂铁皮挡着，有缺口不安全，物业承诺定制围挡未兑现；快递柜、直饮水机、宽带、暖气开户等民生附属问题无进展；雨水倒灌自2019年造成财产损失未解决；物业人员配备严重不足，办公室从近10人减至4人，维修从5人减至2人。
-## 物业方回应与经营困难
-- 物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题，属地产维修责任；监控损坏已优先维修但费用超出运营承担，并称进贼后已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建，不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套，费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业方称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称若被起诉将反诉，并称业委会成立之日自动解除物业合同关系；物业方称诉讼期间无法换物业公司。业主方表示将正常推进业主大会，物业方称本月正式起诉业委会及欠费超一年业主代表。会议未达成一致。</t>
+- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早的业主群已建5、6年；业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系。物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
+- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早的业主群已建5、6年；业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系。物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
+## 小区11项服务缺失问题及物业方回应
+- 业主代表逐条列举11项服务缺失问题：入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏（上个月进贼未从监控获得任何数据）、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重（物业管家称等明年发芽）、北边围墙用烂铁皮挡着且有缺口不安全（物业承诺定制围挡未兑现）、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员配备严重不足（办公室从近10人减至4人、维修从5人减至2人）。物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产维修责任；监控损坏已优先维修但费用超出运营承担，监控室服务称已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建、不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套、费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>21511/1505</t>
+          <t>21511/1504</t>
         </is>
       </c>
     </row>
@@ -2132,13 +2128,13 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌由主持人（多模态大模型与具身智能融合方向）主持，参与讨论的包括于洋老师的博士生雄辉（强化学习）、卢策吾老师的博士生薛寒（数据收集与柔性物体操作）、于洋老师的博士生志龙（具身模型与世界模型）以及赵浩、王岳等老师。研讨围绕具身智能的模型形态、硬件期待、世界模型定义、模仿与强化学习路线及数据scaling五个议题展开。核心痛点在于：具身智能究竟收敛为统一端到端模型还是分层形态、硬件如何支撑真机evaluation的scale up、世界模型是否需要3D inductive bias、模仿学习与强化学习如何取舍，以及真机数据与仿真数据如何配比。
+本次圆桌研讨围绕具身智能展开，由主持人介绍四位博士生背景后依次抛出模型形态、硬件、世界模型、策略学习路线与数据scaling等议题。模型形态上讨论涵盖大脑大模型、小脑大模型、端到端模型及以派零为代表收集6000多小时数据训出的端到端模型，并提出前面fix住、后面做Action refiner的设想。硬件上薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up，现有工业机械臂并非为此设计；发言者2认为具身是软硬件协同优化范式，提到松龄产品第二代、凝胶夹爪可反馈触觉、摩擦力更好。世界模型议题上赵浩从computer vision角度讨论是否需重构所有pixel和3D，志龙从强化学习角度认为world model第一要义是可交互、需能学策略。策略学习路线上派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈；数据采集上杨立新强调视角控制、标定重要，薛寒all in真机采集路线，赵浩提出2025年应推广大规模利用无标注真实数据。
 # 核心观点
-模型形态议题：主持人提出大脑大模型、小脑大模型、端到端模型等形态，并以派灵收集6000多小时数据训出端到端模型为例，询问是统一模型还是前段固定加Action refiner；王岳认为大模型直通底层会消除硬件迭代可能性，至少应分上下层，大脑不变、小脑适应肢体；发言者6认为当前大模型不是终极形态，世界模型可能更接近人脑水平，但也不是最终形态。硬件形态议题：发言者3从机械与传感器角度反问具身身体会收敛成人形还是非人形，并提到机械智能、软手抓取；薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up，现有工业机械臂并非为此设计，需要柔顺硬件结构；主持人认为具身是软硬件协同优化范式，以松龄二代和凝胶夹爪为例，认为协同进化；发言者6认为人形机器人和特种机器人将来都会存在，特斯拉花一半精力做22自由度灵巧手。世界模型议题：主持人介绍赵浩从computer vision角度评价世界模型，涉及是否需重构所有pixel和3D，并提到4D world model投稿；志龙从强化学习角度认为世界模型第一要素是可交互，回溯到Dyna Q和杨乐坤的表征与转移，当前世界模型物理规律欠缺明显；赵浩认为CV界追求重建物理世界动态，可作为RL世界模型的工具，但三维计算机视觉技术栈长，RL博士生难完全学习，并讨论inductive bias随数据规模变化；王岳以游戏跳楼例子认为世界模型可能做不到统一，policy可能是一个；发言者9提出不同物理结构可能有统一表征，讨论condition与M个模型复杂度。策略学习路线议题：主持人提出强化学习与模仿学习两大流派，派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈，语言模型有RLHF和o1思维链、MCTS；发言者10介绍公司采用模型强化加机理融合，监督学习动作空间大、数据分布不足，强化学习强依赖仿真环境、sim-to-real迁移难，需限定决策空间和任务分层；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化都不行；王岳认为pid有反馈就可作为reward，强化必然走得成；发言者11认为IL和RL没有本质冲突，只是想要一个latent状态。数据采集与scaling议题：主持人请杨立新和薛寒分享真机数据收集经验，赵浩和主持人代表仿真生成数据流派；杨立新强调视角控制和标定重要，open X等数据集相机视角不固定，且缺少物体运动信息，其团队采集刚体和关节体；薛寒all in真机采集，认为柔性体仿真需先进图形学技术如IPC、算力要求高、人才少，真机数据是更低成本方案，终极形态可能是脑机接口或可穿戴设备无感采集，互联网视频与机器人所需数据差异大；主持人提到ego4d数据清洗三个月，仿真数据加少量真机数据可显著提升成功率；赵浩认为真实还是仿真看成本，提出2025年应推广大规模利用无标注真实数据，国产仿真系统是产业问题。
+模型形态议题：讨论大脑大模型、小脑大模型、端到端模型及以派零为代表收集6000多小时数据训出的端到端模型，提出是否可前面fix住、后面做Action refiner。王岳认为若大模型直通到底会消除硬件迭代可能性，至少应分上下层，大脑不变、小脑adaptive到肢体。硬件议题：讨论具身身体会收敛成人形还是其他形态，机械领域提到机械智能、软手摩擦与顺应性；薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up；发言者2认为具身是软硬件协同优化范式，提到松龄产品第二代、凝胶夹爪可反馈触觉、摩擦力更好。世界模型议题：赵浩从computer vision角度讨论是否需重构所有pixel和3D，提到ACL上已有4D world model投稿；志龙从强化学习角度认为world model第一要义是可交互、需能学策略，当前物理规律体现欠缺；赵浩认为CV界追求重建物理世界动态，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难完全学习，并提出data bias trade off，认为数据多时需要的inductive bias变少；王岳用游戏跳楼例子认为world model可能做不到统一、policy有可能是一个，发言者9提出不同物理结构可能有统一表征，王岳认为M个独立模型更简单。策略学习路线议题：派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈；发言者10介绍公司采用模型强化加机理融合，监督学习动作空间大、数据分布不足，强化学习强依赖仿真环境、sim-to-real迁移难；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化都不行；王岳认为pid有反馈、反馈可作为reward，强化必然走得成；静波认为RL和IL没有本质冲突，只是想要一个latent状态。数据采集与scaling议题：杨立新强调视角控制、标定重要，open X数据集相机视角不固定、不关注物体，采集需记录物体运动；薛寒all in真机采集路线，认为柔性体仿真需先进图形学技术、算力要求高、人才少，真机采集成本更低，可穿戴设备是较能scale的方案，互联网视频数据与机器人所需数据很不一样；发言者2提到ego4d数据集洗了三个月，仿真数据加少量真机数据成功率显著提升，并问是否强依赖英伟达生态及国产仿真；赵浩认为用真实还是仿真数据看成本、case by case，提出2025年应推广大规模利用无标注真实数据，国产仿真系统是产业问题、有人赌卡脖子做国产替代。
 # 达成共识与解决方案
-研讨未形成正式决议，但各方在以下认知上趋于一致：**具身智能是软硬件协同优化的范式**，硬件需具备高寿命、高可靠性与柔顺结构以支撑真机evaluation的scale up；**模型形态至少应分上下层**，大脑保持稳定、小脑适应肢体与硬件变化，而非单一端到端直通底层；**世界模型与强化学习的关系上**，CV界重建物理世界动态的成果可作为RL世界模型的工具，但RL更关注可交互性与策略学习；**策略学习路线上**，复杂任务宜先模仿后强化，单独模仿或单独强化均难以覆盖，混合多种方式是目前较实际的解；**数据路线上**，真机数据与仿真数据并非相斥，仿真数据加少量真机数据可显著提升成功率，真实还是仿真应case by case看成本。
+研讨未形成正式决议，但各方在若干认知上趋于一致：**具身智能是软硬件协同优化的范式**，硬件需寿命和可靠性高以支持真机evaluation的scale up；**世界模型在CV与RL界关注点不同**，CV界追求重建物理世界动态、可作为RL中world models的工具，RL界更强调可交互与学策略；**复杂任务的策略学习宜先模仿后强化**，单独模仿或单独强化都难以收敛到专家水平；**数据采集需兼顾仿真与真机**，仿真数据加少量真机数据可显著提升成功率，真机采集需控制视角、做好标定并记录物体运动；**2025年应推广大规模利用无标注真实数据**。
 # 未决分歧与后续探索
-未决分歧包括：具身智能最终会收敛成统一端到端模型，还是前段固定加Action refiner的分层形态；具身的身体会收敛成人形机器人还是非人形形态；世界模型是否需要3D inductive bias，还是由数据规模决定；世界模型最终是一个还是多个，policy是否可能统一；模仿学习和强化学习最终路线是单独一种还是混合；未来是否强依赖英伟达生态，还是会有国产仿真产品支持。后续探索方向包括：赵浩提出2025年应推广大规模利用无标注真实数据；薛寒提出可穿戴式设备或脑机接口作为无感采集的终极形态；主持人提出仿真数据与少量真机数据结合的训练方法；国产仿真系统作为产业问题需business by business讨论。</t>
+未决分歧包括：具身智能的模型最终是端到端还是分层，尚未达成一致；具身的身体会收敛成人形还是其他形态，尚未确认；世界模型是否需要3D inductive bias，尚无定论；世界模型最终是一个还是多个、policy是否统一，存在分歧；强化学习与模仿学习最终路线如何组合，未形成统一结论；未来是否强依赖英伟达生态、是否会有国产仿真产品支持，待观察；真机数据采集如何scale up、可穿戴设备精度与遥操数据的gap如何弥补，待确认。后续行动方向包括：在仿真与真机数据配比上继续验证，探索可穿戴设备等低成本采集方案，关注国产仿真系统进展。事项跟进人：赵浩（国产仿真系统产业问题）、杨立新（真机数据采集经验）、薛寒（真机采集与可穿戴设备方案）。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
@@ -2146,7 +2142,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>21458/2146</t>
+          <t>21458/2134</t>
         </is>
       </c>
     </row>
@@ -2645,33 +2641,45 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系国家开发银行（上诉人）与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司（被上诉人）金融借款合同纠纷二审，国开行不服云南省高级人民法院2018云民初88号民事判决向本院提起上诉。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。经核对，各方出庭人员身份均符合法律规定，东源煤电、东源煤业、曲靖电力三方委托共同诉讼代理人合并发表意见，各方确认已收到诉讼文书及开庭传票。庭审围绕三个争议焦点调查辩论：抵押权与融资租赁所有权冲突及善意取得、罚息复利计算及起算日期、东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案，各方均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。
+本案系国家开发银行不服云南省高级人民法院2018云民初88号民事判决提起上诉的二审公开开庭审理，案由为金融借款合同纠纷，被上诉人为云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。庭审经核对出庭人员身份、确认诉讼文书送达及二审权利义务后，围绕抵押权与融资租赁所有权冲突及善意取得、罚息复息计算及起算日期、东源煤电东源煤业是否连带给付违约金三个争议焦点进行调查辩论。合议庭休庭评议后提出调解方案，各方当事人均表示无异议，自愿达成调解协议，法院予以确认并在庭后根据民事诉讼法第97条出具调解书。
 # 原告诉称与被告辩称
-国开行主张其抵押权完整无瑕疵，已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，尽到审慎义务构成善意取得；招银租赁主张国开行未在抵押时点查询融资租赁登记，不构成善意，东源煤电出资系无权处分，招银租赁2012年已取得设备所有权。
+见下表。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利及违约金 | 已按央行规定查询融资租赁系统且无记录，设备为通用设备无唯一标识码，已尽审慎义务；利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源煤电东源煤业应按借款合同第24条第3项支付千分之一违约金 |
-| 被上诉人东源煤电、东源煤业、曲靖电力 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意；罚息不应作为复利计算基数；不应连带给付违约金 | 招银租赁2012年已取得设备所有权，东源煤电出资系无权处分；2018年6月13日宣布提前到期未给合理期限；复利再计算复利无合同依据；国开行未举证证明违约行为且未按合同约定先行限期纠正 |
-| 被上诉人招银租赁 | 主张国开行未在抵押时点查询融资租赁登记，不构成善意 | 国开行应提供2015年12月操作抵押时点在人行征信中心的查询结果；东源煤电出资系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得设备所有权 |
+| 上诉人（原审原告）国家开发银行 | 主张抵押权完整无瑕疵、构成善意取得；请求支持罚息复利计算及违约金连带责任 | 已按央行规定查询融资租赁系统，尽到基本查询义务；抵押设备为通用设备无唯一标识码，仅能对抵押人曲靖电力公司名下融资租赁系统进行查询；2018年6月13日发函宣布贷款提前到期，罚息应自该日起算；东源煤电东源煤业构成违约应按借款合同第24条第3项支付千分之一违约金 |
+| 被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、云南东源煤业集团有限公司 | 主张国开行未尽注意义务、不构成善意；2018年6月13日宣布贷款提前到期未给合理期限；罚息不应作为复利计算基数；国开行未举证证明违约且未先行限期纠正 | 2015年12月2日邮件及东源公司融资情况统计表已告知抵押设备存在融资租赁情形且用红色标注；国开行作为专业金融机构应尽注意义务；合同约定宣布提前到期应限期偿还而非立即偿还；人民币利率管理规定第21条及合同第6条第4款均未将罚息作为复利计算基数；国开行未举证证明东源煤电违反柜台前移和账户管理且未发出纠正函件 |
+| 被上诉人招银金融租赁有限公司 | 主张国开行未在抵押时点查询融资租赁登记、不构成善意；东源煤电出资系无权处分；尊重合议庭审查结果 | 国开行提供的2018年9月查询证书不符合要求，应在2015年12月抵押时点查询；招银租赁2012年即取得租赁设备所有权，东源煤电出资给电力公司系无权处分；融资租赁登记非物权登记，仅产生对抗效力；案涉5套设备为种类物无唯一识别码故未登记 |
 # 举证与法庭调查
-**一、举证与质证**
-国开行提交2018年9月对曲靖电力公司的融资租赁查询证书、证据第54页和第58页东源煤电公司曲靖电力公司对设备权属的证明材料和股东会决议、证据第108页核查表；招银租赁提交2015年12月2日邮件及东源公司融资情况统计表、回租设备清单（证据第7页）、2013年和2015年审计报告（证据第82页、第95页）。
-**二、法官询问要点**
-合议庭就中国人民银行征信中心融资租赁登记的性质及法律后果、融资租赁登记系统查询方式、案涉5套设备是否登记唯一识别码、国开行贷款前风控是否要求保留查询记录、融资租赁司法解释第9条第2款举证责任分担、不同登记机构信息冲突如何处理等问题进行询问。
-**三、双方辩论的争议焦点**
-1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已按央行规定查询融资租赁系统且无记录、设备为通用设备无唯一标识码、构成善意取得；招银租赁主张国开行未在抵押时点查询、不构成善意、东源煤电出资系无权处分、其2012年已取得设备所有权。
-2. 罚息复利计算及起算日期：国开行主张利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源方主张2018年6月13日宣布提前到期未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
-3. 东源煤电东源煤业是否应连带给付违约金：国开行主张按借款合同第24条第3项支付千分之一违约金、东源方未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约行为且未按合同约定先行限期纠正。
+## 一、举证与质证
+- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书（第5组证据第1项），招银租赁质证认为该查询证书不符合要求，国开行应在抵押时点即2015年12月进行融资租赁登记查询。
+- 国开行提交证据第54页、58页东源煤电公司曲靖电力公司对设备权属的证明材料及股东会决议，主张抵押设备所有权属曲靖电力公司。
+- 国开行提交证据第108页核查表，主张已对曲靖电力公司名下融资租赁登记信息进行核查。
+- 招银租赁一审提交证据第7页回租设备清单，仅载明设备名称和生产厂家，未提及型号，所载出厂日期为2012年3月1日；国开行现场核实抵押设备铭牌生产日期均在2013年以后，部分为2013年11月、2013年12月、2014年3月。
+- 招银租赁一审提交2013年和2015年审计报告（证据第82页、第95页），载明曲靖电力公司注册资本4亿元且已实缴。
+- 东源方提交2015年12月2日邮件及东源公司融资情况统计表，主张已告知国开行抵押设备存在融资租赁情形，统计表中招银租赁一栏抵押设备名称与国开行抵押设备名称完全相同且用红色标注。
+## 二、法官询问要点
+- 合议庭询问各方对中国人民银行征信中心融资租赁登记的性质及法律后果的理解。
+- 合议庭询问央行融资租赁登记系统的查询方式及能否保证查询到登记结果。
+- 合议庭询问国开行贷款前风控资料内部规定是否要求查询、未查到结果是否需保留查询记录。
+- 合议庭询问招银租赁在登记系统是否登记设备唯一标识码、该标识码是否为必填项。
+- 合议庭询问违反查询通知规定在多大程度上导致融资租赁司法解释第9条第2款的法律后果，属基本查询义务还是全面审慎查询义务。
+- 合议庭询问若银行通过其他途径已知动产属融资租赁物，是否仍需查询登记系统。
+- 合议庭询问各方对融资租赁司法解释第9条第2款举证责任分担的理解。
+- 合议庭询问各方如何看待不同登记机构产生的登记信息及信息冲突时的意见建议。
+## 三、双方辩论的争议焦点
+- 争议焦点一：抵押权与融资租赁所有权冲突及善意取得。国开行主张已按央行规定查询融资租赁系统、尽到基本查询义务、构成善意取得；东源方主张2015年12月2日邮件已告知抵押设备存在融资租赁情形、国开行未尽注意义务；招银租赁主张国开行未在抵押时点查询融资租赁登记、不构成善意，且东源煤电出资系无权处分。
+- 争议焦点二：罚息复息计算及起算日期。国开行主张利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源方主张2018年6月13日宣布贷款提前到期未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
+- 争议焦点三：东源煤电、东源煤业是否应连带给付违约金。国开行主张按借款合同第24条第3项支付千分之一违约金且对方未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约且未按合同约定先行限期纠正。
 # 庭审结果
-合议庭归纳三个争议焦点：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息复利计算及起算日期；三是东源煤电东源煤业是否应连带给付违约金。合议庭提出调解方案：国开行对东源煤电债权利息罚息复利共计6474.4513万元；确认招银租赁对涉案6项设备享有所有权、对应债权数额1377.4137万元，确认国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置程序，变现价款双方各得50%、实现费用双方各担50%；未实现债权按破产重整计划预留方案实现；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；各方对一审判决第2项第4项无争议按其判项内容在调解书中确认；一审诉讼费用中国开行诉请部分按一审判决执行、招银租赁诉请部分诉讼费用由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%；本协议签订后各方就本案涉及问题不再存在任何争议。各方对调解方案均无异议，诉讼代理人依次在调解协议正式文本上签字，法院予以确认并庭后出具调解书。</t>
+本案争议焦点为三项：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息复息计算及起算日期；三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案：国开行对东源煤电债权扣除破产中已清偿本金外，利息、罚息、复利三项共计6474.4513万元；确认招银租赁对涉案6项设备享有所有权、对应债权1377.4137万元，确认国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%、实现费用双方各担50%，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置；未实现债权待执行法院出具体本裁定后按破产重整计划预留方案实现，若破产管理人不将招银租赁债权纳入预留方案则由东源煤电按此前有担保清偿方案清偿；若司法变现不能实现权益则双方放弃对案涉设备权益、由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；一审判决第2项第4项按判项确认；一审诉讼费用国开行诉请部分按一审判决执行、招银租赁诉请部分由二审法院按规定根据争议财产对应债权数额计算后由国开行承担，二审诉讼费用由法院依法确定后由国开行和东源煤电各承担50%。各方均表示无异议，自愿达成调解协议，法院予以确认，庭后根据民事诉讼法第97条出具调解书。合议庭指出本案涉及生产设备等动产抵押权与融资租赁物所有权冲突系司法实践普遍性难题，根本原因在于国家尚未建立统一动产登记制度、现有融资租赁登记系统与动产抵押登记系统缺乏有效衔接，将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>20.3</v>
+        <v>25.8</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>28485/2240</t>
+          <t>28485/2998</t>
         </is>
       </c>
     </row>
@@ -2828,76 +2836,70 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18号19号提前介入前期摸排，20号召开首次会议，分内业检查和外业检查，按建筑工程、安装工程、机电设备专业方向开展。截止今天已完成卢萨卡点除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收工作，姆皮卡点现场验收工作尚未开展；因带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。内业方面，管理组技术组基本能够按照项目合同从开工到过程中组建项目执行团队并按流程程序开展工作，受疫情及项目特殊情况影响主要人员基本能保证在前方岗位，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求，但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。外业方面，建筑部分原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准，因资料完整整理结果没出来今天不下最后结论；安装部分以钢结构为主，所有材料从国内定制发货到现场，设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。财务验收专家对本项目财务资料进行查阅并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准；不可预见费方面，检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18号19号提前介入前期摸排，20号召开首次会议，分内业检查和外业检查，按建筑工程、安装工程、机电设备专业方向开展。截止今天已完成卢萨卡点除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收工作，姆皮卡点现场验收工作尚未开展；因带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。内业方面，管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，受疫情及项目特殊情况影响主要人员基本能保证在前方岗位，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求，但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。外业建筑部分，原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准，因资料完整整理结果没出来今天不下最后结论。外业安装部分，钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准。财务验收方面，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。验收组提出人员履约、内业资料、现场实体整改及不可预见费使用等整改要求，合作局领导建议尽快补充资料、做好沟通对接，蒙泽厂区混凝土路面开裂需管理组和总包单位共同研究制定整改方案，争取在末次会之前、最迟出报告之前完成整改并形成闭环，交给外方之前继续做好成品保护。
 # 进度追踪
 各模块进展如下：
 - **卢萨卡点验收**：已完成除弹料加工调试以外的所有验收工作。
-- **蒙泽点验收**：已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程。
+- **蒙泽点验收**：已完成全部验收工作，带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。
 - **姆皮卡点验收**：现场验收工作尚未开展，内业资料已提前拿到卢萨卡点。
-- **内业资料**：管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，验收组查阅资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。
-- **建筑部分**：原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论。
-- **安装部分**：钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底。
-- **机电设备**：验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准。
-- **财务**：财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。
-- **不可预见费**：检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接。
+- **内业资料**：管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件有一个点因太远还在分散。
+- **外业建筑部分**：原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来今天不下最后结论。
+- **外业安装部分**：钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准。
+- **财务验收**：财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。
+- **不可预见费**：检查中看到本项目有动用不可预见费的情况，专家组跟施工单位做了沟通，可能在一些内容上还要进一步完善和把资料收集整理清楚，后续时间会做专门对接。
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
 | 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，并利用带料调试厂家在场资源顺带完成整个流程试生产、外方人员操作及产品生产过程 | ✅已完成 |
-| 姆皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | ⛔阻塞 |
-| 内业资料 | 管理组技术组基本按项目合同组建执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，基本评价为满足项目有关标准和规范要求；分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善 | 🔄进行中 |
-| 建筑部分 | 原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来，今天不下最后结论 | 🔄进行中 |
-| 安装部分 | 钢结构所有材料从国内定制发货到现场，施工工艺吊装精确度到现场查看外观质量满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同、参照中国标准按输出产品分三类标准专门定制编制并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，目前厂家团队、技术组和管理组驻厂专家成员在蒙泽点继续培训和交底 | 🔄进行中 |
-| 机电设备 | 验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装正确运行正常、达到国家质量检验有关标准 | ✅已完成 |
-| 财务 | 财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准 | ✅已完成 |
-| 不可预见费 | 检查中看到本项目有动用不可预见费的情况，专家组已与施工单位沟通，有关依据证据和数据还需进一步完善和收集整理清楚，后续会利用时间做专门对接 | 🔄进行中 |
+| 蒙泽点验收 | 已完成全部验收工作，带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道 | ✅已完成 |
+| 姆皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
+| 内业资料 | 管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件有一个点因太远还在分散 | 🔄进行中 |
+| 外业建筑部分 | 原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来今天不下最后结论 | 🔄进行中 |
+| 外业安装部分 | 钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准 | ✅已完成 |
+| 财务验收 | 财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准 | ✅已完成 |
+| 不可预见费 | 检查中看到本项目有动用不可预见费的情况，专家组跟施工单位做了沟通，可能在一些内容上还要进一步完善和把资料收集整理清楚，后续时间会做专门对接 | 🔄进行中 |
 # 风险预警
-整体健康度：🟡低风险。主要风险与瓶颈如下：
-- 人员履约方面，个别同志进出场时间以及护照还需施工部和管理组进一步完善，个别岗位人员因各种原因有申请更换流程，个别特种人员证件有效期可能因出国后国内延期或更新未及时到位。
-- 人员统计数量尤其是技术组对厂家服务人员可能没有计算进去，投标和合同文件对数量有要求。
-- 内业资料分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散。
-- 某厂区非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，若移交外方投入使用后再出现大面积开裂，对外影响不太好。
-- 监控管线因设备启动震动，管线接头处有脱落。
-- 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌。
-- 卢萨卡点廊墙最端头横向分布只有三个竖条，可能影响巡检和维护人员安全保障。
-- 不可预见费使用有关依据证据和数据还需进一步完善，必须做到充分无误。
-- 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方。
-- 赞比亚雨季路况不好，去姆皮卡路途遥远，交通安全风险；新冠疫情防控风险。
+整体健康度：🟡低风险。风险点如下：
+- **人员履约与合同履约资料不闭合**：个别同志进出场时间以及护照还需施工部和管理组进一步完善和提高，以期验收报告时达到闭合条件；个别岗位人员因各种原因有申请更换流程；人员统计数量尤其是技术组对厂家服务人员可能没有计算进去；个别特种人员证件在有效期上，可能出国后国内延期或更新没有及时到位。等级：中；责任人：施工部、管理组、技术组；应对计划：请执行单位跟国内人力资源对接，完善相关资料闭合。
+- **内业资料分类整理及签字规范性不足**：分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善。等级：中；责任人：技术组、管理组；应对计划：按项目执行有关标准和规范及国家有关规范及时把资料汇总到卢萨卡、分类成册、按竣工文件归档要求及时组卷。
+- **竣工文件分散**：全部集中到卢萨卡点过程中有一个点因太远还在分散。等级：中；责任人：技术组；应对计划：验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码。
+- **蒙泽厂区混凝土路面开裂**：非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，当地工人处理裂纹效果不好。等级：高；责任人：管理组、总包单位；应对计划：分析原因，结合赞比亚当地气候特点制定切实可行整改方案，管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核。
+- **监控管线接头脱落**：局部监控管线因设备启动震动、加工设备转子通过转速采集数据的管线接头处有脱落，可能引起机械故障。等级：中；责任人：施工组；应对计划：伴随设备调试全面检查，保证有效性和安全性。
+- **罗萨卡点加工提升桶位置雨水倒灌**：赞比亚雨量大风大、雨水有可能倒灌。等级：中；责任人：施工组；应对计划：检查，即便按原设计施工若不足以解决水的问题要考虑增加覆盖面积或通过技术措施解决。
+- **卢萨卡点廊墙端头竖条不足**：廊墙最端头横向分布只有三个竖条，视觉上感觉不够安全。等级：低；责任人：施工组；应对计划：建议中间再加两个竖条，为巡检和维护工作人员提供安全保障，后面再做一次检查和完善。
+- **成品保护疏忽**：工程实体完工时间较长、带料调试一直没法进行导致验收推后，成品保护可能有疏忽。等级：中；责任人：管理组、总包单位；应对计划：交给外方之前继续做好成品保护，有破损的地方及时修补。
+- **赴姆皮卡交通安全**：赞比亚雨季路况不好、去姆皮卡路途遥远。等级：高；责任人：验收组；应对计划：注意交通安全，争取安安全全平平安安回来。
+- **新冠疫情防疫**：等级：中；责任人：验收组；应对计划：注意新冠防疫。
+- **不可预见费依据证据**：有关依据证据和数据需充分无误。等级：中；责任人：验收组、施工单位；应对计划：后续时间做专门对接，放在末次汇报再进行沟通。
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 人员履约：个别同志进出场时间以及护照资料需完善，个别岗位人员有更换申请流程 | 🟡低风险 | 影响验收报告闭合条件 | 管理组、技术组 | 在形成验收报告之前完善进出场时间及护照资料，达到闭合条件 |
-| 人员统计数量尤其是技术组对厂家服务人员可能未计入 | 🟡低风险 | 投标和合同文件对数量有要求，影响履约统计 | 技术组 | 完善人员统计，将厂家服务人员等EPC项目团队人员计入 |
-| 个别特种人员证件有效期可能因出国后国内延期或更新未及时到位 | 🟡低风险 | 影响人员履约合规性 | 执行单位 | 与国内人力资源对接，确认延期或更新情况并完善 |
-| 内业资料分类整理及少量质检和管理机构验收签字规范性不足 | 🟡低风险 | 影响竣工文件组卷成册 | 执行单位、技术组 | 按项目执行有关标准和规范及国家有关规范，及时汇总卢萨卡、分类成册、按竣工文件归档要求组卷 |
-| 竣工文件全部集中到卢萨卡点过程中有一个点因太远还在分散 | 🟡低风险 | 影响资料集中归档进度 | 执行单位 | 抓紧将三个厂区资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码 |
-| 某厂区非主要通道范围内混凝土路面有少量开裂现象 | 🔴高风险 | 若移交外方投入使用后再出现大面积开裂，对外影响不太好 | 管理组、总包单位 | 共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，在末次会之前、最迟出报告之前完成整改，验收组复核形成闭环 |
-| 监控管线因设备启动震动，管线接头处有脱落 | 🟡低风险 | 影响监控有效性和安全性，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 卢萨卡点加工提升桶往上位置，赞比亚雨量大风大，雨水可能倒灌 | 🟡低风险 | 影响设备运行与成品保护 | 施工组 | 检查并考虑增加覆盖面积或通过技术措施解决 |
-| 卢萨卡点廊墙最端头横向分布只有三个竖条 | 🟢正常 | 可能影响巡检和维护人员安全保障 | 施工组 | 建议中间加两个竖条，从视觉上更安全，为巡检和维护人员提供安全保障 |
-| 不可预见费使用有关依据证据和数据还需进一步完善 | 🟡低风险 | 影响费用动用合规性与验收报告表述 | 验收组、施工单位 | 后续利用时间做专门对接，确保依据证据和数据充分无误 |
-| 工程实体完工时间较长，带料调试一直无法进行导致验收推后，成品保护有疏忽地方 | 🟡低风险 | 影响交付前成品状态 | 管理组、总包单位 | 交给外方之前继续做好成品保护，破损地方及时修补 |
-| 赞比亚雨季路况不好，去姆皮卡路途遥远 | 🟡低风险 | 交通安全风险 | 验收组 | 注意交通安全，争取安安全全平平安安完成任务 |
-| 新冠疫情防控风险 | 🟡低风险 | 影响人员健康与验收进度 | 验收组、参建单位 | 注意新冠疫情防控 |
+| 人员履约与合同履约资料不闭合 | 🟡低风险 | 个别同志进出场时间以及护照还需进一步完善，影响验收报告闭合；个别岗位人员有申请更换流程；人员统计数量尤其是技术组对厂家服务人员可能没有计算进去；个别特种人员证件在有效期上，可能出国后国内延期或更新没有及时到位 | 施工部、管理组、技术组 | 请执行单位跟国内人力资源对接，完善相关资料闭合 |
+| 内业资料分类整理及签字规范性不足 | 🟡低风险 | 分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善 | 技术组、管理组 | 按项目执行有关标准和规范及国家有关规范及时把资料汇总到卢萨卡、分类成册、按竣工文件归档要求及时组卷 |
+| 竣工文件分散 | 🟡低风险 | 全部集中到卢萨卡点过程中有一个点因太远还在分散 | 技术组 | 验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码 |
+| 蒙泽厂区混凝土路面开裂 | 🔴高风险 | 非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，当地工人处理裂纹效果不好，移交外方后若再出现大面积开裂对外影响不好 | 管理组、总包单位 | 分析原因，结合赞比亚当地气候特点制定切实可行整改方案，管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核 |
+| 监控管线接头脱落 | 🟡低风险 | 局部监控管线因设备启动震动、加工设备转子通过转速采集数据的管线接头处有脱落，可能引起机械故障 | 施工组 | 伴随设备调试全面检查，保证有效性和安全性 |
+| 罗萨卡点加工提升桶位置雨水倒灌 | 🟡低风险 | 赞比亚雨量大风大、雨水有可能倒灌 | 施工组 | 检查，即便按原设计施工若不足以解决水的问题要考虑增加覆盖面积或通过技术措施解决 |
+| 卢萨卡点廊墙端头竖条不足 | 🟢正常 | 廊墙最端头横向分布只有三个竖条，视觉上感觉不够安全 | 施工组 | 建议中间再加两个竖条，为巡检和维护工作人员提供安全保障，后面再做一次检查和完善 |
+| 成品保护疏忽 | 🟡低风险 | 工程实体完工时间较长、带料调试一直没法进行导致验收推后，成品保护可能有疏忽 | 管理组、总包单位 | 交给外方之前继续做好成品保护，有破损的地方及时修补 |
+| 赴姆皮卡交通安全 | 🔴高风险 | 赞比亚雨季路况不好、去姆皮卡路途遥远 | 验收组 | 注意交通安全，争取安安全全平平安安回来 |
+| 新冠疫情防疫 | 🟡低风险 | 疫情防控风险 | 验收组 | 注意新冠防疫 |
+| 不可预见费依据证据 | 🟡低风险 | 有关依据证据和数据需充分无误 | 验收组、施工单位 | 后续时间做专门对接，放在末次汇报再进行沟通 |
 # 后续计划
 下一周期核心交付物与关键时间节点如下：
-- **在末次会之前、最迟在出报告之前完成混凝土路面开裂整改**，由管理组和总包单位共同研究会同制定科学合理的整改方案，分析原因并结合赞比亚当地气候特点，整改完成后由验收组进行复核，在报告中形成闭环。
-- **在验收完成第一时间将三个厂区资料全部汇总于卢萨卡**，包括竣工图进行分类汇总、分类组卷及编码，由技术组按验收组专家要求及援外项目执行手册管理办法规定执行。
-- **在形成验收报告之前完善个别同志进出场时间以及护照资料**，达到闭合条件，由管理组和技术组负责。
-- **与国内人力资源对接完善个别特种人员证件有效期延期或更新问题**，由执行单位负责。
-- **全面检查监控管线接头脱落问题**，保证有效性和安全性，由施工组负责。
-- **检查卢萨卡点加工提升桶往上位置雨水倒灌问题**，考虑增加覆盖面积或通过技术措施解决。
-- **建议卢萨卡点廊墙最端头中间加两个竖条**，为巡检和维护人员提供安全保障。
-- **交给外方之前继续做好成品保护**，破损地方及时修补。
-- 会后及时安排接下来的工作情况，通过适当渠道向后方的领导汇报整个工作进展情况。
-*依赖前提：姆皮卡点现场验收工作尚未开展，需在会后安排并注意雨季路况与交通安全；不可预见费有关依据证据和数据需进一步完善，后续专门对接。*</t>
+- **三个厂区资料汇总**：技术组在验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码。
+- **现场实体整改**：严格按照方案编制要求进行逐一整改和落实。
+- **混凝土路面开裂整改**：管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核。
+- **成品保护**：交给外方之前继续做好成品保护，有破损的地方及时修补。
+- **不可预见费**：放在末次汇报再进行沟通。
+- **姆皮卡点现场验收**：会后及时安排接下来的工作，验收组即将前往姆皮卡点。
+*依赖前提：赴姆皮卡路途遥远、赞比亚雨季路况不好，需注意交通安全；同时注意新冠疫情防控。*</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>42.6</v>
+        <v>44.6</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>11110/4902</t>
+          <t>11110/5414</t>
         </is>
       </c>
     </row>
@@ -3108,21 +3110,21 @@
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-本次中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性三大宏观热点展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就反内卷与光伏、人形机器人、游戏板块进行行业更新。会议核心信息包括：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年。整体基调为：大美丽法案对信用周期中长期有利但三季度有流动性波折，美股美债波动提供再配置机会、不悲观；关税大概率是谈判技巧、市场逐渐脱敏；港股三季度流动性边际收紧、指数在23000~24000区间震荡；反内卷政策有望夯实光伏行业底部；人形机器人三季度是二季度迷茫期到商业兑现的过渡阶段；游戏板块在消费、政策和新品周期三重利好下有望在调整后再次实现戴维斯双击。
+本次会议由中金公司策略组刘刚凯文主持，为每周一度的中金宏观策略周会，围绕大美丽法案、关税谈判、港股流动性三大宏观议题展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒首席分析师张雪琴分别更新光伏反内卷、人形机器人和游戏板块。会议核心信息包括：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年（3.8~5%）。整体基调为：对美股美债不悲观，三季度有流动性波折但波动提供再配置机会，四季度美元可能小幅走强、美股可能反弹跑赢；光伏反内卷有望夯实行业底部；人形机器人三季度是从迷茫期到商业兑现的过渡阶段；游戏板块旗帜鲜明看好，认为调整后更健康可上车。
 # 核心信息
-大美丽法案三大块：第一，解决债务上限，提高约**5万亿美元**，违约风险消除；第二，延长2017年减税，新增支出**3.4万亿**、一年**3400亿**，同时减掉其他支出**1.4万**（包括减少对新能源补贴）；第三，取消899条款，避免对海外投资者持有美债利息征税。关税收入每年**3000~4000亿**可对冲支出，赤字率基本维持**5~6%**。7~9月发债约**1万亿**带来流动性抽水，2023年三季度曾发1万亿债推高美债利率从**3.8~5%**、美元走强、美股小幅下跌**4~5%**。关税四点信息：一定会做以支撑收入、需维持**10~12%**有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到**18%**，通胀年底抬升至**3.3~3.4%**但不改变路径。光伏2025年需求**650~700GW**，电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**，产业链价格跌**70~90%**；反内卷政策级别提升：2月国常会、6月29日起人民日报发声、7月1日中财委第六次会议、7月3日工信部座谈会；多晶硅期货反弹至**40元/公斤**、硅片报价涨**10%**、电池涨**2分**。人形机器人二季度A股板块跌约**9%**、跑输机械**12个百分点**，特斯拉供应商回调**30~40%**；智元机器人收购上市、宇树科技年收入破**10亿**、两家中标中国移动**1.2亿**订单。游戏6月单月版号**158个**创2018年以来新高，1~5月游戏市场规模同比增长**17%**多、手游增长**20%**，吉比特《仗剑传说》首月流水**2亿多**、巨人网络《超自然行动组》6月流水**过亿**，当前TTM PE约**30倍**、2025年静态PE约**20倍**。
+大美丽法案三大块：一是提高债务上限约**5万亿美元**，违约风险消除；二是延长2017年减税，新增支出**3.4万亿**（一年**3400亿**），同时减掉其他支出**1.4万亿**；三是取消899条款。关税收入每年**3000~4000亿**可对冲支出，赤字率基本维持**5~6%**。7~9月发债约**1万亿**带来流动性抽水，美债利率可能上行但幅度或小于2023年（**3.8~5%**），期限溢价已处**2013年以来高点**。关税有效税率约**10~12%**，极端回到**18%**，通胀年底抬升至**3.3~3.4%**但不改变路径。港股指数在**23000~24000**区间震荡。光伏主产业链四环节产能严重过剩：电池为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来价格下跌**70~90%**；硅料现金成本**38元/公斤**，头部颗粒硅**28元**、尾部**45元**；多晶硅期货反弹至**40元/公斤**，硅片报价涨**10%**，电池涨**2分**。人形机器人二季度A股板块跌约**9%**、跑输机械**12个百分点**，特斯拉供应商标签股回调**30~40%**；宇树科技年收入破**10亿**，两家同时中标中国移动近**1.2亿**订单。游戏6月单月版号发放**158个**（国产**147**、进口**11**），为**2018年以来最高**；1~5月市场规模同比增长**17%以上**、手游增长**20%**；估值TTM PE约**30倍**、2025年静态PE约**20倍**。
 # 官方表态
-刘刚凯文：&gt; 我们并不是完全的认同，去美元化这个观点的。现在这个预期基本成了一个非常拥挤的共识，而且主要是基于宏大趋势。把美元弱当成去美元化，把美元弱和美股弱直接划等号，是市场两个最大的误区。&gt; 大美丽法案对信用周期中长期有利，但三季度有流动性波折；美股美债波动提供再配置机会，不悲观。&gt; 关税大概率是谈判技巧，市场逐渐脱敏，但需关注8月1日谈判和8月12日中美谈判及转口限制。&gt; 港股三季度流动性边际收紧，指数在23000~24000区间震荡，建议低迷时介入、亢奋时锁定利润。刘佳妮：&gt; 反内卷政策有望夯实行业底部，硅料整合最迫切，头部一体化组件企业穿越周期能力较强。郭文秀：&gt; 三季度是二季度迷茫期到商业兑现的过渡阶段，建议关注华为云生态接入、头部企业出货量跨越500/1000台、电机硬件优化三类信号。张雪琴：&gt; 游戏板块在消费、政策和新品周期三重利好下，有望在调整后再次实现戴维斯双击。
+刘刚凯文：&gt; 我们并不是完全的认同，去美元化这个观点的。现在成了一个高度趋同的共识。市场两个最大的误区：把美元弱当成去美元化；把美元弱和美股弱直接划等号。&gt; 波动提供再配置的机会，我们重申我们这个观点并不悲观。&gt; 在合适的位置拿长期正确的板块。刘佳妮：&gt; 随着反内卷的力度不断的强化升级，我们相信就是价格的恶性竞争有望告一段落。&gt; 对于硅料的整合其实是最为迫切的。郭文秀：&gt; 三季度将是一个二季度的迷茫期到商业兑现过度的这样的一个小阶段。&gt; 技术创新产业需求和工厂替代，往往这三重周期共振的时候，其实是孕育着比较不错的一个投资机会的。张雪琴：&gt; 我们的态度旗帜鲜明是后者（回调一下更健康可以上车）。&gt; 在消费政策和新品周期三重利好下面，游戏行业有望在调整后再次实现戴维斯双击。
 # Q&amp;A环节
-问：大美丽法案对美股美债和美元流动性有什么影响？ → 答：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年，信用周期框架下美国下半年环比改善，四季度美元可能小幅走强、美股可能反弹跑赢。问：关税谈判最新变化及对市场影响？ → 答：关税四点信息为一定会做以支撑收入、需维持10~12%有效税率以收3000~4000亿、不能太高、市场逐渐脱敏；新变化是时间变相拖后、大部分税率相比4月2日回落、加拿大墨西哥欧盟需谈妥，极端情形有效税率回到18%，通胀年底抬升至3.3~3.4%但不改变路径，需关注8月1日谈判和8月12日中美谈判及转口限制。问：反内卷对光伏行业的影响？ → 答：光伏2025年需求650~700GW，电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍，产业链价格跌70~90%；反内卷政策级别提升，硅料环节最易切入，多晶硅期货反弹至40元/公斤、硅片报价涨10%、电池涨2分，组件跟涨意愿但受136号文电价不确定性影响。问：人形机器人三季度核心趋势和投资逻辑？ → 答：二季度A股机器人板块跌约9%、跑输机械12个百分点，特斯拉供应商回调30~40%；三季度三条主线为华为云生态开放、本土企业技术闭环、特斯拉延期带来硬件替代窗口；关注物流端场景、电机和轻量化方向。问：游戏板块最近状态及投资机会？ → 答：政策端友好度空前，6月单月版号158个创2018年以来新高，1~5月游戏市场规模同比增长17%多、手游增长20%；中型厂商新品成为核心催化，当前TTM PE约30倍、2025年静态PE约20倍，新品利润有滞后性、明年兑现，有望在调整后再次实现戴维斯双击。</t>
+问：关税威胁是否只是谈判技巧，还是真的会大幅提高？→ 答：刘刚凯文表示，关税四点信息：一定会做以支撑收入、需维持一定税率（10~12%有效税率即可收3000~4000亿）、不能太高否则通胀受不了、市场逐渐脱敏；姑且把它认作还是一个所谓的谈判技巧。问：加拿大墨西哥欧盟能否谈妥稳住？→ 答：刘刚凯文表示，加拿大墨西哥欧盟贸易占比太高，一定要和他们谈妥稳住，其他的这些国家即便增加一倍都不影响它的有效税率。问：8月12日中美谈判及转口限制进展如何？→ 答：刘刚凯文表示，需要关注8月12号中美谈判进一步的进展，尤其是一些转口的限制；越南的转口限制是40%，我们比这个税率还要低。问：光伏反内卷具体干预措施尚未披露，细节待明确？→ 答：刘佳妮表示，目前我们并没有看到一个干预措施的一个具体的披露，政府近期对于这个光伏行业的接连的发生，说明了光伏产业对于作为一个国家重要的名片的一个重要性。问：组件价格能否跟涨传导，下游电站能否接受产业链价格上涨？→ 答：刘佳妮表示，组件价格也有跟涨的一个意愿，但下游电站受136号文新能源全面入市政策影响，电价未来不确定性大幅增加，能否接受产业链价格上涨的传导还需观望未来一段时间的招标情况。问：特斯拉Optimus硬件问题何时解决，供应商筛选结果如何？→ 答：郭文秀表示，特斯拉由于存在非常多的硬件问题，包括电机的过热、灵巧手的负载不足、还有一些续航问题，目前整体特斯拉是在变更他的方案，包括他的目前的供应商从供应商的一个层面上还是在去进行筛选。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>22868/2459</t>
+          <t>22868/2070</t>
         </is>
       </c>
     </row>
@@ -3437,37 +3439,31 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课程为以「梦想」为主题的班会课，教师先提问班会主题名称并邀请同学分享梦想，有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手，教师提到有同学想当歌手并让其上来唱了两首歌，鼓励自愿为原则在结束前再唱一首。教师随后分享自己的梦想是成为受学生喜爱、有名望的优秀人民教师，并讲述自己曾想考中国美术学院、单考通过但因离家远和没钱未去，最终去了广东技术师范大学（原民族学院，后改名广师大），自己是定向生、免学费、需回龙川县教书，当时哭了三天但后来越来越喜爱教师行业。教师播放航模少年和想成为歌手的普通人的视频，组织4个大组作为梦想观察团讨论实现梦想需要的条件，并以马云中考考两次、高考多次、现成为中国首富为例说明坚持的重要。最后教师请同学们写下自己的梦想清单并分组分享，收齐每个同学的梦想。
+本次班会课以「梦想」为主题，教师先请学生分享梦想，有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手等，并让想当歌手的同学上台唱了两首歌，约定结束时可自愿再唱一首。教师随后分享自己的梦想是成为受学生喜爱、有名望的优秀人民教师，并讲述曾单考通过中国美术学院却因离家远和没钱未去，最终就读广东技术师范大学（原民族学院），作为定向生免学费、定向回龙川县教书，当时哭了三天但现在很开心；大学梦想包括加入学生会、参加各类比赛、保持专业排名第一（专业41人）、考教师资格证、保研等，并说明定向不能考研、只能在职考研且学费自交。教师组织4个大组作为梦想观察团，观察玩航模的小伙子和想成为歌手的普通人两个对象，播放视频后总结航模小伙通过努力走上更大舞台、普通人唱歌走调可通过后天学习调整，讨论得出实现梦想的条件包括坚持、努力、天赋只占1%、勇敢、机会、兴趣、能力、学习等，并小结学习、坚持、行动是梦想条件必不可少的三个。教师又以马云中考考两次、高考多次为例说明起点高低不重要、看能否坚持，提到马云新梦想是希望未来15年世界因他们而改变、享受改变他人的乐趣，并讨论梦想可以一步步立高，如考不进年级前50可先调整为前百再定前50，强调每个人的梦想都是独一无二、不可复制的。最后教师让学生拿出纸写下自己的梦想清单，可列第1、第2、第3个，实现后打勾，并思考实现梦想需要的时间和收获，随后分享部分同学的梦想，建议梦想写得实在、诚恳一点，可先定小目标再定大目标，量力而行并调整，并请各小组第1个同学收齐每位同学的梦想。
 # 核心知识点梳理
-**丑小鸭的梦想**：想变成白天鹅。
-**教师的梦想**：成为受学生喜爱、有名望的优秀人民教师；此前愿望清单包括考中国美术学院（单考通过，因离家远和没钱未去）、加入学生会、参加各种比赛、保持专业排名第一（专业41人）、考教师资格证。
-**定向生**：免学费，需回龙川县教书；定向不能考研，只能在职考研，且学费自交。
-**实现梦想的条件**：学生提到坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结 `学习`、`坚持`、`行动` 是梦想必不可少的三个条件，机会留给有准备的人。
-**马云案例**：中考考两次才考上高中，高考多次，现成为中国首富，说明起点高低不重要、坚持才重要；马云的新梦想是希望未来15年世界因他们而改变，享受改变他人的乐趣。
-**梦想的调整**：梦想可以一步步立高，如先考进年级前百再定前50，实现不了可以调整。
-⭐ 难点：理解定向生不能考研、只能在职考研且学费自交的限制；理解梦想可以调整、一步步立高。
-*易混点*：定向生与普通师范生的区别；梦想实现不了与放弃梦想的区别。
+**梦想的含义与价值**：以丑小鸭想变成白天鹅引入，说明梦想值得尊重，不被嘲笑的梦想才是梦想，每个人的梦想都是独一无二、不可复制的。
+**实现梦想的条件**：通过梦想观察团游戏，观察玩航模的小伙子与想成为歌手的普通人两个案例，得出条件包括**坚持、努力、勇敢、机会、兴趣、能力、学习**；其中天赋只占1%；⭐ 难点在于理解「机会永远都是留给有准备的人」，以及缺少某一条件梦想仍可能实现、条件齐备则实现更快。
+**梦想条件必不可少的三个**：`学习`、`坚持`、`行动`。
+**梦想的调整与阶梯**：梦想可以一步步立高，如考不进年级前50可先调整为前百，再定前50；要量力而行并适时调整。
+**案例**：航模小伙何聪发带着歼10模型表演，想让顶级选手看到进步、在明年世界锦标赛上再一比高下；马云中考考两次、高考多次，起点高低不重要，看能否坚持，其新梦想是希望未来15年世界因他们而改变，享受改变他人的乐趣。
 # 课堂互动与答疑
-问：班会主题叫什么？→ 答：梦想。
-问：同学们有什么梦想？→ 答：有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手。
-问：老师的梦想是什么？→ 答：成为受学生喜爱、有名望的优秀人民教师。
-问：实现梦想需要具备哪些条件？→ 答：坚持、努力、天赋、勇敢、机会、兴趣、能力、学习等；教师总结学习、坚持、行动是必不可少的三个条件。
-问：如果缺少一个条件，梦想还会实现吗？→ 答：具备某一个条件梦想都有可能实现，都具备则会更快实现。
-问：马云的新梦想是什么？→ 答：希望未来15年世界因他们而改变，享受改变他人的乐趣。
+问：实现梦想需要具备哪些条件？ → 答：坚持、努力、勇敢、机会、兴趣、能力、学习等，其中天赋只占1%，机会永远留给有准备的人。
+问：如果缺少了一个条件，梦想还会实现吗？ → 答：具备某一个条件梦想都有可能实现，若条件都具备则会更加快速地实现梦想。
+问：考不进年级前50怎么办？ → 答：可先把梦想调整为考进年级前百，考进后再定前50，一步步往前。
+问：马云的梦想是不可复制的吗？ → 答：每个人的梦想都是不可以复制的，都是独一无二的。
 &gt; 不被嘲笑的梦想就是梦想。
+&gt; 梦想还是要有的，万一实现了呢？
 &gt; 机会都是留给有准备的人。
-&gt; 梦想还是要有的，万一实现了呢？
-&gt; 每一个梦想都是值得我们尊重的。
 # 课后任务与学习建议
-教师请同学们拿出纸写下自己的梦想清单，可列第1个、第2个、第3个，实现之后可以打勾，并思考实现梦想需要的时间和收获。写完后各小组第1个同学分享梦想，教师收齐每个同学的梦想。教师强调写梦想要实在一点、诚恳一点，梦想可以制定多个，先定小目标再定大目标，实现不了可以调整。复习重点为实现梦想的条件（学习、坚持、行动）及梦想可以一步步立高、可以调整。</t>
+教师布置：请同学们拿出纸写下自己的梦想清单，可列第1个、第2个、第3个，实现后给清单打勾，并思考实现梦想需要的时间和实现后收获了什么。写完后每个小组的第1个同学收齐每位同学的梦想。教师建议梦想写得实在一点、诚恳一点，可先定小目标再定大目标，量力而行并适时调整。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>19</v>
+        <v>15.1</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>9362/1348</t>
+          <t>9362/1500</t>
         </is>
       </c>
     </row>
@@ -3642,20 +3638,20 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次内容为新闻联播式综合报道，涵盖新思想引领新时代改革开放的文化建设、赵乐际对俄罗斯正式友好访问并出席中俄议会合作委员会第九次会议、夏粮产量创历史新高、6月国家铁路货运指标增长、上半年快递业发展提速、油气管网建设提速、渝川皖等地应对降雨天气，以及国内国际联播快讯等议题。文化建设方面，报道围绕文化兴国运兴、文化强民族强展开，强调党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展，坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议；今年是中俄建交75周年，双方表示从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障，沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政，访问期间赵乐际向俄无名烈士墓敬献花圈。经济民生方面，今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加主因，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金，小麦质量为近年来最好水平；6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，化肥农药运量增幅最大，同比增长26.2%，中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%；上半年我国快递业务量超800亿件，快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线，每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件；油气管网建设提速，预计全年新增管道里程超4000公里，西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米，目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米，按照规划到2025年初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”天然气干线管网。防汛方面，7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区内涝、滑坡，消防救援人员紧急出动转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来洪峰流量45000立方米每秒量级洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群减小三峡水库入库洪峰流量。国内联播快讯方面，北京上半年计划新开工的320个市区重大项目全部实现开工，总投资超过4000亿元；燕矶长江大桥北岸主塔封顶，下一步转入主缆施工阶段，大桥连接湖北鄂州和黄冈，主跨1860米；第二十三届环青海湖国际公路自行车赛在海北州门源县收官，22支车队154名运动员决出5个奖项冠军；内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底；“中非儿童手拉手”活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。国际联播快讯方面，美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，枪击造成一名观众死亡、两名观众重伤，枪手被特勤局狙击手打死，动机有待查明；以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明谴责；以军袭击黎巴嫩多个边境村镇，黎真主党武装称打击以军集结地；叙利亚大马士革卡夫苏萨地区等遭空袭，造成1名政府军士兵死亡、3人受伤；俄称打击乌军列车点，乌称击退俄军进攻；加拿大东北部林火蔓延，拉布拉多城9600人被疏散，加拿大正在应对500多起活跃林火，其中超400起处于失控状态。
-## 新思想引领新时代改革开放：以文化自信筑牢强国复兴精神之基
-- 报道围绕文化兴国运兴、文化强民族强展开，强调没有高度文化自信就没有中华民族伟大复兴；党的十八大以来在“五位一体”总体布局中对文化建设作战略部署，纵深推进文化体制改革。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革。
-- 习近平总书记就弘扬和发展中华文化提出一系列重要论述，在孔子故里翻看《孔子家语通解》《论语诠解》，在岳麓书院凝望“实事求是”匾额，在三苏祠强调从中华优秀传统文化中汲取治国理政的理念和思维，在武夷山朱熹园提出以时代精神激活中华优秀传统文化的生命力。从深入实施中华文明探源工程到高标准推进国家文化公园建设，从中国共产党历史展览馆、国家版本馆等文化地标落成到《复兴文库》、“中国历代绘画大系”出版，中华优秀传统文化与革命文化、社会主义先进文化融会贯通。深化国有文艺院团改革、树立以人民为中心的创作导向，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
-## 赵乐际对俄罗斯进行正式友好访问并出席中俄议会合作委员会第九次会议
-- 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科的邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。赵乐际向普京转达了习近平主席的亲切问候和良好祝愿，指出今年是中俄建交75周年，中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献。普京请赵乐际转达对习近平主席的亲切问候，表示俄中立法机构始终保持高水平合作。与马特维延科、沃洛金分别会谈时，赵乐际表示要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持，两国立法机构要立足职能职责，用好中俄议会合作委员会、双边友好小组等机制和平台，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障。马特维延科表示发展对华关系得到俄社会的广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，指出两国立法机构要密切战略协作，服务中俄关系发展大局；交流治国理政经验，助力各自国家发展振兴；发挥立法机构职能作用，以法治方式促进务实合作；传承弘扬传统友谊，不断夯实国家关系的社会和民意基础；加强多边协作，从立法机构层面团结壮大“全球南方”力量。访问期间，赵乐际在莫斯科向俄无名烈士墓敬献了花圈。</t>
+本次报道围绕新思想引领新时代改革开放，重点阐述以文化自信筑牢强国复兴精神之基：党的十八大以来，习近平总书记以文化自觉与历史担当推进文化建设，在“五位一体”总体布局中对文化建设作战略部署，在全面深化改革中纵深推进文化体制改革；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展；坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革，深化国有文艺院团改革，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。报道同时汇总多领域运行情况：全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议；今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，夏粮单产每亩375.2公斤，其中小麦单产399.1公斤、比2023年增加10公斤；6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；上半年我国快递业务量超800亿件，截至6月30日已达800亿件；今年以来我国油气管网预计全年新增管道里程超4000公里，目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米、增幅达48%。防汛与国内国际动态方面：7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来一次洪峰流量45000立方米每秒量级的洪水过程。国内快讯包括北京上半年计划新开工的320个市区重大项目已全部实现开工、总投资超过4000亿元，燕矶长江大桥北岸主塔封顶、下一步转入主缆施工阶段，第二十三届环青海湖国际公路自行车赛在海北州门源县收官，“中非儿童手拉手”活动在中国儿童中心启动；国际快讯包括美联邦调查局称前总统特朗普在宾夕法尼亚州巴特勒市竞选集会遭未遂刺杀、枪手被特勤局狙击手打死、具体作案动机有待查明，以军空袭加沙地带南部汗尤尼斯马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明谴责，加拿大东北部纽芬兰与拉布拉多省林火蔓延、拉布拉多城9600人被疏散。
+## 文化建设与中俄议会合作
+- 围绕文化兴国运兴、文化强民族强，阐述党的十八大以来习近平总书记以文化自觉与历史担当推进文化建设，在“五位一体”总体布局中对文化建设作战略部署，在全面深化改革中纵深推进文化体制改革；提及“文博热”“文创风”“国潮”及14亿多中国人文化自信增强；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展；坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革，深化国有文艺院团改革，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。
+- 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议；赵乐际转达习近平主席问候，指出今年是中俄建交75周年，中国全国人大愿同俄罗斯联邦会议从立法机构层面落实两国元首重要共识；普京请赵乐际转达对习近平主席的问候，表示俄中立法机构保持高水平合作；马特维延科表示发展对华关系得到俄社会广泛认同和支持，沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政；10日赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作等；访问期间赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+## 经济民生运行与防汛动态
+- 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤，单产恢复性增长是夏粮产量增加的主要原因；中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金；小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；化肥农药运量增幅最大，同比增长26.2%，煤炭日均装车量、集装箱、商品汽车、冷链货物发送量等均创历史同期新高；6月份中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件；快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件。今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米；目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米；按照规划，到2025年天然气“全国一张网”将更加完善，初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众；强降雨导致安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来一次洪峰流量45000立方米每秒量级的洪水过程，水利部今天联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>7755/3290</t>
+          <t>7755/2993</t>
         </is>
       </c>
     </row>

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -15269,21 +15269,21 @@
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论以闲聊方式围绕多国文学及《西游记》相关话题展开，参与发言的有发言人1、发言人2、发言人3、发言人4。核心探讨问题包括：日本文学（东野圭吾《白夜行》）的叙事手法与阴暗结局、法国文学（雨果《悲惨世界》）的抗争精神与浪漫理想主义、俄国文学（契诃夫、列夫·托尔斯泰、格罗斯曼、《古拉格群岛》《命运与生活》）对人性丑恶的揭露与批判、英国文学（狄更斯《圣诞欢歌》《雾都孤儿》《简爱》）对底层民众的描写、美国文学（马克·吐温、海明威、《了不起的盖茨比》）的现代叙事风格，以及中国文学与影视（《平凡的世界》、台湾电影《假如我是真的》）和《西游记》狮驼岭章节的讨论。讨论未形成明确结论，最后转入练习环节。
+本次讨论以闲聊方式展开，成员围绕日本文学、各国文学比较及《西游记》狮驼岭章节进行交流。发言人2从东野圭吾《白夜行》谈起，认为其结局阴暗、符合日本形象，并提及《菊与刀》对日本人性格的描绘；随后引导比较法国、英国、俄国、美国文学及底层书写。发言人1、发言人3、发言人4分别参与讨论，涉及雨果《悲惨世界》、狄更斯作品、契诃夫与托尔斯泰、马克·吐温与海明威等。讨论还延伸至国内《平凡的世界》、台湾电影《假如我是真的》及《西游记》狮驼岭与佛教批判，最后被发言人3叫停转入练习。
 # 发言要点
-发言人1提到《白夜行》是悬疑小说，叙事手法隐藏、每个人都有嫌疑，结局非常阴暗；认为法国文学有抗争精神，法国革命多，英国小说多写贵族生活；提到国内《平凡的世界》写底层也深刻，但受政策原因很多作品不让看；认为英国狄更斯的《圣诞欢歌》《雾都孤儿》讲底层人，贵族与穷人之间有鸿沟，穷人把希望寄托宗教或虚无；提到美国历史短、美洲大陆相对幸福，并提及《了不起的盖茨比》；提到《一九四二》讲大饥荒和战乱；提到《西游记》狮驼岭章节吓人，认为黑神话悟空没有设计那一章，因太血腥不好过审。发言人2提到《菊与刀》描绘日本人性格特点，认为《白夜行》符合日本形象；提到雨果《悲惨世界》体现浪漫的理想主义精神；提到契诃夫、列夫·托尔斯泰、格罗斯曼，认为俄国文学戏剧性更明显、更多揭露批判人性丑恶，《古拉格群岛》最早为法语版、俄语版在苏联解体后发行；提到台湾电影《假如我是真的》改编自俄国小说并结合文革真实事件，涉及知青上山下乡；提到英国土地承载不了人口膨胀，很多人移民美国；提到美国农业资源广阔、从不缺粮食、从未发生大饥荒；提到高尔基《海燕》体现被压迫后的反抗；详细讲述《西游记》狮驼岭章节，青狮、白象、大鹏三魔头吃掉全城人、尸骸遍地、人皮做地毯、头骨做装饰，距灵山约500公里，与普度众生大相径庭，认为大鹏精是唯一能遛猴子的反派。发言人3提到哈利波特、俄国文学，询问《假如我是真的》讲什么，最后提议停止讨论转入练习。发言人4提到法国只读过《悲惨世界》，英国只看了《简爱》，认为法国小说描绘底层民众多一些、英国都是贵族生活，认为俄国文学更曲折、戏剧性更明显，询问狮驼岭是什么、是否没有拍到电视剧。观点交锋点主要在于法国与俄国文学对底层民众描写的生动性比较，以及各国文学主题特点的差异。
+发言人2主张《白夜行》结局阴暗、符合日本形象，并引《菊与刀》说明日本人性格；认为法国文学体现浪漫理想主义与抗争精神，俄国文学更侧重对人性丑恶的揭露与讽刺批判，美国文学历史短、叙事风格不同于欧洲，北美大平原因农业资源广阔而从未发生饥荒；还提及格罗斯曼《命运与生活》、《古拉格群岛》最早为法语版、俄语版待苏联解体后发行，以及台湾电影《假如我是真的》改编自果戈里《钦差大臣》并结合知青上山下乡与文革真实事件。发言人1认为《白夜行》叙事手法新颖、结局阴暗，法国有抗争精神，英国狄更斯作品写贵族与穷人鸿沟、底层将希望寄托于宗教或虚无之物，国内《平凡的世界》等底层作品因政策原因很多不让看，并提及《一九四二》讲大饥荒与战乱。发言人4认为法国小说描绘底层民众较多、英国多写贵族生活，俄国作品戏剧性更明显，只读过《简爱》。发言人3参与提问与附和，提及哈利波特、俄国契诃夫等。分歧点在于各国文学底层书写谁更生动、法国与俄国文学特点比较。
 # 共识形成
-讨论未形成明确的统一意见或解决方案，各方主要分享了对各国文学及《西游记》狮驼岭章节的个人看法与阅读体验，未进行表决或达成共识。
+小组未形成正式决议或统一意见，讨论以交流观点为主。主要共识性认识包括：**《白夜行》结局阴暗、符合日本形象**；**法国文学体现浪漫理想主义与抗争精神，描绘底层民众较多**；**俄国文学更侧重对人性丑恶的揭露与讽刺批判**；**美国历史较短、叙事风格不同于欧洲，北美大平原因农业资源广阔而从未发生饥荒**；**《西游记》狮驼岭章节中青狮、白象、大鹏三魔吃尽一国之人、距灵山约500公里，与普度众生大相径庭，吴承恩批判佛教被上层用于奴役底层**；**大鹏精是唯一能打败孙悟空的反派**。
 # 未决事项与分工
-需进一步探讨的问题包括：法国和俄国文学哪一个对底层民众的描写更生动；各国文学主题特点的具体比较。后续任务分工未明确，发言人3提议停止讨论并转入练习环节，发言人2回应OK，随后进入提问环节。</t>
+需进一步探讨的问题包括：各国文学底层书写谁更生动、法国与俄国文学特点比较等未形成结论。后续任务分工未明确，讨论被发言人3叫停后转入练习。</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>5886/1222</t>
+          <t>5886/992</t>
         </is>
       </c>
     </row>
@@ -15356,20 +15356,20 @@
       <c r="C54" s="0" t="inlineStr">
         <is>
           <t># 全文摘要
-本次短会围绕手机图库项目整体进展、排期与潜在风险展开。产品侧同步智能分类与相册推荐改版高保真原型已出V1.5版，调整网格视图交互逻辑并为长按手势加入微动效反馈，测试反馈部分低端机上滑列表偶尔掉帧，用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。开发侧同步AI智能标签接口已跑起V2版识别模型，准确率比上一代提升约88%，因新增视频帧提取功能单次请求耗时从800毫秒涨到约1.5秒，产品侧否决异步推送、确定采用本地缓存策略，开发1下午拉分支改逻辑预计三天联调完，并讨论端侧轻量级预过滤可平均压耗时一半。云相册同步模块弱网环境下断点续传出现状态机紊乱，同步队列积压到一千张以上时部分机型OOM崩溃，开发2已加分片加载机制每次只拉五十张但会拖慢整体同步进度，后台静默同步权限审核严大概率下不了。缩略图渲染改用新图片解码库后内存占用降约30%、CPU占用上升，已在主流三款机型灰度帧率稳定60帧、低端机约50帧，批量删除照片同时触发回收站重建索引时数据库偶尔锁死、已用消息队列排队临时规避、正式修复排到下下周版本。时间轴视图测试提三个高优Bug，滑动到二十年前老照片时页面卡死三秒以上，准备加本地索引预加载。会议确定调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化；里程碑按原定计划月底封版，内测包暂定下周三发。
+本次短会围绕手机图库项目整体进展、排期与风险展开。产品侧同步智能分类与相册推荐改版高保真原型已出V1.5版，调整了网格视图交互逻辑并对长按手势做微动效反馈，测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。开发侧同步后端V2版识别模型已跑起来，准确率比上一代提升约88%，但因加视频帧提取功能单次请求耗时从八百毫秒涨到约一点五秒；云相册同步断点续传在弱网下状态机紊乱，同步队列积压到一千张以上时部分机型OOM崩溃（尤其iOS），已加分片加载每次只拉五十张；缩略图渲染换新解码库后内存占用降约百分之三十、CPU占用上升，主流三款机型灰度帧率稳定六十帧、低端机约五十帧。会议明确异步推送不做，采用本地CQLite缓存层方案，端侧加轻量级预过滤过滤gif或截图后再走全量云端识别、平均耗时压一半，首次使用下载做成按需加载；后台同步权限审核严大概率下不了，先按分片加载方案走但进度不能拖；批量删除照片数据库锁死的临时规避先稳住、正式修复排进V1.2迭代；时间轴预加载改动可以、注意别跟云同步模块抢资源；AI修图本次不硬塞，PRD先写接口逻辑和UI占位、开发侧做插件化架构预留，非核心UI微调往后排、资源给到管线重构和AI标签优化。排期方面，里程碑按原定计划月底封版，内测包暂定下周三发并拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表、开发两位准备日志抓取工作；周四性能评审要求拿达标数据，性能报告iOS和安卓对比数据分开列、测试组合并成一份总览，产品经理下午两点参加UI走查并要求提前发稿。
 ## 产品侧交互迭代与用户反馈
-- 智能分类和相册推荐改版，高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势做微动效反馈；测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通，考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。
-- 隐私相册入口提上去没问题，不算大改动，需出交互方案供评审；掉帧问题得抓紧，下周进性能压测。
+- 智能分类和相册推荐改版，高保真原型出V1.5版，调整网格视图交互逻辑，长按手势做微动效反馈；测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通，考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单，产品经理评估范围变更。
+- 隐私相册入口提上去没问题，不算大改动，产品出交互方案由产品经理评审；掉帧问题得抓紧，下周要进性能压测。
 ## AI智能标签接口与多模态识别模型部署
-- 后端已跑起V2版识别模型，准确率比上一代提升约88%；因加视频帧提取功能，单次请求耗时从800毫秒涨到约1.5秒；产品侧认为异步推送不行，提出本地缓存策略，开发1确认可加CQLite缓存层，下午拉分支改逻辑，预计三天联调完，缓存命中率低仍需回溯；讨论端侧轻量级预过滤，过滤gif或截图后再走全量云端识别，可平均压耗时一半，需评估模型体积和端侧推理开销，可能需申请两百兆本地缓存空间；安装包加两三百兆问题不大，但首次使用下载体验做成按需加载，用现有资源下发模块约两天搞定。</t>
+- 后端已把V2版识别模型跑起来，准确率比上一代提升约88%；因加视频帧提取功能，单次请求耗时从八百毫秒涨到约一点五秒；产品侧认为异步推送不行，用户点开相册没实时结果会觉得卡死，提出先做本地缓存策略，开发1认为可行，本地加CQLite缓存层，下午拉分支改逻辑，预计三天联调完，缓存命中率低仍需回溯；产品经理提出端侧轻量级预过滤，过滤gif或截图后再走全量云端识别，平均耗时压一半；端侧跑可能需再申请两百兆本地缓存空间，产品评估安装包体积影响，安装包加两三百兆问题不大，但首次使用下载体验做成按需加载，开发1认为按需下载没问题，用现有资源下发模块，大概两天搞定。</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>3605/1019</t>
+          <t>3605/1201</t>
         </is>
       </c>
     </row>

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="390" windowWidth="21600" windowHeight="13545" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞品对比" sheetId="1" state="visible" r:id="rId1"/>
@@ -481,17 +481,17 @@
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>纪要</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>消耗时间</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>文本长度</t>
         </is>
@@ -568,23 +568,21 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议发表讲话并回答提问，围绕多极化世界阐述中方立场。王毅表示，多极化是历史必然并正在成为现实，中国主张推动平等有序的世界多极化，中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。他提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅还就中欧关系表示，欧洲是多极世界的重要一极，中欧是伙伴而不是对手，今年是中欧建交50周年。在答问环节，王毅就乌克兰问题、中美关系等阐明中方立场。
+王毅在慕尼黑安全会议上发表演讲，阐述中国推动平等有序世界多极化的主张，提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。他强调中国是现行国际秩序的受益者和维护者，反对双重标准，支持联合国核心作用，并愿推动高质量共建“一带一路”与欧盟全球门户战略对接。在回应主持人提问时，王毅表示中国将继续维护联合国权威，遵守联合国宪章宗旨和原则，推动国际秩序更加公正合理；在乌克兰危机上，中国主张通过对话政治解决争端，反对武力和制裁，已提出劝和促谈并同巴西等发起“和平之友”，乐见包括美俄达成的共识在内的一切和平努力，并认为欧洲应发挥重要作用。关于中美关系，王毅表示中国对美政策保持连续性和稳定性，遵循相互尊重、和平共处、合作共赢三原则，愿构建稳定健康可持续的双边关系；但若美方打压遏制，中方将奉陪到底，坚决维护国家主权和正当发展权利。
 # 核心信息
-王毅提出四点主张：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，联合国宪章宗旨和原则是国际关系根本遵循，国家不论大小强弱都是国际法治利益攸关方，大国要带头讲诚信讲法治，摒弃言行不一、零和博弈，遵守国际法不能搞双重标准，应支持中国实现完全统一；三是践行多边主义，联合国是推进全球治理的核心平台，应固本强基而非拆梁毁柱，中国承担超过**20%**的联合国会费，切实履行`巴黎协定`，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己，去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**，愿推动高质量共建`一带一路`同欧盟`全球门户`战略相互对接。中欧关系方面，今年是中欧建交**50周年**，中方愿同欧方用好这一契机深化战略沟通和互利合作。
+王毅在慕尼黑安全会议上发表演讲，指出世界走向多极化是历史必然，中国主张推动平等有序的世界多极化。他提出四点看法：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，维护联合国宪章宗旨和原则，中国加入了几乎所有普遍性的政府间国际组织和600多项国际公约；三是践行多边主义，中国承担超过20%的联合国会费，建成世界上最大的清洁发电体系，提出并落实全球发展倡议、全球安全倡议、全球文明倡议；四是坚持开放共赢，去年中国GDP增长5%，对世界经济增长的贡献率接近30%，愿推动高质量共建“一带一路”与欧盟全球门户战略对接。
 # 官方表态
-关于国际秩序与规则：中国是在现行国际秩序中发展起来的，是这个秩序的受益者，要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展；需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。关于乌克兰问题：中国同俄罗斯是两大邻国，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中国同俄罗斯之间的交往是正常的国与国之间的交往；&gt; 如果中国不从俄罗斯买，哪个国家能够提供如此巨量的油气来满足中国民众的需求呢？那是不可能的，也是不保险的。中方历来主张一切争端和冲突都应该通过对话寻求政治解决，从这场危机爆发的第2天开始，就是2022年2月25号，中方就提出了对话协商解决；习近平主席提出的4点主张是中国立场的最权威的阐释，即各国的主权领土完整应该得到尊重，联合国的宪章应该得到遵守，各国的合理安全关切应该得到重视，一切致力于和平的努力都应该得到支持；中方派出的特使去各国斡旋，同巴西等南方国家发起了和平之友；中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识；所有当事方包括利益攸关方，都应该适时参与到和谈进程当中，欧洲更有必要为此发挥重要作用。关于中美关系：中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼；对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢；中美制度不一样是各自人民做出的选择，如果想改造或者颠覆对方是不切实际的；中美两个大国总不能冲突起来，因为那将殃及整个世界；中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系；如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，必将坚定维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决回击美方的单边和霸凌行径。
+关于国际秩序与规则：王毅回应称，中国是现行国际秩序的受益者，主张维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是国际社会的最大公约数。关于乌克兰危机：王毅表示，中俄是正常国家交往，中国不会停止购买俄罗斯油气，因为其他国家无法提供如此巨量的油气满足中国民众需求；中国主张通过对话政治解决争端，反对武力和制裁，已提出劝和促谈，并同巴西等南方国家发起“和平之友”，乐见包括美俄达成的共识在内的一切和平努力，认为欧洲应发挥重要作用。关于中美关系：王毅表示，中国对美政策保持连续性和稳定性，遵循相互尊重、和平共处、合作共赢三原则，愿构建稳定健康可持续的双边关系；若美方打压遏制，中方将奉陪到底，坚决维护国家主权和正当发展权利。
 # Q&amp;A环节
-问：你是否继续相信联合国？是否相信联合国宪章？是否会为联合国及其宪章改革而努力？这在你优先事项中排多高？ → 答：王毅表示，提问涉及秩序和规则两个关键词；真正要挑战秩序、毁约退群的国家出现了，而中国是在现行国际秩序中发展起来的，是受益者，要做的就是按照大多数国家的愿望推动这个秩序朝着更加公正合理的方向发展；需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。
-问：中国是否有可能对俄施压，如削减俄对华供气、降低价格或停止部分两用物资，以推动结束战争？ → 答：王毅表示，中国同俄罗斯是两大邻国，两国关系过去经历过曲折，之后双方吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系；中国同俄罗斯之间的交往是正常的国与国之间的交往；如果中国不从俄罗斯买，哪个国家能够提供如此巨量的油气来满足中国民众的需求，那是不可能的，也是不保险的；中方不会允许把经贸问题政治化、当做打压中国的工具，要为人民负责任；中方历来主张一切争端和冲突都应该通过对话寻求政治解决，乌克兰问题上同样如此，从2022年2月25号起中方就提出了对话协商解决，习近平主席提出的4点主张是中国立场的最权威阐释，中方不断推进劝和促谈，派出特使去各国斡旋，同巴西等南方国家发起了和平之友；中方乐见一切致力于和平的努力，包括这两天美国同俄罗斯达成的共识，认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要发挥重要作用。
-问：请简要预览一下中美关系将如何发展？ → 答：王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉；对美政策就是习近平主席提出的三原则，相互尊重、和平共处、合作共赢；中美制度不一样是各自人民做出的选择，如果想改造或者颠覆对方是不切实际的，正确的态度就是相互尊重；中美两个大国总不能冲突起来，因为那将殃及整个世界，所以还是要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美开展合作，全球性挑战也需要中美携手应对；中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道；如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底，必将坚定维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决回击美方的单边和霸凌行径。</t>
+问：中国是否仍相信联合国和联合国宪章？是否推动联合国改革？答：中国是现行国际秩序的受益者，主张维护以联合国为核心的国际体系，遵守联合国宪章宗旨和原则，这是国际社会的最大公约数。问：中国是否会采取措施施压俄罗斯以结束乌克兰战争？答：中俄是正常国家交往，中国不会停止购买俄罗斯油气，因为其他国家无法提供如此巨量的油气满足中国民众需求；中国主张通过对话政治解决争端，反对武力和制裁，已提出劝和促谈，并同巴西等南方国家发起“和平之友”，乐见包括美俄达成的共识在内的一切和平努力，认为欧洲应发挥重要作用。问：中美关系将如何发展？答：中国对美政策保持连续性和稳定性，遵循相互尊重、和平共处、合作共赢三原则，愿构建稳定健康可持续的双边关系；若美方打压遏制，中方将奉陪到底，坚决维护国家主权和正当发展权利。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>7004/2458</t>
+        <v>37.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7004/1376</t>
         </is>
       </c>
     </row>
@@ -751,28 +749,25 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次沟通交流会为电子科学与工程学院面向考生和家长的直播宣讲，由三位老师及学生代表介绍学院整体情况与各研究方向，并解答夏令营相关问题。段院介绍学院历史沿革、学科布局、师资与科研数据；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术、电路与系统方向；李天明教授介绍物理电子学方向；2023级博士研究生田雨桐分享择校理由与建议。段院就夏令营安排答复：今年计划举办夏令营活动，具体时间待定，相关信息通过QQ群978499108及时发布。直播最后进行抽奖互动，口令为“一生一世，逐梦未来”，奖品为学校马克杯套装。
+本次宣讲会由电子科学与工程学院面向考生和家长举办，段院介绍学院历史沿革：1956年建校成立无线电系，历经4次院系调整，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设5个二级学科方向及3个国防特色学科。学院现有本科生1545人、研究生1975人，教师302人（含两院院士2人、领军人才19人、青年人才28人），近5年科研经费稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，拥有两个国家级平台。柳教授介绍电子信息材料与元器件方向：以材料为基础、器件为核心、应用为目标，指出中国是电子产品生产大国但非强国，2021年集成电路进口额达2.8万亿元（约为原有进口量的1.7倍），先进电子材料元器件是卡脖子问题；研究团队包括邓龙江院士团队（19人）和张怀武教授团队（17人），依托两个国家级平台，科研面积2万余平米，拥有大型设备500余台套，毕业生去向包括英特尔、中芯国际、华为等。张教授介绍电磁场与微波技术（含4个细分方向）和电路与系统（含3个方向）两个学科：电磁场与微波技术始于1956年，由林卫干和谢楚芳创建，所属一级学科入选双一流A类，介绍了杨世文、樊勇、李恩、延波等教授团队的研究成果（四维天线阵列、毫米波平面集成天线、太赫兹雷达成像等）；电路与系统学科1981年开始招收研究生，拥有国家级人才4人，人才培养方面连续三年获全国大学生集成电路创新创业大赛奖项。李天明教授介绍物理电子学方向：是物理学与电子科学技术交叉学科，典型应用包括微波电子学、光电子学；学校物理电子学起源于1956年电子控器件专业，1979年成立高能电子学研究所，2018年并入电子科学与工程学院，经过近70年发展内涵不断扩展（纵向含仿真设计、人工智能引入，横向含频段上移和学科交叉）；团队共9个，每年科研经费接近2亿元，是国际最大真空器件研究中心。博士生田雨桐分享选择电子学院的8个理由（城市成都产业优势、学校电子信息学科群、电子科学与技术学科评估A+、研究团队实力、奖助体系等），建议学生先选团队再选导师，利用文献检索网站了解导师情况。
 # 信息同步
-**段院（学院整体情况）**：介绍学院历史沿革，1956年建校成立无线电系等，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科；本科生1545人，招生专业为工科试验班电子工程类，含电子科学技术、电磁场与无线技术；研究生1975人；教师302人，两院院士2人，领军人才19人，青年人才28人；近5年科研到账经费稳定在3~4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利1600余件；20个科研团队，年度经费过千万团队15个，过亿团队1个；拥有2个国家级平台、4个国际合作平台、7个省部级科研平台；国际交流共建姊妹院系2个，主办国际会议13场。
-**柳教授（电子信息材料与元器件方向）**：该方向以电子材料与电子器件为核心，服务电路系统与电子装备；中国集成电路电子产品2021年进口额度达2.8万元（原文），是卡脖子问题之一；应用于6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域；元器件向微型化、片式化、集成化、薄膜化、智能化发展；研究队伍含国家级人才10余人，两个团队：邓龙江院士电磁辐射控制材料与技术团队（19人，正高13、副高15，论文300余篇，课题130余项，年均经费3000多万元，授权专利100余项，国家科技进步/技术发明二等奖3项）、张怀武教授磁电薄膜与微型器件团队（17人，正高15、副高2，课题100余项，二等奖3项，SCI论文400余篇，年均经费2000余万元）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室；科研面积2万余平米，超精尖3000平，两条国家重大任务试验生产线，大型设备500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等。
-**张教授（电磁场与微波技术和电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向；电磁场与微波技术始于1956年，由林卫干先生和谢楚芳先生创建；有6个团队；拥有中国高校最先进的微波暗室群体；研究成果包括杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵应用于中电14所某大型机载相控阵雷达，樊勇教授团队毫米波平面集成天线、太Hz雷达成像系统（0.22/0.34/0.42太Hz，分辨率小于1厘米）2023年成都大运会示范应用，李恩教授团队微波毫米波测量技术、生物医学电磁学，延波教授团队微波毫米波太Hz芯片等；电路与系统81年招收研究生，88年成立首批博士后流动站，国家级人才4人，教授10人，副教授22人；人才培养连续三年获全国大学生集成电路创新创业大赛奖项等。
-**李天明教授（物理电子学方向）**：是物理学与电子科学技术交叉学科，研究微波与电子相互作用（微波电子学）、光与电子相互作用（光电子学）等；起源于1956年建校时前苏联专家帮助下成立的电子控器件专业，1979年刘成刚院士带领下成立高能电子学研究所；经过近70年发展，纵向向上游仿真设计数字模拟材料、下游系统应用发展，横向向毫米波到太赫兹频段及与医学交叉发展；拥有自主知识产权商用软件MMST和切皮克；每年到校科研经费接近两个亿，是学院最多；是世界上最大的真空器件研究中心；团队共9个；学生出口约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-**田雨桐（学生代表）**：2023级博士研究生，分享选择电子学院的8个理由：城市成都（新一线城市、电子信息产业前端，英特尔华为京东方等汇聚）、学校是电子信息人才培育代名词、专业电子科学与技术第4轮学科评估A+全国第一、研究团队实力、奖助体系全覆盖高额度长周期等；建议先选研究团队再选导师，可借助文献检索网站如HBO E和中国知网了解导师论文和指导研究生毕业情况，提前沟通交流。
-**夏令营答疑**：有朋友询问夏令营具体时间形式；段院回答今年计划夏令营活动时间还待定，感兴趣同学可加入QQ群978499108，相关信息会及时发布；主持人念QQ群号并邀请扫码加入。
+**学院整体情况（段院）**：学院历史沿革为1956年建校成立无线电系，历经4次院系调整，2023年成立电子科学与工程学院与集成电路学院；电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，以及电磁场与微波军用关键材料、电子元器件3个国防特色学科。学院党委入选教育部首批全国党建工作标杆院系，荣获全国教育系统先进集体。本科生1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；研究生1975人，学硕/博士为电子科学与技术，硕士含材料科学与工程，专业学位博士为电子信息，硕士含电子信息、材料工程。教师302人，其中教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人；两院院士2人、领军人才19人、青年人才28人、其他类型人才12人。拥有两个全国高校黄大年式教师团队（电磁辐射与散射等），2022年获批4个国家自然科学基金创新群体。近5年科研经费稳定在3-4亿元，以纵向项目为主、横向为辅，牵头获国家科技奖励11项，发表高水平论文2000余篇，申请专利1600余件、授权1300余件；20个科研团队中年度经费过千万元的15个、过亿元的1个。拥有国家电子辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室两个国家级平台，4个国际合作平台、7个省部级科研平台，与香港大学电机工程电子系、香港城市大学电子工程系共建国际姊妹院系，主办高水平国际会议13场，学生长短期交流项目20余个。
+**电子信息材料与元器件方向（柳教授）**：该方向以材料为基础、器件为核心、应用为目标，涉及电子材料与器件设计研制生产应用。指出中国是电子产品生产大国但非强国，2021年集成电路进口额达2.8万亿元（约为原有进口量的1.7倍），先进电子材料元器件是卡脖子问题；电子产品在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域作用重要，市场规模达万亿美元量级，正向小型化、多功能、低功耗、智能化发展，元器件向微型化、片式化、集成化、薄膜化、智能化发展，强调材料和器件一体化，集成技术结合摩尔定律与超摩尔定律。研究队伍含国家级人才10余人，两个团队：邓龙江院士领导的电磁辐射控制材料与技术团队（研究人员19人，正高13人、副高15人，发表含Nature在内论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000余万元，授权发明专利100余项，获国家科技进步或技术发明二等奖3项）；张怀武教授领导的磁电薄膜与微型器件团队（研究人员17人，正高15人、副高2人，开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目、国际合作等项目100余项，获科技进步二等奖3项，发表SCI论文400余篇，年均到账经费2000余万元）。依托两个国家级平台：国家电磁辐射控制材料工程技术研究中心（历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级，开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地）；电磁薄膜与集成器件全国重点实验室（2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子薄膜材料和集成器件开展基础应用、工程应用研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向）。科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；材料制备设备50余台套（液相外延、磁控溅射、化学气相沉积、原子沉积等），微纳加工设备30台套（步进式光刻机、反应离子刻蚀机等），微观表征设备10余台套（X射线衍射仪、扫描电镜、透射电镜等），性能测试设备50余台套（拉曼光谱分光光度计、差热分析仪、傅立叶红外光谱等）。获国家技术发明等奖项共7项，毕业生遍布英特尔、中芯国际、华为、德州仪器及高校科研院所；在读学生杨伟豪以第一作者在Nature Electronics、Nature Communications各发表一篇论文，5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖，黄飞获斯坦福大学博士全额奖学金，李凤霞读博期间发表论文16篇（一作6篇），严巍获王大珩光学奖并以优秀青年学者身份加入苏州大学，万位任河北美泰电子科技公司副总，带领团队采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
+**电磁场与微波技术和电路与系统方向（张教授）**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。电磁场与微波技术学科始于1956年，由林卫干和谢楚芳创建，形成电磁场与无线技术国家特色专业、电波传播与天线国防紧缺特色专业，所属一级学科入选双一流A类。学科有6个团队：电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容技术、微波测试与成像技术、无线技术与集成系统。平台含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室，拥有中国高校最先进的微波暗室群体及微波毫米波太赫兹仿真测试平台。主要成果：杨世文教授团队研究四维天线阵列技术（为天线阵列设计提供新自由度，实现低成本高性能），在强耦合超宽带相控阵方面取得进展并应用于中电14所某大型机载相控阵雷达，计算电磁学算法被评为20世纪十大算法之一，电磁测井仪器获国家科技进步二等奖并在中海油推广应用；樊勇教授团队研究毫米波平面集成天线（应用于毫米波通信雷达系统），研制出0.22THz、0.34THz、0.42THz雷达成像系统（分辨率小于1厘米），太赫兹通信成果在2023年成都大运会田径项目示范应用；李恩教授团队引领微波毫米波测量技术（60多年技术积累，突破众多技术封锁），面向5G通信、高性能系统、生物医学、新能源等方向提供应用，生物医学电磁学及成像方向发表大量高水平论文并有20余项国家发明专利；延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委支持，应用于新一代高速通信系统，在微波毫米波器件与系统方面取得固态合成功率源、天线阵列、扩电网络等成果，在微系统技术方面研制出三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。电路与系统学科1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站，含教育部国际合作联合实验室、国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。集成物理方向：樊勇教授和李廷军教授团队研制高速磁浮交通38GHz车地通信系统；樊勇教授和张静（本人）团队从事毫米波通信雷达CMOS芯片研究；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统、雷达系统研制成果。人才培养方面连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖，学生获互联网+、国际HPV等奖项，就业领域包括华为、中兴等领军企业及研究所、高校。
+**物理电子学方向（李天明教授）**：物理电子学是物理学与电子科学技术交叉学科，将物理学最新研究成果应用于电子学产生新电子器件，典型应用包括微波电子学（产生微波电真空器件）、光电子学（产生光电器件）；学科内容不断充实（如量子电子学），边界不一定清晰（如光电子学也可属光学工程）。学校物理电子学起源于1956年建校时在苏联专家帮助下成立的电子控器件专业（归属电子器件系），1979年在刘盛纲院士带领下成立高能电子学研究所，2001年物理系、应用所、高能所成立物理电子学，2018年物理电子学院、电工学院、微工学院部分合并成立电子科学与工程学院。经过近70年发展，内涵纵向扩展（上游仿真设计、数字模拟材料，下游系统应用，拥有自主知识产权商用软件MMST和切皮克，引入人工智能到器件设计），横向扩展（频段从微波上移至毫米波、太赫兹，与医学交叉开展太赫兹成像诊断、光电融合太赫兹源、太赫兹保密通信和高速通信）。拥有3个四川省工程中心或重点实验室，每年科研经费接近2亿元（学院内最多），是国际最大真空器件研究中心，2023年成功举办行业顶级会议。物理电子学方向共9个团队，学生出口约1/3硕博连读、1/3去企业、1/3去研究所或公务员。
+**学生视角（博士生田雨桐）**：分享选择电子学院的8个理由：城市成都（四川省会、国家中心城市、新一线城市、历史文化名城，电子信息产业发达，英特尔、华为、京东方等巨头汇聚，提供实践平台和就业资源）；学校是电子信息人才培育代名词（有电子信息博物馆，记录我国第一台晶体管收音机诞生，构建最完整电子信息学科群）；电子科学与技术学科在第4轮学科评估获A+稳居全国第一；研究团队实力强（所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖从芯片、封装、天线、电路、模块到系统的全面知识）；奖助体系全覆盖、高额度、长周期（含国家奖学金、学业奖学金、专项奖学金、新生奖学金、国家助学贷款等）；团队硕博毕业生实现100%就业率，就业单位含民营企业、大型央国企和头部科研院所；校园生活丰富（2021年跨年300架无人机灯光秀拼出UESTC字样）；建议学生先选研究团队再选导师，利用学院网站和文献检索网站（如IEEE、中国知网）了解导师论文和指导研究生情况，提前沟通交流。
 # 达成共识
-各方确认的信息：段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍各研究方向，田雨桐分享择校理由与建议。
-达成的共识：**今年计划举办夏令营活动，具体时间待定，相关信息通过QQ群978499108及时发布。**
-&gt; 段院：今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会唉到时会及时的发布。
+各方确认的信息与共识：段院确认学院今年计划举办夏令营活动，时间待定，相关信息将通过QQ群（群号978499108）及时发布；主持人确认考生和家长可通过添加QQ群进行详细咨询和了解。段院、柳教授、张教授、李天明教授、田雨桐同学共同参与宣讲，向考生和家长介绍学院整体情况及专业方向，欢迎考生报考。
 # 待协调事项
-无</t>
+**夏令营时间与形式**：事项描述：学院计划举办夏令营活动，具体时间和形式待定。对接人：段院。负责人：段院。预计完成时间或后续沟通计划：相关信息将通过QQ群（群号978499108）发布，考生和家长可加群关注后续通知。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>13887/2280</t>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13887/5206</t>
         </is>
       </c>
     </row>
@@ -1309,21 +1304,21 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会围绕2023年度经营数据、年终奖发放标准、个人与部门评价及颁奖抽奖展开。老板通报年终奖转账总额226,000元，人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27；最高工资含年终奖两三人拿到手20万多，平均到手1万多；2023年平均人工支出相对提高，平时工资提高约25万，年终奖比去年多1312万多；干满一年从去年四五人到今年12人。总量提升但成本往上跑，公司结余到账往下跑，还有百来万没收回来；老板每人比去年少拿约10万，承担亏100万风险。年终奖发放标准为：入职两三个月或半年以内发红包，去年600、800，今年可能1000左右；满一年以一个月基本工资为基准；超过一年不过多考虑年限，看当年表现。老板逐人评价并颁奖，共6人5项奖，最佳新人奖颁给红叶子、张扬，最佳进步奖颁给欧阳小元，最佳员工奖颁给游腾宇，特别贡献奖颁给李海腾。老板明确对后期有所侧重，是唯一愿意解释的一点；成本控制问题、年终奖额度问题、张扬的具体问题、徐艺玲更高的期待均明年再说。
+本次复盘会为公司年终总结会，预期目标为公布年度经营数据、发放年终奖与奖项、进行部门评价与展望。实际结果：年终奖总额226,000元，个人数额不一一公布；全年实打实支出390万元，利润率约24%或27%，成本控制较差；最高到手工资约20万元（两三人），平均到手工资1万多元；2023年公司总量提升、员工到手收入提升，但成本上升、结余缩水，尚有百来万未收回。老板自评对员工关心关注不够、管理不够雷厉风行，成本控制问题明年开会再议。会议逐一点评员工并颁发奖项，各部门总结展望，最后抽奖结束。
 # 亮点事项
-短视频部门整体表现超出预期：视频号粉丝从3月1日的700多人涨到8万，小红书从2000多涨到6.4万，抖音从2000多涨到5.7万，B站从3.1万涨到7.6万，整体转变从6月20日第一条外出拍摄视频开始。账号变现课程拍到十分满分达到7.05分，直播在视频号播了4到5场，平均每场在线5000人加，前100人平均在线50分钟以上。郭东辉在6月20日前被潘老师多次提醒出去找工作的情况下坚持不放弃，破釜沉舟说服潘老师外出拍摄，并一人负责多个平台运营，同时学习课程上架、开店、开企业店等琐碎事务，所有内容决策均有数据支撑，会抽时间刷同类英语老师直播间研究内容与互动。刘腾宇职业性、专业性、纪律性最好，无之一，沟通回复专业，几乎不迟到，请假严格按规定并提前告知工作安排，宁波罗峰反馈如果不是小姑娘做得好早就投诉，林海腾聊5分钟有4分钟在夸她，年终奖在既定标准上再拉一档。张扬作为请来的人才，来半年基本达到期待，职业态度和工作能力有目共睹，老板认为2023年干到最有价值的一件事就是把他招进来。宋俊逸10月来，编导岗位，第一次安排宁波两分钟宣传片文稿就让人觉得能干这个活，效率不错，监狱或财经项目没出现任何问题，段位较高。徐武安灵光、眼里有活，警察学院驻场孤苦伶仃但反馈不错，拍摄技术水平好于后期。张启商务表现高于预期，本以为害羞反而挺外向，有主观能动性，主动联系客户打电话。
+超出预期的成果包括：短视频账号粉丝大幅增长，视频号从719人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，且账号变现课程评分约7.5分（满分10分），直播平均在线5000人以上；商务部门实打实项目约300万元；员工整体表现高于预期，如刘腾宇、张扬、宋俊逸等获高度评价。促成成功的关键动作：郭东辉在6月20日说服潘老师到外面拍摄，成为涨粉转折点，其坚持与破釜沉舟的决心是关键；老板认真准备评价与奖项，注重仪式感；员工主动解决问题、跨部门协作顺畅。最具复用价值的经验：**坚持与破釜沉舟的决心**，以及**以数据支撑决策、主动学习对标**（如郭东辉每晚刷直播间学习）。
 # 不足事项
-成本控制非常差，是最大的问题，现象是人员工资、外援配音字幕租机器等实打实花出去390万，利润率约24%或27，根因是老板对一些关心或关注不够，不够雷厉风行，出现问题没有及时解决。公司结余到账往下跑，还有百来万没收回来，稍微缩水，老板每人比去年少拿约10万，承担亏100万风险。郭东辉克服本不该面对的困难，公司限制其发挥，应该表示歉意。张文倩在法院项目上沟通吃力，对方踢皮球，不知道标准怎么做。钱德峰后半年拍摄密集，两个月连轴转没有一天休息。外援成本大，有些东西公司自己人内部就可以搞定但凑不出人。后期加班严重，后半年基本都在加班，很少正常休息，人不够是加班最大的因素，是老板判断失误。李国宇沟通能力有问题且很严重。张启项目上对同事沟通和甲方做得不太好。
+未达预期的环节：成本控制非常差，利润率低，全年支出390万元，结余缩水，有百来万未收回；加班多，人员不足，老板判断失误；外援成本高，内部人员参与拍摄不足；账号变现与直播重点项目尚未完成。现象 → 根因：成本控制差 → 老板对员工关心关注不够、管理不够雷厉风行，出现问题未及时解决；加班多 → 人员不足，老板未及时招合适人数；外援成本高 → 内部人员技术水平或参与度不足。关键根因：**老板管理不够雷厉风行、对员工关心不够**，以及**人员配置不足**。
 # 改进计划
-成本控制问题明年开会再说，责任人无，时间明年。年终奖额度问题明年开会再说，责任人无，时间明年。张扬的具体问题明年再说，责任人无，时间明年。徐艺玲更高的期待明年再说，责任人无，时间明年。短视频部门期待账号开始变现，老板投入更大精力，责任人无，时间明年。执行部门期待老板更多组织协调，减少侵占休息时间，责任人无，时间明年。商务部门明年给予更多支持，责任人无，时间明年。</t>
+后续改进计划：明年开会讨论成本控制问题；明年再议年终奖额度；短视频部门期待账号开始变现，老板将投入更大精力；执行部门期待老板更多组织协调、减少侵占休息时间；商务部门老板将给予更多支持和帮助；鼓励员工参与拍摄，提升自身市场价值；老板反思对员工支持、管理、关心不够，明年改进。责任人：老板（成本控制、组织协调、支持商务）、郭东辉（短视频变现）、林海腾（后期安排）。时间：明年。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>24562/1571</t>
+        <v>54.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24562/1002</t>
         </is>
       </c>
     </row>
@@ -1866,20 +1861,20 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕小区物业服务缺失、业主大会召开与业委会成立等矛盾进行协调。业主方称已有200来户业主接龙要求召开业主大会，业委会工作组有6个群、准业主分5个群，最早的业主群已建5、6年，业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系；物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主代表逐条列举11项服务缺失问题，包括入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重、北边围墙用烂铁皮挡着且有缺口不安全、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员配备严重不足。物业方逐项回应称门柱灯因能耗成本无法运营、水系属地产维修责任、监控损坏已优先维修但费用超出运营承担、绿化死亡因业委会10月成立时已入冬、北边围墙属红线以外且涉违建、民生覆盖属地产前期配套、雨水倒灌属地产设计问题、人员配备不足因地产补亏款未结账，并称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分。双方就召开业主大会、换物业及起诉问题激烈交锋，业主方称已无调解必要、将正常推进业主大会，物业方称诉讼期间无法换物业公司，会议未达成一致。
-## 业主大会召开与业委会成立
-- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早的业主群已建5、6年；业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系。物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
-- 业主方称有200来户业主接龙要求召开业主大会，业委会工作组有6个群，准业主分5个群，最早的业主群已建5、6年；业主方建议尽快召开业主大会由全体业主表决，并称业委会成立之日自动解除与物业的合同关系。物业方称事先未接到任何通知，质疑程序合法性，并称已与集团法务沟通、本月正式起诉业委会及欠费超一年的业主代表。业主方表示将正常推进业主大会，物业方称诉讼期间无法换物业公司。
-## 小区11项服务缺失问题及物业方回应
-- 业主代表逐条列举11项服务缺失问题：入户庭院门柱灯从未开启、内部水系与售楼处门口迎宾水系从未开启、监控几乎全部损坏（上个月进贼未从监控获得任何数据）、监控室24小时值班及一键直达服务自王艳芳上任后荒废、绿化死亡严重（物业管家称等明年发芽）、北边围墙用烂铁皮挡着且有缺口不安全（物业承诺定制围挡未兑现）、快递柜直饮水机宽带暖气开户等民生附属问题无进展、雨水倒灌自2019年造成财产损失未解决、物业人员配备严重不足（办公室从近10人减至4人、维修从5人减至2人）。物业方逐项回应：门柱灯因能耗成本无法运营；水系存在严重质量问题属地产维修责任；监控损坏已优先维修但费用超出运营承担，监控室服务称已第一时间将画面截取给派出所和刑警；绿化死亡因业委会10月成立时已入冬；北边围墙属红线以外且涉违建、不属物业服务范围，协调施工单位因费用太高未果；民生覆盖属地产前期配套、费用应由业主承担；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结账。物业称园区保护收入100来万、人工成本100多万，每年亏损，外面欠物业费170多万，要求年前回40万才拿出钱修一部分，账上一分钱没有。</t>
+本次会议为小区业委会与物业就长期服务问题（门柱灯、水系、监控、绿化、围墙、雨水倒灌等）的专项协调会。业委会成员列举了小区存在的11项问题，要求召开业主大会表决是否更换物业；物业方表示已与集团法务沟通，将于本月起诉业委会，并称诉讼期间业主大会无法召开。双方就物业费欠费、服务缺失等问题激烈争论，未达成一致。物业方称业主欠费170多万元，公司每年亏损，人工成本100多万元，无力承担维修费用；业委会成员认为物业服务不应以先收费为前提。物业方宣布将于本月正式起诉业委会，并称掌握业主群内煽动拒缴物业费的证据；业委会成员表示将反诉，并称业委会成立之日已自动解除物业合同关系。会议未达成实质和解，业委会表示将正常推进业主大会，物业方表示将在本月正式起诉。
+## 业主大会召开与物业去留
+- 业委会成员提出小区存在11项问题，要求召开业主大会表决是否更换物业；物业方表示已与集团法务沟通，将于本月起诉业委会，并称诉讼期间业主大会无法召开；双方就物业费欠费、服务缺失等问题激烈争论，未达成一致。
+- 业委会成员列举了门柱灯不亮、水系从未开启、监控损坏、监控室无人值班、绿化死亡、北边围墙缺失、民生配套未落实、雨水倒灌、物业人员配备不足等10条问题；物业方逐条回应，称部分属地产责任、部分因费用不足，并称已与业委会沟通但未获支持。
+## 物业费欠费与法律诉讼
+- 物业方称业主欠费170多万元，公司每年亏损，人工成本100多万元，无力承担维修费用；业委会成员认为物业服务不应以先收费为前提。物业方宣布已与集团法务沟通，将于本月起诉业委会，并称掌握业主群内煽动拒缴物业费的证据；业委会成员表示将反诉，并称业委会成立之日已自动解除物业合同关系。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>21511/1504</t>
+        <v>34.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21511/719</t>
         </is>
       </c>
     </row>
@@ -2128,21 +2123,21 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌研讨围绕具身智能展开，由主持人介绍四位博士生背景后依次抛出模型形态、硬件、世界模型、策略学习路线与数据scaling等议题。模型形态上讨论涵盖大脑大模型、小脑大模型、端到端模型及以派零为代表收集6000多小时数据训出的端到端模型，并提出前面fix住、后面做Action refiner的设想。硬件上薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up，现有工业机械臂并非为此设计；发言者2认为具身是软硬件协同优化范式，提到松龄产品第二代、凝胶夹爪可反馈触觉、摩擦力更好。世界模型议题上赵浩从computer vision角度讨论是否需重构所有pixel和3D，志龙从强化学习角度认为world model第一要义是可交互、需能学策略。策略学习路线上派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈；数据采集上杨立新强调视角控制、标定重要，薛寒all in真机采集路线，赵浩提出2025年应推广大规模利用无标注真实数据。
+本次圆桌论坛围绕具身智能展开，参与人员包括多位老师、博士生及业界嘉宾，重点探讨了大模型与硬件协同、世界模型定义、强化学习与模仿学习路线、数据采集与仿真等议题。关于硬件形态，王老师认为模型应分层，大脑不变，小脑自适应；赵老师认为人形和特种机器人都会存在；薛寒博士提出硬件需高可靠性和寿命。关于世界模型，志龙强调可交互性，赵老师认为CV的世界模型可作为RL的工具，王老师提出世界模型可能无法统一，而policy可以统一。关于策略学习路线，业界嘉宾介绍模型强化加机理融合的方式，王老师认为先模仿后强化是复杂任务的可行解，静波认为两者并不冲突。关于数据，杨老师分享数据采集经验，薛寒博士认为真实数据是低成本方案，赵老师提出2025年应利用无标注数据，并讨论国产仿真系统。
 # 核心观点
-模型形态议题：讨论大脑大模型、小脑大模型、端到端模型及以派零为代表收集6000多小时数据训出的端到端模型，提出是否可前面fix住、后面做Action refiner。王岳认为若大模型直通到底会消除硬件迭代可能性，至少应分上下层，大脑不变、小脑adaptive到肢体。硬件议题：讨论具身身体会收敛成人形还是其他形态，机械领域提到机械智能、软手摩擦与顺应性；薛寒提出硬件需寿命和可靠性高，因真机evaluation中机器人撞几次就坏、难以scale up；发言者2认为具身是软硬件协同优化范式，提到松龄产品第二代、凝胶夹爪可反馈触觉、摩擦力更好。世界模型议题：赵浩从computer vision角度讨论是否需重构所有pixel和3D，提到ACL上已有4D world model投稿；志龙从强化学习角度认为world model第一要义是可交互、需能学策略，当前物理规律体现欠缺；赵浩认为CV界追求重建物理世界动态，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难完全学习，并提出data bias trade off，认为数据多时需要的inductive bias变少；王岳用游戏跳楼例子认为world model可能做不到统一、policy有可能是一个，发言者9提出不同物理结构可能有统一表征，王岳认为M个独立模型更简单。策略学习路线议题：派零团队收集上千小时近万小时数据后仍看到模仿学习瓶颈；发言者10介绍公司采用模型强化加机理融合，监督学习动作空间大、数据分布不足，强化学习强依赖仿真环境、sim-to-real迁移难；发言者9认为复杂任务应先模仿后强化，单独模仿或单独强化都不行；王岳认为pid有反馈、反馈可作为reward，强化必然走得成；静波认为RL和IL没有本质冲突，只是想要一个latent状态。数据采集与scaling议题：杨立新强调视角控制、标定重要，open X数据集相机视角不固定、不关注物体，采集需记录物体运动；薛寒all in真机采集路线，认为柔性体仿真需先进图形学技术、算力要求高、人才少，真机采集成本更低，可穿戴设备是较能scale的方案，互联网视频数据与机器人所需数据很不一样；发言者2提到ego4d数据集洗了三个月，仿真数据加少量真机数据成功率显著提升，并问是否强依赖英伟达生态及国产仿真；赵浩认为用真实还是仿真数据看成本、case by case，提出2025年应推广大规模利用无标注真实数据，国产仿真系统是产业问题、有人赌卡脖子做国产替代。
+硬件形态与模型收敛：王老师认为大模型不应端到端，应分层，大脑不变，小脑自适应；赵老师认为人形和特种机器人都会存在；薛寒博士提出硬件需高可靠性和寿命。世界模型定义：志龙强调可交互性，赵老师认为CV的世界模型可作为RL的工具，王老师提出世界模型可能无法统一，而policy可以统一，双方就统一模型与解耦模型展开交锋。强化学习与模仿学习路线：业界嘉宾介绍模型强化加机理融合的方式，王老师认为先模仿后强化是复杂任务的可行解，静波认为两者并不冲突。数据采集与仿真：杨老师分享数据采集经验，薛寒博士认为真实数据是低成本方案，赵老师提出2025年应利用无标注数据，并讨论国产仿真系统。
 # 达成共识与解决方案
-研讨未形成正式决议，但各方在若干认知上趋于一致：**具身智能是软硬件协同优化的范式**，硬件需寿命和可靠性高以支持真机evaluation的scale up；**世界模型在CV与RL界关注点不同**，CV界追求重建物理世界动态、可作为RL中world models的工具，RL界更强调可交互与学策略；**复杂任务的策略学习宜先模仿后强化**，单独模仿或单独强化都难以收敛到专家水平；**数据采集需兼顾仿真与真机**，仿真数据加少量真机数据可显著提升成功率，真机采集需控制视角、做好标定并记录物体运动；**2025年应推广大规模利用无标注真实数据**。
+**具身智能需软硬件协同优化**，硬件形态上人形与特种机器人将并存。**世界模型在强化学习与计算机视觉领域关注点不同**，CV的世界模型可作为RL的工具。**复杂任务宜采用先模仿后强化的混合路线**，业界实践表明模型强化加机理融合有效。**数据采集应结合真实数据与仿真数据**，并重视无标注数据的利用。
 # 未决分歧与后续探索
-未决分歧包括：具身智能的模型最终是端到端还是分层，尚未达成一致；具身的身体会收敛成人形还是其他形态，尚未确认；世界模型是否需要3D inductive bias，尚无定论；世界模型最终是一个还是多个、policy是否统一，存在分歧；强化学习与模仿学习最终路线如何组合，未形成统一结论；未来是否强依赖英伟达生态、是否会有国产仿真产品支持，待观察；真机数据采集如何scale up、可穿戴设备精度与遥操数据的gap如何弥补，待确认。后续行动方向包括：在仿真与真机数据配比上继续验证，探索可穿戴设备等低成本采集方案，关注国产仿真系统进展。事项跟进人：赵浩（国产仿真系统产业问题）、杨立新（真机数据采集经验）、薛寒（真机采集与可穿戴设备方案）。</t>
+具身智能机器人的最终形态是人形还是特种，未达成一致。世界模型是否需要统一的模型，存在分歧。强化学习与模仿学习的最终路线，尚未定论。仿真数据与真实数据的比例如何确定，未明确。国产仿真系统是否依赖英伟达生态，有待观察。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>21458/2134</t>
+        <v>27.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21458/921</t>
         </is>
       </c>
     </row>
@@ -2641,45 +2636,26 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系国家开发银行不服云南省高级人民法院2018云民初88号民事判决提起上诉的二审公开开庭审理，案由为金融借款合同纠纷，被上诉人为云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司。合议庭由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。庭审经核对出庭人员身份、确认诉讼文书送达及二审权利义务后，围绕抵押权与融资租赁所有权冲突及善意取得、罚息复息计算及起算日期、东源煤电东源煤业是否连带给付违约金三个争议焦点进行调查辩论。合议庭休庭评议后提出调解方案，各方当事人均表示无异议，自愿达成调解协议，法院予以确认并在庭后根据民事诉讼法第97条出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司（东源煤电）、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院（2018）云民初88号民事判决提起上诉。本案由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，依法公开开庭审理。庭审围绕三个争议焦点展开：国开行抵押权是否构成善意取得、罚息复利计算及起算日期、违约金承担。经合议庭评议提出调解方案，各方当事人均无异议，同意签署调解协议。
 # 原告诉称与被告辩称
-见下表。
+各方当事人对调解方案均无异议，同意签署调解协议。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（原审原告）国家开发银行 | 主张抵押权完整无瑕疵、构成善意取得；请求支持罚息复利计算及违约金连带责任 | 已按央行规定查询融资租赁系统，尽到基本查询义务；抵押设备为通用设备无唯一标识码，仅能对抵押人曲靖电力公司名下融资租赁系统进行查询；2018年6月13日发函宣布贷款提前到期，罚息应自该日起算；东源煤电东源煤业构成违约应按借款合同第24条第3项支付千分之一违约金 |
-| 被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、云南东源煤业集团有限公司 | 主张国开行未尽注意义务、不构成善意；2018年6月13日宣布贷款提前到期未给合理期限；罚息不应作为复利计算基数；国开行未举证证明违约且未先行限期纠正 | 2015年12月2日邮件及东源公司融资情况统计表已告知抵押设备存在融资租赁情形且用红色标注；国开行作为专业金融机构应尽注意义务；合同约定宣布提前到期应限期偿还而非立即偿还；人民币利率管理规定第21条及合同第6条第4款均未将罚息作为复利计算基数；国开行未举证证明东源煤电违反柜台前移和账户管理且未发出纠正函件 |
-| 被上诉人招银金融租赁有限公司 | 主张国开行未在抵押时点查询融资租赁登记、不构成善意；东源煤电出资系无权处分；尊重合议庭审查结果 | 国开行提供的2018年9月查询证书不符合要求，应在2015年12月抵押时点查询；招银租赁2012年即取得租赁设备所有权，东源煤电出资给电力公司系无权处分；融资租赁登记非物权登记，仅产生对抗效力；案涉5套设备为种类物无唯一识别码故未登记 |
+| 上诉人（国开行） | 请求撤销一审判决，改判支持其抵押权、罚息复利及违约金主张 | 已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，审查义务仅限于抵押人曲靖电力公司，构成善意取得；利息应计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；东源煤电、东源煤业违约应支付违约金 |
+| 被上诉人（东源煤电、东源煤业、曲靖电力） | 请求驳回上诉，维持一审判决 | 2015年12月2日邮件已告知设备情况，国开行未尽注意义务；贷款提前到期应给予合理期限，罚息不应计收复利，复利不应再计复利；国开行未举证证明违约行为，且未按合同约定先行限期纠正 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 国开行未在抵押时点查询融资租赁登记系统，不构成善意；东源煤电出资行为系无权处分，电力公司未取得设备所有权；招银租赁2012年已取得租赁设备所有权 |
 # 举证与法庭调查
-## 一、举证与质证
-- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书（第5组证据第1项），招银租赁质证认为该查询证书不符合要求，国开行应在抵押时点即2015年12月进行融资租赁登记查询。
-- 国开行提交证据第54页、58页东源煤电公司曲靖电力公司对设备权属的证明材料及股东会决议，主张抵押设备所有权属曲靖电力公司。
-- 国开行提交证据第108页核查表，主张已对曲靖电力公司名下融资租赁登记信息进行核查。
-- 招银租赁一审提交证据第7页回租设备清单，仅载明设备名称和生产厂家，未提及型号，所载出厂日期为2012年3月1日；国开行现场核实抵押设备铭牌生产日期均在2013年以后，部分为2013年11月、2013年12月、2014年3月。
-- 招银租赁一审提交2013年和2015年审计报告（证据第82页、第95页），载明曲靖电力公司注册资本4亿元且已实缴。
-- 东源方提交2015年12月2日邮件及东源公司融资情况统计表，主张已告知国开行抵押设备存在融资租赁情形，统计表中招银租赁一栏抵押设备名称与国开行抵押设备名称完全相同且用红色标注。
-## 二、法官询问要点
-- 合议庭询问各方对中国人民银行征信中心融资租赁登记的性质及法律后果的理解。
-- 合议庭询问央行融资租赁登记系统的查询方式及能否保证查询到登记结果。
-- 合议庭询问国开行贷款前风控资料内部规定是否要求查询、未查到结果是否需保留查询记录。
-- 合议庭询问招银租赁在登记系统是否登记设备唯一标识码、该标识码是否为必填项。
-- 合议庭询问违反查询通知规定在多大程度上导致融资租赁司法解释第9条第2款的法律后果，属基本查询义务还是全面审慎查询义务。
-- 合议庭询问若银行通过其他途径已知动产属融资租赁物，是否仍需查询登记系统。
-- 合议庭询问各方对融资租赁司法解释第9条第2款举证责任分担的理解。
-- 合议庭询问各方如何看待不同登记机构产生的登记信息及信息冲突时的意见建议。
-## 三、双方辩论的争议焦点
-- 争议焦点一：抵押权与融资租赁所有权冲突及善意取得。国开行主张已按央行规定查询融资租赁系统、尽到基本查询义务、构成善意取得；东源方主张2015年12月2日邮件已告知抵押设备存在融资租赁情形、国开行未尽注意义务；招银租赁主张国开行未在抵押时点查询融资租赁登记、不构成善意，且东源煤电出资系无权处分。
-- 争议焦点二：罚息复息计算及起算日期。国开行主张利息自2017年12月21日至2018年6月12日合计2179.5727万元、罚息自2018年6月13日至2019年2月19日合计4105.0579万元、复利自2018年3月21日至2019年2月19日合计191.8206万元；东源方主张2018年6月13日宣布贷款提前到期未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
-- 争议焦点三：东源煤电、东源煤业是否应连带给付违约金。国开行主张按借款合同第24条第3项支付千分之一违约金且对方未配合办理账户管理及柜台前移手续；东源方主张国开行未举证证明违约且未按合同约定先行限期纠正。
+庭审中，国开行主张已按央行规定查询融资租赁登记系统，未发现曲靖电力公司设备有融资租赁登记，且设备为通用设备无唯一标识码，审查义务仅限于抵押人曲靖电力公司，构成善意取得；东源煤电反驳称2015年12月2日邮件已告知设备情况，国开行未尽注意义务；招银租赁认为国开行未在抵押时点查询，不构成善意。各方对融资租赁登记性质、查询义务程度、举证责任分担等发表意见。关于罚息复利，国开行主张利息计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算，并列出具体金额；东源煤电认为贷款提前到期应给予合理期限，罚息不应计收复利，复利不应再计复利。关于违约金，国开行主张东源煤电、东源煤业违约应支付违约金；东源煤电反驳称国开行未举证证明违约行为，且未按合同约定先行限期纠正。
 # 庭审结果
-本案争议焦点为三项：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息复息计算及起算日期；三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案：国开行对东源煤电债权扣除破产中已清偿本金外，利息、罚息、复利三项共计6474.4513万元；确认招银租赁对涉案6项设备享有所有权、对应债权1377.4137万元，确认国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%、实现费用双方各担50%，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置；未实现债权待执行法院出具体本裁定后按破产重整计划预留方案实现，若破产管理人不将招银租赁债权纳入预留方案则由东源煤电按此前有担保清偿方案清偿；若司法变现不能实现权益则双方放弃对案涉设备权益、由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；一审判决第2项第4项按判项确认；一审诉讼费用国开行诉请部分按一审判决执行、招银租赁诉请部分由二审法院按规定根据争议财产对应债权数额计算后由国开行承担，二审诉讼费用由法院依法确定后由国开行和东源煤电各承担50%。各方均表示无异议，自愿达成调解协议，法院予以确认，庭后根据民事诉讼法第97条出具调解书。合议庭指出本案涉及生产设备等动产抵押权与融资租赁物所有权冲突系司法实践普遍性难题，根本原因在于国家尚未建立统一动产登记制度、现有融资租赁登记系统与动产抵押登记系统缺乏有效衔接，将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议。</t>
+经合议庭评议，结合我国动产担保及融资租赁登记不完善的现实背景，提出调解方案：确定国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元；确定招银租赁对涉案6项设备享有所有权，国开行对93项设备有抵押权；招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用各担50%。各方当事人对调解方案均无异议，同意签署调解协议。调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序；若司法变现不能，国开行和招银租赁权益通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营；案涉设备上的管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置。一审诉讼费用中对于国开行诉请部分按照一审判决执行，对于招银租赁诉请部分由二审法院按规定计算后由国开行承担；二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>28485/2998</t>
+        <v>49.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28485/1515</t>
         </is>
       </c>
     </row>
@@ -2836,70 +2812,50 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，验收组于18号19号提前介入前期摸排，20号召开首次会议，分内业检查和外业检查，按建筑工程、安装工程、机电设备专业方向开展。截止今天已完成卢萨卡点除弹料加工调试以外的所有验收工作，蒙泽点已完成全部验收工作，姆皮卡点现场验收工作尚未开展；因带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。内业方面，管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，受疫情及项目特殊情况影响主要人员基本能保证在前方岗位，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求，但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善。外业建筑部分，原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准，因资料完整整理结果没出来今天不下最后结论。外业安装部分，钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准。财务验收方面，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。验收组提出人员履约、内业资料、现场实体整改及不可预见费使用等整改要求，合作局领导建议尽快补充资料、做好沟通对接，蒙泽厂区混凝土路面开裂需管理组和总包单位共同研究制定整改方案，争取在末次会之前、最迟出报告之前完成整改并形成闭环，交给外方之前继续做好成品保护。
+本次会议为原占比二玉米面加工厂项目中期验收会议。验收组已完成卢萨卡点除带料调试外的所有验收工作，蒙泽点已全部完成并顺带完成带料调试流程试生产，姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展。内业检查涵盖人员履约、程序性文件、过程性检查文件等，基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善；外业检查分建筑、安装、设备三部分，建筑部分整体品质良好但存在局部损伤、排水需清理、混凝土路面开裂等问题，安装部分结构无问题但监控管线接头脱落，设备部分运行正常、产能符合设计指标。验收组提出人员履约、内业资料、现场整改等要求，管理组田组长表示会后与技术组细化检查并制定方案处理，技术组龚总汇报三点整改计划：收集人员护照证书、汇总内业资料、编制现场整改方案。合作局领导强调资料补充沟通、路面开裂原因分析及整改闭环、成品保护；公司林总强调按合同标准仔细验收、提醒当地用户建议、注意交通安全和防疫。验收组发现项目有动用不可预见费情况，需完善依据证据和数据，确保充分无误，后续将专门对接。
 # 进度追踪
-各模块进展如下：
-- **卢萨卡点验收**：已完成除弹料加工调试以外的所有验收工作。
-- **蒙泽点验收**：已完成全部验收工作，带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道。
-- **姆皮卡点验收**：现场验收工作尚未开展，内业资料已提前拿到卢萨卡点。
-- **内业资料**：管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，编制施工组织计划、管理计划、实施细则及各项专项预案，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件有一个点因太远还在分散。
-- **外业建筑部分**：原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来今天不下最后结论。
-- **外业安装部分**：钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准。
-- **财务验收**：财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准。
-- **不可预见费**：检查中看到本项目有动用不可预见费的情况，专家组跟施工单位做了沟通，可能在一些内容上还要进一步完善和把资料收集整理清楚，后续时间会做专门对接。
+**验收工作总体进展**：卢萨卡点除带料调试外所有验收工作已完成；蒙泽点全部验收完成，并顺带完成带料调试流程试生产；姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展。
+**内业检查**：人员履约、程序性文件、过程性检查文件等基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善。
+**外业检查**：建筑部分整体品质良好，但存在局部损伤、排水需清理、混凝土路面开裂等问题；安装部分结构无问题，但监控管线接头脱落；设备部分运行正常，产能符合设计指标。
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除弹料加工调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，带料调试厂家工作人员在现场，验收组与技术组顺带把整个流程试生产、外方人员操作、产品生产过程过了一道 | ✅已完成 |
-| 姆皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
-| 内业资料 | 管理组技术组基本能按项目合同组建项目执行团队并按流程程序开展工作，验收组查阅内业资料、现场抽检及问询交流，基本评价为满足项目有关标准和规范要求；但分类整理及少量质检和管理机构验收签字的规范性还需进一步规范和完善，竣工文件有一个点因太远还在分散 | 🔄进行中 |
-| 外业建筑部分 | 原材料除国内采购出口建筑材料外，主要主材包括预制构件、年广场地砖从卢萨卡大规模成建制有质量管控体系的供货单位集中预制采购、从200多公里以外拉过去，内在品质通过查验资料、外在表观通过现场抽检和检测达到很好标准；因资料完整整理结果没出来今天不下最后结论 | 🔄进行中 |
-| 外业安装部分 | 钢结构所有材料从国内定制发货到现场，满足规范和标准要求；设备由技术组执行单位与国内中粮西安设计院及相关厂家签订专项供货合同，参照中国标准，按输出产品分三类标准专门定制编制设备并生产三套成套设备，厂家高峰期派十几名工作人员到现场指导安装，验收组对工艺设备逐台复核并投料试运行，工艺设备运行正常、工艺流程满足生产要求、产能符合设计指标，机电设备安装达到国家质量检验有关标准 | ✅已完成 |
-| 财务验收 | 财务验收专家查阅本项目财务资料并与相关人员沟通，本项目财务从账户设置、资金往来、银行开户等过程完全符合财务处理有关规范和标准 | ✅已完成 |
-| 不可预见费 | 检查中看到本项目有动用不可预见费的情况，专家组跟施工单位做了沟通，可能在一些内容上还要进一步完善和把资料收集整理清楚，后续时间会做专门对接 | 🔄进行中 |
+| 验收工作总体进展 | 卢萨卡点除带料调试外所有验收工作已完成；蒙泽点全部验收完成，并顺带完成带料调试流程试生产；姆皮卡点内业资料已提前拿到卢萨卡，现场验收尚未开展 | 🔄进行中 |
+| 内业检查 | 人员履约、程序性文件、过程性检查文件等基本满足规范要求，但存在人员统计不完整、特种人员证件有效期问题、资料分类整理和签字规范性需完善 | 🔄进行中 |
+| 外业检查-建筑 | 整体品质良好，但存在局部损伤、排水需清理、混凝土路面开裂等问题 | 🔄进行中 |
+| 外业检查-安装 | 结构无问题，但监控管线接头脱落 | 🔄进行中 |
+| 外业检查-设备 | 运行正常，产能符合设计指标 | ✅已完成 |
 # 风险预警
-整体健康度：🟡低风险。风险点如下：
-- **人员履约与合同履约资料不闭合**：个别同志进出场时间以及护照还需施工部和管理组进一步完善和提高，以期验收报告时达到闭合条件；个别岗位人员因各种原因有申请更换流程；人员统计数量尤其是技术组对厂家服务人员可能没有计算进去；个别特种人员证件在有效期上，可能出国后国内延期或更新没有及时到位。等级：中；责任人：施工部、管理组、技术组；应对计划：请执行单位跟国内人力资源对接，完善相关资料闭合。
-- **内业资料分类整理及签字规范性不足**：分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善。等级：中；责任人：技术组、管理组；应对计划：按项目执行有关标准和规范及国家有关规范及时把资料汇总到卢萨卡、分类成册、按竣工文件归档要求及时组卷。
-- **竣工文件分散**：全部集中到卢萨卡点过程中有一个点因太远还在分散。等级：中；责任人：技术组；应对计划：验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码。
-- **蒙泽厂区混凝土路面开裂**：非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，当地工人处理裂纹效果不好。等级：高；责任人：管理组、总包单位；应对计划：分析原因，结合赞比亚当地气候特点制定切实可行整改方案，管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核。
-- **监控管线接头脱落**：局部监控管线因设备启动震动、加工设备转子通过转速采集数据的管线接头处有脱落，可能引起机械故障。等级：中；责任人：施工组；应对计划：伴随设备调试全面检查，保证有效性和安全性。
-- **罗萨卡点加工提升桶位置雨水倒灌**：赞比亚雨量大风大、雨水有可能倒灌。等级：中；责任人：施工组；应对计划：检查，即便按原设计施工若不足以解决水的问题要考虑增加覆盖面积或通过技术措施解决。
-- **卢萨卡点廊墙端头竖条不足**：廊墙最端头横向分布只有三个竖条，视觉上感觉不够安全。等级：低；责任人：施工组；应对计划：建议中间再加两个竖条，为巡检和维护工作人员提供安全保障，后面再做一次检查和完善。
-- **成品保护疏忽**：工程实体完工时间较长、带料调试一直没法进行导致验收推后，成品保护可能有疏忽。等级：中；责任人：管理组、总包单位；应对计划：交给外方之前继续做好成品保护，有破损的地方及时修补。
-- **赴姆皮卡交通安全**：赞比亚雨季路况不好、去姆皮卡路途遥远。等级：高；责任人：验收组；应对计划：注意交通安全，争取安安全全平平安安回来。
-- **新冠疫情防疫**：等级：中；责任人：验收组；应对计划：注意新冠防疫。
-- **不可预见费依据证据**：有关依据证据和数据需充分无误。等级：中；责任人：验收组、施工单位；应对计划：后续时间做专门对接，放在末次汇报再进行沟通。
+**整体健康度：🟡低风险**
+**混凝土路面开裂**：等级中，影响项目移交后使用，存在大面积开裂隐患，责任人未明确，应对计划为分析原因（气候、施工工艺、材料），制定科学合理整改方案，在出报告前完成整改，验收组复核。
+**监控管线接头脱落**：等级低，影响设备运行安全，可能引起机械故障，责任人未明确，应对计划为伴随设备调试全面检查，保证有效性和安全性。
+**雨季排水阻塞**：等级中，影响厂区及办公区排水，责任人未明确，应对计划为雨季前对屋面排水、室外通道进行最后清理和排查。
+**姆皮卡点路途交通安全**：等级中，影响验收组前往姆皮卡点开展现场验收，责任人未明确，应对计划为注意交通安全和防疫，确保安全完成验收任务。
+**疫情及雨季影响验收工作**：等级低，影响验收进度，责任人未明确，应对计划为按计划推进，注意防疫和交通安全。
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 人员履约与合同履约资料不闭合 | 🟡低风险 | 个别同志进出场时间以及护照还需进一步完善，影响验收报告闭合；个别岗位人员有申请更换流程；人员统计数量尤其是技术组对厂家服务人员可能没有计算进去；个别特种人员证件在有效期上，可能出国后国内延期或更新没有及时到位 | 施工部、管理组、技术组 | 请执行单位跟国内人力资源对接，完善相关资料闭合 |
-| 内业资料分类整理及签字规范性不足 | 🟡低风险 | 分类整理以及少量质检和管理机构验收签字的规范性还需进一步规范和完善 | 技术组、管理组 | 按项目执行有关标准和规范及国家有关规范及时把资料汇总到卢萨卡、分类成册、按竣工文件归档要求及时组卷 |
-| 竣工文件分散 | 🟡低风险 | 全部集中到卢萨卡点过程中有一个点因太远还在分散 | 技术组 | 验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码 |
-| 蒙泽厂区混凝土路面开裂 | 🔴高风险 | 非主要通道范围内混凝土路面有少量开裂现象，可能与基础碾压和混凝土扬升过程有关，当地工人处理裂纹效果不好，移交外方后若再出现大面积开裂对外影响不好 | 管理组、总包单位 | 分析原因，结合赞比亚当地气候特点制定切实可行整改方案，管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核 |
-| 监控管线接头脱落 | 🟡低风险 | 局部监控管线因设备启动震动、加工设备转子通过转速采集数据的管线接头处有脱落，可能引起机械故障 | 施工组 | 伴随设备调试全面检查，保证有效性和安全性 |
-| 罗萨卡点加工提升桶位置雨水倒灌 | 🟡低风险 | 赞比亚雨量大风大、雨水有可能倒灌 | 施工组 | 检查，即便按原设计施工若不足以解决水的问题要考虑增加覆盖面积或通过技术措施解决 |
-| 卢萨卡点廊墙端头竖条不足 | 🟢正常 | 廊墙最端头横向分布只有三个竖条，视觉上感觉不够安全 | 施工组 | 建议中间再加两个竖条，为巡检和维护工作人员提供安全保障，后面再做一次检查和完善 |
-| 成品保护疏忽 | 🟡低风险 | 工程实体完工时间较长、带料调试一直没法进行导致验收推后，成品保护可能有疏忽 | 管理组、总包单位 | 交给外方之前继续做好成品保护，有破损的地方及时修补 |
-| 赴姆皮卡交通安全 | 🔴高风险 | 赞比亚雨季路况不好、去姆皮卡路途遥远 | 验收组 | 注意交通安全，争取安安全全平平安安回来 |
-| 新冠疫情防疫 | 🟡低风险 | 疫情防控风险 | 验收组 | 注意新冠防疫 |
-| 不可预见费依据证据 | 🟡低风险 | 有关依据证据和数据需充分无误 | 验收组、施工单位 | 后续时间做专门对接，放在末次汇报再进行沟通 |
+| 混凝土路面开裂 | 中 | 影响项目移交后使用，存在大面积开裂隐患 | 未明确 | 分析原因（气候、施工工艺、材料），制定科学合理整改方案，在出报告前完成整改，验收组复核 |
+| 监控管线接头脱落 | 低 | 可能引起机械故障 | 未明确 | 伴随设备调试全面检查，保证有效性和安全性 |
+| 雨季排水阻塞 | 中 | 影响厂区及办公区排水 | 未明确 | 雨季前对屋面排水、室外通道进行最后清理和排查 |
+| 姆皮卡点路途交通安全 | 中 | 影响验收组前往姆皮卡点开展现场验收 | 未明确 | 注意交通安全和防疫，确保安全完成验收任务 |
+| 疫情及雨季影响验收工作 | 低 | 影响验收进度 | 未明确 | 按计划推进，注意防疫和交通安全 |
 # 后续计划
-下一周期核心交付物与关键时间节点如下：
-- **三个厂区资料汇总**：技术组在验收完成第一时间将三个厂区的资料全部汇总于卢萨卡，包括竣工图进行分类汇总、分类组卷及编码。
-- **现场实体整改**：严格按照方案编制要求进行逐一整改和落实。
-- **混凝土路面开裂整改**：管理组和总包单位共同研究会同制定科学合理整改方案，研究出技术方案后尽快整改，争取在末次会之前、最迟出报告之前完成整改，报告里形成闭环，出报告之前完成整改后验收组还要复核。
-- **成品保护**：交给外方之前继续做好成品保护，有破损的地方及时修补。
-- **不可预见费**：放在末次汇报再进行沟通。
-- **姆皮卡点现场验收**：会后及时安排接下来的工作，验收组即将前往姆皮卡点。
-*依赖前提：赴姆皮卡路途遥远、赞比亚雨季路况不好，需注意交通安全；同时注意新冠疫情防控。*</t>
+**核心交付物**：
+- **技术组收集所有参与项目现场人员的护照证书**，完善人员履约资料。
+- **技术组将三个厂区资料全部汇总至卢萨卡**，包括竣工图，进行分类汇总、分类组卷及编码。
+- **技术组编制现场实体整改方案**，并逐一整改落实。
+- **管理组和技术组细化验收组提出的问题**，制定方案处理并落实整改。
+**关键时间节点**：
+- 路面开裂问题在出报告前完成整改，形成闭环，验收组复核。
+- 验收组后续将开展姆皮卡点现场验收。
+**依赖前提**：*混凝土路面开裂原因需先分析明确，再制定整改方案*；*不可预见费使用的依据证据和数据需完善，后续专门对接*。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>11110/5414</t>
+        <v>55.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11110/2133</t>
         </is>
       </c>
     </row>
@@ -3110,21 +3066,21 @@
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-本次会议由中金公司策略组刘刚凯文主持，为每周一度的中金宏观策略周会，围绕大美丽法案、关税谈判、港股流动性三大宏观议题展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒首席分析师张雪琴分别更新光伏反内卷、人形机器人和游戏板块。会议核心信息包括：大美丽法案三大块为提高债务上限约5万亿美元、延长2017年减税（新增支出3.4万亿、一年3400亿）、取消899条款；关税收入每年3000~4000亿可对冲支出，赤字率基本维持5~6%；7~9月发债约1万亿带来流动性抽水，美债利率可能上行但幅度或小于2023年（3.8~5%）。整体基调为：对美股美债不悲观，三季度有流动性波折但波动提供再配置机会，四季度美元可能小幅走强、美股可能反弹跑赢；光伏反内卷有望夯实行业底部；人形机器人三季度是从迷茫期到商业兑现的过渡阶段；游戏板块旗帜鲜明看好，认为调整后更健康可上车。
+本次中金宏观策略周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性、光伏反内卷、人形机器人及游戏板块等热点展开，向投资者汇报宏观策略与行业最新观点。刘刚凯文分析大美丽法案三大块内容，认为信用周期改善，对美股美债不悲观，三季度有流动性波折但波动提供再配置机会；关税大概率是谈判技巧，市场静观其变；港股流动性三季度边际收紧，但基本面强可盖过影响。行业方面，刘佳妮、郭文秀、张雪琴分别就光伏反内卷、人形机器人、游戏板块给出投资观点，整体基调偏积极，强调在结构性行情中于合适位置布局长期正确板块。
 # 核心信息
-大美丽法案三大块：一是提高债务上限约**5万亿美元**，违约风险消除；二是延长2017年减税，新增支出**3.4万亿**（一年**3400亿**），同时减掉其他支出**1.4万亿**；三是取消899条款。关税收入每年**3000~4000亿**可对冲支出，赤字率基本维持**5~6%**。7~9月发债约**1万亿**带来流动性抽水，美债利率可能上行但幅度或小于2023年（**3.8~5%**），期限溢价已处**2013年以来高点**。关税有效税率约**10~12%**，极端回到**18%**，通胀年底抬升至**3.3~3.4%**但不改变路径。港股指数在**23000~24000**区间震荡。光伏主产业链四环节产能严重过剩：电池为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来价格下跌**70~90%**；硅料现金成本**38元/公斤**，头部颗粒硅**28元**、尾部**45元**；多晶硅期货反弹至**40元/公斤**，硅片报价涨**10%**，电池涨**2分**。人形机器人二季度A股板块跌约**9%**、跑输机械**12个百分点**，特斯拉供应商标签股回调**30~40%**；宇树科技年收入破**10亿**，两家同时中标中国移动近**1.2亿**订单。游戏6月单月版号发放**158个**（国产**147**、进口**11**），为**2018年以来最高**；1~5月市场规模同比增长**17%以上**、手游增长**20%**；估值TTM PE约**30倍**、2025年静态PE约**20倍**。
+大美丽法案三大块：提高债务上限5万亿美元；延长2017年减税法案，新增支出3.4万亿美元，每年额外支出3400亿美元，同时减少新能源补贴等支出1.4万亿美元；取消899条款。刘刚凯文测算财政赤字率维持5-6%，关税收入可弥补支出，三季度美债供给压力约1万亿美元，可能推升利率但幅度或不及2023年。关税方面，有效税率10-12%，极端情况18%，通胀年底3.3-3.4%，关注8月1日、8月12日中美谈判及转口限制。港股流动性方面，港币弱至7.85，三季度流动性边际收紧。光伏行业产能过剩严重，硅料供需比超200%，硅片组件约2倍，电池1.5倍，价格下跌70-90%；反内卷政策升级，6月底至7月初高层多次发声，多晶硅期货价格反弹至40元/公斤。人形机器人二季度板块回调9%，跑输机械12个百分点。游戏板块6月版号单月发放158个（国产147个、进口11个），创2018年以来单月最高，1-5月市场规模同比增长17%，手游增长20%。
 # 官方表态
-刘刚凯文：&gt; 我们并不是完全的认同，去美元化这个观点的。现在成了一个高度趋同的共识。市场两个最大的误区：把美元弱当成去美元化；把美元弱和美股弱直接划等号。&gt; 波动提供再配置的机会，我们重申我们这个观点并不悲观。&gt; 在合适的位置拿长期正确的板块。刘佳妮：&gt; 随着反内卷的力度不断的强化升级，我们相信就是价格的恶性竞争有望告一段落。&gt; 对于硅料的整合其实是最为迫切的。郭文秀：&gt; 三季度将是一个二季度的迷茫期到商业兑现过度的这样的一个小阶段。&gt; 技术创新产业需求和工厂替代，往往这三重周期共振的时候，其实是孕育着比较不错的一个投资机会的。张雪琴：&gt; 我们的态度旗帜鲜明是后者（回调一下更健康可以上车）。&gt; 在消费政策和新品周期三重利好下面，游戏行业有望在调整后再次实现戴维斯双击。
+刘刚凯文对大美丽法案表态：提高债务上限至少使违约风险消失，可提振部分增长；延长减税并非新增减税，而是避免今年底大幅加税；取消899条款避免影响美元体系根基。对关税表态：关税一定会做，需维持一定税率（约10-12%有效税率）以收上3000-4000亿美元收入，不能太高以免通胀受不了，市场逐渐脱敏，威胁提高税率可能是谈判技巧。对港股流动性表态：美元美债利率并非绝对主导港股市场的唯一变量，自身基本面强可盖过影响，但三季度流动性边际收紧。刘佳妮对光伏反内卷表态：反内卷力度和政策级别进一步提升，价格恶性竞争有望告一段落，行业底部夯实。郭文秀对人形机器人表态：三季度是迷茫期到商业兑现的过渡阶段，关注三类信号。张雪琴对游戏板块表态：在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。
 # Q&amp;A环节
-问：关税威胁是否只是谈判技巧，还是真的会大幅提高？→ 答：刘刚凯文表示，关税四点信息：一定会做以支撑收入、需维持一定税率（10~12%有效税率即可收3000~4000亿）、不能太高否则通胀受不了、市场逐渐脱敏；姑且把它认作还是一个所谓的谈判技巧。问：加拿大墨西哥欧盟能否谈妥稳住？→ 答：刘刚凯文表示，加拿大墨西哥欧盟贸易占比太高，一定要和他们谈妥稳住，其他的这些国家即便增加一倍都不影响它的有效税率。问：8月12日中美谈判及转口限制进展如何？→ 答：刘刚凯文表示，需要关注8月12号中美谈判进一步的进展，尤其是一些转口的限制；越南的转口限制是40%，我们比这个税率还要低。问：光伏反内卷具体干预措施尚未披露，细节待明确？→ 答：刘佳妮表示，目前我们并没有看到一个干预措施的一个具体的披露，政府近期对于这个光伏行业的接连的发生，说明了光伏产业对于作为一个国家重要的名片的一个重要性。问：组件价格能否跟涨传导，下游电站能否接受产业链价格上涨？→ 答：刘佳妮表示，组件价格也有跟涨的一个意愿，但下游电站受136号文新能源全面入市政策影响，电价未来不确定性大幅增加，能否接受产业链价格上涨的传导还需观望未来一段时间的招标情况。问：特斯拉Optimus硬件问题何时解决，供应商筛选结果如何？→ 答：郭文秀表示，特斯拉由于存在非常多的硬件问题，包括电机的过热、灵巧手的负载不足、还有一些续航问题，目前整体特斯拉是在变更他的方案，包括他的目前的供应商从供应商的一个层面上还是在去进行筛选。</t>
+问：大美丽法案对美股、美债、美元流动性及港股流动性有何影响？答：刘刚凯文分析法案三大块，认为信用周期改善，财政赤字率维持5-6%，三季度美债供给压力约1万亿美元，可能推升利率但幅度或不及2023年，美股美债波动提供再配置机会，四季度美元可能小幅走强，对港股流动性边际偏负面但基本面强可盖过。问：关税升级为何市场反应冷静？答：刘刚凯文总结四点：关税一定会做、需维持一定税率、不能太高、市场逐渐脱敏；新变化为时间拖后、大部分税率较4月2日回落，有效税率10-12%，极端18%，通胀压力可控，市场静观其变。问：光伏反内卷政策对行业有何影响？答：刘佳妮介绍反内卷政策升级，高层多次发声，硅料环节最易整合，光伏玻璃第二轮产能出清，多晶硅期货价格反弹至40元/公斤，现货上涨，组件价格跟涨意愿但下游接受度待观察。问：人形机器人三季度有哪些催化剂？答：郭文秀提出三条主线：华为云生态开放、本土企业技术闭环、特斯拉延期带来的硬件替代窗口，关注物流场景、电机过热、轻量化等方向。问：游戏板块调整后是否还有机会？答：张雪琴认为政策友好、版号发放创新高，中型厂商新品成为核心催化，估值TTM PE约30倍，2025年静态PE约20倍，新品利润有滞后性，明年兑现，调整后有望戴维斯双击。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>22868/2070</t>
+        <v>52.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22868/1583</t>
         </is>
       </c>
     </row>
@@ -3439,31 +3395,21 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次班会课以「梦想」为主题，教师先请学生分享梦想，有同学说想当保安、喜剧人、太空人、世界冠军、主角、歌手等，并让想当歌手的同学上台唱了两首歌，约定结束时可自愿再唱一首。教师随后分享自己的梦想是成为受学生喜爱、有名望的优秀人民教师，并讲述曾单考通过中国美术学院却因离家远和没钱未去，最终就读广东技术师范大学（原民族学院），作为定向生免学费、定向回龙川县教书，当时哭了三天但现在很开心；大学梦想包括加入学生会、参加各类比赛、保持专业排名第一（专业41人）、考教师资格证、保研等，并说明定向不能考研、只能在职考研且学费自交。教师组织4个大组作为梦想观察团，观察玩航模的小伙子和想成为歌手的普通人两个对象，播放视频后总结航模小伙通过努力走上更大舞台、普通人唱歌走调可通过后天学习调整，讨论得出实现梦想的条件包括坚持、努力、天赋只占1%、勇敢、机会、兴趣、能力、学习等，并小结学习、坚持、行动是梦想条件必不可少的三个。教师又以马云中考考两次、高考多次为例说明起点高低不重要、看能否坚持，提到马云新梦想是希望未来15年世界因他们而改变、享受改变他人的乐趣，并讨论梦想可以一步步立高，如考不进年级前50可先调整为前百再定前50，强调每个人的梦想都是独一无二、不可复制的。最后教师让学生拿出纸写下自己的梦想清单，可列第1、第2、第3个，实现后打勾，并思考实现梦想需要的时间和收获，随后分享部分同学的梦想，建议梦想写得实在、诚恳一点，可先定小目标再定大目标，量力而行并调整，并请各小组第1个同学收齐每位同学的梦想。
+本次班会课以“梦想”为主题，老师先询问学生的梦想，学生回答包括当保安、喜剧人、太空人、世界冠军、歌手等。老师分享自己的梦想是成为受学生喜爱的有名望的优秀人民教师，并讲述个人经历：曾梦想考中国美术学院，单考通过但未就读，因离家远和没钱，后选择定向生，就读广东技术师范大学（原民族学院），毕业后回龙川教书。老师还分享大学梦想：加入学生会、参加比赛、保持专业排名第一（专业41人，大学四年排名第一）、考教师资格证。随后播放航模爱好者和普通歌手追梦的视频，讨论实现梦想的条件：坚持、努力、勇敢、机会、兴趣、能力、学习。最后让学生写下梦想清单，并分享部分学生的梦想。
 # 核心知识点梳理
-**梦想的含义与价值**：以丑小鸭想变成白天鹅引入，说明梦想值得尊重，不被嘲笑的梦想才是梦想，每个人的梦想都是独一无二、不可复制的。
-**实现梦想的条件**：通过梦想观察团游戏，观察玩航模的小伙子与想成为歌手的普通人两个案例，得出条件包括**坚持、努力、勇敢、机会、兴趣、能力、学习**；其中天赋只占1%；⭐ 难点在于理解「机会永远都是留给有准备的人」，以及缺少某一条件梦想仍可能实现、条件齐备则实现更快。
-**梦想条件必不可少的三个**：`学习`、`坚持`、`行动`。
-**梦想的调整与阶梯**：梦想可以一步步立高，如考不进年级前50可先调整为前百，再定前50；要量力而行并适时调整。
-**案例**：航模小伙何聪发带着歼10模型表演，想让顶级选手看到进步、在明年世界锦标赛上再一比高下；马云中考考两次、高考多次，起点高低不重要，看能否坚持，其新梦想是希望未来15年世界因他们而改变，享受改变他人的乐趣。
+**梦想的定义与价值**：梦想是个人追求的目标，每个梦想都值得尊重，不被嘲笑的梦想不是梦想。**实现梦想的条件**：坚持、努力、勇敢、机会、兴趣、能力、学习，其中学习、坚持、行动是必不可少的三个条件；机会留给有准备的人。**梦想的调整与分阶段实现**：梦想可以分阶段调整，如先定小目标再定大目标，目标实现不了可调整。**案例**：老师个人经历（考中国美术学院未就读，后定向就读广东技术师范大学，回龙川教书）；航模爱好者何宗发通过努力走上更大舞台；普通歌手通过后天学习调整唱歌走调。⭐ **难点**：梦想与现实的平衡，如定向生不能考研但可在职考研。
 # 课堂互动与答疑
-问：实现梦想需要具备哪些条件？ → 答：坚持、努力、勇敢、机会、兴趣、能力、学习等，其中天赋只占1%，机会永远留给有准备的人。
-问：如果缺少了一个条件，梦想还会实现吗？ → 答：具备某一个条件梦想都有可能实现，若条件都具备则会更加快速地实现梦想。
-问：考不进年级前50怎么办？ → 答：可先把梦想调整为考进年级前百，考进后再定前50，一步步往前。
-问：马云的梦想是不可复制的吗？ → 答：每个人的梦想都是不可以复制的，都是独一无二的。
-&gt; 不被嘲笑的梦想就是梦想。
-&gt; 梦想还是要有的，万一实现了呢？
-&gt; 机会都是留给有准备的人。
+问：老师以前的梦想是什么？答：考中国美术学院，单考通过但未就读，因离家远和没钱，后选择定向生，就读广东技术师范大学。问：实现梦想需要什么条件？答：坚持、努力、勇敢、机会、兴趣、能力、学习。问：梦想实现不了怎么办？答：可以调整目标，如先考进年级前百再考前50。&gt; 老师原话：“不被嘲笑的梦想不是梦想。”“机会都是留给有准备的人。”
 # 课后任务与学习建议
-教师布置：请同学们拿出纸写下自己的梦想清单，可列第1个、第2个、第3个，实现后给清单打勾，并思考实现梦想需要的时间和实现后收获了什么。写完后每个小组的第1个同学收齐每位同学的梦想。教师建议梦想写得实在一点、诚恳一点，可先定小目标再定大目标，量力而行并适时调整。</t>
+老师布置学生写下自己的梦想清单，列出梦想、实现所需时间及实现后的收获，写完后由每组第一位同学收齐交给老师。老师强调复习重点：实现梦想的条件（坚持、努力、勇敢、机会、兴趣、能力、学习），并建议学生将梦想分阶段调整，先定小目标再定大目标。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>9362/1500</t>
+        <v>24.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9362/877</t>
         </is>
       </c>
     </row>
@@ -3638,20 +3584,20 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次报道围绕新思想引领新时代改革开放，重点阐述以文化自信筑牢强国复兴精神之基：党的十八大以来，习近平总书记以文化自觉与历史担当推进文化建设，在“五位一体”总体布局中对文化建设作战略部署，在全面深化改革中纵深推进文化体制改革；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展；坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革，深化国有文艺院团改革，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。报道同时汇总多领域运行情况：全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议；今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高，夏粮单产每亩375.2公斤，其中小麦单产399.1公斤、比2023年增加10公斤；6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；上半年我国快递业务量超800亿件，截至6月30日已达800亿件；今年以来我国油气管网预计全年新增管道里程超4000公里，目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米、增幅达48%。防汛与国内国际动态方面：7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众；安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来一次洪峰流量45000立方米每秒量级的洪水过程。国内快讯包括北京上半年计划新开工的320个市区重大项目已全部实现开工、总投资超过4000亿元，燕矶长江大桥北岸主塔封顶、下一步转入主缆施工阶段，第二十三届环青海湖国际公路自行车赛在海北州门源县收官，“中非儿童手拉手”活动在中国儿童中心启动；国际快讯包括美联邦调查局称前总统特朗普在宾夕法尼亚州巴特勒市竞选集会遭未遂刺杀、枪手被特勤局狙击手打死、具体作案动机有待查明，以军空袭加沙地带南部汗尤尼斯马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明谴责，加拿大东北部纽芬兰与拉布拉多省林火蔓延、拉布拉多城9600人被疏散。
-## 文化建设与中俄议会合作
-- 围绕文化兴国运兴、文化强民族强，阐述党的十八大以来习近平总书记以文化自觉与历史担当推进文化建设，在“五位一体”总体布局中对文化建设作战略部署，在全面深化改革中纵深推进文化体制改革；提及“文博热”“文创风”“国潮”及14亿多中国人文化自信增强；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性与“两个结合”，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想；《深化文化体制改革实施方案》为中央深改小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展；坚持社会效益首位、社会效益和经济效益相统一，推进文化领域供给侧结构性改革，深化国有文艺院团改革，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”。
-- 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议；赵乐际转达习近平主席问候，指出今年是中俄建交75周年，中国全国人大愿同俄罗斯联邦会议从立法机构层面落实两国元首重要共识；普京请赵乐际转达对习近平主席的问候，表示俄中立法机构保持高水平合作；马特维延科表示发展对华关系得到俄社会广泛认同和支持，沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政；10日赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作等；访问期间赵乐际在莫斯科向俄无名烈士墓敬献花圈。
-## 经济民生运行与防汛动态
-- 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤，单产恢复性增长是夏粮产量增加的主要原因；中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金；小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；化肥农药运量增幅最大，同比增长26.2%，煤炭日均装车量、集装箱、商品汽车、冷链货物发送量等均创历史同期新高；6月份中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件；快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件。今年以来我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米；目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米；按照规划，到2025年天然气“全国一张网”将更加完善，初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众；强降雨导致安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌；水利部针对“七下八上”防汛关键期即将到来和雨情水情形势逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将再迎来一次洪峰流量45000立方米每秒量级的洪水过程，水利部今天联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。</t>
+会议围绕文化自信与中华民族现代文明建设展开，回顾了党的十八大以来文化体制改革成就，强调以文化自信筑牢强国复兴精神之基，推动中华优秀传统文化创造性转化、创新性发展，建设中华民族现代文明。会议报道了赵乐际于7月9日至13日对俄罗斯进行正式友好访问并出席中俄议会合作委员会第九次会议，双方强调从立法机构层面落实两国元首共识，深化多层级、多领域、多渠道交流合作，俄方坚定恪守一个中国原则。会议通报了夏粮产量创历史新高（2996亿斤，比2023年增加72.5亿斤）、6月份国家铁路货运多项指标稳定增长（发送货物3.32亿吨，同比增长6.1%）、上半年快递业务量超800亿件、油气管网建设提速（预计全年新增管道里程超4000公里）等经济与基础设施领域进展，以及渝川皖等地应对降雨天气的防汛安排。
+## 文化自信与中华民族现代文明建设
+- 强调文化自信的重要性，回顾习近平总书记对中华优秀传统文化的重视，提出‘两个结合’特别是‘第二个结合’的重大意义。2023年6月召开文化传承发展座谈会，10月首次提出习近平文化思想。实施《深化文化体制改革实施方案》和《关于实施中华优秀传统文化传承发展工程的意见》，推动文化领域供给侧结构性改革，深化国有文艺院团改革，坚持以社会主义核心价值观引领文化建设。
+- 赵乐际于7月9日至13日对俄罗斯进行正式友好访问，会见普京，与马特维延科、沃洛金会谈，出席中俄议会合作委员会第九次会议。双方强调从立法机构层面落实两国元首共识，深化多层级、多领域、多渠道交流合作，俄方坚定恪守一个中国原则。
+## 经济与基础设施领域进展
+- 夏粮产量达2996亿斤，比2023年增加72.5亿斤，单产每亩375.2公斤，小麦单产399.1公斤；6月份国家铁路发送货物3.32亿吨，货运周转量2665亿吨公里，同比分别增长6.1%、5.3%；上半年快递业务量超800亿件，日均业务量近5亿件；油气管网预计全年新增管道里程超4000公里，西气东输四线投产后年输气能力提升150亿立方米。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>7755/2993</t>
+        <v>32.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7755/848</t>
         </is>
       </c>
     </row>
@@ -3890,42 +3836,21 @@
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课为三讲光学中的第一讲，部分同学是新学、部分是复习，内容涵盖光的直线传播、光的反射（平面镜、凸面镜、凹面镜即球面镜）、光的折射（凸透镜、凹透镜）及透镜应用（显微镜、望远镜），初中光学统称几何光学，高中不再讲几何光学而讲干涉、衍射。光源定义为自身能够发光的物体，分自然光源（太阳、萤火虫）与人造光源（火把、蜡烛、煤油灯、电灯），光线用带箭头直线表示、是物理模型并非真实存在。光在均匀介质中沿直线传播，实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成；小孔成像一定成倒立实像、放大缩小不一定、与孔形状无关。光在真空中传播速度为3×10^8米每秒即3×10^5千米每秒，约每秒绕地球赤道7圈半，水中约为真空中的3/4、玻璃中约为2/3。光的反射定律为反射光线、入射光线和法线在同一平面内，反射光线与法线、入射光线分居法线两侧，反射角等于入射角；平面镜成正立、等大的虚像；凸面镜对光线起发散作用、成正立缩小的虚像，凹面镜对光线起会聚作用、有焦点F。
+本次课程为初中物理光学复习课，系统讲解光的直线传播、光速、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。光源分为自然光源（太阳、萤火虫）与人造光源（电灯等），光线是带箭头的直线，为物理模型；光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。光在真空中速度为3×10^8米/秒，空气中略慢，水中为真空中的3/4，玻璃中为2/3。
 # 核心知识点梳理
-**几何光学**：初中光学（直线传播、反射、折射）统称几何光学，2000多年前古希腊哲学家已发现相关规律；高中不再讲几何光学，转而讲干涉、衍射。
-**光源**：自身能够发光的物体。自然光源如太阳、萤火虫；人造光源从火把、蜡烛、煤油灯到电灯。
-**光线**：用带箭头的直线表示，是物理模型，并非真实存在。光源按形状可分点光源（如蜡烛）和平行光源（如太阳）。
-**光在均匀介质中沿直线传播**：可用玻璃罩加熏香或点香、激光笔照射证明；吸管弯折后激光打不到墙上同一点。实例包括三点一线瞄准、队列看齐、木工看尺、激光准直、小孔成像、日食月食、影子形成。
-⭐ **小孔成像**：一定成倒立实像，放大缩小不一定，与孔形状无关，如树荫下光斑。
-⭐ **日食月食**：日食为太阳、月球、地球同一直线且月球在中间，分日全食、日偏食、日环食；月食为太阳、地球、月球同一直线且地球在中间，月偏食是月球部分在1号区域、部分在2或3区域。
-**光速**：真空中 `3×10^8米每秒` 即 `3×10^5千米每秒`，约每秒绕地球赤道7圈半；空气中约 `2.99×10^8米每秒`，近似取 `3×10^8`；水中约为真空中的3/4，玻璃中约为2/3。练习中激光从地球到月球1.25秒，距离为 `3.75×10^8米`；雷电先见闪电后闻雷声因光速比声速快，15度时声速340米每秒。
-**光的反射定律**：通过硬纸壳、透明胶带、平面镜和激光笔的探究实验验证。定义入射光线AO、入射点O、反射光线OB、法线OP（垂直于镜面、是角AOB的角平分线）、入射角与反射角；法线不存在、画虚线。三句话：反射光线、入射光线和法线在同一平面内（共面）；反射光线与法线、入射光线分居法线两侧；反射角等于入射角。垂直入射时入射角和反射角均为0度，反射光线与平面镜夹角40度时入射角为50度；作图先画法线、保留作图痕迹、利用对称找点。
-**镜面反射与漫反射**：镜面反射是平行光射到光滑镜面后反射光线仍平行、只在特定方向看到反射光；漫反射是表面凹凸不平时反射光线射向各个方向、生活中大多数反射是漫反射。黑板、电影银幕、投影幕布发生漫反射，黑板反光看不清字是镜面反射；无论镜面反射还是漫反射都遵守光的反射定律。雨后夜晚迎着月光走亮处是水潭、背着月光走暗处是水潭；光路可逆。
-**平面镜成像**：实验用玻璃板代替平面镜以便移动蜡烛找像，用刻度尺比较像与物到镜面的距离，选两段完全相同蜡烛比较像与物大小；平面镜成正立、等大的虚像，不能用光屏承接，像与物连线与镜面垂直、像到镜面距离与物到镜面距离相等；玻璃板与水平面不垂直或玻璃板有厚度（两面反射成像）会导致数据不相等或看到两个像；平静水面、光滑金属表面可充当平面镜。
-**球面镜**：凸面镜对光线起发散作用、成正立缩小的虚像，用于汽车后视镜、丁字路口拐弯处；凹面镜对光线起会聚作用、有焦点F，用于手电筒、汽车前大灯、探照灯、耳鼻喉科医生头镜、西藏太阳灶；作图可用以直代曲方法。
+**光源**：自身能够发光的物体，分为自然光源（太阳、萤火虫）与人造光源（电灯等）。**光线**：带箭头的直线，是物理模型，并非真实存在。**光在均匀介质中沿直线传播**：实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。⭐ **小孔成像**：成倒立、实像，放大或缩小取决于物距与像距，与孔形状无关。**光速**：真空中为3×10^8米/秒，空气中略慢，水中为真空中的3/4，玻璃中为2/3。**光的反射定律**：三线共面、分居两侧、反射角等于入射角；法线为辅助线，垂直镜面，垂直入射时入射角为0度。**镜面反射与漫反射**：镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向，两者均遵守反射定律。**平面镜成像**：成正立、等大的虚像，原理是光的反射。**球面镜**：凸面镜发散，成缩小的像；凹面镜会聚，用于手电筒、太阳灶等。易混点：*小孔成像成倒立实像，平面镜成像成正立虚像*。
 # 课堂互动与答疑
-问 → 答：为什么用玻璃板代替平面镜做实验？→ 因为若用镜子虽有反射，但无法移动后面的蜡烛来找像，故用玻璃板代替平面镜。
-问 → 答：实验为什么选用刻度尺？→ 为了便于比较像与物相对镜面的距离。
-问 → 答：为什么选取两段完全相同的蜡烛？→ 为了比较像与物的大小。
-问 → 答：光屏能否接收到蜡烛的烛焰的像？→ 不能，因为实际光线没有到达后面，成的是虚像。
-问 → 答：记录数据中蜡烛到玻璃板的距离与像到玻璃板的距离有几组不相等，原因可能是什么？→ 一是玻璃板与水平面不垂直，二是玻璃板有厚度、它的两个面发生反射成像。
-问 → 答：在玻璃板同一侧看到同一个蜡烛的两个像，原因是什么？→ 玻璃板有厚度，它的两个面发生反射成像的结果。
-问 → 答：为什么引进法线？→ 主要是为后面讲折射作准备，法线真实不存在，画虚线。
-&gt; 光线是真实存在的吗？我画一个写上它实际上是一个物理模型。
-&gt; 三点一线实际上原理是什么？就是这个光在均匀介质中沿直线传播。
-&gt; 光在真空中传播速度是3×10^8米每秒，基本上一秒钟绕地球赤道7圈半。
-&gt; 无论哪种反射都要遵守光的反射定律。
-&gt; 作图一定是先去做一条法线，作图痕迹要留下。
+问：为什么研究反射要引入法线？答：法线是辅助线，垂直镜面，便于统一描述入射角与反射角，也为后续学习折射做准备。问：光垂直射到镜面上，入射角是多少？答：0度，因为入射角是入射光线与法线的夹角。问：为什么用玻璃板代替平面镜做实验？答：玻璃板透明，便于确定像的位置。问：为什么玻璃板有厚度会看到两个像？答：玻璃板两个面都能反射成像。问：为什么平面镜成虚像？答：实际光线没有到达像的位置，是反射光线的反向延长线会聚而成。教师提醒：作图时先画法线，再根据反射角等于入射角画光线，作图痕迹要保留。
 # 课后任务与学习建议
-教师布置的课堂练习为练习第1至5题、第10和第11题、第13至24题等，要求当堂完成并讲解答案。复习重点为：光在均匀介质中沿直线传播及其实例、光的反射定律三句话、镜面反射与漫反射的区别、平面镜成像特点（正立、等大的虚像）、凸面镜与凹面镜的作用与应用。学习建议：可在家用纸杯底部用针扎小孔、蒙塑料布、点蜡烛做小孔成像实验；用硬纸壳、透明胶带、平面镜和激光笔做反射定律实验；用白纸和小镜子配合手电筒观察镜面反射与漫反射；建议购买激光笔辅助研究直线传播与反射实验。教师提醒注意保护眼睛，长时间看屏幕、判卷等最费眼睛，视力下降后矫正视力约0.7，应重视用眼健康。</t>
+本讲未布置书面作业，但强调复习重点：光的直线传播实例、光的反射定律、平面镜成像特点及实验注意事项、镜面反射与漫反射的区别。建议同学们在家用激光笔、纸杯、蜡烛等器材动手验证小孔成像和平面镜成像实验，加深理解。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>25691/2518</t>
+        <v>35.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25691/987</t>
         </is>
       </c>
     </row>
@@ -4036,33 +3961,45 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课为《电气工程基础》课程导论，该课是进入专业课接触的第一门课，也是专业入门课。教学目的有两个：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程要求对电路理论和电机学知识有一定了解，特别是变压器和同步电机相关知识要求较高，有欠缺的同学需下去补充；后续最重要的四门课程为电力系统分析、电力系统继电保护、电力系统自动化和高电压技术。第一章涉及电力系统基本概念最多、最重要，要求掌握电力系统、电力网、动力系统和变电站等基本概念，理解电力系统特点及由此引起的最基础理论，理解对电力系统提出的要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中心点接地方式特点。课程还梳理了电力发展简史、三相交流输电优势，以及电力系统形成与定义、电网分类与变电站分类。
+本次课程为《电气工程基础》导论，属于电气工程专业入门课。课程旨在使学生掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及整体关系，并掌握分析、设计、运行、管理的基础理论、技术与计算方法。前修课程要求电路理论和电机学知识，特别是变压器和同步电机；后续课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。第一章为概念最多且最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及要求，掌握电能质量指标国家标准，了解中心点接地方式。课程还梳理了电力发展简史，从早期直流输电到交流输电占主导，再到直流输电在联网中重新受关注，并介绍了电力系统的形成过程与电网分类。
 # 核心知识点梳理
-**一、课程定位与目标**：电气工程基础是进入专业课接触的第一门课、专业入门课。教学目的：①掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；②掌握电力系统分析、设计、运行管理方面最基础的理论、最基本的技术和基本计算方法。前修课程：电路理论、电机学，特别是变压器和同步电机相关知识要求较高。后续最重要的四门课程：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
-**二、第一章重点内容**：①学习和掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站；②理解电力系统的特点及由这些特点引起的设计运行等方面最基础的理论；③理解对电力系统提出的要求，涉及运行、设计和维护各方面；④掌握电力系统的电能质量指标，包括国家标准对这些指标规定的范围；⑤了解电力系统常用的接地方式，特别是工作接地即中心点接地方式的不同特点。
-⭐**三个学习难点**：①由电力系统特点引出的最基本原理，如电能不能大量储存，决定了电力系统的有功功率和无功功率的动态平衡问题；②电力系统额定电压的规定非常繁杂，要注意把这些规定搞清楚；③各种中心点的接地方式，直接影响后面所学习的多个章节内容，学习起来也比较困难。
-**三、学习方法建议**：对基本概念注意其内涵和外延，并适当结合实际；思考方法上从电力系统的特点要求出发，注意从最基础的原理去推导，不要去记结论，因为结论性东西在使用条件变化时就会发生变化；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。
-**四、电力发展简史**：电力发展从直流开始。福泰勒使用2000米导线连接瓦斯发电机，拖动直流发电机和电动机，证明直流远距离两公里输电可行。1874年俄国工程师在彼得堡建立4.5公里直流输电线路，功率4.5千瓦。1882年法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端343伏、末端850伏，输送功率200瓦，损耗78%。1883年德普勒进行14公里输电试验，输送功率1.1千瓦，损耗55%。1882年10月英国科学家发明直流输电三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展为五线制。19世纪末法国方剑将多台直流发电机串联提高电压，将75千瓦电力送75千米。20世纪初瑞典科学家在串联直流发电机上装短路器，之后20多年建15条直流输电线路，最大为1906年投运的法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦线路，1927年改建为260公里、125千伏、19000千瓦。直流输电受制约因素多、设备复杂、运行方式复杂、造价高、可靠性差。
-交流方面：1876年俄国科学家发明单相变压器，主要用于照明；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行；威斯汀豪斯与爱迪生进行交直流电力战争，爱迪生和凯尔文主张直流，威斯汀豪斯和特斯拉主张交流；1886年威斯汀豪斯在麻省进行1000米、30千伏交流输电示范，又在意大利建成17英里高压输电线路；1886年俄国科学家发明三相交流电和三相异步电动机；法国到德国的交流输电线路被认为是第一条交流输电线路。交流输电随高电压技术和绝缘技术发展：1898年发明真实绝缘子，美国加利福尼亚输电电压提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，首次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压1150千伏线路投运后降压到500千伏运行。国内：220千伏1941年投运，330千伏1972年投运，500千伏1981年投运，2009年1000千伏交流特高压投运。直流用于联网：1954年瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆，100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。中国第一个直流输电工程连接舟山群岛与浙江定海电网；第二个是1989年葛上直流，葛洲坝电厂到上海，±500千伏；今年6月投运云广直流±800千伏特高压直流工程。
-**五、三相交流输电优势**：交流指ABC三相对称系统，优点：①易于产生旋转磁场，三相电动机容易做驱动；②瞬时功率恒定，不随时间变化；③输电线路导线量即金属消耗量最少。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流。国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小。
-**六、电力系统的形成与定义**：最早单台发电机孤立向附近负荷供电，可靠性差。后将多台发电机连接起来提高可靠性，但导线有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离不能太长。解决办法是升高电压，电压升高后电流减小，有功功率损耗和电压降落减小，输电距离变长，采用变压器升压降压。这样构成电力系统雏形，多台发电机共同向负荷供电，可装大机组，供电范围越来越大，带来经济效益。输电距离很长时，中间装设变电站用降压变压器向当地供电，并解决稳定问题。现代电力系统：发电机发出电，通过升压变压器升压，经输电线路传输到负荷中心，再降压给用电设备使用。**电力系统**定义为变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能，由发电、输电、配电、用电四个环节组成。**电力网**是变压器和输电线路构成的网络，即电力系统去掉发电机和用电设备的部分。**动力系统**是电力系统基础上加上发电厂动力部分（如火电厂锅炉、汽机、煤炭输送处理系统，水电厂水轮机、水坝、水库等）。
-**七、电网分类与变电站分类**：按规模将电网分为地方电力网、区域电力网、超高压远距离输送网络。地方电力网向固定地方供电，电压等级早期35千伏及以下，现在常为110千伏及以下，供电半径20~50公里；区域电力网电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心；超高压远距离输送网络电压等级500千伏或1000千伏，东北有330千伏，主要任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统，如特高压系统从山西晋东南到湖北荆门，跨三省，连接华北电网和华中电网。举例：武汉电网属地方电力网，主要供电电压110千伏和35千伏，少数220千伏；华中网是典型区域网；葛上直流、三峡到上海输电线路属超高压远距离输电网络。变电站分类常见三种：按电压等级分类，按最高电压等级称为多少千伏变电站，如华工变电站10千伏、关山变电站220千伏、凤凰山变电站500千伏；按主要功率流通方向分为升压变电站和降压变电站，大部分功率从高压侧向低压侧传输为降压变电站，从低压侧向高压侧为升压变电站。
+**课程目标**：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及整体关系；掌握分析、设计、运行、管理的基础理论、技术与计算方法。
+**第一章重点**：
+- 基本概念：`电力系统`、`电力网`、`动力系统`、`变电站`。
+- 电力系统特点及要求，电能质量指标国家标准，中心点接地方式。
+⭐ **难点**：
+1. 由电力系统特点引出的基本原理，如电能不能大量储存决定的有功功率和无功功率动态平衡问题。
+2. 电力系统额定电压的规定繁杂，需理清规律。
+3. 各种中心点接地方式的特点及其对后续章节的影响。
+**电力发展简史**：
+- 直流输电早期试验：1874年俄国彼得堡4.5公里直流线路；1882年法国德普勒57公里试验线路（首端电压343伏，末端850伏，输送功率200瓦，损耗78%）；1883年14公里试验（输送功率1.1千瓦，损耗55%）。
+- 直流输电受电压提升困难限制，19世纪末法国方剑串联直流发电机送75千瓦电力75千米；20世纪初瑞典科学家加装短路器，20多年建15条直流线路，最大为1906年法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦。
+- 交流输电发展：1876年俄国发明单相变压器；1883年特斯拉制造感应电机；1885年匈牙利科学家设计变压器并联运行；1886年威斯汀豪斯在美国麻省示范1.2千米30千伏交流输电，又在意大利建成17英里高压线路；1886年俄国发明三相交流电。
+- 交直流电力战争：爱迪生与凯尔文主张直流电，威斯汀豪斯与特斯拉主张交流电；交流电因变压器升压优势胜出。
+- 电压等级提升：1898年发明瓷绝缘子，美国33千伏；1906年悬式绝缘子，110千伏；1912年发现电晕临界电压与导线直径成比例，美国154千伏；1923年均压阀技术，220千伏；1936年美国287千伏；1952年瑞典380千伏（首次采用分裂导线）；1956年苏联400千伏双回线路；1965年加拿大735千伏；1969年美国765千伏；1985年苏联1150千伏特高压（后降压至500千伏运行）。
+- 中国：1941年220千伏投运；1972年330千伏；1981年500千伏；2009年1000千伏交流特高压投运。
+- 直流输电在联网中重新受关注：1954年瑞典本土与哥特兰岛世界首个工业海底电缆工程（100千伏、96公里，汞弧阀）；1970年扩建50千伏1万千瓦晶闸管换流阀试验工程；1972年加拿大世界首个晶闸管换流阀背靠背直流工程；中国首个直流输电工程连接舟山群岛与浙江定海；1989年葛上直流（葛洲坝电厂到上海）±500千伏；今年6月云广直流±800千伏特高压直流工程投运。
+**三相交流优势**：
+- 三相交流系统三个优点：①易于产生旋转磁场，三相电动机易做驱动；②瞬时功率恒定；③输电线路导线金属消耗量最少。
+- 三相三线制传输效率最高、金属消耗量最小，因此在交流输电中占主导地位。
+**电力系统的形成**：
+- 从单机向负荷供电，通过并联发电机提高可靠性；但输电线路电阻电抗导致电压损耗和功率损耗，需升压传输。
+- 电力系统由发电机、变压器、输电线路、用电设备组成，完成生产、输送、分配、消耗职能。
+- `电力网`：去除发电机和用电设备的部分；`动力系统`：电力系统加上发电厂动力部分（如锅炉、汽机、水轮机等）。
+- 电网按规模分类：`地方电力网`（110千伏及以下，供电半径20-50公里）、`区域电力网`（110-500千伏，供电半径超50公里）、`超高压远距离输送网络`（500千伏及以上，跨省跨地区）。
+- 变电站分类：按最高电压等级（如10千伏、220千伏、500千伏变电站）；按功率流向分为升压变电站和降压变电站。
 # 课堂互动与答疑
-问：我们国家为什么采用交流、为什么采用三相三线制？→ 答：交流指ABC三相对称系统，至少具有三个方面的优点：第一，易于产生旋转磁场，因此三相电动机很容易做驱动；第二，瞬时功率是恒定的，不随时间变化；第三，输电线路所采用的导线量即金属消耗量最少。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此三相三线制输电系统在交流输电领域得到广泛应用。除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电都采用三相交流，只有在联网过程中才采用直流联网方式。
-&gt; 对基本概念，我们要注意它的内涵和外延，并且适当地结合实际。
-&gt; 对于思考的方法，我们要从电力系统的特点要求出发，注意从最基础的原理去进行推导，不要去记一些结论。
-&gt; 这些结论性的东西，往往当它的使用条件变化的时候就将发生变化。
-&gt; 关于这方面的内容，我希望大家下去做一些进一步的阅读，作为电气专业的学生，我们应该了解我们电力发展的一个基本的发展史。
+课堂中教师提到，多年以来很多同学上课时问到“我们国家为什么采用交流？为什么采用交流三相三线制？”教师通过讲解三相交流系统的三个优点（易于产生旋转磁场、瞬时功率恒定、导线金属消耗量最少）及三相三线制传输效率最高、金属消耗量最小来解答。教师还提醒，对于基本概念要注意其内涵和外延，并适当记忆；思考方法要从电力系统的特点要求出发，从最基础的原理去推导，不要只记结论，因为结论在使用条件变化时可能失效。
 # 课后任务与学习建议
-教师推荐三本书，供大家下去阅读。教师强调第一章为重点内容，要求大家以重点内容进行掌握，并提醒学完章节后仔细体会学习方法：注意基本概念的内涵和外延并适当结合实际；从电力系统的特点要求出发，从最基础的原理去推导，不记结论；注意寻找额定电压规定之间的基本规律；注意比较各种不同中心点接地方式之间的特点。教师要求对电路理论和电机学知识有欠缺的同学下去把相关内容做一定的补充，特别是变压器和同步电机的相关知识。教师希望学生下去对电力发展史方面的内容做进一步的阅读，了解电力发展的基本发展史。原文未提及具体作业提交要求。</t>
+教师推荐三本书供学生课后阅读，以了解电力发展的基本历史。教师强调，作为电气专业学生应了解电力发展的基本发展史。第一章为本章重点内容，学生应掌握基本概念、电力系统特点及要求、电能质量指标国家标准、中心点接地方式等。学习方法建议：①对基本概念注意内涵和外延，适当记忆；②从电力系统特点要求出发，从最基础原理推导，不记结论；③寻找额定电压规定之间的基本规律；④比较不同中心点接地方式的特点。对电路理论和电机学知识（特别是变压器和同步电机）有欠缺的同学，应下去补充相关内容。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>11163/4089</t>
+        <v>48.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11163/2332</t>
         </is>
       </c>
     </row>
@@ -4143,25 +4080,39 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本笔记围绕调和级数收敛与发散这一经典问题展开，核心议题是评论 Stack Exchange（MSE）上网友对该问题的多种证明思路。UP主皮卡从高中数学讲起，先给出级数收敛与发散的简化定义：序列 `an=1/n`，前n项和 `sn`，若所有 `sn` 都小于某个固定实数 `a` 则收敛，若 `sn` 大于某个无界递增的 `bn` 则发散。随后评论了网友的分组求和证明，并补充柯西凝聚判别法，指出其证明过程与分组求和一模一样，对非负不增序列，收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1。UP主还联想到高斯求和 `1+2+…+100` 时用 `1+100`、`2+99` 等分组，每组 `101`，说明分组求和思路普遍。第二个证明用调和数 `hn` 大于 `log(n+1)` 证明发散，涉及积分估计与差分两种流派；网友取对数将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`，UP主认为这与差分方法本质相同，是故弄玄虚。第三个流派用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+本笔记围绕调和级数收敛性的证明方法展开，源自皮卡在Stack Exchange上对网友回答的评论。皮卡首先介绍了级数收敛与发散的定义，随后评述了分组求和、柯西凝聚判别法、积分估计、对数差分等证明思路，并指出这些方法背后的本质联系。他批评了某些证明的故弄玄虚，认为其本质是简单的分组或积分估计，却故意写成复杂形式，妨碍理解；同时指出部分证明（如对数差分、Stolz定理）有“先射箭后画靶”之嫌，不够自然。皮卡计划根据本期视频的反响决定是否继续该系列。
 # 核心概念
-**级数收敛与发散的定义**：序列 `an=1/n`，前n项和 `sn=1+1/2+…+1/n`。若所有 `sn` 都小于某个固定实数 `a`，则收敛；若 `sn` 大于某个明显递增且无界的 `bn`，则发散。
-**分组求和证明**：将 `1/2+1/3` 分为一组，`1/4` 至 `1/7` 为一组，`1/8` 至 `1/15` 为一组，每组和都大于 `1/2`，任意多组相加无上界，故发散。
-**柯西凝聚判别法**：证明过程与分组求和一模一样，对非负不增序列，其收敛发散性等价于 `2^k·(1/2^k)` 的收敛发散性，和等于1，便于判断增长缓慢的序列。
-**高斯求和**：`1+2+…+100` 用 `1+100`、`2+99`、`3+98` 等分组，每组 `101`，只需数有多少个 `101`，体现分组求和思路的普遍性。
-**调和数 `hn` 与 `log(n+1)`**：第二个证明用 `hn` 大于 `log(n+1)` 证明发散，`log` 无上界故 `hn` 无上界；有积分估计流派和差分流派，积分估计用矩形面积近似 `hn` 并放缩。
-**取对数与连乘积**：网友两边取对数，利用 `e^(a+b)=e^a·e^b` 将和变为连乘积，放缩 `e^(1/k)&gt;1+1/k`，连乘积相邻相消得 `n+1`。
-**Stolz 定理**：第三个流派试图证明 `hn` 与 `log n` 同增长级别，用 Stolz 定理求 `hn/log n` 极限为1，UP主认为这是先知道结果再凑，不自然。
+**级数收敛与发散的定义**
+- 对于正向级数，若所有部分和 `sn` 都小于某个固定实数 `a`，则级数收敛；若部分和大于某个无界递增的 `bn`，则级数发散。
+**分组求和法**
+- 将调和级数分组，每组和均大于 `1/2`，从而证明其发散。
+- 皮卡指出，该思路与**柯西凝聚判别法**的证明过程完全一致，即通过分组估计部分和。
+**柯西凝聚判别法**
+- 对于非负不增序列，其收敛性与凝聚后的序列 `2^k * a_{2^k}` 相同。
+- 应用于调和级数时，等价于判断 `Σ 1` 的收敛性，显然发散。
+**积分估计法**
+- 利用积分曲线面积近似部分和，证明 `hn &gt; log(n+1)`，因 `log` 无上界，故调和级数发散。
+**对数差分法**
+- 通过 `e^{1/k} &gt; 1 + 1/k` 放缩，连乘积化简为 `n+1`，证明发散。
+- 皮卡认为此法与积分估计本质相同，但形式复杂，有“装逼”之嫌。
+**Stolz定理法**
+- 利用 `hn / log n` 的差分极限为 `1`，证明二者同阶，从而发散。
+- 皮卡批评此法不自然，属于“先射箭后画靶”。
 # 核心结论
-核心结论：调和级数发散，网友的分组求和证明、柯西凝聚判别法、`hn&gt;log(n+1)` 证明、取对数连乘积证明以及 Stolz 定理求极限均指向这一结论。易混淆点：**分组求和与柯西凝聚判别法证明过程一模一样**；**取对数连乘积方法与差分方法本质相同**；**Stolz 定理求 `hn/log n` 极限为1是先知道结果再凑，不自然**。待澄清问题：UP主表示后面还有很多方法，有机会再评论；下次是否出下一期取决于反响。</t>
+**核心结论**：调和级数发散，可通过分组求和、柯西凝聚判别法、积分估计、对数差分、Stolz定理等多种方法证明，这些方法本质相通。
+**易混淆点**：
+- **收敛与发散的定义**：需明确部分和是否有上界。
+- **柯西凝聚判别法**与分组求和法的证明思路完全一致。
+- **对数差分法**与积分估计法本质相同，只是形式不同。
+**待澄清问题**：皮卡未明确说明柯西凝聚判别法的完整证明细节，仅指出其与分组求和法相同；也未深入展开“dialectic分解”思路。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>7465/1391</t>
+        <v>22.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7465/982</t>
         </is>
       </c>
     </row>
@@ -4224,43 +4175,47 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本笔记围绕 GitHub 作为资源库的知识主题展开，核心议题包括 GitHub 上的实用热门项目、国内访问加速方法、页面汉化与搜索技巧，以及项目主页功能与热门项目跟踪方式。主要观点为：GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到，涵盖麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂面试题与面试经验，Google、阿里等大公司最新开源大模型，以及用 AI 搞副业赚钱的教程和 AI 学习资料等。整体逻辑框架为：先介绍正经与不正经的实用项目，再逐一解决访问、汉化、搜索等使用问题，最后说明文档整理与领取方式。
+本次视频由老李主讲，围绕GitHub这一资源平台，介绍了多个实用热门项目及访问、使用技巧。内容涵盖工作性价比评估、表情包合集、健康指南、证件照制作、健身指导、教材资源、AI视频生成、声音克隆、AI学习资源库等，并针对网络不通、页面全英文、搜索功能不好用等常见问题，分享了使用加速软件、镜像站、翻译插件、汉化插件及AI搜索等方法。老李还讲解了GitHub项目页面的基本功能，包括star、watch、fork的含义，以及about、release、read me、commit日期等要素，并推荐通过explore的trending查看热门项目。整体逻辑框架为：先介绍项目，再解决访问与使用问题，最后讲解页面功能。
 # 核心概念
-## **GitHub 资源库定位**
-GitHub 不只是全球最大的同性交友平台，更是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。正经资源包括麻省理工、斯坦福等名校公开课，字节、阿里、腾讯等大厂的面试题和面试经验，Google、阿里等大公司最新的开源大模型，用 AI 搞副业赚钱的教程，AI 学习资料等；不正经资源包括国内这些年全网火爆的表情包大合集、活到 150 岁养生指南、国内 996 最严重的大厂黑名单等。
-## **实用热门项目**
-- **B 班值不值得上**：评估工作性价比，输入年薪、工作地区、年假、通勤时长、学历、工作年限及领导同事是否 SB 等因素，综合给出工作性价比分数和评级。
-- **表情包博物馆**：国内过去这些年全网爆火的表情包大合集，包含甄嬛传、罗翔老师、特朗普、马保国等表情包。
-- **活到 150 岁指南**：分享经过科学研究证实的健康知识，如间歇性进食对身体有好处，会促进胆汁代谢、炎症自愈；吃天然发酵类食品可以改善肠道菌群生态等。
-- **一键做证件照**：上传一张大头照即可一键抠图换背景，生成不同标准的证件照和各种规格的打印模板。
-- **丐版健身教练**：可选择自重、哑铃、弹力带、长凳等，选择要练习的肌肉群后给出用身体自重练习的参考动画。
-- **PDF 教材合集**：收集国内所有小学、初中、高中一部分大学的 PDF 教材，全部免费用。
-- **全自动视频生成项目** `Morning Printer Turbo`。
-- **声音克隆模型** `ChatTTS`：零样本语言克隆，情感控制非常到位，克隆的声音就像真人说话一样。
-- **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI 等最新 AI 技术，教程内容整理成一份 500 多页的 PDF 文档，含大量示意图。
-- **awesome AI apps**：收录大模型最新的 agent 应用，如医学影像数据分析的 agent、AI 投资的 agent、竞争对手情报分析 agent 等。
-## **GitHub 访问加速方法**
-- **Watt Toolkit 加速软件**：进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选 GitHub 加速，即可流畅上 GitHub。
-- **GitHub 镜像站**：如 `gh proxy`，浏览器点开就直接上 GitHub，默认是镜像的项目地址，搜其他项目也没问题。
-- **魔法**：个人最推荐的方法。
-## **GitHub 页面汉化**
-给浏览器装翻译插件，推荐谷歌 `Translate` 或 `沉浸式翻译`，装好后可直接把网页翻译成中文；动手能力强的还可给浏览器安装汉化插件。
-## **GitHub 搜索技巧**
-- **原生搜索**：按搜索词精准匹配，搜 `screen record` 和 `screen recording` 按星标排序结果不一样。
-- **AI 搜索**：推荐用 ChatGPT 等工具，用中文指令如“在 github 上帮我找好用的录屏软件”，能搜全热门录屏工具并总结成表格。
-## **项目主页功能与热门项目跟踪**
-- **项目主页功能**：`star` 相当于收藏和点赞，`watch` 是关注项目，`fork` 是复制项目，`about` 是项目简介，`release` 是软件安装包，`readme` 是项目说明书，`commit` 日期可理解为最近更新时间。
-- **跟踪热门项目**：点开左侧 `explore`，在 `trending` 里能看到全站当天、本周、本月最热门的项目；也可用 ChatGPT 找 `github daily`。
+**GitHub热门项目**
+- **工作性价比评估**：项目“b班值不值得上”可输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等，综合评估工作性价比并给出分数和评级。
+- **表情包博物馆**：收录国内过去几年全网爆火的表情包大合集，如甄嬛传、罗翔、特朗普、马保国等。
+- **健康指南**：项目“教你健康的活到150岁”分享经科学验证的健康知识，如间歇性进食促进胆汁代谢、炎症自愈，吃天然发酵类食品改善肠道菌群等。
+- **一键做证件照**：上传大头照即可一键抠图换背景，生成不同标准证件照和打印模板。
+- **健身教练项目**：提供自重哑铃、弹力带、长凳等健身方式，可选择肌肉群并查看参考动画。
+- **教材合集**：收集国内小学、初中、高中及部分大学PDF教材，全部免费。
+- **全自动视频生成项目**：名为“morning printer Turbo”。
+- **声音克隆模型**：`chat box TTS`，零样本语音克隆，情感控制到位，克隆声音像真人。
+- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
+- **awesome AI apps**：收录大模型最新agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等。
+**GitHub访问与使用问题解决**
+- **网络加速**：使用`watch tool Kit`加速软件，进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可。
+- **镜像站**：如`gh proxy`，浏览器直接打开即可访问GitHub，可搜索其他项目，但速度和稳定性较差。
+- **魔法（VPN）**：老李个人最推荐的方法。
+- **注册**：用国内QQ邮箱即可注册GitHub。
+- **汉化**：给浏览器安装翻译插件，如谷歌浏览器的`谷歌translate`或`沉浸式翻译`，可翻译网页；动手能力强的可安装汉化插件。
+- **搜索**：GitHub原生搜索按关键词精准匹配，对国人不好用；推荐用AI工具如ChatGPT，用中文描述需求，AI可总结成表格。
+**GitHub项目页面功能**
+- **star**：相当于收藏和点赞，star数代表项目受欢迎程度。
+- **watch**：关注项目。
+- **fork**：复制项目到自己的账号。
+- **about**：项目简介。
+- **release**：软件安装包，可下载最新版本。
+- **read me**：项目说明书，默认在项目最下方展开，介绍项目用途、安装使用方法。
+- **commit日期**：最近更新时间，若更新日期是好几年前，项目可能无人维护。
+- **explore**：左侧explore中的`trending`可查看全站当天、本周、本月最热门项目。
 # 核心结论
-GitHub 是每个人都可以用的巨大宝藏资源库，几乎想找的资源、教程、工具都能找到。国内访问 GitHub 卡顿难，可用 Watt Toolkit 加速软件、gh proxy 等镜像站或魔法解决，其中 Watt Toolkit 更流畅，镜像站速度稳定性较差，个人最推荐魔法。页面满屏英文可装谷歌 Translate 或沉浸式翻译插件汉化。原生搜索按精准匹配，搜 `screen record` 与 `screen recording` 结果不一致，推荐用 ChatGPT 等 AI 工具以中文指令搜索。项目主页的 `star`、`watch`、`fork`、`about`、`release`、`readme`、`commit` 日期等功能需了解；跟踪热门项目可看 `explore` 的 `trending`，或用 ChatGPT 找 `github daily`。所有开源项目、教程及视频未提到的项目都整理在文档里，需要的可以三连关注免费领取。</t>
+**核心结论**：GitHub是巨大的资源库，能找到名校公开课、大厂面试题、开源大模型、AI学习资料等实用资源。访问GitHub推荐使用`watch tool Kit`加速软件（更流畅），镜像站速度和稳定性较差，最推荐使用魔法（VPN）。搜索项目时，GitHub原生搜索按精准匹配，效果不佳，推荐用AI工具如ChatGPT搜索。项目页面的`star`数代表项目受欢迎程度，`commit`日期可判断项目是否活跃。
+**易混淆点**：`watch`是关注项目，`fork`是复制项目，`star`是收藏点赞，三者含义不同。`release`是安装包，`read me`是说明书。
+**待澄清问题**：原文未提及。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>4014/2303</t>
+        <v>32.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4014/1852</t>
         </is>
       </c>
     </row>
@@ -4631,105 +4586,68 @@
       <c r="C16" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本次对话由窦文涛主持，嘉宾为马先生与《明朝那些事》作者当年明月，从刚播完的日本电视剧《大奥》谈起，认为它是《大长今》之后最有影响的外国剧，三部剧时间跨度约相当于中国晚明到清初，另有一部在明治维新之前。对话认为日本文化核心是极端精神与忠诚文化，凡事做到尽头、发自内心，与中国讲中庸、讲融合的文化差异极大，并举例战后日本用30年成为世界第二经济强国、跳槽率最低、终身雇佣制、豆腐厂按点开工、做绳子的人几年不赚钱铺市场等。关于生死观，对话提到日本人重视死亡而非单纯藐视生命，剖腹自杀、看樱花只看落的那一天，被认为源于岛国生存条件恶劣。关于明史，当年明月表示写明朝是因为明史资料最多、自己最熟，但明清史料说法不一如罗生门，明朝本身跌宕起伏，朱元璋从乞丐到皇帝被推崇为人才，历史经验教训难以套用。对话还提到正德皇帝被写坏、豹房实为动物园、晚明江南市民生活富足、明末灾荒与瘟疫导致李自成起义和明朝灭亡，以及中国王朝约300年大限。
+本期《锵锵三人行》围绕日剧《大奥》与《明朝那些事儿》展开，主持人窦文涛与嘉宾马先生、当年明月（石悦）共同探讨中日文化差异及明朝历史。节目先讨论《大奥》的历史背景，认为该剧反映日本从晚明至清初再到明治维新前的历史，并指出日本文化具有极端精神，强调做事做到极致，忠诚文化体现在具体行为中，如剧中阿福40年不出于私心、完全公心。随后话题转向明朝历史，当年明月解释自己写明史是因为明史资料最多，但同一事件常有多个不同说法，如同罗生门；他推崇朱元璋，认为其从乞丐到皇帝是人才决定论的体现，并强调历史经验教训难以直接套用，因为后人并不比前人聪明。嘉宾还讨论了明朝兴亡的经验，认为明末江南市民生活富足，艺术与工艺精细，但李自成起义源于陕西灾荒；同时指出明朝历史跌宕起伏，皇帝行为多样，如正德皇帝被后世评价偏低，可能因嘉靖朝修史存在偏颇。
 # 访谈详细记录
-一、《大奥》与日本文化
-- 发言者3认为《大奥》是大长今以后可能最有影响的外国电视剧，拍得非常好。
-- 发言者3介绍该剧三部，前两部大概相当于中国晚明到清初，发言者2补充后来还有一部在明治维新之前，是一部有跨越性的历史剧。
-- 发言者2表示吸引他的是严谨的精神，看日本剧看不到群众演员笑场。
-- 发言者3称听人说这是大长今以后最重要的外国剧，第1集片头将军出场时所有人呈45度开始鞠躬，依次鞠躬，场面之华丽包括色彩，一看就不一样。
-- 发言者3介绍大奥就是普通话说的后宫，日本话的奥指很深的地方，屋子最里处叫奥，一般人不准进去。
-- 发言者2说明日本天皇一直是摆设，实际掌管权力的是幕府将军，德川家康开创德川幕府后日本所有权力掌握在一个人手上。
-- 发言者2称从实际上看幕府将军对天皇一点都不崇拜，天皇没钱办活动找将军要钱，将军不给，活动没办，后来还有为表示对幕府抗议而退位的。
-- 发言者2认为日本文化从头到尾没有变，核心是极端精神，所有事情要做到尽头。
-- 发言者3称日本是发自内心的，战后1945年以后用30年成为世界第二经济强国，是必然不是偶然，是唯一没有资源的国家。
-- 发言者2认为中国文化精神是中庸，讲究融合，是一条最适合的路；日本精神恰相反，坚持一个原则。
-- 发言者3称日本是忠诚文化的典型国度，坚韧不拔，做到极致。
-- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
-- 发言者3称日本跳槽率最低，每一次跳槽都是社会资源的浪费。
-- 发言者2称西方经济学家一直不能理解日本终身雇佣制，认为缺乏竞争会导致效率极低下，但日本终身雇佣了人家还是积极性特别高。
-- 发言者3举例去日本参观最底层工厂，豆腐规定当天做当天卖，夜里11:45所有人坐好看着表，12点整所有人站起来开始工作，四点多钟干完，然后上市，今天的豆腐今天卖。
-- 发言者2认为日本是岛国，没有资源，经常火山地震，人对世界有极强求生欲望，必须融入团体按固定规则做事才能生存。
-- 发言者3称日本投机取巧的人没有生存环境，社会文化的鄙视非常难过，所以不能生存。
-- 发言者3举例日本做绳子做到全日本第一的人，长达几年不赚钱，从批发处进货一分钱不赚送给客户，等把市场铺平后，拿单子跟两边各加2%，全国4%就是不得了的一个数。
-- 发言者2称慢慢走或者不偷奸耍滑，是一条更快到达成功的道路。
-- 发言者3称在这种文化中你愿意也做不成，你的文化不允许这种现象生存；强调忠诚最终一定要落到一个好处，所以这个民族才团结。
-- 发言者2称很不愿意做日本人，因为很多时候像盲从，而且他们有一种寻死的潜在欲望。
-二、日本生死观与忠诚
-- 发言者2称日本人看樱花不看发芽的时候，只看落那一天，由于常年以来生活在岛国上，生存条件太恶劣，对死亡不是藐视，是有点向往或者说不惧怕。
-- 发言者2称二战时日军到中国有那么多暴行，是一种藐视生命的行为。
-- 发言者3认为日本民族不是藐视生命，是重视死亡，是翻着的；剖腹自杀不是藐视生命，是重视死亡；经济危机时日本很多身家万贯的人剖腹自杀。
-- 发言者1提到有极端批评说日本人的忠诚叫家奴、奴。
-- 发言者3称我们不能再用另外一个标准去评判它。
-三、明朝历史与明史研究
-- 发言者2表示写明朝是因为明史最熟，明史资料最多；历史界研究有两个难点，第一是先秦春秋，没史料，史记就那么一两篇，都是编的；第二是明清，明实录几千万字，明代史官的记录，明通鉴、明史纪事本末、明会典、纲目三编这些书堆得比山还高，但一个说法可能有7个不同，一个事件可能有7个不同说法，就好像罗生门。
-- 发言者3称明朝本身260多年的过程跌宕起伏，几次都要死没死了，土木堡之变、夺门之变各种之变特别多，皇上已经被瓦剌军抓起来了，哥几个一攒吧说那不算，又把弟弟扶起来了，完全构成一个现代版的电视剧。
-- 发言者1提到当年明月对朱元璋好像很推崇。
-- 发言者3称一个乞丐坐到最上面独此一份，刘邦好歹是个村长亭长。
-- 发言者2称推崇朱元璋因为他太不容易了，从一乞丐一直到最后推翻元朝当上了皇帝，定了多少规章制度，明朝的规章制度由他定下来，基本上没有什么太大的改动。
-- 发言者3认为人的因素最大，改变时势一定是出现一个人。
-- 发言者2称朱元璋天分相当高，举例李云龙没上过军事院校能打仗，会打仗的人打仗，不用看兵书，天赋。
-- 发言者1提到朱元璋的选择有点逼上梁山的性质，好友汤和让他去参加起义军，他在庙里犹豫，怕被杀头，后来因为信差送信被人告发，没办法只能去起义。
-- 发言者2称历史最重要的是你一定要弄明白它是发生过的，当年那是造反，于他而言是非常有风险的事儿。
-- 发言者3称历史你回过头看谁都是一个聪明人，你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
-- 发言者3称明朝有仁宣盛世，晚明时尽管史书上一再说政治如何黑暗、皇帝如何不上朝，但老百姓生活很好。
-- 发言者4提到金瓶梅写的西门庆是一个阶层。
-- 发言者2称明末那段时间很多真相是被掩盖的，市民生活特别轻松舒服，想去哪去哪，连皇册都不用了，到处走，去给人打工；当年江浙一带兴起了工商业，给人当雇工活得很滋润；三言二拍这种娱乐产品的出现说明有能够养活自己的资本；后来李自成闹起义是因为陕西那一带发生了大规模的灾荒。
-- 发言者3称从当时器皿可以看到人的生活乐趣，明末工艺变得非常精细，有点像日本的工艺，日本派了大量工匠跟中国交流。
-- 发言者2称看到的史料穿什么都有，至少江南那一带确实非常富足。
-- 发言者3称文征明、唐寅、董其昌都是那个时期的人。
-- 发言者3称一到朱搭的时候，八大山人明末了，画的都是翻白眼，前面无文化派的人画的都是小桥流水。
-- 发言者2称历史经验教训说多少次了，我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-- 发言者2称历史那个事儿发生的时候是有背景的，你不比前人聪明，甚至可能比前人笨，当那种情况出现的时候，你也得那么办。
-- 发言者2称史书上记载下来是照片，而实际上古人的生活都是录像，你不知道为那一幕之前跟之后是什么，不知道当时为什么要做这个选择，所以千万不能套用，套用那一定要倒霉。
-- 发言者2称明代这个朝代很有趣，什么事都有，宦官专政魏忠贤、刘瑾，文官专政张居正，皇帝专政朱元璋、朱棣，谁都可能当老大，而且什么都能发生，皇帝出去了还能回来了，还能做皇帝。
-- 发言者2称晚明时期吴三桂跟满清合作要入关，陈圆圆是一个原因，还有一个原因是他认为崇祯死了，当时说法是我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝。
-- 发言者2称1644年明朝灭亡那一年，李自成军打到京城没有人抵抗，因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天看疙瘩瘟就是天花。
-- 发言者3称中国的历史王朝300年都是大限，一逼近300年的时候你自己就没就完了。
-- 发言者3称中国历史上如果严格讲跨过300年大限的只有宋朝，南北宋接上以后，退让了大半个国土，保证了它延续了319年；汉朝中间隔断14年是彻底空的；唐朝明朝清朝都没跨过这个界限。
-- 发言者2称今天数世界上公司超过276人的有几家呢，没有几家，明朝做公司多大摊子几千万人。
-四、明朝皇帝与晚明社会
-- 发言者1提到一种观点说明朝和清朝在美这方面，故宫金碧辉煌大红大紫是满族人的趣味，真正明朝不是这样。
-- 发言者3称宋明两个朝代是典型的汉人政权，汉人是文人政权，对美的判断不是表象的；满族是异族，对美的判断都是表象的；今天凡是那种非常外在美直观能看到美的都卖得非常贵，但在100年前晚清到民国初年的收藏，这种东西都不值钱，一定是素雅的。
-- 发言者2称明朝皇帝是九五至尊，但皇上说要去一趟江南，大臣说不行就不行，明武宗正德皇帝要去，不让去，全跪金水桥前面，后来气坏了到锦衣卫去打，打死了十几个，还是不让去。
-- 发言者1提到明朝有些史官就是要跟皇帝说点难听的，让你砍我的头，这样我青史留名，冒死就为了个名。
-- 发言者3称这就是文化的力量，文化的力量是一个超出我们想象的力量。
-- 发言者2称明武宗正德后来打服了一批人，非要去不去不行，到扬州说我要什么东西，政府说没有东西没有了，有也不给，皇帝不生气，说那我就回去，还让人准备酒席，然后说吃不了，你们把酒席折合成银两，我带回去。
-- 发言者3称正德皇帝是明朝整个皇帝中最特殊、最鬼怪的一个个性，过去对他的评价非常低，说他荒淫，豹房是他弄的。
-- 发言者1提到一个爱当木匠的皇帝，发言者3称那是天启，直接干活，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好，他成就感特大。
-- 发言者3称这从侧面反映了当时社会的一种时尚，当时家具在每个人心目中地位高，明式家具现在在国际上那么高的地位绝对不是偶然的。
-- 发言者2称明代皇帝本身确实也没什么事干，明神宗几十年不上朝，但他不出去。
-- 发言者2称但凡是明朝的皇帝，后人不会说前朝自己朝代的皇帝多差，正德特别差是因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以不能够把他写得太好。
-- 发言者2称正德皇帝被说特别荒淫，豹房其实就是玩的地方，里边养了豹子，有动物园，女人肯定是有的，但在后宫也是女人，不影响其他什么问题。
-- 发言者3称正德皇帝是有定论的说明朝最荒淫的皇帝，清朝最荒淫的是咸丰，咸丰还留了个种，正德不留种，没少找女人但没有生育能力。
-- 发言者3称正德皇帝对宫廷以外的女人都有兴趣，宫廷内的女人确实没兴趣，因为宫廷内的女人被训练过，禁忌太多，太保守。
-- 发言者2称据说正德去过，但没有具体的史料能够确实，史料没法记。
-- 发言者2称正德从江南回来，没有进京城，在通州先停了半天，先派人打探，这是史料记载的，先停在这儿，你们先给我把情况看清楚了，京城里有没有人想搞埋伏搞圈套，非常有城府。
-- 发言者2称明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般都有某些程度的偏颇，因为嘉靖上台先搞了个大礼仪事件，为这事死了很多人，为给自己父亲争个名分，他父亲是王爷，他要把他追封为皇帝。
-- 发言者1称很多人研究历史就有傲慢与偏见，没有设身处地，老觉得自己聪明，判断他昏庸无能。
+议题一：日剧《大奥》与日本文化
+- 马先生认为《大奥》是继《大长今》之后最有影响的外国电视剧，拍摄极好，反映日本从晚明到清初，再到明治维新前的历史，是一部有跨越性的历史剧。
+- 当年明月表示被该剧吸引是因为其严谨精神，指出日本历史剧中群众演员不会笑，而中国历史剧如《三国演义》中群众演员会笑。
+- 马先生描述《大奥》第一集片头将军出场时，所有人呈45度鞠躬，场面华丽，色彩鲜明，令人震撼。
+- 窦文涛欣赏日本人的礼仪，如穿和服走小碎步、尊贵人物到来时两旁的人伏地行礼。
+- 马先生解释“大奥”即后宫，日语中“奥”指很深的地方，即屋子最里处，中文中“堂奥”“深奥”保留此意，且一般人不得进入。
+- 当年明月指出日本天皇一直是摆设，实际权力掌握在幕府将军手中，德川家康开创德川幕府后，权力集中于一人，将军想干什么就干什么。
+- 当年明月举例说明天皇不受尊重：德川家掌权后，天皇想举办活动但没钱，找将军要钱被拒，活动未办成，天皇为抗议甚至退位。
+- 马先生认为日本文化具有极端精神，所有事情要做到尽头，且是发自内心的，这与中国的“中庸”文化不同。
+- 当年明月对比中日文化：中国文化精神是中庸，讲究融合，走最适合的路；日本精神则坚持一个原则，如“鞠一刀”，炮手开炮时忘记一切只记得开炮，即达到最高境界。
+- 马先生指出日本战后用30年成为世界第二经济强国（绝对量），是必然结果，源于全民族的极端精神，且日本是唯一没有资源的强国。
+- 马先生提到日本跳槽率最低，终身雇佣制虽违背经济学原理，但日本人积极性仍高。
+- 窦文涛讲述《大奥》剧情：一女子本有情人，情人发誓救她，但将军死后情人放火来救，女子却拒绝跟走，因将军曾告诉她即使掉到井里也能有自己的天空，她选择留下甚至出家。马先生认为这是日本忠诚文化的具体体现，靠具体事例而非说教。
+- 马先生举例：阿福25岁进大奥当奶妈，65岁去世，40年完全出于公心，不出于私心，即使被伤害，对方也认为她出于公心，最终成为楷模。
+- 当年明月总结：所有人按自己角色做事，最节省成本，形成合力，效率极高。
+- 马先生讲述参观日本豆腐厂：豆腐当天做当天卖，夜里11:45所有人坐好等钟，12点整准时开始工作，到四点多干完上市，无人闲聊。
+- 当年明月分析原因：日本是岛国，无资源，常火山地震，生存条件恶劣，人必须融入团体按规则行事才能生存，因此对世界悲观，必须努力求生。
+- 马先生指出日本投机取巧者没有生存环境，社会文化鄙视使其无法生存；举例日本做绳子的人，几年不赚钱铺市场，最后通过加价2%获得巨大利润。
+- 当年明月表示不愿做日本人，因其有盲从和寻死的潜在欲望，如看樱花只看落的那天，对死亡不惧怕甚至向往。
+- 马先生认为日本民族不是藐视生命，而是重视死亡，如经济危机时身家万贯的人剖腹自杀。
+议题二：明朝历史与《明朝那些事儿》
+- 窦文涛提到很多人对明史感兴趣，包括金庸晚年研究明史。
+- 当年明月解释自己写明史是因为明史资料最多，历史研究有两个难点：一是先秦春秋，史料少，如孙武事迹多靠编；二是明清，史料多但同一事件有多个不同说法，如同罗生门。
+- 马先生补充明朝260多年过程跌宕起伏，几次要死没死，如土木堡之变、夺门之变，皇上被瓦剌军抓走，又扶弟弟上位，情节堪比现代电视剧。
+- 当年明月推崇朱元璋，认为其从乞丐到皇帝，历史上独此一份，刘邦好歹是亭长，朱元璋要过饭，知道每一层的猫腻，疑心重，但太不容易，且明朝规章制度由他定下，基本无大改动。
+- 马先生认为人的因素最大，改变时势一定出现一个人，持英雄史观。
+- 当年明月以《亮剑》李云龙为例，说明会打仗的人靠天赋和经验，而非兵书。
+- 窦文涛提到朱元璋参加起义军是逼上梁山：好友汤和写信让他参加，信被泄露，他怕被杀头才去。当年明月强调历史最重要的是弄明白事情是真的，朱元璋当时参加起义是掉脑袋的风险。
+- 马先生认为历史经验能体现，如明朝仁宣盛世，晚明虽政治黑暗，但老百姓生活很好，如《金瓶梅》中西门庆代表一个阶层。
+- 当年明月指出明末很多真相被掩盖，市民生活轻松舒服，江浙工商业兴起，雇工活得很滋润，娱乐产品如“三言二拍”出现说明有养活自己的资本；李自成起义源于陕西大规模灾荒。
+- 马先生提到明末工艺精细，日本派大量工匠来中国交流，江南富足，文征明、唐寅、董其昌等艺术家生活好才能画出小桥流水，而八大山人画翻白眼是因对社会愤愤不平。
+- 当年明月引用名言：“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”并解释历史事件发生时有背景，后人并不比前人聪明，史书只是照片，而生活是录像，不能套用经验。
+- 当年明月指出明代有趣在于什么事都有：宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），皇帝出去还能回来做皇帝。
+- 当年明月提到吴三桂与满清合作入关，原因之一是崇祯皇帝死了，吴三桂忠诚于崇祯，入关是为崇祯复仇；1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，即天花），李自成军打到京城无人抵抗。
+- 马先生指出中国王朝300年大限，只有宋朝（南北宋接上）延续319年，汉朝中间隔断14年，唐朝、明朝、清朝都没跨过300年。
+- 马先生对比宋明与清朝审美：宋明是汉人文人政权，审美高，对美的判断不是表象；满族是异族，对美的判断是表象的，如故宫大红大紫是满族趣味，而晚清民国初年收藏讲究素雅。
+- 当年明月举例明朝皇帝受限制：明武宗要去江南，大臣跪在金水桥前抗议，皇帝打死十几人仍不让去。
+- 窦文涛提到明朝史官冒死进谏以青史留名，马先生认为这是文化的力量。
+- 当年明月为明武宗正德翻案：正德从江南回来在通州停半天，先派人打探京城情况，说明有城府；明武宗实录是嘉靖朝编的，嘉靖因大礼仪事件为父亲争名分，可能修史有偏颇。
+- 马先生提到正德皇帝是明朝最荒淫的皇帝，但没留种，对宫廷内女人没兴趣，因禁忌太多，喜欢乔装改扮找民女。
+- 窦文涛总结研究历史要有设身处地的态度，不能有傲慢与偏见。
 # 关键引语与金句
-&gt; 慢慢来才是最快的方法。
-&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 历史最重要的是什么呢？就是你一定要弄明白它是发生过的。
-&gt; 史书上记载下来是什么。照片，我打个比方是照片照片，而我们实际上我们的生活，古人的生活都是录像。
-&gt; 你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
-&gt; 文化的力量是一个超出我们想象的力量。
-&gt; 所有人按照自己的角色去做自己的事情，最节省成本了，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
-&gt; 我是商人就做商人的事儿，我是奶妈就做奶妈的事儿，我是王后就是王后的事，我什么都可以做自己的事，就是不管别人的事。
-&gt; 中国的文化精神是什么？是中庸。
-&gt; 日本的精神就恰相反，他坚持一个原则。
-&gt; 一个乞丐对有这个历史上有这种最底层的人坐到最上面独此一份。
-&gt; 他太不容易了，我们今天说你做个什么事能做成呢？这人从一乞丐一直到最后推翻元朝当上了皇帝。
-&gt; 历史你回过头看谁都是一个聪明人，你当时都不聪明。
+&gt; “写的好，写的比较放松，写的放松，对我们过去写这个书的人呢都拘着，生怕哪块做的不合适。其实我大家了解历史，尤其对广大读者来说就是大概是怎么回事就行了。”
+&gt; “慢慢来才是最快的方法。”
+&gt; “所有人按照自己的角色去做自己的事情，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。”
+&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
+&gt; “历史它那个事儿发生的时候是有背景的，就是什么意思呢？就是当你要明白你不比前人聪明，你是甚至可能比前人笨，就是当那种情况出现的时候，你也得那么办。”
+&gt; “史书上记载下来是什么。照片，我打个比方是照片，而我们实际上我们的生活，古人的生活都是录像。”
+&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。”
+&gt; “日本的精神就恰相反，他坚持一个原则，你看鞠一刀就知道，所以说比方说一个炮手在开炮的时候，当他忘记所有的事情，只记得把这一炮开出去，它就达到了它的最高境界。”
+&gt; “日本民族不是藐视生命，它是重视死亡，它是翻着的。”
 &gt; 原话引语……</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>14719/5104</t>
+        <v>55.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>14719/3328</t>
         </is>
       </c>
     </row>
@@ -5066,27 +4984,26 @@
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者张学恒，48岁，成都人，在成都轻工研究所从事科研工作，本次就诊于消化专科。主诉上腹反复疼痛3个月，4年来经常发作、每年春天较多，心窝处有烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大，疼痛可忍受、白天发作、无夜间痛醒；曾出现两次黑大便，一次一年前、一次三个月前，均查大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后转黄；最近两个月吐过几次黄水样酸的东西，晚上胀想吐、吐后舒服。既往16岁得过甲肝、在三医院住院一个月、出院各项指标正常，对磺胺药过敏，无手术史。医生表示等检查资料更全面后再判断是否需要手术，能药物控制治好就不用手术；要求患者留大便做检查，胃镜预约在后天进行，并将在总结情况后向上级医生张医生汇报再讨论治疗。
+48岁男性患者张学恒，因上腹心窝处反复烧灼样疼痛4年、近3个月加重，就诊于消化专科门诊，由严医生接诊。患者疼痛与进食冷硬食物、工作紧张劳累相关，刺激性食物可诱发，曾两次出现黑便，近两个月有呕吐。初步考虑消化系统疾病，需排查消化道出血及恶性病变可能。医生建议留取大便标本检查，并预约后天行胃镜检查，待检查结果全面后向上级张医生汇报，再商定治疗方案。
 # 诊断与检查结果
-医生本次未给出明确诊断结论，表示等检查资料都更加全面以后再判断是否需要做手术，临床上有很多药物对消化系统疾病有很好的治疗效果，若能用药控制病情治好就不用做手术。关键检查方面，患者曾两次因黑大便查大便提示大便出血并住院，第一次黑便断续约一个月、每天最多两次、住院约10天，第二次住院两三天后大便转黄；最近三个月大便均为黄色、无灰色大便，小便正常。患者自述有低血压约90/60，父亲76岁也有低血压；母亲75岁诊断冠心病、吃药控制较好。本次就诊尚未做检查，医生要求留大便做检查以了解有无相关出血，并安排胃镜及活检。
+本次门诊未进行新的检查，医生通过详细病史采集作出初步判断。患者上腹疼痛呈烧灼样，与进食冷硬食物、工作紧张劳累相关，刺激性食物可诱发，近3个月存在完全不痛时段；曾于一年前和三个月前两次出现黑便，均住院检查确诊为大便出血，住院两三天后大便转黄；近两个月呕吐数次，吐出黄水样酸味物，为当日早午餐食物，吐后舒适，无呕血。近三个月无黑便，大便黄色正常，小便正常。既往16岁患甲肝，在三医院住院一个月，出院时肝功能正常，此后体检肝功均正常；对磺胺药过敏。家族中婶婶（叔叔的爱人）患胃癌，但医生解释无血缘关系。
 # 治疗方案与医嘱
-用药方案：患者自述最近一直吃药，先服“大叔”，刚开始一天两次、每次一颗有效，后效果越来越差、量加至每天四五次仍不好；又开过武汉药厂国产`奥美拉唑`和`阿莫西林`，还吃所里医务室配制的胃炎合剂，反复用药反复发作。治疗计划：医生要求患者留大便做检查，因曾两次黑便需了解有无相关出血；胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结情况向上级医生张医生汇报后再商量下一步处理意见，是否需要手术待检查资料更全面后判断。生活注意事项：医生指出经常熬夜对疾病有一定影响，**以后还是得注意**；**抽烟对疾病有影响，应尽量少抽或不抽**，患者已限制在10支以内并想慢慢戒；**酒对胃上的疾病影响挺大**，患者有便血情况，以后需注意；医生建议尽量少喝酒、若能戒烟对疾病有好处。
+患者近期自行服药情况：最初服用某药（可能为“达喜”类）有效，后效果变差，加量至每日4-5次仍不佳；近期加用奥美拉唑（国产，武汉药厂）和阿莫西林，以及单位医务室自配胃炎合剂，效果短暂，停药后复发。医生建议患者戒烟、少饮酒，因工作紧张、经常熬夜可能影响病情，需注意休息。具体用药方案待检查结果明确后由上级张医生确定。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 大叔 | 最初每次一颗，后加量 | 最初一天两次，后加至每天四五次 | 口服 | 刚开始有效，后效果越来越差，加量后效果仍不好 |
-| 奥美拉唑 | 未明确 | 未明确 | 口服 | 武汉药厂国产；刚开始吃有些效果，停药后反复出现疼痛 |
-| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同开，具体剂量频次未明确 |
-| 胃炎合剂 | 未明确 | 未明确 | 口服 | 所里医务室自己配制，效果反复 |
+| 奥美拉唑（国产，武汉药厂） | 未明确 | 未明确 | 口服 | 效果短暂，停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同用 |
+| 胃炎合剂（单位医务室自配） | 未明确 | 未明确 | 口服 | 效果短暂，停药后复发 |
 # 复诊与预警信号
-复诊时间：胃镜预约在后天进行，做胃镜活检后正好张大夫查房；医生将总结患者情况后向上级医生张医生汇报，再回来与患者商量下一步处理意见。需立即就医的预警信号：原文未明确列出具体预警症状，医生要求患者留大便做检查，因曾出现两次黑便，需了解有无相关出血。</t>
+复诊时间：胃镜预约在后天进行，以便患者爱人陪同；医生将总结患者情况后向上级张医生汇报，再商定下一步处理意见。需立即就医的预警症状：⚠️ 若再次出现黑便、呕血、剧烈腹痛或体重明显下降，应立即就医。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>8519/1371</t>
+        <v>52.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8519/913</t>
         </is>
       </c>
     </row>
@@ -6041,50 +5958,43 @@
       <c r="C18" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系国家开发银行因与云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，对本案公开开庭审理，各方当事人均已到庭，法庭准备工作就绪。庭审围绕三个争议焦点展开调查辩论：一是抵押权与融资租赁所有权冲突及善意取得，二是罚息、复利计算，三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，公开开庭审理。庭审围绕三个争议焦点展开：抵押权与融资租赁所有权冲突、罚息复利计算、违约金。经法庭调查与辩论，合议庭在查明事实、分清是非基础上提出调解方案，各方当事人均无异议，自愿达成调解协议，法院予以确认并出具调解书。
 # 原告诉称与被告辩称
-见下表。
+庭审中，国开行主张其已尽审查义务，构成善意取得抵押权；招银租赁认为国开行未查询融资租赁登记系统，不构成善意。国开行主张罚息自2018年6月13日起算且复利有合同依据；东源公司认为罚息不应计收复利，且宣布提前到期未给合理期限。国开行主张东源煤电违约应支付违约金；东源公司认为国开行未举证违约事实，且未履行限期纠正程序。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人国家开发银行 | 主张抵押权完整无瑕疵，构成善意取得；请求支持罚息复利计算及违约金请求 | 已按人民银行规定程序完成贷款抵押刑事审查、资料审查、法律审查；2018年9月查询曲靖电力公司租赁情况无融资租赁登记；2018年核查表（证据108页）显示曲靖电力公司名下仍无融资租赁登记；评估报告明确曲靖电力公司在建工程价值5.7亿、机械设备价值5.1亿；设备为通用设备无唯一标识，只能对抵押人名下信息调查；抵押设备金额、使用上均明确为曲靖电力公司；借款合同第24条第三项约定千分之一违约金，东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约 |
-| 被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司 | 主张2018年6月13日宣布贷款提前到期不符合合同约定，未给合理期限；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金，应予驳回 | 2015年12月2日邮件发送时间与2015年12月20日签订抵押合同时间吻合；统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务；借款合同第24条第二款第二项约定宣布提前到期应发通知并限期偿还，限期偿还与立即偿还概念不同；人民币利率管理规定第21条针对贷款期内不能按期支付的利息计收复利，不包括逾期罚息；东源公司以煤炭开采为主营业务，2015年下半年资金链断裂，2019年2月19日破产重整受理时负债76.2亿元，2016年去产能安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠 |
-| 被上诉人招银金融租赁有限公司 | 主张国开行未查询人行征信中心融资租赁登记，不构成善意；东源煤电出资行为系无权处分；招银租赁2012年即取得租赁设备所有权 | 2012年8月对东源煤电相关设备进行物权确权审查，要求提供六项设备买卖合同、大部分发票及到货确认单；设备交付到货即取得所有权，招银租赁同时获得租赁设备所有权；国开行2015年办理抵押登记，时间在后且未进行相应审查义务；融资租赁登记系统初始登记附件清单载明设备名称、数量、进场时间、生产厂商及存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台；设备唯一标识码非必填项，暗设五套设备当时刚交付无唯一识别码故未登记 |
+| 原告 | 请求确认对案涉设备享有抵押权，判令被告支付利息、罚息、复利及违约金 | 已尽审查义务，构成善意取得抵押权；罚息自2018年6月13日起算，复利有合同依据；东源煤电违约应支付违约金 |
+| 被告 | 请求驳回上诉，维持原判 | 国开行未查询融资租赁登记系统，不构成善意；罚息不应计收复利，宣布提前到期未给合理期限；国开行未举证违约事实，未履行限期纠正程序 |
 # 举证与法庭调查
-## 一、举证与质证
-### （一）国开行举证
-1. 2018年9月对曲靖电力公司租赁情况的查询证书（第五组证据第一项），用以证明已对融资租赁登记信息进行核查。招银租赁质证认为该查询证书不符合要求，根据201493号中国人民银行关于融资租赁登记系统规定，国开行在操作抵押时点未查询人行征信中心结果，无论以设备名义还是以电力公司名义查询，均未进行相应查询。
-2. 证据四冶合成58亿，含东源煤电公司、曲靖电力公司对案涉设备的权属证明，用以证明设备所有权确属曲靖电力公司。
-3. 2018年核查表（证据108页），用以证明2018年再次核查曲靖电力公司名下仍无融资租赁登记信息。
-4. 2015年12月2日邮件及统计表，东源方用以证明已告知设备融资租赁情况。国开行质证认为该邮件正文及附表均无设备存在融资租赁的文字，统计表中招银租赁一栏记载的融资额度及抵押类型为不动产抵押，看不出东源方履行过告知义务。
-### （二）东源方举证
-1. 2015年12月2日邮件及融资情况表，主张邮件发送时间与2015年12月20日签订抵押合同时间吻合，统计表中两家公司抵押设备名称完全相同且用红色标注，国开行作为专业金融机构应尽注意义务。
-2. 东源公司经营困难情况说明：以煤炭开采为主营业务，2015年下半年出现资金链断裂，2019年2月19日人民法院受理破产重整时点负债高达76.2亿元，2016年响应去产能政策安置职工1万3000多人，最困难时近半年未发工资、社会保险严重拖欠。
-### （三）招银租赁举证
-1. 一审提交证据7页回租设备清单，载明设备名称和生产厂家，未提及设备型号。国开行质证认为即便提交该清单，开行角度亦无法对设备进行同一性测试；清单提示2012年3月1日，而抵押设备铭牌记载生产日期均在2013年以后，部分为2013年11月、2013年12月、2014年3月，看不出是同一设备。
-2. 2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4个亿且已实缴。国开行认为招银租赁有理由知道或应当知道设备出资情况。
-3. 融资租赁登记系统初始登记附件清单，含设备名称、数量、进场时间、生产厂商及存放地点，显示存放地点为登封矿区梅干石电厂，该电厂只有汽轮机两台、发电机两台、锅炉两台。
-## 二、法官询问要点
-1. 合议庭询问各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果。国开行认为系行业强制性规范，目的是防范动产设备多处抵押或融资冲突；招银租赁认为系行业性质、非物权法定登记，仅强化动产权利外观、可能产生对抗效力，不影响所有权设立转移；东源方认为系行业指导性规范文件，非强制性，不当然产生物权后果。
-2. 合议庭询问央行金融租赁查询方式能否保证查询到登记结果。国开行称能使用的查询方式就是查询单位；招银租赁称可通过公司名称或设备两种方式查询，以设备查询涉及种类物区分问题。
-3. 合议庭询问设备唯一标识码是否为必填项。招银租赁称不是必填项，发电机组铭牌只有型号和参数，无发动机号类唯一标识；暗设五套设备当时刚交付、无唯一识别码，故未登记。
-4. 合议庭询问国开行内部风控是否规定必须查询、未查到是否需将未查到单据作为风控材料。国开行称办理动产抵押时需调查该系统并筛查，因无表现故未保留筛查记录，内部无此规定。
-5. 合议庭询问国开行认为未查到登记结果即可免责的逻辑。国开行称按央行规定查询融资租赁系统，抵押人为曲靖电力公司，查询后系统无记载，2018年6月截图亦无显示，至今无结果，说明行为无过失。
-6. 合议庭询问若通过其他渠道知道抵押设备存在租赁是否仍需查询。招银租赁称仍需通过央行系统查询，央行规定出台背景是实践中大量存在此类案例，只有确定标准才能衡量双方是否善意。
-7. 合议庭询问各方如何看待因不同登记机构产生登记瑕疵。国开行认为涉及人民银行融资租赁登记系统与动产抵押登记的冲突，系统信息不完整、体系相互隔离、信息不流畅，未形成相互联通，可能带来交易风险；东源方称非专业机构，提供不了相关建议；招银租赁认为规范不统一、登记机构不统一、信息不对称，建议从立法层面统一对金融主体和市场主体要求，发挥行业协会作用，从操作和技能方面推动登记平台统一化。
-## 三、双方辩论的争议焦点
-1. 抵押权与融资租赁所有权冲突及善意取得：国开行主张已尽合理审慎义务、构成善意取得；东源方主张邮件已告知且设备名称相同并用红色标注、国开行应尽注意义务；招银租赁主张2012年即取得设备所有权、国开行2015年办理抵押时未查询登记、不构成善意。
-2. 罚息、复利计算：国开行主张利息自2017年12月21日至2018年6月12日合计2179万5727.08元、罚息自2018年6月13日至2019年2月19日合计4105万零579.57元、复利自2018年3月21日至2019年2月19日合计191万8206元；东源方主张2018年6月13日宣布贷款提前到期不符合合同约定、未给合理期限、罚息不应作为复利计算基数、复利再计算复利无合同依据。
-3. 违约金连带责任：国开行主张依借款合同第24条第三项约定应支付千分之一违约金、东源煤电未按第13条、第14条约定配合办理账户管理及柜台前手续构成违约；东源方主张国开行未举证证明东源煤电违反柜台协议且未按合同约定限期纠正即主张违约金、应予驳回。
+**举证与质证**
+- 国开行提交证据：2018年6月13日向东源煤电、东源煤业发送的偿还贷款本金函件；2018年9月对曲靖电力公司的融资租赁查询证书；设备权属证明、工商出资证明、人民银行征信查询结果等。
+- 招银租赁提交证据：回租设备清单（载明设备名称、生产厂家，未载明型号）；2013年、2015年审计报告（载明曲靖电力公司注册资本4亿元且已实缴）；2018年核查表（显示曲靖电力公司名下无融资租赁登记）。
+- 东源公司提交证据：2015年12月2日发送的邮件及附表（载明抵押设备情况，设备名称与招银租赁设备一致，并以红色标注）。
+**质证意见**
+- 国开行认为：东源公司邮件未明确告知融资租赁情况，统计表仅显示招银租赁抵押物已登记，不能得出已告知的结论；设备为通用设备，无唯一标识，无法逐一核查；已按人民银行规定完成查询，未发现登记，构成善意取得。
+- 招银租赁认为：国开行2018年查询证书不符合要求，未在抵押时点查询；东源煤电出资行为系无权处分；招银租赁2012年已取得设备所有权，国开行抵押权在后且未尽审查义务，不构成善意。
+- 东源公司认为：邮件发送时间（2015年12月2日）早于抵押合同签订（2015年12月20日），且设备名称一致并以红色标注，国开行应尽注意义务进行核查。
+**法官询问要点**
+- 询问各方对人民银行征信中心融资租赁登记性质及法律后果的理解。
+- 询问国开行贷款前审查是否内部规定必须查询融资租赁系统，未查到结果是否需保留单据作为风控材料。
+- 询问招银租赁在融资租赁登记系统中设备唯一标识码是否为必填项。
+- 询问国开行与招银租赁查询方式能否保证查询到登记结果。
+- 询问各方对融资租赁司法解释第九条举证责任分配的意见。
+- 询问各方对因不同登记机构产生登记瑕疵的意见和建议。
+**争议焦点辩论**
+- 争议焦点一：抵押权与融资租赁所有权冲突。国开行主张已尽审查义务构成善意取得；招银租赁认为国开行未查询系统不构成善意；东源公司认为国开行未尽注意义务。
+- 争议焦点二：罚息、复利计算。国开行主张罚息自2018年6月13日起算，复利有合同依据；东源公司认为罚息不应计收复利，且宣布提前到期未给合理期限。
+- 争议焦点三：违约金。国开行主张东源煤电违约应支付违约金；东源公司认为国开行未举证违约事实，且未履行限期纠正程序。
 # 庭审结果
-本案争议焦点为三项：一是抵押权与融资租赁所有权冲突及善意取得；二是罚息、复利计算；三是东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人对调解方案均无异议，依次在调解协议正式文本上签字。经本院主持调解，各方当事人自愿达成调解协议，本院予以确认，并在庭后根据民事诉讼法第97条规定出具调解书。调解方案主要内容：确定国开行对东源公司债权扣除破产中已清偿本金外，利息2017年12月21日至2018年6月12日合计2179万5727.08元、罚息2018年6月13日至2019年2月19日合计4105万零579.57元、复利2018年3月21日至2019年2月19日合计191万8206元，三项共计6474万4513元；确定招银租赁对涉案六项设备享有所有权、对应债权数额1377万4137万元，确定国开行对93项设备有抵押权，双方对案涉全部发电设备整体盘活处置并从变现款中实现各自债权，生效20日内由国开行向一审法院提出执行申请启动司法变现，变现价格双方各50%、实现费用双方各担50%；变现款不足清偿债务或变现后招银租赁未实现债权，在执行法院处具体本裁定后按破产重整计划中预留方案实现债权，破产管理人对招银租赁债权予以纳入预留方案，由东源煤电按此前招银租赁在东源煤电破产重组程序中有担保清偿方案予以清偿；如司法变现不能实现国开行和招银租赁权益，通过前述方法实现后均放弃对案涉设备权益，由东源曲靖电力自主生产经营；各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认；一审诉讼费用中对于国开行诉请部分按一审判决执行，对于招银租赁诉请部分诉讼费由二审法院按规定根据证据确定，二审诉讼费由本院依法确定。合议庭指出本案涉及生产设备的动产抵押权与融资租赁物所有权冲突是司法实践中普遍性难题，金融风险防控还有较大空间，根本原因在于国家还未建立统一的动产登记制度，现有动产融资租赁登记系统和动产抵押登记系统缺乏有效衔接，将根据最高人民法院关于加强司法建议工作的意见向有关部门提出司法建议，共同推进国家治理现代化。</t>
+本案争议焦点为：一、国开行对案涉设备是否享有抵押权，是否构成善意取得；二、罚息、复利的计算方式；三、东源煤电、东源煤业是否应连带给付违约金。经合议庭评议，各方当事人自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：确定国开行对93项设备有抵押权，招银租赁对六项设备有所有权；双方对案涉全部发电设备整体盘活处置，从变现款中实现各自债权；司法变现价格双方各50%，费用各担50%；变现款不足或变现不能时，招银租赁未实现债权按破产重整计划预留方案清偿；司法变现不能时，双方均放弃设备权益，由东源曲靖电力自主生产经营。各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认。一审诉讼费中国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定确定，二审诉讼费由本院依法确定。各方之间就本案涉及的问题不再存在任何争议。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t>30731/4434</t>
+        <v>47.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30731/1997</t>
         </is>
       </c>
     </row>
@@ -6191,28 +6101,24 @@
       <c r="C19" s="4" t="inlineStr">
         <is>
           <t># 候选人概况与面试岗位
-本次为公务员面试模拟，面试共20分钟、回答4个问题，考生确认准备好后由计时员计时，题纸和草稿纸可用但不得在题纸上做任何记录。考生依次作答四题：第一题围绕骏马、风筝、陀螺三句绳子意象谈对公务员工作的启示；第二题以市政府办公室工作人员小王身份谈如何组织本市AI相关企业调研；第三题以市级服务标兵小王身份现场模拟答复记者关于地下排水管道返堵的质疑；第四题从公共服务角度谈道路改造与雨污分流工程扰民矛盾的处理思路。四题均作答完毕，考官询问是否还有需要补充的内容，考生表示没有要补充的，面试到此结束。
+本次面试为公务员结构化面试，共四道题，分别考察综合分析、计划组织、应急应变和公共服务能力。考生围绕绳子哲理对公务员工作的启示、AI企业调研方案、应对记者关于管道问题的模拟答复、处理道路改造引发社会矛盾的思路展开作答。第一题中，考生从骏马、风筝、陀螺与绳子的关系展开联想，分别对应自我反省、权利与责任平衡、工作动力与责任感，并联系单位风气、权利清单责任清单、材料撰写等公务员工作场景。第二题中，考生作为市政府办公室工作人员小王，提出调研步骤：前期补课学习、借鉴兄弟城市经验、摸清上级指示，制定方案报领导审阅；实施阶段通过企业对接、调查问卷、座谈会等方式了解市场状况、服务需求和管理措施。第三题中，考生模拟片区负责人小王答复记者，解释管道老化、老城区改造难度大、夏季用水高峰问题集中，已联系维修师傅，并汇报上级部门争取综合保障工程，承认工作失职，请求媒体解释说明。第四题中，考生从公共服务角度分析主要矛盾（时间上的需求不满足）和次要矛盾（噪音、出行、舆论），提出督促施工方加快进度、防噪降尘、建议便道、交通广播引导、增加公交班次、加强宣传和网络公告等措施。整体面试表现：考生答题结构完整，能结合具体工作场景展开论述，但部分表述存在重复和口语化现象。
 # 能力评估
-按专业/技术能力、项目经验、沟通协作三个维度评估，评级与依据见下表。
+按维度用表格呈现各项能力的评级与依据，评级用 ⭐ 数量或"优/良/中/差"标注，每项须附具体事例，若包含多个项目经验，可以用符合markdown语法的多层级展开描述
 | 评估维度 | 推荐评级 | 评估依据（具体事例） |
 | --- | --- | --- |
-| 专业/技术能力 | 良 | 第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省（吾日三省吾身）、权利与责任（权利清单、责任清单）、连轴转的动力（基层与机关加班加点、材料撰写中的责任感与成就感）；第二题提出查阅国务院、中央办公厅人工智能发展指导意见及省厅相关举措，制定包含客观与主观两方面、分市场状况、服务需求、管理措施三部分的调研方案；第四题区分主要矛盾与次要矛盾并提出防噪墙、洒水降尘等具体措施。 |
-| 项目经验 | 中 | 第二题以市政府办公室工作人员小王身份提出AI相关企业调研的组织实施思路：先补课充实AI知识储备、学习兄弟城市调研经验、摸清上级领导和中央部门指示要求；与企业对接阅读发展报告、制定调查问卷并请单位AI专家学者修改完善、以座谈会形式听取企业意见，询问人才对口引进、政策倾斜、用地审批、人才吸引机制和长效培养机制等具体服务需求。 |
-| 沟通协作 | 良 | 第三题现场模拟答复记者时先询问记者姓氏并自称片区负责人小王，说明管道为上世纪90年代社区集中整治时所修建、城区属老城区改造难度大、夏天用水高峰问题集中出现，表示已联系维修师傅正赶往现场维修，长久管道硬件问题已汇报上级部门，将通过城市综合保障工程完善硬件、改善基础设施，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题提出通过交通广播推荐出行路线、加强宣传引导市民多使用公交、以公告形式在网络上发布政府举措。 |
-| 应变与时间管理 | 中 | 面试共20分钟、回答4个问题，考生确认准备好后由计时员计时；第四题作答中收到“离本场考试结束还有3分钟”提示，考生误称“考生开始回答第三第四题”，随后完成作答；考官询问是否还有需要补充的内容，考生表示没有要补充的。 |
-| 岗位匹配度 | 良 | 第一题提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第三题承认工作有失职之处，希望媒体给予改进机会；第四题提出将政府各种举措公正公开透明表达出来以获得市民理解和支持。 |
-| 面试表现 | 良 | 四题均作答完毕，第一题、第二题、第三题、第四题均以“考生作答完毕”结束；第三题以现场模拟方式完成答复；第四题因时间提示未进一步展开。 |
-| 潜在风险点 | 中 | 第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”。 |
+| 专业/技术能力 | 良 | 第一题中能结合骏马、风筝、陀螺与绳子的关系，分别对应自我反省、权利与责任平衡、工作动力与责任感，并联系单位风气、权利清单责任清单、材料撰写等公务员工作场景；第二题中提出调研步骤，包括前期补课学习、借鉴兄弟城市经验、摸清上级指示，制定方案报领导审阅，实施阶段通过企业对接、调查问卷、座谈会等方式了解市场状况、服务需求和管理措施。 |
+| 项目经验 | 中 | 第二题中作为市政府办公室工作人员小王，提出调研方案，但未提及具体项目经验；第三题中模拟片区负责人小王，解释管道老化、老城区改造难度大、夏季用水高峰问题集中，已联系维修师傅，并汇报上级部门争取综合保障工程，但未涉及具体项目执行细节。 |
+| 沟通协作 | 良 | 第三题中模拟答复记者，能解释管道问题原因，承认工作失职，请求媒体解释说明，体现沟通意识；第四题中提出通过交通广播、网络公告等方式与市民沟通，建议增加公交班次，体现协作思路。 |
 # 综合素质
-突出亮点：第一题以骏马、风筝、陀螺三句绳子意象分别对应自我反省、权利与责任、连轴转的动力，并引用“吾日三省吾身”，提出单位应形成紧张、活泼、团结、有趣的风气，同事之间相比的是能力和效率；第二题提出先补课充实AI知识储备、学习兄弟城市调研经验、查阅国务院及中央办公厅人工智能发展指导意见与省厅相关举措，制定包含客观（企业发展现状）和主观（政府应提供的服务需求）两方面的工作方案，分市场状况、服务需求、管理措施三部分调研，方案呈报领导审阅后按意见修改实施；第三题现场模拟中承认工作有失职之处，希望媒体给予改进机会，并希望媒体向公众解释政府难处和管道真正存在的问题；第四题区分主要矛盾（时间上过去、现在和未来的诉求和需求不满足）和次要矛盾（噪音污染、出行问题、舆论问题），提出防噪墙、洒水降尘、交通广播推荐路线、引导市民多使用公交、以公告形式在网络上发布等具体措施。潜在风险点：第三题答复中称“这样一个问题并不能够成为我们的责任”，与随后承认工作有失职之处表述不一致；第四题作答时误称“考生开始回答第三第四题”，且因时间提示（离本场考试结束还有3分钟）未对第四题作进一步展开。推进建议：原文未提及。</t>
+突出亮点：考生在第二题中主动承认自身知识盲区，提出利用工作之余补课，体现学习意识；在第三题中能结合老城区改造难度、夏季用水高峰等具体背景解释问题，并承认工作失职，态度诚恳。潜在风险点：第一题中部分表述重复（如"绳子"多次出现），第四题中"主要矛盾"与"次要矛盾"的划分略显笼统，且未明确具体时间节点。推进建议：建议后续面试中注意语言精炼，避免重复；在分析矛盾时进一步细化具体措施和可操作性。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>5808/1866</t>
+        <v>35.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5808/1295</t>
         </is>
       </c>
     </row>
@@ -6281,40 +6187,21 @@
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t># 参观概况
-本次讲解沿故宫中轴线及东西六宫展开，依次介绍午门、太和门广场、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、东筒子夹道、延禧宫、景仁宫、御花园、神武门等景点。午门为排队检票处，明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官；太和门广场五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。太和门为明朝御门听政处，门口铜狮为故宫六对铜狮中最大一对；太和殿即金銮殿，用于皇帝登基、皇后册封等盛大典礼，文武百官文东武西，西边弘义阁为皇帝银库，东边体仁阁为缎库。中和殿为典礼时皇帝休息室，保和殿自乾隆五十四年起为科举殿试考场。乾清门为皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边为军机处；乾清宫为皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。交泰殿放25块传国玉玺，坤宁宫住皇后，明朝所有皇后都住此。储秀宫为慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，其子在此出生；慈宁宫为康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真；珍宝馆也是宁寿全宫，为乾隆给自己修建的养老院，退休后没放权仍照常上朝，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室。神武门为紫禁城北门，出门左手边有两个盖章点。讲解者总结三条游览路线，并标注七个可以免费盖章的位置。
+本次参观为故宫博物院游览，讲解围绕午门、太和殿、中和殿、保和殿、乾清宫、坤宁宫、储秀宫、珍宝馆等主要景点展开，涵盖历史功能、建筑细节与相关典故，并推荐三条游览路线及七个免费盖章点。整体过程沿中轴线及东西两侧动线推进，从午门检票进入，经太和门广场、三大殿、后三宫、西六宫、东六宫至御花园和神武门结束，全程约需2小时至一整天不等。
 # 核心看点与讲解
-## 午门与太和门广场
-午门是排队检票处，明朝皇帝在此杖打犯错大臣，清朝在此颁朔；午门明三暗五，正门仅皇帝可走，皇后大婚进一次、状元榜眼探花出一次，旁门走皇亲国戚和文武百官。太和门广场有五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。
-## 太和门与太和殿
-太和门是明朝皇帝御门听政处，门口铜狮子是故宫六对铜狮中最大一对，建议不要站在底下合影。太和殿即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封；文武百官在太和殿广场朝拜，文东武西。西边弘义阁是皇帝银库，东边体仁阁是缎库。
-## 中和殿、保和殿与汉字馆
-中和殿是盛大典礼时皇帝休息室。保和殿从乾隆五十四年起为科举殿试考场。保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章；故宫不止一处可买紫禁城100，每家店印章不同，买了之后不能去其他店铺盖章，汉字馆印章数量据说最多，可邮寄或自背。
-## 乾清门与后宫区域
-乾清门是皇帝上早朝处，东边九卿直房供等级高的大臣等待召见，西边是军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫不该看不该听。进门后乾清宫是皇帝睡觉处，据说有27张龙床防刺客，正大光明匾后藏立储诏书。门口铜鹤铜龟旁有设计江山金殿，是紫禁城最小宫殿。
-## 交泰殿、坤宁宫与御花园
-交泰殿放25块传国玉玺。坤宁宫住皇后，明朝所有皇后都住此。坤宁宫东北角文创店有5枚免费印章。御花园有钦安殿，供奉真武大帝。
-## 储秀宫、慈宁宫与冰窖书吧
-储秀宫是慈禧住了20多年的地方，现为慈禧五十大寿原状陈列，她儿子在此出生；旁边文创店有3枚免费印章。往南是翊坤宫和永寿宫，永寿宫西边太极殿是东西六宫唯一被称为殿的。慈宁宫是康熙为孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住地。冰窖书吧有3枚免费印章，印章造型好，讲解者在此买了冰嬉图。
-## 断虹桥、武英殿与文华殿
-断虹桥是网红打卡地，石狮子形态各异，最有名的是武当狮。断虹桥往西是武英殿，后改陶瓷馆，目前关闭只能在门口看。往东穿过太和门广场到文华殿，讲解者去时未开，据说现在有展览。
-## 箭亭、钟表馆与珍宝馆
-箭亭是清朝皇帝及子孙练习骑马射箭处，旁边商店可买文创雪糕。钟表馆展示各年代钟表。珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头刷白漆以假乱真。珍宝馆不是单独展厅，院子周围屋子都可进；游客太多，看凤冠没点技术挤不进去。珍宝馆也是宁寿全宫，乾隆给自己修建的养老院，退休后没放权仍照常上朝。皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后乐寿堂是故宫唯一能进去参观的皇家寝室，有二龙仙楼设计。再往后是珍妃井，井口石小眼不是珍妃进去的地方。珍宝馆出口右手边商店有3枚免费印章。
-## 东筒子夹道、延禧宫与景仁宫
-东筒子夹道是很多小姐姐喜欢来的拍照出片地。往南拐弯到网红打卡地延禧宫，旁边景仁宫是甄嬛被封熹妃时住处，珍妃也住过。逛完景仁宫可去御花园。
-## 神武门与盖章点
-神武门是故宫紫禁城北门。出门左手边有两个盖章点：角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。
+参观从午门开始，讲解指出午门过去并非斩首之地，明朝皇帝在此杖打犯错大臣，清朝皇帝在此举行颁朔之礼；午门门洞为明三暗五结构，中间正门仅供皇帝通行，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次，两侧门供皇亲国戚和文武百官行走。进入太和门广场，可见五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供黄金国器使用，最边上的桥供文武百官行走。太和门是明朝皇帝御门听政的上朝之处，门口铜狮子为故宫六对铜狮中最大的一对，脚踩寰宇象征权力。太和殿即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封，文武百官在太和殿广场向皇帝高呼万岁；百官站位遵循文东武西原则，西边弘义阁为皇帝银库，东边体仁阁为缎库。中和殿是盛大典礼时皇帝的休息室，保和殿自乾隆五十四年起为殿试考场，东北角有汉字馆，内有4枚免费印章，可购买紫禁城100并现场盖章，但各店印章不同且不能跨店盖章。乾清门为后宫入口，东边九卿直房是等级高的大臣等待召见之处，西边为军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。乾清宫是皇帝睡觉之处，内有27张龙床以防刺客，正大光明牌匾后藏有立储诏书；门口有铜鹤铜龟及紫禁城最小宫殿社稷江山金殿，提醒皇帝将江山社稷放在第一位。交泰殿内放有25块传国玉玺，坤宁宫为皇后居所，明朝所有皇后都住于此，东北角文创店有5枚免费印章。储秀宫为慈禧居住20多年之处，现为慈禧五十大寿时期原状陈列，因慈禧儿子在此出生而受其喜爱，旁边文创店有3枚免费印章。翊坤宫、永寿宫及东西六宫中唯一被称为殿的太极殿亦在参观之列。慈宁宫为康熙为孝庄皇太后修建的养老院，寿康宫为甄嬛居住之处，旁边冰窖书吧有3枚免费印章。断虹桥上有形态各异的石狮子，其中最有名的为武当狮；武英殿后改为陶瓷馆，目前关闭，文华殿在东边，据称有展览。箭亭为清朝皇帝及子孙练习骑马射箭之处，旁边商店可购买文创雪糕。钟表馆展示各式钟表，珍宝馆门口有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据传为当年烧制琉璃时弄坏后以木刷白漆替代；珍宝馆实为宁寿全宫，是乾隆为自己修建的养老院，退休后仍照常上朝办公，皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂，是故宫内唯一能进去参观的皇家寝室，内有二龙仙楼设计，再往后为珍妃井，井口石为后加。东筒子夹道为拍照出片之处，延禧宫为网红打卡地，景仁宫为甄嬛被封熹妃时所住、珍妃也曾居住。御花园内有钦安殿，供奉真武大帝，与景山形似人像的传说相呼应。最后至神武门结束，出门左手边有角楼咖啡和故宫文创两个盖章点，各有2枚免费印章。
 # 互动与体验
-讲解中介绍了多处盖章体验：保和殿东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章，讲解者称这感觉真是盖了帽了，并提到故宫里不止一处可以买到紫禁城100，每家店里的印章有所不同，买了之后不能去其他店铺盖章，据说汉字馆印章数量最多，盖完可选择邮寄到家或背着走。坤宁宫东北角文创店有5枚免费印章。储秀宫旁边文创店有3枚免费印章。冰窖书吧有3枚免费印章，讲解者称盖章时有批折子的感觉，并在此买了一个冰嬉图。珍宝馆出口右手边商店有3枚免费印章。神武门出门左手边角楼咖啡有2枚免费印章，故宫文创有2枚免费印章。讲解者还提到箭亭旁边商店可买文创雪糕，并询问雪糕上的人物是谁。讲解者建议不要站在太和门铜狮子底下合影，单独给它拍张照即可。
+参观过程中有多个互动环节：在汉字馆可购买紫禁城100并现场盖章，体验乾隆盖章之乐；在冰窖书吧盖章时有批折子的感觉；在箭亭旁商店可购买文创雪糕，并引发对雪糕形象人物的讨论；在珍宝馆可近距离观赏凤冠等珍贵文物，但游客众多，需一定技术才能挤入观看；在东筒子夹道可拍照打卡，非常出片；在断虹桥可寻找武当狮。个人感受方面，讲解者对珍宝馆的文物表示惊艳，对钟表馆的钟表造型感到开眼，对故宫内免费盖章点的印章造型评价颇高。
 # 收获与建议
-讲解者总结三条游览路线：第一条走完视频内所有景点，早起排队一进门沿中轴线往后走，可错开旅游团，适合打算待一整天的朋友，一天走了3万步，注意休息补水；第二条进门沿中轴线往后走，看完坤宁宫去景仁宫和延禧宫，再逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，约半天；第三条适合时间有限不想走太多路，进门沿中轴线往后走，看完坤宁宫去储秀宫，出来去御花园，从神武门出，预计2小时左右。视频标注了七个可以免费盖章的位置，有需要的章友可截图保存。讲解者强烈建议来珍宝馆，并提醒珍宝馆游客太多，看凤冠没点技术挤不进去。</t>
+本次参观收获丰富：了解了午门明三暗五的门洞结构及通行规则、太和殿作为典礼场所而非上朝之处的功能、文东武西的百官站位、乾清宫正大光明牌匾后的立储秘密、社稷江山金殿的寓意、珍宝馆即宁寿全宫为乾隆养老院等历史知识。对后续参观者的建议包括：早到排队检票并沿中轴线往里冲，可错开大批旅游团人群；根据时间选择三条路线之一，全天路线约3万步，半天路线约半天，2小时省力路线适合时间有限者；游览过程中注意适当休息和补充水分；喜欢盖章者可前往七个免费盖章点，但各店印章不同且不能跨店盖章，需有所取舍；陶瓷馆目前关闭，文华殿有展览可关注。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>4497/2520</t>
+        <v>40.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4497/1737</t>
         </is>
       </c>
     </row>
@@ -6459,23 +6346,23 @@
       <c r="C21" s="4" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈走访了农村老人、村干部与民政局干部、城市社区社工等对象，目的是了解农村养老制度与城市社区养老经验，探讨解决乡村养老问题的启示。核心议题包括留守老人与独居现状、农村养老政策与困境、城市社区志愿者制度与养老服务中心、社工制度困境。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住；农村方面2021年公安数据为73万多、占比约17.8%，预计老龄化程度会越来越严重。受访者普遍反映独居老人存在无人照料、无人慰藉、就医困难等问题，农村空巢老人面临无亲人陪伴、经济困难、子女不在身边、生病住院麻烦、娱乐方式少等困境，城市社区则以志愿者一对一帮扶和养老服务中心应对，但社工制度面临需求大而供给不足、资金有限、专业人才欠缺的困境。整体反馈基调为如实陈述现状与困难，并呼吁政府、子女、社区及专业养老服务机构共同关怀。
+本次访谈围绕农村留守老人养老问题展开，受访对象包括农村独居老人、村政府和民政局干部、城市社区养老社工等。访谈目的是了解农村养老现状、政策实施情况、存在困境及城市社区养老经验，以探索解决路径。整体反馈基调为：农村留守老人面临无人照料、无人慰藉、就医困难等突出问题，养老政策覆盖有限、运营经费不足，城市社区志愿者制度与养老服务中心提供了一定借鉴，但社工行业存在供给不足、工资低、转行率高等困境。
 # 核心反馈
-**独居老人无人照料、无人慰藉、就医困难**：据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边、无奈独居，仅26.8%与子女同住，独居老人不同程度存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自一人在家中发生意外。典型场景包括：黑龙江绥滨一位独居老奶奶报警称有人敲门，民警上门调查后老奶奶承认因一个人在家太寂寞、想找个人聊聊天才报了警；上海一名67岁独居老人在家中去世，直到多日之后家中满出刺鼻气味才被邻居发现；杭州一小区一名67岁独居老人不幸在家中去世，数天之后才被发现。
-**农村空巢老人经济困难、子女不在身边、生病住院麻烦、娱乐方式少**：村干部与民政局干部反映，空巢老人可能面临的问题第一是没有很多亲人来陪伴，第二是经济比较困难，这个地方经济不太发达，生病、锻炼等都受影响，子女不在身边一旦生病住院就比较麻烦，娱乐方式少，只能坐在一起聊聊天、打打牌。有受访者说：&gt; 现在80%都是都提醒这个在外面做做这些事的，年轻人都卖出去了。
-**农村养老公共设施运营经费后续没有支持**：干部介绍，之前其实也探索过在一些农村建养老公共设施，提供日托、休闲娱乐、沟通交友的平台，但不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的。
-**城市小区留守老人社交机会更少、易孤独抑郁**：相比之下，城市小区中的留守老人们与外界社交的机会更少，更容易产生孤独、抑郁等情绪。社工谈到曾帮助一位存在心理问题的老人，其与邻里关系处理不和谐、半夜摔门，社区派志愿者上门但老人出现抗拒，觉得周围的人都是陌生的、没有关心他的人，内心可能有一点仇恨式的；经日复一日关心照料后，现在与邻里关系还算好了，能够理解一些、也可以接受一些意见，之前是不接受任何人的建议的，他今天都打来电话说寂寞空虚、得不到人关注。
-**社工制度需求大而供给不足、资金有限、专业人才欠缺**：社工姐姐认为，目前社工制度的困境主要在于社会需求量大而供给不足，由于政府和社区资金有限，难以承担长期的专业社工服务费用，人民的需求得不到满足，大量社工迫于生计选择转行，这同时也阻碍着社工行业的长期发展。每个街道和乡镇派了两名社工驻点，主要围绕老人、小孩这一类去服务，但说实在话也很难能够走下来；社工行业工资都比较低，会影响就业率，基本上很多同学没做多久就垮了，可能不超过一年。服务需要花钱购买，不一定能够今年服务了、明年又能服务，要看领导能不能争取到这样的项目，一年的服务成效并不是那么的明显；资金拨不下来了，项目也结束了，但服务成效不一定就达到了。整个湖南省有这么大，这个街道也要花十来万块钱，省里还是拨了钱的，但很多社工并不是专业的、学社工专业出来的，在专业上其实还是很欠缺的。
+**无人照料与慰藉缺失**：2021年报告显示65.5%的老人子女长期不在身边，26.8%与子女同住；独居老人存在无人照料、无人慰藉、就医困难等问题，甚至发生意外。案例：黑龙江绥滨独居老人因寂寞报警；杭州67岁独居老人去世多日才被发现。
+**经济困难**：农村养老金每月118元，与工人养老金待遇不同；五保户分散供养每月475元生活费加护理补贴，残疾人按等级纳入低保，标准为160、270、380元。干部反映“经济比较困难”“子女不在身边，一旦生病住院就比较麻烦”。
+**娱乐方式少**：老人只能坐在一起聊天、打牌；此前探索建设的养老公共设施因运营经费无后续支持而难以为继。
+**就医障碍**：有视障老人反映就医遇到障碍。
+**城市社区老人社交机会更少**：更易产生孤独、抑郁情绪；社工帮助过一位心理问题老人，老人曾抗拒关心、与外界隔绝，经日复一日照料后心理问题逐渐好转。
 # 关键洞察与建议
-核心洞察：农村与城市留守老人问题均突出，农村空巢老人受经济困难、子女不在身边、娱乐方式少等多重因素叠加影响，城市小区留守老人社交机会更少、更易孤独抑郁；农村养老公共设施建设存在只考虑建设、不考虑后续持续运营经费的问题；社工制度面临社会需求量大而供给不足、资金有限、专业人才欠缺、服务成效不易显现的困境。受访者提出的建议与偏好：一是请专业施工人进行陪伴；二是尽量倡导在外务工的子女多跟他们联系；三是丰富他们的文化生活，能够有更多的娱乐方式；四是希望老年协会能够专项执行、专门建养老设施，有一个固定的场地，定期可以有一些施工人员或宣传，如板报宣传或健康知识讲座，并要给一个持续运营的经费，不管考虑建设还要考虑后续的持续运营，才能更好地发挥作用。城市社区方面的做法与倾向：志愿者制度实行一对一帮扶，通过定期表彰、志愿者积分兑换、雷锋超市兑换礼品让志愿者长期坚持；今年做小手拉大手，从儿童青少年着手拉动家长加入；周四准备开展送春联活动，邀请书法老师写对联让孩子上门送给老人；去年中秋节开展做月饼活动，还做过百家宴，让大家感觉社区就是一个大家庭；2023年的目标是家长他们自己来组织，社区作为一个协助者。受访者还表示，解决养老问题绝非易事，不仅需要政府的关心和重视，也离不开子女、社区乃至更专业的养老服务机构的耐心陪伴与关怀。</t>
+建议包括：请专业施工人进行陪伴；倡导在外务工子女多与老人联系；丰富老人文化生活，增加娱乐方式；希望老年协会专项建设养老设施，提供固定场地，定期开展健康知识讲座等，并需考虑后续持续运营经费。城市社区经验可借鉴：建立志愿者一对一帮扶制度，志愿者积分兑换礼品，开展送春联、做月饼、百家宴等活动，让老人融入社区；社区养老服务中心提供理疗、按摩、老年大学、心理咨询等服务。社工制度困境在于社会需求量大而供给不足，政府和社区资金有限，社工工资低、转行率高、专业欠缺，项目资金不稳定，服务成效不明显，需加强专业队伍建设与资金保障。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>5309/2110</t>
+        <v>32</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5309/871</t>
         </is>
       </c>
     </row>
@@ -7082,21 +6969,21 @@
       <c r="C22" s="4" t="inlineStr">
         <is>
           <t># 沟通概况
-本次372班家长会由班主任林瑞主持，面向全体家长，围绕费用与反诈、班级基本情况、教师团队、班级存在问题及解决思路、给家长的建议等板块展开。费用方面，书费预交11000元尚未结算，书箱未购买部分将退费，相关费用约100元或70元、4000元购买、700元、120元、123元等；明确不在微信群收取家长任何费用，费用由学生交给生活委员，并提醒家长和学生注意反诈。班级共60人，男生25人、女生35人，整体时间观念执行力强、班风关系良好、班风纪律好，少数同学周末玩游戏、懒散、思考能力差、自习课纪律差。家长代表张宇波校长分享家庭教育经验，家委会建议至少三人自愿报名，保险、电子学生证、学校资助等事项一并沟通。
+班主任林瑞在372班家长会上与家长沟通，班级共60人，男生25人、女生35人，学生处于青春期不稳定时期。老师反馈班级亮点为时间观念执行力强、班风良好，需关注之处为少数同学周末玩手机、自习课效率低、个别学生书写不良、有学生带镜子及谈恋爱等问题。会议明确费用由学生交给生活委员、不在微信群转账，并提醒防诈骗；要求手机统一上交并贴名字，家长配合检查。后续将加强思想教育、制定详细班规、严格请假制度，并建议家长多关注学生心理健康、注意安全、创造良好家庭环境。家长代表张宇波分享家庭教育经验，强调关注孩子身心健康、尊重孩子、多倾听交流、配合学校工作。班主任建议成立家委会，至少三人，家长自愿报名，有家长响应。另说明保险可自行购买，电子学生证套餐78元（移动套餐满78元可办理），高中资助补助打在医保卡上，提醒家长注意孩子使用。
 # 沟通内容
-**亮点**：整体来看，第一个月时间观念执行力加强，班风关系全部良好，班风纪律非常好，地面干净，卫生良好；写字还是不错的，学生手册可查看；老师多数是老教师、优秀教师、师范院校毕业，有3年以上经验，部分6年以上，各科老师认真备课、用心上课、关爱每一位学生。**需关注之处**：少数同学周末玩游戏、懒散，思考能力比较差，自习课纪律差，班主任在时较乖、不在时乱哄哄；个别学生行动时间方面有问题，书写需练字，建议家长买字帖；自习课效率比较低；存在玩手机、看小说、镜子、微信、网瘾、打游戏充值400元、直播、不健康内容、谈恋爱、QQ、抖音、快手等情况；手机管理要求每个手机贴名字，家长处理掉多余手机，周一到周五不定时打电话检查手机是否开机；班主任将加强人员管理和班委培训，自习时给10分钟讨论，继续加强思想教育，制定详细班规，严格请假制度，定期沟通。
+**亮点**：班级时间观念执行力强，班风班貌纪律良好，地面干净、卫生好；多数学生能主动向老师请教问题。**需关注之处**：少数同学周末玩手机、有网瘾，自习课效率低、老师不在时纪律差；个别学生书写不良需练字；有学生带镜子、看小说、谈恋爱；个别学生生活费使用不当，存在乱花钱现象。
 # 家长反馈
-家长代表张宇波校长分享家庭教育经验：要控制孩子的身体健康和心理健康，高中阶段仍是长身体的关键时期；先做人，让孩子学会做人，千万不能带上不良风气；家长对待孩子要有平常心，孩子面临的学习压力很大，对挫折和失败要帮助孩子重新定位；要尊重孩子，给孩子自由空间，不轻易下消极评价；多倾听、多交流，把更多关爱与理解给孩子；遵守学校制度，配合老师工作。张宇波校长原话：&gt; 无论怎样，那你都是爸爸妈妈心里最优秀的儿子。班主任林瑞反馈家长需配合支持占30%，建议避免过分关注孩子、认为孩子不需要学习、过分期望、放任不管、给过多钱等误区，关注心理健康、交通安全（未满16周岁骑电动车非常危险，可能载两三个）、运动安全、饮食安全、防诈骗、防溺水、防校园欺凌，学习上不懂就问、不与他人比较，创造良好环境、和睦家庭气氛、制定小目标、多鼓励少指责。
+家长代表张宇波（372班语文老师）分享家庭教育经验，强调关注孩子身体健康和心理健康，认为高中阶段仍是长身体关键时期；主张先做人再成才，家长要有平常心，尊重孩子、给孩子自由空间，多倾听多交流，配合学校制度与老师工作。她提到自己对孩子说：'无论怎样，你都是爸爸妈妈心里最优秀的儿子'，认为先肯定再批评效果更深刻。
 # 共识与配合事项
 [明确家校达成的共识、后续配合措施及跟进计划，用 `- [ ]` 待办格式列出双方分工；课程名、作业名、工具名可用 `具体内容` 标注]</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>17334/1136</t>
+        <v>38.7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17334/755</t>
         </is>
       </c>
     </row>
@@ -7177,29 +7064,35 @@
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t># 例会概况
-本次为10月28日周会，主题是总结工作，会议等级为自愿级，会议资料为工作报告、这班看法、这班型社区介绍，会议目标是初步统一成员意见、统一对社区的认识。会上讨论了工作报告与下周工作安排，提到项目创建学习资料并分为多个算术，服务定价权交给消费者，公司以前用传统方法现在用AI效率高质量好，需在实践中探索改进；还提到参加互联网加创业大赛、根据学校学习所需技能、实现教师改革，以及需要政府报告并符合要求、组建教育团队、确定路线、修订纲领章程。任务方面目前有四个任务，课程开发是其中之一，最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；大运发放需要调试，任务分配需安排，需招聘20多位师傅；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。学习介绍修改方面，把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号，服务时间还有工具需要改一下。待遇与角色方面，按照角色分为学生、教师、家长、学校、教育主管，待遇有上班5000、额外有奖励、还会有提成，周五半天加周末两天休假，需要公开的及时向当事人说明理由。会议时间已一个小时，决定会后线下继续一起学习；确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
+本次会议为10月28日周会，主题是总结工作，等级为自愿级，会议资料包括工作报告、这班看法、这班型社区介绍，目标是初步统一成员意见，统一对社区的认识。会议讨论了工作方向，认为需要修正张力，确定路线，修订纲领章程，组建教育团队，参加互联网加创业大赛，实现教师改革。会议确认下个月主要任务是组建执法队伍，目前共有四个任务，课程开发是其中之一，大运发放需要调试，任务分配需考虑条件差异。学习介绍已修改完成，将“我们是谁”提到最上面，调整镜头衔接，修改参数，下一步邀请同事加入。待遇问题明确为上班5000元，额外有奖励，还会有提成；休假为周五半天加周末两天。下周工作安排需完成两个活动，需要政府报告，要符合要求。
 # 工作进展
-- 学习介绍修改：🔄进行中。已把「我们是谁」提到最上面，修改了使命感、目标感、主要任务感、成员要求，根据参数修改，留下公众号；服务时间还有工具需要改一下。
-- 任务分配与课程开发：🔄进行中。目前有四个任务，课程开发是其中之一；任务分配需安排；任务第一步是确定路线、修订纲领章程，然后安排任务，并修订303。
-- 组建执法队伍：🔄进行中。最大任务是组建执法队伍，下个月主要任务就是组建执法队伍；需招聘20多位师傅。
-- 大运发放：🔄进行中。需要调试。
-- 待遇与角色：🔄进行中。按照角色分为学生、教师、家长、学校、教育主管；待遇有上班5000、额外有奖励、还会有提成；周五半天加周末两天休假；需要公开的及时向当事人说明理由。
-- 下一步：确定期限，先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊；会后线下继续一起学习。
+### 工作方向与任务安排
+- 确定路线，修订纲领章程（🔄进行中）
+- 组建教育团队（🔄进行中）
+- 参加互联网加创业大赛（🔄进行中）
+- 实现教师改革（🔄进行中）
+- 下周需完成两个活动，需政府报告并符合要求（🔄进行中）
+### 任务分配与执法队伍组建
+- 目前共有四个任务，课程开发是其中之一（🔄进行中）
+- **下个月主要任务是组建执法队伍**（🔄进行中，最高优先级）
+- 大运发放需要调试（🔄进行中）
+- 任务分配需考虑条件差异（🔄进行中）
+### 学习介绍修改
+- 学习介绍已修改完成，将“我们是谁”提到最上面，调整镜头衔接，修改参数（✅已完成）
+- 下一步邀请同事加入（🔄进行中）
+### 待遇与休假
+- 待遇：上班5000元，额外有奖励，还会有提成（✅已明确）
+- 休假：周五半天加周末两天（✅已明确）
 # 协作需求
-- 邀请同事加入：先把学习介绍弄完，下一步开始邀请同事加入，会后看有谁愿意聊。
-- 组建教育团队：需要政府报告并符合要求，组建教育团队，确定路线，修订纲领章程。
-- 任务分配：任务分配需安排，任务第一步确定路线、修订纲领章程，然后安排任务。
-- 招聘师傅：需招聘20多位师傅。
-- 大运发放：需要调试。
-- 学习介绍：服务时间还有工具需要改一下。</t>
+邀请同事加入，共同制作解决方案；学习介绍修改完成后，需邀请同事加入；任务分配需考虑条件差异，需协调安排；大运发放需调试，需相关负责人员配合；下周工作安排需完成两个活动，需政府报告并符合要求。</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>4999/1098</t>
+        <v>26.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4999/782</t>
         </is>
       </c>
     </row>
@@ -7656,27 +7549,27 @@
       <c r="C24" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者张春和，48岁，因上腹反复不适3个月到消化内科就诊，由严医生接诊。患者4年来每年春天多发，心窝处烧灼感，吃冷、硬、辛辣食物或工作紧张劳累时发作，与油腻关系不大；疼痛可忍受、白天发作、无夜间痛醒，3个月中有完全不痛的时候。曾出现两次黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近两个月出现几次呕吐，为酸味食物，晚上吐后舒服，有隔夜食物吐出，呕吐物无红色或黑色；最近3个月无黑便，大便黄色正常，小便正常，睡眠可。医生提出需留大便检查以了解有无出血，并安排后天做胃镜，待向上一级医生张医生汇报后再商定下一步处理意见。
+患者张春和，男，48岁，因反复上腹烧灼痛4年、近3个月加重伴两次黑便及呕吐，于消化内科门诊就诊。疼痛与进食冷硬、辛辣食物及工作紧张劳累相关，与油腻关系不大；白天疼痛，夜间无痛醒，近3个月有完全不痛的时候。曾两次出现黑便，分别在一年前和三个月前，每次持续约一个月，大便干、形状正常，两次均住院两三天后自行好转。近两个月出现呕吐，吐出酸水样物，含当日或隔日食物，吐后舒适。近期服用斯达舒效果不佳，加量至每日四五次仍效果不好；也服用奥美拉唑（武汉产）和阿莫西林及单位医务室胃炎合剂，停药后复发。近3个月无黑便，大便黄色正常，小便正常，睡眠可。严医生初步建议留大便检查以排查出血，并预约后天做胃镜。
 # 诊断与检查结果
-医生尚未给出明确诊断结论，表示需等检查资料更全面后再判断是否需要手术，若药物能控制病情则不用手术。患者曾两次出现黑便，一次一年前、一次三个月前，均住院，第一次持续约一个月、第二次住院两三天后转黄；最近3个月无黑便，大便黄色正常。患者16岁时得过甲肝，在三医院住院一个月，出院时肝功能完全恢复，以后体检肝功正常。患者本人有低血压（90/60），父亲76岁有低血压，母亲75岁诊断过冠心病、吃药控制较好。医生提出需留大便检查以了解有无出血，并安排后天做胃镜。
+医生尚未给出明确诊断结论，需待检查资料全面后判断。关键检查安排：留大便做检查，以排查消化道出血；预约后天做胃镜。患者有两次黑便史，需排查消化道出血。患者有胃癌家族史（婶婶，无血缘关系），但严医生解释不必担心遗传。
 # 治疗方案与医嘱
-治疗计划：医生提出需留大便检查以了解有无出血，并安排后天做胃镜；将总结病情向上一级医生张医生（指导教授、权威）汇报后，再与患者商定下一步处理意见；关于手术，等检查资料更全面后再判断，若药物能控制则不用手术，如需手术再商量。生活注意事项：医生指出经常加班熬夜对疾病有影响，以后需注意；抽烟对身体不好，应尽量少抽或不抽，患者现把抽烟限制在10支以内并考虑戒烟；酒对胃肠道疾病影响大，需注意，患者应酬时少喝一点。重点禁忌：患者小时候因扁桃体炎在儿童医院吃华安药后左手起红疹、约半个月才好，医生告知对药物过敏，**不能吃该药**。
+患者近期自行服用斯达舒、奥美拉唑（武汉产）、阿莫西林及单位医务室胃炎合剂，但效果不佳，停药后复发。严医生建议留大便检查、做胃镜，待检查结果后商定治疗方案。生活注意事项：建议戒烟、尽量少喝酒，因吸烟饮酒可能影响胃肠道疾病；注意休息，避免熬夜劳累，因工作紧张劳累可能加重病情。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 斯达舒 | 最初一天两次，每次一颗；后加量至每天四五次 | 最初一天两次，后每天四五次 | 口服 | 最初有效，后效果不好，加量后仍效果不好 |
-| 奥美拉唑 | 未提及 | 未提及 | 口服 | 武汉药厂，国产 |
-| 阿莫西林 | 未提及 | 未提及 | 口服 | 未提及 |
-| 胃炎合剂 | 未提及 | 未提及 | 口服 | 所里医务室自己配置 |
+| 斯达舒 | 未明确（患者自述加量至每日四五次） | 每日四五次 | 口服 | 患者自述效果不佳 |
+| 奥美拉唑（武汉产） | 未明确 | 未明确 | 口服 | 停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 停药后复发 |
+| 胃炎合剂（单位医务室配置） | 未明确 | 未明确 | 口服 | 停药后复发 |
 # 复诊与预警信号
-复诊时间：胃镜预约在后天进行，因患者爱人后天可请假陪同；后天张大夫查房。医生将总结病情向上一级医生张医生汇报后，再与患者商定下一步处理意见。预警信号：原文未提及需立即就医的预警症状。</t>
+复诊时间：后天做胃镜，胃镜后正好张大夫查房。需立即就医的预警症状：⚠️ 若再次出现黑便或呕血，应立即就医。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>10297/1145</t>
+        <v>44.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10297/865</t>
         </is>
       </c>
     </row>
@@ -8015,46 +7908,49 @@
       <c r="C25" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次汇报由基金经理肖楠面向投资者进行，主题为过去一段时间的研究布局、研究认知成果以及投资理念与框架的反思与更新。肖楠首先明确反对市场上流行的抱团与均值回归两个观点，随后汇报过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向，并分享围绕四大领域的重要认知，最后用五点反思梳理对投资框架的更新：对商业模式的反思、对终局判断的反思、对长期隐性变量的反思、深度价值可能长期无效（打问号，未得结论）、小企业X factor。汇报后进入客户提问交流环节，肖楠就终局判断与格局演进、伟大公司判断标准、全市场基金选股逻辑、血制品行业壁垒、农林牧渔行业提升、商增商减分析、伟大企业增长曲线、财富管理行业、企业家精神观察心得等问题逐一作答。
+本次讲座由基金经理肖楠主讲，面向机构投资者汇报其过去一年的研究布局、投资框架反思与认知升级。肖楠首先指出投资者关心的“What happen next”类问题用处有限，因为知识与信息之间存在巨大鸿沟；随后明确反对市场上流行的“抱团”与“均值回归”观点，认为收益率呈幂律分布，投资核心在于寻找长线超级大牛股。他介绍了在互联网、财富管理、新消费、高端制造四个方向的研究布局，并分享了五点投资框架反思，包括对商业模式分类的反思、从商增角度理解商业模式、对企业家定价的思考、深度价值可能长期无效（打问号）以及小企业的X factor。最后，肖楠回答了投资者关于投资逻辑、行业观点、增长曲线、企业家精神等提问。
 # 核心观点与论证
-**论点一：反对抱团与均值回归两种流行观点。** 肖楠认为抱团定义不本质，基金经理之间是竞争关系，主观上不具备抱团意愿，同一公司研究员推荐被广泛认可买入也不叫抱团，且抱团只是截面数据忽略了时间维度；均值回归是特别不本质的局部正确，90%时间正确但10%错误代价惨重，举例某商学院老师在海螺水泥上做波段十年赚两三倍，2016至2017年卖出后该股约两年涨五六倍再未买回，并指出收益率是幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献。
-**论点二：四大研究布局方向。** 过去一年研究资源投入互联网、财富管理、新消费、高端制造四个方向。互联网：全球仅中美能做成巨大产业，中国十几年迭代出流量、运营管理、算法三代企业，港股通开通后可投；财富管理：中国进入小康，人均收入中位数前移带来巨额剩余财富待专业机构管理，行业空间远超想象；新消费：富裕年代诞生的消费公司从CEO理念、组织架构到生产方式与匮乏年代企业完全不同；高端制造：中国几乎是唯一拥有全产业链的国家，很多细分领域已占据主导地位，欧美日企业份额已是中国企业碗里的肉。
-**论点三：研究认知成果。** 新消费领域看起来产品差不多的公司收入利润差距巨大，企业眼中产品差异在三年五年十年维度被放大；传统消费龙头赚钱龙二龙三也赚钱，新消费同一行业一家赚很多钱另一家完全不挣钱；从`商增`角度理解企业商业模式，商增过快导致企业走向失败，成长企业靠什么吸收熵增是关键。
-**论点四：投资框架五点反思。** 一是对商业模式，世界上没有一劳永逸坐地收钱的生意、极端稀缺，单一维度出发可能错失机会，商增角度理解商业模式更本质，企业家精神是否值得定价存疑并与张坤争论过；二是对终局判断，因终局判断不清晰或悲观而放弃中期十倍机会，需在坚持终局判断基础上争取研究格局演进阶段性特征；三是对长期隐性变量，为什么日本德国没有出巴菲特索罗斯，中国基金经理放到日本韩国不一定有好收益率，国运等长期变量解释相当部分收益率来源，并研究奢侈品和白酒文化强势案例；四是深度价值可能长期无效（打问号，未得结论），深度价值只是结果，去年投的深度价值标的result非常差；五是小企业X factor，经典`DCF`/`DDM`都是线性假设，企业发展是曲线，曲率因素无法定价但长期起作用，超额认知来自这些方面。
+讲座围绕三个部分展开：研究布局、研究成果与投资框架反思。
+**一、反对抱团与均值回归**
+肖楠明确反对市场上两个流行观点。关于“抱团”，他认为该定义不本质，基金经理之间是竞争关系，主观上不可能抱团；同一公司买同一板块也不叫抱团，研究员推荐股票获广泛认可后大家买入是正常现象。关于“均值回归”，他认为这是“特别不本质的局部正确”，90%时间正确但10%错误代价惨重，并以某商学院老师在海螺水泥上做波段、最终两年错过五六倍涨幅为例说明。他强调收益率是幂律分布而非正态分布，美国股市200年价值增量由4%公司贡献，投资核心是找到长线超级大牛股。
+**二、过去一年研究布局**
+肖楠介绍四个重点方向：互联网（全球只有中美能产生巨大公司，已迭代三代企业）、财富管理（行业空间巨大，人均收入中位数提升将带来巨额剩余财富）、新消费（新公司从CEO到组织架构完全不同于传统企业）、高端制造（中国在多个细分领域占据主导地位，未来空间可见）。
+**三、投资框架反思与认知升级**
+肖楠分享五点反思：1. 对商业模式分类的反思，认为没有一劳永逸的坐地收钱生意，长期看所有企业都会死去；2. 从商增角度理解商业模式更本质，企业成长过程中商增过快会导致失败；3. 对企业家定价的思考，认为无法定价但需考虑长期变量，如中国和平稳定高速发展30多年这一隐藏的巨大变量；4. 深度价值可能长期无效（打问号），深度价值只是结果，原因不变则结果最好也只是不输；5. 小企业的X factor，驱动企业增长且不被线性描述的因子，经典模型无法定价但长期重要，超额认知来源于此。
 # 金句总结
-「知识和信息之间是有着巨大的鸿沟的。」——背景：肖楠在开场说明投资者关心的What happen next类问题对提问者用处不大，看好某板块对本人是knowledge，对他人只是一条信息。
-「务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。」——背景：肖楠以巴菲特代表的极端务实派与索罗斯代表的极端务虚派说明基金经理理念处于两个极端中间，强调理念没有好坏。
-「均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。」——背景：肖楠反对均值回归观点，以海螺水泥波段操作案例说明。
-「收益率是幂律分布的，不是正态分布的。」——背景：肖楠论证均值回归不本质，指出美国股市200年价值增量由4%的公司贡献。
-「长期看所有的企业都要死去，就是我们不能够抱着就是抱定说我我们要买一个千秋万代的这种企业。」——背景：肖楠反思对商业模式的理解，指出没有一劳永逸坐地收钱的生意。
-「我们一定要把底线的风险搞好。我们一致同意的就是这个东西它不可被定价，它不能被定价。」——背景：肖楠回答企业家精神观察心得，强调不乱归因、不轻易定价。
+1. “知识和信息之间是有着巨大的鸿沟的。”——肖楠以此说明投资者关心的“What happen next”问题用处有限，因为知识无法直接传递。
+2. “务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”——肖楠在对比巴菲特与索罗斯两个投资流派时强调理念无好坏。
+3. “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”——肖楠反对均值回归观点，强调其局部正确性。
+4. “收益率是幂律分布的，不是正态分布的。”——肖楠以此论证投资核心是寻找长线超级大牛股。
+5. “我们一定要对市场保持谦卑。”——肖楠在讨论长期变量时提醒投资者保持谦虚。
+6. “驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”——肖楠在介绍X factor时强调其重要性。
 # Q&amp;A 环节
-问：您刚刚讲到在对于终局结果的重视的过程中，也更加去关注格局演进的过程中阶段性的特征、中期投资机会，请问您能对这一点再详细描述一下吗？
-→ 答：肖楠表示不太好说具体标的，这个想法最早来自过去错过了一些特别大的机会，之所以错过是因为判断这些行业终局可能不大行，但明明判断对了却在两三年时间里深深错过了十几倍的涨幅。复盘看当时完全可以在既考虑终局可能没那么好的前提下依然做出漂亮投资。这类企业的重要特征是做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。后来在一些投资中，对终局可能没那么强的标的，依然能够做出好的投资，希望未来不要再去错过类似机会。
-问：您在年报中也讲到过，坚定持有优秀乃至伟大的公司。请问您能否对优秀乃至伟大的公司的判断标准，有一些具体的财务指标？
-→ 答：肖楠称伟大公司是在财务指标里面看不出来的。举例A、B两家同属一个大行业但不同细分子行业的国企，投资逻辑非常像，都在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于B公司没有太多研发、靠精益求精的管理做到成本极低；A公司每年有高额研发支出，关键技术指标以非常强速度迭代，还有很多特别前沿的研发项目，这些方向上的技术目前掌握在德国人、日本人手里。A公司在发展初期被德国人、日本人坑过，从董事长到总经理到技术骨干都有强烈的产业报国、技术报国理想，从跟着日本人学、跟着德国人学，到越做越强、超越对手，再到对手跑过来跟他们学、开始做全产业链布局，这种企业堪称伟大的企业。
-问：我们是全市场基金，能否介绍一下这个产品的投资逻辑呢？对于消费以外的行业的选股，主要是基于什么逻辑呢？
-→ 答：肖楠称很难分消费内消费外，选股逻辑都是一样的，都是不可能三角、企业三阶段、三种商业模式这一类的，消费行业只许买消费所以只能在消费行业里面选，两者选股逻辑完全一样。
+问：您刚刚有讲到是在对于终局结果的重视的过程中，也更加去关注格局演进的过程中阶段性的特征，中期投资机会，请问您能对这一点再详细描述一下吗？
+答：这个想法最早来自于我们过去错过了一些特别大的机会，我们判断这些行业的终局可能不大行，但明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘发现，这些企业虽然某一代产品被追上，但做出了第二增长曲线，且壁垒更深。所以我们开始承认终局可能没那么强，但依然能做出好的投资。
+问：您在年报中也讲到过，坚定持有优秀乃至伟大的公司。请问您对于优秀乃至伟大公司的判断标准，是否有具体的财务指标？
+答：伟大公司在财务指标里看不出来。我举两个企业的例子，它们都在自己领域把成本做到行业最低，但A公司每年有高额研发支出，技术迭代快，且从董事长到技术骨干都有强烈的产业报国情绪；B公司不怎么做研发，靠精益求精的管理做到成本最低。A公司这种有产业报国基因、从跟着学到超越对手的企业堪称伟大。
+问：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业的选股，主要是基于什么逻辑？
+答：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的“不可能三角”、企业三阶段、三种商业模式等。消费行业只许买消费，所以只能在消费行业里选，两者选股逻辑完全一样。
 问：您是怎么看待血制品行业的竞争壁垒呢？
-→ 答：肖楠称血制品行业初初研究过，觉得壁垒不是特别的强，不是想要的那种强壁垒，研究不是特别多，相比之下买了另外一些强壁垒的公司，还有一些基金经理买了血制品行业，可以请教他们。
-问：农林牧渔行业是有所提升，请问您对这个行业的观点能够给我们讲一下吗？
-→ 答：肖楠称这行业太大了，农林牧渔行业的提升是因为牧原股份那一只股票，不是因为先看好农林牧渔行业再去选了牧原股份，就是牧原股份的比例提高了。
+答：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒，这个就不展开了。
+问：农林牧渔行业有所提升，请问您对这个行业的观点？
+答：农林牧渔行业的提升是因为牧原股份那一只股票，不是我先看好农林牧渔行业再去选牧原，就是牧原股份的比例提高了。
 问：您能够再具体讲一下生意模式里边商增和商减的这个分析吗？
-→ 答：肖楠用直白例子说明：企业从小到大，部门越来越多，中层干部一大堆，上面要分领导、还有副总裁，传达效率变低、效率开始变差，内部腐败开始出现，企业为解决供应商利益关联问题又要设置巡视检查部门，部门人员要加工资、提级别，多部门老总今年提哪个明年提哪个；企业要扩张，往下游或上游多做业务，又要多一个副总裁、多个部门。有些生意模式收入10个亿跟100个亿时没多多少机构、没多几个部门，有些企业是商增把自己拖死的。行业里剩两家大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生，差别在于做得不好的公司从一开始就没考虑好企业大了以后商增怎么处理效率问题和人员问题。建议读一读党史，看组织如何保持活力，很多政府或企业确实是处理商增的高手。
-问：您讲到伟大的企业的增长曲线，您能否对于这个曲线的情况再具体跟大家讲一下呢？
-→ 答：肖楠称每年看企业今年增长20、明年15、后年17.5都是线性的，站10年周期看企业跟竞争对手之间拉开极大差距。举例快递行业疫情时只有顺丰能送，一下子把竞争对手甩出一大截；家电领域过去格力一直是老大，美的做渠道扁平化、T加三一直没看到成果，疫情来了美的占有率一下子超过格力。当企业在埋头做一些事情、还没体现到报表时，我们往往忽略其未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的，就像平时走在路上大家都走得好好的，突然来一场雨，发现有一个人带伞了，别人都淋成了落汤鸡。
-问：您刚刚有讲到财富管理行业，能否对这个行业具体展开，讲一下投资逻辑和投资机会呢？
-→ 答：肖楠称财富管理行业话题特别大且分层，顶级富豪、普通中产阶级、中低收入人员的财富管理都有不同的公司和商业模式。最早关注这个行业是研究保险时发现，某些保险公司一个保险员一单能签七八千的首次保费，有些公司平均一个业务员大概三千多、有些两千多，差距巨大，背后是结构设置、机构设置、激励机制、文化等差异。发基金时也发现同样渠道经理，有的问的问题超级专业，有的永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司一口气拿掉行业增量的绝大部分，有些公司拿掉70%、80%，剩下的第二名只能拿到剩下的20%的80%，这种特别偏激、密分布特别偏激的行业里有可能诞生特别大的企业。因监管和法律规则原因有些标的不能投，未来合同设置更清晰时可能会在投资上有所体现。
-问：您刚刚讲到曲线的方面，第二第三增长曲线需要卓越的企业家精神，企业家精神应该是投资中比较艺术的部分，请问您在观察这个指标的方面会有什么心得和把握呢？
-→ 答：肖楠称第一个心得是评判这个因素时要特别小心谨慎，不要乱归因，不要因为一个企业成功就说企业家特别厉害，就像不要因为一个基金经理过去业绩很好就说他特别厉害，一定要把所有能够被归因到数据里的客观指标因素全部归因完，再特别谨慎地评价比较虚的因素。第二个心得是不要轻易给这些因素定价，绝对不要说因为这个企业家在所以公司就能值多少多少。始终强调的是避免错误的归因，避免因为对企业家的认可去犯投资上的错误，一定要把底线的风险搞好。这些因素不可被定价，只能在有限范围内做两两比较，比如两个公司做同样生意、同样产品，可以比较两个企业家的水平高低、理念先后，仅此而已，不要跨行业、跨业务、跨产品去比较，一定要非常谨慎地使用所谓企业家精神、伟大企业这些说法。</t>
+答：用直白的理论讲，企业从小到大，部门越来越多，传达效率变低，内部腐败出现，企业要设部门巡视检查，又多了部门，人员要加工资提级别。有些生意收入10亿和100亿时机构没多多少，有些企业不需要设那么多副总裁就能做成。有些企业被商增拖死，比如互联网大厂一家效率高、一家山头林立。建议读党史，看组织如何保持活力。
+问：伟大的企业的增长曲线，您能否再具体讲一下？
+答：有些企业每年看是线性增长，但拉长10年看与竞争对手拉开极大差距。比如疫情时只有顺丰能送，一下子甩开竞争对手；家电领域美的做渠道扁平化，疫情一来占有率超过格力。这些企业平时直线发展，但在特殊时刻拐上去，就像突然下雨时发现有人带了伞。
+问：财富管理行业能否具体展开，讲一下投资逻辑和投资机会？
+答：财富管理行业话题特别大，且分层，顶级富豪、中产阶级、中低收入者的财富管理方式不同，商业模式也不同。我们最早研究保险时发现，不同保险公司业务员单均保费差距巨大，背后是结构设置、激励机制、文化的差异。财富分布超级不均匀，头部公司可能拿走行业增量的绝大部分，这种偏激分布可能诞生特别大的企业。
+问：第二第三增长曲线需要卓越的企业家精神，请问您在观察这个指标方面有什么心得和把握？
+答：第一，评判这个因素要特别小心谨慎，不要乱归因，把所有能归因到数据里的客观指标的因素都归因完，再谨慎评价虚的因素。第二，不要轻易给这些因素定价，绝对不要说因为企业家在所以公司值多少。我们一致同意它不可被定价。这些虚的因素在所有客观归因穷尽后再考虑，且只能在有限范围内做两两比较，不要跨行业比较。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>26252/4226</t>
+        <v>59.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>26252/2773</t>
         </is>
       </c>
     </row>
@@ -8219,31 +8115,28 @@
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t># 辩论内容概述
-本场辩论赛围绕「是否应拥有让所爱之人爱上自己的超能力」展开，正方为RUC棒辩论队，反方为对方辩友。正方认为爱本身并非自由意志的产物，以「坠入爱河」而非「跳入爱河」说明爱是情非得已，并援引丘脑分泌多巴胺产生爱的感觉、但科学无法解释为何偏偏对某人有感觉，故归于玄学；正方还认为红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方认为打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸，并认为通过洗脑获取爱更像变态的占有，不是爱；反方还认为月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。双方就爱到底是不是自由意志的产物、超能力发挥的机制究竟是洗脑还是其他方式、爱是玄学还是可被科学解释均未达成一致，本场辩论未形成统一结论。
+本次辩论赛围绕“拥有让任何人爱上自己的超能力是否美好”展开，正方主张超能力能成就真爱，反方认为其剥夺自由意志、本质是占有。双方就爱的本质、自由意志、洗脑与占有、放手的爱等议题交锋，最终正方获胜。正方认为爱是超能力，月老丘比特是浪漫象征，超能力掌握在爱你的人手里比蒙眼小孩好；反方认为爱是自由意志的产物，超能力抹杀对方决定，类似洗脑和占有。正方反驳爱非意志可控，用“坠入爱河”等例证。反方质疑超能力剥夺对方自由选择，类比强奸违背意志；正方认为爱发生机理未知，打响指可能改变自己或对方，不一定是洗脑。反方坚持洗脑不是爱，正方反问洗脑能否获得真爱。反方认为用超能力获取爱是占有而非爱，正方认为爱是付出，超能力是让爱你的人掌握红线。反方提出放手的爱，正方认为若相处不合适会放手，但不用超能力会留下遗憾。
 # 核心论点
-正方观点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制，若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方观点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
+正方观点：拥有让任何人爱上自己的超能力是美好的，因为爱是超能力，月老丘比特是浪漫象征，超能力掌握在爱你的人手里比蒙眼小孩好；爱是付出，超能力是让爱你的人掌握红线。反方观点：拥有让任何人爱上自己的超能力不美好，因为爱是自由意志的产物，超能力抹杀对方决定，类似洗脑和占有；用超能力获取爱是占有而非爱，剥夺对方选择空间，是自私。
 | 阵营 | 立论框架 | 核心论点 | 支撑论据 |
 | --- | --- | --- | --- |
-| 正方 | 爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已 | 超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好 | 丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学；若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从 |
-| 反方 | 打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸 | 通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱 | 这个人原来不爱你的，但是你打了响指，他就一定爱上你了，这个和很多有必要的强奸犯讲的道理是一样的 |
+| 正方 | 爱是超能力，月老丘比特是浪漫象征，超能力掌握在爱你的人手里比蒙眼小孩好 | 爱是付出，超能力是让爱你的人掌握红线 | 用“坠入爱河”等例证说明爱非意志可控；超能力能拯救被渣男伤害的人 |
+| 反方 | 爱是自由意志的产物，超能力抹杀对方决定，类似洗脑和占有 | 用超能力获取爱是占有而非爱，剥夺对方选择空间，是自私 | 类比强奸违背意志；指出超能力让使用者成为世界中心，对方爱意来源不真实 |
 # 自由辩论环节
-争议点一：超能力是否剥夺对方自由意志。反方攻：打响指让对方爱上自己，是违背对方意志强行介入亲密关系，类比强奸。正方防：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已。
-争议点二：超能力是否等同于洗脑与占有。反方攻：通过洗脑获取爱更像变态的占有，不是爱。正方防：若通过洗脑方式，要么不爱他，要么不可能真正获得爱，只能获得服从。
-争议点三：爱是玄学还是可被科学解释。正方攻：丘脑分泌多巴胺产生爱的感觉，但科学无法解释为何偏偏对某人有感觉，故归于玄学。反方防：质疑对方未论证爱是玄学。
-争议点四：放手的爱与是否应使用超能力。反方攻：追问相处后发现不合适是否再用超能力。正方防：若无法在一起会选择放手。反方再攻：一旦用过超能力，今后面对新感情会永远留下遗憾。
-争议点五：月老丘比特与红线掌握在谁手里。正方攻：红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方防：月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。
-&gt; 正方：「我们说的是坠入爱河，而不是说去跳入爱河。」
-&gt; 反方：「这个人原来不爱你的，但是你打了响指，他就一定爱上你了。这个和很多有必要的强奸犯讲的道理是一样的。」
+1. 攻：反方质疑超能力剥夺对方自由选择，类比强奸违背意志。防：正方认为爱发生机理未知，打响指可能改变自己或对方，不一定是洗脑。反方坚持洗脑不是爱，正方反问洗脑能否获得真爱。
+2. 攻：反方认为用超能力获取爱是占有而非爱。防：正方认为爱是付出，超能力是让爱你的人掌握红线。反方提出放手的爱，正方认为若相处不合适会放手，但不用超能力会留下遗憾。
+3. 攻：反方指出超能力让使用者成为世界中心，对方爱意来源不真实。防：正方认为超能力能拯救被渣男伤害的人，反方认为这剥夺对方选择空间，是自私。
+4. 攻：反方质疑超能力剥夺对方自由选择，类比强奸违背意志。防：正方认为爱发生机理未知，打响指可能改变自己或对方，不一定是洗脑。反方坚持洗脑不是爱，正方反问洗脑能否获得真爱。
 # 结辩与评委点评
-正方结辩核心升华点：爱本身并非自由意志的产物，用「坠入爱河」而非「跳入爱河」说明爱是情非得已；超能力发挥机制更可能不是直接洗脑精神控制；红线掌握在爱你的人手里比掌握在蒙眼的小孩子手里好。反方结辩核心升华点：打响指让对方爱上自己是违背对方意志强行介入亲密关系，类比强奸；通过洗脑获取爱更像变态的占有，不是爱；月老丘比特让有情人终成眷属才浪漫，若强行牵线则破坏真爱。评委点评意见：未提及。获胜方：正方。</t>
+正方结辩：爱是超能力，月老丘比特是浪漫象征，超能力掌握在爱你的人手里比蒙眼小孩好；爱是付出，超能力是让爱你的人掌握红线。反方结辩：爱是自由意志的产物，超能力抹杀对方决定，类似洗脑和占有；用超能力获取爱是占有而非爱，剥夺对方选择空间，是自私。评委点评：正方获胜。</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>12403/1626</t>
+        <v>30.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12403/1269</t>
         </is>
       </c>
     </row>
@@ -8600,26 +8493,24 @@
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者于23年9月因腹痛一晚上确诊结肠癌，行结肠癌切除手术及8期化疗，复查发现肝转移，从老家到北京做PET-CT。去年9月行肝消融及乳腺结节切除，当时已有腹膜转移，切肠时可能切得不干净；术后行紫杉化疗，仅第一次有效，后续因肝功能不行停用靶向，至3月底复查发现肝、肺、腹膜又有转移。本次就诊为家属代述病史并咨询后续治疗，医生建议以全身系统治疗（化疗、靶向、免疫）为主，介入不是当前主要问题，并建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍。
+患者为结肠癌术后患者，2023年9月因结肠癌行切除手术，术后完成8期化疗，后出现肝转移，去年9月行肝消融和乳腺结节切除，因肝功能不佳停用部分化疗药，3月底复查发现肝、肺、腹膜转移。患者主诉近期肚子疼，疼了一晚上，既往吃海鲜易上吐下泻，肠胃较弱。初步诊断为结肠癌术后多发转移（肝、肺、腹膜）。医生建议优先进行全身系统治疗（化疗、靶向、免疫），而非局部介入，并建议进行基因检测和免疫评估以指导后续治疗。
 # 诊断与检查结果
-医生指出患者为结肠癌术后多发转移，累及肝、肺、腹膜及肠壁。PET-CT显示肝、肺、腹膜有转移；肠镜显示没事但PET显示有问题，今天说可能是肠镜做得不好。4月份做的检查。医生强调现在化疗是否有效并不清楚，基因检测推荐或不推荐都需参考；免疫细胞状态很重要，数量不足需创造。
+诊断结论：结肠癌术后多发转移，累及肝脏、肺部及腹膜。关键检查结果：3月底复查发现肝、肺、腹膜转移；上个月肠镜显示未见异常，但PET-CT显示有转移，医生认为可能肠镜做得不好；CT显示肝上有一块病灶，背部也有一块。基因检测方面，医生强调重复检测的重要性，认为第一次和第二次检测结果可能不同，建议再次检测以获取更多信息。
 # 治疗方案与医嘱
-治疗计划以全身系统治疗为主，包括化疗、靶向、免疫，需选靶向、选免疫；靶向和免疫治疗与原来化疗机制不同、可能协同。建议做第二次结肠确认基因检测，把之前切片拿过去再做一遍，第一次、第二次、第三次切片可对比，从对讲中找可用信息。生活注意事项：让患者把状态调整好，提升免疫力靠自己，大夫和手术有限；要做免疫评估，但方案由家属定。**若涨幅到10公分则要命，需先系统治疗**。
+治疗计划：当前应优先进行全身系统治疗，包括化疗、靶向治疗和免疫治疗，而非局部介入。医生建议进行基因检测和免疫评估，以指导后续治疗。生活注意事项：患者肠胃较弱，吃海鲜易上吐下泻，建议注意饮食，避免诱发肠胃不适。重点提醒：肝功能不佳时需调整化疗药物，停用部分药物。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 紫杉化疗 | 未提及 | 未提及 | 化疗 | 仅第一次有效，后续因肝功能不行停用靶向 |
-| 靶向药 | 未提及 | 未提及 | 靶向治疗 | 后续因肝功能不行停用 |
-| 四联康 | 未提及 | 未提及 | 口服 | 肚子不好时用 |
+| 未提及 | — | — | — | — |
 # 复诊与预警信号
-复诊时间未提及。⚠️ 若涨幅到10公分则要命，需立即就医。</t>
+复诊时间：未明确提及具体复诊时间。预警信号：⚠️ 若出现腹痛加剧、出血、肝功能异常等需立即就医。</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>7063/797</t>
+        <v>20.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7063/666</t>
         </is>
       </c>
     </row>
@@ -8782,35 +8673,40 @@
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t># 产品概况
-本次发布会由海尔洗衣机用户研发中心主办，围绕洗干集成新物种迭代H2展开，主题为体验海尔洗衣机的科技创新之路、共同见证洗干集成新物种的诞生。发布背景源于全球家庭洗护需求洞察：欧洲作为滚筒洗衣机发源地，许多家庭有独立洗衣房、洗烘套装并排摆放；而在中国，80%的用户把洗烘套装放在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便，正是这些问题孕育了洗干集成新物种的诞生。迭代H2定位为客阳一体空间的黄金选择，是海尔为中国家庭打造的原创之作，目标是让每一个向往整洁有序新阳台的用户都能体验这种生活方式。
+海尔洗衣机创新发布会正式推出洗干集成新物种叠黛H2，专为中国家庭阳台场景打造。针对中国80%用户将洗烘套装在阳台叠放使用带来的屏幕过高、开门方向相反、水盒太高太沉等痛点，叠黛H2专为客阳一体空间设计，采用一体集成机身，解决洗烘套叠放带来的震动等安全隐患。产品高度降为167厘米，超薄机身完美嵌入60厘米标准橱柜，纯平不突出，让阳台更加美观整洁。叠黛H2是海尔为中国家庭打造的原创之作，希望每一个向往整洁有序新阳台的用户都能体验这种生活方式。
 # 市场定位与目标用户
-迭代H2专为客阳一体空间设计，面向中国当下最流行的客阳一体家居风格，是希望拥有整洁有序新阳台用户的黄金选择。典型使用场景为年轻人最喜欢的阳台风格之一，他们在阳台休闲、娱乐、健身、社交，悬挂晾衣既不美观又占空间，H2帮助其彻底告别晾晒。目标人群包括：渴望从漫长家务中解放出来的年轻人、对残留泡沫敏感的人、养宠物的人群，以及有宝宝的家庭。差异化竞争力方面，与洗烘套装的貌合神离不同，H2独有的灵犀洗烘联动可实现数据共享，让烘干和洗涤无缝连接；一体集成机身解决了洗烘套叠放带来的震动等安全隐患。
+叠黛H2面向中国家庭，尤其是客阳一体家居风格的用户。原文指出，欧洲家庭有独立洗衣房、洗烘套装并排摆放，而中国80%的用户把洗烘套装放在阳台叠放使用，存在操作不便的问题。叠黛H2专为客阳一体空间设计，同向开门尊重使用习惯，取放衣物流畅自如，采用无水盒设计无需手动倒水。产品还针对年轻人喜欢的阳台休闲娱乐、健身社交场景，帮助用户告别悬挂晾衣的不美观与占空间问题，并适合养宠物和有宝宝的家庭。
 # 核心卖点与技术参数
-**🏠 客阳一体设计与集成机身**：专为客阳一体空间设计，一体集成机身解决洗烘套叠放带来的震动等安全隐患；高度降为 `167厘米`，不用踮脚尖即可轻松操作；超薄机身完美嵌入 `60厘米` 标准橱柜，纯平不突出；同向开门尊重使用习惯，取放衣物流畅自如；采用无水盒设计，无需手动倒水。
-**🧠 智慧大脑与灵犀洗烘联动**：以屏幕为核心可全面操控洗涤、烘干和护理等多种模式；H2全新升级智慧大脑，利用中枢神经式智能网络让上下桶默契配合；H2独有灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接；洗涤结束前上桶提前 `15分钟` 主动预热，进一步缩短烘干时长。
-**🌀 烘干与洗涤技术**：搭载原创双擎热泵技术，大件烘干不缠绕；首次引入行业领先黑科技3D透视烘干，羽绒服或水洗被均可一次烘透，免去二次晾晒烦恼；升级精华洗2.0，能够激活洗衣液，`39分钟` 洗净一周衣物；新鲜净水漂洗减少洗衣液残留。
-**🐾 居家健康与静音**：搭载空净过滤系统，轻松去除衣物线屑和毛絮，更适合养宠物人群；洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭；搭载三台变频电机，洗涤、甩干、烘干全过程噪音都很低。
+**🧠 智慧联动**
+叠黛H2搭载全新升级的智慧大脑，利用中枢神经式的智能网络，让上下桶默契配合。独有的灵犀洗烘联动可实现数据共享，让烘干和洗涤无缝连接；洗涤结束前，上桶将提前15分钟主动预热，进一步缩短烘干时长。
+**🔥 烘干技术**
+搭载原创双擎热泵技术，大件烘干不缠绕；首次引入行业领先黑科技3D透视烘干，无论是羽绒服还是水洗被都可以一次烘透，免去二次晾晒的烦恼。
+**🧼 洗衣技术**
+升级精华洗2.0，能够激活洗衣液，39分钟洗净一周衣物；更有新鲜净水漂洗，减少洗衣液残留，对残留泡沫敏感的人是巨大的福音。
+**🌬️ 健康守护**
+搭载空净过滤系统，能够轻松去除衣物的线屑和毛絮，更适合养宠物的用户；洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭。
+**🔇 静音设计**
+搭载三台变频电机，洗涤、甩干、烘干全过程噪音都很低，让用户充分享受安静陪伴的时光。
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 机身高度 | 167厘米 | 洗烘套装叠放 | 降低高度，不用踮脚尖即可操作 |
-| 机身嵌入 | 超薄机身，完美嵌入60厘米标准橱柜，纯平不突出 | 洗烘套装叠放 | 全平不突出，阳台更美观整洁 |
-| 开门方式 | 同向开门 | 洗烘套装开门方向相反 | 尊重使用习惯，取放衣物流畅自如 |
-| 水盒 | 无水盒设计 | 水盒太高太沉 | 无需手动倒水 |
-| 洗烘联动 | 灵犀洗烘联动，数据共享，洗涤结束前上桶提前15分钟主动预热 | 洗烘套装貌合神离 | 烘干和洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术、3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透 |
-| 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 减少洗衣液残留 |
-| 过滤系统 | 空净过滤系统 | 未提及 | 去除衣物线屑和毛絮 |
-| 电机 | 三台变频电机 | 未提及 | 洗涤、甩干、烘干全过程噪音都很低 |
+| 机身设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，纯平不突出 | 洗烘套装叠放，存在震动等安全隐患 | 解决叠放安全隐患，操作更便捷，阳台更美观 |
+| 开门方式 | 同向开门，取放衣物流畅自如 | 开门方向相反 | 更符合使用习惯 |
+| 水盒设计 | 无水盒设计，无需手动倒水 | 水盒太高太沉 | 使用更轻松 |
+| 洗烘联动 | 灵犀洗烘联动，数据共享，上桶提前15分钟预热 | 洗烘套装貌合神离 | 烘干洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术，3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服水洗被一次烘透 |
+| 洗衣技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 洗衣更高效，减少洗衣液残留 |
+| 过滤系统 | 空净过滤系统 | 未提及 | 去除线屑毛絮，适合养宠和有宝宝家庭 |
+| 电机 | 三台变频电机 | 未提及 | 洗涤、甩干、烘干全过程噪音低 |
 # 定价与发售信息
-海尔为这款平嵌超薄产品公布诚意满满的定价：10kg 3D透视烘干款12998元，10kg双擎热泵款10998元。发售时间、购买渠道及预售政策未提及。</t>
+发布会公布两款定价：10kg 3D透视烘干款12998元，10kg净净双擎热泵款10998元。发售时间、购买渠道及预售政策原文未提及。</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>7311/1601</t>
+        <v>111.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7311/1404</t>
         </is>
       </c>
     </row>
@@ -9013,20 +8909,20 @@
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为改选中共巢湖市银屏镇白母山村芦塘支部委员会，支部共有党员8名（正式党员8名），有选举权的应到8名，因病请假1名，实到会有选举权党员7名，符合法定人数，会议可以召开；应邀参加的有银屏镇党委组织委员钱小丽同志。会议依次通过上届支部委员会工作报告、党员大会选举办法草案、支委候选人名单、监票人及计票人名单，四位候选人依次进行竞职演说，随后进行支部委员会委员选举和书记选举。上届支部委员会工作报告经讨论无意见、鼓掌通过，报告回顾3年来支部落实党建工作要求、加强思想政治建设和理论学习、抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告同时指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。选举办法草案明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。银屏镇党委批复（2019年10月12日）同意委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊，书记候选人预备人选卢燕娇，委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。随后召开第一次支部委员会全体会议，支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准；会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言表示将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。
-## 大会审议与选举办法通过
-- 上届支部委员会向会议做工作报告，请同志们审议；报告回顾3年来支部落实党建工作各项要求，加强思想政治建设和理论学习，抓好党支部建设，新发展党员一名，按规定收缴党费2640元上交上级党组织，开展两学一做学习教育常态化制度化和讲严例专题警示教育，推进党务公开，抓好党风党纪教育；报告指出存在不足：一是党建工作制度还不够完善，二是党员主体意识尚需进一步提高、个别党员干部顶推中心服务大局的意识还不强，三是党支部对党员的教育管理监督还不够深入。报告经讨论无意见，鼓掌通过。杜军晓同志宣读党员大会选举办法草案，明确大会选举支部委员会委员三名、候选人四名，差额不少于应选名额20%，按姓氏笔画为序排列，采用无记名投票方式；委员和书记选举分两步进行，先差额选举委员，再从当选委员中等额选举书记，两次分别投票、计票和宣布结果；参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举，收回选票等于或少于发出选票选举有效、多于则无效应重新选举，候选人赞成票超过应到会选举人数半数方可当选；选举设监票人一名、工作人员两名，提名作为支部委员候选人的不能担任监票人和工作人员。选举办法草案一致通过。
-- 杜军晓同志宣读银屏镇党委关于同意中共巢湖市银屏镇白母山村芦塘支部委员会组成人员候选人预备人选的批复（2019年10月12日），委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇；委员实行差额选举、差额一人，书记实行等额选举，选举结果报镇党委批准。会议对候选人名单无不同意见，鼓掌通过。会议提议由贾淑玲同志担任监票人，经酝酿无意见，表决一致通过；宣布大会计票人员名单为黄婷丽、刘彩云。四位候选人依次进行竞职演说：卢燕娇表示如当选将加强支部建设、落实三会一课、推动村集体经济发展、抓好民生工程落实；杜军强表示如成为支部委员可更好担当纽带角色为党员和群众服务；辛东升表示严格要求自己、做合格党员干部、圆满完成上级党组织分配的各项任务；秦磊表示有较强责任心和较高思想觉悟，配合上级工作，当一名合格的支部委员。
-## 选举结果与委员分工
-- 选举环节应到会有选举权党员8名、请假1名、实到7名，达到应到会选举权党员人数的4/5，可以进行选举；发出选票7张、收回选票7张，选举有效；计票结果卢燕娇6票、杜军强6票、秦磊2票，根据选举办法，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。随后召开第一次支部委员会全体会议，宣读选举办法草案，介绍书记候选人建议名单卢燕娇，经鼓掌通过；提议由辛东升同志担任监票人和计票人，表决一致通过；支部有委员3个，发出选票3张、收回选票3张，卢燕娇当选为新一届党支部书记，最后结果以报镇党委批准为准。会议明确辛东升同志负责组织宣传工作，杜军强同志负责纪检工作。新当选支委代表发言，代表新当选的三位支部委员感谢信任和支持，表示下一步将抓好支部学习工作争创学习型支部、抓好支部制度建设工作争创制度型支部、完善基层党组织建设争创服务型支部，并希望党员对工作提出建议和批评。会议宣布换届选举大会圆满结束。</t>
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会，改选支部委员会。支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。镇党委组织委员钱小丽到会讲话，提出三点意见：充分认识大会意义、正确行使选举权、服从大局遵守纪律。上届支部委员会作工作报告，总结三年工作：加强思想政治建设、抓好支部建设、开展主题教育、党务公开、党风党纪教育，并指出存在不足：党建工作制度不完善、党员主体意识不高、教育管理监督不深入。报告经讨论无意见，鼓掌通过。大会依次通过党员大会选举办法、支委候选人名单（卢燕娇、辛东升、杜军强、秦磊）、监票人贾淑玲及计票人黄婷丽、刘彩云名单。四位候选人分别发表竞职演说。经无记名投票，发出选票7张、收回7张，计票结果：卢燕娇6票、杜军强6票、秦磊2票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。召开第一次支委会，选举产生支部书记，卢燕娇以3票当选；随后分工：辛东升负责组织宣传工作，杜军强负责纪检工作。新当选支委代表发言，表示将抓好学习、制度建设、服务型支部建设。大会圆满结束，奏国际歌。
+## 换届选举大会开幕及领导讲话
+- 主持人宣布会议开始，奏国歌。镇党委组织委员钱小丽讲话，提出三点意见：充分认识大会意义、正确行使选举权、服从大局遵守纪律。
+- 上届支部委员会作工作报告，总结三年工作：加强思想政治建设、抓好支部建设、开展主题教育、党务公开、党风党纪教育。指出存在不足：党建工作制度不完善、党员主体意识不高、教育管理监督不深入。报告经讨论无意见，鼓掌通过。
+## 选举新一届支部委员会及书记
+- 大会依次通过党员大会选举办法、支委候选人名单（卢燕娇、辛东升、杜军强、秦磊）、监票人贾淑玲及计票人黄婷丽、刘彩云名单。四位候选人分别发表竞职演说。经无记名投票，发出选票7张、收回7张，计票结果：卢燕娇6票、杜军强6票、秦磊2票，卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。召开第一次支委会，选举产生支部书记，卢燕娇以3票当选；随后分工：辛东升负责组织宣传工作，杜军强负责纪检工作。新当选支委代表发言，表示将抓好学习、制度建设、服务型支部建设。大会圆满结束，奏国际歌。</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>8414/2327</t>
+        <v>37.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8414/908</t>
         </is>
       </c>
     </row>
@@ -9163,23 +9059,24 @@
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t># 报告概况
-国务院向大会报告政府工作，请予审议，并请全国政协委员提出意见。报告回顾2023年工作：全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元、增长5.2%，城镇新增就业1244万人，城镇调查失业率平均5.2%，居民消费价格上涨0.2%；国产大飞机C919投入商业运营，新能源汽车产销量占全球比重超过60%；粮食产量1.39万亿斤再创历史新高，居民人均可支配收入增长6.1%，脱贫地区农村居民收入增长8%。报告明确2024年经济社会发展总体要求和政策取向：今年是中华人民共和国成立75周年、实现十四五规划目标任务的关键一年，坚持稳中求进工作总基调，统筹扩大内需和深化供给侧结构性改革、统筹新型城镇化和乡村全面振兴、统筹高质量发展和高水平安全。报告部署2024年十项政府工作任务，并指出面临的困难和挑战。
+《政府工作报告》由国务院总理代表国务院向全国人民代表大会报告，报告期间为2023年工作回顾与2024年工作部署。报告指出，2023年面对异常复杂的国际环境和艰巨繁重的改革发展稳定任务，全年经济社会发展主要目标任务圆满完成，国内生产总值超过126万亿元，增长5.2%，城镇新增就业1244万人，居民人均可支配收入增长6.1%。报告同时分析了面临的困难和挑战，提出2024年坚持稳中求进工作总基调，统筹高质量发展和高水平安全，巩固和增强经济回升向好态势，以中国式现代化全面推进强国建设、民族复兴伟业。整体基调务实进取，既肯定成绩，也直面问题，强调政策聚焦发力、工作加倍努力。
 # 核心政策
-2024年主要预期目标：国内生产总值增长**5%左右**，城镇新增就业**1120万人以上**，城镇调查失业率**5.5%左右**，居民消费价格涨幅**3%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，粮食产量**1.3万亿斤以上**，单位国内生产总值能耗降低**2.5%左右**，生态环境质量持续改善。财政政策：积极的财政政策要适度加力、提质增效，赤字率按**3%**安排，赤字规模**4.06万亿元**，一般公共预算支出规模**28.5万亿元**，安排地方政府专项债券**3.9万亿元**；为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，今年先发行**10000亿元**。货币政策：稳健的货币政策要灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。民生指标：居民医保人均财政补助标准提高**30元**，城乡居民基础养老金月最低标准提高**20元**，继续提高退休人员基本养老金。
+2024年主要预期目标：**国内生产总值增长5%左右**，**城镇新增就业1120万人**，**城镇调查失业率5.5%左右**，**居民消费价格涨幅3%左右**，**居民收入增长和经济增长同步**，**国际收支保持基本平衡**，**粮食产量1.3万亿斤以上**，**单位国内生产总值能耗降低2.5%左右**，生态环境质量持续改善。宏观政策取向：积极的财政政策适度加力、提质增效，**赤字率按3%安排**，**地方政府专项债券3.9万亿元**，**发行超长期特别国债10000亿元**，专项用于国家重大战略实施和重点领域安全能力建设；稳健的货币政策灵活适度、精准有效，保持流动性合理充裕，促进社会综合融资成本稳中有降。核心政策包括：大力推进现代化产业体系建设，加快发展新质生产力；深入实施科教兴国战略；着力扩大国内需求；坚定不移深化改革；扩大高水平对外开放；更好统筹发展和安全；坚持不懈抓好三农工作；推动城乡融合和区域协调发展；加强生态文明建设；切实保障和改善民生。
 # 重点工作
-经济领域：大力推进现代化产业体系建设，加快发展新质生产力，推动产业链供应链优化升级，实施制造业重点产业链高质量发展，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展，打造更多有影响力的中国制造品牌；促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划；深入推进数字经济创新发展，开展人工智能加行动，实施制造业数字化转型行动。着力扩大国内需求，促进消费稳定增长，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；积极扩大有效投资，发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施十四五规划重大工程项目。坚定不移深化改革，激发各类经营主体活力，深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，加快全国统一大市场建设，谋划新一轮财税体制改革。扩大高水平对外开放，推动外贸质升量稳，促进跨境电商等新业态健康发展，全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，推动高质量共建一带一路走深走实。更好统筹发展和安全，优化房地产政策，促进房地产市场平稳健康发展，统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
-民生领域：多措并举稳就业促增收，突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作，多渠道增加城乡居民收入，扩大中等收入群体规模。提高医疗卫生服务能力，居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，促进中医药传承创新。加强社会保障，城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，健全分层分类的社会救助体系。丰富人民群众精神文化生活，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。维护国家安全和社会稳定，提高公共安全治理水平，坚决遏制重特大事故发生，坚持和发展新时代枫桥经验，建设更高水平的平安中国。
-三农与城乡区域领域：坚持不懈抓好三农工作，扎实推进乡村全面振兴，学习运用千村示范、万村整治工程经验，稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平；毫不放松巩固拓展脱贫攻坚成果，加强防止返贫监测帮扶，确保不发生规模性返贫；启动第二轮土地承包到期后再延长30年整省试点。推动城乡融合和区域协调发展，积极推进新型城镇化，把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用。
-生态环保领域：加强生态文明建设，推进绿色低碳发展，深入践行绿水青山就是金山银山的理念，协同推进降碳、减污、扩绿、增长；深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，组织打好三北工程三大标志性战役；大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展，建设美丽中国先行区；积极稳妥推进碳达峰碳中和，扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系。
-&gt; 使命重在担当，奋斗创造未来，我们要更加紧密地团结在以习近平同志为核心的党中央周围，高举中国特色社会主义伟大旗帜，以习近平新时代中国特色社会主义思想为指导，坚定信心，开拓进取，努力完成全年经济社会发展目标任务。</t>
+**经济领域**：实施制造业重点产业链高质量发展行动，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展；巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划；深入推进数字经济创新发展，开展`人工智能+`行动，实施制造业数字化转型行动。着力扩大国内需求，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；积极扩大有效投资，重点支持科技创新、新型基础设施、节能减排降碳等领域，加快实施十四五规划重大工程项目。
+**科教领域**：制定实施教育强国建设规划纲要，开展基础教育扩优提质行动，大力提高职业教育质量；充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，强化企业科技创新主体地位；实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度。
+**改革与开放领域**：深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制；加快全国统一大市场建设，专项治理地方保护、市场分割、招商引资不当竞争等突出问题。扩大高水平对外开放，推动外贸稳规模优结构，全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入；推动高质量共建`一带一路`走深走实，抓好八项行动落实落地。
+**安全与三农领域**：更好统筹发展和安全，优化房地产政策，加快构建房地产发展新模式，加大保障性住房建设和供给；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案；全方位夯实粮食安全根基，严守耕地红线，提高高标准农田建设投资补助水平；启动第二轮土地承包到期后再延长30年整省试点，深入实施乡村建设行动。
+**生态领域**：深入践行绿水青山就是金山银山的理念，协同推进降碳、减污、扩绿、增长；深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理；积极稳妥推进碳达峰碳中和，扎实开展碳达峰十大行动，加快建设新型能源体系。
+**民生领域**：多措并举稳就业促增收，预计今年高校毕业生超过1170万人，强化促进青年就业政策；提高医疗卫生服务能力，**居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层；加强社会保障，**城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金；丰富人民群众精神文化生活，创新实施文化惠民工程。</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>9903/2479</t>
+        <v>53.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9903/1764</t>
         </is>
       </c>
     </row>
@@ -10014,34 +9911,27 @@
       <c r="C31" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-本次直播为杭州医学院检验医学院、生物工程学院专场，由学院党委书记、副院长宋宝峰副教授介绍2026年医学技术专业硕士点招生情况。该学位点为2024年获批的新学位点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，其中检验技术细分为医检和卫检两个方向。2025年录取64位考生，检验方向38人、影像方向11人、康复方向13人、智能方向24人。2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。
+杭州医学院医学技术专业硕士点招生宣讲直播于2026年举行，由检验医学院、生物工程学院党委书记、副院长宋宝峰副教授主讲，面向考生及家长介绍学位点基本情况、学科优势、研究方向、师资队伍、培养与就业、2026年招考计划及复试安排，并解答考生关于就业前景、备考、跨专业报考等问题。学位点于2024年获批，由检验医学院、生物工程学院合署办公，共建学院包括医学影像学院、康复学院和信息工程学院，聚焦检验技术（细分为医检和卫检）、医学影像技术、康复治疗、智能医学工程四个方向，2025年录取64人。学科建设方面，2023年获批省一流学科B类，近五年获国家级基金项目19项，纵向科研经费1300万，横向合作课题经费2200多万，获省科技进步一等奖2项、二等奖1项、三等奖2项。师资队伍有专任教师90人，高级职称53人，博士55人，硕导69人。培养学制三年，就业方向涵盖医院科室、疾控中心、企业、公务员及事业单位等。2026年计划招生34人（仅供参考，以教育部正式下达人数为准），初试科目为思想政治理论、英语及按方向自主命题的专业课，复试初试占60%、复试占40%。
 # 信息同步
-**学位点基本情况**：2024年获得医学技术专业硕士点，由检验学院、生物工程学院（合署办公）及医学影像学院、康复学院、信息工程学院共5个学院共同承担培养工作，聚焦检验技术、医学影像技术、康复治疗、智能医学工程四个专业方向，检验技术细分为医检和卫检两个方向。
-**2025年招生情况**：2025年录取64位考生，其中检验方向38人、影像方向11人、康复方向13人、智能方向24人。
-**学科建设情况**：医学技术2023年获批省一流学科B类；近五年获国家级基金项目19项、省部级项目1项，纵向科研经费1300万，横向合作课题经费2200多万；获省科技进步一等奖2项、二等奖1项、三等奖2项；建成国家级一流本科课程2门、国家级一流本科专业建设点2个；拥有省生物标志物与器官诊断转化重点实验室、省神经系统疾病数字化装备研发重点实验室等多个省级平台。
-**学科优势**：体外诊断领域优势显著，疫情时期与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品并获NMPA注册；医学影像技术方向在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优质方向；康复治疗方向依托省人民医院康复医学科；智能医学工程方向聚焦阿尔茨海默病智能预警生物标志物，居国际领跑水平。
-**主要研究方向**：医学检验技术方向负责人吕建新教授，聚焦重大疾病新型生物标志物筛选及机制等五大块；卫生检验检疫方向负责人金大志教授，聚焦新发突发传染病病原体检测检验新技术方法开发及卫生检验技术研究；医学影像技术方向负责人徐秀芳教授，含多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位四个方向；康复治疗方向负责人倪湘明教授，含技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病五个方向；智能医学工程方向负责人李海教授，聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断五个方面。
-**师资队伍与领军人物**：专任教师90人，高级职称占30%以上共53人，博士55人；硕导69人，其中正高35人，博士占比46人；有省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。领军人物包括学位点负责人吕建新教授、徐秀芳教授、叶小明教授、金大志研究员、李凯教授等。
-**硕士培养与毕业去向**：培养目标为面向健康中国发展需要、服务区域行业产业发展的高层次应用型人才；全日制专业学位学制三年，最长不超过五年；课程学习实行学分制，毕业前要求取得不少于24个学分，其中专业必修课不少于12个学分，专业选修课不少于5-6个学分；就业方向包括医院相关科室、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等。
-**2026年招考计划**：2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准；初试科目为思想政治理论、英语及对应方向专业综合（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；专业综合满分300分，考试时长180分钟；检验综合中卫生生物学检验占40%、生物化学检验占30%、微生物学检验占30%；参考书及考试大纲以杭州医学院研究生招生网公布为准。
-**复试安排**：复试采用线上线下结合、目前以线下为主；初试占60%、复试占40%；复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%；复试具体形式和内容以学校当年复试录取办法为基础，可参考2025年复试办法。
-**考生问答**：就业前景方面，宋宝峰表示就业优先，专业就业前景非常好，可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等；跨专业报考方面，允许非该专业本科考生跨专业自主报考；交通方面，学校有三个校区，主城区黄路校区交通便利；竞赛方面，学校重视竞赛，以赛促学、以赛促教、以赛促改。
+一、学位点基本情况：医学技术专业硕士点于2024年获批，由检验医学院、生物工程学院合署办公，共建学院包括医学影像学院、康复学院和信息工程学院，聚焦检验技术（细分为医检和卫检）、医学影像技术、康复治疗、智能医学工程四个方向。2025年录取64人，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。
+二、学科建设与优势：医学技术学科2023年获批省一流学科B类，近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万，横向合作课题经费2200多万，获省科技进步一等奖2项、二等奖1项、三等奖2项，建有国家级一流本科课程2门、国家级一流本科专业建设点2个。省级平台包括省生物标志物与器官诊断转化重点实验室、检验诊断关键技术研究室、康复模块和机器人国际联合实验室、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室。学科优势：体外诊断领域显著，疫情期间联合开发新冠核酸检测、抗原检测、抗体检测产品并获NMPA注册；医学影像技术方向在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势；康复治疗方向依托省人民医院康复医学科，综合实力强；智能医学工程方向聚焦阿尔茨海默病智能预警生物标志物，居国际领跑水平。
+三、主要研究方向：医学检验技术方向负责人吕建新教授，研究方向包括重大疾病新型生物标志物筛选及机制、新发突发传染病生物标志物及致病机制、重大疾病体外诊断检测技术、新型药物系统治疗难治疾病、神经免疫与再生；卫生检验检疫方向负责人金大志研究员，研究方向包括新发突发传染病病原体检测检验新技术、艰难梭菌致病机制及耐药机制、卫生检验技术；医学影像技术方向负责人徐秀芳教授，研究方向包括多参数MRI、肿瘤分子影像学、神经导航引导脑肿瘤穿刺技术、脑肿瘤术前功能区定位；康复治疗方向负责人倪湘明教授（附属人民医院），研究方向包括技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病；智能医学工程方向负责人李海教授，研究方向包括脑认知与脑疾病智能诊疗及康复、健康大数据与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断。
+四、师资队伍与领军人物：专任教师90人，高级职称53人（占30%以上），博士55人，硕导69人（正高35人、博士46人）。人才称号：教育部医学技术类专业技能教授委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。学科领军人物：吕建新教授（学位点负责人，国家百千万人才工程、国家行业企业专家、15万人计划技术人才、领军人才，主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技奖一等奖3项、优秀教学成果奖2项）；徐秀芳教授（浙江省151人才第三层次、省高校中青年学科带头人、研究生院院长、医学影像学院院长，国家一流本科专业建设点负责人）；叶祥明教授（省人民医院主任医师、二级教授、博导，省卫生领军人才，国家区域医疗中心浙江省重点培育专科康复医学学科带头人，主持国家级课题3项、省重大课题2项，发表SCI论文98篇）；金大志研究员（美国华盛顿大学博士后，省创新人才，主持国家自然科学基金面上项目、863子项、科技部重大专项子课题等25项，发表SCI论文50多篇，获省科技进步二等奖1项、三等奖1项）；李凯教授（信息工程学院院长，复旦大学公共卫生学院博士，早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长）。
+五、硕士培养与毕业去向：培养目标为面向健康中国发展需要，培养熟练掌握医学技术领域专业知识技能、具有创新实践能力的高层次应用型人才；培养方式为教学、专业实践与学位论文相结合；学制三年，最长不超过五年；课程学分要求学业课程不少于24学分、专业必修课分方向不少于12学分、专业选修课不少于5-6学分；培养环节为第二学期开题、第三四学期过程性考核、研一第二学期论文答辩。就业方向涵盖医院科室（检验科、输血科、病理科、放射科、超声科、康复医学科、骨科、神经科、运动医学科）、疾控中心（CDC）、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等。
+六、2026年招考计划：计划招生34人（仅供参考，以教育部正式下达人数为准）；初试科目为思想政治理论、英语（统考）及按方向自主命题的专业课（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；考试大纲包括考试内容、形式、试卷结构、知识点、参考书目；实践分值300分、考试时长180分钟；检验综合占比为卫生生物学检验40%、生物化学检验30%、微生物学检验30%；复试采用线上线下结合（目前以线下为主），初试占60%、复试占40%，复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%。
+七、考生问答：就业前景广阔，可深造读博、进入三甲医院、疾控中心、企业等，研究生学历有核心竞争力；备考建议为暑期是关键时期，英语难度介于四级和六级之间，建议做真题，并关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲和参考书；允许非本专业考生跨专业报考医学技术专业；学校重视竞赛，通过以赛促学、以赛促教、以赛促改提高教学质量；学校有三个校区，主校区在市中心黄路校区，交通便利。
 # 达成共识
-**2026年计划招生34人（后提及32人），仅供参照，以教育部2026年正式下达人数为准。**
-**初试科目为思想政治理论、英语及对应方向专业综合，专业综合满分300分，考试时长180分钟。**
-**复试采用线上线下结合、目前以线下为主，初试占60%、复试占40%，复试内容分英语能力测试20%、专业能力测试40%、综合能力测试40%。**
-**允许非该专业本科考生跨专业自主报考医学技术专业。**
-&gt; 允许非该专业的考生跨专业来报考我们这个医学技术。
+各方确认的信息与共识：杭州医学院医学技术专业硕士点于2024年获批，由检验医学院、生物工程学院合署办公，共建学院包括医学影像学院、康复学院和信息工程学院，聚焦检验技术（细分为医检和卫检）、医学影像技术、康复治疗、智能医学工程四个方向；2025年录取64人，其中检验方向38人、影像方向11人、康复方向13人、智能医学工程方向2人。学科建设方面，医学技术学科2023年获批省一流学科B类，近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万，横向合作课题经费2200多万，获省科技进步一等奖2项、二等奖1项、三等奖2项，建有国家级一流本科课程2门、国家级一流本科专业建设点2个及多个省级科研平台。师资队伍方面，专任教师90人，高级职称53人（占30%以上），博士55人，硕导69人（正高35人、博士46人），拥有教育部医学技术类专业技能教授委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。培养与就业方面，学制三年（最长不超过五年），课程学分要求学业课程不少于24学分、专业必修课分方向不少于12学分、专业选修课不少于5-6学分，培养环节为第二学期开题、第三四学期过程性考核、研一第二学期论文答辩；就业方向涵盖医院科室、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等。2026年招考计划方面，计划招生34人（仅供参考，以教育部正式下达人数为准），初试科目为思想政治理论、英语（统考）及按方向自主命题的专业课，复试初试占60%、复试占40%。考生问答方面，就业前景广阔，可深造读博、进入三甲医院、疾控中心、企业等，研究生学历有核心竞争力；备考建议为暑期是关键时期，英语难度介于四级和六级之间，建议做真题，并关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲和参考书；允许非本专业考生跨专业报考医学技术专业；学校重视竞赛，通过以赛促学、以赛促教、以赛促改提高教学质量；学校有三个校区，主校区在市中心黄路校区，交通便利。
 # 待协调事项
 无</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t>23026/2233</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23026/3652</t>
         </is>
       </c>
     </row>
@@ -10598,46 +10488,30 @@
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课为历史小论文写作讲评课，围绕自命题类、观点提示类、图表信息类三类题型讲解解题步骤与方法，并逐一分析学生作答。总体要求是观点必须明确亮出，不能只是简单陈述或加个名词；论证写两到三条，不宜太多，要能支撑论点；先打开学术背景再引出自己的观点；可用序号也可直接罗列，但逻辑要清晰，按时间脉络（如700时期、明清时期）或国内外等维度罗列清楚；最后论述要升华观点，不能简单照抄观点。自命题类以武汉长江大桥为例，学生作答涉及新中国成立、改革开放、对内改革对外开放的时间顺序，老师指出按顺序应先写对内改革再写对外开放，并强调要写清时间和重大国家利益。观点提示类以1940年抗战时期某材料为例，学生分析四个观点并选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。图表信息类以中国历代民德等级变化图表为例，涉及春秋、东汉、宋明等时期，讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系。
+本次课程为历史小论文写作指导课，围绕小论文写作的解题步骤与方法展开。课程首先强调观点必须明确，论证一般写两到三条，逻辑要清晰，最后需总结升华。随后通过自命题、观点提示、图表信息等题型进行例题分析，讲解审题、读材料、列事实、论述升华的步骤。以武汉长江大桥为例，指出学生答案存在背景、对内改革、对外开放等时间顺序问题。观点提示类题型需选择核心观点，明确表达判断，不能照抄材料，并结合时代背景论证。图表信息类需迅速提取关键信息，分析关系变化，结合社会状态与思想（如儒家思想）进行论证。
 # 核心知识点梳理
-**一、小论文写作总体要求**
-- **观点必须明确亮出**：不能只是简单陈述或加个名词，要把自己的观点亮出来，观点还要有凝聚力。
-- **论证写两到三条**：不宜太多，要能支撑论点；先打开学术背景，再引出自己的观点。
-- **逻辑清晰**：可用序号，也可不用序号直接罗列，但要让老师看清写了几条；可按时间脉络（如700时期、明清时期）或国内外、内衣外衣等维度罗列清楚。
-- **最后论述要升华**：不能简单把观点抄一遍，要说明写这个东西是为了什么。
-**二、自命题类解题步骤**
-1. 先审题：看要求，注意「小红帽」的要求及形成标准。
-2. 认真读材料：先抓主要信息，再细看它们之间的关系。
-3. 题目先写好，再罗列事实：事实要与材料相关，不要乱罗列。
-4. 最后进行升华。
-案例：武汉长江大桥。学生作答涉及新中国成立、改革开放；老师指出按时间顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
-**三、观点提示类解题方法**
-- 先看有哪些观点，按选择和观点的关系处理。
-- 选择核心观点，清晰表明自己认为正确或错误，把不同观点在论点中详细表述。
-- 注意不能照抄。
-- 最后简单总结观点并升华。
-案例：1940年抗战时期某材料，四个观点分别为：国民对本国历史应略有所知；了解本国利益会有威胁和利益；对本国历史有敬意则不会偏激；经济方面观点。学生选择第二条作答，涉及中华文化优越性、丝绸之路、四大发明对欧洲贡献等。
-**四、图表信息类解题方法**
-- 迅速看图表关键信息，包括题头、横向纵向信息。
-- 注意信息之间的关系变化，提取有效信息再分析。
-案例：中国历代民德等级变化图表，涉及春秋、东汉、宋明等时期；讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
+**小论文写作基本要求**：观点必须明确，不能只是陈述形式；论证一般写两到三条，不宜过多；内容需支撑论点；写作顺序可先写背景学术报告再写观点；可用序号或直接列出，但逻辑要清晰，如按时间脉络或国内外分类；最后需进行总结升华，不能简单重复观点。
+**自命题类题型解题步骤**：先审题，注意要求如世界史知识、范围限制、小红帽要求及形成标准；再读材料，抓主要信息，细看关系；最后控制，先写题目，罗列事实，与材料相关，再论述升华。以武汉长江大桥为例，指出背景、对内改革、对外开放等时间顺序问题。
+**观点提示类题型**：需先看观点，选择核心观点，明确表达自己的判断，不能照抄材料；用角度分析，最后总结升华。以1940年材料为例，分析四个观点，学生选择第二条，讨论中华文化优越性、丝绸之路、四大发明等，并指出需结合时代背景。
+**图表信息类题型**：需迅速看图表关键信息，如题头、横向纵向信息，注意关系变化，提取有效信息分析。以中国历代民德等级变化图为例，讨论春秋、东汉、宋明等时期，结合社会状态、思想如儒家思想，并分析官方答案，如梁启超观点、唐朝国力与民德关系等。
 # 课堂互动与答疑
-问 → 答：学生就武汉长江大桥一题作答，涉及新中国成立、改革开放、对内改革对外开放的时间顺序。老师指出按顺序应先写对内改革，再写对外开放，并强调要写清时间和重大国家利益。
-问 → 答：学生就1940年抗战时期材料分析四个观点并选择第二条作答。老师追问为什么在这个时期写这个东西，提醒学生写的时候要想清楚写作背景。
-问 → 答：学生就中国历代民德等级变化图表作答，涉及春秋、东汉、宋明等时期。老师引导讨论唐朝国力强盛但民德、宋明民德较高与社会状态的关系，以及国家是否强盛、民德是否高尚与制度是否改善的关系。
-&gt; 观点必须明确亮出，不能只是简单陈述或加个名词。
-&gt; 论证写两到三条，不宜太多，要能支撑论点。
-&gt; 最后论述要升华，不能简单把观点抄一遍。
+问：武汉长江大桥这道题，学生写的答案有什么问题？
+答：教师指出，学生答案存在背景、对内改革、对外开放等时间顺序问题，应先写对内改革，再写对外开放。
+问：观点提示类题型中，1940年材料有四个观点，如何选择？
+答：学生选择第二条，讨论中华文化优越性、丝绸之路、四大发明等，教师指出需结合时代背景，如1940年抗战时期，文人用回攻法存在致命缺点，容易否定我们的理由。
+问：图表信息类题型中，中国历代民德等级变化图如何分析？
+答：教师引导学生讨论春秋、东汉、宋明等时期，结合社会状态、思想如儒家思想，并分析官方答案，如梁启超观点、唐朝国力与民德关系等。
+&gt; 教师提醒：写小论文时，观点必须明确，不能只是陈述形式；论证一般写两到三条，不宜过多；最后需进行总结升华，不能简单重复观点。
 # 课后任务与学习建议
 未提及</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>12357/1540</t>
+        <v>33.7</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12357/1107</t>
         </is>
       </c>
     </row>
@@ -10794,19 +10668,19 @@
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t># 报告概况
-国务院总理李强代表国务院向第十四届全国人民代表大会第三次会议作政府工作报告，请代表审议并请全国政协委员提出意见。报告回顾2024年工作，指出过去一年我国发展历程很不平凡，党的二十届三中全会对进一步全面深化改革、推进中国式现代化作出部署，我们隆重庆祝中华人民共和国成立75周年；面对外部压力加大、内部困难增多的复杂严峻形势，经济运行总体平稳、稳中有进，全年经济社会发展主要目标任务顺利完成，高质量发展扎实推进，新质生产力稳步发展。报告同时指出面临的困难与挑战，明确2025年经济社会发展总体要求和政策取向，并部署2025年政府工作任务。报告强调，今年是十四五规划收官之年，要高质量完成十四五规划目标任务，为实现十四五良好开局打牢基础，并开展十五规划编制工作。
+《政府工作报告》由国务院总理李强在第十四届全国人民代表大会第三次会议上代表国务院作报告，报告期间为2024年全年及2025年工作部署。报告回顾2024年工作，指出经济运行总体平稳、稳中有进，国内生产总值达134.9万亿元、增长5%，城镇新增就业1256万人，居民消费价格上涨0.2%，粮食产量1.4万亿斤，新能源汽车产量突破1300万辆，嫦娥六号实现月球背面采样返回；同时指出外部环境复杂严峻，内需不振、预期偏弱等问题。报告提出2025年经济社会发展总体要求，坚持稳中求进工作总基调，实施更加积极有为的宏观政策，推动经济持续回升向好，高质量完成“十四五”规划目标任务。整体基调务实进取，既正视困难挑战，又坚定发展信心。
 # 核心政策
-2025年主要预期目标：国内生产总值增长**5%左右**；城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**；居民消费价格涨幅**2%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.4万亿斤左右**；单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。财政政策方面，实施更加积极的财政政策，今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；发行超长期特别国债**1.3万亿元**；发行特别国债**5000亿元**，支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。货币政策方面，实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配。政策取向强调强化宏观政策民生导向，经济政策着力点更多转向惠民生、促消费，推动更多资金资源投资于人、服务于民生；打好政策组合拳，健全和用好宏观政策取向一致性评估工作机制。
+2025年主要预期目标：**国内生产总值增长5%左右**，**城镇调查失业率5.5%左右**，**城镇新增就业1200万人以上**，**居民消费价格涨幅2%左右**，居民收入增长和经济增长同步，国际收支保持基本平衡，**粮食产量1.4万亿斤左右**，**单位国内生产总值能耗降低3%左右**，生态环境质量持续改善。财政政策：**赤字率拟按4%左右安排**，**赤字规模5.66万亿元**，拟发行**超长期特别国债1.3万亿元**，拟发行**特别国债5000亿元**支持国有大型商业银行补充资本，安排**地方政府专项债券4.4万亿元**，合计新增政府债务总规模**11.86万亿元**。货币政策：实施适度宽松的货币政策，适时降准降息，保持流动性充裕。
 # 重点工作
-经济领域：大力提振消费、提高投资效益，全方位扩大国内需求，实施提振消费专项行动，安排超长期特别国债**3000亿元**支持消费品以旧换新，今年中央预算内投资已安排**7350亿元**；因地制宜发展新质生产力，加快建设现代化产业体系，培育生物制造、量子科技、具身智能、6G等未来产业，持续推进人工智能加行动；推动标志性改革举措加快落地，高质量完成国有企业改革深化提升行动，纵深推进全国统一大市场建设，综合整治内卷式竞争；扩大高水平对外开放，稳外贸、稳外资，扩大电信、医疗、教育等领域开放试点，推动高质量共建一带一路走深走实。民生领域：更大力度稳定和扩大就业，实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；强化基本医疗卫生服务，深化以公益性为导向的公立医院改革，优化药品集采政策；完善社会保障和服务政策，城乡居民基本养老金最低标准再提高**20元**，适当提高退休人员基本养老金，制定促进生育政策、发放育儿补贴；加强精神文明建设，推进群众身边运动场地设施建设。科教领域：深入实施科教兴国战略，制定实施教育强国建设三年行动计划，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科、加快双一流建设；推进高水平科技自立自强，加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合。三农与区域领域：着力抓好三农工作，稳定粮食播种面积，严守耕地红线，有序推进第二轮土地承包到期后再延长30年试点、扩大整省试点范围；推进新型城镇化和区域协调发展，科学有序推进农业转移人口市民化，支持经济大省挑大梁。环保领域：协同推进降碳、减污、扩绿、增长，持续深入推进蓝天碧水净土保卫战，建立一批零碳园区、零碳工厂，加快建设沙戈荒新能源基地。风险防范领域：有效防范化解重点领域风险，持续用力推动房地产市场止跌回稳，稳妥化解地方政府债务风险，积极防范金融领域风险。&gt; 报告强调，确保十四五规划圆满收官，为以中国式现代化全面推进强国建设、民族复兴伟业不懈奋斗。</t>
+**一、经济领域**：大力提振消费、提高投资效益，全方位扩大国内需求，实施提振消费专项行动，安排超长期特别国债3000亿元支持消费品以旧换新；因地制宜发展新质生产力，培育壮大新兴产业、未来产业，推动传统产业改造升级，激发数字经济创新活力；扩大高水平对外开放，稳定对外贸易发展，大力鼓励外商投资，推动高质量共建“一带一路”走深走实。**二、民生领域**：更大力度稳定和扩大就业，实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；强化基本医疗卫生服务，深化以公益性为导向的公立医院改革；完善社会保障和服务政策，城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金，制定促进生育政策、发放育儿补贴；着力抓好“三农”工作，持续增强粮食等重要农产品稳产保供能力，巩固拓展脱贫攻坚成果。**三、生态环保领域**：协同推进降碳、减污、扩绿、增长，加强污染防治和生态建设，积极稳妥推进碳达峰碳中和，建立零碳园区、零碳工厂，开展煤电低碳化改造试点示范。**四、改革与风险防范**：推动标志性改革举措加快落地，高质量完成国有企业改革深化提升行动，纵深推进全国统一大市场建设；有效防范化解重点领域风险，持续用力推动房地产市场止跌回稳，稳妥化解地方政府债务风险，积极防范金融领域风险。</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>10273/1661</t>
+        <v>35.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10273/1199</t>
         </is>
       </c>
     </row>
@@ -11019,20 +10893,20 @@
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为景城苑项目物业管理服务招标答辩与评审，三家投标单位依次陈述并回答评委提问。长沙富佳物业答辩称改造项目已在标书117页列明共12大改造点、预计一年内完成，针对车辆乱停将先分析原因再增加停车位或派保安客服现场劝阻，承接查验方面提出提前两周项目负责人入场摸底、提前一周服务人员到位培训，交接不畅时先私下沟通、再请业委会或街道社区组织协调会、仍无法解决则在业委会及业主大会和街道社区许可下采取强制措施，并针对监控门禁失效提出增设人行门禁、升级大堂报到系统、地面增设隔离墩、建设外围停车场、增设电动车停车场五方面改善。深圳资平物业介绍公司成立于04年、总部深圳、全国367个项目其中127个业委会项目、创始人陈志平为万科物业创始人，提出洗理静音、疏金活选、疑难杂症、有效提升四步计划，计划半年到八个月内完成、一年以内保证小区有序，团队编制16人、薪酬福利高于同类项目、一线人员直招不外包；包干制方面称湖南11个项目中10个为包干制，强调财务透明和业主知情权，公益服务包括居家上门免费、家政、24小时业主护送服务等有偿和无偿业务；承接查验方面提出与社区街道派出所沟通、与现有物业及业委会明确设备设施和债务债权、按专业线分组并调动集团工程师协助查验、在16人团队基础上增派150%人员；安保方面提出关键岗位用老员工、来访人员车辆登记核实后放行、收集业主车辆信息制定停车管理方案和公约、升级道闸识别外来人员和业主；针对楼层顶层堆放杂物和乱搭乱晒提出宣传引导、联合社区应急管理部门、给业主时间段处理杂物、设集中晾晒区并提供免费上门拉送增值服务，强调要疏而不是强制。评标环节评委打分去掉一个最高分和一个最低分，品牌质量需三人签名，打分环节全程保密、暂停会场网络直播、录像材料不予公开。公布排名为第二名长沙富佳物业管理有限公司72.91分、第三名湖南恒居恒基居业物业管理有限公司60.73分、第四名重庆新东源物业管理有限公司54.48分，第一名中标候选人为深圳市资平物业发展有限公司。
-## 富佳物业答辩
-- 评委问中标后从哪些方面改善小区现状及预计时间，富佳回应改造项目已在标书117页详细说明，共12大改造点，预计一年内完成。针对车辆停放不规范、电动车乱停现象，富佳回应先分析乱停原因（停车场地不够、业主觉得远、不自觉），再针对性制定措施：车位不够则增加停车位，不自觉则派保安和客服现场说服劝阻纠正。承接查验方面，富佳称有丰富二手小区交接经验，提前两周项目负责人入场摸底，提前一周服务人员到位培训；交接分顺利和不顺利两种情况，不顺利时先与县物业私下沟通，公司间无法解决则请业委会或街道社区组织协调会，仍无法解决则在业委会、业主大会及街道社区许可下采取强制措施。针对监控门禁失效与停车管理混乱，富佳提出五方面改善：大门口增设人行门禁系统（微信、卡、密码进出）；升级大堂大门报到系统，录入业主车辆信息统一管理，临时车辆由安保登记放行；地面增设隔离墩禁止公共场所停车，保证消防和人行通道畅通；建设外围停车场并安装停车管理系统；增设电动车停车场。关于类似项目管理经验与满意度收费率，富佳称没有很相似的小区，采取用心倾听、如实记录、马上处理、及时反馈的方法处理业主投诉和反馈。
-- 评委问包干制经验及中标后公益性福利拓展服务，资平称湖南11个项目中10个为包干制，强调财务透明和业主知情权，团队直招，管理干部30%来自现有、60%左右来自现有物业优秀员工及招聘，公益服务包括居家上门免费（材料费业主自买或代购）、家政、24小时业主护送服务等有偿和无偿业务。承接查验方面，资平提出前期准备要充足，与社区街道派出所沟通，与现有物业及业委会明确设备设施和债务债权；按专业线分专业组，调动集团工程师协助查验；在现有16人团队基础上增派150%人员；成立成熟小组，建立标准，确保查出问题不遗留不明事项。安保方面，资平回应关键岗位（门岗、门勤岗、车务）用老员工，对来访人员和车辆管控登记核实后放行；收集业主车辆信息，制定停车管理方案和公约，升级道闸识别外来人员和业主；监控方面利用自有设备公司和技术手段解决关键岗位和部位监控。针对楼层顶层堆放杂物与乱搭乱晒，资平提出宣传引导，上门宣传和海报，让业主明白风险和法律责任；联合社区应急管理部门；全面沟通；给业主时间段处理杂物；物业可提供闲置区域临时堆放但限期解决；针对晾晒，设集中晾晒区，物业可提供免费上门拉送增值服务，强调要疏而不是强制。
-## 评标结果公布
-- 评委打分去掉最高最低分，品牌质量需三人签名。公布排名：第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。第一名中标候选人为深圳市资平物业发展有限公司。打分环节全程保密，暂停会场网络直播，录像材料不予公开。</t>
+本次会议为景城苑小区物业招标答疑及评标会，两家物业公司（富家物业、资平物业）分别就改造计划、停车管理、承接查验、安防整改、业主满意度与收费率、楼层杂物与晾晒等问题回答业主提问。富家物业称具体改造项目在标书117页，预计一年内完成；资平物业提出四步举措：进场一个月集中资源整改环境绿化，半年内排查设备设施，八个月内完成重大改造，一年内保证小区有序。评标委员会打分，去掉最高最低分，最终确定深圳市资平物业发展有限公司为中标候选人。
+## 改造计划与时间
+- 富家物业称具体改造项目在标书117页，预计一年内完成。资平物业提出四步举措：进场一个月集中资源整改环境绿化，半年内排查设备设施，八个月内完成重大改造，一年内保证小区有序。
+- 停车管理方面，富家物业提出分析乱停原因，增加停车位、保安劝阻；资平物业提出收集业主车辆信息，制定停车管理方案，升级道闸系统，增设电动车停车场。承接查验方面，富家物业提出提前两周入场摸底，提前一周培训人员，交接不畅时先私下沟通，再请业委会或街道协调，必要时采取强制措施；资平物业强调前期准备、专业分组验收、增派150%人员。安防整改方面，富家物业提出增设人行门禁、升级道闸系统、增设隔离墩、建设外围停车场、增设电动车停车场；资平物业强调关键岗位用老员工，收集车辆信息，升级道闸，技术手段监控。
+## 业主满意度与评标结果
+- 业主满意度与收费率方面，富家物业提出四句话：用心倾听、如实记录、马上处理、及时反馈；资平物业提出财务透明、管理透明、导入顾客管理系统、开展社区文化活动。楼层杂物与晾晒问题，资平物业提出宣传引导、联合社区、上门沟通、设置临时堆放区、集中晾晒区，强调疏导而非强制。评标委员会打分，去掉最高最低分，最终确定深圳市资平物业发展有限公司为中标候选人。</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>11743/1996</t>
+        <v>27.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11743/754</t>
         </is>
       </c>
     </row>
@@ -11155,31 +11029,21 @@
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本期由李正主讲，讲述康熙朝总理南书房大臣、文渊阁大学士陈廷敬的一生。讲座分三个阶段：母亲张氏的开蒙、圣祖康熙的讲师、至公无私的落幕。主讲人首先澄清影视剧中陈廷敬支持撤藩、招抚台湾、维护征剿噶尔丹粮草等情节历史上均未做过，但康熙临终前仍询问大臣中是否有像陈廷敬一样的人。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第六代读书为官，母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》，14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
+本期视频由主讲人李正（正直讲史）讲述康熙朝文渊阁大学士陈廷敬的一生，按母亲张氏开蒙、康熙讲师、至公无私落幕三个阶段展开。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，书香门第，六代读书人。其母张氏自幼读书，亲自为陈廷敬开蒙，陈廷敬6岁前已背完论语、孟子、大学、中庸及诗经。陈廷敬14岁中秀才，20岁中举人，21岁中进士，入翰林院任庶吉士，因与直隶陈敬重名主动上书改名，顺治赐名廷敬。顺治18年顺治驾崩，母亲病倒，陈廷敬请假归乡三年。回朝后，陈廷敬历任国子监司业、日讲起居注官、经筵讲官、翰林院掌院学士，整顿国子监送礼风气，其母去世时康熙打破满汉界限派大臣祭奠并追封其母。康熙23年任左都御史，针对捐纳买官者提出追加考试，获康熙支持；此后历任工部、户部、吏部尚书。康熙26年湖广巡抚张谦贪污案牵连陈廷敬，陈廷敬否认受贿，康熙下令只处理张谦不扩大株连，陈廷敬主动辞官但留京修书，康熙29年复出再任左都御史。康熙42年升文渊阁大学士并总理南书房，康熙46年起多次申请退休均被拒，直至康熙49年第四次申请才获准，康熙赐匾额和楹联并称自此不再给人写字。陈廷敬一生清廉，康熙对其信任有加，最终在康熙49年准其退休。
 # 核心观点与论证
-第一阶段「妈妈张氏的开蒙」：论点为陈廷敬童年学习一大半在母亲张氏关照与注视下展开。论据包括：母亲张氏自幼随父张弘毅读书，通晓儒家经典与《资治通鉴》，嫁入陈家后每日干完家务即读书背诵，半夜不睡继续看书；陈廷敬6岁外出上学前已由母亲口授背完四书与《诗经》；9岁作《咏牡丹》诗，母亲夸其为天才；14岁以童子第一入州学，20岁中举人，21岁中进士入选翰林院庶吉士。
-第二阶段「圣祖康熙的讲师」：论点为康熙重用陈廷敬主要因其课教得好、专业过硬、教学风格外放狠辣。论据包括：陈廷敬入翰林时与直隶通州同届进士陈敬重名，因对方不习清书被顺治点名批评并罚俸一年，22岁的陈廷敬主动上书改名廷敬，传说廷字为顺治所赐；顺治18年庶吉士毕业考试获同届第一，授秘书院检讨；顺治驾崩、母亲病倒后请假归乡三年；康熙六年考察一等称职，32岁升国子监司业，整顿国子监拒收学生见面礼，两年内连升三级，34岁官居翰林院侍讲学士，35岁被19岁康熙任为日讲官；康熙15年九月以内阁学士兼礼部侍郎充经筵讲官，时年39岁；康熙16年正月任翰林院长院学士教习庶吉士，同年母亲张氏去世，终年59岁，康熙令满汉一体遣大臣往祭，礼部以封号不合规反对，康熙追封按学士品级官方祭奠。
-第三阶段「至公无私的落幕」：论点为陈廷敬21岁入官场，75岁去世，宦海浮沉50年声名清白、恪守初心。论据包括：康熙20年守孝三年后重返官场执掌翰林院；康熙23年47岁升从一品左都御史，上奏要求捐纳买官者正式上岗前追加考试，吏部反对，康熙支持并令各地督府详查已任命官员，凡不识字义者查参修治；此后连续出任工部、户部、吏部三部尚书。康熙26年50岁时湖广巡抚张谦贪污案发，张谦为陈廷敬老乡兼亲家，口供称曾贿赂陈廷敬、徐乾学、高士奇，证据为三人劝其好好当官的信件；康熙传旨主审官马齐只处理张谦一人，不得扩大株连，其他人事后密查；51岁陈廷敬主动上书辞官，康熙准许辞官但留京修书；康熙29年53岁重新启用为左都御史，后一年刑部尚书、六年户部尚书、四年吏部尚书；康熙42年66岁升文渊阁大学士兼总理南书房；康熙46年70岁起连续三次申请退休被拒，康熙49年73岁第四次申请获准，康熙赐匾额五亭山村及楹联；两年后病逝，终年75岁，谥号文贞。
-争议点：张谦案真相至今没有公开定论，康熙一时间无法确定徐乾学、高士奇、陈廷敬三人谁干净谁不干净；主讲人个人倾向陈廷敬无辜，理由为李光地称张谦案始终皆徐乾学所为、徐乾学贪污事迹多且热衷结党、徐乾学与高士奇后均因贪污被罢官而陈廷敬仅辞官一年即被康熙重新启用为左都御史。
+讲座按三个阶段展开：第一阶段“妈妈张氏的开蒙”，主讲人指出陈廷敬的童年教育由母亲张氏负责，张氏自幼随父张弘毅读书，精通儒家经典，陈廷敬6岁前已背完《论语》《孟子》《大学》《中庸》及《诗经》，9岁作《咏牡丹》获母亲称赞。陈廷敬14岁以全省第一中秀才，20岁中举人，21岁中进士入翰林院任庶吉士，因与直隶陈敬重名主动上书改名，顺治赐名廷敬。顺治18年顺治驾崩，母亲病倒，陈廷敬请假归乡三年。第二阶段“圣祖康熙的讲师”，陈廷敬回朝后康熙六年考察一等，两年后升国子监司业，整顿国子监送礼风气；康熙11年充日讲起居注官，康熙15年充经筵讲官，康熙16年任翰林院掌院学士。其母去世时，康熙打破满汉界限派大臣祭奠并追封其母。第三阶段“至公无私的落幕”，康熙23年任左都御史，针对捐纳买官者提出追加考试，吏部反对但康熙支持；此后历任工部、户部、吏部尚书。康熙26年湖广巡抚张谦贪污案牵连陈廷敬，张谦称曾贿赂陈廷敬，陈廷敬否认，康熙下令只处理张谦不扩大株连，陈廷敬主动辞官但留京修书，康熙29年复出再任左都御史。康熙42年升文渊阁大学士并总理南书房，康熙46年起多次申请退休均被拒，直至康熙49年第四次申请才获准，康熙赐匾额和楹联并称自此不再给人写字。主讲人强调陈廷敬一生清廉，康熙对其信任有加，最终在康熙49年准其退休。
 # 金句总结
-「朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？」——背景：康熙临终前仍询问陈廷敬，体现康熙对陈廷敬的念念不忘。
-「无鼠相存，譬犹唇齿，不必智者而知之。全记上书以讨荆州自效，明年全破斩云长传其手，全其屯权也哉。」——背景：陈廷敬在文集中指责孙权背刺关羽，体现其教学风格外放狠辣、三观坚定。
-「以平靖世将握秦而恩福待，吾何以劝劳臣乎？」——背景：礼部反对官方祭奠陈廷敬母亲，康熙以此表态，最终追封按学士品级祭奠。
-「自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。」——背景：陈廷敬任左都御史时上奏要求捐纳买官者追加考试。
-「临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治。」——背景：康熙支持陈廷敬并令各地督府详查已任命官员。
-「臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节，所以臣之心迹极此可白，而臣之自处虚实所疑，唯当隐退田间，永衔恩于高厚。」——背景：陈廷敬因张谦案主动上书辞官。
-「朕特殊匾联赐卿，自此不与人写字矣。」——背景：康熙49年准陈廷敬退休，赐匾额五亭山村及楹联。
-「苟正其身矣，于从政乎何有？」——背景：主讲人引《论语》总结陈廷敬一生，称其儿时学过的道理直到死都没有违背过。
+主讲人引用康熙原话：“朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？”体现康熙对陈廷敬的倚重。陈廷敬自述：“臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。”表明其清廉自守。主讲人总结：“清者自清，浊者自浊，有时也并非一句空话。”并引用《论语》“苟正其身矣，于从政乎何有？”强调品行端正对治理的重要性。
 # Q&amp;A 环节
 未提及</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>9132/2003</t>
+        <v>49</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9132/1307</t>
         </is>
       </c>
     </row>
@@ -11800,74 +11664,29 @@
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本次对话由马先生与当年明月参与，围绕刚播完的日本历史剧《大奥》与《明朝那些事》展开。当年明月指出《大奥》三部跨越日本晚清至明治维新前，吸引他的是严谨精神，剧中演员认真、片头将军出场时众人呈45度鞠躬的场面令他印象深刻；马先生补充大奥即后宫之意，日本话中“奥”指屋子最深处，大奥规矩严谨、后宫不许进人。当年明月由此引申日本文化核心是极端精神，即所有事情做到尽头，并以日本战后用30年成为世界第二经济强国、且是强国中唯一没有资源的国家为例。马先生则从多次赴日经历谈到日本人的坚韧不拔与忠诚，称日本是忠诚文化的典型国家，并举例日本豆腐厂规定当天做当天卖、夜里11点45分所有人坐着看表、12点整才开始干活。话题转向明朝历史与《明朝那些事》，当年明月表示自己写明朝是因为明史最熟、资料最多，历史研究两大难点是先秦与明清，明清资料如明实录几千万字、明通鉴、明史记事本末、明会典等堆得比山高，但一个说法可能有七个不同。当年明月表示推崇朱元璋，因为他是历史上唯一由最底层乞丐坐上皇位的人，刘邦好歹是村长，朱元璋要过饭、知道每一层猫腻所以疑心重，推翻元朝当上皇帝并定下明朝规章制度、基本没有太大改动。当年明月还称“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因为史书只留下照片、而古人的生活是录像，不知道当时的前因后果，不能套用。
+本期《锵锵三人行》节目围绕日本历史剧《大奥》与明朝历史展开，受访者为《明朝那些事儿》作者当年明月及嘉宾马先生。节目首先讨论《大奥》所反映的日本历史阶段与文化精神，对比中日文化差异，涉及忠诚、极端精神、终身雇佣制等话题；随后当年明月解释其写作明史的原因，谈及朱元璋的崛起、明朝制度、明末市民生活及历史经验教训；最后讨论正德、天启等明代皇帝的个性行为，以及明式家具在国际上的地位，反映当时社会审美。
 # 访谈详细记录
-一、《大奥》与日本文化
-- 当年明月指出《大奥》三部大概前两部相当于中国的晚清到清初这个时段，后来还有一部是在明治维新之前的一段时间，是一个有跨越性的历史剧。
-- 当年明月称吸引他的是觉得有一种严谨的精神，回头看三国演义会看到很多群众演员会笑，但看日本剧看不到笑的，每一个人非常认真、特别有专业精神，而且都像大腕跟那演。他看第一集一个片头就被震了：将军出场的时候，所有的人呈45度开始鞠躬，依次那个场面之华丽，包括色彩，一看就不一样。
-- 马先生称大奥就是咱们的普通话叫后宫，日本话的这个奥是指很深的地方，就是屋子最里处叫奥，比如咱们现在还保留这种痕迹，就是说这个道理，深奥，奥是很深的地方。
-- 当年明月称从大奥那个剧可以看出来，一个日本文化，其实他从头到尾没有变，就是日本人一种精神，叫极端精神，所有的事情要做到尽头。
-- 马先生称日本战后1945年以后，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然，就是他全民族的这种极端精神，是一个国家在战后这样一个不利的局面下，只需要30年的时间，他进入世界第二经济强国，是以绝对量，不是人均量，绝对量，他是一个世界上这个强国里唯一没有资源的国家。
-- 当年明月称日本的文化跟中国的文化存在一个极大的不同，中国的文化精神是中庸，讲究这个世界上有一种道，不是对也不是错，不是黑也不是白，不是真理也不是谬误，就是太极，但是这条路可以走得通，叫融合。他以马先生家具店中拿了一番木头，特别硬的木头，上面刻的是云彩为例，说这么硬的一个东西能做的这么柔软，这就是中庸。
-- 当年明月称日本的精神就恰恰相反，他坚持一个原则，假如一个炮手开炮的时候，当他忘记所有的事情，只记得把这一炮开出去，他就达到了他的最高境界。
-- 马先生称我们文化中有很多东西可以从电视剧里去看，他实际上看很大程度是看日本文化，我们的文化跟他的差异性非常大，所以导致很多民族的这个观念性的冲突。他去过、多次去过日本，在日本中没有感受到很难过的时候，也没有谁对你非礼。文化上的差异从这个电视剧看得清清楚楚，比如日本人的坚韧不拔，他说的做到极致，再有他的一个忠诚，它是一个忠诚文化的典型国家。
-- 马先生称日本人的跳槽率是最高的，每一次跳槽都是社会资源的浪费，你刚把这个人培养好了，能给你为你工作了吧，他跳槽了。当年明月称这是经济学上的一个奇迹，西方经济学还是不能理解，为什么他们有一个原则，经济学原理可以讲，叫终身雇佣制，就是这个缺乏竞争，日本可能公司终身雇佣，不会解雇你的，一定会导致工作效率的极低效，但是日本不对，日本是终身雇用了，人家还是基金特别高。
-- 马先生举例日本豆腐厂规定当天做当天卖，夜里11:45，所有人都在那做好不动手，在那坐着看着表，那表到12点，夜里12点一整，所有人都赶紧开车，最后那秒是8一到那所有人开始干活，然后到4点多钟干完，然后就开始上市。当年明月称这叫一丝不苟。
-- 当年明月称日本没有资源，什么都没有，还经常火山地震，说难听点你跑都没地方跑，所以人本身对这个世界有一种极强的求生欲望，或者说他对于这个世界是悲观的，必须努力求生存的，所以他就学会了一点，人只有融入到那个团体之内，按照一个固定的规则去做事，于是我们才能往前走，才能生存下来。
-- 马先生称日本的这种聪明人都没有生存环境，他社会的那种文化的抵制是非常难过的。他举例日本原来做绳子，可能一根绳子能做到全日本第一的人，他在长达几年的时间内是不赚钱的，他是从这个地把什么批发出来给那个人送去1分钱都不赚，那所有人跟他竞争是竞争不过，因为他是不赚钱为代价的，等他全部把市场都铺平了以后，他会把两张单子给你看，你看我是这个钱进的，就是这个钱卖的，你怎么也得让我挣一点钱吧，你能不能让给我2%，然后这时候是不好意思再给你加个2%，拿这张单子跟这边说，你看我卖了以后这个也不挣，所以你再给我加2%，那全国的东西它就4%就是不得了的一个数，它就挣那么大钱。
-- 当年明月称慢慢来才是最快的方法，所有人按照自己的角度去做自己的，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走，我是商人就做商人事，我是奶妈就做奶妈的事，我是王后就做王后的事，我什么都可以做自己的事，就是不管别人的事，但这种情况下，形成合力就非常可怕。
-- 当年明月称说实话这是很不愿意做日本人，因为他很多时候就像你说盲从，他们本身还有一个特点，有一种寻死的那种潜在欲望，看樱花开的时候不看，发芽都不看，就是落那一天就看，他们总觉得由于常年以来生活在岛国上，确实生态环境太恶劣了，所以他对于死亡他不是说藐视死亡，他是应该说是有点向往的感觉，或者说不惧怕。他称二战日军到中国会有那么暴行，他是一种藐视生命。
-- 马先生称日本民族不是藐视生命，他是重视，是翻着的，日本人在经济危机的时候，很多身家万贯的跳楼。
-二、明朝历史与《明朝那些事》
-- 当年明月称自己写明朝是因为明史最熟，因为明史的资料最多，历史界研究有两个难点，第一个是先秦，第二个难点就是明清，明清没法说，明实录几千万明代史官的记录，明通鉴、明史记事本末、明会典等堆的比山还高，但一个说法可能有七个不同，一个事件可能有七个不同的说法，就好像罗生门，一件事五个人看，个个都不同。
-- 马先生称明朝本身260多年的过程本身就跌宕起伏，从某种意义上讲，明朝几次都要死没死了，土木堡之变、夺门之变就是各种之变特别多，皇上已经被瓦剌军给抓起来了，要把弟弟扶起来，这类事完全构成一个现代版的电视剧，因为只有电视剧才能捏造出来这种极为离奇的情节，但生活中不幸就发生了。
-- 当年明月称推崇朱元璋，因为一个乞丐，历史上由最底层的人坐在位上，叫他独此一个，刘邦好歹是个村长，朱元璋要过饭，他因为知道每一层的猫腻，他就疑心重，但他全知道，这种人才上。他称朱元璋从一起干，一直到最后，推翻元朝，当上了皇帝，定了多少规章制度，明朝的规章制度是由他定下来的，基本上没有什么太大的改动，这个人是多了不起的人才。
-- 马先生称人的因素最大，就是改变时势一定是出现一个人，是英雄史观。
-- 当年明月以亮剑中李云龙没上过军事院校能打仗为例，称会打仗的人打，不用看兵书，一个人到战场上死死生生多少年，没死，最后积累下来经验，然后一上战场就知道敌人会往哪走，我该怎么打。
-- 当年明月称历史最重要的是你要明白它是发生过的，很多人看历史会觉得这个故事好玩，他不好玩，旁观者你看的多好玩，一跺脚就去参加起义去了，那不可能，你想他掉脑袋的。他称你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
-- 马先生称明朝还是有很多时期非常不错，比如明朝的仁宣盛世，现在不怎么提，时间因为太短，晚明的时候尽管过去史书上一代说政治如何如何黑暗，皇帝如何如何不上朝，但老百姓生活很好。
-- 当年明月称明末那段时间很多真相都被掩盖了，那个市民生活特别特别轻松，想去哪去哪，当时连那个皇册都不用了，到处走，而且当时去给人打工，当年江浙一带兴起的工商业，就是给人当雇工，那活得很滋润，就像三言二拍这种市民小说，娱乐产品出现才说明它是有能够养活自己的资本了。后来李自成那个时候闹起义，那是因为那个时候陕西那一带发生了大规模的灾荒。
-- 马先生称当时江南的也比电影中很多当时的器皿中就可以看到人的那个生活的乐趣，比如一个瓷器，我们的工艺品到了明末的时候彻底改观，变得非常精细，有点像日本的工艺，非常精细，日本有很多东西学我们明末的，派了大量的工匠跟中国交流。
-- 当年明月称看到的史料就是穿什么都有，至少江南那一带他确实非常富裕。马先生称吴门画派像文征明、唐寅，都是那个时期的，他如果生活不好，这些人就也画不出那个东西来，他画的一定都是兵荒马乱的。一到朱耷的时候，八大山人，他默了，你看他画的都是那翻白眼，为什么呀？就他对这社会有点愤愤不平了。他前面这部分人，吴门画派的那些人都能画的都是那个小桥流水，画一个风雨归舟图都是充满了欣赏的感觉。
-- 当年明月称我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训，因为这事儿不是你办的，你总觉得那个以往人就该怎么办，都是聪明的，错误的，我们没有意识到一个问题，历史他那个事儿发生的时候是有背景的，当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。他称我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像，在史书上下来的只是一个照片咔嚓，但你不知道为那一幕之前和之后是什么，你就不知道他当时为什么要做这个选择，所以很多人对历史有误解，他总觉得从中可以得到什么经验教训，那千万不能套用。
-- 当年明月称明代这个朝代很有趣，什么都有，宦官专政魏忠贤，文官专政张居正，皇帝专政朱元璋，而且什么都能发生，皇帝出去了还能回来，回来了还能做皇帝。
-- 当年明月称晚明时期就更可笑了，吴三桂要跟满清合作要入关，陈圆圆，但是还有个原因，他认为崇祯死了，当时人家的说法，我们入关是为崇祯皇帝复仇，吴三桂很忠诚于崇祯皇帝，崇祯皇帝当然可以不死，早点跑应该不跑。还有包括1644年就是明朝灭亡那一年，为什么你们曾经打到京城没有人抵抗呢？因为有些史料记载1644年明朝首都北京闹瘟疫，叫疙瘩瘟，今天你看疙瘩瘟就什么天花。
-- 马先生称中国的历史王朝300年都是大限，你一逼近300年的时候，你自己就没了，和人一样，这人一到八九十岁的时候，你的大限就快到了。他称中国历史上如果严格的讲，超过300年大限的只有宋朝，南北宋接上以后，因为他好在是接上的，汉朝中间往往隔断14年是彻底空的，那么他呢是退让了大半个国土，保证了他延续了300年，剩下的唐朝、明朝、清朝都没他。
-- 当年明月称你说你今天数世界上公司超过279人有几家？没有几家，人家公司多容易管呐，当年刚成立的时候可能三五个人，你说明朝做多大多大摊子啊？几千万人。
-- 马先生称中国在宋明这两个朝代是典型的汉人政权，汉人是文人政权，文人肯定是欣赏的审美都比较高，所以他对美的判断不是表象的，但是满族因为他毕竟是个异族，他进来以后呢，他对你的判断都是表象的。他称今天凡是那种非常外在的直观能看到的都卖的非常贵，但是在100年前的时候，就是晚清到民国初年的时候，这个东西值钱的一定是素雅的。
-- 当年明月称明朝皇帝九五至尊，想干什么干什么，但皇上说我要去一趟江南，皇上当然不行，真不行就不行，咱就是不让你去，明武宗要去，不让去不让去，跪金水桥前门，就是全部跪了，跪着抗议，后来气坏了，就到锦衣卫去打，打死了十几个。
-- 马先生称这种文化的力量，我们一直过去有时候老忽略这种力量，我们现在是没这种文化的力量，他文化的力量是一个超出我们想象的。
-- 当年明月称明武宗正德到扬州说我要什么东西，这时候没有啊东西没有了，有也不给，然后就说什么，那行，那我就回去，他让人准备酒席，他说那个吃不了，说怎么办呢？这样吧，把你们那个酒席折合的银两我带回去，我这皇帝他打这个秋风。
-- 马先生称正德皇帝在明朝的整个皇帝不是一个最最特殊的行为，最鬼怪个性，我们对他的过去的评价是非常低的，说他荒淫，报房是他闹的。他称爱当木匠的是天启，最后了直接干活，干完活了他干的乐就更更有意思，他干完活以后，他拆大盆去卖，卖完回来还打听，卖的怎么样？他说卖的很好，他成就感特大。
-- 马先生称他从侧面去反映了当时社会的一种时尚，他绝对不是凭空，当时这个家具在每个人心里边地位高，为什么我们明式家具现在在国际上那么高的地位，这绝对不是偶然的，所有的偶然中一定有个必然的因素，当时皇帝能下那么大力气去做，可见这个东西对他的影响之深。
-- 当年明月称明神宗几十年不上朝，但他不出去，包括明武宗正德，但凡是明朝皇帝，一般说来后人是不会说乾隆自己朝代的呀，我都是明朝人，我怎么会说我朝的皇帝多差呢？为什么他特别差？因为接他班的是嘉靖，嘉靖不是他的儿子，是他堂兄弟，所以他不能够把他写的太好，所以说像正德皇帝为什么说他特别荒淫？我们都来报房，其实就玩，报房，他那个有动物园，他真是有动物园，他里边养了豹子，后宫也是女人嘛，爆房也是女人，放哪都是一样的，不影响其他什么问题。
-- 马先生称正德皇帝是有定论的，说清朝明朝最荒淫的皇帝，那清朝最荒淫的是咸丰，咸丰干的那个事都很过分，但咸丰还留了个种，这正德不留种，这事很奇怪，就他这个人没少找女人，但他不留种。当年明月称不好说。马先生称他有没有生育，有记载他怀过吗？但反正他就是没有正宗的传下来，到嘉靖这是拐弯嘛。
-- 马先生称正德皇帝对东平以外的那个女人确实没兴趣，那女人是被训练过的，禁忌多，太保守了，再说这人是王丽一去就自个就先睡了半边，那个民女不知他是谁，不是圆了干，他就不一样，关键是野花不知道他是。
-- 当年明月称据说是去过，但是这个没有具体的史料能够去，哪个史官说皇上今天出去嫖娼，我要打死了，不能记的。他称这个人绝不是史料上所写的那么那么蠢，他从江南回来，他没有进京城，他在通州先停了半年，为什么呢？先派人打探里边有没有人带，这是史料记载，通州停了半年或一天，先停在这，你们先给我把情况看清楚，京城里有没有人想搞埋伏，搞圈套。马先生称很有城府。
-- 当年明月称这个人还真的是被写坏的，就是嘉靖那个时候因为明武宗实录是嘉靖时候编的，具体说就是嘉靖指派杨廷和这些人编的，这些人一般来说，他都有某些程度的偏颇，因为如果你把他说太好，嘉靖上台先搞了个叫什么大礼仪事件，为这事死了很多人，也折腾了很多人，就会给自己父亲真的明白，因为他父亲是王，他又把他追封为皇帝。所以说历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
-- 马先生称看很多人专家写历史，就觉得现在不爱聊什么西方傲慢与偏见嘛，实际很多人研究历史就有傲慢与偏见，就是你没有设身处地，你老觉得你自个聪明，我判断他昏庸无能。
+议题一：日本历史剧《大奥》与文化差异。当年明月认为《大奥》反映日本历史阶段，前两部相当于中国晚清到清初，第三部在明治维新之前，是一部有跨越性的历史剧。他欣赏该剧的严谨精神，指出日本演员人人认真、有专业精神，将军出场时众人呈45度鞠躬，场面华丽。马先生补充《大奥》即后宫，日本话中“奥”指很深的地方，如“深奥”。当年明月提到日本天皇长期是摆设，实际权力在幕府将军手中，德川家康开创德川幕府后权力集中，天皇曾因没钱办活动而抗议退位。他对比中日文化，认为中国文化精神是中庸，日本精神是极端，所有事情做到尽头，并以日本战后30年成为世界第二经济强国为例，强调这是全民族极端精神的必然结果。马先生指出日本是忠诚文化的典型国家，多次访日未感到难过或受非礼，文化差异从电视剧中看得清楚。当年明月以《大奥》中阿福25岁入宫当奶妈、65岁去世、40年无私心为例，说明日本忠诚文化靠具体事例体现。马先生提到日本豆腐厂规定当天做当天卖，夜里11:45所有人等待，12点整开始干活，体现一丝不苟。当年明月认为日本因资源匮乏、环境恶劣，人必须融入团体按规则做事才能生存，聪明人在日本没有生存环境。他举例日本做绳子的人几年不赚钱，先铺市场再要求加价2%，最终全国加4%获利。马先生强调忠诚文化使民族繁荣，但当年明月表示不愿做日本人，因其有盲从和寻死倾向，如看樱花只看落的那天，对死亡不惧怕甚至向往，并认为二战日军暴行源于藐视生命。马先生反驳称日本民族不是藐视生命而是重视，经济危机时很多身家万贯的人选择自杀。
+议题二：明朝历史与明史研究。当年明月解释为何写明朝历史，因明史资料最多，但历史研究有两个难点：先秦资料少且多编造，明清资料多但说法不一，一个事件可能有七个不同说法，如罗生门。马先生补充明朝260多年过程跌宕起伏，如土木堡之变、夺门之变，皇帝被瓦剌军抓走又回来，构成离奇情节。当年明月推崇朱元璋，因其从乞丐当上皇帝，历史上最底层人坐上帝位独此一个，刘邦好歹是村长，朱元璋要过饭，知道每层猫腻，疑心重但全知道，且明朝规章制度由他定下，基本无大改动。马先生认为人的因素最大，改变时势一定出现一个人，是英雄史观。当年明月以《亮剑》李云龙为例，说明会打仗的人不用看兵书，靠战场经验积累。他讲述朱元璋参加起义是被逼无奈，因信差送信被人告发，只能去起义，强调历史最重要的是明白它是发生过的，旁观者觉得好玩，但当事人要掉脑袋。马先生认为明朝经验能体现在兴亡上，如仁宣盛世、晚明市民生活好，有文徵明、金瓶梅、三言二拍等娱乐产品，江浙工商业兴起，但陕西灾荒导致李自成起义。当年明月指出明末很多真相被掩盖，市民生活轻松，江南富裕，吴门画派如文徵明、唐寅画小桥流水，而八大山人朱耷画翻白眼，因对社会愤愤不平。他引用名言“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，认为历史事件发生时有背景，不能套用经验，史书只是照片，生活是录像。他列举明朝有趣之处：宦官专政魏忠贤、文官专政张居正、皇帝专政朱元璋，皇帝出去还能回来做皇帝。吴三桂入关为崇祯复仇，1644年北京闹瘟疫（疙瘩瘟，可能是天花），明朝灭亡蹊跷。马先生认为中国王朝300年是大限，只有宋朝超过300年，因退让大半个国土延续。
+议题三：明代皇帝与明式家具。马先生认为宋明是典型汉人政权，文人审美高，对美的判断不是表象，而满族是异族，判断是表象的，今天外在直观的东西卖得贵，100年前值钱的一定是素雅的。当年明月提到明武宗正德皇帝要去江南，大臣跪在金水桥前抗议，他打锦衣卫打死十几个。马先生指出正德皇帝被评价为明朝最荒淫的皇帝，但可能被写坏，因接班的嘉靖是堂兄弟，不能把他写太好。当年明月认为正德皇帝有城府，从江南回来在通州停半年，先派人打探京城有无埋伏，史料记载此事。他提到明神宗几十年不上朝，天启皇帝爱当木匠，干完活拆大盆去卖，卖完打听卖得怎么样，成就感特大。马先生认为这反映当时社会时尚，明式家具在国际上地位高绝非偶然，所有偶然中一定有必然因素。
 # 关键引语与金句
+&gt; 慢慢来才是最快的方法。
 &gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 慢慢来才是最快的方法。
-&gt; 历史最重要的是你要明白它是发生过的。
+&gt; 历史最重要的是什么？就是你要明白它是发生过的。
 &gt; 你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。
-&gt; 我们史书上记载下来是什么？照片，而我们实际上我们的生活古人的生活都是录像。
-&gt; 中国的文化精神是中庸。
-&gt; 日本的精神就恰恰相反，他坚持一个原则。
-&gt; 日本战后以后呢，他用30年的时间成为世界第二经济强国，他不是一个偶然，他是一个必然。
-&gt; 他是一个世界上这个强国里唯一没有资源的国家。
-&gt; 这叫一丝不苟。
 &gt; 所有的偶然中一定有个必然的因素。
-&gt; 历史就非常玄幻，就是有些事你看到你以为这么回事，实际上不是这么回事。
+&gt; 日本的文化跟中国的文化存在一个极大的不同，中国的文化精神是中庸。
+&gt; 日本人的坚韧不拔，他说的做到极致，再有他的一个忠诚。
+&gt; 一个人到战场上死死生生多少年，没死，最后积累下来经验，然后我一上战场我就知道敌人会往哪走，我该怎么打。
 &gt; 原话引语……</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>17496/6601</t>
+        <v>42.6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17496/2121</t>
         </is>
       </c>
     </row>
@@ -12238,80 +12057,58 @@
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本次访谈围绕作家余华的写作历程、创作状态与面对批评和网络关注的心态展开。余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段：第一阶段逼自己坐下来写，让屁股和椅子建立友谊；第二阶段受卡夫卡启发，写内心动荡不安的人物；第三阶段受威廉·福克纳启发，用视觉描写替代心理描写，如《狂人日记》中赵家的狗看人一眼。3.0之后没再升级，他认为《活着》可能是4.0版但已不是难题，3.0版本已经是大海，够了。他自述最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品；2006年开始写的一部长篇小说，现在身体状态可能还能维持激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来，他估计能好好写作的时间可能只剩十年左右。他回应《第七天》出来时有教授说他变得仁慈了，说自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。面对批评，他形成的方式是：第一不要去看，第二有些批评要重视；他在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期，但自媒体时代会把几十年前的事情和以前说过的话翻出来，互联网上关于他的话有一半不是他说的。被问及希望以什么姿态留在历史长河，他回答“遗忘的姿态”，假如历史长河里有主题，主题就是一个世界、一个一个人。
+本次采访中，作家余华回顾了其文学创作历程，将创作分为3.0阶段：1.0是逼自己坐下来写，2.0受卡夫卡启发，3.0受福克纳影响，用视觉描写心理。他认为3.0版本已足够，不再升级，写作已成熟，不再追求高度，转而追求宽度。余华认为最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品。他提到2006年开始写的一部长篇小说因感觉远去而搁置，现在身体状态还能维持激烈，但感觉找不回来。他计划开学时与学生见面，处理学校事务后回三亚继续写作，希望尽快完成一部喜剧，改变读者对他悲观印象。余华分享《兄弟》出版时遭遇批评的经历，后来学会不看批评，但重视有道理的批评，如《第七天》中关于小人物善良的批评，会在以后作品中考虑。他谈到网络走红后曾停一年活动，发现自媒体时代会翻旧账，互联网上关于他的话有一半不是他说的。他不担心热度消散，因为他的工作是写作，不是说话。余华分享面对中年危机的感受，认为只有写作能带来新东西。他建议年轻人通过选择知道什么来隔离负面消息，进行自我调节。他希望以遗忘的姿态留在历史长河中，认为历史长河的主题是一个个世界、一个个的人。
 # 访谈详细记录
-一、自学游泳与文学创作的三阶段
-- 余华将自学游泳分为1.0家门口池塘、2.0江河、3.0大海，对应文学创作三个阶段。
-- 第一阶段：逼着自己坐下来写，“让屁股和椅子建立友谊”，这是年轻时候最重要的；如果离开写字桌躺到床上幻想作品多牛逼，可能就不会去写它。
-- 第二阶段：受卡夫卡启发，写内心动荡不安的人物；写一个人物内心平静没有意思，内心动荡不安的话写1万个字。
-- 第三阶段：受威廉·福克纳启发，福克纳写一个穷白人把一个富白人杀了之后的内心状态，采用“让心脏停止跳动，让眼睛睁开”，心理描写没有心理，是视觉描写；如《狂人日记》中赵家的狗看人一眼，就知道这个人精神状态。余华去过精神病医院，认为精神病人说话逻辑是清晰的，只是方向不同。
-- 3.0版本之后没再升级，他认为《活着》可能是4.0版，但对他来说已不是难题，写作已经很成熟；写一个没什么文化的农民讲述自己的故事，要用最朴素的语言。他认为3.0版本已经是大海，够了。
-二、写作状态与身体、感觉的流失
-- 余华认为最好的写作状态在40多岁到50多岁，即《兄弟》到《第七天》期间，但那段最好时间被浪费，只出了两部作品。
-- 2006年开始写的一部长篇小说，时间跨度与《兄弟》一样，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写；现在身体状态可能还能维持这种激烈，但那个时代的感觉没了，80、90年代的感觉在远去，很难找回来。
-- 他估计能好好写作的时间可能只剩十年左右。
-- 他提到《十八岁出门远行》一天就写完，有6000字，对写字较慢的他来说是奇迹。
-三、《兄弟》的创作与时代变化
-- 《兄弟》1996年动笔，当时中国社会变化复杂；2003、2004年重新拿回来写时，庆幸1996年没写完，因为从2004年看，1996年的变化不算什么，那才是真正大的变化。
-四、作品出版间隔与下一步计划
-- 从《在细雨中呼喊》到《兄弟》隔了十年，《兄弟》到《第七天》隔了八年，《第七天》到《文城》又隔了八年。
-- 余华希望快一点，已把这边整理完，开学时要去和学生们见一下，学校还有一些事情要处理，完了以后回三亚继续往前，安安静静把感觉找回来。
-- 被问下一步长篇是否在2029年，余华未明确确认。
-五、童年看海与人生感受
-- 余华童年第一次看到大海，感受到人生是宽广的。
-- 小时候每年夏天在海盐游泳，有一次进入海流，不能挣扎只能跟着海流走，一直漂到40里外才爬上来，赤脚沿海边走回来，天快亮了。海流把他带回海岸线，没有带到太平洋。
-- 在三亚看到童年星空，发现月光是金色的，不是银色的。
-六、《第七天》的仁慈与悲剧/喜剧转向
-- 有教授说《第七天》出来时余华变得仁慈了。余华回应自己活着也蛮仁慈，作品几乎都是悲剧，这次回来选择写一篇喜剧，想先把一个喜剧写完，改变读者对他悲观的印象。
-- 已确认：余华决定先完成一部喜剧作品。
-七、追求宽度而非高度
-- 余华表示对高度已经不追求了，现在追求宽度。认为作为作家，写作能走到的高度已经是现在的高度，允许自己下滑一下但不要下滑太多。
-- 年纪大了，知道自己的能力、长处和还有多少潜力，不再像年轻时充满野心。
-八、文学理想与马尔克斯的影响
-- 余华认为这一代中国作家很大程度上被马尔克斯误导，都想在一本书里写一个世纪的故事，但其实没有必要。
-- 托尔斯泰、狄更斯、莎士比亚、巴尔扎克、福楼拜、司汤达、契诃夫等都没有这样做。马尔克斯写拉丁美洲最混乱的世界所以能写出来，别人不一定写得出来。
-- 余华现在知道自己要什么，就是把所处的时代通过更多方式表现出来。
-九、莫言与莎士比亚故居之行
-- 余华说莫言小说对话精彩，想写话剧，20多年前就开始写话剧，但写了没拿出来。
-- 余华、苏童、莫言三人一起去莎士比亚故居，莫言在雕塑前发誓要成为剧作家，余华认为那是瞎扯，莫言当时在挑帽子，帽子钱还是余华付的，三人买了三顶一模一样的深蓝色帽子，上面有莎士比亚名字，后来找不着了。
-十、面对批评与网络时代的心态
-- 《兄弟》出版时余华以为会是一片赞扬，结果一片骂声，他接受很多采访努力解释。
-- 《第七天》出来时只接收一个采访，告诉朋友们做好思想准备，果然一片骂声。《文城》出来时骂声还有但少一点。
-- 余华找到对待批评的方式：第一不要去看，第二有些批评要重视。批评宋凡平写得太完美没有道理，因为宋凡平不是贯穿全书的人物；但批评《第七天》中社会底层人未必都善良，这句话很好，以后写小人物会考虑进去。
-- 已确认：余华形成对待批评的方式，有道理的批评会在以后作品中考虑。
-十一、网络热度与一年冷静期
-- 余华在互联网火起来后有一年停了一年，任何活动、采访都不做，称为一年冷静期。
-- 按过去经验一年后就在媒体上消失，但自媒体时代不是这样，几十年前的事情都被翻出来，以前说过的话也被翻出来。
-- 互联网上关于他的话有一半不是他说的，比如“精神内耗”“想要命好”等都不是他说的。
-- 他不担心喜欢会消散，因为他的工作是写作，不是靠说话。
-十二、中年危机与自我调节
-- 余华34岁时在年终总结中说成年人每到年底都会发现一种虚无，对生活充满信心的人变成面试者。
-- 当时感觉生活每天在呼吸，人口增加、孩子来了，空间没有变得宽敞。只有写作能得到新的东西，虚构世界带来新东西，现实世界每天都是。
-- 面对年轻人巨大的不安和焦虑，余华认为只有自我调节：发生的事情无法选择让它发生或不发生，但可以选择让自己知道什么、不知道什么，负面消息太多就屏蔽掉，选择积极的。
-十三、希望以遗忘的姿态留在历史长河
-- 被问及希望以什么姿态留在历史长河，余华回答“遗忘的姿态”，就是一个遗忘的人。
-- 那些能够勉强被微风吹进耳朵的人，也是勉强吹进来的。假如历史长河里有主题，主题就是一个世界、一个一个人。
+一、文学创作阶段与理念
+余华将文学创作分为3.0阶段：1.0是逼自己坐下来写，2.0受卡夫卡启发，3.0受福克纳影响，用视觉描写心理。他认为3.0版本已足够，不再升级，写作已成熟，不再追求高度，转而追求宽度。
+二、写作状态与遗憾
+余华认为最好的写作状态在40多岁到50岁，但那段时光被浪费，只出了两部作品。他提到2006年开始写的一部长篇小说因感觉远去而搁置，现在身体状态还能维持激烈，但感觉找不回来。
+三、未来写作计划
+余华希望尽快完成一部喜剧，改变读者对他悲观印象。他计划开学时与学生见面，处理学校事务后回三亚继续写作，找回感觉。
+四、对批评的态度
+余华分享《兄弟》出版时遭遇批评的经历，后来学会不看批评，但重视有道理的批评，如《第七天》中关于小人物善良的批评，会在以后作品中考虑。
+五、网络热度与公众人物
+余华谈到网络走红后曾停一年活动，发现自媒体时代会翻旧账，互联网上关于他的话有一半不是他说的。他不担心热度消散，因为他的工作是写作，不是说话。
+六、中年危机与自我调节
+余华分享面对中年危机的感受，认为只有写作能带来新东西。他建议年轻人通过选择知道什么来隔离负面消息，进行自我调节。
+七、历史长河中的姿态
+余华希望以遗忘的姿态留在历史长河中，认为历史长河的主题是一个个世界、一个个的人。
 # 关键引语与金句
-&gt; 坐下来让屁股和椅子建立友谊，这是很重要的。
-&gt; 假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的。
-&gt; 让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视觉描写。
-&gt; 我觉得我活着也蛮仁慈的。
-&gt; 把悲伤留给虚构，把欢乐留给现实。
-&gt; 第一，你就不要去看就行了。第二，有些批评你要重视。
+&gt; 当年的感觉已经远去，这是很痛苦的，我已经把那个40多最好的一段时间浪费了，就拖了2个多月，活着也蛮认真的。
+&gt; 兄弟出版的时候，我认为肯定是一片太阳，你知道吧？我是带着这样的一种期待去的，结果一片骂声弄得我有点。在互联网上，起码我看到的我看到的啊，关于我这说的话，有一半不是我说的。
+&gt; 假如那个历史的长河里边有一个主题的话，这个主题就是。哎，姑娘，你好，谢谢你，谢谢你过来，哎，对，好的。
+&gt; 假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。
+&gt; 当时。我觉得我将可能我的目标是对着那个托尔斯泰和陀思妥耶夫斯基去的，现在我知道我离他们的距离是不可逾越的，但是我就就是这种野心，这种幻想，然后呢能够支撑让我一篇篇写下来。
+&gt; 福克纳所采用的方式就是让心脏停止跳动，让眼睛睁开。心理描写没有心理，它是视视觉描写。
+&gt; 因为我是去过精神病医院，对精神病人跟你说话逻辑是清晰的，一点都不混乱。但是它的空向跟你是不一个方向，但是逻辑是是是完全是是我们的逻辑。
+&gt; 人不可能永远是在那么一个好的一个状态，因为。作家有时候需要一点运气，作家就是什么时候写什么作品很重要。
+&gt; 我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。
+&gt; 我在这的工作很简单，就就是那个写作，然后呢读书听音乐。还有就是锻炼。
+&gt; 小的时候我每年夏天都在这游泳，有一天我就想一直游，然后我发现自己已经进入一个海流了，我就知道我不能挣扎，我只能跟着海流走，一直到了40里外的那个地方，我才爬上来，然后赤脚沿着海边走回来，天快亮了。
+&gt; 人生就是被无穷无尽的。就是我们永远不知道明天会发生什么，是吧？但是呢，感受不一样。因为小时候的人生的感受是是向前看的，现在的人生感受是往后看来的，就回忆占多了。
+&gt; 所以通过光阴我才发现，其实月光是金色的，它不是银色的。
+&gt; 我觉得海浪带我回家了。假如没有海流的话，我很可能游到一个让我游不回来的地方。
+&gt; 把悲伤悲伤留给虚构，把欢乐留给现实。
+&gt; 我现在追求这个宽度。
+&gt; 我们整整一代中国作家都想在一本书里边写那个一个世纪的故事，但是其实没有必要。
+&gt; 莫言那个，你那是他瞎扯，你知道吧？莫言我是知道的，莫言的小说对话是很精彩的，那么你不会写对话的。
+&gt; 我在莎士比亚的附近发誓，他发什么誓呀？他在那挑选帽子，后来那个帽子钱还是我付的。
+&gt; 但是莎士比亚没有给予我们任何一点灵感。
+&gt; 你只要一年的事情，你马上在媒体上消失了，就马上。但是我后来发现啊，自媒体时代不是这样，他把你的那个几十年前的事情都给翻出来了。
+&gt; 因为我的工作是写作，所以不说话其实也也挺好。
+&gt; 一个成年人每到年底都会发现一种虚无。
+&gt; 只有写作是能够得到一些新的东西，就虚构的世界给你带来一些新的东西，而现实世界是每天都是。
 &gt; 发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。
-&gt; 遗忘的姿态。就是一个遗忘的人。
-&gt; 假如那个历史的长河里边有一个主题的话，这个主题就是一个世界，一个一个人。
-&gt; 我已经把那个40多岁到50岁最好的一段时间浪费掉了。
-&gt; 那个过去那个时代那个感觉没有了。我写到那个80年代的和90年代那个感觉，也在，感觉都在远去。
+&gt; 遗忘的姿态。就是一个遗忘的人，因为那些能够勉强被微风吹进耳朵的人，那是其实那也是勉强吹进来的。假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。
 &gt; 原话引语……</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>11212/3364</t>
+        <v>42</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11212/2398</t>
         </is>
       </c>
     </row>
@@ -12422,46 +12219,21 @@
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次研讨会围绕第二次世界大战欧洲战场最后一次大规模战役——柏林战役展开，由发言人1主讲，系统梳理了战役背景、双方部署、进攻过程、希特勒自杀、德军投降及战后格局。1945年同盟国与苏俄从不同方向攻入德国本土，苏军已进抵奥德河、尼斯河一线，距柏林仅60公里，英美联军刚到达易北河一带，距柏林100至120公里，苏联获得先发制人机会。苏军由朱可夫元帅和克列夫元帅指挥，白俄罗斯第一方面军从奥德河一线北部突击包围，乌克兰第一方面军从南部绕到波斯坦地区实施西部包围，苏军两个方面军总计约250万人形成合围；德军防守约100万人，以从东线撤离的中央集团军群残兵为主力，另有柏林卫戍部队及由老人和16岁以下孩子组成的国民制弹兵部队。战役第一阶段于1945年4月16日开始，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击；因德军在桑多梅日桥头堡之前修筑防线，苏军拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日突进柏林市区，德军温克第十二集团军与苏军周旋。4月30日柏林被围死，苏联红军离希特勒地堡只有两条街，希特勒与夫人艾娃·布劳恩一起举枪自尽，其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据。4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束，战役从4月16日持续到5月2日。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
+本次研讨会由主讲人系统介绍柏林战役的经过与细节，涵盖战役背景、双方兵力、进攻阶段、关键事件及结局，并解答听众关于城市战特点、希特勒自杀、英美未攻柏林、影视推荐等问题。1945年苏军进抵奥德河-尼斯河一线，距柏林60公里，英美联军距柏林100-120公里；苏军白俄罗斯第一方面军（朱可夫）和乌克兰第一方面军（科涅夫）共约250万人，德军中央集团军群残部及国民掷弹兵约100万人。战役于1945年4月16日开始，苏军炮击并突击，4月20日进抵柏林城区，4月24日突入市区；4月30日希特勒自杀，苏军占领国会大厦，5月2日德军投降，5月9日德国无条件投降。主讲人补充了城市战中敌人可从各处攻击、坦克和车辆在街道上易受攻击的特点，以及希特勒在地堡自杀、尸体被焚烧、遗体未全貌导致外界说法不一等细节。关于英美未攻柏林，主讲人说明丘吉尔想抢占柏林，但盟国已协议柏林战后属苏联，艾森豪威尔认为攻占柏林会增加伤亡且得不偿失，不如占领德国精华地带。此外还介绍了易北河会师是偶然、红旗是临时用床单绘制、士兵曾戴抢来的手表被要求摆拍等细节，并推荐苏联《柏林战役》和德国《帝国的毁灭》两部影视作品。
 # 核心观点与论证
-论点一：苏联不惜代价强攻柏林，源于占领柏林可获至高无上的荣誉与战后地位。论据：1945年同盟国和苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题；柏林是法西斯德国大本营及纳粹最大巢穴，谁占领柏林谁在二战后可获得至高无上的地位，因此苏联从上到下团结一致，以柏林为目标进行不惜代价的强攻。
-论点二：苏联在部署上已获得先发制人机会。论据：苏军已进抵奥德河、尼斯河一线，即今天德国和波兰的边境地区，距柏林只有60公里；英美联军才刚刚到达易北河一带，距柏林还有100到120公里。
-论点三：苏军以两个方面军形成合围，兵力占优。论据：白俄罗斯第一方面军指挥官为朱可夫元帅，从奥德河一线、奥德法兰克福方向北部对柏林进行突击与包围；乌克兰第一方面军指挥官为克列夫元帅，由克拉科夫以及德雷斯顿方向前出，从南部绕到柏林前突至波斯坦地区，对柏林实施西部包围。苏军两个方面军总计约250万人，从北部石切清一直到南部德雷斯顿形成合围网。德军主要防守部队为从东线撤离的中央集团军群残缺部队、柏林卫戍部队以及国民制弹兵部队（由年纪较大的老人及16岁以下孩子组成的民兵），总共有约100万人，以中央集团军群残兵为主力。
-论点四：战役进程受德军防线修筑影响而延迟。论据：第一阶段1945年4月16日，苏军以数以千计的火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河突击，乌克兰第一方面军越过尼斯河突击；但由于德军在桑多梅日桥头堡之前修筑防线，一直拖到4月20日左右才进抵柏林城区潘科区及帕卡洛镇一带，24日才突进柏林市区，由白俄罗斯第一方面军进行突击，此时乌克兰第一方面军还在艰难摸索向柏林边缘靠近。德军温克第十二集团军与苏军一直周旋。
-论点五：城市作战与野外作战存在明显区别。论据：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
-论点六：希特勒自杀及遗体争议。论据：1945年4月30日柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽；其部下用汽油焚烧尸体，至今未见到遗体全貌，只有烧焦焦炭，外界说法不一，无确切证据；除少数亲信外，大部分人坚信纳粹没有覆灭，自欺欺人继续战斗，导致谣言盛起。
-论点七：英美未进攻柏林的原因。论据：丘吉尔想抢占柏林，但盟国已达成协议柏林战后属于苏联，会分出一半区域给西方盟国即西柏林；艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤回去，得不偿失，不如占领更多德国精华地带如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，盟军还有求于苏联一起对日本战斗。
-论点八：战役结束与战后格局。论据：4月30日夜间苏军占领国会大厦，5月2日柏林德军全部放下武器投降，除少部分由第九集团军及温克第十二集团军残余部队在其将领温克率领下渡过易北河向英美盟军投降外，柏林城防司令魏德林宣布其余德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，欧洲部分正式结束。战后奠定冷战欧洲部分基调，德国分裂成东西两个德国，边界从罗斯托克到图灵根，直到1990年统一；亚洲部分日本于9月2日在密苏里号签署无条件投降书，二战彻底结束。
+主讲人首先阐述战役背景：1945年同盟国与苏俄已攻入德国本土，纳粹政权覆灭只是时间问题；对苏联而言，占领柏林可获得至高无上的荣誉，因此苏军上下团结一致，以柏林为目标进行不惜代价的强攻。此时苏军进抵奥德河-尼斯河一线，距柏林仅60公里，而英美联军才到达易北河一带，距柏林100-120公里，苏联获得先发制人的机会。苏军部署为白俄罗斯第一方面军（朱可夫元帅）从奥德河-法兰克福方向北部突击与包围，乌克兰第一方面军（科涅夫元帅）由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。德军防守力量主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵（由老人和16岁以下孩子组成的民兵），总计约100万人；苏军两个方面军总计约250万人，从北部的什切青到南部的德累斯顿形成合围网。战役第一阶段自1945年4月16日开始，苏军以数千门火炮和卡秋莎火箭炮轰击德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河突击；因德军在桑多梅日桥头堡的防线修筑，苏军至4月20日左右才进抵柏林城区（潘科区及帕卡洛镇一带），4月24日白俄罗斯第一方面军突入市区，而科涅夫部队仍在向柏林边缘靠近。德军温克的第十二集团军与苏军周旋。主讲人强调城市战特点：敌人可从各处攻击，坦克和车辆在街道上易受攻击，非常困难且危险。4月30日希特勒与夫人艾娃·布劳恩在地堡自杀，尸体被部下焚烧，因遗体未全貌导致外界说法不一。5月2日柏林德军全部缴械投降，柏林城防司令魏德林宣布投降；5月9日德国无条件投降，将所属领空、领海、机械设备及海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）交与盟军及苏俄最高统帅，二战欧洲部分结束。关于英美未攻柏林，主讲人说明丘吉尔想抢占柏林，但盟国已协议柏林战后属苏联，艾森豪威尔认为攻占柏林会增加伤亡且得不偿失，不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带，且盟军还需苏联协助对日作战。战役影响方面，柏林战役奠定冷战欧洲基调，德国分裂为东西两个德国，沿罗斯托克至图林根边界，直至1990年统一。
 # 金句总结
-「谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。」——背景：主讲人分析苏联不惜代价强攻柏林的动机，指出柏林是法西斯德国大本营及纳粹最大巢穴，占领柏林可获至高无上的荣誉与战后地位。
-「城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。」——背景：主讲人回答听众关于城市作战与野外作战区别的提问，说明城市作战的困难与危险。
-「希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了，就和他的夫人艾娃·布劳恩一起。」——背景：主讲人回答听众关于希特勒是否自杀的提问，说明希特勒自杀的原因与方式。
-「除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以说各种流传到民间的说法褒贬不一，导致很多后时候谣言还在盛起。」——背景：主讲人解释希特勒自杀细节为何引人关注，指出遗体被焚烧后无确切证据，导致谣言盛起。
-「与其这样，还不如说是尽可能去占领更多德国的精华地带，比如说慕尼黑、斯图加特以及纽伦堡，还有就是汉堡、法兰克福这些地方，柏林就让给苏联吧。」——背景：主讲人分析艾森豪威尔认为美军攻占柏林得不偿失，不如占领更多德国精华地带。
-「那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。」——背景：发言人5补充红旗插上国会大厦的细节，说明旗帜是士兵临时用床单和颜料绘制。
+主讲人指出：“谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。”此句强调柏林对苏联的战略意义，是苏军不惜代价强攻的核心动因。关于城市战，主讲人说明：“敌人可以从各处攻击你的部队，坦克和车辆在街道上易受攻击，非常困难且危险。”此句概括城市战与野外作战的本质区别。关于希特勒自杀后的影响，主讲人提到：“除了少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己。”此句揭示希特勒尸体被焚烧后外界说法不一、谣言盛起的原因。
 # Q&amp;A 环节
-问：城市作战跟野外作战有什么明显的区别？
-答：城市作战中敌人可从各处攻击，坦克和汽车只能在街道行动，敌人从建筑或街道用机枪攻击，非常困难和危险。
-问：是不是这个战役里面希特勒自杀了？
-答：是的。1945年4月30日，德国离兵败之日不远，柏林已被苏联围死，没有任何突围希望，苏联红军离希特勒所处地堡只有两条街的距离，希特勒不甘于兵败后被苏联俘虏，与夫人艾娃·布劳恩一起举枪自尽。
-问：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么引关注？
-答：因为在他自尽之后，他的部下用汽油把尸体焚烧了，到今天为止也没有见到希特勒遗体全貌，只是获得一堆烧焦的焦炭，外界说法各种不一，也没有确切证据证明。实际上他自杀后尸体被焚烧，除少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗，所以各种流传到民间的说法褒贬不一，导致很多谣言还在盛起。
-问：如果想了解更多这个战役，有什么影视推荐吗？
-答：苏联有拍柏林战役，德国有《帝国的毁灭》。德国角度更多是希特勒最后生平以及关于柏林防守上的人事任命；苏联方面更多强调从高层到基层的各方面描写，高层的运筹帷幄以及基层官兵的舍生忘死。
-问：主要进攻柏林的是苏联方面的部队，那为什么英美他不打柏林呢？
-答：丘吉尔当时想抢占柏林，但盟国事先已在战后德国地盘划分占领上达成协议，柏林战后属于苏联，会分出一半区域给西方盟国即后来的西柏林。美军统帅艾森豪威尔认为美军去攻占柏林会增加不必要伤亡，同时占领柏林后还是要撤回去，得不偿失，不如尽可能占领更多德国精华地带，如慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福，柏林就让给苏联。毕竟打完德国之后，盟军还有求于苏联一起跟日本进行战斗。
-问：这场战役大概持续了多久？
-答：从4月16号开始，一直进行到了5月2号。
-问：有什么书可以看的吗？
-答：可以看朱可夫自传、崔可夫自传，以及斯大林传记里面写到的关于柏林战役后苏俄和西方的博弈，涉及西柏林地区划分以及德国边境重新划定。</t>
+问：城市作战与野外作战有什么明显区别？答：城市战中敌人可从各处攻击，坦克和车辆在街道上易受攻击，敌人可能用火箭筒和机枪从建筑或其他街道攻击，非常困难且危险。问：希特勒是不是在战役中自杀了？答：是的，1945年4月30日，柏林已被苏军围死，苏军距希特勒地堡仅两条街，希特勒不甘被俘，与夫人艾娃·布劳恩一起举枪自尽。问：希特勒自杀细节为何引发关注？答：他自尽后尸体被部下焚烧，至今未获遗体全貌，外界说法不一，导致谣言盛起。问：英美为何不攻打柏林？答：丘吉尔想抢占柏林，但盟国已协议柏林战后属苏联，艾森豪威尔认为攻占柏林会增加伤亡且得不偿失，不如占领德国精华地带，且盟军还需苏联协助对日作战。问：有什么影视推荐？答：苏联有《柏林战役》，德国有《帝国的毁灭》；德国视角侧重希特勒最后生平及人事任命，苏联视角强调高层运筹帷幄与基层官兵舍生忘死。</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>4609/3614</t>
+        <v>40.9</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4609/1989</t>
         </is>
       </c>
     </row>
@@ -12610,20 +12382,20 @@
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-会议围绕生活中约定俗成的规则是否合理以及AI/机器人未来展开自由讨论，并测试多人同时说话的语音标注效果。与会者就买房、结婚生子、工作等规则交换意见，认为经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对；工作方面提出工作可能是合理的，但工作状态应合理，即干自己想做的、不要跟钱太保密，并讨论理想工作状态是每天起来想干啥就干啥、参考自己兴趣干活，举例宠物博主发宠物日常剪视频赚钱、游戏高手，同时提出脏活累活没人愿意承担的问题。在AI与机器人议题上，提出应让AI去做苦活累活而不是搞创作艺术，设想机器人负责生产、人负责享受，提到扫地机器人及未来可打扫家、做饭的机器人，并讨论AI普及普惠到实体、机器人有自己思维后人类能否控制；进一步讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影，提到机器人可能成为犯罪代理人、职业杀手、超级战士，以及智能与思想可能无法分开、思想可能带来不好影响。讨论还涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。
-## 约定俗成规则与理想工作状态讨论
-- 讨论买房、结婚生子、工作等约定俗成规则是否合理；提到经济好时可行、经济不好时不太可以，取决于遇到什么样的人、自身经济能力和能力，不能太绝对。
-- 讨论理想工作状态，提到每天起来想干啥就干啥、参考自己兴趣干活；举例宠物博主发宠物日常剪视频赚钱、游戏高手；提出脏活累活没人愿意承担的问题。
-## AI与机器人替代及失控风险讨论
-- 提出应让AI去做苦活累活而不是搞创作艺术；设想机器人负责生产、人负责享受；提到扫地机器人及未来可打扫家、做饭的机器人；讨论AI普及普惠到实体、机器人有自己思维后人类能否控制。讨论机器人有独立思想意识后可能不受人类控制、罢工、反向控制人类，类比终结者、斯皮尔伯格人工智能电影；提到机器人可能成为犯罪代理人、职业杀手、超级战士；讨论智能与思想可能无法分开，思想可能带来不好影响。涉及半机械人与军事应用，提到合成体、军队单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，以及游戏重返德军总部超级战士、数码宝贝守卫兽和机械装甲兽升级进化成安多路兽；并讨论数码宝贝第一部、第二部剧情，机械邪龙兽是精密机械式超级计算机形成的生命体，安多路兽在九几年已有人脸识别构想，第二部第七集被黑色魔轮控制后仍能通过人工识别和人脸识别判断人是谁，主角嘉儿通过记忆和回忆唤醒其最终记忆。最后讨论两人一起说话时标注效果，提到标注的人需要认识声音、单人麦效果较强，决定同时混一下测试。</t>
+会议围绕结婚、买房、工作等社会约定俗成规则的合理性展开讨论，认为这些规则是否合理取决于个人能力、经济条件及所遇之人，经济条件影响可行性，工作因需创造财富而具有合理性，但理想工作形态应基于个人兴趣，如宠物博主、游戏高手等。讨论延伸到AI与机器人的未来，提出由AI或机器人承担苦活累活，但担忧机器人拥有思想意识后可能不受控制、反抗人类甚至奴役人类，引用终结者、人工智能电影、数码宝贝等例子，并提及智能枪械、外骨骼等军事应用。会议最后进行语音分离标注测试，测试两人同时说话时的标注效果，结论为单人麦克风效果较强，标注人需认识声音。
+## 社会规则合理性讨论
+- 讨论结婚、买房、工作等社会规则的合理性，认为取决于个人能力和遇到的人，经济条件影响可行性。
+- 理想工作形态为根据兴趣选择，如宠物博主、游戏高手，但存在脏活累活无人承担的问题，提出由AI或机器人承担苦活累活。
+## AI与机器人未来风险及语音分离测试
+- 讨论机器人拥有思想意识后可能反抗人类、成为犯罪代理人等风险，引用终结者、人工智能电影、数码宝贝等例子，并提及智能枪械、外骨骼等军事应用；随后进行语音分离标注测试，结论为单人麦克风效果较强，标注人需认识声音。</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>3931/1305</t>
+        <v>18.7</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3931/516</t>
         </is>
       </c>
     </row>
@@ -12718,20 +12490,20 @@
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕哥斯拉系列电影起源、各版本剧情及怪兽设定展开自由讨论，并延伸至核废水、核污染与生物变异话题。1954年第一部哥斯拉电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物并对人类展开报复攻击；哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验破坏生态。美国版剧情方面，2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版方面，人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。关于哥斯拉与奥特曼的关系，两者最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。
-## 哥斯拉电影起源与设定
-- 1954年第一部哥斯拉题材电影诞生，起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
-- 哥斯拉在日本神话中是大自然的守护神，攻击人类因人类无限制搞核试验、破坏大自然生态；相关扩展题材涉及人类频繁搞战争和核试验后唤醒沉睡生物及招致外星生物入侵。
-## 哥斯拉各版本剧情梳理
-- 美国版：2014年第一部中两个物种（蝙蝠）以核弹、核废料为能源，哥斯拉与人类携手将其团灭；第二部人类核试验唤醒沉睡怪兽，基多拉降临地球，人类曾用水下子母弹和核试验试图让哥斯拉窒息，反被基多拉差点溺死，后人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉；第三部哥斯拉大战金刚，反派残余势力将基多拉仅存头颅加装机械，金刚挺身而出与哥斯拉一起打败机械基多拉。日本版：人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀；2016年新哥斯拉为海里蜥蜴类生物喝核废水后不断壮大，吸收核废料升级，人类武器攻击反而增强其战斗力，最后以无人机投放炸弹耗光能量、冷冻剂封印。哥斯拉与奥特曼最早都是圆谷英二导演，但属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星；两者都是正派形象，无法直接战斗；哥斯拉里的反派翼龙拉顿曾在奥特曼作品中与奥特曼战斗过。核废水与核污染影响方面，讨论日本排放核废水、核废料可能导致生物变异；提到切尔诺贝利核反应堆被水泥封存，普里皮亚季和切尔诺贝利方圆百里为无人区，被称为鬼城；认为相比日本，切尔诺贝利至少拦截封存了反应堆。</t>
+会议围绕哥斯拉系列电影剧情展开讨论，发言人1系统梳理了该系列从1954年首部至今约70年的发展脉络，涵盖美日两版不同剧情线：美国版包括2014年《哥斯拉》、2019年《哥斯拉2：怪兽之王》、2021年《哥斯拉大战金刚》，其中基多拉作为外星反派，其残骸被人类改造成机械基多拉；日本版包括2004年《哥斯拉：最后的战斗》（章子怡参演）和2016年《新哥斯拉》。讨论还涉及哥斯拉的起源设定（海底生物吸食核废料变异）、其作为日本神话中大自然守护神的定位，以及哥斯拉与奥特曼的关系（不同时间线、均为正派）。讨论延伸至核废水危害，提及日本排放核废水可能导致生物变异和健康问题（如白血病），并对比切尔诺贝利核事故：该地区生物畸形、反应堆被水泥封存、方圆百里成为无人区，发言人认为日本在核废水处理上不如切尔诺贝利负责。发言人2补充其在日本留学期间因担心核废水影响，购买中国进口的鱼，并指出日本国产食品价格昂贵。
+## 哥斯拉系列电影剧情梳理
+- 哥斯拉起源于1954年首部电影，设定为海底生物吸食核废料后变异成庞然大物，在日本神话中是大自然守护神，因人类频繁核试验破坏生态而报复人类。
+- 美国版剧情线包括2014年《哥斯拉》、2019年《哥斯拉2：怪兽之王》和2021年《哥斯拉大战金刚》，基多拉作为外星反派，其残骸被人类改造成机械基多拉，最终由金刚与哥斯拉联手击败；日本版包括2004年《哥斯拉：最后的战斗》（章子怡参演）和2016年《新哥斯拉》，后者以无人机投放炸弹耗尽能量并以冷冻剂封印收尾。
+## 核废水危害与切尔诺贝利事件对比
+- 讨论指出日本排放核废水可能导致生物变异和健康问题（如白血病），并对比切尔诺贝利核事故：该地区生物畸形、反应堆被水泥封存、方圆百里成为无人区，发言人认为日本在核废水处理上不如切尔诺贝利负责；发言人2补充其在日本留学期间购买中国进口的鱼，因日本国产食品价格昂贵。</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>5319/1287</t>
+        <v>24.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5319/800</t>
         </is>
       </c>
     </row>
@@ -12972,21 +12744,21 @@
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议为一场围绕18岁以前特别深刻的印象和记忆展开的自由分享会，由发言人1发起并主持，参与者包括发言人1至发言人6。核心探讨问题为18岁前是否有逃课、去网吧打游戏、追星、参加音乐会或乐队等经历，并延伸至小说漫画阅读、电脑游戏与单机游戏、第一人称射击与僵尸题材游戏、游戏与影视改编先后、塔防游戏与使命召唤等话题。发言人1回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐。发言人2称18岁前没逃过课，上大学后逃过一次；发言人3认为逃课是正常现象；发言人4称上大学就不算。
+本次会议围绕18岁以前的深刻印象和记忆展开分享，成员包括发言人1、发言人2、发言人3、发言人4、发言人5、发言人6等。核心探讨问题涵盖逃课经历、网吧游戏（穿越火线、CS online、魔兽等）、追星、乐队、漫画小说（郭敬明、柯南、老夫子等）等内容。初中时期每周一下午四点放学后，大家常聚集于游戏厅、网吧，流行穿越火线、反恐精英online、使命召唤、战地、魔兽等游戏；高中因高考压力不敢逃课，转向追星和乐队活动，偏好朋克金属风格。会议深入讨论了穿越火线、求生之路、生化危机、使命召唤等游戏，涉及游戏内容、暴力程度、年龄限制、游戏与电影的关系等话题。
 # 发言要点
-发言人1作为主要发起者，回忆初中走读时每周一下午4点放学后聚集游戏厅、网吧，流行穿越火线CF、反恐精英online、使命召唤、战地、魔兽等，高中因高考压力不敢逃课，主要追星并搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属音乐；其称穿越火线抄袭，自己曾在贴吧和QQ空间写文章骂穿越火线被封禁，后成为CS铁杆粉，喜欢僵尸模式，并介绍求生之路第二部有东洋刀、电锯、砍刀砍丧尸，很暴力，后来有年龄限制，未成年人不能注册Steam账号，需18岁以上，还称求生之路精准预测美国政府在灾难中的表现，2020年新冠疫情后游戏重新火起来。发言人2称18岁前没逃过课，上大学后逃过一次；称看郭敬明小说挺难受、挺扭曲，并提到《梦里花落知多少》，还提到《意林》《读者》《故事会》并称意林讲得特别好；提到穿越火线、地下城与勇士、魔兽争霸，称欧美玩家爱玩打僵尸游戏，称植物大战僵尸有特别变态的版本，后期满屏子弹，电脑都卡，称使命召唤这游戏太男性了。发言人3认为逃课是正常现象，称小时候经常玩塔防游戏，现在还在玩植物大战僵尸和Kindle rush。发言人4称上大学就不算逃课，称班里特别流行看柯南，提到摩尔庄园、赛尔号，提到仙剑三最火且有电视剧。发言人5提到特别喜欢郭敬明的小说，提到当时还有一些杂志，提到萌化三国，提到仙剑四、仙辕剑、古剑四，质疑当时游戏没有年龄限制、内容暴力，小孩能否玩。发言人6提到生活杂志、柯南、老夫子、仙剑、Steam图标、僵尸题材，称艺术源于生活。观点交锋点包括：逃课是否正常及上大学后是否算逃课；郭敬明小说是否令人难受扭曲；穿越火线是否抄袭及游戏暴力与年龄限制；求生之路与生化危机、惊变48小时的影视游戏先后关系；变形金刚先有玩具还是电影；英雄联盟与DOTA的鄙视链及王者荣耀处于鄙视链最低端。
+发言人1分享了初中走读时每周一下午四点放学后聚集游戏厅、网吧的经历，流行穿越火线、CS online、使命召唤、战地、魔兽等游戏；高中因高考压力不敢逃课，转向追星和乐队活动，偏好朋克金属风格。发言人2表示18岁前未逃过课，大学才逃过一次，并提到喜欢看漫画，玩过魔兽争霸、穿越火线、地下城与勇士等游戏。发言人3认为逃课是正常现象。发言人4提到初中流行摩尔庄园、赛尔号，高中玩过仙剑三，并指出仙剑三最火且有电视剧。发言人5表示特别喜欢郭敬明的小说，玩过仙剑四，并提到游戏年龄限制问题。发言人6提到喜欢僵尸类游戏，并提及最后生还者。观点交锋点包括：关于仙剑系列哪部最经典，发言人4认为仙剑三最火，发言人5提到仙剑一和仙剑四拍了电视剧；关于游戏鄙视链，发言人5提出英雄联盟、DOTA、王者荣耀之间存在鄙视链，发言人2认为王者荣耀处于最底端；关于穿越火线，发言人1认为其抄袭CS，并因在贴吧和QQ空间写文章骂穿越火线而被平台封禁，成为CS铁杆粉丝。
 # 共识形成
-小组未形成正式决议或统一意见，讨论以自由分享与回忆为主。形成的共同认知包括：**逃课在初中高中阶段被视为正常现象，但上大学后逃课一般不算**；**郭敬明小说、柯南、老夫子、意林读者故事会等是当时流行的阅读内容**；**穿越火线、CS、求生之路、仙剑、魔兽、摩尔庄园、赛尔号、植物大战僵尸等是当时流行的游戏**；**求生之路第二部因暴力内容后来设有年龄限制，未成年人不能注册Steam账号，需18岁以上**；**生化危机先有游戏后有电影，求生之路是在惊变48小时、生化危机基础上先有电影后有游戏**；**变形金刚先有玩具，后有MV和电影**；**英雄联盟与DOTA存在鄙视链，王者荣耀处于鄙视链最低端**。
+小组最终达成以下统一意见：**求生之路第二部因血腥暴力被设定年龄限制，未成年人需18岁以上注册Steam账号才能游玩**；**生化危机先有游戏后有电影，求生之路则基于惊变48小时和生化危机等电影改编**；**变形金刚先有玩具，后有MV和电影**。此外，大家一致认为游戏中的恐惧源于火力不足，并认可求生之路制作团队精准预测了美国政府在新冠疫情中的表现。
 # 未决事项与分工
-需进一步探讨的问题包括：发言人5质疑当时游戏没有年龄限制、内容暴力，小孩能否玩，该问题未形成结论；发言人2问游戏和电影谁先有，讨论中仅就生化危机、求生之路、变形金刚等具体作品给出先后关系，未形成一般性结论；发言人1称求生之路精准预测美国政府在灾难中的表现，该观点未获其他成员明确回应。后续任务分工未在原文中明确。</t>
+未提及需进一步探讨的问题及后续任务分工。</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>6453/1554</t>
+        <v>20.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6453/928</t>
         </is>
       </c>
     </row>
@@ -13261,21 +13033,21 @@
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论为闲聊式交流，开场由发言人1提议大家讨论待会儿说啥，并确定继续聊《红楼梦》及相关古典小说话题，随后依次展开红楼官场暗线与四大家族、红楼细节与版本差异、金瓶梅与水浒传关系及人物、西游记佛教描写、三国孙权二宫之争等话题。参与讨论的成员包括发言人1、发言人2、发言人3、发言人4，围绕四大家族兴衰、人物结局版本差异、小说朝代背景及佛教描写等核心问题交换看法。讨论中未形成明确结论，多处内容为参与者凭印象回忆，部分细节表示记不清或未看过。会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。
+会议围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的情节、人物、版本差异及历史背景展开自由讨论，无明确结论。讨论涉及《红楼梦》中的官场暗线、四大家族（贾、史、王、薛）的兴衰及护官符诗句，提及吃螃蟹、冷香丸等细节，认为作者曹雪芹有大家族经历。讨论《金瓶梅》与《水浒传》的关系，西门庆的结局、武松报仇线、西门庆的官场发展，以及《金瓶梅》中佛教的黑暗面；还讨论了《西游记》中佛教的虚伪，如来佛祖收黄金、寺院住持贪袈裟等情节。讨论了几部小说的历史背景：《红楼梦》无明确朝代，且当时为禁书；《金瓶梅》和《水浒传》为北宋时期；提及三国二宫之争。
 # 发言要点
-发言人3提出红楼梦还有一条官场上的线，即朝堂政权变化，四大家族如王熙凤娘家在官场上的地位与其前期、后期地位及结局相关，其兄长先死也影响其结局，并表示对暗线很好奇；还提到四大家族整体在走下坡路，是王朝家族衰败，并介绍冷香丸配方需雨水、小雪及白牡丹、白荷花、白芙蓉、白梅花，以及120回版本中薛宝钗嫁贾宝玉后为无性婚姻、贾宝玉出家，另有版本称其怀有孩子。发言人4认为四大家族感觉没几个人，每家两家人多一点，薛宝钗家没什么靠山，并回忆小时候看红楼梦对吃螃蟹讲究印象深刻，还提到金瓶梅中潘金莲有心机、西门庆有十个老婆。发言人1补充四大家族形容诗句「丰年好大雪，珍珠如土金如铁」「白玉为堂金作马」「东海缺少白玉床，龙王来请金陵王」，并说明金瓶梅从武松杀武大郎之后写起，武松报仇时西门庆翻窗逃脱、武松后被发配，西门庆霸凌武大郎并攀附权贵，其结局在水浒中被砍头、在金瓶梅中纵欲过度而死，还提到西游记中如来佛祖收300两黄金。发言人2询问四大家族如何形容、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件，并提到孙权二宫之争中王夫人和孙鲁班有心机、反杀搅乱东吴政局。分歧点在于薛宝钗结局版本差异、西门庆结局版本差异及红楼梦是否有真实历史事件，各方均未达成一致。
+发言人3提出《红楼梦》存在官场暗线，四大家族兴衰与朝堂变化相关，如王熙凤地位与其兄长在官场地位相关，结局悲惨也因其兄长先死；并指出四大家族整体走下坡路。发言人4质疑四大家族感觉没几个人，每家就两家人多一点，薛宝钗家没什么靠山，发言人3回应薛宝钗家是做生意的，可能有钱。发言人1补充护官符诗句：贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁。发言人4提到小时候看《红楼梦》对吃螃蟹讲究印象深刻，发言人3提及冷香丸需雨水、小雪等节气之水及四季花蕊。关于薛宝钗结局，发言人3提到120回版本中她嫁给贾宝玉，但贾宝玉不久出家，有人说是无性婚姻，后来好像怀了孩子，但那是狗血版本，发言人1认为不至于那么狗血。关于《金瓶梅》，发言人1指出其与《水浒传》同线，武松报仇线中武松去找西门庆时，西门庆在楼上喝茶，仆人报信后翻窗逃走，水浒传中直接砍头，金瓶梅中翻窗后武松被发配，转而讲西门庆线；武松报仇总被打压，因官职、财富、权势不如西门庆。发言人3认为西门庆是无赖却能爬到高位，反映官场黑暗。发言人4提到西门庆摆宴吃东西写得好，发言人3提到西门庆有十个老婆，潘金莲属于有心机、较强势的。发言人3还提到西门庆一个老婆生病信和尚不去治病而死，佛教收灯油钱很黑。关于《西游记》，发言人1提到如来佛祖说帮国家后收300两黄金，发言人2提到狮驼岭和寺院住持贪唐僧袈裟引火自焚。关于历史背景，发言人3指出《红楼梦》无明确朝代，是写得很虚的故事，发言人4认为作者是那个时代的人，映射当时，有人说映射曹雪芹经历，发言人1提到《红楼梦》当时是禁书，不说朝代更禁。发言人2提到《水浒传》《金瓶梅》是北宋时期，与三国二宫之争类比，提到孙权二宫之争中王夫人和孙鲁班有心机，搅乱东吴政局。
 # 共识形成
-小组未形成统一意见或明确解决方案，讨论中确认的共识性内容为：**金瓶梅与水浒传为北宋时期平行故事线，红楼梦为单独故事线**；**红楼梦没有明确朝代，是写得很虚的故事，映射明末清初及曹雪芹经历**；**四大家族整体在走下坡路，是王朝家族衰败**。
+小组未达成明确统一意见，讨论以自由交流为主，无正式决策或创意产出。
 # 未决事项与分工
-需进一步探讨的问题包括：四大家族具体如何形容、薛宝钗结局版本差异、西门庆与宋江是否有交集、西门庆结局在不同版本中的差异、宰相/丞相最终结局、红楼梦是否有真实历史事件。后续任务分工未明确，会议临近结束时主持人提示时间差不多，暂停当前话题并转入下一个场景。</t>
+未决问题包括：红楼梦是否映射曹雪芹经历；金瓶梅中西门庆的结局是否因纵欲过度而死；金瓶梅中潘金莲是否最有心机。后续任务分工未提及。</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>5893/1087</t>
+        <v>29.6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5893/1163</t>
         </is>
       </c>
     </row>
@@ -13562,20 +13334,20 @@
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为轻松对话与录制调度，前半段围绕小说阅读、综艺剧集偏好、专业背景与洗发水等生活话题闲聊，后半段转入日本现代化转型主题并协调八爪鱼、金融、中央会等录制安排。发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。
-## 小说阅读与综艺剧集偏好
-- 发言人1提到自己看过很多遍《红楼梦》，高中时读不太懂，反复读后觉得有意思；发言人2表示不怎么看小说，更多刷短剧。发言人2看电视剧和综艺多一点，发言人4也看娱乐综艺，烧脑类看得少，提到旅游类、户外类、做饭类综艺；发言人1看过《种地吧》和英国综艺《克拉克森的农场》。
-- 关于《种地吧》，发言人1介绍十个男孩子走偶像路线但走小众路，大部分搞音乐，后来组成组合开演唱会；录制几乎一天24小时，一录录半年，素材特别多；成立农业公司创业，发展新型农业；种小月季和水培蔬菜，有鱼塘但未认真搞；项目有亏有盈，十人是实际股东每人掏钱，主要收益还是综艺。
-## 专业背景与生活话题
-- 发言人2是俄语专业但就业未往俄语方向，五六年没用会忘记；提到北方做贸易可能用得到，俄罗斯人生意内部消化多、往外营销少，相关科普来自康鹏。发言人1学数学后学统计，是理科生；发言人4是理科生，学软件工程，属工科；发言人1的姐姐是软件工程。发言人4换着用洗发水，家里有三种轮着用，之前一天就油后来好一些；发言人2询问是否有海飞丝，发言人4表示用的牌子不认识、叫不来，答应找订单告知。发言人6提出谈日本现代化转型，涉及明治维新与和平宪法；发言人5表示不懂；发言人6提到彪子在日本上学是主场，但彪子表示对日本不太懂。发言人5协调八爪鱼、金融、中央会等录制安排，提到小慧是八爪鱼同性别三到六、不录女生，三楼有空会议室，金融不着急可先走。</t>
+会议前半段为闲聊，参与者交流了个人阅读习惯、综艺喜好、专业背景及洗发水使用等生活话题。其中一人提到反复阅读《红楼梦》多次，另一人分享观看综艺《种地吧》及英国综艺《克拉克森的农场》的体会，并谈及该综艺参与者成立农业公司、尝试种植月季和水培蔬菜等创业项目，部分项目盈利、部分亏损。闲聊中还涉及各自专业背景，包括俄语、数学、统计、软件工程等，并提及洗发水换用对头发的影响。后半段转向讨论日本现代化转型主题，涉及明治维新与和平宪法，但参与者表示不熟悉该话题，讨论未深入。
+## 闲聊话题
+- 讨论个人阅读习惯，包括反复阅读《红楼梦》多次。
+- 交流综艺喜好，提及《种地吧》和《克拉克森的农场》，并讨论其参与者成立农业公司、种植月季和水培蔬菜等创业项目，部分盈利、部分亏损。
+## 日本现代化转型
+- 提出讨论日本现代化转型，涉及明治维新与和平宪法，但参与者表示不熟悉，讨论未深入。</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>5310/1279</t>
+        <v>14</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5310/393</t>
         </is>
       </c>
     </row>
@@ -13732,61 +13504,21 @@
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次研讨会由主讲人（发言人1）围绕朝鲜半岛从分裂到朝鲜战争爆发、停战及今日朝韩格局展开分享。主讲人梳理了1945年日本投降后美苏军队分别进入朝鲜南北、以北纬38度为基准形成三八线的由来，并指出1949年新中国宣布废除列强在华租界与特权、涉及苏联在东北的中长铁路及大连旅顺利益后，苏联鼓动朝鲜进攻韩国，希望以仁川或釜山类似城市替代旅顺大连地位并继续在亚洲发挥影响力。战争进程方面，1950年6月北朝鲜军队率先越过三八线南进，朝鲜人民军一度打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，麦克阿瑟任联合国军总司令，美军以联合国军身份参战，另有十六个国家共同出兵；美军越过三八线招致中国强烈不满，中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束，此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带并扩展至三七线，第五次战役为最后一次大规模战役，1953年7月27日双方正式达成停战协定，朝韩名义上停战，未实现真正和平。问答环节还涉及朝鲜战争的影响与评价、越南统一、朝韩旅游与朝鲜现状、朝鲜半岛文明与历史沿革、南北割裂的历史渊源、美国对朝鲜的态度、朝韩统一前景、中俄朝关系与图们江出海口、韩国军队在朝鲜战争中的作用，以及中国选择抗美援朝而非收复台湾的原因等议题，会议未形成决议。
+本次讲座由主讲人系统回顾朝鲜战争历史，涵盖朝鲜半岛从分裂到统一再到二战后再次分裂的历程，重点讲述1945年美苏以北纬38度划分三八线、1949年新中国废除列强特权引发苏联不满并鼓动朝鲜进攻韩国、1950年6月朝鲜战争爆发、各方称谓差异、朝鲜人民军一度打到洛东江、美军仁川登陆后反攻、中国以志愿军形式出兵、历经五次战役，最终于1953年7月27日签订停战协定，朝韩至今未实现真正和平。主讲人还指出朝鲜战争奠定了中国的强国地位，美国在越南战争中未敢越过北纬十七度线，并讨论了朝鲜旅游限制、社会封闭、脱北者现象、朝鲜半岛文明历史、朝韩分裂原因、美国对朝鲜态度、朝韩统一可能性、图们江出海口问题、韩军战斗力演变以及中国为何选择抗美援朝而非解放台湾等话题。
 # 核心观点与论证
-**论点一：三八线是美苏分区受降的产物，朝鲜半岛分裂源于冷战格局。** 论据：1945年二战结束、日本投降后，美苏军队分别进入朝鲜南北，以北纬38度为基准形成三八线；最初设想不同占领区受降后像奥地利那样普选建立统一民选政府，但美苏关系急转直下，扶植领导人各有心思，意识形态不同，最终建立两个国家。美国在三八线以南单独建立韩国以保护日本免遭苏联及共产主义势力影响，苏联在朝鲜北部建立卫星附属国。
-**论点二：朝鲜战争爆发与各方称谓不同。** 论据：1950年6月北朝鲜军队率先越过三八线向南进攻；朝鲜称祖国统一解放战争，中国称抗美援朝，韩国称625事件，美国及西方国家称朝鲜战争或韩战，台湾地区称韩战。
-**论点三：战争进程经历多次战役，最终在三八线附近形成今日边境。** 论据：朝鲜人民军从三八线打到洛东江环形防御圈（今大邱到釜山一带）；1950年9月15日美军仁川登陆成功，分割包围并逐次歼灭朝鲜人民军，收复三八线以南韩国领土；中国决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩国军队第一次交火，11月5日第一次战役结束；此后进行第二次战役（长津湖战役）、第三次战役越过三八线占领汉城（今首尔）、仁川、水源一带，扩展至三七线（北纬37度）；后期美军反攻，双方鏖战于三七线和三八线之间；第五次战役为最后一次大规模战役，结束后双方在三八线基础上互有攻防，形成今日朝韩边境。西部中朝方面向南占领开城、延安半岛和望京半岛一带；东部美军向北占领今韩国襄阳地区及金刚山地区。1953年7月27日双方正式达成停战协定，延续至今。
-**论点四：朝鲜战争对中国具有战略意义。** 论据：从中国角度奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期中国警告美国不得越过北纬17度线，美国未敢越过；美国称此战为被遗忘的战争，联合国军最后一任司令官马克克拉克承认是美国历史上第一次未取得胜利情况下签署停战协议的司令官；伤害最深的是朝鲜和韩国，一脉相承的血肉同胞分裂成两个国家。
-**论点五：中国选择抗美援朝而非收复台湾，因海军实力不足与战略主动考量。** 论据：台湾和大陆之间有一道约100公里海峡，中共刚建国没有相应海军实力；1950年朝鲜战争爆发，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾；美国后期越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，唇亡齿寒深入人心，解放军陆军很强，海上没办法战斗就只能在陆地上战斗；长津湖和上甘岭接连让美军惨败。
-**论点六：韩国军队在朝鲜战争中的作用与战斗力演变。** 论据：韩国军队一开始瞎指挥，差点被朝鲜团灭；6月25日朝鲜战争爆发，7月10日以后朝鲜南部地面战斗主要是美军和朝鲜人民军进行，韩军负责冲人头角色；1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力；此前韩军对美军类似猪队友，志愿军跟美军占不到便宜时都从韩国军队战线突击，美军每次兵败都是韩国军队战线崩溃引起；第五次战役中志愿军从朝鲜半岛东部形成反包围突击，打崩韩国军队前线，美国把韩国第三军团全部撤销；韩军以二战时期日本扶植的伪军和傀儡部队军官为骨干，士兵类似国民党抓壮丁强征农村青年；一直贯彻二战昭和日军武士道精神管理体制，老兵欺负新兵，军队霸凌事件蔓延至今。
-**论点七：朝韩统一前景与中俄朝关系。** 论据：若当时美国未下场救援韩国，今日朝鲜可能是苏联卫星国附属，用来牵制中国并威胁美国在亚洲尤其日本的不稳定定时炸弹；现在若朝韩统一，大概率是韩国兼并朝鲜，因经济影响和综合实力；北方有充足优质兵源及核武器和导弹等尖端武器，若统一对整个东北亚都是不稳定定时炸弹；越南统一时宣布继承法国在中南半岛所有地盘和疆域，统一第二年进攻柬埔寨和泰国，导致1979年中国出兵对越南自卫反击战。中俄朝各怀鬼胎；中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落；图们江是俄罗斯和朝鲜的界江，是日本海出海口，在中朝俄边境，国际水域航道可通行，但俄罗斯和朝鲜建了一座小桥，大船无法通过；俄罗斯和朝鲜都不希望中国过分强大，不想过多依附中国，把图们江出海口封死。
+主讲人首先阐述朝鲜半岛分裂的历史背景：1945年二战后美苏军队以北纬38度为基准划分三八线，1949年新中国宣布废除列强在华特权，包括苏联在东北的中长铁路及大连旅顺特区，苏联不甘心失去利益，鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺大连的地位。1950年6月北朝鲜军队率先越过三八线，朝鲜战争爆发，各方称谓不同：朝鲜称`祖国统一解放战争`，中国称`抗美援朝`，韩国称`625事件`，美国及西方国家称`朝鲜战争`或`韩战`。战争初期朝鲜人民军打到洛东江环形防御圈（今大邱至釜山一带），1950年9月15日美军仁川登陆成功，分割包围并歼灭朝鲜人民军，收复三八线以南领土。美军以联合国军身份参战，共十六国出兵，联合国军总司令麦克阿瑟想扩大战果吞并北朝鲜，中国因`唇亡齿寒`决定以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束，此后经历第二次战役（长津湖战役）、第三次战役（越过三八线占领汉城、仁川、水原，推进至三七线），后期美军反攻，双方在三七线与三八线之间鏖战，第五次战役后互有攻防，形成今日朝韩边境：西部中朝占领开城、延安半岛、望京半岛，东部美军占领襄阳、金刚山地区。1953年7月27日双方达成停战协定，朝韩名义上停战，未实现真正和平。主讲人强调朝鲜战争奠定了中国强国地位，美国在越南战争中未敢越过北纬十七度线，并称此战在美国被称为`被遗忘的战争`，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利的情况下签署停战协议。
 # 金句总结
-&gt; “朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的一个状态。”
-背景：主讲人在讲述美军越过三八线后中国决定出兵时提出，用以说明中国以志愿军形式出兵的战略考量。
-&gt; “美国再也不敢小瞧我们了。”
-背景：主讲人在回答朝鲜战争影响时提出，指出此战从中国角度奠定了强国地位，并提及1967年越南战争时期中国警告美国不得越过北纬17度线。
-&gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
-背景：主讲人引述联合国军最后一任司令官马克克拉克的承认，说明美国称此战为被遗忘的战争。
-&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。”
-背景：主讲人在评价朝鲜战争影响时提出，指出朝韩名义上停战，未实现真正和平。
-&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
-背景：主讲人在回答中国选择抗美援朝而非收复台湾的原因时提出，指出解放军陆军很强，台湾海峡约100公里且当时没有海军实力。
-&gt; “各怀鬼胎。”
-背景：主讲人在回答中俄朝关系时提出，指出中国和朝鲜、俄罗斯的问题主要是图们江出海口问题，至今拖着没有着落。
+主讲人指出：“朝鲜半岛对于中国的意义来说，就是一个唇亡齿寒的状态。”此句解释了1950年中国决定以志愿军形式出兵抗美援朝的根本原因，即朝鲜半岛安全直接关系中国东北边境稳定。另一金句为：“美国再也不敢小瞧我们了。”此句总结了朝鲜战争对中国国际地位的影响，并关联到1967年越南战争期间中国警告美国不得越过北纬十七度线，美国未敢越线。
 # Q&amp;A 环节
-问：战争开始和结束，韩国和朝鲜他们作战的势力有很大的差别吗？这个战争的改变大吗？
-→ 答：主要从中国的角度来说，奠定了我们一个强国的一个地位。美国再也不敢小瞧我们了，导致在一九六七年的越南战争时期，中国这边向美国发出的警告，绝对不允许越过北纬十七度线。那个时候就是南越和北越的一个边境线，如果说美国胆敢越过北纬十七度线的话，那中国必将出兵越南，导致美国在越战的时候未敢越过北纬十七度线，然后奠定了我们的一个地位。同时这场战役在美国被称为被遗忘的战争，因为联合国军，也就美军当时在朝鲜的最后一任司令官马克克拉克，他自己就说了一句他承认了，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官，然后伤害最深的其实还是朝鲜和韩国。
-问：现在越南还分南北吗？
-→ 答：没有。越南它还是统一的，因为美国最终还是放弃了南越，然后北越趁这个机会把南越给统一了。
-问：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
-→ 答：当然是韩国更好玩一点的。因为朝鲜他那边旅游就有点就是没有人身自由。当我们如果说是进入朝鲜的境内，第一件事就是什么呢？没有对搜手机检查，然后没有无线网，就没有网络。然后只有平壤，不就他们自己的网络运营商，而且就是类似于咱们国家八九十年代的那样的一个状态。然后他们的手机就是很落后、很慢，然后国际漫游和网络就非常的贵。然后那几天就是就是参观他们的，就是所谓的伟大的今日成员在的感召之下的各种主体思想和社会主义的辉煌建设成就。然后就类似于像以前我们的文革时期的那种，就是呃无产阶级，就是就是高于一切那样的一个思想，然后就活在一种就是异次元的世界当中。
-问：他们普通人可以上网吗？
-→ 答：不行啊，普通人不能上网。对，普通人是一般的。就是他那个，就局域网都已经很有限。然后普通人连电脑和就是咱们的，就是这些5G手机都用不起，他们怎么上网啊？因为主要是外部有韩国，然后光是韩国用韩剧作为意识形态的宣传武器，老百姓都会就是起来，要是知道真相之后也会颠覆他们的政权。否则的话，为什么那么多朝鲜就是老百姓，不管是吃不饱肚子，还是受意识形态的公式的关宣传之下，都往韩国跑？鲜有韩呃韩国人会去朝鲜的。对，脱北者。
-问：朝鲜那边有啥好玩的？
-→ 答：也就平壤那边看看志愿军的那些抗美援朝那些功绩，还有就是开城嘛，毕竟是朝鲜半岛三千年古都，然后就那边特产小人参。
-问：朝鲜是不是和什么我们北京或者是俄罗斯利亚有一个很大的一个广场，就是平壤的金日成广场？
-→ 答：以领导人来命名，就他们大将军、大元帅这样的啊。战争类的也可以用吧。
-问：它这个南北之间的割裂，是有什么历史渊源吗？为什么它会成为两个政权？
-→ 答：主要一开始的时候，美国和苏联都希望在朝鲜半岛建立一个缓冲区。然后美国主要是为了在建，在分出三八线以南的领土，单建单独建立一个韩国，是为了保护日本免遭苏联以及共产主义势力的一个影响，然后。在韩国形成一个缓冲区，而苏联也需要在亚洲建立一个卫星附属国，所以说就在朝鲜北部，在韩国独立的一个建国的一个基础之上，然后也宣布北朝鲜独。鼓励奉行的就是呃，对苏联马首是瞻的一个指示。所以说就是两边最开始的一个诉求，本来是一开始就是说，在就是不同的占领区受降，日本人的投降之后，像奥地利那样形成一个普选，然后建建立一个统一的民选政府。可谁都没想到，当时美国和苏联的关系恶化的非常快，急转直下的关系可以说是。然后，同时所扶植的领导人也各自有各自的心思。由于意识形态的不同，然后最终就是建立了不同的两个国家。所以说这也是朝鲜战争爆发的缘由。
-问：当时美国没有打败朝鲜嘛，然后你觉得现在美国对朝鲜的态度是怎样的？
-→ 答：因为就是什么呢？因为美国是因为惧怕朝鲜背后的中国和俄罗斯这么一个因素在里面。因为朝鲜战争爆发的时候，呃，当时朝鲜已经快被美国完全占领了，然后中国这边出动了志愿军部队，然后帮着朝鲜把美国打回去，而苏联当时也是提供了空军掩护和武器的一个后勤支持，所以说是中国和苏联联手，可以说是把美国给打回到三八线以南这么一个状态。所以说美国就比较忌惮这一块的因素，所以说就是没有，就是主动进攻朝鲜，也没有再次挑起这个朝鲜半岛的武装冲突，然后同时朝鲜当前的一个状态，金家也担心他们的那个江山，呃。在一旦贸然发动战争了之后，重新被颠覆了，所以说也不敢贸然发动战争，就这样的。
-问：现在的朝韩对立这个局面，可以认为是现在韩国还有还有还有西方国家在背后支撑嘛，可以认为它是一个微妙的平衡。如果不妨畅想一下，如果当时没有形成这种这个冷战布局，就是互相争夺这个半岛的控制权的话。这个大一统的朝鲜半岛会是一个什么形态？会是一个大号的朝鲜，还是一个平衡的韩朝？
-→ 答：如果当时朝鲜战争爆发的时候，美国没有下场去救援韩国，今日朝鲜可能会是呃一个就是苏联的卫星国附属之下的，然后当时用来牵制咱们国家的一颗钉子，也要也是威胁美国在亚洲，尤其是日本那一块的一个就是不稳定的定时炸弹，就这样的一个状态。但是现在如果说是。朝韩要是统一，大概率应该是韩国兼并朝鲜。毕竟经济影响和综合实力摆在这儿，然后北方，然后也有就是就是充足的优质兵源以及核武器和导弹这一块的一些尖端武器的话，今日朝韩如果统一的话，那对于整个东北亚地区来说，都是一颗不稳定的定时炸弹。毕竟当年越南当时统一的时候，他当时说要宣布继承法国在中南半岛的所有地盘和疆域。越南统一的第二年就去进攻柬埔寨和泰国，然后被咱们也被逼到79年出兵对越南发动自卫反击战。所以说越南尚且如此，朝鲜半岛统一之后局势更加不可控。
-问：你感觉现在中国俄罗斯和朝鲜之间关系其实怎么样？
-→ 答：各怀鬼胎。咱们和朝鲜的问题，还有俄罗斯的问题，主要就是图们江出海口的那个问题，到现在今天还拖着这个事没有着落。图们江就是俄罗斯和朝鲜就是那个，就是有一条有一条界江，但是那个地方是日本海的出海口，然后咱们在，就是在中朝俄边境那一块。就是图们江，就国际水域航道是可以通行，但是俄罗斯和朝鲜在那建了一座小桥。大船没法从那过去，所以说就俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了，然后都不想把那个出海口让给我们。
-问：你觉得就是朝鲜战争中那个朝鲜的军队，那韩国的军队有没有发挥什么作用？
-→ 答：好像在刚开始就差点让人发挥。一开始的时候，因为韩国的军队当时瞎指挥，就是什么呢？差点被朝鲜团灭，然后差不多在6月25号朝鲜战争爆发，可是从7月10号以后，朝鲜的南部的地面战斗主要是美军和朝鲜人民军进行战斗，然后韩军一开始就是负责一个冲人头的一个角色，就是，然后差不多是在1952年之后，美国把韩国重新整军训练备战之后，韩军才形成了一个基本的一个战斗力。在此之前，呃，韩国的军队对于美军来说一直有点类似于像猪队友的一个存在，就是接连被美国不被。中朝的军队给接连打败，然后美国每一次战役里边就是什么呢？志愿军跟美军占不到便宜的时候，都从韩国军队的那个战线那边进行突击，然后导致美军每一次的兵败都是韩国军队的战线崩溃所引起的。然后最后是呃，在第五次战役，也就是朝鲜战争最大的一次运动战的里面，呃，志愿军当时从韩国军队的就。朝鲜半岛的东部那一块就是形成一次反包围突击，然后把整个韩国军队前线都给打崩。然后美国当时把韩国第三军团全部给撤销，然后是美国人在韩国的领土上把韩国军队给撤销了。所以说关于韩国军队的战斗力，在一九五二年之前我不敢恭维，在一九五二年之后还是不可小视，毕竟韩军的主。要形成，他还是以军官的主体，是二战时期日本人扶植起来的伪军和傀儡部队的为骨干。然后士兵就是有点类似于像国民党时期抓壮丁的一个形式，强征来的一些就是呃农村青年这么一个形式。然后韩国的军队，他从朝鲜战争成军的时候一直到现在，他一直贯慢贯彻的。以前二战时期昭和日军的那套武士道精神的那种管理体制，就是就是关西兵，然后老兵欺负新兵，军队的霸凌事件一直蔓延到今天都屡见不鲜，所以说他就是一支充满着昭和军国主义时期那种思想余孽的，就是旧日军部队的一种延伸。
-问：就是他不是五零年五零年去援那个汉明嗯然后四九年国呃中国刚成立。然后他当时好像没找到选择，一个是受服台湾，一个是去抗美援朝。因为当时他自己的实力不是很强的，所以他选这个。他为什么选择了抗美援朝，而不是选择受服台湾？
-→ 答：首先，台湾和大陆之间有一道漫长的海峡，这个距离差不多得有个就是100公里左右。当时的中共刚刚建国，也没有相应的一个海军实力。然后50年的时候，朝鲜当时爆发了战争，在美国的参众两院普遍看来，这是共产主义世界对自由世界的一次全面进攻，然后连带着就是把台湾和韩国共同纳入到了美国的亚太实力圈。保护圈里面然后。连带的影响的就是美军的陆军，就是出兵朝鲜半岛，海军第七舰队进驻台湾。一来防止就是就是解放军解放台湾，二来说是防止国民党反攻大陆。然后因为当时解放军当时建军的时候没有相应的海军实力，所以说没办法进行。解放台湾的战斗。但是由于美国后期又越过三八线，向朝鲜以及中朝边境进发，然后触动了咱们的一个敏感神经，唇亡齿寒这么一个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争，因为台湾那个事儿已经让咱们已经很被动了，朝鲜半岛这一场，既然。要就是争取战略。主动，那就索性就是解放军的陆军当时就很强，就是在陆地上进行战斗。既然海上没办法进行战斗，那就只能在陆地上进行战斗。所以说这也是后来咱们当时就是一种战斗意志的体现，就是在长津湖和上甘岭，就是接连让美军惨败，这两场战役也到今天也是美国人挥之不去的梦魇。</t>
+问：朝鲜战争开始和结束时，韩国和朝鲜的势力有很大差别吗？战争的改变大吗？答：从中国角度来说，奠定了我们强国地位，美国再也不敢小瞧我们，导致1967年越南战争时中国警告美国不得越过北纬十七度线，美国未敢越线。此战在美国被称为被遗忘的战争，最后一任司令官马克·克拉克承认是美国历史上第一次在未取得胜利的情况下签署停战协议，伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线悲剧延续至今。问：现在美国对朝鲜的态度是怎样的？答：美国惧怕朝鲜背后的中国和俄罗斯，朝鲜战争时中国出动志愿军，苏联提供空军掩护和武器后勤支持，联手把美国打回三八线以南，所以美国不敢主动进攻朝鲜，朝鲜金家也担心贸然发动战争会颠覆政权，因此双方维持现状。问：如果当时没有冷战布局，大一统的朝鲜半岛会是什么形态？答：如果美国没有下场救援韩国，今日朝鲜可能是苏联卫星国，牵制中国并威胁美国在亚洲尤其是日本的定时炸弹；若朝韩统一，大概率是韩国兼并朝鲜，因经济实力和综合国力占优，但北方有优质兵源及核武器导弹，统一后对东北亚是不稳定定时炸弹，类比越南统一后进攻柬埔寨泰国，被中国1979年自卫反击。问：中国、俄罗斯和朝鲜之间关系如何？答：各怀鬼胎，主要问题是图们江出海口，俄罗斯和朝鲜在界江建小桥，大船无法通过，都不希望中国过分强大，所以封死出海口。问：朝鲜战争中朝鲜军队和韩国军队有没有发挥作用？答：韩军一开始瞎指挥差点被朝鲜团灭，7月10日后南部地面战斗主要是美军和朝鲜人民军，韩军负责冲人头，1952年后美国整军训练才形成战斗力，此前对美军像猪队友，志愿军常从韩军战线突击导致美军兵败，第五次战役中志愿军从东部反包围打崩韩军前线，美国撤销韩国第三军团。韩军军官主体是二战时日本人扶植的伪军傀儡部队骨干，士兵类似抓壮丁，一直贯彻昭和日军武士道精神，霸凌事件至今屡见不鲜。问：中国为何选择抗美援朝而非解放台湾？答：台湾与大陆隔100公里海峡，中共刚建国没有海军实力，1950年朝鲜战争爆发后美国参众两院视为共产主义全面进攻，将台湾和韩国纳入亚太保护圈，美军陆军出兵朝鲜，海军第七舰队进驻台湾，既防解放军解放台湾也防国民党反攻大陆。美国越过三八线进犯中朝边境，触动唇亡齿寒神经，即便不愿与美国全面战争也不得不打，解放军陆军强，海上无法战斗就在陆地战斗，长津湖和上甘岭让美军惨败，成为美国人挥之不去的梦魇。</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>7464/6822</t>
+        <v>37.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7464/2157</t>
         </is>
       </c>
     </row>
@@ -13975,25 +13707,20 @@
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t># 对话概况
-本次对话为多人围绕出门与上班随身物品展开的闲聊，参与者包括发言人1、发言人2、发言人3、发言人4、发言人5。发言人2提出出门必带手机、充电宝、指甲刀，称指甲刀为多功能可磨手掌，并已用电子锁多年、以指甲刀平替钥匙；发言人3提出钥匙、纸巾、伞；发言人1强调必须带钥匙，自家为指纹锁、手机充电线够用；发言人4提到家钥匙及必带绑头发的皮圈；发言人5提出手机、耳机和工卡。上班随身物品方面，发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒。话题还延伸至长发打理与北京下雨，发言人3提到每年下雨园区门口都是水、李博之前开幕的地方被淹。会议未形成正式结论，发言人4在时间差不多时提议先停。
+本次会议为一场多人闲聊，围绕出门必带物品展开，场景为日常办公间隙的即兴讨论。发言人2提出必带手机、充电宝、指甲刀，并解释指甲刀用于磨手掌、戳钥匙等；发言人1强调必须带钥匙，但家中使用指纹锁，钥匙概念淡化；发言人4提到必带皮圈绑头发；发言人2补充上班必带刮胡刀，平均每三天带一次；发言人5提到手机、耳机和工卡；发言人3提到纸巾和伞。讨论延伸至头发打理与个人形象，发言人2认为披发显头小，发言人3建议弄公分；发言人2分享曾想留长发大胡子的梦想，但因打理困难放弃。随后讨论下雨季节与居住安全，发言人1认为北京下雨少且无季节性，发言人4认为夏天易下雨；发言人3提到园区门口积水及李博家被淹，发言人2建议住三楼以上。会议无明确结论或决策。
 # 交流内容
-出门必带物品话题：发言人2提出手机、充电宝、指甲刀，称指甲刀是多重指甲刀，可刮指甲、磨手掌；发言人3提出钥匙；发言人1强调必须带钥匙，并称自家门是指纹锁、手机充电线够用；发言人4提到家钥匙；发言人2称已用电子锁多年，用指甲刀平替钥匙；发言人4提到必带绑头发的皮圈；发言人3提到纸巾、伞。
-上班随身物品话题：发言人2称上班必带三件套为充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子长得快、一天长几毫米、不刮脖子下会痒；发言人5提出手机、耳机和工卡；发言人2称耳机和工卡放单位、刷脸进入；发言人1提到打卡用手机、领夜宵需工卡，出差肯定不带手机卡；发言人2认为充电宝既能充电也能防身，最好带一块砖重量。
-长发打理话题：发言人2好奇初中男生为何喜欢薅女生头发圈，称若自己是女生会披发显脑袋小；发言人1称绑的没有散头发好看；发言人4提到女生披肩发；发言人2称高中时想留长发留大胡子学民谣吉他，后因不好打理打消念头，曾留胡子被误认为新疆少数民族。
-北京下雨话题：发言人1称北京下雨很少、没季节性、秋天容易下雨；发言人2质疑往常是春天容易下雨；发言人4认为北京夏天容易下雨；发言人1称夏天容易暴雨；发言人3提到每年下雨园区门口都是水，李博之前开幕的地方被淹、去年也有；发言人2提出住三楼以上远离水淹；发言人3提到一个妹子没买大雨、一早送孩子。
+话题一：出门必带物品。发言人2提出出门必带手机、充电宝、指甲刀，并解释指甲刀为多重用途，可刮指甲、磨手掌等；发言人1强调必须带钥匙，但家中使用指纹锁，钥匙概念淡化；发言人4提到必带皮圈绑头发；发言人2补充上班必带刮胡刀，平均每三天带一次，因胡子长得快，一天能长几毫米；发言人5提到手机、耳机和工卡；发言人3提到纸巾和伞。话题二：头发打理与个人形象。发言人2认为披发显头小，若自己是女生肯定不绑头发；发言人3建议弄公分；发言人2分享曾想留长发大胡子的梦想，但因打理困难放弃，尝试留胡子时被误认为新疆少数民族。话题三：下雨季节与居住安全。发言人1认为北京下雨少且无季节性，发言人4认为夏天易下雨；发言人3提到园区门口积水及李博家被淹，发言人2建议住三楼以上。
 # 共识与分歧
-共识：**出门与上班随身物品因人而异，未形成统一清单**；**发言人2以指甲刀平替钥匙、上班必带充电宝、手机、刮胡刀**；**发言人1打卡用手机、领夜宵需工卡**。
-分歧：出门必带的三样东西到底是什么，未达成一致；为什么初中很多男生喜欢薅女生后边的头发圈，未解决；为什么秋天容易下雨而不是春天容易下雨，未解决；字节员工不录工卡会有什么样的惩罚，未解决。
-# 后续规划
-未提及</t>
+共识：多人认同出门必带物品因人而异，且电子锁普及后钥匙概念淡化；发言人2与发言人1均认为披发比绑发好看；发言人2与发言人3均认为长发、胡子不好打理。分歧：关于北京下雨季节，发言人1认为无季节性，发言人4认为夏天易下雨；关于是否带工卡，发言人1认为领夜宵需带工卡，发言人2表示领完即放回工位。未解决分歧：初中男生喜欢薅女生头发圈的原因；为什么秋天容易下雨。
+# 后续规划</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>3851/1105</t>
+        <v>23.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3851/852</t>
         </is>
       </c>
     </row>
@@ -14190,21 +13917,21 @@
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人1至发言人5共同参与，围绕各自手机中最常用的APP及使用习惯展开交流，核心探讨问题包括常用APP类别、AI助手与浏览器的取舍、视频平台付费方式、音乐APP选择与听歌场景，以及歌手与乐队偏好。讨论中涉及的具体APP包括知乎、小红书、谷歌、微信、抖音、淘宝、京东、B站、YouTube、豆包、百度、千问、吉米、重庆元宝、腾讯视频、爱奇艺、优酷、芒果TV、网易云、酷狗、酷我、虾扎、苹果music等。微信是否算最常用APP、大家为什么不喜欢用浏览器、Taylor Swift为什么重新火起来成为讨论中的开放问题。
+本次会议围绕手机常用APP及使用习惯展开闲聊，成员包括发言人1至发言人5。核心探讨问题包括社交、短视频、购物、AI助手、视频、音乐等APP的使用偏好，以及歌手与乐队偏好。发言人2常用知乎、小红书、谷歌；发言人3常用微信、抖音、淘宝、京东；发言人4常用微信、小红书；发言人5常用B站、YouTube，大家普遍使用微信。在AI助手方面，发言人4使用小布小布，发言人3下载了豆包，发言人1有百度千问等；发言人3认为AI助手更全面、回答更精准、总结性强，而发言人2表示不信任AI，仍使用浏览器、纸质地图、尺子铅笔标注。视频播放方面，发言人3常用腾讯视频、爱奇艺、优酷、芒果TV，发言人2因广告太长用B站，发言人5因APP太多不知开哪个VIP，发言人3提到看广告换VIP时长。音乐方面，发言人5用网易云但单框架手机不适配，用卓翼通；发言人2以前用酷狗酷我，提到欧美音乐平台虾扎；发言人1用苹果音乐，听歌时间集中在上班、通勤、地铁。歌手偏好方面，发言人3喜欢谢霆锋，提到Taylor Swift；发言人1认为五月天以前好但新发唱不上去；发言人2疑惑Taylor Swift为何重新火起来，提到绯闻和影响力。
 # 发言要点
-发言人2提到常用知乎、小红书、谷歌，并表示仍停留在浏览器加地图测绘用尺子标注的年代，不太喜欢用AI软件，不确定其是否正确，还提到欧美音乐平台虾扎、欧美演唱会版本更多、小众翻唱多、大版权有纠纷播不出来，并疑惑Taylor Swift为何重新火起来，提到她中学时火、后因绯闻消沉、对九零后和零零后影响深，以及Love Story、猫头鹰之城、亚当杨、绯闻、表白。发言人3提到微信、抖音、淘宝、京东，表示已下载豆包，提到重庆元宝，认为AI小助手更全面、回答更精准、总结性更强，还提到腾讯视频、爱奇艺、优酷、芒果TV等播放器APP，开VIP、看广告获得VIP时长，以及谢霆锋、Taylor Swift、玉蝴蝶。发言人4提到微信、小红书，提到用小布小布代替浏览器，提到通勤路上听歌、要降噪耳机，提到歌名有英文、Taylor Swift的全球影响力。发言人5提到B站、YouTube，指出小布小布是豆包，常用网易云，提到单框架手机网易云不适配、用卓翼通，提到APP太多不知道开哪个。发言人1提到百度、千问、吉米等，提到苹果music，发现国内付费电视剧在YouTube上不要钱，提到五月天、周杰伦。观点交锋点包括微信是否算常用APP、AI助手能否判断对错、视频平台广告与付费方式、音乐APP选择与适配问题。
+发言人2常用知乎、小红书、谷歌，表示不信任AI，仍使用浏览器、纸质地图、尺子铅笔标注，并提到欧美音乐平台虾扎，疑惑Taylor Swift为何重新火起来。发言人3常用微信、抖音、淘宝、京东，下载了豆包，认为AI助手更全面、回答更精准、总结性强，常用腾讯视频、爱奇艺、优酷、芒果TV，提到看广告换VIP时长，喜欢谢霆锋。发言人4常用微信、小红书，使用小布小布，认为不用浏览器直接搜小布小布。发言人5常用B站、YouTube，用网易云但单框架手机不适配，用卓翼通，因APP太多不知开哪个VIP。发言人1有百度千问等，用苹果音乐，认为五月天以前好但新发唱不上去。观点交锋点：发言人2不信任AI，与发言人3认为AI助手更全面形成分歧；发言人2因广告太长用B站，与发言人3使用多个视频平台形成对比。
 # 共识形成
-小组未形成统一意见或解决方案，讨论中提出的主要观点包括：AI小助手更全面、回答更精准、总结性更强；视频平台广告时间长，可用B站直接看或开VIP、看广告获得VIP时长；小网站不用花钱，因平台大才有版权纠纷需付费；欧美音乐平台演唱会版本更多、小众翻唱多；听歌场景包括上班、通勤路上、地铁，降噪耳机可提升体验。
+小组未达成明确统一意见或解决方案，仅就手机常用APP及使用习惯进行了交流，无关键产出。
 # 未决事项与分工
-需进一步探讨的问题包括：微信是否算最常用APP、大家为什么不喜欢用浏览器了、Taylor Swift为什么重新火起来。后续任务分工未提及。</t>
+未提及需进一步探讨的问题及后续任务分工。</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>4259/1069</t>
+        <v>23.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4259/944</t>
         </is>
       </c>
     </row>
@@ -14381,21 +14108,21 @@
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论围绕2022年俄乌战争爆发后俄军战场表现是否为其真正应有状态展开，由发言人1主持并主讲，发言人2、发言人3、发言人4参与讨论。发言人1指出，战前外界普遍认为俄罗斯会一边倒取胜、基辅很快被占领、泽连斯基会流亡，但泽连斯基扛住进攻并把俄军从基辅打回白俄罗斯和乌克兰边境。与会者从腐败、基层官兵、游戏影视形象、直观战斗力、欧洲认知及俄罗斯旅行见闻等多个角度发表了看法。讨论认为俄军单兵素质很厉害但总体拉垮，主要问题在后勤和指挥上；欧洲人把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，乌克兰被称为欧洲之门。
+本次讨论围绕2022年俄乌战争以来俄军的战场表现展开，对比游戏与媒体中的俄军形象，分析其后勤指挥短板、乌克兰抵抗意志及欧洲地缘认知。发言人1指出俄军传统钢铁洪流印象与实际表现反差，基辅进攻失败，泽连斯基抵抗成功；并分析普京信息茧房、情报经费贪污、基层官兵误以为演习、民兵自发抵抗导致持久战。发言人3提及腐败，如国防部长贪污；发言人4认为俄军被动时战斗力强，主动进攻差。讨论延伸至游戏与媒体中的俄军形象，认为西方主导游戏抹黑苏联，如心灵控制器、暴力美学；发言人4认为游戏形象夸张。关于俄军战斗力，发言人1总结俄军单兵素质强但后勤指挥拉垮，比喻为矮脚巨人；发言人4认为俄乌战场与二战相比进步有限，仅多无人机，并讨论乌克兰用细线防无人机。发言人1分析乌克兰为欧洲之门，欧洲视俄罗斯为亚洲半兽人，因蒙古统治历史不被接纳，欧洲支援乌克兰以挡俄罗斯于亚洲之外。最后分享俄罗斯旅游经历，提及东宫博物馆藏品丰富，圣彼得堡夏天不错，并讨论俄罗斯历史与掠夺藏品，涉及欧洲、亚洲、中东等地。
 # 核心观点与论证
-核心论点一：俄军腐败问题突出。支撑论据为情报官员把用于策反乌克兰官员的经费全部贪污瓜分，导致乌克兰高官未收到策反经费；2014年俄罗斯占领克里米亚后乌克兰上下迸发民族仇恨，对政府无能与腐败不满。核心论点二：俄军基层官兵与战争初期情况。支撑论据为俄军基层官兵不知道2022年会进攻乌克兰，好多部队收到命令还以为是去演习，第一批部队进入乌克兰时遭遇民兵自发抵抗而非军队有组织进攻，闪电战变成持久战。核心论点三：游戏与影视中的俄军/苏联形象。支撑论据为从苏联时期开始俄军给人钢铁洪流印象，在各国游戏里苏联或俄罗斯常作为反派；红警等游戏被指为黑苏联，把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。核心论点四：对俄军的直观印象与战斗力评价。支撑论据为俄军单兵素质很厉害但总体拉垮，主要后勤和指挥上，像矮脚巨人、柯基腿短支撑不起庞大身子；俄乌战场打得跟二战没啥进步，多了点无人机，双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸，从钢铁洪流变成菜鸡互啄；俄罗斯无人机靠伊朗给，乌克兰由北约持续输血，类似越战形式；车臣、格鲁吉亚、瓦格纳、库尔德武装等地方武装战斗力挺强。核心论点五：欧洲对俄罗斯的认知与乌克兰的地缘意义。支撑论据为乌克兰在欧洲人认知里被称为欧洲之门，欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待；俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳；欧洲自发支援乌克兰，不让俄罗斯打赢，要把俄罗斯挡在亚洲之外；乌克兰死活不能向俄罗斯妥协。核心论点六：俄罗斯旅行与东宫藏品。支撑论据为出俄罗斯后签证上会写、办美签可能被拒；发言人1因去过好几次俄罗斯，在美国边境入口被拦下询问去俄罗斯干嘛，差点被怀疑是间谍；东宫是世界四大艺术博物馆之一，连续去了三次不同区域都没逛完，圣彼得堡夏天不错；东宫藏品来源包括列强殖民、探险队名义、俄国东扩、二战后从德国运回，以及王室联姻赠送品，涉及欧洲、中东、东亚、西夏王陵、敦煌、中亚、埃及、北非、奥斯曼帝国等地。核心论点七：俄罗斯地域与民族构成。支撑论据为讨论俄罗斯欧洲部分与亚洲部分差别是否很大，远东地区风格和欧洲那头；提到境内好多共和国，但总的来说以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。
+发言人1首先提出俄军传统钢铁洪流印象与2022年实际表现的反差：全世界预期战争天平向俄罗斯一边倒，基辅会很快被占领，泽连斯基会流亡，但泽连斯基扛住进攻并将俄军打回白俄罗斯与乌克兰边境。发言人3提及腐败，如国防部长贪污；发言人4认为俄军被动时战斗力强，主动进攻差。发言人1分析普京活在自己的信息茧房，情报官员贪污策反乌克兰官员的经费，基层官兵误以为演习而进入乌克兰，遭遇民兵自发抵抗，从闪电战变成持久战。发言人1总结俄军单兵素质强但后勤指挥拉垮，比喻为矮脚巨人；发言人4认为俄乌战场与二战相比进步有限，仅多无人机，并讨论乌克兰用细线防无人机。发言人1分析乌克兰为欧洲之门，欧洲视俄罗斯为亚洲半兽人，因蒙古统治历史不被接纳，欧洲支援乌克兰以挡俄罗斯于亚洲之外。最后分享俄罗斯旅游经历，提及东宫博物馆藏品丰富，圣彼得堡夏天不错，并讨论俄罗斯历史与掠夺藏品，涉及欧洲、亚洲、中东等地。
 # 金句总结
-发言人1："俄军他总的来说，给我看来，他就是单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，然后就是矮脚巨人的感觉是不是就有点像柯基的感觉，就是腿特别短，支撑不起他庞大的身子的那种感觉。"——背景为讨论俄军在乌克兰的表现时对俄军整体战斗力的评价。发言人1："从一种钢铁洪流变成了最后的菜鸡互啄。"——背景为描述双方把重装备耗光后隔着战壕互相扔手雷或用无人机互炸的战场状态。发言人1："乌克兰在欧洲人的认知里面是被称为欧洲之门。"——背景为阐述欧洲对俄罗斯的认知与乌克兰的地缘意义。发言人1："欧洲的边界是在乌克兰，所以说一定要守，要武装并守好乌克兰，要把俄罗斯给挡在亚洲之外。"——背景为解释欧洲自发支援乌克兰、不让俄罗斯打赢的原因。
+发言人1："俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，就是矮脚巨人的感觉。"（背景：对比俄军传统钢铁洪流印象与实际战场表现，指出其后勤指挥短板。）发言人1："从一种钢铁洪流变成了最后的菜鸡互啄。"（背景：双方重装备耗光，只能隔着战壕扔手雷或无人机互炸。）发言人1："没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家。"（背景：分析乌克兰对俄罗斯的地缘战略意义，欧洲视乌克兰为欧洲之门。）
 # Q&amp;A 环节
-问：俄罗斯在俄乌战争的表现是否是俄军真正应有的一种状态？→ 答：发言人1提出该问题供讨论，与会者从腐败、基层官兵、游戏形象、直观战斗力、欧洲认知等角度发表看法，未形成明确结论。问：大家对于游戏里的俄军是一个什么样的印象？→ 答：发言人2、发言人4认为红警等游戏是西方主导为黑苏联而做，苏联形象多为反面、很猛很变态、研究非常邪乎的武器、大规模夸张；发言人1指出把共产主义解放世界思想抹黑成心灵控制器，把毛字形容成暴力美学形象代言。问：对于俄罗斯被西欧称半兽人这种印象，大家怎么看？→ 答：发言人1解释欧洲人认为欧亚分界线在乌克兰那边，把俄罗斯人当成亚洲人、亚洲野蛮人、半兽人看待，俄罗斯被蒙古人统治过二百年，不被欧洲人认可接纳。问：俄罗斯欧洲那边跟亚洲这边差别很大吗，远东地区的风格和欧洲那头？→ 答：发言人1表示总的来说还是以俄罗斯族为主，俄国东扩像美国西进一样源源不断淘金移民。</t>
+问：游戏里的俄军是什么印象？答：发言人4认为红警等游戏是西方为了抹黑苏联而制作，形象夸张，如心灵控制器、暴力美学；发言人1补充说西方把共产主义解放世界的思想抹黑成心灵控制器，把毛子形容成暴力美学形象代言。</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t>6103/1947</t>
+        <v>30.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6103/1162</t>
         </is>
       </c>
     </row>
@@ -14498,27 +14225,21 @@
       <c r="C48" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次讨论围绕电影《南京照相馆》展开，由发言人1介绍历史背景并辨析影片虚构与真实。发言人3在抖音看过切片、也去电影院看过，觉得挺好看；发言人4认为是灾难电影，印象最深的是几个人在地下室吃喝睡觉、最后老弱妇孺还活着；发言人2觉得深刻、好看；发言人5表示题材不太习惯、没看过。发言人1介绍：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据。发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
+会议围绕电影《南京照相馆》展开讨论，成员分享了观影印象：有人看过抖音切片，有人觉得深刻好看，有人因题材沉重未看，有人提到地下室场景。主持人介绍了1937年八一三淞沪抗战、日军进攻南京及南京大屠杀的历史背景，并说明日军军纪失控、松井石根被替换、朝香宫鸠彦发布不留俘虏命令等细节。主持人辨析了电影虚构与真实：主要人物虚构，但照片拍摄真实，实际由美国传教士拍摄，中国冲洗人员偷拷证据，战后递交国民政府军事法庭作为审判日本战犯的证据；电影中中华门战斗、挹江门惨案、战犯审判等为真实历史。成员还分享了参观伪满洲国博物馆、唐山大地震纪念馆、上海抗战纪念馆等经历，提到南京大屠杀纪念馆预约难。
 # 核心观点与论证
-发言人1首先介绍历史背景：1937年8月13日国民党军队与日本人在上海激战，因实力原因国军从上海撤退，日军从上海追击到南京；自1931年九一八事变到八一三淞沪抗战前，日本占领东北、华北未遭遇成规模抵抗，淞沪抗战是日本第一次遭受迎头痛击，战场惨烈、伤亡惨重，日军缺乏纪律和军纪约束，加上长达四个月作战已杀红眼，攻破南京城后导致南京大屠杀发生。
-在虚构与真实之辨上，发言人4问片中日本军官及主角与其建立友谊是否虚构，发言人1说明电影主要人物是虚构的，但照片拍摄是真实的，真实历史是两个美国传教士拍摄日军暴行，同时期一名负责为日本人冲洗照片的后期人员无意发现这些暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交给国民政府军事法庭作为审判日本战犯的证据，而非电影人物所拍摄留存。
-发言人1还指出影片中的真实细节包括开头中华门城墙的战斗、义江门撤退时宪兵没让撤出去、守义江门部队未收到撤退命令导致信息差造成惨案，以及电影尾声对打进南京部队（如谷寿夫、第六师团师团长及上新闻的基层日军军官）的审判和枪决；发言人5提到现在好多日本人还不承认这个事情。
-关于日军暴行成因与指挥更替，发言人1解释上海抗战介绍多是因为中日第一场大规模战斗在上海；日军到南京进行大屠杀，因其自九一八以来未遭大规模战争，认为遭受前所未有的侮辱及战场应激创伤，结合日本攻破敌方城镇以屠城狂欢麻痹的历史，以及自上而下高压武士道精神下的欺凌霸凌宣泄；原指挥官松井石根因生病被临时替换，他曾发布命令避免日军在上海至南京沿线烧杀抢掠，以免招致中国军民反感、增强抵抗意志；替换为裕仁亲王的叔叔朝香宫鸠彦亲王，其追随脱亚入欧思想，上任后第一道命令是不留俘虏、格杀无论，导致日军军纪失控，蔓延至对老百姓群体，最终导致南京大屠杀。
+主持人首先介绍历史背景：1937年8月13日八一三淞沪抗战，国军从上海撤退后日军追击至南京；自九一八事变以来日军未遭成规模抵抗，八一三淞沪抗战是首次迎头痛击，日军伤亡惨重、军纪失控，攻破南京后发生南京大屠杀。其次辨析电影虚构与真实：主要人物虚构，但照片拍摄真实，实际由两名美国传教士拍摄日军暴行，中国冲洗人员偷偷拷贝并藏起，战后递交国民政府军事法庭作为审判日本战犯的证据；电影中中华门城墙战斗、挹江门撤退惨案、战犯审判（谷寿夫等被枪决）均为真实历史。再次分析日军暴行原因：日军未遭像样抵抗、遭受前所未有的侮辱与应激创伤，结合日本屠城传统、高压武士道精神，以及松井石根因病被替换为朝香宫鸠彦亲王，后者发布不留俘虏命令，导致军纪失控。
 # 金句总结
-发言人1在介绍日军暴行成因时指出：“从他们的角度来说，就是我也去过什么日本当时的那些个博物馆……觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”其背景是解释日军攻破南京城后为何进行大屠杀。
-发言人1在说明指挥更替时指出：朝香宫鸠彦亲王“上任之后发布的第一道命令就是不留俘虏，格杀无论”，随后“蔓延到了对老百姓群体的一种发生，然后最终导致了南京大屠杀”。
-发言人1在辨析影片真实与虚构时指出：“电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。”
+主持人指出：“从他们当时那样的心态来说，觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”此句关联日军在南京暴行的心理动因。另一处：“攻破了敌方的城镇，都要以屠城来进行自己那种狂欢与麻痹。”此句解释日军屠城的历史传统。
 # Q&amp;A 环节
-问（发言人4）：电影里面虚构的，它里面有一个日本的军方关系叫什么？就是主角一度好像和他建立一次友谊吧？不知道这个是虚构的，就是有没有这个日本军官是是不是真实？
-→ 答（发言人1）：电影里的主要的人物是虚构，但是照片的拍摄是真实的，但不是以电影里所描述的一个方式进行的。真实的一个历史是，当时是两个美国的传教士，然后当时是拍摄的当时日军的这一块相关的一个暴行。然后同时期也有咱们国家当时就是负责给日本人冲洗照片的一个，就是那个我不能说是摄影师，他应该是后期，就类似于就照片冲洗这样一个状态吧。然后他无意间发现了这一些个，就是日本所拍摄这些暴行，在日本当时是属于禁文，他偷偷拷贝了下来，藏起来了之后，然后是于抗战之后把这个递交给当时国民政府的军事法庭，就是作为审判日本战犯的一个证据，而不是当时就是南京照相馆里面的那些电影人物所就是拍摄留存下来的这么个情况。</t>
+问：电影里主角与日本军官建立友谊，这是虚构还是真实？答：电影主要人物是虚构的，但照片拍摄是真实的，实际由两名美国传教士拍摄日军暴行，中国冲洗人员偷偷拷贝并藏起，战后递交国民政府军事法庭作为审判日本战犯的证据。</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t>4228/1960</t>
+        <v>23</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4228/863</t>
         </is>
       </c>
     </row>
@@ -14607,21 +14328,21 @@
       <c r="C49" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议围绕日本国家概况、对日本的印象与了解展开自由讨论，由发言人1主持并引导，发言人2参与发言。发言人1提出日本在国人印象中较为复杂：历史原因导致中日曾发生战争与悲剧，但今天日本在中国外部投资中占很大比重，中日也是主要贸易伙伴；上学、上班人群喜欢去日本旅游，日本服务业和购物体验在各国中首屈一指。发言人2提到读研时上过讲日本文化的课，读《四世同堂》后觉得民族仇恨还是应该有一点影响。讨论涉及日本文化的来源与历史分期、天皇制度与君主立宪、旅游购物与中古店、日本民族性格与岛国环境等话题。
+本次会议围绕日本国家概况及大家对日本的印象和了解展开讨论，成员包括发言人1和发言人2。核心探讨问题包括日本文化的历史阶段与转型、日本民族性格与天皇地位、日本旅游与购物等话题。发言人1指出日本文化缺乏原创，是外来接收的本土化改进，并列举了三次转型：大化改新、明治维新、和平宪法转型，分别对应向中国、欧美、美国学习。发言人2提到喜欢日本文化，包括传统文化如漆艺、茶艺，以及现代文化艺术。发言人1补充天皇在古代是吉祥物般的存在，二战后麦克阿瑟迫使天皇公开露面，打破神性认知，推动社会转型；现在天皇是象征性存在，无实权，类似英国和西班牙的君主立宪制。发言人1还分享日本旅游偏好，如爬富士山、逛古城和博物馆，喜欢镰仓气候；购物方面提到奢侈品、中古店（Vintage shop），并解释中古店源于广场协议后经济崩溃，上班族变卖奢侈品催生二手产业。
 # 发言要点
-发言人1主张日本文化没有原创，属外来接收后本土化改进，经历三次转折：古代大化改新（向中国、朝鲜半岛学习，形成和服、制茶、漆器等传统）、近代明治维新（对标清朝、向欧美列强学习，学英国和德国法度利器）、二战后和平宪法转型（美国制定和平宪法，社会结构大规模调整，向美国看齐）；并谈到古代日本君臣关系与中国差别大，天皇对各地封建君主而言更像吉祥物，被当神灵供奉以精神层面控制百姓，1945年二战结束后美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，推动社会转型；现今天皇如君主立宪制下英国、西班牙那样的象征性存在，不能参与政治和国家事务，政治由国会和内阁选出首相执政，美国把日本改造成英美海洋法系国家结构，天皇没有实权，靠政府养着，存在感不如英国国王。发言人1还谈到旅游购物：长崎、东京、大阪、秋叶原等城市，秋叶原可买数码宝贝、铁甲小宝等原装手办以及美妆、护肤品、玩具；日本奢侈品便宜，有Vintage中古店，广场协议后日本经济急剧恶化、泡沫经济崩溃，上班族失业后把原先买的高档大衣、西装、皮具、皮鞋等通过二手回收寄卖，催生中古二手店产业，上海也有很多这类店，能买到LV、Burberry、古奇等上个世纪知名大牌，男性款式相对少；其本人喜欢去日本爬山、爬富士山、看古城、逛博物馆，如镰仓、京都、名古屋，喜欢镰仓夏天舒服的气候。发言人2提到日本传统文化如漆艺、茶艺以及现代文化艺术，并提到听过一种评论：日本是岛国，气候非常不稳定，发展农业可能遇海啸导致收成没了，所以民族性格比较容易极端。双方分歧点在于：发言人1追问日本文化具体指哪一个历史阶段，发言人2未明确；发言人1认为日本民众现在对天皇没有崇拜，发言人2则追问是否还有崇拜，未达成一致。
+发言人2：表示之前喜欢日本，读研时上过讲日本文化的课，读过老舍的《四世同堂》，认为民族仇恨还是应该有一点影响；提到日本文化包括传统文化如漆艺、茶艺，以及现代文化艺术；提出日本民族性格极端可能源于岛国气候不稳定。发言人1：指出日本文化缺乏原创，是外来接收的本土化改进，列举三次转型（大化改新、明治维新、和平宪法转型）；补充天皇在古代是吉祥物般的存在，二战后麦克阿瑟迫使天皇公开露面，打破神性认知，现在天皇是象征性存在，无实权；分享日本旅游购物偏好，解释中古店源于广场协议后经济崩溃。观点交锋点：发言人2认为民族仇恨应有影响，发言人1认为没那么严重；发言人2提到日本文化影响，发言人1追问具体历史阶段。
 # 共识形成
-小组未形成明确统一意见或解决方案，讨论中形成的共同认识包括：日本在国人印象中较为复杂，中日既有历史战争与悲剧，也是主要贸易伙伴；日本文化属外来接收后本土化改进，经历大化改新、明治维新、二战后和平宪法转型三次转折；现今天皇为君主立宪制下的象征性存在，无实权；日本有Vintage中古店产业，上海也有这类店。
+小组最终达成统一意见：日本文化经历了三次转型，分别是大化改新、明治维新和战后和平宪法转型，形成了不同阶段的文化特征；天皇在二战后被改造为象征性存在，无实权，日本政治由国会和内阁主导。关键产出：**日本文化三次转型论**和**天皇象征性地位**。
 # 未决事项与分工
-需进一步探讨的问题：日本文化具体指哪一个历史阶段的日本文化，尚未明确；日本民众现在对天皇是否还有崇拜，未达成一致。后续任务分工未提及。</t>
+需进一步探讨的问题：日本民众现在对天皇是否还有崇拜？日本文化具体指哪一个历史阶段？后续任务分工未提及。</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>4892/1239</t>
+        <v>22.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4892/879</t>
         </is>
       </c>
     </row>
@@ -14834,21 +14555,21 @@
       <c r="C50" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次会议承接此前西游记的文学话题，延伸讨论大家对三国与红楼梦的印象与看法，参与者为发言人1至发言人5。三国部分围绕整体印象与阵营偏好、刘备与孙刘联盟、白衣渡江与吕蒙评价、东吴大都督与陆逊、蜀汉内斗与姜维魏延、三顾茅庐与隆中对展开；红楼梦部分围绕版本与作者、判词与人物结局、后四十回官方地位及曹雪芹小道等北京地点展开。核心探讨问题包括：对三国印象最深刻的章节与阵营偏好、正史中刘备与孙刘联盟的演变、白衣渡江的评价、东吴大都督的结局、蜀汉内斗与姜维魏延、三顾茅庐与隆中对战略，以及红楼梦前八十回与后四十回的作者差异、判词与人物结局、后四十回为何成为官方结尾。
+本次会议为文学讨论延伸，围绕《三国演义》与《红楼梦》两部经典展开。参会成员共五人（发言人1至发言人5），核心探讨问题包括三国正史与演义差异、东吴内斗、蜀汉北伐，以及红楼梦前八十回与后四十回作者差异、判词解读与人物命运。三国部分，发言人1补充了诸葛亮去世后的正史后续，并分析刘备称汉中王引发的连锁反应；红楼梦部分，发言人3指出前八十回为曹雪芹所写，后四十回为他人续写，发言人4探讨了判词与人物命运。会议以自由交流为主，未形成正式决策。
 # 发言要点
-发言人2表示三国没看完，看到诸葛亮去世就不想看了，认为后面没意思；印象最深刻的是赤壁，认为前面比后面有意思；受三国演义影响一般偏向蜀汉刘备阵营；认为白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好；对陆逊印象是火烧连营，认为东吴后期政治斗争严重、内斗狠；提到蜀汉也内斗、魏延被砍；红楼梦方面提到四个丫鬟、袭人、晴雯，提到解读说林黛玉代表明、薛宝钗代表清，问为何最终选高鄂后四十回作为官方结尾，提到植物园有曹雪芹小道。发言人1补充正史后续姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴；认为刘备晚年若未称汉中王，孙权可能不会彻底决裂，称王引发吕蒙白衣渡江、刘备伐吴夷陵惨败等连锁反应；讲述刘备入川占成都后不还南郡、孙权派兵夺荆南三郡、曹操取汉中迫使刘备回师并签订湘水之盟，单刀赴会实为鲁肃与关羽各不带兵士在中立区谈判被罗贯中美化；认同白衣渡江开坏头，称吕蒙被后世与小偷鼠辈等价；称正史上周瑜被曹人射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；称刘禅自知能力不行完全放权诸葛亮，诸葛亮去世后姜维难力挽狂澜，刘禅轻信黄浩谗言，姜维是魏国降将靠诸葛亮提拔才有说服力；称正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，若非姜维断后挡住司马懿军队后果不敢想象，其行为与谋反无实质区别，实为与杨仪个人矛盾；补充隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾，诸葛亮北伐目标在关中平原和陇西，第一次北伐赢面大但因马谡兵败街亭而破产。发言人3称红楼梦只写了前八十回，后面是别人写的；称第五回贾宝玉梦游太虚幻境已把结局交代，以判词形式；称北苑所旁边村子有曹雪芹小道，爬山时看到过。发言人4称红楼梦有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；称第一遍读高鄂续版本时觉得合理，后来知道后四十回不是同一作者，反复读前八十回后再接触后四十回，发现林黛玉性格变了很多；称判词没点那么明确，探春、史湘云结局都是猜的，最后谁和贾宝玉在一起也是猜的；称林黛玉死不是原作写的，但原作意图肯定是悲剧；称晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；称第五回贾宝玉在秦可卿床上做梦到太虚幻境，看到判词，十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；称最终选高鄂后四十回因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及；称北京植物园底下有他的工具。发言人5讲述三顾茅庐：刘备中原屡战屡败，深感缺乏谋士，经人推荐得知隆中诸葛亮有卧龙之才，携关羽、张飞三次前往拜访，前两次未见到，第三次见到诸葛亮，诸葛亮被打动提出隆中对战略，联合孙权，最终同意辅佐刘备；问悲剧原因，如贾宝玉与林黛玉真心相爱却被迫娶薛宝钗。
+三国部分：发言人2表示三国未看完，诸葛亮去世后便不再看，认为赤壁是印象最深刻的章节，阵营偏好受演义影响倾向蜀汉；发言人1补充正史后续（姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴），分析刘备称汉中王引发吕蒙白衣渡江、夷陵惨败的连锁反应，并指出借荆州、湘水划界、单刀赴会等史实与演义差异；发言人2认为白衣渡江突破底线，吕蒙口碑差；发言人1指出东吴大都督周瑜中箭、鲁肃瘟疫、吕蒙病故、陆逊被逼死，并分析蜀汉内斗，刘禅放权诸葛亮，姜维因降将身份缺乏说服力，魏延烧栈道行为等同谋反；发言人5讲述三顾茅庐与隆中对，发言人1分析隆中对在白衣渡江后失效，诸葛亮北伐目标关中陇西，因马谡失街亭失败，后期北伐为绝望抗争。红楼梦部分：发言人4提出红楼梦有多种解读角度，可当爱情小说看，巧在未解之谜；发言人3指出前八十回为曹雪芹所写，后四十回为他人续写；发言人4表示初读高鹗续本觉得合理，反复读前八十回后发现林黛玉性格变化；发言人3提到第五回贾宝玉梦游太虚幻境以判词交代结局，探春、史湘云结局靠猜；发言人5询问悲剧原因，发言人4指出黛玉之死为后四十回内容，但原作意图是悲剧；讨论晴雯为黛玉替身，袭人性格似宝钗，晴雯之死为曹雪芹原作；发言人2提及林黛玉代表明朝、薛宝钗代表清朝的解读，发言人4补充秦可卿为前朝公主的解读；讨论金陵十二钗判词，正钗对应小姐、副钗对应丫鬟；发言人2质疑为何选高鹗后四十回为官方结尾，发言人4解释官方说法为在残稿上梳理完善，未违背作者原意。
 # 共识形成
-小组未形成正式决议，讨论中形成的共同认识包括：三国方面，大家印象最深刻的是赤壁，受三国演义影响一般偏向蜀汉刘备阵营；白衣渡江伪装成商人开了一个坏头、突破底线、口碑不好，吕蒙被后世与小偷鼠辈等价；东吴后期政治斗争严重，周瑜正史中被射毒箭阵亡、鲁肃得瘟疫病故、吕蒙病故、陆逊在二宫之争中被孙权活活逼死；正史上魏延没有谋反，只是不甘心大军撤退、烧毁悬崖边栈道，其行为与谋反无实质区别，实为与杨仪个人矛盾；隆中对为横跨荆益、外结好孙权、西和诸戎、趁魏国有变北伐，但白衣渡江后蜀汉失去荆州全境，横跨荆益不成立，外结好孙权与夺回荆州相矛盾；诸葛亮第一次北伐赢面大但因马谡兵败街亭而破产，此后只能拖延魏国灭蜀。红楼梦方面，大家认为其有很多解读角度，常被当爱情小说看，讲贾宝玉、薛宝钗、林黛玉的爱情故事，巧在没有解开的谜底；只写了前八十回，后面是别人写的；第五回贾宝玉梦游太虚幻境已以判词形式交代结局，但判词没点那么明确；晴雯是林黛玉替身、性格像林黛玉，袭人性格像薛宝钗，晴雯的死是曹雪芹写的、映照后面；十二金钗分正钗（小姐）和副钗（丫鬟），判词对应每人命运；最终选高鄂后四十回作为官方结尾，因其总体比较合理，官方解释是在残稿上梳理完善、没有违背作者原意，但写作细节和诗词能力不及。
+小组未形成统一意见或解决方案，讨论以观点交流为主。三国部分，成员对白衣渡江突破底线、吕蒙口碑差、东吴大都督结局、蜀汉内斗等史实解读基本一致；红楼梦部分，成员对前八十回为曹雪芹所写、后四十回为他人续写、判词交代结局等观点达成共识。关键产出为**对三国正史与演义差异的系统梳理**及**对红楼梦版本与判词解读的深入探讨**。
 # 未决事项与分工
-未决事项包括：红楼梦后四十回到底是谁写的、什么版本，真正意义是否与当时朝代社会有关；探春、史湘云的结局以及最后谁和贾宝玉在一起，都是猜的，没有明确答案；为什么最终选高鄂的后四十回作为官方结尾。后续任务分工未提及。</t>
+未决事项：红楼梦后四十回作者身份及高鹗续本是否违背作者原意尚未定论；探春、史湘云等人物结局仅靠判词猜测，无明确答案；林黛玉代表明朝、薛宝钗代表清朝及秦可卿为前朝公主等解读仅为猜测，未获证实。后续任务分工：未提及。</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>6453/2163</t>
+        <v>34.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6453/1149</t>
         </is>
       </c>
     </row>
@@ -14965,21 +14686,21 @@
       <c r="C51" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论由发言人1主导串场，发言人2、发言人3参与，从兵法和战法角度延伸三国故事线，核心探讨赤壁之战的影响、合肥之战与孙权北伐、白衣渡江与火烧连营、陆逊与孙家关系、北伐方向与孙权早期败仗、蜀汉曹魏印象与武将战力、魏延守街亭假设等议题。讨论认为赤壁之战不是曹军实力不行，而是骑兵没法打水战；合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下。
+本次会议围绕三国战役的兵法与战法展开讨论，成员包括发言人1、发言人2和发言人3。核心探讨问题包括赤壁之战的影响、合肥之战中孙权军事能力的评价、火烧连营的经过与陆逊的战术，以及关羽、张飞、黄忠、五子良将等武将的战斗力。发言人1详细分析了赤壁之战中曹军因缺乏水军而败于东吴水军，以及东吴陆战能力弱导致合肥之战失利；发言人2补充了对孙权军事能力的看法；发言人3提出孙权早期也曾被其他将领击败，并参与武将能力讨论。会议还延伸至北伐路线、街亭守将等话题。
 # 发言要点
-发言人1主张：曹操军队以虎豹骑为主擅长陆战，刚收服荆州无像样水军，江东以水军为主，曹军无法打水战而败；后期东吴北伐如合肥之战，吴军擅长划船、摇橹、打水战、游泳，上岸后无法与曹军对抗，双方僵持。合肥像钉子钉在东吴北伐路线上，从建业过长江到江北、经小河到巢湖上岸，打下合肥才能靠近淮河继续北伐；公元215年合肥之战，曹军主力在汉中，合肥只有张辽、李典、乐进三将且矛盾重，张辽率800死士骑马冲锋大败吴军，孙权差点被张辽抓住，张辽问俘虏骑马好、箭准、上长下短、小胡子的人是谁，得知是孙权后后悔没抓住。刘备体恤下属让士兵在密林扎营抵御酷暑，陆逊抓住秋季干燥、树叶飘落时机在秋老虎时期一口气放火，连营七百里的营地被烧，刘备只身逃回白帝城。陆逊是江东四杰，孙策孙坚是外来户，孙策被称为小霸王，过于冒失后被刺杀，曹操说生子当如孙仲谋，孙权开疆拓土能力不行但能守住家业。对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家；刘备汉中之战打得好，夷陵之战被仇恨冲昏头脑冒进，汉中之战有法正和黄权辅佐，靠地势地利耗出汉中；关羽水淹七军、斩颜良诛文丑，阵中斩将历史第一人；黄忠阵斩夏侯渊；张飞长坂坡、和马超大战五百回合；五子良将有曹仁、张辽、夏侯渊、张郃、徐晃、于禁，于禁被关羽生擒；曹操人多血厚能耗得起。如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，不会像马谡轻易丢掉街亭，第一次北伐可能成功，魏延想法大胆但不太符合蜀汉当时实际支撑，地盘太小。发言人2提出：小时候觉得生子当如孙仲谋，孙权厉害，长大感觉反转厉害；并问陆逊和孙家是否有仇。发言人3提出：除朱元璋从南往北打，其余都是来首都就不错，北伐南、南下容易；孙权在孙十万之前也打过一场坑仗，好几万人去打人家，被几千几百人追着打；关羽只知水淹七军，张飞只知长坂坡。分歧点在于孙权早期败仗的对手是谁，是刘表、刘琦还是曹仁时期，未确认。
+发言人1：主张赤壁之战曹军败于不擅水战，并非实力不济，因曹操军队以虎豹骑为主、擅长陆战，缺乏水军；东吴水军擅长水战但陆战能力弱，在合肥之战中失利。详细描述公元215年合肥之战，孙权率十万大军进攻合肥，张辽率八百死士大破吴军，孙权差点被俘，后人以“孙十万”调侃其军事能力。认为孙权一生未打下合肥，军事能力受质疑。还分析火烧连营中刘备因体恤士兵在密林扎营，被陆逊抓住秋季干燥时机火攻，连营七百里被烧，刘备逃回白帝城。评价关羽阵中斩将改变战局，张飞长坂坡、黄忠斩夏侯渊等，并推测诸葛亮第一次北伐若用魏延守街亭可能成功，但魏延想法不符合蜀汉实际支撑。发言人2：表示小时候认为孙权厉害，长大后看法反转，认为孙权军事能力不佳，不仅“孙十万”，后续合肥之战也兵败而归。发言人3：提出孙权在孙策刚死时曾与刘表（或他人）交战，几万人被几千人追着打，认为孙权打仗颓废；认为刘备汉中之战打得还行，但夷陵之战因仇恨冲昏头脑而冒进；对关羽战绩仅知水淹七军，认可关羽阵中斩将改变战局，但认为张飞无经典战役，仅知长坂坡。观点交锋：发言人1与发言人3就孙权早期败绩的具体对象（刘表、刘琦等）进行讨论，未能确认；发言人3质疑关羽个人战力与部队打仗的区别，发言人1强调阵中斩将直接改变战场局势。
 # 共识形成
-小组未形成正式决议，讨论中形成的统一意见包括：**赤壁之战不是曹军实力不行，而是骑兵没法打水战**；**张八百大破孙十万是长期划船游泳的人不擅长陆地冲锋，双方僵持**；**合肥像钉子钉在东吴北伐路线上，孙权一生朝打合肥努力但没打下**；**孙权开疆拓土能力不行但能守住家业**；**对蜀汉和曹魏印象更好，曹老板喜欢明着来，不像孙十万喜欢偷家**；**如果诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，第一次北伐可能成功，但魏延想法不太符合蜀汉当时实际支撑，地盘太小**。
+小组最终达成以下共识：**赤壁之战曹军败于不擅水战，并非实力不济**；**孙权一生未打下合肥，军事能力受质疑**；**火烧连营因刘备冒进和陆逊抓住时机导致**；**关羽阵中斩将改变战局，张飞长坂坡、黄忠斩夏侯渊等武将能力受认可**；**诸葛亮第一次北伐若用魏延守街亭可能成功，但魏延想法不符合蜀汉实际支撑**。
 # 未决事项与分工
-需进一步探讨的问题：孙权早期被几千几百人追着打的败仗对手是谁，是刘表、刘琦还是曹仁时期，未确认。后续任务分工未提及。</t>
+未提及需进一步探讨的问题及后续任务分工。</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>4899/1301</t>
+        <v>27.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4899/966</t>
         </is>
       </c>
     </row>
@@ -15042,41 +14763,29 @@
       <c r="C52" s="4" t="inlineStr">
         <is>
           <t># 讲座概况
-本次研讨会围绕1979至1989年苏联入侵阿富汗战争（苏阿战争）展开讲解并组织提问讨论。讲解指出阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带和兵家必争之地，国土纵深90%为高原山地，易守难攻，被称为帝国坟场，谁控制了阿富汗谁就控制住了亚洲的咽喉。讲解梳理了战前国情与苏联出兵过程：20世纪50年代阿富汗实行君主立宪制，同时与苏联和西方保持友好交往，精英与知识界奉行亲英与亲苏两头政策，文化上向英国靠拢、国家建设和工业向苏联看齐，基辛格评价阿明用苏联的火柴点美国的香烟。因阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入，1979年12月24日平安夜趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营，此举招致阿拉伯国家、中国、西方盟国不满。讨论环节分析了苏联出兵原因与阿富汗难打的原因：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克，加上阿富汗是特殊战略要地及苏联错判，导致大的战略性失误，同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。阿富汗90%为高原山地，是天然游击战地区，除喀布尔、坎大哈等主要城市外大部分乡村实行部落长老制、各自为政，政府无控制力；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助毒刺防空火箭筒等先进单兵武器，有效压制苏联雌鹿武装直升机，坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机，苏联基层官兵厌战、士气一落千丈，1989年从上到下扛不住压力最终撤军。关于各国援助，讲解说明阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契，中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+本次讲座由主讲人系统讲解1979年至1989年苏联入侵阿富汗战争（苏阿战争），涵盖阿富汗的地理位置、历史地位、苏联入侵前的国内形势、1979年12月24日苏联入侵过程、国际反应及十年游击战消耗，最终于1989年撤军。主讲人指出，阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，是兵家必争之地；其国土百分之九十为高原山地，易守难攻，历史上多次获得“帝国坟场”称号。苏联因担心阿富汗倒向美国而决定武力介入，以兵变形式扶植代理人卡尔迈勒上台，此举招致阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗抵抗组织，中国提供武器并传授地道战、地雷战等战法，美国援助毒刺导弹等单兵武器，有效压制苏军武装直升机。问答环节中，主讲人解答了阿富汗战略价值、石油资源、圣战者含义及帝国坟场原因等问题，并补充中国援助细节，包括提供五六式冲锋枪和半自动步枪，以及派遣专家教授兵法，但未派兵参战。
 # 核心观点与论证
-论点一：阿富汗地理位置关键，是亚洲咽喉要地，易守难攻。论据：阿富汗位于亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦，西邻伊朗，被称为亚洲的中间走廊地带，兵家必争之地；国土纵深90%为高原山地，易守难攻，被称为帝国坟场；谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-论点二：20世纪50年代阿富汗同时与苏联和西方保持友好交往，实行君主立宪制，精英与知识界奉行亲英与亲苏两头政策。论据：文化上向英国靠拢，如英国议会制度、君主立宪制度及大学现代科学的承办师从英国；国家建设和工业方面向苏联看齐；基辛格评价阿明用苏联的火柴点美国的香烟，获得墙头草称号。
-论点三：苏联出兵阿富汗的决策与过程。论据：阿明对苏联干涉内政不满并过度导向美国，苏联高层政治局决定在阿富汗彻底导向美国之前以兵变和武力介入；1979年12月24日平安夜，苏联趁阿富汗高层及军队被先前释放的清散信号麻痹，以阿富汗请求救援为说法强行派兵，从东部、中部、西部（塔吉克斯坦及土库曼斯坦方向）分路推进，一晚控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗纳入苏联阵营；此举招致阿拉伯国家、中国、西方盟国不满。
-论点四：苏联出兵是冷战思维与战略错判共同导致。论据：用冷战思维看，阿富汗被苏联视为苏联大家庭一员，根据勃列日涅夫逻辑不允许任何成员外出，如同之前出兵捷克；阿富汗是特殊战略要地，加上苏联错判，导致大的战略性失误；同时期冷战处于苏攻美守，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓。
-论点五：圣战者含义。论据：圣战者指狂烈激进的伊斯兰圣战思想，从上到下宗教式洗脑，导致阿富汗圣战者具备像二战日本军国主义荼毒下日本军民那样不顾一切、抱着同归于尽思想进行圣战。
-论点六：阿富汗难打的原因与游击战。论据：阿富汗90%为高原山地，是天然游击战地区；除喀布尔、坎大哈等主要城市外，大部分乡村实行部落长老制，各自为政，政府无控制力，列强及城市政府无法有力控制高原山地；中国帮助阿富汗圣战抵抗者教兵法（地道战、地雷战），美国援助先进单兵武器如毒刺防空火箭筒，有效压制苏联雌鹿武装直升机；坦克和步兵战车在阿富汗无法形成有效战斗力，高原山地需步兵加武装直升机；苏联基层官兵厌战，士气一落千丈，1989年从上到下扛不住压力最终撤军。
-论点七：各国对阿富汗的援助。论据：阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源共同支持阿富汗抵抗组织，进行长达十年游击战争；中国援助五六式冲锋枪和五六式半自动步枪（与AK47同型号），通过援助形式稀释已饱和的军工业，同时为抵抗苏联霸权主义与西方盟国达成秘而不宣的默契；中国主要派专家教兵法、地道战、地雷战，只提供军火没有派人。
+主讲人首先介绍阿富汗的地理位置与历史地位，指出其地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为“亚洲的中间走廊地带”，是兵家必争之地；国土百分之九十为高原山地，易守难攻，历史上多次获得“帝国坟场”称号，如第一次大英帝国入侵后被阿富汗反推回巴基斯坦地区。随后梳理苏联入侵前的国内形势：20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏两头政策，文化上向英国靠拢（如议会制度、君主立宪制度、大学现代科学），国家建设和工业方面向苏联看齐；基辛格评价当时的国王阿明“用苏联的火柴点美国的香烟”，两边要好处。苏联因阿明对苏联干涉内政不满及过度导向美国，担心阿富汗脱离掌控会使其中亚地区被动，故于1979年12月24日平安夜，以阿富汗请求苏联救援为借口，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔政府高层，处决阿明一家，扶植代理人卡尔迈勒上台，将阿富汗变为傀儡。此举招致阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗抵抗组织，形成“阿富汗和穆斯林国家出兵源，中国和西方盟国出武器与情报资源”的默契，展开长达十年的游击战争。主讲人强调，阿富汗百分之九十地区为高原山地，是天然游击战地区，除喀布尔、坎大哈等城市外，广大乡村由部落长老制控制，政府无控制力；中国传授地道战、地雷战等战法，美国援助毒刺导弹等单兵武器，有效压制苏军武装直升机（如雌鹿），而坦克和步兵战车在高原山地无法形成有效战斗力；苏联基层官兵普遍厌战，士气低落，最终于1989年撤军。
 # 金句总结
-「谁控制了阿富汗，谁就控制住了亚洲的咽喉。」——背景：在回答听众提问“阿富汗到底有啥好、为啥都想打它”时，主讲人以此说明阿富汗地理位置的关键性。
-「他是用的苏联的火柴在点的美国的香烟。」——背景：主讲人引述基辛格对阿明的评价，说明阿富汗当时同时从苏联和西方两边获取好处、被称为墙头草的外交状态。
-「阿富汗多次获得其帝国坟场的称号。」——背景：主讲人梳理历史上列强入侵阿富汗的结果，指出阿富汗国土纵深90%为高原山地、易守难攻，因而得名帝国坟场。
-「苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。」——背景：主讲人分析阿富汗高原山地地形使苏联坦克和步兵战车无法形成有效战斗力，加上基层官兵厌战、士气一落千丈，最终苏联于1989年撤军。
+“谁控制了阿富汗，谁就控制住了亚洲的咽喉。”——主讲人以此回答阿富汗的战略价值，强调其地理位置的关键性。
+“它是用的苏联的火柴在点的美国的香烟。”——主讲人引用基辛格对阿富汗国王阿明的评价，说明阿富汗在苏联与西方之间两头要好的“墙头草”状态。
 # Q&amp;A 环节
-问：阿富汗到底有啥好，为啥都想打它？
+问：阿富汗到底有啥好呀？为啥都想打它？
 答：地理位置的原因，因为谁控制了阿富汗，谁就控制住了亚洲的咽喉。
 问：是不是阿富汗有石油啊？
-答：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如说是西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
-问：为什么苏联要出兵阿富汗？
-答：用当时的冷战思维来看，阿富汗当时被苏联化为苏联势力，就是苏联大家庭中的一员，根据勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的，所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，所以加上苏联这个错判，导致苏联的大的战略性失误。同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人的进行意识形态的扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
-问：阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
-答：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式那种洗脑，然后导致了其阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民的那样一样，不顾一切的就是抱着一种同归于尽的思想进行一种圣战的方式。
+答：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+问：圣战者是什么意思？
+答：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样，不顾一切地抱着同归于尽的思想进行圣战。
 问：为什么阿富汗这个位置这么难打？
-答：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。它除了以喀布尔和坎大哈那几个主要城市为首的城市地区以外，剩下大部分百分之九十的地区都是乡村部落长老制的那种制度。你到乡村，政府没有任何的控制力，都是由部落的长老控制的该部落，然后各个村落与部落各自为政，然后导致了任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。
-问：中国对阿富汗提供了哪些援助？
-答：也是给了一些枪炮，比如说像咱们给的和AK47同样型号的五六式冲锋枪和五六式半自动步枪，也是通过这个援助的一个形式，然后我把咱们国家就是已经饱和的军工业这个产业给它稀释掉，同时也是大家为了抵抗苏联的霸权主义和西方盟国达成了一种就是秘而不宣的默契。专家派的主要就教一些兵法、地道战、地雷战这一块的，只提供军火，但是没有派人。</t>
+答：因为这个国家百分之九十都是处于高原山地地带，是天然的游击战地区；除喀布尔和坎大哈等主要城市外，大部分地区都是乡村部落长老制，政府没有任何控制力，各个村落与部落各自为政，导致任何列强及阿富汗城市政府都无法对广大高原山地形成有力控制。</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t>3129/3273</t>
+        <v>28.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3129/1583</t>
         </is>
       </c>
     </row>
@@ -15269,21 +14978,21 @@
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t># 讨论议题与背景
-本次讨论以闲聊方式展开，成员围绕日本文学、各国文学比较及《西游记》狮驼岭章节进行交流。发言人2从东野圭吾《白夜行》谈起，认为其结局阴暗、符合日本形象，并提及《菊与刀》对日本人性格的描绘；随后引导比较法国、英国、俄国、美国文学及底层书写。发言人1、发言人3、发言人4分别参与讨论，涉及雨果《悲惨世界》、狄更斯作品、契诃夫与托尔斯泰、马克·吐温与海明威等。讨论还延伸至国内《平凡的世界》、台湾电影《假如我是真的》及《西游记》狮驼岭与佛教批判，最后被发言人3叫停转入练习。
+本次会议为闲聊性质，由发言人1、发言人2、发言人3、发言人4参与，围绕各国文学展开讨论。从日本东野圭吾《白夜行》谈起，发言人1认为其叙事手法新颖、结局阴暗，发言人2引用《菊与刀》指出《白夜行》体现了日本人性格特点。随后对比法国、英国、俄国、美国文学，发言人2认为法国文学如雨果《悲惨世界》体现浪漫理想主义，法国文学多描绘底层民众，英国文学多贵族生活，发言人4认为法国文学比英国更生动，发言人2认为俄国文学更讽刺，揭露人性丑恶。发言人1提到国内底层文学因政策原因受限。最后发言人2详细解读《西游记》狮驼岭章节，认为原著揭露佛教虚伪，批判藏传佛教。
 # 发言要点
-发言人2主张《白夜行》结局阴暗、符合日本形象，并引《菊与刀》说明日本人性格；认为法国文学体现浪漫理想主义与抗争精神，俄国文学更侧重对人性丑恶的揭露与讽刺批判，美国文学历史短、叙事风格不同于欧洲，北美大平原因农业资源广阔而从未发生饥荒；还提及格罗斯曼《命运与生活》、《古拉格群岛》最早为法语版、俄语版待苏联解体后发行，以及台湾电影《假如我是真的》改编自果戈里《钦差大臣》并结合知青上山下乡与文革真实事件。发言人1认为《白夜行》叙事手法新颖、结局阴暗，法国有抗争精神，英国狄更斯作品写贵族与穷人鸿沟、底层将希望寄托于宗教或虚无之物，国内《平凡的世界》等底层作品因政策原因很多不让看，并提及《一九四二》讲大饥荒与战乱。发言人4认为法国小说描绘底层民众较多、英国多写贵族生活，俄国作品戏剧性更明显，只读过《简爱》。发言人3参与提问与附和，提及哈利波特、俄国契诃夫等。分歧点在于各国文学底层书写谁更生动、法国与俄国文学特点比较。
+发言人1：分享《白夜行》阅读感受，认为叙事手法新颖，结局阴暗；提到国内底层文学如《平凡的世界》因政策原因受限；认为英国文学如《圣诞欢歌》《雾都孤儿》也描绘底层人，体现贫富鸿沟；提到电影《一九四二》讲述大饥荒与战乱。发言人2：引用《菊与刀》指出《白夜行》体现日本人性格；认为法国文学如《悲惨世界》体现浪漫理想主义与奉献精神；认为俄国文学更讽刺，揭露人性丑恶，推荐契诃夫《变色龙》《装在套子里的人》《凡卡》及格罗斯曼《命运与生活》；详细解读《西游记》狮驼岭章节，认为原著揭露佛教虚伪，批判藏传佛教，并提到《假如我是真的》电影结合果戈里《钦差大臣》与知青上山下乡背景。发言人4：认为法国文学比英国更生动，描绘底层民众更多；提到自己只读过简爱。观点交锋点：在比较法国与俄国文学时，发言人2认为俄国文学更讽刺，发言人4认为法国文学戏剧性更明显；在讨论底层文学时，发言人1认为国内底层文学因政策受限，发言人2补充台湾电影《假如我是真的》批判大陆上山下乡时期的不公。
 # 共识形成
-小组未形成正式决议或统一意见，讨论以交流观点为主。主要共识性认识包括：**《白夜行》结局阴暗、符合日本形象**；**法国文学体现浪漫理想主义与抗争精神，描绘底层民众较多**；**俄国文学更侧重对人性丑恶的揭露与讽刺批判**；**美国历史较短、叙事风格不同于欧洲，北美大平原因农业资源广阔而从未发生饥荒**；**《西游记》狮驼岭章节中青狮、白象、大鹏三魔吃尽一国之人、距灵山约500公里，与普度众生大相径庭，吴承恩批判佛教被上层用于奴役底层**；**大鹏精是唯一能打败孙悟空的反派**。
+本次会议未形成明确共识或解决方案，主要围绕各国文学特点进行观点交流。发言人2对《西游记》狮驼岭章节的解读获得部分认同，发言人1认为该章节过于血腥和深刻，黑神话悟空未设计该章节。
 # 未决事项与分工
-需进一步探讨的问题包括：各国文学底层书写谁更生动、法国与俄国文学特点比较等未形成结论。后续任务分工未明确，讨论被发言人3叫停后转入练习。</t>
+未提及。</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
-        <is>
-          <t>5886/992</t>
+        <v>24</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5886/830</t>
         </is>
       </c>
     </row>
@@ -15353,23 +15062,23 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C54" s="0" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t># 全文摘要
-本次短会围绕手机图库项目整体进展、排期与风险展开。产品侧同步智能分类与相册推荐改版高保真原型已出V1.5版，调整了网格视图交互逻辑并对长按手势做微动效反馈，测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单。开发侧同步后端V2版识别模型已跑起来，准确率比上一代提升约88%，但因加视频帧提取功能单次请求耗时从八百毫秒涨到约一点五秒；云相册同步断点续传在弱网下状态机紊乱，同步队列积压到一千张以上时部分机型OOM崩溃（尤其iOS），已加分片加载每次只拉五十张；缩略图渲染换新解码库后内存占用降约百分之三十、CPU占用上升，主流三款机型灰度帧率稳定六十帧、低端机约五十帧。会议明确异步推送不做，采用本地CQLite缓存层方案，端侧加轻量级预过滤过滤gif或截图后再走全量云端识别、平均耗时压一半，首次使用下载做成按需加载；后台同步权限审核严大概率下不了，先按分片加载方案走但进度不能拖；批量删除照片数据库锁死的临时规避先稳住、正式修复排进V1.2迭代；时间轴预加载改动可以、注意别跟云同步模块抢资源；AI修图本次不硬塞，PRD先写接口逻辑和UI占位、开发侧做插件化架构预留，非核心UI微调往后排、资源给到管线重构和AI标签优化。排期方面，里程碑按原定计划月底封版，内测包暂定下周三发并拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表、开发两位准备日志抓取工作；周四性能评审要求拿达标数据，性能报告iOS和安卓对比数据分开列、测试组合并成一份总览，产品经理下午两点参加UI走查并要求提前发稿。
-## 产品侧交互迭代与用户反馈
-- 智能分类和相册推荐改版，高保真原型出V1.5版，调整网格视图交互逻辑，长按手势做微动效反馈；测试反馈部分低端机上滑列表偶尔掉帧，已与开发2沟通，考虑降低预览图缩放级别换帧；用户调研吐槽隐私相册入口太深，建议下一版提到首部顶部二级菜单，产品经理评估范围变更。
-- 隐私相册入口提上去没问题，不算大改动，产品出交互方案由产品经理评审；掉帧问题得抓紧，下周要进性能压测。
-## AI智能标签接口与多模态识别模型部署
-- 后端已把V2版识别模型跑起来，准确率比上一代提升约88%；因加视频帧提取功能，单次请求耗时从八百毫秒涨到约一点五秒；产品侧认为异步推送不行，用户点开相册没实时结果会觉得卡死，提出先做本地缓存策略，开发1认为可行，本地加CQLite缓存层，下午拉分支改逻辑，预计三天联调完，缓存命中率低仍需回溯；产品经理提出端侧轻量级预过滤，过滤gif或截图后再走全量云端识别，平均耗时压一半；端侧跑可能需再申请两百兆本地缓存空间，产品评估安装包体积影响，安装包加两三百兆问题不大，但首次使用下载体验做成按需加载，开发1认为按需下载没问题，用现有资源下发模块，大概两天搞定。</t>
+会议围绕手机图库项目进展、排期与潜在风险展开对齐。产品侧推进智能分类与相册推荐改版，高保真原型V1.5版调整网格视图交互与长按微动效；测试反馈低端机上滑列表掉帧，已与开发2沟通降低预览图缩放级别。用户反馈隐私相册入口太深，决定上提至首部顶部二级菜单，产品经理出交互方案评审。技术侧同步多项优化：后端V2识别模型准确率提升88%，但视频帧提取致单次请求耗时从800ms涨至1.5s，决定采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完；端侧预过滤方案可行，需评估模型体积与推理开销，并申请200MB本地缓存空间。云同步模块弱网下状态机紊乱，同步队列积压超1000张时部分机型OOM崩溃，已加分片加载机制每次拉50张，但拖慢进度；后台同步权限审核严大概率下不了，先按分片加载方案走，进度不能拖。缩略图渲染用新解码库将JPEG硬解换软解，内存占用降30%但CPU上升，主流三款车型灰度帧率稳定60帧，低端机50帧；批量删除照片触发回收站重建索引致数据库锁死，临时规避用消息队列排队，正式修复排进V1.2迭代。时间轴滑动到老照片卡死三秒以上，因EXIF解析耗时与磁盘IO瓶颈，开发1准备加本地索引预加载，最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，互不影响，需用户授权媒体和存储权限，产品设计引导弹窗。AI修图快捷入口本次不硬塞，PRD中预留接口逻辑和UI占位，开发侧做插件化架构，后端接口做成标准RESTful加Swagger文档；非核心UI微调往后排，资源给到管线重构和AI标签优化。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表，开发准备日志抓取。
+## 产品交互迭代与用户反馈
+- 产品侧推进智能分类和相册推荐改版，高保真原型V1.5版调整网格视图交互和长按微动效。测试反馈低端机上滑列表掉帧，已与开发2沟通降低预览图缩放级别。用户反馈隐私相册入口太深，决定上提至首部顶部二级菜单，产品经理出交互方案评审。
+- AI智能标签接口与性能优化：后端V2识别模型准确率提升88%，但视频帧提取致单次请求耗时从800ms涨至1.5s，决定采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完；端侧预过滤方案可行，需评估模型体积与推理开销，并申请200MB本地缓存空间。云同步与内存管理：弱网下状态机紊乱，同步队列积压超1000张时部分机型OOM崩溃，已加分片加载机制每次拉50张，但拖慢进度；后台同步权限审核严大概率下不了，先按分片加载方案走，进度不能拖。缩略图渲染与性能评审：用新解码库将JPEG硬解换软解，内存占用降30%但CPU上升，主流三款车型灰度帧率稳定60帧，低端机50帧；批量删除照片触发回收站重建索引致数据库锁死，临时规避用消息队列排队，正式修复排进V1.2迭代。时间轴视图加载优化：滑动到老照片卡死三秒以上，因EXIF解析耗时与磁盘IO瓶颈，开发1准备加本地索引预加载，最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，互不影响，需用户授权媒体和存储权限，产品设计引导弹窗。
+## 项目里程碑与后续计划
+- AI修图快捷入口本次不硬塞，PRD中预留接口逻辑和UI占位，开发侧做插件化架构，后端接口做成标准RESTful加Swagger文档；非核心UI微调往后排，资源给到管线重构和AI标签优化。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表，开发准备日志抓取。</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>3605/1201</t>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3605/1499</t>
         </is>
       </c>
     </row>
@@ -15453,23 +15162,23 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C55" s="0" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t># 全文摘要
-本次月度研讨会围绕上月案场数据复盘与下月去化目标展开。上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面。会议确认工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干；周末办业主答谢会，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练，每人必须参加、课后现场抽考，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房；财务和法务周六日轮流值班、在案场外围待命。下月总去化目标120套，拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。散会后半小时内，销售组长把会议纪要和任务分解表发到工作群；销冠下周晨会分享逼定案例。
-## 上月案场数据复盘与客户流失抗性分析
-- 上月案场总到访320组，环比增15%；成交76套，转化率23%，较上月27%下降；渠道带看占比65%，自然来访35%；蓄客约3200组，认购到成交流失率约18%，整体量够但卡在逼定和转化环节。
-- 流失客户抗性集中在价格预期（竞品推特价房、首付分期、送物业费）和交付信心（园林选材、地下车库层高、外墙保温层）两方面；客户怕买错，需把工地实时进展、材料样板拉到面前看。
-## 下月去化目标与执行动作
-- 下月总去化目标120套，按人员配置和上月产出权重拆分：销冠28套，销售A、销售B加组长共50套，剩余12套作为机动和渠道攻坚储备。工地开放日标准化定在每周三、提前两天在CRM系统推送意向客户，由组长出方案；下月起渠道带看必须实名登记并有明确需求标签，否则扣减渠道积分，渠道部由总监沟通；现场物料本周出新版，下月做权益可视化台卡；跟进节奏提速、客户不过夜、分片包干，组长带销售A和销售B回访上周未成交三百多组，销冠梳理二十几个高意向客户周末逼定；周末办业主答谢会，销冠带人协助、销售B主抓流程、销售A负责邀约和逼定记录，邀约话术统一为老业主专属品鉴宴；本周安排两次专项演练（竞品对比与抗性化解、逼定时机与谈判心理学），每人必须参加、课后现场抽考、过不了加练，结果挂钩下周绩效系数；销控必须实时同步、群里喊一声并CRM锁房，再出问题直接问责；财务和法务周六日轮流值班、在案场外围待命；散会后半小时内，销售组长把会议纪要和任务分解表发到工作群，销冠下周晨会分享逼定案例。</t>
+本次月度研讨会聚焦上月转化率下滑问题，分析原因为价格预期与交付信心两大抗性，并制定下月去化120套的具体行动方案。上月案场总到访320组，环比增15%，成交76套，转化率23%，较上月降1个百分点；渠道带看占比65%，自然来访35%，蓄客量3200组，认购到成交流失率18%。会议确定多项动作：工地开放日标准化，定于每周三下午，提前两天在CRM系统推送意向客户；逼定采用'算总账'与'权益可视化'策略，更新逼定函物料；渠道带看自下月起实行实名制并需明确需求标签，质量不达标扣减渠道积分；周末举办业主答谢会，统一话术为'老业主专属品鉴宴'，财务和法务周六日轮流值班在案场外围待命。下月总去化目标120套，拆分方案为：销冠28套，组长、销售A、销售B三人一组共50套，剩余12套作为机动和渠道攻坚储备。本周安排两次专项培训（'竞品对比与抗性化解'和'逼定时机与谈判心理学'），每人必须参加，课后抽考，过不了加练；销控必须实时同步，CRM系统锁房，专人每小时刷新销控大屏，违规问责。
+## 上月数据复盘与转化率问题分析
+- 上月案场总到访320组，环比增15%，成交76套，转化率23%，较上月降1个百分点；渠道带看占比65%，自然来访35%，蓄客量3200组，认购到成交流失率18%。销冠复盘流失客户集中在价格预期和交付信心两大抗性；销售A反馈工地开放日频率不够，流程繁琐，报备审批要半天。结论为量够但转化不足，卡在逼定和转化环节，需提升自主拓客和案场拦截能力。
+- 工地开放日标准化，定于每周三下午，提前两天在CRM系统推送意向客户；逼定采用'算总账'与'权益可视化'策略，更新逼定函物料，明确权益条款；渠道带看自下月起实行实名制并需明确需求标签，质量不达标扣减渠道积分；周末举办业主答谢会，统一话术为'老业主专属品鉴宴'，财务和法务周六日轮流值班在案场外围待命。
+## 下月目标拆分与任务分配
+- 集团下月总去化目标120套，比上月多50%。拆分方案为：销冠28套，组长、销售A、销售B三人一组共50套，剩余12套作为机动和渠道攻坚储备。销售A手头有15个准客户等认筹通知，销售B计划通过老带新和自然来访突破。本周安排两次专项培训（'竞品对比与抗性化解'和'逼定时机与谈判心理学'），每人必须参加，课后抽考，过不了加练；销控必须实时同步，CRM系统锁房，专人每小时刷新销控大屏，违规问责。</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>4211/1165</t>
+        <v>61.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4211/1001</t>
         </is>
       </c>
     </row>
@@ -15543,23 +15252,23 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C56" s="0" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议围绕上周ASR模型迭代进度、线上推理延迟与长音频解码卡死问题展开，A与B分别同步数据训练与推理侧现状。数据侧混合语料库清洗流水线跑完第二轮，长尾噪音、极端口音与背景人声重叠片段单独分流，有效语音时长占比从89%提升到94%左右，重新校对CTC blank token分布后发现多音字与连读场景切分点偏，本周用新基准跑消融；验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时易吞过渡音或重复解码。模型侧计划将全纯Transformer换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练，RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线与压测数据未跑完，明天下午发压力测试日志和截图。推理侧现有队列切分导致首字延迟波动在150ms到300ms之间，计划改为静态分段加流式解码组合方案，音频按2秒切块、前端VAD预过滤、后端RNN-T增量解码，首字延迟控制在80ms以内、吞吐量稳在120路并发，VAD阈值卡在-25dB并结合能量与谱熵双模型判断，下周拉线上流量回放做端到端对比。长音频卡死问题方面，线上用户输入超长连续且带方言口音音频导致解码loop卡死、解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题。组长提出三点要求：流式架构切换不能影响现有非流式离线批处理，双线都要保、测试用例覆盖全；VAD阈值由B做消融实验，误切率与漏切率画曲线找最优解；A的模型训练算力下周一开始划拨三块A100做增量训练，注意别和NLP组项目撞车、排队看调度面板错峰跑。会议明确稳定性优先、精度次之，下周先出热修复版本上灰度，专业术语后续做词表扩展和热词注入；CI/CD自动评估流水线由A负责评估脚本与流水线配置、预计三天周四前出V1版本，B配合把压测数据输出成标准JSON格式；监控面板接Prometheus和Grafana，B出监控指标定义文档明天下班前发组长转发运维负责人，告警分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。
-## 数据与模型训练进展
-- 混合语料库数据清洗流水线跑完第二轮，长尾噪音、极端口音和背景人声重叠片段单独分流，有效语音时长占比从89%提到94%左右；重新校对CTC blank token分布，发现多音字和连读场景切分点偏，本周用新基准跑消融。验证集WER降约0.8个点，但低资源语言混合边界场景切分有毛刺，中英文切换时模型易吞过渡音或重复解码，排查为CTC对齐阶段跨语言边界和轻声尾音处理不够平滑。
-- 计划把全纯Transformer换成流式RNN-T和Transformer混合形态，先在20小时核心数据上训练；数据增强加时间偏移，对背景白噪声和混响鲁棒性差，准备引入MixUp和Cut再迭代。RNN-T prefix LM缓存做INT8量化配合动态缓存释放，预计压30%显存占用，具体显存曲线和压测数据未跑完，明天下午发压力测试日志和截图。
-## 推理优化与线上稳定性
-- 现有队列切分导致首字延迟波动在150ms到300ms之间，产品反馈体验不连贯；计划改成静态分段加流式解码组合方案，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，首字延迟控制在80ms以内，吞吐量稳在120路并发；VAD阈值卡在-25dB，结合能量和谱熵双模型判断，下周拉线上流量回放做端到端对比。线上用户输入超长连续且带方言口音音频导致解码loop卡死，解码器陷入无效循环并致服务器节点重启，默认max steps为2048个token、超时5秒，部分音频解码序列超阈值且解码器未做优雅降级直接报OOM，日志显示RNN-T attention权重一直震荡没收敛；建议加early stopping机制，连续30步置信度低于0.2强制截断并返回当前序列，可解决90%以上卡死问题，同时加超时熔断和降级返回。前端SDK采样率仍为16k而新模型为32k输入，前端不升级上采样会引入高频伪影影响识别率，前端对接人称排期推到下个月，32k模型在长尾词上比16k好0.5%的WER。</t>
+会议围绕ASR模型迭代进度、线上推理延迟和长音频卡死问题展开，确认了流式RNN-T混合架构、2秒切分方案、VAD阈值消融、热修复版本及监控面板建设等多项决策，并明确了各负责人和时间节点。数据清洗流水线完成第二轮，有效语音时长占比从89%提升至94%，WER下降0.8个点；低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音被吞或重复解码。计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，在20小时核心数据上训练，并引入MixUp和Cut数据增强。推理侧将动态Batching改为静态分段加流式解码，2秒切块，VAD预过滤，RNN-T增量解码，首字延迟控制在80ms以内，吞吐量120路并发；VAD阈值卡在-25dB，需平衡误切率和漏切率，计划拉线上流量回放做端到端对比。长音频卡死问题确认加early stopping机制，连续30步置信度低于0.2强制截断，B负责改解码逻辑，A配合长序列数据配比和边界用例验证，下周出热修复版本上灰度。
+## ASR模型迭代与数据优化
+- 数据清洗流水线完成第二轮，有效语音时长占比从89%提升至94%，WER下降0.8个点；低资源语言混合边界场景存在切分毛刺，中英文切换时过渡音被吞或重复解码。计划将全纯Transformer架构改为流式RNN-T和Transformer混合形态，在20小时核心数据上训练，并引入MixUp和Cut数据增强。
+- 推理侧将动态Batching改为静态分段加流式解码，2秒切块，VAD预过滤，RNN-T增量解码，首字延迟控制在80ms以内，吞吐量120路并发；VAD阈值卡在-25dB，需平衡误切率和漏切率，计划拉线上流量回放做端到端对比。
+## 长音频卡死与稳定性修复
+- 长音频卡死问题确认加early stopping机制，连续30步置信度低于0.2强制截断，B负责改解码逻辑，A配合长序列数据配比和边界用例验证，下周出热修复版本上灰度。</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
-        <is>
-          <t>3912/1826</t>
+        <v>51.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3912/836</t>
         </is>
       </c>
     </row>
